--- a/salf/丙種職業安全衛生業務主管題庫.xlsx
+++ b/salf/丙種職業安全衛生業務主管題庫.xlsx
@@ -483,7 +483,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I1404"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.45" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.45"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="55" customWidth="1" min="2" max="2"/>
@@ -982,14 +982,10 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>答案是 以上皆是。
-依據《職業安全衛生法》第 2 條第 1 款規定，「工作者」的定義包含：
-勞工：指受僱從事工作獲致工資者。
-自營作業者：指獨立從事勞動或技藝工作獲致報酬，且未僱用有酬人員幫同工作者。
-其他受工作場所負責人指揮或監督從事勞動之人員：如派遣工、技術生或接受職業訓練等人員。</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="n"/>
+          <t>為何顯示此頁 我們的系統偵測到您的電腦網路送出的流量有異常情況。這頁是為了確認要求確實出自您本人，不是由自動程式發出。為什麼會發生這種情況？ IP 位址：203.72.21.238 時間：2026-09-21T06:28:06Z 網址：</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr"/>
     </row>
     <row r="13" ht="92.59999999999999" customHeight="1">
       <c r="A13" s="2" t="n">

--- a/salf/丙種職業安全衛生業務主管題庫.xlsx
+++ b/salf/丙種職業安全衛生業務主管題庫.xlsx
@@ -483,7 +483,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I1404"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.45"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.45" outlineLevelCol="0"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="55" customWidth="1" min="2" max="2"/>
@@ -1281,12 +1281,10 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>動力堆高機為中央主管機關（勞動部）依《職業安全衛生法施行細則》第12條指定公告之機械。
-臺中市總工業會
-根據《職業安全衛生法》第7條規定，對於中央主管機關指定之機械、設備或器具，其構造、性能及防護未符合安全標準者，不得產製運出廠場、輸入、租賃、供應或設置。選項中的鍋爐、升降機雖屬危險性機械或設備，但在此條文規定的源頭及供應流向管理中，專門被點名列入安全標準與張貼標示規範的為「動力堆高機」（與動力衝剪機械、研磨機等同屬第7條之指定品項）。</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="n"/>
+          <t>為何顯示此頁 我們的系統偵測到您的電腦網路送出的流量有異常情況。這頁是為了確認要求確實出自您本人，不是由自動程式發出。為什麼會發生這種情況？ IP 位址：36.236.220.100 時間：2026-09-21T06:30:23Z 網址：</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr"/>
     </row>
     <row r="20" ht="108.9" customHeight="1">
       <c r="A20" s="2" t="n">
@@ -1322,13 +1320,10 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>依職業安全衛生法規定，雇主設置動力衝剪機械應符合中央主管機關所定防護標準。
-相關法規重點
-正確選項：動力衝剪機械。
-其他規定：起重機、升降機等則屬於「具有危險性之機械」，需依規定辦理檢查或代檢，而符合中央主管機關所定安全構造與防護標準（如機械設備器具安全標準）指定的項目則包含動力衝剪機械、手推刨床、木材加工用圓盤鋸、動力堆高機等。</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="n"/>
+          <t>為何顯示此頁 我們的系統偵測到您的電腦網路送出的流量有異常情況。這頁是為了確認要求確實出自您本人，不是由自動程式發出。為什麼會發生這種情況？ IP 位址：203.72.21.238 時間：2026-09-21T06:32:27Z 網址：</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr"/>
     </row>
     <row r="21" ht="77.15000000000001" customHeight="1">
       <c r="A21" s="2" t="n">
@@ -1364,7 +1359,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>為何顯示此頁 我們的系統偵測到您的電腦網路送出的流量有異常情況。這頁是為了確認要求確實出自您本人，不是由自動程式發出。為什麼會發生這種情況？ IP 位址：203.72.21.238 時間：2026-09-21T06:04:32Z 網址：</t>
+          <t>為何顯示此頁 我們的系統偵測到您的電腦網路送出的流量有異常情況。這頁是為了確認要求確實出自您本人，不是由自動程式發出。為什麼會發生這種情況？ IP 位址：203.72.21.238 時間：2026-09-21T06:34:40Z 網址：</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr"/>
@@ -1403,7 +1398,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>為何顯示此頁 我們的系統偵測到您的電腦網路送出的流量有異常情況。這頁是為了確認要求確實出自您本人，不是由自動程式發出。為什麼會發生這種情況？ IP 位址：203.72.21.238 時間：2026-09-21T06:06:04Z 網址：</t>
+          <t>為何顯示此頁 我們的系統偵測到您的電腦網路送出的流量有異常情況。這頁是為了確認要求確實出自您本人，不是由自動程式發出。為什麼會發生這種情況？ IP 位址：114.27.87.59 時間：2026-09-21T06:36:40Z 網址：</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr"/>
@@ -1442,7 +1437,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>為何顯示此頁 我們的系統偵測到您的電腦網路送出的流量有異常情況。這頁是為了確認要求確實出自您本人，不是由自動程式發出。為什麼會發生這種情況？ IP 位址：36.236.220.100 時間：2026-09-21T06:07:36Z 網址：</t>
+          <t>為何顯示此頁 我們的系統偵測到您的電腦網路送出的流量有異常情況。這頁是為了確認要求確實出自您本人，不是由自動程式發出。為什麼會發生這種情況？ IP 位址：203.72.21.238 時間：2026-09-21T06:38:49Z 網址：</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr"/>
@@ -1481,7 +1476,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>為何顯示此頁 我們的系統偵測到您的電腦網路送出的流量有異常情況。這頁是為了確認要求確實出自您本人，不是由自動程式發出。為什麼會發生這種情況？ IP 位址：203.72.21.238 時間：2026-09-21T06:09:09Z 網址：</t>
+          <t>為何顯示此頁 我們的系統偵測到您的電腦網路送出的流量有異常情況。這頁是為了確認要求確實出自您本人，不是由自動程式發出。為什麼會發生這種情況？ IP 位址：114.27.87.59 時間：2026-09-21T06:44:36Z 網址：</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr"/>
@@ -1520,7 +1515,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>為何顯示此頁 我們的系統偵測到您的電腦網路送出的流量有異常情況。這頁是為了確認要求確實出自您本人，不是由自動程式發出。為什麼會發生這種情況？ IP 位址：114.27.87.59 時間：2026-09-21T06:10:41Z 網址：</t>
+          <t>為何顯示此頁 我們的系統偵測到您的電腦網路送出的流量有異常情況。這頁是為了確認要求確實出自您本人，不是由自動程式發出。為什麼會發生這種情況？ IP 位址：203.72.21.238 時間：2026-09-21T06:46:51Z 網址：</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr"/>
@@ -1559,7 +1554,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>為何顯示此頁 我們的系統偵測到您的電腦網路送出的流量有異常情況。這頁是為了確認要求確實出自您本人，不是由自動程式發出。為什麼會發生這種情況？ IP 位址：114.27.87.59 時間：2026-09-21T06:12:13Z 網址：</t>
+          <t>為何顯示此頁 我們的系統偵測到您的電腦網路送出的流量有異常情況。這頁是為了確認要求確實出自您本人，不是由自動程式發出。為什麼會發生這種情況？ IP 位址：114.27.87.59 時間：2026-09-21T06:48:59Z 網址：</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr"/>
@@ -1598,7 +1593,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>為何顯示此頁 我們的系統偵測到您的電腦網路送出的流量有異常情況。這頁是為了確認要求確實出自您本人，不是由自動程式發出。為什麼會發生這種情況？ IP 位址：203.72.21.238 時間：2026-09-21T06:13:45Z 網址：</t>
+          <t>為何顯示此頁 我們的系統偵測到您的電腦網路送出的流量有異常情況。這頁是為了確認要求確實出自您本人，不是由自動程式發出。為什麼會發生這種情況？ IP 位址：203.72.21.238 時間：2026-09-21T06:51:03Z 網址：</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr"/>
@@ -1637,7 +1632,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>為何顯示此頁 我們的系統偵測到您的電腦網路送出的流量有異常情況。這頁是為了確認要求確實出自您本人，不是由自動程式發出。為什麼會發生這種情況？ IP 位址：203.72.21.238 時間：2026-09-21T06:15:17Z 網址：</t>
+          <t>為何顯示此頁 我們的系統偵測到您的電腦網路送出的流量有異常情況。這頁是為了確認要求確實出自您本人，不是由自動程式發出。為什麼會發生這種情況？ IP 位址：114.27.87.59 時間：2026-09-21T06:53:17Z 網址：</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr"/>
@@ -1676,7 +1671,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>為何顯示此頁 我們的系統偵測到您的電腦網路送出的流量有異常情況。這頁是為了確認要求確實出自您本人，不是由自動程式發出。為什麼會發生這種情況？ IP 位址：203.72.21.238 時間：2026-09-21T06:16:49Z 網址：</t>
+          <t>為何顯示此頁 我們的系統偵測到您的電腦網路送出的流量有異常情況。這頁是為了確認要求確實出自您本人，不是由自動程式發出。為什麼會發生這種情況？ IP 位址：36.236.220.100 時間：2026-09-21T06:58:57Z 網址：</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr"/>
@@ -1715,7 +1710,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>為何顯示此頁 我們的系統偵測到您的電腦網路送出的流量有異常情況。這頁是為了確認要求確實出自您本人，不是由自動程式發出。為什麼會發生這種情況？ IP 位址：203.72.21.238 時間：2026-09-21T06:18:21Z 網址：</t>
+          <t>為何顯示此頁 我們的系統偵測到您的電腦網路送出的流量有異常情況。這頁是為了確認要求確實出自您本人，不是由自動程式發出。為什麼會發生這種情況？ IP 位址：36.236.220.100 時間：2026-09-21T07:00:56Z 網址：</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr"/>
@@ -1754,7 +1749,7 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>為何顯示此頁 我們的系統偵測到您的電腦網路送出的流量有異常情況。這頁是為了確認要求確實出自您本人，不是由自動程式發出。為什麼會發生這種情況？ IP 位址：36.236.220.100 時間：2026-09-21T06:19:53Z 網址：</t>
+          <t>為何顯示此頁 我們的系統偵測到您的電腦網路送出的流量有異常情況。這頁是為了確認要求確實出自您本人，不是由自動程式發出。為什麼會發生這種情況？ IP 位址：203.72.21.238 時間：2026-09-21T07:03:02Z 網址：</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr"/>
@@ -1793,7 +1788,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>為何顯示此頁 我們的系統偵測到您的電腦網路送出的流量有異常情況。這頁是為了確認要求確實出自您本人，不是由自動程式發出。為什麼會發生這種情況？ IP 位址：203.72.21.238 時間：2026-09-21T06:21:25Z 網址：</t>
+          <t>為何顯示此頁 我們的系統偵測到您的電腦網路送出的流量有異常情況。這頁是為了確認要求確實出自您本人，不是由自動程式發出。為什麼會發生這種情況？ IP 位址：203.72.21.238 時間：2026-09-21T07:05:07Z 網址：</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr"/>
@@ -1832,10 +1827,10 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>結論：選2「體格檢查」。理由：本題問的是檢查主責機構。依《勞動檢查法》，勞動檢查機構負責職業安全衛生檢查，因此選「體格檢查」。 法條：《職業安全衛生法》第1、5、6、34、36、37、38、39條：規定職業安全衛生目的、雇主責任、工作場所安全衛生要求、工作守則訂定、健康檢查、職業災害通報與統計。</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="n"/>
+          <t>為何顯示此頁 我們的系統偵測到您的電腦網路送出的流量有異常情況。這頁是為了確認要求確實出自您本人，不是由自動程式發出。為什麼會發生這種情況？ IP 位址：203.72.21.238 時間：2026-09-21T07:07:12Z 網址：</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr"/>
     </row>
     <row r="34" ht="92.59999999999999" customHeight="1">
       <c r="A34" s="2" t="n">
@@ -1871,10 +1866,10 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>結論：選4「癌症篩檢」。理由：本題問的是檢查主責機構。依《勞動檢查法》，勞動檢查機構負責職業安全衛生檢查，因此選「癌症篩檢」。 法條：《職業安全衛生法》第1、5、6、34、36、37、38、39條：規定職業安全衛生目的、雇主責任、工作場所安全衛生要求、工作守則訂定、健康檢查、職業災害通報與統計。</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="n"/>
+          <t>為何顯示此頁 我們的系統偵測到您的電腦網路送出的流量有異常情況。這頁是為了確認要求確實出自您本人，不是由自動程式發出。為什麼會發生這種情況？ IP 位址：203.72.21.238 時間：2026-09-21T07:59:56Z 網址：</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr"/>
     </row>
     <row r="35" ht="92.59999999999999" customHeight="1">
       <c r="A35" s="2" t="n">

--- a/salf/丙種職業安全衛生業務主管題庫.xlsx
+++ b/salf/丙種職業安全衛生業務主管題庫.xlsx
@@ -1229,23 +1229,19 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>根據職業安全衛生法第7條及同法施行細則第12條規定，移動式起重機並非職安法第7條所稱「張貼安全標示」之指定機械、設備或器具（它是屬於第8條規定應經型式驗證合格並張貼合格標章的設備）。
-職安法第7條規定的指定對象
-依職業安全衛生法施行細則第12條所列，中央主管機關（勞動部）指定應符合安全標準並辦理資訊申報與張貼安全標示的機械、設備或器具包含：
+          <t>「移動式起重機」非職業安全衛生法第7條及同法施行細則第12條所指定的源頭管理機械、設備或器具對象（移動式起重機屬於職安法第16條規定的「危險性機械」，應經檢查合格，而非第7條的登錄與張貼安全標示對象）。
+職安法第7條指定機械、設備或器具範圍
+依職業安全衛生法施行細則第12條規定，中央主管機關指定之項目包含：
 動力衝剪機械
 手推刨床
 木材加工用圓盤鋸
 動力堆高機
-研磨機
-研磨輪
+研磨機、研磨輪
 防爆電氣設備
-動力衝剪機械之光電式安全裝置
-手推刨床之刃部接觸預防裝置
-木材加工用圓盤鋸之反撥預防裝置及鋸齒接觸預防裝置
-其他經中央主管機關指定公告者</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="n"/>
+上述相關安全裝置（如光電式安全裝置等）</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr"/>
     </row>
     <row r="19" ht="77.15000000000001" customHeight="1">
       <c r="A19" s="2" t="n">
@@ -1281,7 +1277,17 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>為何顯示此頁 我們的系統偵測到您的電腦網路送出的流量有異常情況。這頁是為了確認要求確實出自您本人，不是由自動程式發出。為什麼會發生這種情況？ IP 位址：36.236.220.100 時間：2026-09-21T06:30:23Z 網址：</t>
+          <t>本題答案為：動力堆高機。
+解析
+依據《職業安全衛生法施行細則》第12條規定，職業安全衛生法第7條第1項所稱中央主管機關指定之機械、設備或器具，包含：
+動力衝剪機械
+手推刨床
+木材加工用圓盤鋸
+動力堆高機
+研磨機、研磨輪
+防爆電氣設備
+以及相關安全裝置等
+選項中的鍋爐、升降機及電焊機雖亦為職安法規管制的危險性或重點機械/設備，但並不屬於該條文所指定、限制「未符合安全標準者不得產製運出廠場、輸入、租賃、供應或設置」的公告品目。</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr"/>
@@ -1320,7 +1326,16 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>為何顯示此頁 我們的系統偵測到您的電腦網路送出的流量有異常情況。這頁是為了確認要求確實出自您本人，不是由自動程式發出。為什麼會發生這種情況？ IP 位址：203.72.21.238 時間：2026-09-21T06:32:27Z 網址：</t>
+          <t>依職業安全衛生法規定，雇主設置動力衝剪機械應符合中央主管機關所定防護標準。
+相關法規重點
+依據：職業安全衛生法第7條第1項規定。
+應符合防護標準之機械、設備或器具包含：
+動力衝剪機械
+手推刨床
+木材加工用圓盤鋸
+動力堆高機
+研磨機、研磨輪
+其他經中央主管機關指定公告之機械、設備或器具</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr"/>
@@ -1359,7 +1374,11 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>為何顯示此頁 我們的系統偵測到您的電腦網路送出的流量有異常情況。這頁是為了確認要求確實出自您本人，不是由自動程式發出。為什麼會發生這種情況？ IP 位址：203.72.21.238 時間：2026-09-21T06:34:40Z 網址：</t>
+          <t>依據《職業安全衛生法》第7條規定，此規定不適用於勞工。
+相關法規重點
+規範對象：依職業安全衛生法規定，負有此項機械、設備或器具安全責任的對象包含製造者、輸入者、供應者或雇主（使用者）。
+不適用對象：勞工本身並非負責產製、輸入、租賃、供應或設置機具的商業或經營主體，因此不適用本條之規範。
+勞動部職業安全衛生署</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr"/>
@@ -1398,7 +1417,8 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>為何顯示此頁 我們的系統偵測到您的電腦網路送出的流量有異常情況。這頁是為了確認要求確實出自您本人，不是由自動程式發出。為什麼會發生這種情況？ IP 位址：114.27.87.59 時間：2026-09-21T06:36:40Z 網址：</t>
+          <t>答案為：驗證機構。
+依職業安全衛生法第8條第1項規定：「製造者或輸入者對於中央主管機關公告列入型式驗證之機械、設備或器具，非經中央主管機關認可之驗證機構實施型式驗證合格及張貼合格標章，不得產製運出廠場或輸入。」</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr"/>
@@ -1437,7 +1457,10 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>為何顯示此頁 我們的系統偵測到您的電腦網路送出的流量有異常情況。這頁是為了確認要求確實出自您本人，不是由自動程式發出。為什麼會發生這種情況？ IP 位址：203.72.21.238 時間：2026-09-21T06:38:49Z 網址：</t>
+          <t>依職業安全衛生法第8條規定，正確答案為：型式驗證合格及張貼合格標章。
+相關規定說明
+法源依據：依據《職業安全衛生法》第8條第1項規定，製造者或輸入者對於中央主管機關公告列入型式驗證之機械、設備或器具，非經中央主管機關認可之驗證機構實施型式驗證合格及張貼合格標章，不得產製運出廠場或輸入。
+違規罰則：若未取得合格標章擅自產製、運出或輸入，最高可依同法處高額罰鍰並得命限期回收。</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr"/>
@@ -1476,7 +1499,13 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>為何顯示此頁 我們的系統偵測到您的電腦網路送出的流量有異常情況。這頁是為了確認要求確實出自您本人，不是由自動程式發出。為什麼會發生這種情況？ IP 位址：114.27.87.59 時間：2026-09-21T06:44:36Z 網址：</t>
+          <t>提高產能速度非機械防護器具設計時之考慮要點。
+機械防護器具設計之考慮要點
+機械安全防護器具（如護罩、護圍等）的設計首重安全與維護便利性，其主要考量包含：
+堅固耐用：確保防護器具在作業環境中不易損壞或變形。
+不致造成新的危害：防護器具本身不能具有銳利邊角或引發其他安全衛生問題。
+便利檢查、調整、修護與潤滑：方便日常維護與作業，避免因維修不便而遭拆除或失效。
+而「提高產能速度」屬於生產效率與經濟效益之考量，並非安全防護器具設計時的安全要點。</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr"/>

--- a/salf/丙種職業安全衛生業務主管題庫.xlsx
+++ b/salf/丙種職業安全衛生業務主管題庫.xlsx
@@ -1719,8 +1719,14 @@
       <c r="G29" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H29" s="2" t="n"/>
-      <c r="I29" s="2" t="n"/>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>事業單位勞工人數在 50 人以上者，應置勞工健康服務人員或委託勞工健康服務專業機構。
+正確答案為：50 人。
+依據 職業安全衛生法第 22 條 規定，事業單位勞工人數達 50 人以上時，即應配置相關醫護或健康服務人員來辦理勞工健康管理、職業病預防及健康促進等保護事項。</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr"/>
     </row>
     <row r="30" ht="92.59999999999999" customHeight="1">
       <c r="A30" s="2" t="n">
@@ -1754,8 +1760,13 @@
       <c r="G30" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H30" s="2" t="n"/>
-      <c r="I30" s="2" t="n"/>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>雇主對於新進勞工施行的「體格檢查」，依現行法規並未強制規定由哪一方負擔，實務上是由勞資雙方自行協商決定的。因此選項應為「沒有規定」（或由雙方議定），與在職勞工的「健康檢查」強制由雇主負擔不同。
+勞動部職業安全衛生署</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr"/>
     </row>
     <row r="31" ht="92.59999999999999" customHeight="1">
       <c r="A31" s="2" t="n">
@@ -1789,8 +1800,20 @@
       <c r="G31" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H31" s="2" t="n"/>
-      <c r="I31" s="2" t="n"/>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>心電圖檢查為非規定之一般體格檢查項目。
+刷題王
+說明
+依據台灣現行《勞工健康保護規則》之規定，雇主僱用勞工時應實施之「一般體格檢查」項目包含：
+既往病歷及作業經歷之調查
+胸部 X 光（大片）攝影檢查
+血色素及白血球數檢查
+其他如身高、體重、視力、色盲、聽力、血壓、尿液檢查及生化檢查（肝腎功能、膽固醇等）
+心電圖檢查並非新進勞工一般體格檢查的法定必做項目。</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr"/>
     </row>
     <row r="32" ht="92.59999999999999" customHeight="1">
       <c r="A32" s="2" t="n">

--- a/salf/丙種職業安全衛生業務主管題庫.xlsx
+++ b/salf/丙種職業安全衛生業務主管題庫.xlsx
@@ -483,7 +483,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I1404"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.45"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.45" outlineLevelCol="0"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="55" customWidth="1" min="2" max="2"/>
@@ -1847,8 +1847,15 @@
       <c r="G32" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H32" s="2" t="n"/>
-      <c r="I32" s="2" t="n"/>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>雇主於僱用勞工時，應實施之健康檢查為一般體格檢查。
+相關法規與目的
+一般體格檢查：依據《職業安全衛生法》第20條規定，雇主於僱用勞工時，應施行一般體格檢查。
+檢查目的：主要為識別勞工的工作適性，評估其身體健康狀況與體能是否適合從事該項作業，以避免分派不適任的工作。</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr"/>
     </row>
     <row r="33" ht="92.59999999999999" customHeight="1">
       <c r="A33" s="2" t="n">
@@ -1882,8 +1889,17 @@
       <c r="G33" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H33" s="2" t="n"/>
-      <c r="I33" s="2" t="n"/>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>體格檢查非屬雇主對在職勞工應實施之健康檢查。
+相關法規說明
+依據《職業安全衛生法》第20條規定：
+體格檢查：是雇主於僱用勞工時（新進人員）所實施的檢查。
+在職勞工健康檢查：包含「一般健康檢查」、「從事特別危害健康作業者之特殊健康檢查」以及「經中央主管機關指定為特定對象及特定項目之健康檢查」。
+NDHU</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr"/>
     </row>
     <row r="34" ht="92.59999999999999" customHeight="1">
       <c r="A34" s="2" t="n">
@@ -1917,8 +1933,19 @@
       <c r="G34" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H34" s="2" t="n"/>
-      <c r="I34" s="2" t="n"/>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>答案是：癌症篩檢。
+Quizlet
+依據《職業安全衛生法》第20條規定，雇主對在職勞工應實施的健康檢查包含：
+一般健康檢查
+特殊健康檢查（從事特別危害健康作業者）
+特定對象及特定項目之健康檢查（經中央主管機關指定公告者）
+清華大學衛生保健組 因此，癌症篩檢非屬法規強制雇主應對在職勞工實施的項目。
+Quizlet</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr"/>
     </row>
     <row r="35" ht="92.59999999999999" customHeight="1">
       <c r="A35" s="2" t="n">
@@ -1952,8 +1979,12 @@
       <c r="G35" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H35" s="2" t="n"/>
-      <c r="I35" s="2" t="n"/>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>Google AI 摘要未抓取到，請手動補充。</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr"/>
     </row>
     <row r="36" ht="92.59999999999999" customHeight="1">
       <c r="A36" s="2" t="n">
@@ -1987,8 +2018,16 @@
       <c r="G36" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H36" s="2" t="n"/>
-      <c r="I36" s="2" t="n"/>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>這題的正確答案是 以上皆是（在過去舊法或部分考古題題庫中，選項 A、B、C 分別對應舊規或免檢標準的年齡週期描述）。
+不過需特別注意，依據現行最新《勞工健康保護規則》第17條規定，在職勞工一般健康檢查的定期實施頻率實為：
+未滿40歲者：每3年檢查1次
+40歲以上未滿60歲者：每2年檢查1次
+年滿60歲以上者：每年檢查1次</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr"/>
     </row>
     <row r="37" ht="92.59999999999999" customHeight="1">
       <c r="A37" s="2" t="n">
@@ -2022,8 +2061,15 @@
       <c r="G37" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H37" s="2" t="n"/>
-      <c r="I37" s="2" t="n"/>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>依據職業安全衛生法（原勞工安全衛生法）第17條規定，勞工工作場所之建築物，應由依法登記開業之建築師設計。
+正確答案為：(C) 建築師。
+相關法規重點
+法條依據：職業安全衛生法第17條明定，勞工工作場所之建築物，應由依法登記開業之建築師依建築法規及該法有關安全衛生之規定設計。</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr"/>
     </row>
     <row r="38" ht="77.15000000000001" customHeight="1">
       <c r="A38" s="2" t="n">
@@ -2057,8 +2103,22 @@
       <c r="G38" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H38" s="2" t="n"/>
-      <c r="I38" s="2" t="n"/>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>依職業安全衛生法第34條規定，正確答案為 勞工代表。
+祐昕技術顧問
+雇主應依該法規會同勞工代表訂定適合其需要之安全衛生工作守則，報經勞動檢查機構備查後，公告實施。
+祐昕技術顧問
+需要查詢安全衛生工作守則的訂定內容或相關規定嗎？
+應備內容（依施行細則）
+罰則資訊
+線上申辦方式
+祐昕技術顧問
+安全衛生工作守則是什麼？一定要訂嗎？ - 祐昕技術顧問
+依《職業安全衛生法》第34 條，雇主應依職安法及相關規定，會同勞工代表訂定適合其需要的安全衛生工作守則，報經勞動檢查機構備查後，公告實施。工作守則是事業單位安全衛生管理的「基本法」，內容通常涵蓋各級人員權責、設備維護與檢查、工作安全衛生標準、教育訓練、急救與搶... 內容</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr"/>
     </row>
     <row r="39" ht="108" customHeight="1">
       <c r="A39" s="2" t="n">
@@ -2092,8 +2152,21 @@
       <c r="G39" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H39" s="2" t="n"/>
-      <c r="I39" s="2" t="n"/>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>直接答案：(D) 只要合理即可不需考慮其可行性 是錯誤的敘述。
+錯誤原因解析
+選項 (D) 錯誤：訂定安全衛生工作守則時，必須考量實際作業環境的可行性與合宜性，不能只講求合理卻無法執行。
+正確做法：依據職業安全衛生法第34條，雇主應會同勞工代表訂定適合需要的守則，報經勞動檢查機構備查後公告實施，且安全衛生最終屬於雇主責任，不得轉嫁。
+相關法規重點
+訂定主體：雇主應會同勞工代表訂定。
+主管機關：報經勞動檢查機構備查（非認可或核准）後公告實施。
+法律效力：效力及於在職之全體勞工。
+責任歸屬：屬於雇主法規責任，不得轉嫁給勞工。
+行動學習網</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr"/>
     </row>
     <row r="40" ht="92.59999999999999" customHeight="1">
       <c r="A40" s="2" t="n">
@@ -2127,8 +2200,23 @@
       <c r="G40" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H40" s="2" t="n"/>
-      <c r="I40" s="2" t="n"/>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>答案是：環境汙染預防。
+說明
+依據《職業安全衛生法施行細則》規定，安全衛生工作守則的內容應參照下列事項訂定：
+taipei.ardswc.gov.tw
+事業之安全衛生管理及各級之權責。
+機械、設備或器具之維護及檢查。
+工作安全及衛生標準。
+教育及訓練。
+急救及搶救。
+健康指導及管理措施。
+其他有關安全衛生事項。
+臺北市勞動檢查處 「環境汙染預防」屬於環境保護（環保法規）的範疇，並非職業安全衛生法規中規定的安全衛生工作守則內容。</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr"/>
     </row>
     <row r="41" ht="92.59999999999999" customHeight="1">
       <c r="A41" s="2" t="n">
@@ -2162,8 +2250,19 @@
       <c r="G41" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H41" s="2" t="n"/>
-      <c r="I41" s="2" t="n"/>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>「應報經地方主管機關備查」是錯誤的規定。
+依據《職業安全衛生法》第34條第1項規定，安全衛生工作守則的正確程序為：雇主應依本法及有關規定會同勞工代表訂定適合其需要之安全衛生工作守則，報經勞動檢查機構（檢查機構）備查後，公告實施，而非報經地方主管機關備查。
+臺北市政府全球資訊網
+正確規定摘要
+訂定依據：應依職業安全衛生法及有關規定訂定適合其需要。
+參與人員：應會同勞工代表訂定。
+呈報與實施：應報經勞動檢查機構備查後，再公告實施。
+臺北市政府全球資訊網</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr"/>
     </row>
     <row r="42" ht="92.59999999999999" customHeight="1">
       <c r="A42" s="2" t="n">
@@ -2197,8 +2296,13 @@
       <c r="G42" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H42" s="2" t="n"/>
-      <c r="I42" s="2" t="n"/>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>依據職業安全衛生法第34條規定，制定安全衛生工作守則並無僱用勞工人數的限制，只要有僱用勞工就必須訂定。因此選項中的 1 人、5 人、15 人、30 人皆非正確的門檻限制（法定規定只要有雇用勞工即應訂定，不限人數）。若以常見的國家考試或測驗題庫標準來看，通常此類法規對安全衛生工作守則的適用是「只要有僱用勞工（即 1 人以上）」即須辦理。
+臺北市勞動檢查處</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr"/>
     </row>
     <row r="43" ht="77.15000000000001" customHeight="1">
       <c r="A43" s="2" t="n">
@@ -2232,8 +2336,17 @@
       <c r="G43" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H43" s="2" t="n"/>
-      <c r="I43" s="2" t="n"/>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>事業單位所訂安全衛生工作守則經報請勞動檢查機構備查並公告實施後，效力及於在職之全體勞工。
+正確答案
+效力及於在職之全體勞工
+重點解析
+法源依據：依據《職業安全衛生法》第34條規定，雇主應會同勞工代表訂定安全衛生工作守則，報經檢查機構備查後公告實施，在職全體勞工均有切實遵行的義務。
+效力範圍：該守則經合法公告後即具有強制性與事業單位內規之效力，不以個別勞工事後同意與否為限，因此全體在職勞工皆受其拘束。</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr"/>
     </row>
     <row r="44" ht="92.59999999999999" customHeight="1">
       <c r="A44" s="2" t="n">
@@ -2267,8 +2380,17 @@
       <c r="G44" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H44" s="2" t="n"/>
-      <c r="I44" s="2" t="n"/>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>依據職業安全衛生法第34條規定，雇主應會同勞工代表訂定適合其需要之安全衛生工作守則，報經勞動檢查機構備查後，公告實施。因此正確答案為「安全衛生工作守則」。
+各項措施處理方式對照
+安全衛生工作守則：需會同勞工代表訂定，並報請勞動檢查機構備查後公告實施。
+職業安全衛生管理計畫：依事業規模與性質訂定，主要係留存廠場內紀錄以備查，無須全面事先報請勞檢機構備查。
+勞工體格檢查結果：由實施檢查之醫療機構通報中央主管機關備查，或由雇主保存紀錄。
+新僱勞工安全衛生教育訓練：依法辦理並留存訓練紀錄備查。</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr"/>
     </row>
     <row r="45" ht="92.59999999999999" customHeight="1">
       <c r="A45" s="2" t="n">
@@ -2302,8 +2424,18 @@
       <c r="G45" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H45" s="2" t="n"/>
-      <c r="I45" s="2" t="n"/>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>依職業安全衛生法施行細則規定，第一優先為由工會推派。
+相關法規規定（職業安全衛生法施行細則第43條）
+依據 職業安全衛生法施行細則 第43條，勞工代表的產生方式依優先順序如下：
+第一優先：事業單位設有工會者，由工會推派之。
+第二優先：無工會組織而有勞資會議者，由勞方代表推選之。
+第三優先：無工會組織且無勞資會議者，由勞工共同推選之。
+勞動部職業安全衛生署</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr"/>
     </row>
     <row r="46" ht="92.59999999999999" customHeight="1">
       <c r="A46" s="2" t="n">
@@ -2337,8 +2469,14 @@
       <c r="G46" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H46" s="2" t="n"/>
-      <c r="I46" s="2" t="n"/>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>依現行《職業安全衛生法》第40條規定，雇主未提供必要安全衛生設備致發生勞工死亡職業災害，最高可處 5年 以下有期徒刑。正確選項為 5年。
+(註：過去舊法規定為3年以下有期徒刑，立法院三讀修正並經總統公布後，已將刑期上限提高至5年，併科罰金最高新臺幣150萬元)。
+傑報人力資源服務集團</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr"/>
     </row>
     <row r="47" ht="92.59999999999999" customHeight="1">
       <c r="A47" s="2" t="n">
@@ -2372,8 +2510,16 @@
       <c r="G47" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H47" s="2" t="n"/>
-      <c r="I47" s="2" t="n"/>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>依職業安全衛生法規定，勞工如不接受職業安全衛生教育訓練者，處新台幣 3,000 元以下罰鍰（題目文字因辨識或錯別字誤植為戰鈴、戰鍰等）。
+國立臺北藝術大學 相關法源依據
+法規義務：依職業安全衛生法第32條第3項規定，勞工對雇主辦理之安全衛生教育訓練，有接受之義務。
+處罰規定：若勞工不接受，依同法第46條規定，處新台幣 3,000元以下罰鍰。
+臺北市勞動檢查處</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr"/>
     </row>
     <row r="48" ht="92.59999999999999" customHeight="1">
       <c r="A48" s="2" t="n">
@@ -2407,8 +2553,12 @@
       <c r="G48" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H48" s="2" t="n"/>
-      <c r="I48" s="2" t="n"/>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>勞工不遵守安全衛生工作守則之處罰，由當地主管機關處罰（通常依《職業安全衛生法》相關規定處以罰鍰）。</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr"/>
     </row>
     <row r="49" ht="108" customHeight="1">
       <c r="A49" s="2" t="n">
@@ -2442,8 +2592,21 @@
       <c r="G49" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H49" s="2" t="n"/>
-      <c r="I49" s="2" t="n"/>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>本題敘述有誤的選項為：「為實施勞動檢查，必要時得告知事業單位有關勞工申訴人身分」（即選項 C）。
+說明與法規依據
+正確觀念（主管機關必須嚴守秘密）：
+依據《勞動基準法》第74條規定，主管機關或檢查機構對於申訴人之身分資料應「嚴守秘密，不得洩漏足以識別申訴人身分之資訊」。因此，實施勞動檢查時，絕對不得告知事業單位有關勞工申訴人的身分，以保護吹哨者免受報復。
+傑報人力資源服務集團
+其他選項解析：
+事業單位不得對勞工申訴人終止勞動契約：雇主不得因勞工申訴而予解僱等處分，違者無效。
+勞動檢查機構受理勞工申訴必須保密：主管機關與檢查機構負有法定保密義務。
+任何情況下，事業單位都不得有不利勞工申訴人之行為：依勞基法第74條，雇主不得對申訴人為解僱、降調、減薪或其他不利處分。
+Blogger.com</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr"/>
     </row>
     <row r="50" ht="77.15000000000001" customHeight="1">
       <c r="A50" s="2" t="n">
@@ -2477,8 +2640,25 @@
       <c r="G50" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H50" s="2" t="n"/>
-      <c r="I50" s="2" t="n"/>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+敘述有誤的選項為：「不得分別提起訴願、異議」。
+正確觀念解析
+可分別或單獨提起：事業單位對勞動檢查結果通知書如有不服，可以依《勞動檢查法施行細則》第21條規定單獨於10日內提出異議，亦可依《訴願法》規定單獨於30日內提起訴願。因此「不得分別」的敘述是錯誤的。
+104 職場力 正確救濟途徑：
+異議：於通知書送達之次日起 10 日內，以書面述明理由向勞動檢查機構提出。
+訴願：於通知書送達之次日起 30 日內，繕具訴願書經由勞檢機關向其上級機關（或裁處機關）提出。
+併提：受檢單位也可以選擇同時併提訴願及異議。
+104 職場力
+勞動檢查系列- 雇主須注意勞檢後勞檢機關的「書面通知」
+2019年12月8日 — 於該通知書送達之次日起30日內,繕具訴願書經由勞檢機關向其上級機關提出訴願;亦可依勞動檢查法施行細則第21條規定
+第21 條 - 勞動部-條文內容
+事業單位對勞動檢查機構所發檢查結果通知書有異議時,應於通知書送達之次日起十日內,以書面敘明理由向勞動檢查機構提出。
+顯示全部 內容</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr"/>
     </row>
     <row r="51" ht="92.59999999999999" customHeight="1">
       <c r="A51" s="2" t="n">
@@ -2512,8 +2692,17 @@
       <c r="G51" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H51" s="2" t="n"/>
-      <c r="I51" s="2" t="n"/>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>該事業單位如有不服，得向勞動部提起訴願。
+解析
+原處分機關：依《勞動檢查法》規定，當地的勞動檢查機構（如勞動部職業安全衛生署所屬分署，或委由地方政府勞動檢查機構）執行職安法裁罰時，其處分權或督導上級機關歸屬中央主管機關。在此題庫標準答案中，經當地檢查機構處分不服時，其訴願管轄機關為中央主管機關即勞動部。
+（註：若原處分機關為勞動部本身，其直屬上級機關則為行政院，但本題敘述為「經當地檢查機構予以罰鍰處分」，故向其上級主管機關勞動部提起訴願。）
+Threads
+·chenthen</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr"/>
     </row>
     <row r="52" ht="108" customHeight="1">
       <c r="A52" s="2" t="n">
@@ -2547,8 +2736,17 @@
       <c r="G52" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H52" s="2" t="n"/>
-      <c r="I52" s="2" t="n"/>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>工作場所有立即發生危險之虞時，雇主或工作場所負責人未即令停止作業並使勞工退避至安全場所，依職業安全衛生法規定，其罰則為處 1 年以下有期徒刑、拘役或科或併科新台幣 18 萬元以下罰金。
+新北市政府電子法規查詢系統
+相關法規重點
+觸犯法條：職業安全衛生法第 18 條第 1 項。
+刑事罰則：依同法第 41 條第 1 項第 2 款規定處罰；若為法人犯前項之罪，除處罰其負責人外，對該法人亦科以該項罰金。
+新北市政府電子法規查詢系統</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr"/>
     </row>
     <row r="53" ht="92.59999999999999" customHeight="1">
       <c r="A53" s="2" t="n">
@@ -2582,8 +2780,13 @@
       <c r="G53" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H53" s="2" t="n"/>
-      <c r="I53" s="2" t="n"/>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>依據現行《職業安全衛生法》第27條及第43條規定，事業單位與承攬人分別僱用勞工共同作業時，若未依規定設置協議組織，處新台幣 3萬元以上30萬元以下 罰鍰（註：依最新修法及罰則調整，部分舊法或舊題庫常呈現 3 萬元以上 30 萬元以下之選項）。
+因此，正確選項為：3 萬元以上 30 萬元以下。</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr"/>
     </row>
     <row r="54" ht="92.59999999999999" customHeight="1">
       <c r="A54" s="2" t="n">
@@ -2617,8 +2820,16 @@
       <c r="G54" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H54" s="2" t="n"/>
-      <c r="I54" s="2" t="n"/>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>依據《職業安全衛生法》第43條規定，規避、妨礙或拒絕主管機關或勞動檢查機構所為之檢查、調查、抽驗、市場查驗或查核者，處新台幣 3萬元以上30萬元以下 罰鍰。
+相關規定重點
+法源依據：《職業安全衛生法》第43條。
+裁罰金額：新台幣 3萬元以上30萬元以下。
+臺北市政府全球資訊網</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr"/>
     </row>
     <row r="55" ht="92.59999999999999" customHeight="1">
       <c r="A55" s="2" t="n">
@@ -2652,8 +2863,15 @@
       <c r="G55" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H55" s="2" t="n"/>
-      <c r="I55" s="2" t="n"/>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>依職業安全衛生法規定，違反危險性機械或設備操作人員應經認可訓練或檢定合格之規定，雇主應處新台幣 3 萬元以上 30 萬元以下罰鍰。
+相關法規重點
+規範依據：依據職業安全衛生法第24條規定，經中央主管機關指定具有危險性之機械或設備操作人員，雇主應僱用經中央主管機關認可之訓練或經技能檢定合格之人員充任之。
+罰則內容：若雇主未依規定僱用合格操作人員，依同法相關罰則規定，處新臺幣 3 萬元以上 30 萬元以下罰鍰。</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr"/>
     </row>
     <row r="56" ht="108" customHeight="1">
       <c r="A56" s="2" t="n">
@@ -2687,8 +2905,16 @@
       <c r="G56" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H56" s="2" t="n"/>
-      <c r="I56" s="2" t="n"/>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>答案是 新台幣 5~300 萬元以下罰鍰。
+💡 法律依據解析
+通報義務：根據《職業安全衛生法》第 37 條第 2 項規定，事業單位工作場所發生重大職業災害時，雇主應於 8 小時內 通報勞動檢查機構。
+律點通 罰則修正：依據最新修正通過並施行的《職業安全衛生法》第 43 條第 2 款規定，違反第 37 條第 2 項通報義務者，罰鍰額度已提高至處 新臺幣 5 萬元以上 300 萬元以下罰鍰（過去舊制為新台幣 3~30 萬元）。
+請確認這份考題所適用的法規版本（若是過往歷史考古題，舊答案可能為 3~30 萬元，但依最新現行法規標準，正確答案已全面調高為 5~300 萬元）。</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr"/>
     </row>
     <row r="57" ht="108" customHeight="1">
       <c r="A57" s="2" t="n">
@@ -2722,8 +2948,22 @@
       <c r="G57" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H57" s="2" t="n"/>
-      <c r="I57" s="2" t="n"/>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>依《職業安全衛生法》規定，答案是：移動式起重機超過規定使用期間未經再檢查而繼續使用而發生死亡職業災害。
+相關法條解析
+移動式起重機未經再檢查而繼續使用，且發生死亡職業災害：
+依據《職業安全衛生法》第 40 條第 1 項規定，雇主違反第 16 條第 1 項（危險性機械或設備未經檢查合格，或超過規定使用期間未經再檢查合格而繼續使用），致發生第 37 條第 2 項第 1 款之災害（發生死亡職業災害）者，處 五年以下有期徒刑、拘役或科或併科新臺幣三十萬元以下罰金。
+其他選項之處罰規定
+雇主僱用勞工時未施行體格檢查：
+違反第 20 條第 1 項，依第 45 條第 1 款規定，處新臺幣 3 萬元以上 15 萬元以下罰鍰。
+未設置安全衛生組織或管理人員：
+違反第 23 條第 1 項，依第 45 條第 1 款規定，處新臺幣 3 萬元以上 15 萬元以下罰鍰。
+未對勞工施以從事工作必要之安全衛生教育訓練：
+違反第 32 條第 1 項，依第 45 條第 1 款規定，處新臺幣 3 萬元以上 15 萬元以下罰鍰。</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr"/>
     </row>
     <row r="58" ht="92.59999999999999" customHeight="1">
       <c r="A58" s="2" t="n">
@@ -2757,8 +2997,17 @@
       <c r="G58" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H58" s="2" t="n"/>
-      <c r="I58" s="2" t="n"/>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>依職業安全衛生法規定，參加工會非屬勞工之義務（(A) 參加工會）。
+詳細說明
+參加工會：屬於勞工依《工會法》享有的權利與自由，並非《職業安全衛生法》所規定的勞工法定義務。
+接受健康檢查：依職安法第20條規定，勞工有接受健康檢查之義務。
+接受安全衛生教育訓練：依職安法第32條規定，勞工有接受安全衛生教育訓練之義務。
+遵守安全衛生工作守則：依職安法相關規定，勞工有遵守工作守則之義務。</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr"/>
     </row>
     <row r="59" ht="92.59999999999999" customHeight="1">
       <c r="A59" s="2" t="n">
@@ -2792,8 +3041,14 @@
       <c r="G59" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H59" s="2" t="n"/>
-      <c r="I59" s="2" t="n"/>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>勞工不遵守工作守則之處罰，是由雇主處分。
+說明
+雇主：工作守則是由雇主依法訂定並公告實施的內部規範。勞工若未遵守，雇主得依工作規則進行內部懲處（如記過、警告等），因此處分主體為雇主。</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr"/>
     </row>
     <row r="60" ht="92.59999999999999" customHeight="1">
       <c r="A60" s="2" t="n">
@@ -2827,8 +3082,15 @@
       <c r="G60" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H60" s="2" t="n"/>
-      <c r="I60" s="2" t="n"/>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>實施職業安全衛生檢查的機構為勞動檢查機構。
+相關說明
+勞動檢查機構：依據《勞動檢查法》設置，專責執行職場安全衛生、勞動條件等監督檢查。
+職權分工：包含勞動部職業安全衛生署所屬的職業安全衛生中心，以及授權地方政府設立的勞動檢查處等專責單位。</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr"/>
     </row>
     <row r="61" ht="77.15000000000001" customHeight="1">
       <c r="A61" s="2" t="n">
@@ -2862,8 +3124,13 @@
       <c r="G61" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H61" s="2" t="n"/>
-      <c r="I61" s="2" t="n"/>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>答案為：勞動場所。
+依據《職業安全衛生法》第2條規定，所稱之勞動場所，係指於勞動契約存續中，由雇主所提示，使勞工履行契約提供勞務之場所；自營作業者實際從事勞動之場所；及其他受工作場所負責人指揮或監督從事勞動之人員，實際從事勞動之場所。</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr"/>
     </row>
     <row r="62" ht="92.59999999999999" customHeight="1">
       <c r="A62" s="2" t="n">
@@ -2897,8 +3164,16 @@
       <c r="G62" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H62" s="2" t="n"/>
-      <c r="I62" s="2" t="n"/>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>勞動場所中，接受雇主或代理雇主指示處理有關勞工事務之人所能支配、管理之場所稱之為工作場所。
+依據《職業安全衛生法》第2條規定：
+勞動場所：指勞工履行契約提供勞務、自營作業或受指揮監督實際從事勞動之場所。
+工作場所：指勞動場所中，接受雇主或代理雇主指示處理有關勞工事務之人所能支配、管理之場所。
+作業場所：指工作場所中，從事特定工作目的之場所。</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr"/>
     </row>
     <row r="63" ht="92.59999999999999" customHeight="1">
       <c r="A63" s="2" t="n">
@@ -2932,8 +3207,15 @@
       <c r="G63" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H63" s="2" t="n"/>
-      <c r="I63" s="2" t="n"/>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>從事特定工作目的之場所，屬於作業場所。
+依據台灣《職業安全衛生法》相關法規與定義：
+作業場所：指工作場所中，從事特定工作目的之場所。
+工作場所：指勞動場所中，接受雇主或代理雇主指示處理有關勞工事務之人所能支配、管理之場所。</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr"/>
     </row>
     <row r="64" ht="108" customHeight="1">
       <c r="A64" s="2" t="n">
@@ -2967,8 +3249,17 @@
       <c r="G64" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H64" s="2" t="n"/>
-      <c r="I64" s="2" t="n"/>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>工作場所有立即發生危險之虞時，雇主或工作場所負責人應優先採取下令停止作業，使其退避至安全場所。
+相關法規與處置重點
+依據《職業安全衛生法》第18條規定：
+雇主責任：工作場所有立即發生危險之虞（如大量化學品外洩、走山崩塌、爆炸火災危機等）時，雇主或工作場所負責人應即令停止作業，並使勞工退避至安全場所。
+iPEDIA 百科 勞工退避權：勞工若執行職務發現有立即發生危險之虞時，在不危及其他工作者安全的情形下，也能自行停止作業及退避至安全場所，並立即向直屬主管報告。
+保障措施：雇主不得因勞工行使上述退避權而予以解僱、調職、不給付停工期間工資或其他不利處分。</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr"/>
     </row>
     <row r="65" ht="92.59999999999999" customHeight="1">
       <c r="A65" s="2" t="n">
@@ -3002,8 +3293,15 @@
       <c r="G65" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H65" s="2" t="n"/>
-      <c r="I65" s="2" t="n"/>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>依職業安全衛生法施行細則之規定，事業單位之職業安全衛生管理，由雇主或對事業具有管理權限之雇主代理人綜理，由事業各部門主管負執行之責。
+長榮高中
+正確答案為：事業各部門主管。
+長榮高中</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr"/>
     </row>
     <row r="66" ht="92.59999999999999" customHeight="1">
       <c r="A66" s="2" t="n">
@@ -3037,8 +3335,20 @@
       <c r="G66" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H66" s="2" t="n"/>
-      <c r="I66" s="2" t="n"/>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>依《職業安全衛生法施行細則》第 33 條規定，安全衛生人員包括：職業安全衛生業務主管、職業安全管理師、職業衛生管理師及職業安全衛生管理員。因此，不包括「施工架組配作業主管」（或作業主管系列）。
+相關法規重點
+依據：《職業安全衛生法施行細則》第 33 條
+包含人員：
+職業安全衛生業務主管
+職業安全管理師
+職業衛生管理師
+職業安全衛生管理員
+作業主管（如施工架組配作業主管、營造作業主管等）屬於特定作業安全管理之指揮、監督人員，並非本條所稱之專職/專責安全衛生管理規劃人員。</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr"/>
     </row>
     <row r="67" ht="108" customHeight="1">
       <c r="A67" s="2" t="n">
@@ -3072,8 +3382,24 @@
       <c r="G67" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H67" s="2" t="n"/>
-      <c r="I67" s="2" t="n"/>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>勞工保險被保險人因執行職務而致傷病審查準則非屬職業安全衛生法之附屬法規。
+Quizlet
+詳細說明
+勞工保險被保險人因執行職務而致傷病審查準則：此係依據勞工保險條例授權訂定之法規，屬於勞工保險相關法規，而非職業安全衛生法之附屬法規。
+職業安全衛生設施規則、起重升降機具安全規則及有機溶劑中毒預防規則：皆為依據《職業安全衛生法》之授權所訂定之安全衛生附屬法規。
+Quizlet
+需要複習其他職業安全衛生法相關法規考題嗎？
+勞工健康保護規則
+職業安全衛生教育訓練規則
+危險性機械及設備安全檢查規則
+Quizlet
+甲業題庫單詞卡 - Quizlet
+下列何者非屬職業安全衛生法之附屬法規？ 1.起重升降機具安全規則 2.勞工健康保護規則 3.危險性機械及設備安全檢查規則 4.職工福利委員會組織準則. 4.職工福利委員會組織準則. 下列何者非屬職業安全衛生法及附屬法規？ 1.勞工保險被保險人因執行職務和致傷病... 內容</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr"/>
     </row>
     <row r="68" ht="92.59999999999999" customHeight="1">
       <c r="A68" s="2" t="n">
@@ -3107,8 +3433,18 @@
       <c r="G68" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H68" s="2" t="n"/>
-      <c r="I68" s="2" t="n"/>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>高壓氣體勞工安全規則屬勞動部（前身為行政院勞工委員會）主管之職業安全衛生法規。
+法規主管機關對照
+高壓氣體勞工安全規則：依《職業安全衛生法》授權訂定，屬勞動部主管。
+公共危險物品及可燃性高壓氣體設置標準暨安全管理辦法：依《消防法》授權訂定，屬內政部（消防署）主管。
+加氣站設置管理規則：依《石油管理法》授權訂定，屬經濟部主管。
+常壓液態罐槽車罐槽體檢驗及管理辦法：依《消防法》或相關公路監理／危險物品運輸規定辦理，非勞動部主管之職安法規。
+消防法令查詢系統</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr"/>
     </row>
     <row r="69" ht="108" customHeight="1">
       <c r="A69" s="2" t="n">
@@ -3142,8 +3478,18 @@
       <c r="G69" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H69" s="2" t="n"/>
-      <c r="I69" s="2" t="n"/>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>依《職業安全衛生法》第30條第2項規定，雇主不得使分娩後（產後）未滿一年之女性勞工從事下列危險性或有害性工作：
+礦坑工作
+鉛及其化合物散布場所之工作
+鑿岩機及其他有顯著振動之工作
+一定重量以上之重物處理工作
+其他經中央主管機關規定之危險性或有害性之工作
+因此，選項中屬於產後未滿一年女工不得從事的是「鑿岩機及其他有顯著振動之作業」（題目中之「荳震機」應為「鑿岩機」之筆誤）。</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr"/>
     </row>
     <row r="70" ht="77.15000000000001" customHeight="1">
       <c r="A70" s="2" t="n">
@@ -3177,8 +3523,15 @@
       <c r="G70" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H70" s="2" t="n"/>
-      <c r="I70" s="2" t="n"/>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>依據《職業安全衛生法》第20條第2項規定，雇主執行勞工體格檢查及健康檢查，應由中央主管機關會商中央衛生主管機關認可之醫療機構之醫師為之。
+勞動部勞動力發展署全球資訊網
+因此，正確選項為：中央衛生主管機關。
+勞動部勞動力發展署全球資訊網</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr"/>
     </row>
     <row r="71" ht="92.59999999999999" customHeight="1">
       <c r="A71" s="2" t="n">
@@ -3212,8 +3565,15 @@
       <c r="G71" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H71" s="2" t="n"/>
-      <c r="I71" s="2" t="n"/>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>依據《職業安全衛生法》第30條第1項第10款規定，起重機運轉工作為雇主不得使妊娠中之女性勞工從事之危險性或有害性工作。
+法規重點
+正確選項：(D) 起重機運轉工作（依規定屬禁止妊娠中女性從事之危險性工作）。
+其他選項：文書作業、噪音作業、電子零件裝配作業均非該條明文禁止孕婦從事之項目。</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr"/>
     </row>
     <row r="72" ht="92.59999999999999" customHeight="1">
       <c r="A72" s="2" t="n">
@@ -3247,8 +3607,19 @@
       <c r="G72" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H72" s="2" t="n"/>
-      <c r="I72" s="2" t="n"/>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>依據《職業安全衛生法》第30條規定，雇主不得使妊娠中之女性勞工從事的危險性或有害性工作包含礦坑工作、鉛及其化合物散布場所之工作、異常氣壓之工作等，因此不包括者為噪音作業。
+相關法規重點
+法定禁止從事項目（部分）：
+礦坑工作
+鉛及其化合物散布場所之工作
+異常氣壓之工作
+正確選項：
+噪音作業（非《職業安全衛生法》第30條第一項明文全面禁止妊娠中女性從事的14類絕對禁止危險工作之一）</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr"/>
     </row>
     <row r="73" ht="92.59999999999999" customHeight="1">
       <c r="A73" s="2" t="n">
@@ -3282,8 +3653,21 @@
       <c r="G73" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H73" s="2" t="n"/>
-      <c r="I73" s="2" t="n"/>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>答案是：勞工代表參與（有誤）。
+重點解析
+依據《女性勞工母性健康保護實施辦法》第2條規定，母性健康保護是指對於女性勞工從事有母性健康危害之虞之工作所採取之措施，包含下列項目：
+危害評估與控制
+醫師面談指導
+風險分級管理
+工作適性安排 及其他相關措施
+選項中的「勞工代表參與」並未列在法規定義的具體保護措施項目中，因此是有誤的選項。
+女性勞工母性健康保護實施辦法 - 勞動部年5月31日 — 本辦法用詞，定義如下： 一、母性健康保護：指對於女性勞工從事有母性健康危害之虞之工作所採取之措施，包括危害評估與控制、醫師面談指導、風險分級管理、工作適性安排及其他相關措施。 二、母性健康保護期間（以下簡稱保護期間）：指雇主於得知女性勞工妊娠之日起至分娩後一年...
+顯示全部 內容</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr"/>
     </row>
     <row r="74" ht="92.59999999999999" customHeight="1">
       <c r="A74" s="2" t="n">
@@ -3317,8 +3701,18 @@
       <c r="G74" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H74" s="2" t="n"/>
-      <c r="I74" s="2" t="n"/>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>對於變更管理，非必要之採行措施為採取矯正措施。
+變更管理的必要措施
+依職業安全衛生相關法規與管理系統指引，變更管理應包含下列重點：
+實施風險評估：於修改製程、作業、設備前評估職業災害風險。
+有關人員應被告知：確保與變更有關之人員均被告知或接受訓練。
+有關文件資料應一併檢討修正：更新相關的操作程序與技術文件。
+財團法人職業災害預防及重建中心 而「採取矯正措施」通常是用於異常、稽核缺失或事故發生後的改善行動，並非變更管理程序本身的必要預防步驟。</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr"/>
     </row>
     <row r="75" ht="92.59999999999999" customHeight="1">
       <c r="A75" s="2" t="n">
@@ -3352,8 +3746,14 @@
       <c r="G75" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H75" s="2" t="n"/>
-      <c r="I75" s="2" t="n"/>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+依據勞工作業環境監測實施辦法規定，高溫作業場所應每隔 3 個月（一季）測定綜合溫度熱指數（WBGT）一次以上。
+正確答案為：3 個月。</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr"/>
     </row>
     <row r="76" ht="77.15000000000001" customHeight="1">
       <c r="A76" s="2" t="n">
@@ -3387,8 +3787,13 @@
       <c r="G76" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H76" s="2" t="n"/>
-      <c r="I76" s="2" t="n"/>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>依勞工作業環境監測實施辦法之最新修正規定，鉛作業之作業場所應每隔 6個月 測定其濃度一次以上。若勞工暴露濃度高於或等於容許濃度標準時，則應改為每3個月實施監測一次以上。
+勞工作業環境監測及暴露危害管理</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr"/>
     </row>
     <row r="77" ht="77.15000000000001" customHeight="1">
       <c r="A77" s="2" t="n">
@@ -3422,8 +3827,12 @@
       <c r="G77" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H77" s="2" t="n"/>
-      <c r="I77" s="2" t="n"/>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>依據勞工作業環境監測實施辦法之規定，粉塵危害預防標準所稱之特定粉塵作業場所，應每隔 6個月 測定其粉塵濃度一次以上。正確答案為 6個月。</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr"/>
     </row>
     <row r="78" ht="92.59999999999999" customHeight="1">
       <c r="A78" s="2" t="n">
@@ -3457,8 +3866,18 @@
       <c r="G78" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H78" s="2" t="n"/>
-      <c r="I78" s="2" t="n"/>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>依據《職業安全衛生法施行細則》第45條及《勞動部職業安全衛生諮詢會設置要點》規定，題幹所述內容多處有誤，正確的敘述僅有「由中央主管機關召開」。
+正確法規對照表
+項目	法規規定（正確）	題幹敘述（錯誤）
+委員人數	置委員 9 人至 15 人	7 人至 12 人
+委員任期	任期 2 年（期滿得續聘）	任期 3 年
+召開機關	由中央主管機關召開（正確）	由中央主管機關召開
+組成方式	由中央主管機關就勞工團體、雇主團體、職業災害勞工團體、有關機關代表及安全衛生學者專家遴聘之	各公（協）會團體推派代表組成</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr"/>
     </row>
     <row r="79" ht="92.59999999999999" customHeight="1">
       <c r="A79" s="2" t="n">
@@ -3492,8 +3911,15 @@
       <c r="G79" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H79" s="2" t="n"/>
-      <c r="I79" s="2" t="n"/>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>技術士技能檢定及發證辦法非屬職業安全衛生法之附屬法規。
+詳細說明
+技術士技能檢定及發證辦法：依據《職業訓練法》授權訂定，而非《職業安全衛生法》。
+職業安全衛生管理辦法、危險性機械及設備安全檢查規則及缺氧症預防規則：皆為依據《職業安全衛生法》授權訂定之附屬法規（安全衛生法施行細則、規則或辦法）。</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr"/>
     </row>
     <row r="80" ht="92.59999999999999" customHeight="1">
       <c r="A80" s="2" t="n">
@@ -3527,8 +3953,18 @@
       <c r="G80" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H80" s="2" t="n"/>
-      <c r="I80" s="2" t="n"/>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>廢棄物處理作業非屬該規定之特殊危害作業。
+依據現行《職業安全衛生法》（原勞工安全衛生法第19條）規定，在高溫場所工作之勞工，雇主不得使其每日工作時間超過六小時；另如異常氣壓作業、高架作業、精密作業、重體力勞動或其他對於勞工具有特殊危害之作業，亦應規定減少勞工工作時間，並在工作時間中予以適當之休息。選項中的高溫作業、精密作業、高架作業皆屬法規明列之特殊危害或應減少工作時間作業，僅「廢棄物處理作業」非屬。
+國立臺灣師範大學－環境安全衛生中心 需要查詢其他職業安全衛生法規或考古題解析嗎？
+國立臺灣師範大學－環境安全衛生中心
+高架作業相關法規 - 環境安全衛生中心
+2021年8月21日 — 第19 條. 在高溫場所工作之勞工，雇主不得使其每日工作時間超過六小時；異常氣. 壓作業、高架作業、精密作業、重體力勞動或其他對於勞工具有特殊危害. 之 ...
+顯示全部 內容</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr"/>
     </row>
     <row r="81" ht="92.59999999999999" customHeight="1">
       <c r="A81" s="2" t="n">
@@ -3562,8 +3998,13 @@
       <c r="G81" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H81" s="2" t="n"/>
-      <c r="I81" s="2" t="n"/>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>答案為：予以解雇（有誤）。
+依據現行《職業安全衛生法》（及原《勞工安全衛生法》）相關規定，當健康檢查發現或勞工因職業上原因致不能適應原有工作時，雇主應採取的正確措施包括予以醫療、變更勞工工作場所（或更換工作）、縮短其工作時間及其他適當的保護與安置措施，不得直接予以解雇。</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr"/>
     </row>
     <row r="82" ht="92.59999999999999" customHeight="1">
       <c r="A82" s="2" t="n">
@@ -3597,8 +4038,22 @@
       <c r="G82" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H82" s="2" t="n"/>
-      <c r="I82" s="2" t="n"/>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>在職業安全衛生法規中，代表雇主從事管理、指揮或監督勞工從事工作之人員係指 工作場所負責人。
+高雄市政府全球資訊網
+依據《職業安全衛生法施行細則》規定，工作場所負責人係指雇主或於該工作場所代表雇主從事管理、指揮或監督工作之人。
+高雄市政府全球資訊網
+需要解答其他職業安全衛生法規的考題嗎？
+勞工權利與義務
+安全衛生管理事項
+災害通報與調查
+高雄市政府全球資訊網
+工作場所負責人及各級主管安全衛生職責
+工作場所負責人. • 指雇主或於該工作場所代表雇主從事管理、. 指揮或監督工作者從事勞動之人(職安法施行細. 則第3條). – 職安法第2條第1款. • 工作者定義. – 第18條第1項. 內容</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr"/>
     </row>
     <row r="83" ht="92.59999999999999" customHeight="1">
       <c r="A83" s="2" t="n">
@@ -3632,8 +4087,12 @@
       <c r="G83" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H83" s="2" t="n"/>
-      <c r="I83" s="2" t="n"/>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>Google AI 摘要未抓取到，請手動補充。</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr"/>
     </row>
     <row r="84" ht="92.59999999999999" customHeight="1">
       <c r="A84" s="2" t="n">
@@ -3667,8 +4126,12 @@
       <c r="G84" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H84" s="2" t="n"/>
-      <c r="I84" s="2" t="n"/>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>職業安全衛生教育訓練規則係依職業安全衛生法之第32條規定所訂。</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr"/>
     </row>
     <row r="85" ht="77.15000000000001" customHeight="1">
       <c r="A85" s="2" t="n">
@@ -3702,8 +4165,19 @@
       <c r="G85" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H85" s="2" t="n"/>
-      <c r="I85" s="2" t="n"/>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+火災爆炸危害等級非化學品分級管理據以評估健康危害風險等級之項目。
+說明
+化學品分級管理（Control Banding，簡稱 CCB）是用來評估健康危害風險的工具，其評估項目主要包含：
+健康危害分類
+散布狀況（或稱散布情況、逸散程度）
+使用量
+而「火災爆炸危害等級」屬於物理性或安全危害的範疇，不包含在健康危害風險分級的評估項目中。</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr"/>
     </row>
     <row r="86" ht="92.59999999999999" customHeight="1">
       <c r="A86" s="2" t="n">
@@ -3737,8 +4211,18 @@
       <c r="G86" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H86" s="2" t="n"/>
-      <c r="I86" s="2" t="n"/>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>依職業安全衛生法規定，事業單位應依其規模、性質，訂定 職業安全衛生管理計畫。
+tainan.ardswc.gov.tw
+相關規定重點
+法源依據：依據《職業安全衛生法》第23條及《職業安全衛生管理辦法》規定，雇主應依事業單位規模與性質訂定管理計畫，並設置安全衛生組織、人員以實施安全衛生管理。
+臺北市勞動檢查處 規模差異：
+勞工人數 30 人以下：得以安全衛生管理執行紀錄或文件代替。
+勞工人數 100 人以上：除管理計畫外，應另訂定「職業安全衛生管理規章」。</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr"/>
     </row>
     <row r="87" ht="92.59999999999999" customHeight="1">
       <c r="A87" s="2" t="n">
@@ -3772,8 +4256,13 @@
       <c r="G87" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H87" s="2" t="n"/>
-      <c r="I87" s="2" t="n"/>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>依職業安全衛生法第23條及相關規定，雇主應依其事業單位之規模及性質，以訂定職業安全衛生管理計畫。因此正確選項為 性質（選項 D）。
+勞動部職業安全衛生署</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr"/>
     </row>
     <row r="88" ht="92.59999999999999" customHeight="1">
       <c r="A88" s="2" t="n">
@@ -3807,8 +4296,16 @@
       <c r="G88" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H88" s="2" t="n"/>
-      <c r="I88" s="2" t="n"/>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>職業安全衛生管理計畫總共有 16項 項目。
+社團法人中華民國技能發展協會
+不過，若以題目給予的選項（4項、8項、15項、24項）來對照考試題庫的標準答案，此題通常是指「職業安全衛生管理計畫表」或「指導原則」中核心具體列舉並具備考核、紀錄的前 15項 核心實施項目（第16項通常為概括性的「其他安全衛生管理措施」），因此最符合的選項為 15項。
+臺南市政府衛生局 依據相關法規與指導原則，該計畫包含工作環境危害辨識、機械設備管理、化學品管理、作業環境監測、安全評估、承攬與採購管理、作業標準、檢查巡視、教育訓練、防護具管理、健康管理、資訊運用、緊急應變、災害調查及績效評估等 15 項核心項目，外加第 16 項其他安全衛生管理措施。完整內容可參閱相關法規與說明。
+社團法人中華民國技能發展協會</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr"/>
     </row>
     <row r="89" ht="92.59999999999999" customHeight="1">
       <c r="A89" s="2" t="n">
@@ -3842,8 +4339,16 @@
       <c r="G89" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H89" s="2" t="n"/>
-      <c r="I89" s="2" t="n"/>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>依職業安全衛生管理計畫規定，對不合格品不須實施調查處理及統計分析。
+說明：
+「不合格品」的管制與統計分析屬於品質管理系統（如 ISO 9001）的範疇。
+依《職業安全衛生管理辦法》及相關規定，職業安全衛生管理計畫中須針對「職業災害、虛驚事故（事件）、影響身心健康事件」實施調查處理及統計分析。
+社團法人中華民國技能發展協會</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr"/>
     </row>
     <row r="90" ht="92.59999999999999" customHeight="1">
       <c r="A90" s="2" t="n">
@@ -3877,8 +4382,15 @@
       <c r="G90" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H90" s="2" t="n"/>
-      <c r="I90" s="2" t="n"/>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>答案為 營業績效評估。
+解析
+營業績效評估 屬於企業的商業營運與財務管理範疇，非屬職業安全衛生管理計畫所應包括的安全衛生事項。
+其他選項（虛驚事故統計、個人防護具之管理、作業環境監測）皆屬於職業安全衛生管理計畫中應規範或涵蓋的環安衛管理項目。</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr"/>
     </row>
     <row r="91" ht="92.59999999999999" customHeight="1">
       <c r="A91" s="2" t="n">
@@ -3912,8 +4424,16 @@
       <c r="G91" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H91" s="2" t="n"/>
-      <c r="I91" s="2" t="n"/>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>依據《職業安全衛生管理辦法》規定，勞工人數在 30 人以上之事業單位，應訂定職業安全衛生管理計畫。
+重點整理
+30 人以上未滿 100 人：應訂定職業安全衛生管理計畫。
+100 人以上：除應訂定職業安全衛生管理計畫外，應另訂定職業安全衛生管理規章。
+30 人以下：得以安全衛生管理執行紀錄或文件代替職業安全衛生管理計畫。</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr"/>
     </row>
     <row r="92" ht="92.59999999999999" customHeight="1">
       <c r="A92" s="2" t="n">
@@ -3947,8 +4467,14 @@
       <c r="G92" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H92" s="2" t="n"/>
-      <c r="I92" s="2" t="n"/>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>訂定職業安全衛生管理計畫時，先要確立的重點為「基本方針」（或稱計畫方針、政策）。
+重點解析
+基本方針：是最高指導原則與方向，其他細部的計畫目標、項目與期間都必須依循此方針來展開與擬定。</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr"/>
     </row>
     <row r="93" ht="108" customHeight="1">
       <c r="A93" s="2" t="n">
@@ -3982,8 +4508,21 @@
       <c r="G93" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H93" s="2" t="n"/>
-      <c r="I93" s="2" t="n"/>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>正確的敘述為：須應用規劃、實施、查核及改進等管理手法提升改善。
+各選項解析
+正確：須應用規劃、實施、查核及改進等管理手法提升改善
+職業安全衛生管理計畫必須依循 PDCA循環（Plan 規劃、Do 實施、Check 查核、Action 改進），藉此提升整體績效。
+錯誤：安全衛生目標，應交由專業團體協助訂定
+安全衛生目標與計畫應由事業單位依自身規模與性質自行訂定並諮詢員工意見，而非全權交由外部專業團體。
+錯誤：應藉由持續不斷的稽核制度發現問題，並等有經費再行採取糾正措施
+發現問題後應即時採取矯正及預防措施，不能消極地「等有經費再做」。
+錯誤：計畫之內容應一致，無須考量規模、性質
+職業安全衛生管理計畫與規章之內容必須配合各單位的規模與性質來量身打造，並非千篇一律。</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr"/>
     </row>
     <row r="94" ht="92.59999999999999" customHeight="1">
       <c r="A94" s="2" t="n">
@@ -4017,8 +4556,16 @@
       <c r="G94" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H94" s="2" t="n"/>
-      <c r="I94" s="2" t="n"/>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>依據《職業安全衛生管理辦法》第11條規定，職業安全衛生委員會應置委員 7 人以上。正確答案為 7 人。
+重點摘述
+法規依據：《職業安全衛生管理辦法》第11條
+人數規定：委員會置委員七人以上
+組成成員：包含雇主（當然委員）、勞工代表、各部門主管及職業安全衛生相關人員等。</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr"/>
     </row>
     <row r="95" ht="92.59999999999999" customHeight="1">
       <c r="A95" s="2" t="n">
@@ -4052,8 +4599,13 @@
       <c r="G95" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H95" s="2" t="n"/>
-      <c r="I95" s="2" t="n"/>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>依職業安全衛生管理辦法規定，職業安全衛生委員會之委員中由工會推派或勞工推選之勞工代表，應佔委員人數之三分之一以上（選項為第二個：三分之一）。
+依據《職業安全衛生管理辦法》第11條規定，事業單位設置之職業安全衛生委員會，其勞工代表應佔全體委員人數的三分之一以上。</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr"/>
     </row>
     <row r="96" ht="92.59999999999999" customHeight="1">
       <c r="A96" s="2" t="n">
@@ -4079,8 +4631,14 @@
       <c r="G96" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H96" s="2" t="n"/>
-      <c r="I96" s="2" t="n"/>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>依據職業安全衛生管理辦法第12條規定，職業安全衛生委員會應每 3 個月至少開會一次。選項為 3。
+勞動部職業安全衛生署 答案：3（即每3個月至少舉行會議一次）
+勞動部職業安全衛生署</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr"/>
     </row>
     <row r="97" ht="108" customHeight="1">
       <c r="A97" s="2" t="n">
@@ -4114,8 +4672,16 @@
       <c r="G97" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H97" s="2" t="n"/>
-      <c r="I97" s="2" t="n"/>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>應設置直接隸屬雇主之一級職業安全衛生管理單位之選項為：僱用勞工人數在 100 人以上之金屬基本工業。
+法規依據說明
+依據勞動部之職業安全衛生管理辦法規定：
+第一類事業（具顯著風險者，如「金屬基本工業」屬之）：勞工人數在 100 人以上者，應設直接隸屬雇主之專責一級管理單位。
+第二類事業：勞工人數在 500 人以上者（部分舊條文或特定條件為 300 人以上，但金融保險、廣播電視、汽車租賃不屬於 100 人以上之一級單位設置標準），應設一級管理單位。</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr"/>
     </row>
     <row r="98" ht="108" customHeight="1">
       <c r="A98" s="2" t="n">
@@ -4149,8 +4715,15 @@
       <c r="G98" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H98" s="2" t="n"/>
-      <c r="I98" s="2" t="n"/>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>依《職業安全衛生管理辦法》第2-1條規定，應設職業安全衛生管理單位的標準為：第一類事業勞工人數在 100 人以上者，應設直接隸屬雇主之專責一級管理單位；第二類事業勞工人數在 300 人以上者，應設直接隸屬雇主之一級管理單位。
+對應您列出的選項，正確的標準為：
+第一類事業之事業單位勞工人數 100 人
+第二類事業之事業單位勞工人數 300 人</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr"/>
     </row>
     <row r="99" ht="92.59999999999999" customHeight="1">
       <c r="A99" s="2" t="n">
@@ -4184,8 +4757,14 @@
       <c r="G99" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H99" s="2" t="n"/>
-      <c r="I99" s="2" t="n"/>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+依據《職業安全衛生管理辦法》規定，計算事業單位勞工人數時，包含原事業單位與共同作業之承攬商勞工人數總計達 105 人（70 + 35 = 105 人），且電子零件加工廠屬於第一類事業，人數在 100 人以上者，應設直接隸屬雇主之專責一級管理單位（即一級專責單位）。
+正確答案為：一級專責單位。</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr"/>
     </row>
     <row r="100" ht="92.59999999999999" customHeight="1">
       <c r="A100" s="2" t="n">
@@ -4219,8 +4798,14 @@
       <c r="G100" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H100" s="2" t="n"/>
-      <c r="I100" s="2" t="n"/>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>依職業安全衛生管理辦法第 5-1 條規定，對於僅須置職業安全衛生業務主管，而不須置職業安全管理師、職業衛生管理師及職業安全衛生管理員的事業單位，該業務主管之職責為規劃及推動安全衛生管理事項（具體條文明定為「擬訂、規劃、推動及查核安全衛生管理事項」）。
+選項中的正確對應職責為：
+規劃及推動安全衛生管理事項（擬訂、規劃、推動及查核）</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr"/>
     </row>
     <row r="101" ht="92.59999999999999" customHeight="1">
       <c r="A101" s="2" t="n">
@@ -4254,8 +4839,14 @@
       <c r="G101" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H101" s="2" t="n"/>
-      <c r="I101" s="2" t="n"/>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>依據職業安全衛生管理辦法第5-1條規定，對於置有職業安全衛生管理員、職業安全管理師或職業衛生管理師的事業單位，其職業安全衛生業務主管之主要職責為主管及督導安全衛生管理事項。
+主管及督導安全衛生管理事項（選項中對應為「督導安全衛生管理事項」或「主管及督導」）。
+(註：若事業單位「未」置有上述管理師或管理員，其業務主管之職責才是負責「擬訂、規劃、推動及查核」安全衛生管理事項。)</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr"/>
     </row>
     <row r="102" ht="108" customHeight="1">
       <c r="A102" s="2" t="n">
@@ -4289,8 +4880,20 @@
       <c r="G102" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H102" s="2" t="n"/>
-      <c r="I102" s="2" t="n"/>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>各級主管之職責為「依職責指揮、監督所屬執行安全衛生管理事項，並協調及指導有關人員實施」。
+依據《職業安全衛生管理辦法》第 5-1 條規定，各級主管與工作場所負責人的法規職責明確劃分如下：
+高雄市政府全球資訊網 各級主管職責
+指揮與監督：依職責指揮、監督所屬人員執行各項安全衛生管理工作。
+協調與指導：協調並指導相關作業人員正確落實安全衛生實施事項。
+其他相關職責對照
+擬訂、規劃及推動安全衛生管理事項：屬於職業安全衛生管理單位或管理師、管理員之職責。
+對雇主擬訂之安全衛生政策提出建議，並審議、協調及建議：屬於職業安全衛生委員會之職責。
+因此，選項中的第一項「依職責指揮、監督所屬執行安全衛生管理事項，並協調及指導有關人員實施」才是各級主管的正確職責。</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr"/>
     </row>
     <row r="103" ht="108" customHeight="1">
       <c r="A103" s="2" t="n">
@@ -4324,8 +4927,18 @@
       <c r="G103" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H103" s="2" t="n"/>
-      <c r="I103" s="2" t="n"/>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+依據《職業安全衛生管理辦法》第 5-1 條規定，敘述正確的選項為 (A) 職業安全衛生管理單位為擬訂、規劃、督導及推動安全衛生管理事項，並指導有關部門實施。
+各選項錯誤原因解析：
+(A) 正確：職業安全衛生管理單位之職責即為擬訂、規劃、推動及督導安全衛生管理事項，並指導有關部門實施。
+(B) 錯誤：依職權指揮、監督所屬執行安全衛生管理事項，並協調及指導有關人員實施，屬於各級主管的職責，而非職業安全衛生委員會。
+(C) 錯誤：針對雇主擬訂之安全衛生政策提出建議，並審議、協調、考核及建議安全衛生相關事項，屬於職業安全衛生委員會之職責；而管理師與管理員的職責為擬訂、規劃、推動及查核安全衛生管理事項，並指導有關部門實施。
+(D) 錯誤：工作場所負責人之職責為綜理該工作場所之安全衛生管理事項；各級主管則是依職權指揮、監督所屬執行安全衛生管理事項。</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr"/>
     </row>
     <row r="104" ht="92.59999999999999" customHeight="1">
       <c r="A104" s="2" t="n">
@@ -4359,8 +4972,20 @@
       <c r="G104" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H104" s="2" t="n"/>
-      <c r="I104" s="2" t="n"/>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>自動檢查計畫之內容包括哪些？這是一題標準的職業安全衛生法規或管理觀念選擇題。
+答案是 「以上皆是」。
+根據職業安全衛生管理辦法，一個完整的自動檢查計畫為了確保執行有效，內容通常必須全面涵蓋以下項目：
+對象：明訂哪些機械、設備或作業程序需要進行檢查。
+項目：具體列出各個設備需要檢驗的關鍵部位或安全性能。
+時間（週期）：規定檢查的頻率，例如每日、每月、每季或每年定期檢查。
+方法：定義檢查的具體手段，如目視、聽音、量測或功能測試。
+單位及人員：指定負責執行檢查的部門以及具備資格的檢查人員。
+經費：編列確保檢查與後續維修保養能順利執行所需的預算。</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr"/>
     </row>
     <row r="105" ht="92.59999999999999" customHeight="1">
       <c r="A105" s="2" t="n">
@@ -4394,8 +5019,18 @@
       <c r="G105" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H105" s="2" t="n"/>
-      <c r="I105" s="2" t="n"/>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>設備之重新檢查不是職業安全衛生管理辦法規定的自動檢查種類。
+自動檢查的種類
+依據《職業安全衛生管理辦法》規定，自動檢查主要包含以下三種：
+祐昕技術顧問
+機械設備之定期檢查
+機械、設備之重點檢查
+機械、設備之作業檢點</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr"/>
     </row>
     <row r="106" ht="92.59999999999999" customHeight="1">
       <c r="A106" s="2" t="n">
@@ -4429,8 +5064,14 @@
       <c r="G106" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H106" s="2" t="n"/>
-      <c r="I106" s="2" t="n"/>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+依據職業安全衛生管理辦法規定，自動檢查包含機械之定期檢查、設備之定期檢查、機械設備之重點檢查、機械設備之作業檢點及作業檢點。
+因此，題目中「機械、設備之不定期檢查」（或寫作不定期栓查）不是法定自動檢查之種類。</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr"/>
     </row>
     <row r="107" ht="92.59999999999999" customHeight="1">
       <c r="A107" s="2" t="n">
@@ -4464,8 +5105,15 @@
       <c r="G107" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H107" s="2" t="n"/>
-      <c r="I107" s="2" t="n"/>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>事業單位各部門提出之自動檢查執行計畫係由職業安全衛生人員彙整。
+重點解析
+正確答案：職業安全衛生人員（如職業安全衛生管理員、管理師等）。
+職責說明：依規定，職安人員主要負責擬訂、規劃及推動安全衛生管理事項，並指導有關部門實施與彙整各部門的自動檢查相關計畫。</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr"/>
     </row>
     <row r="108" ht="92.59999999999999" customHeight="1">
       <c r="A108" s="2" t="n">
@@ -4499,8 +5147,19 @@
       <c r="G108" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H108" s="2" t="n"/>
-      <c r="I108" s="2" t="n"/>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>答案是 以上皆是。
+根據《職業安全衛生管理辦法》第 80 條規定，雇主實施定期檢查、重點檢查時，應記錄下列事項並保存三年：
+檢查年月日
+檢查方法
+檢查部分
+檢查結果
+實施檢查者之姓名
+依檢查結果應採取改善措施之內容</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr"/>
     </row>
     <row r="109" ht="92.59999999999999" customHeight="1">
       <c r="A109" s="2" t="n">
@@ -4534,8 +5193,32 @@
       <c r="G109" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H109" s="2" t="n"/>
-      <c r="I109" s="2" t="n"/>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>🎯 答案：3 年
+這是一題非常高頻的職安衛考試基本題！依據台灣的《職業安全衛生管理辦法》第 12 條之 1 規定，職業安全衛生管理事項之執行應作成紀錄，並保存三年。除了管理執行紀錄外，包含自動檢查紀錄、職安衛委員會會議紀錄、變更管理與採購管理紀錄等，法規的基本要求也大多都是保存三年。
+💡 職安衛紀錄保存年限快記口訣
+在考題或實務中，大多數的「執行紀錄」與「自動檢查」都是基本款的 3 年，只有特定危害或健康檢查才會拉長喔！
+📋 3 年（基本款）：
+安全衛生管理執行紀錄
+自動檢查紀錄（定期檢查、重點檢查）
+職業安全衛生委員會會議紀錄
+教育訓練紀錄、緊急應變演練紀錄
+爵鼎企業顧問 🩺 7 年（進階健康款）： 勞工一般體格與健康檢查紀錄（依勞工健康保護規則）。
+爵鼎企業顧問
+⚠️ 10 ~ 30 年（特殊危害款）： 暴露於石綿、鉛、電離輻射等特殊危害作業的健康檢查紀錄與環境監測紀錄（例如石綿作業紀錄須保存 30 年）。
+想進一步提升答題勝率嗎？您可以挑選以下方向繼續複習：
+進行一組 3-5 題的職安法規精選歷屆試題 快閃測驗。
+瞭解法規在哪些特殊情況下，紀錄必須保存 7 年或 30 年 的必考陷阱。
+索取這章節常考的「自動檢查項目」核心重點整理。
+爵鼎企業顧問
+職災紀錄的保存與管理原則：完整指南，法規、分類
+2025年4月24日 — 職業安全衛生管理執行紀錄:依據《職業安全衛生管理辦法》第12-1條,保存三年 ・ 機械、設備、器具、物料、原料及個人防護具驗收紀錄 ・ 定期檢查、重點檢查紀錄
+顯示全部
+AI 回覆可能有誤。如需法律建議，請諮詢專業人士。 瞭解詳情</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="inlineStr"/>
     </row>
     <row r="110" ht="92.59999999999999" customHeight="1">
       <c r="A110" s="2" t="n">
@@ -4569,8 +5252,17 @@
       <c r="G110" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H110" s="2" t="n"/>
-      <c r="I110" s="2" t="n"/>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>依據現行職業安全衛生法規，實施自動檢查無僱用勞工人數的最低門檻限制（即答案選 無規定）。
+相關法規重點
+法源依據：
+依據 職業安全衛生法 第 23 條及 職業安全衛生管理辦法 第 79 條規定，只要事業單位內有使用應實施自動檢查的機械、設備或具危害性工作場所，不論員工人數多寡（即使未滿 50 人或 30 人），雇主皆須訂定自動檢查計畫並據以實施。
+人數差異的規範：
+人數多寡主要影響的是「設置安全衛生組織或置安全衛生管理人員/業務主管」的層級與專職與否，而不是「要不要做自動檢查」的條件。</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr"/>
     </row>
     <row r="111" ht="92.59999999999999" customHeight="1">
       <c r="A111" s="2" t="n">
@@ -4604,8 +5296,17 @@
       <c r="G111" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H111" s="2" t="n"/>
-      <c r="I111" s="2" t="n"/>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>雇主雇用勞工人數在 100 人以上者，應設置 (A) 甲種 職業安全衛生業務主管。
+依據台灣現行《職業安全衛生管理辦法》規定，事業單位應依勞工人數規模設置對應等級之業務主管：
+祐昕技術顧問
+未滿 30 人：應設置丙種職業安全衛生業務主管
+30 人以上未滿 100 人：應設置乙種職業安全衛生業務主管
+100 人以上：應設置甲種職業安全衛生業務主管</t>
+        </is>
+      </c>
+      <c r="I111" s="2" t="inlineStr"/>
     </row>
     <row r="112" ht="92.59999999999999" customHeight="1">
       <c r="A112" s="2" t="n">
@@ -4639,8 +5340,18 @@
       <c r="G112" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H112" s="2" t="n"/>
-      <c r="I112" s="2" t="n"/>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>雇主雇用勞工人數在 30 人以上，未滿 100 人者，應設置乙種職業安全衛生業務主管。答案為乙。
+新竹市政府勞工及青年處 相關法規標準
+依據《職業安全衛生管理辦法》及相關附表規定：
+未滿 30 人：應設置丙種職業安全衛生業務主管。
+30 人以上未滿 100 人：應設置乙種職業安全衛生業務主管（部分事業單位並需配置職業安全衛生管理員）。
+100 人以上：應設置甲種職業安全衛生業務主管。
+桃園市政府</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="inlineStr"/>
     </row>
     <row r="113" ht="92.59999999999999" customHeight="1">
       <c r="A113" s="2" t="n">
@@ -4674,8 +5385,17 @@
       <c r="G113" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H113" s="2" t="n"/>
-      <c r="I113" s="2" t="n"/>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>雇主僱用勞工人數未滿 30 人者，應設置丙種職業安全衛生業務主管。
+桃園市政府 相關法規重點
+未滿 30 人：應置丙種職業安全衛生業務主管。
+30 人以上未滿 100 人：應置乙種職業安全衛生業務主管及職業安全衛生管理員各一人。
+100 人以上未滿 300 人：應置甲種職業安全衛生業務主管。
+新竹市政府勞工及青年處</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="inlineStr"/>
     </row>
     <row r="114" ht="92.59999999999999" customHeight="1">
       <c r="A114" s="2" t="n">
@@ -4709,8 +5429,14 @@
       <c r="G114" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H114" s="2" t="n"/>
-      <c r="I114" s="2" t="n"/>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>第二類及第三類事業單位，勞工人數在 5 人以下者，應設置丁種職業安全衛生業務主管。正確選項為(D) 丁。
+依據《職業安全衛生管理辦法》第四條規定，風險屬性相對較低之第二類及第三類事業，若勞工人數在 5 人以下，雇主或其代理人僅需接受至少 6 小時的丁種職業安全衛生教育訓練並經測驗合格，即可擔任該事業單位之職業安全衛生業務主管。
+台灣省工礦安全衛生技師公會</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="inlineStr"/>
     </row>
     <row r="115" ht="92.59999999999999" customHeight="1">
       <c r="A115" s="2" t="n">
@@ -4744,8 +5470,20 @@
       <c r="G115" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H115" s="2" t="n"/>
-      <c r="I115" s="2" t="n"/>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+勞工人數未滿 30 人的公司，依《職業安全衛生管理辦法》規定，以「職業安全衛生業務主管得由該公司經營負責人擔任」為正確選項（選項 B）。
+詳細解析
+正確選項 (B)：依《職業安全衛生管理辦法》第 4 條規定，事業單位勞工人數未滿 30 人者，其應置之職業安全衛生業務主管，得由事業經營負責人或其代理人（經安全衛生教育訓練合格）擔任。
+其他選項錯誤原因：
+(A) 級別錯誤：勞工人數未滿 30 人，依法應設置丙種職業安全衛生業務主管，而非甲種（甲種適用於 100 人以上或特定規模）。
+(C) 備查規定：未滿 30 人設置之業務主管無須特別報請檢查機構備查。
+(D) 專職規定：未滿 30 人之事業單位，其業務主管得由經營負責人或代理人兼任，不強制規定為專職。
+祐昕技術顧問</t>
+        </is>
+      </c>
+      <c r="I115" s="2" t="inlineStr"/>
     </row>
     <row r="116" ht="92.59999999999999" customHeight="1">
       <c r="A116" s="2" t="n">
@@ -4779,8 +5517,16 @@
       <c r="G116" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H116" s="2" t="n"/>
-      <c r="I116" s="2" t="n"/>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>依據《職業安全衛生管理辦法》第86條規定，勞工人數在 30人 以上之事業單位，設職業安全衛生管理單位或置職業安全衛生人員時，應填具設置報備書陳報勞動檢查機構備查。正確答案為 30 人。
+勞動部職業安全衛生署 相關規定重點
+法定人數：勞工人數達 30人（含）以上。
+辦理期限：應於設置或變更後 30日內 至勞動部職業安全衛生署網站完成線上登錄及報備。
+法源法律網</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="inlineStr"/>
     </row>
     <row r="117" ht="92.59999999999999" customHeight="1">
       <c r="A117" s="2" t="n">
@@ -4814,8 +5560,13 @@
       <c r="G117" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H117" s="2" t="n"/>
-      <c r="I117" s="2" t="n"/>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>事業單位勞工人數未滿 30人 者，其應置之職業安全衛生業務主管得由事業經營負責人或其代理人擔任。正確答案為 30人。
+依據《職業安全衛生管理辦法》第4條規定，勞工人數未滿30人之事業單位，雇主或其代理人經職業安全衛生業務主管安全衛生教育訓練合格，得擔任該事業單位之職業安全衛生業務主管（通常須接受丙種或丁種業務主管訓練）。</t>
+        </is>
+      </c>
+      <c r="I117" s="2" t="inlineStr"/>
     </row>
     <row r="118" ht="92.59999999999999" customHeight="1">
       <c r="A118" s="2" t="n">
@@ -4849,8 +5600,16 @@
       <c r="G118" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H118" s="2" t="n"/>
-      <c r="I118" s="2" t="n"/>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>依法令規定，雇用勞工人數在 100 人以上之事業單位，應另訂定職業安全衛生管理規章。
+正確選項為：100 人。
+法律百科Legispedia 重點說明
+100 人以上：依法應訂定「職業安全衛生管理規章」。
+30 人以下：得以安全衛生管理執行紀錄或文件代替職業安全衛生管理計畫。</t>
+        </is>
+      </c>
+      <c r="I118" s="2" t="inlineStr"/>
     </row>
     <row r="119" ht="92.59999999999999" customHeight="1">
       <c r="A119" s="2" t="n">
@@ -4884,8 +5643,97 @@
       <c r="G119" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H119" s="2" t="n"/>
-      <c r="I119" s="2" t="n"/>
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t>，請稍後再試。
+網頁搜尋結果
+職業安全衛生管理辦法(民國115 年06 月29 日修正)
+› FLAW › FLAWDAT0202
+下列事業單位，雇主應依國家標準CNS 45001同等以上規定，建置適合該事業單位之職業安全衛生管理系統，並據以執行： 一、第一類事業勞工人數在二百人以上者。 二、第二類 ...
+缺少字詞： 依法 ‎今
+事業單位部分工作場所前已適用勞工安全衛生法
+勞動部職業安全衛生署
+› ...
+二、復以管理辦法第2條之1、第3條、第6條規定，第一類事業之事業單位勞工人數在100人以上者，應設直接隸屬雇主之專責一級管理單位，第二類事業勞工人數在300人以上者，應設 ...
+缺少字詞： 依法 ‎今 ‎建 ‎200 ‎500
+100. 依職業安全衛生管理辦法規定，第一類事業單位勞工 ...
+› item-100.+依職業安全衛生管理辦法...
+2025年4月2日 — 具體來說，以下幾種情況需要建置職業安全衛生管理系統：. 第一類事業：: 勞工人數在200人以上者。 第二類事業：: 勞工人數在500人以上者。 從事石油裂解的 ...
+缺少字詞： 今 ‎| 必須包含以下字詞： 今
+相關問題
+第一類事業單位的員工數要多少人以上?
+依規定勞工人數多少人以上,應訂定職業安全衛生管理規章？
+勞資會議30人以下要開嗎？
+事業單位勞工人數在多少人以上需要僱用或特約醫護人員辦理健康管理、職業病預防及
+網頁搜尋結果
+我的公司需要依法建置職業安全衛生管理系統嗎？
+祐昕技術顧問
+› who-must-build-oshms
+依《職業安全衛生法》第23 條及《職業安全衛生管理辦法》第12-2 條，下列事業單位應建置職業安全衛生管理系統：. 一、第一類事業勞工人數在200 人以上者；二、第二類 ...
+1 個答案
+·
+最佳解答:
+依《職業安全衛生法》第 23 條及《職業安全衛生管理辦法》第 12-2 條，下列事業單位應建置職業安全衛生管理系統： ...
+缺少字詞： 今 ‎300
+第三章職業安全衛生管理措施
+› flaw › FLAWDAT0201
+下列事業單位，雇主應依國家標準CNS 45001同等以上規定，建置適合該事業單位之 ... 一、第一類事業勞工人數在二百人以上者。 二、第二類事業勞工人數在五百人以上者。
+缺少字詞： 依法 ‎今 ‎300
+【重要快訊】職業安全衛生管理辦法修法，第一類事業需設置 ...
+宜蘭縣勞工教育協進會
+› content › 【重要快訊】職業安...
+【重要快訊】職業安全衛生管理辦法修法，第一類事業需設置職業安全衛生管理系統的人數標準從300人下修為200人 · 一、第一類事業勞工人數在二百人以上者。 · 二、第二類事業 ...
+缺少字詞： 依法 ‎今
+職業安全衛生管理辦法部分條文及第三條附表二
+新竹市政府勞工及青年處
+› uploaddowndoc
+PDF
+上規定，建置適合該事業單位之職業安全衛生管理系統，. 並據以執行：. Page 3. 3. 一、第一類事業勞工人數在二百人以上者。 二、第二類事業勞工人數在五百人以上者。 三 ...
+缺少字詞： 依法 ‎今 ‎200 ‎300
+職業安全衛生管理辦法部分條文修正條文
+輔仁大學環安衛中心
+› DownloadNewsFileServlet
+PDF
+第一類事業之事業單位勞工人數在一百人以上者，所置. 管理人員應為專職；第二類事業之事業單位勞工人數在三百. 人以上者，所置管理人員應至少一人為專職。 依前項規定所置 ...
+缺少字詞： 依法 ‎今 ‎200 ‎300
+附表一：不同事業事業單位應設置之職業安全衛生管理單位
+南投縣社會及勞動局
+› FileDownload
+PDF
+附表三：不同事業種類及規模應執行之職業安全衛生管理事項. 30 人以下之事業. 31-99 人之事業. 100 人以上之事業. 200 人以上之第一類事業. 500 人以上之第二類事業. 事業 ...
+缺少字詞： 依法 ‎今 ‎建
+其他人也搜尋了以下項目
+職業安全衛生人員設置標準
+職業安全衛生管理辦法附表一
+職業安全衛生管理人員設置
+職業安全衛生管理辦法附表二
+第一類事業單位有哪些
+公共工程職業安全衛生人員設置
+職業安全衛生法施行細則
+第一類事業單位職業安全衛生管理系統
+頁面導覽
+1
+2
+3
+4
+5
+6
+7
+8
+9
+10
+下一頁
+頁尾連結
+台灣
+708 臺南市安平區 - 根據你的 IP 位址
+- 更新位置
+說明
+提供意見
+隱私權
+服務條款</t>
+        </is>
+      </c>
+      <c r="I119" s="2" t="inlineStr"/>
     </row>
     <row r="120" ht="92.59999999999999" customHeight="1">
       <c r="A120" s="2" t="n">
@@ -4919,8 +5767,16 @@
       <c r="G120" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H120" s="2" t="n"/>
-      <c r="I120" s="2" t="n"/>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>依據《職業安全衛生管理辦法》規定，第二類事業之勞工人數在 500 人以上之事業單位，應建置職業安全衛生管理系統。
+相關規定重點
+第一類事業：勞工人數在 200 人以上者，應建置職業安全衛生管理系統。
+第二類事業：勞工人數在 500 人以上者，應建置職業安全衛生管理系統。
+正確選項：500 人。</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="inlineStr"/>
     </row>
     <row r="121" ht="92.59999999999999" customHeight="1">
       <c r="A121" s="2" t="n">
@@ -4954,8 +5810,13 @@
       <c r="G121" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H121" s="2" t="n"/>
-      <c r="I121" s="2" t="n"/>
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t>依職業安全衛生管理辦法第 12 條之二規定，第一類事業（具顯著風險者）之勞工人數達到 200 人以上時，必須建置及推動職業安全衛生管理系統。在選項中，屬於第一類事業的是水電燃氣業（如電力供應業、氣體燃料供應業等）。
+正確答案：水電燃氣業</t>
+        </is>
+      </c>
+      <c r="I121" s="2" t="inlineStr"/>
     </row>
     <row r="122" ht="108" customHeight="1">
       <c r="A122" s="2" t="n">
@@ -4989,8 +5850,15 @@
       <c r="G122" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H122" s="2" t="n"/>
-      <c r="I122" s="2" t="n"/>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>選項敘述「前項勞工人數之計算，以總機構作業勞工之人數為準」有誤。
+說明：
+依據《職業安全衛生管理辦法》第6條規定，設有總機構者，其總機構設置管理單位及管理人員時，勞工人數之計算，應包含總機構及所屬各地區事業單位作業勞工之總人數，而非僅以總機構作業勞工之人數為準。
+高雄榮民總醫院全球資訊網</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="inlineStr"/>
     </row>
     <row r="123" ht="92.59999999999999" customHeight="1">
       <c r="A123" s="2" t="n">
@@ -5024,8 +5892,16 @@
       <c r="G123" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H123" s="2" t="n"/>
-      <c r="I123" s="2" t="n"/>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t>依職業安全衛生管理辦法規定，大眾傳播業不屬第一類事業（具顯著風險者），它屬於第三類事業（具低度風險者）。
+機械設備製造業：屬第一類事業（製造業中之機械設備製造修配業）。
+電力供應業：屬第一類事業（依規定屬具顯著風險之相關能源/公用事業範圍）。
+大眾傳播業：屬第三類事業（低度風險）。
+土木工程業：屬第一類事業（營造業中之土木工程業）。</t>
+        </is>
+      </c>
+      <c r="I123" s="2" t="inlineStr"/>
     </row>
     <row r="124" ht="92.59999999999999" customHeight="1">
       <c r="A124" s="2" t="n">
@@ -5059,8 +5935,19 @@
       <c r="G124" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H124" s="2" t="n"/>
-      <c r="I124" s="2" t="n"/>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>事業單位訂定要求各級主管及管理、指揮、監督等有關人員執行與職業安全衛生有關之內部管理程序等文件稱為職業安全衛生管理規章。
+相關說明
+定義：職業安全衛生管理規章是指事業單位為防止職業災害，促進勞工安全與健康，所訂定的內部管理程序與規範。
+勞動部職業安全衛生署
+其他選項：
+公司章程：規範公司組織與營運基本事項的法律文件。
+工廠管理規則：針對工廠營運、生產秩序等所訂定的管理規範。
+施工計畫：針對工程施工方法、進度及安全措施等所擬定的具體作業計畫。</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="inlineStr"/>
     </row>
     <row r="125" ht="92.59999999999999" customHeight="1">
       <c r="A125" s="2" t="n">
@@ -5094,8 +5981,15 @@
       <c r="G125" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H125" s="2" t="n"/>
-      <c r="I125" s="2" t="n"/>
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t>依法令規定，職業安全衛生管理計畫應由雇主擬訂（訂定）。
+國立岡山高級農工職業學校 相關法規說明
+雇主責任：依據《職業安全衛生法》第23條及《職業安全衛生管理辦法》規定，雇主應依事業單位之規模、性質，訂定職業安全衛生管理計畫，並要求各級主管及負責指揮、監督之有關人員執行。
+執行方式：勞工人數在30人以下之事業單位，得以安全衛生管理執行紀錄或文件代替職業安全衛生管理計畫。</t>
+        </is>
+      </c>
+      <c r="I125" s="2" t="inlineStr"/>
     </row>
     <row r="126" ht="108" customHeight="1">
       <c r="A126" s="2" t="n">
@@ -5129,8 +6023,18 @@
       <c r="G126" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H126" s="2" t="n"/>
-      <c r="I126" s="2" t="n"/>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>有關職業安全衛生管理規章之敘述，正確的選項為：規章之結構應含制定目的、適用範圍。
+職業安全衛生管理規章重點說明
+正確選項解析：依據職業安全衛生管理規章及職業安全衛生管理計畫指導原則，規章之架構通常應包含制定目的、適用範圍、規章內容及權責單位等項目。
+其他選項錯誤原因：
+直接套用他廠規章：各事業單位規模、危害風險與作業環境不同，應依自身實際狀況訂定，不宜直接盲目套用。
+無須頒布：內部管理規章訂定後應公開頒布並讓相關人員周知與遵循。
+不可作為依據：實務上訂定規章時，組織管理經驗、職災統計及文獻資料等皆可作為重要參考與研究依據。</t>
+        </is>
+      </c>
+      <c r="I126" s="2" t="inlineStr"/>
     </row>
     <row r="127" ht="92.59999999999999" customHeight="1">
       <c r="A127" s="2" t="n">
@@ -5164,8 +6068,15 @@
       <c r="G127" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H127" s="2" t="n"/>
-      <c r="I127" s="2" t="n"/>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>選項 (D) 對員工不具有強制的規範 的敘述有誤。
+解析
+正確觀念：職業安全衛生管理規章在實質上對員工具有強制的規範，員工必須遵守，且不可違反相關法令。
+其他選項：(A)、(B)、(C) 皆為正確敘述，管理規章屬於事業單位內部管理程序文件，目的在要求執行職安衛生事項，並用以要求各級主管及管理、指揮、監督等有關人員執行。</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="inlineStr"/>
     </row>
     <row r="128" ht="92.59999999999999" customHeight="1">
       <c r="A128" s="2" t="n">
@@ -5199,8 +6110,17 @@
       <c r="G128" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H128" s="2" t="n"/>
-      <c r="I128" s="2" t="n"/>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>事業單位訂定要求各級主管及管理、指揮、監督等有關人員執行與職業安全衛生有關之內部管理程序等文件稱為職業安全衛生管理規章。
+相關名詞說明
+職業安全衛生管理規章：事業單位為防止職業災害、促進勞工安全健康，明定各級主管與管理、指揮、監督人員職責與內部程序的正式規範。
+公司章程：公司組織與營運的基本規範。
+工廠管理規則：針對工廠營運與廠務管理的規定。
+庶務規則：關於日常總務、行政雜務處理的內部行政規則。</t>
+        </is>
+      </c>
+      <c r="I128" s="2" t="inlineStr"/>
     </row>
     <row r="129" ht="92.59999999999999" customHeight="1">
       <c r="A129" s="2" t="n">
@@ -5234,8 +6154,15 @@
       <c r="G129" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H129" s="2" t="n"/>
-      <c r="I129" s="2" t="n"/>
+      <c r="H129" s="2" t="inlineStr">
+        <is>
+          <t>答案為職業安全衛生委員會。
+根據職業安全衛生管理辦法規定：
+職業安全衛生委員會：為事業單位內負責審議、協調、考核及建議職業安全衛生有關業務之組織。
+職業安全衛生管理單位：負責擬訂、規劃、推動及督導安全衛生管理事項。</t>
+        </is>
+      </c>
+      <c r="I129" s="2" t="inlineStr"/>
     </row>
     <row r="130" ht="92.59999999999999" customHeight="1">
       <c r="A130" s="2" t="n">
@@ -5269,8 +6196,13 @@
       <c r="G130" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H130" s="2" t="n"/>
-      <c r="I130" s="2" t="n"/>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>答案是 消防損失（或消防損失防阻）。
+依據《職業安全衛生管理辦法》規定，雇主應執行或規劃之職業安全衛生事項（如安全衛生資訊之蒐集及運用、防護具之管理、虛驚事故調查處理與統計等），並不包含「消防損失」。</t>
+        </is>
+      </c>
+      <c r="I130" s="2" t="inlineStr"/>
     </row>
     <row r="131" ht="92.59999999999999" customHeight="1">
       <c r="A131" s="2" t="n">
@@ -5304,8 +6236,16 @@
       <c r="G131" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H131" s="2" t="n"/>
-      <c r="I131" s="2" t="n"/>
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t>依職業安全衛生設施規則及相關自動檢查規定（《職業安全衛生管理辦法》第80條，實務上多納入自動檢查紀錄規定），雇主實施定期檢查或重點檢查應記錄並保存3年的法定事項包含：一、檢查年月日、二、檢查方法、三、檢查部分、四、檢查結果、五、實施檢查者之姓名、六、依檢查結果應採取改善措施之內容。
+因此，下列何者非屬應記錄事項：
+檢查態度
+.依職業安全衛生管理辦法規定,雇主依規定實施之定期檢查 ...
+2024年10月7日 — 190.依職業安全衛生管理辦法規定,雇主依規定實施之定期檢查表單,下列何者非屬應記錄事項? (A)檢查年月日 (B)檢查方法 (C)檢查態度 (D)檢查結果。 答案：登入後查看 統計： A(3), B(1), C(415), D(1), E(0) #33260...</t>
+        </is>
+      </c>
+      <c r="I131" s="2" t="inlineStr"/>
     </row>
     <row r="132" ht="108" customHeight="1">
       <c r="A132" s="2" t="n">
@@ -5339,8 +6279,18 @@
       <c r="G132" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H132" s="2" t="n"/>
-      <c r="I132" s="2" t="n"/>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>依《職業安全衛生管理辦法》第7條規定，職業安全衛生業務主管應可由相關主管或辦理職業安全衛生事務者選任。
+新竹市政府勞工及青年處
+正確選項為：可由相關主管或辦理職業安全衛生事務者選任。
+依據法規細節：
+選任資格：雇主應自該事業單位之相關主管或辦理職業安全衛生事務者選任之。
+營造業例外：營造業之事業單位，則應由曾受營造業職業安全衛生業務主管教育訓練合格者擔任。
+新竹市政府勞工及青年處</t>
+        </is>
+      </c>
+      <c r="I132" s="2" t="inlineStr"/>
     </row>
     <row r="133" ht="92.59999999999999" customHeight="1">
       <c r="A133" s="2" t="n">
@@ -5374,8 +6324,15 @@
       <c r="G133" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H133" s="2" t="n"/>
-      <c r="I133" s="2" t="n"/>
+      <c r="H133" s="2" t="inlineStr">
+        <is>
+          <t>依職業安全衛生管理辦法規定，事業單位置職業安全管理師或職業衛生管理師達 2 人以上者，其中至少 1 人應為職業衛生管理師。
+重點整理
+正確答案：職業衛生管理師
+法規依據：依據勞動部的《職業安全衛生管理辦法》附表規定，置職業安全（衛生）管理師二人以上者，其中至少一人應為職業衛生管理師（但於103年7月3日前已置有職業安全衛生人員者不在此限）。</t>
+        </is>
+      </c>
+      <c r="I133" s="2" t="inlineStr"/>
     </row>
     <row r="134" ht="92.59999999999999" customHeight="1">
       <c r="A134" s="2" t="n">
@@ -5409,8 +6366,17 @@
       <c r="G134" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H134" s="2" t="n"/>
-      <c r="I134" s="2" t="n"/>
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t>bc
+勞動部職業安全衛生署 依據法規
+依《職業安全衛生管理辦法》第89條之一規定，政府機關（構）因其他法規限制，得於組織修編完成前，以報經中央主管機關（勞動部）核定的職業安全衛生管理規章或職業安全衛生管理計畫替代之。
+正確選項解析
+b. 職業安全衛生管理計畫：適用時應檢附。
+c. 職業安全衛生管理規章：勞工人數在100人以上者應另訂定並檢附。</t>
+        </is>
+      </c>
+      <c r="I134" s="2" t="inlineStr"/>
     </row>
     <row r="135" ht="92.59999999999999" customHeight="1">
       <c r="A135" s="2" t="n">
@@ -5444,8 +6410,14 @@
       <c r="G135" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H135" s="2" t="n"/>
-      <c r="I135" s="2" t="n"/>
+      <c r="H135" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+依職業安全衛生管理辦法規定，答案是 檢點。
+根據《職業安全衛生管理辦法》第 50-1 條規定：「雇主對高空工作車，應於每日作業前就其制動裝置、操作裝置及作業裝置之性能實施檢點。」</t>
+        </is>
+      </c>
+      <c r="I135" s="2" t="inlineStr"/>
     </row>
     <row r="136" ht="92.59999999999999" customHeight="1">
       <c r="A136" s="2" t="n">
@@ -5479,8 +6451,13 @@
       <c r="G136" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H136" s="2" t="n"/>
-      <c r="I136" s="2" t="n"/>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>應由事業經營負責人具名陳報。
+依據《職業安全衛生管理辦法》相關規定，事業單位向勞動檢查機構陳報職業安全衛生管理單位或人員設置（或變更）報備書及相關資料時，應由事業經營負責人具名負責。</t>
+        </is>
+      </c>
+      <c r="I136" s="2" t="inlineStr"/>
     </row>
     <row r="137" ht="92.59999999999999" customHeight="1">
       <c r="A137" s="2" t="n">
@@ -5514,8 +6491,14 @@
       <c r="G137" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H137" s="2" t="n"/>
-      <c r="I137" s="2" t="n"/>
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t>依職業安全衛生管理辦法之規定，局部排氣裝置或除塵裝置於開始使用、拆卸、改裝或修理時，應實施重點檢查。
+第47 條 - 勞動部-條文內容
+雇主對局部排氣裝置或除塵裝置,於開始使用、拆卸、改裝或修理時,應依下列規定實施重點檢查: 一、導管或排氣機粉塵之聚積狀況。 內容</t>
+        </is>
+      </c>
+      <c r="I137" s="2" t="inlineStr"/>
     </row>
     <row r="138" ht="92.59999999999999" customHeight="1">
       <c r="A138" s="2" t="n">
@@ -5549,8 +6532,13 @@
       <c r="G138" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H138" s="2" t="n"/>
-      <c r="I138" s="2" t="n"/>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>依據職業安全衛生管理辦法第 12 條之 6 規定，緊急狀況預防、準備及應變之計畫及其定期實施演練之執行紀錄，應至少保存 3 年。
+正確答案為：3 年（選項 B）。</t>
+        </is>
+      </c>
+      <c r="I138" s="2" t="inlineStr"/>
     </row>
     <row r="139" ht="92.59999999999999" customHeight="1">
       <c r="A139" s="2" t="n">
@@ -5584,8 +6572,15 @@
       <c r="G139" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H139" s="2" t="n"/>
-      <c r="I139" s="2" t="n"/>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>依據《職業安全衛生管理辦法》第81條規定，雇主實施自動檢查發現有異常時，應採取立即檢修及採取必要措施。
+相關法規重點
+法規依據：職業安全衛生管理辦法第81條第二項。
+正確措施：發現異常時應立即檢修及採取必要措施，以防止機械設備危害或職業災害發生。</t>
+        </is>
+      </c>
+      <c r="I139" s="2" t="inlineStr"/>
     </row>
     <row r="140" ht="92.59999999999999" customHeight="1">
       <c r="A140" s="2" t="n">
@@ -5619,8 +6614,16 @@
       <c r="G140" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H140" s="2" t="n"/>
-      <c r="I140" s="2" t="n"/>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>依職業安全衛生管理辦法規定，第一類事業勞工人數在一百人以上時，所設置之職業安全衛生管理人員應為專職。
+正確答案為：100 人。
+重點整理
+第一類事業：勞工人數達 100 人以上者，設置的管理人員應為專職。
+第二類事業：勞工人數達 300 人以上者，所置管理人員應至少一人為專職。</t>
+        </is>
+      </c>
+      <c r="I140" s="2" t="inlineStr"/>
     </row>
     <row r="141" ht="92.59999999999999" customHeight="1">
       <c r="A141" s="2" t="n">
@@ -5654,8 +6657,86 @@
       <c r="G141" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H141" s="2" t="n"/>
-      <c r="I141" s="2" t="n"/>
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t>，請稍後再試。
+網頁搜尋結果
+509. 依職業安全衛生管理辦法規定，雇主對機械、設備實施 ...
+› item-509.++依職業安全衛生管理辦法...
+2022年12月11日 — 509. 依職業安全衛生管理辦法規定，雇主對機械、設備實施定期檢查、 重點檢查或作業檢點，應訂定下列何種計畫？ (A)災害防止計畫 (B)機械設備維修計畫 (C) ...
+200. 依職業安全衛生管理辦法規定,雇主對機械、設備實施 ...
+› item-200.+依職業安全衛生管理辦法...
+2024年10月7日 — 200. 依職業安全衛生管理辦法規定,雇主對機械、設備實施定期檢查、重點檢查或作業檢點,應訂定下列何種計畫? (A)災害防止計畫 (B)機械設備維修計畫 (C)自動 ...
+第四章自動檢查
+› flaw › FLAWDAT0201
+雇主對以動力驅動之衝剪機械，應每年依下列規定機械之一部分，定期實施檢查一次： 一、離合器及制動裝置。 二、曲柄軸、飛輪、滑塊、連結螺栓及連桿。 三、一行程一停止 ...
+缺少字詞： 災害 ‎| 必須包含以下字詞： 災害
+相關問題
+定期檢查、重點檢查、作業檢點是什麼?
+依 職業安全衛生 管理 辦法 規定 下列 哪些 機械 設備 於 開始 使用 時 須 實施 重點 檢查？
+依 職業安全衛生 管理 辦法 規定 事業單位 勞工 在 多少 人 以上 時 雇主 應 訂 定 職業安全衛生 管理 規章？
+堆高機的定期檢查項目有哪些?
+網頁搜尋結果
+國內機械設備自動檢查實務手冊
+財團法人職業災害預防及重建中心
+› files
+PDF
+2024年5月16日 — 自動檢查是事業單位針對單位內部各項機械、設備依照其性質、使用時. 間進行固定周期性檢查，依照職業安全衛生管理辦法第13 條至第85 條辦. 理，目的主要係 ...
+72 頁
+自動檢查是什麼？公司要做哪些自動檢查？
+祐昕技術顧問
+› automatic-inspection
+「自動檢查」是指事業單位自主對機械、設備及作業實施的檢查，依《職業安全衛生管理辦法》分為三大類：機械設備之定期檢查（如堆高機、起重機、鍋爐、壓力容器等依規定 ...
+缺少字詞： 防止 ‎| 必須包含以下字詞： 防止
+勞動部-條文內容
+› FLAW › FLAWDOC01
+（三）執行機械之定期檢查、設備之定期檢查及機械設備之重點檢查，應就下列事項記錄，並保存三年： 1.檢查年、月、日。 2.檢查方法。 3.檢查部分。 4.檢查結果。 5.實施 ...
+缺少字詞： 雇主 ‎災害 ‎防止
+職業安全衛生管理辦法- 勞動新知
+中華民國勞資關係協進會
+› ... › 職業安全衛生法規
+2020年5月3日 — 第20 條雇主對移動式起重機，應每年就該機械之整體定期實施檢查一次。 雇主對前項移動式起重機、應每月依下列規定定期實施檢查一次： 一、過捲預防裝置、 ...
+學工安】：職業安全衛生實務：自動檢查與安衛管理措施📌 前言
+Facebook · 工安百科
+超過 150 個回應 · 6 年前
+1️⃣ 定期檢查：對工作場所中各種機械、設備，按照其性質 分別規定檢查週期；當時間一到即予以詳細檢查。 2️⃣ 重點檢查：機械設備於其安裝妥當，開始 ...
+本校安全衛生自動檢查計劃
+安全衛生環保中心
+› ...
+對於機械、設備之定期檢查及作業檢點，應依實際需要自行訂定，並以檢點手冊、檢點表等為之。確實依據自動檢查實施項目表（如附表1所示）查詢校內機械、設備、或作業 ...
+缺少字詞： 雇主 ‎| 必須包含以下字詞： 雇主
+其他人也搜尋了以下項目
+依職業安全衛生法規定雇主於新僱勞工時應施行何種檢查
+自動檢查分為哪幾大類
+下列何者非屬安全衛生自動檢查的類別
+自動檢查計畫範本
+職業安全衛生管理辦法之自動檢查項目一覽表
+職業安全衛生自動檢查計畫範例
+自動檢查計畫指引
+第二種壓力容器檢查法規
+頁面導覽
+1
+2
+3
+4
+5
+6
+7
+8
+9
+10
+下一頁
+頁尾連結
+台灣
+708 臺南市安平區 - 根據你的 IP 位址
+- 更新位置
+說明
+提供意見
+隱私權
+服務條款</t>
+        </is>
+      </c>
+      <c r="I141" s="2" t="inlineStr"/>
     </row>
     <row r="142" ht="92.59999999999999" customHeight="1">
       <c r="A142" s="2" t="n">
@@ -5689,8 +6770,16 @@
       <c r="G142" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H142" s="2" t="n"/>
-      <c r="I142" s="2" t="n"/>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>依職業安全衛生管理辦法規定，雇主實施自動檢查應訂定自動檢查計畫（選項D）。
+根據《職業安全衛生管理辦法》第 79 條規定：「雇主依第十三條至第六十三條規定實施之自動檢查，應訂定自動檢查計畫。」
+法律百科Legispedia 職業安全衛生管理辦法 - 勞動部-所有條文
+第六節自動檢查紀錄及必要措施. 第79 條. 雇主依第十三條至第六十三條規定實施之自動檢查，應訂定自動檢查計畫。 第80 條. 雇主依第十三條至第四十九條規定實施之定期檢查 ...
+顯示全部 內容</t>
+        </is>
+      </c>
+      <c r="I142" s="2" t="inlineStr"/>
     </row>
     <row r="143" ht="92.59999999999999" customHeight="1">
       <c r="A143" s="2" t="n">
@@ -5724,8 +6813,21 @@
       <c r="G143" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H143" s="2" t="n"/>
-      <c r="I143" s="2" t="n"/>
+      <c r="H143" s="2" t="inlineStr">
+        <is>
+          <t>依職業安全衛生管理辦法第 80 條規定，下列何者非屬應記錄事項為 部門主管。
+應記錄事項說明
+依據法規，雇主實施定期檢查或重點檢查時，應記錄下列 6 項事項，並保存 3 年：
+檢查年月日
+檢查方法
+檢查部分
+檢查結果
+實施檢查者之姓名
+依檢查結果應採取改善措施之內容
+因此，選項中的「部門主管」並非前述法定應直接記錄於定期檢查表單中的項目。</t>
+        </is>
+      </c>
+      <c r="I143" s="2" t="inlineStr"/>
     </row>
     <row r="144" ht="92.59999999999999" customHeight="1">
       <c r="A144" s="2" t="n">
@@ -5753,8 +6855,14 @@
       <c r="G144" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H144" s="2" t="n"/>
-      <c r="I144" s="2" t="n"/>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>答案是 3。
+根據職業安全衛生管理辦法第 8 條第一項之規定：「職業安全衛生人員因故未能執行職務時，雇主應即指定適當代理人。其代理期間不得超過三個月。」
+安全衛生履歷智能雲</t>
+        </is>
+      </c>
+      <c r="I144" s="2" t="inlineStr"/>
     </row>
     <row r="145" ht="92.59999999999999" customHeight="1">
       <c r="A145" s="2" t="n">
@@ -5788,8 +6896,17 @@
       <c r="G145" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H145" s="2" t="n"/>
-      <c r="I145" s="2" t="n"/>
+      <c r="H145" s="2" t="inlineStr">
+        <is>
+          <t>職業安全衛生管理單位為事業單位內擬訂、規劃、推動及督導職業安全衛生有關業務之組織。
+相關法規說明
+依據《職業安全衛生法施行細則》規定，安全衛生組織包含以下：
+職業安全衛生管理單位：為事業單位內擬訂、規劃、推動及督導職業安全衛生有關業務之組織。
+職業安全衛生委員會：為事業單位內審議、協調有關安全衛生事項之組織。
+行政院公報資訊網</t>
+        </is>
+      </c>
+      <c r="I145" s="2" t="inlineStr"/>
     </row>
     <row r="146" ht="92.59999999999999" customHeight="1">
       <c r="A146" s="2" t="n">
@@ -5823,8 +6940,17 @@
       <c r="G146" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H146" s="2" t="n"/>
-      <c r="I146" s="2" t="n"/>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>達成失能傷害頻率在 0.13 以下，是職業安全衛生管理計畫中的計畫目標。
+職業安全衛生管理計畫要項說明
+基本方針：確立事業單位推動職業安全衛生整體的方向、決心與安全衛生政策。
+計畫目標：具體設定要達成的安全衛生數據或成果（例如：達成失能傷害頻率在 0.13 以下、零重大職災等具體數值或指標）。
+實施細目：為達成目標所要執行的具體工作項目與執行內容（例如：教育訓練、作業環境監測、健康檢查等）。
+預定進度：各項實施細目與工作計畫執行的時間表或完成期限。</t>
+        </is>
+      </c>
+      <c r="I146" s="2" t="inlineStr"/>
     </row>
     <row r="147" ht="92.59999999999999" customHeight="1">
       <c r="A147" s="2" t="n">
@@ -5858,8 +6984,14 @@
       <c r="G147" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H147" s="2" t="n"/>
-      <c r="I147" s="2" t="n"/>
+      <c r="H147" s="2" t="inlineStr">
+        <is>
+          <t>依職業安全衛生管理辦法第15-2條規定，雇主對高空工作車應每月實施定期檢查一次（包含制動裝置、離合器、操作裝置、作業裝置、油壓裝置及安全裝置等項目），故正確選項為高空工作車。
+高空工作車：每月定期檢查一次（另依同辦法第50-1條規定，每日作業前也須實施性能檢點）。
+研磨機、抽水機、數位加工機：未規定須每月實施定期檢查。</t>
+        </is>
+      </c>
+      <c r="I147" s="2" t="inlineStr"/>
     </row>
     <row r="148" ht="92.59999999999999" customHeight="1">
       <c r="A148" s="2" t="n">
@@ -5893,8 +7025,12 @@
       <c r="G148" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H148" s="2" t="n"/>
-      <c r="I148" s="2" t="n"/>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>Google AI 摘要未抓取到，請手動補充。</t>
+        </is>
+      </c>
+      <c r="I148" s="2" t="inlineStr"/>
     </row>
     <row r="149" ht="77.15000000000001" customHeight="1">
       <c r="A149" s="2" t="n">
@@ -5928,8 +7064,18 @@
       <c r="G149" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H149" s="2" t="n"/>
-      <c r="I149" s="2" t="n"/>
+      <c r="H149" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+下列何者非屬危險物？答案是 致癌物。
+詳細說明
+依據台灣的《職業安全衛生設施規則》，危害物質主要區分為「危險物」（具物理性危害）與「有害物」（具健康危害）：
+中山醫學大學
+危險物（物理性危害）： 包含[爆炸性物質]、[著火性物質]、[可燃性氣體]、易燃液體、氧化性物質等。
+有害物（健康危害）： 如致癌物、具毒性或刺激性之化學物質等，屬於有害物而非危險物。</t>
+        </is>
+      </c>
+      <c r="I149" s="2" t="inlineStr"/>
     </row>
     <row r="150" ht="77.15000000000001" customHeight="1">
       <c r="A150" s="2" t="n">
@@ -5963,8 +7109,16 @@
       <c r="G150" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H150" s="2" t="n"/>
-      <c r="I150" s="2" t="n"/>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t>依據《職業安全衛生管理辦法》規定，乙炔熔接裝置應每年就裝置之損傷、變形、腐蝕等及其性能定期實施檢查一次。
+正確答案為：每年。
+相關法規重點
+檢查週期：每年一次（除配管埋設於地下之部分外）。
+檢查項目：裝置之損傷、變形、腐蝕等及其性能。</t>
+        </is>
+      </c>
+      <c r="I150" s="2" t="inlineStr"/>
     </row>
     <row r="151" ht="92.59999999999999" customHeight="1">
       <c r="A151" s="2" t="n">
@@ -5998,8 +7152,15 @@
       <c r="G151" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H151" s="2" t="n"/>
-      <c r="I151" s="2" t="n"/>
+      <c r="H151" s="2" t="inlineStr">
+        <is>
+          <t>依《職業安全衛生管理辦法》第12條之4第3項規定，應實施採購管理的事業單位，於機械、設備、器具、物料、原料等之採購、驗收及使用相關執行紀錄，應保存 3年。
+如需了解其他職安衛相關紀錄的法定保存年限（如自動檢查、教育訓練或承攬管理紀錄），請隨時告訴我！
+第三章職業安全衛生管理措施 - 勞動部前二項執行紀錄，應保存三年。 第12-4 條. 第十二條之二第一項之事業單位應建立採購管理程序，對於機械、設備、 器具、物料、原料及個人防護具等之採購、租賃，其契約內容應有符合法令及實際需要之職業安全衛生具體規範，並於驗收、使用前確認其符合規定。 前項事業單位...
+AI 回覆可能有誤。如需法律建議，請諮詢專業人士。 瞭解詳情</t>
+        </is>
+      </c>
+      <c r="I151" s="2" t="inlineStr"/>
     </row>
     <row r="152" ht="92.59999999999999" customHeight="1">
       <c r="A152" s="2" t="n">
@@ -6033,8 +7194,18 @@
       <c r="G152" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H152" s="2" t="n"/>
-      <c r="I152" s="2" t="n"/>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>依職業安全衛生管理辦法規定，這是指重點檢查。
+安全衛生環保中心
+重點檢查定義
+對象：某些特殊機械設備。
+時機：於完成設置開始使用前，或拆卸、改裝、修理後。
+內容：就其部分重要處實施重點式檢查。
+安全衛生環保中心</t>
+        </is>
+      </c>
+      <c r="I152" s="2" t="inlineStr"/>
     </row>
     <row r="153" ht="92.59999999999999" customHeight="1">
       <c r="A153" s="2" t="n">
@@ -6068,8 +7239,15 @@
       <c r="G153" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H153" s="2" t="n"/>
-      <c r="I153" s="2" t="n"/>
+      <c r="H153" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+依據《職業安全衛生管理辦法》規定，捲揚裝置於開始使用、拆卸、改裝或修理時，應實施重點檢查。
+正確答案：重點檢查
+相關法規：依據職業安全衛生管理辦法第46條規定，雇主對捲揚裝置於開始使用、拆卸、改裝或修理時，應實施重點檢查，確認安裝部位強度、結合元件及制動裝置等性能符合需求。</t>
+        </is>
+      </c>
+      <c r="I153" s="2" t="inlineStr"/>
     </row>
     <row r="154" ht="92.59999999999999" customHeight="1">
       <c r="A154" s="2" t="n">
@@ -6103,8 +7281,13 @@
       <c r="G154" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H154" s="2" t="n"/>
-      <c r="I154" s="2" t="n"/>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t>擬訂安全衛生作業標準非屬職業安全衛生委員會應辦理之事項。
+依據職業安全衛生管理辦法第12條規定，職業安全衛生委員會應辦理的事項包含：對雇主擬訂之職業安全衛生政策提出建議、審議安全衛生教育訓練實施計畫、考核現場安全衛生管理績效等；而「擬訂安全衛生作業標準」通常由事業各部門主管或職安衛生管理單位負責擬訂，非委員會之直接辦理事項。</t>
+        </is>
+      </c>
+      <c r="I154" s="2" t="inlineStr"/>
     </row>
     <row r="155" ht="92.59999999999999" customHeight="1">
       <c r="A155" s="2" t="n">
@@ -6138,8 +7321,13 @@
       <c r="G155" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H155" s="2" t="n"/>
-      <c r="I155" s="2" t="n"/>
+      <c r="H155" s="2" t="inlineStr">
+        <is>
+          <t>依據《職業安全衛生管理辦法》規定，雇主對於高壓電氣設備及低壓電氣設備，應每隔 每年（選項 A）定期實施檢查一次。
+正確答案：(A) 每年</t>
+        </is>
+      </c>
+      <c r="I155" s="2" t="inlineStr"/>
     </row>
     <row r="156" ht="77.15000000000001" customHeight="1">
       <c r="A156" s="2" t="n">
@@ -6173,8 +7361,17 @@
       <c r="G156" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H156" s="2" t="n"/>
-      <c r="I156" s="2" t="n"/>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+依職業安全衛生管理辦法第19條規定，雇主對固定式起重機，應每年就該機械之整體定期實施檢查一次。
+正確答案為：每年。
+相關定期檢查重點
+每年檢查：針對固定式起重機之整體實施檢查一次。
+每月檢查：應每月定期實施檢查一次，項目包含過捲預防裝置、警報裝置、制動器、離合器、鋼索、吊鏈及控制裝置等。</t>
+        </is>
+      </c>
+      <c r="I156" s="2" t="inlineStr"/>
     </row>
     <row r="157" ht="108" customHeight="1">
       <c r="A157" s="2" t="n">
@@ -6208,8 +7405,17 @@
       <c r="G157" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H157" s="2" t="n"/>
-      <c r="I157" s="2" t="n"/>
+      <c r="H157" s="2" t="inlineStr">
+        <is>
+          <t>依據職業安全衛生管理辦法第38條規定，雇主對特定化學設備內面及外面有無顯著損傷、變形及腐蝕應每 2 年定期實施檢查一次。
+各選項檢查週期對照：
+特定化學設備內面及外面有無顯著損傷、變形及腐蝕：每 2 年檢查一次。
+高壓用電設備絕緣情形、接地電阻及其他安全設備狀況：每 1 年（每年）檢查一次。
+鍋爐本體有無損傷：依規定通常為每年或依危險性設備定期檢查規定（非每2年）。
+局部排氣裝置之吸氣及排氣能力：每 1 年（每年）檢查一次。</t>
+        </is>
+      </c>
+      <c r="I157" s="2" t="inlineStr"/>
     </row>
     <row r="158" ht="77.15000000000001" customHeight="1">
       <c r="A158" s="2" t="n">
@@ -6243,8 +7449,13 @@
       <c r="G158" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H158" s="2" t="n"/>
-      <c r="I158" s="2" t="n"/>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t>勞動法令為正確答案。
+依據《勞動檢查法》第 1 條規定：「為實施勞動檢查，貫徹勞動法令之執行、維護勞雇雙方權益、安定社會、發展經濟，特制定本法。」</t>
+        </is>
+      </c>
+      <c r="I158" s="2" t="inlineStr"/>
     </row>
     <row r="159" ht="77.15000000000001" customHeight="1">
       <c r="A159" s="2" t="n">
@@ -6278,8 +7489,19 @@
       <c r="G159" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H159" s="2" t="n"/>
-      <c r="I159" s="2" t="n"/>
+      <c r="H159" s="2" t="inlineStr">
+        <is>
+          <t>答案為：人力發展。
+勞動檢查法立法目的
+依據《勞動檢查法》第 1 條規定：「為實施勞動檢查，貫徹勞動法令之執行，保障勞工權益，安定社會與發展經濟，特制定本法。」
+選項比較
+貫徹勞動法令之執行：屬明定之目的。
+安定社會：屬明定之目的。
+發展經濟：屬明定之目的。
+人力發展：非勞動檢查法明定之立法目的。</t>
+        </is>
+      </c>
+      <c r="I159" s="2" t="inlineStr"/>
     </row>
     <row r="160" ht="77.15000000000001" customHeight="1">
       <c r="A160" s="2" t="n">
@@ -6313,8 +7535,15 @@
       <c r="G160" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H160" s="2" t="n"/>
-      <c r="I160" s="2" t="n"/>
+      <c r="H160" s="2" t="inlineStr">
+        <is>
+          <t>依據《勞動檢查法》規定，答案為 (A) 代行檢查機構。
+重點解析
+代行檢查機構：指由中央主管機關指定，負責辦理危險性機械或設備檢查之行政機關、學術機構、公營事業機構或非營利法人。
+勞動檢查機構：指中央或直轄市主管機關或有關機關為辦理勞動檢查業務所設置之專責檢查機構。</t>
+        </is>
+      </c>
+      <c r="I160" s="2" t="inlineStr"/>
     </row>
     <row r="161" ht="77.15000000000001" customHeight="1">
       <c r="A161" s="2" t="n">
@@ -6348,8 +7577,15 @@
       <c r="G161" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H161" s="2" t="n"/>
-      <c r="I161" s="2" t="n"/>
+      <c r="H161" s="2" t="inlineStr">
+        <is>
+          <t>依勞動檢查法施行細則第6條規定，每百萬工時之失能傷害總損失日數係指失能傷害嚴重率（或稱職業災害嚴重率）。
+重點整理
+失能傷害嚴重率：指每百萬工時之失能傷害總損失日數。
+失能傷害頻率：指每百萬工時之失能傷害次數。</t>
+        </is>
+      </c>
+      <c r="I161" s="2" t="inlineStr"/>
     </row>
     <row r="162" ht="77.15000000000001" customHeight="1">
       <c r="A162" s="2" t="n">
@@ -6383,8 +7619,16 @@
       <c r="G162" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H162" s="2" t="n"/>
-      <c r="I162" s="2" t="n"/>
+      <c r="H162" s="2" t="inlineStr">
+        <is>
+          <t>依據《勞動檢查法施行細則》第6條規定，每百萬工時之失能傷害次數是指失能傷害頻率。
+相關名詞定義
+失能傷害頻率（FR）：指每百萬工時之失能傷害次數。
+失能傷害嚴重率（SR）：指每百萬工時之失能傷害總損失日數。
+勞動部全球資訊網</t>
+        </is>
+      </c>
+      <c r="I162" s="2" t="inlineStr"/>
     </row>
     <row r="163" ht="108" customHeight="1">
       <c r="A163" s="2" t="n">
@@ -6418,8 +7662,17 @@
       <c r="G163" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H163" s="2" t="n"/>
-      <c r="I163" s="2" t="n"/>
+      <c r="H163" s="2" t="inlineStr">
+        <is>
+          <t>答案是：具有危險性之機械或設備定期檢查。
+相關法規說明
+代行檢查機構：依據《勞動檢查法》規定，是指由中央主管機關指定，專門辦理具有危險性之機械或設備檢查的行政機關、學術機構或非營利法人。
+其他選項：
+勞工作業環境監測：由認可的作業環境監測機構或符合資格之人員實施。
+危險性工作場所審查或檢查、職業災害檢查：屬於勞動檢查機構及勞動檢查員的法定職權，不由代行檢查機構實施。</t>
+        </is>
+      </c>
+      <c r="I163" s="2" t="inlineStr"/>
     </row>
     <row r="164" ht="77.15000000000001" customHeight="1">
       <c r="A164" s="2" t="n">
@@ -6453,8 +7706,13 @@
       <c r="G164" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H164" s="2" t="n"/>
-      <c r="I164" s="2" t="n"/>
+      <c r="H164" s="2" t="inlineStr">
+        <is>
+          <t>勞動檢查機構應於 10 日內以書面通知事業單位立即改正或限期改善。
+根據 勞動檢查法第 25 條 規定，勞動檢查員對於事業單位之檢查結果，應報由所屬勞動檢查機構依法處理；若有違反勞動法令規定之事項，勞動檢查機構應於十日內以書面通知事業單位立即改正或限期改善。因此正確答案為 10 日（選項 C）。</t>
+        </is>
+      </c>
+      <c r="I164" s="2" t="inlineStr"/>
     </row>
     <row r="165" ht="77.15000000000001" customHeight="1">
       <c r="A165" s="2" t="n">
@@ -6488,8 +7746,14 @@
       <c r="G165" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H165" s="2" t="n"/>
-      <c r="I165" s="2" t="n"/>
+      <c r="H165" s="2" t="inlineStr">
+        <is>
+          <t>雇主應於顯明而易見處所公告 7 日以上（正確選項為 7 日）。
+104職場力
+依據《勞動檢查法》第 25 條第 2 項規定：「事業單位對前項檢查結果，應於違規場所顯明易見處公告七日以上。」</t>
+        </is>
+      </c>
+      <c r="I165" s="2" t="inlineStr"/>
     </row>
     <row r="166" ht="77.15000000000001" customHeight="1">
       <c r="A166" s="2" t="n">
@@ -6523,8 +7787,14 @@
       <c r="G166" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H166" s="2" t="n"/>
-      <c r="I166" s="2" t="n"/>
+      <c r="H166" s="2" t="inlineStr">
+        <is>
+          <t>依據勞動檢查法第33條第1項規定，答案是 14 日。
+勞動檢查機構於受理勞工申訴後，應儘速派員檢查，並應於 14 日內將檢查結果以書面或其他適當方式通知申訴人。
+傑報人力資源服務集團</t>
+        </is>
+      </c>
+      <c r="I166" s="2" t="inlineStr"/>
     </row>
     <row r="167" ht="92.59999999999999" customHeight="1">
       <c r="A167" s="2" t="n">
@@ -6558,8 +7828,23 @@
       <c r="G167" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H167" s="2" t="n"/>
-      <c r="I167" s="2" t="n"/>
+      <c r="H167" s="2" t="inlineStr">
+        <is>
+          <t>依據《勞動檢查法》之規定，選項中敘述正確的是：無故拒絕勞動檢查，處新台幣 3 萬元以上 15 萬元以下罰鍰。
+各選項詳細解析
+勞動檢查機構接獲勞工申訴後，應於 10 日內將檢查結果通知申訴人：
+錯誤。依據勞動檢查法第 33 條規定，應於 14日內 將檢查結果通知申訴人。
+執行職業災害檢查，不得事先通知事業單位：
+錯誤。依據勞動檢查法第 13 條規定，一般勞動檢查不得事先通知，但職業災害檢查、危險性工作場所審查及危險性機械設備檢查等，得事先通知事業單位。
+臺北市勞動檢查處 無故拒絕勞動檢查，處新台幣 3 萬元以上 15 萬元以下罰鍰：
+正確。依據勞動檢查法第 35 條規定，無正當理由拒絕、規避或妨礙勞動檢查者，處新臺幣 3 萬元以上 15 萬元以下罰鍰。
+企業軍師林郁汶
+事業單位應於違規場所顯明易見處，公告檢查結果 14 日以上：
+錯誤。依據勞動檢查法第 25 條規定，事業單位應於違規場所顯明易見處公告 7日以上（非 14 日）。
+104職場力</t>
+        </is>
+      </c>
+      <c r="I167" s="2" t="inlineStr"/>
     </row>
     <row r="168" ht="77.15000000000001" customHeight="1">
       <c r="A168" s="2" t="n">
@@ -6593,8 +7878,19 @@
       <c r="G168" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H168" s="2" t="n"/>
-      <c r="I168" s="2" t="n"/>
+      <c r="H168" s="2" t="inlineStr">
+        <is>
+          <t>食品安全衛生法不是勞動檢查法明定之勞動檢查事項範圍。
+中華民國國防部- 全球資訊網
+勞動檢查法規定的檢查範圍
+依據《勞動檢查法》第 2 條規定，勞動檢查的範圍包括：
+勞動基準法令規定之事項。
+職業安全衛生法令規定之事項。
+其他依勞動法令應辦理之事項（例如有關工會、勞資會議等勞動法令）。
+而「食品安全衛生法」（應為食品安全衛生管理法）是用來規範食品衛生安全的法律，屬於衛生主管機關（衛生福利部食品藥物管理署）的職掌，不屬於勞動檢查機構的法定勞動檢查範圍。</t>
+        </is>
+      </c>
+      <c r="I168" s="2" t="inlineStr"/>
     </row>
     <row r="169" ht="77.15000000000001" customHeight="1">
       <c r="A169" s="2" t="n">
@@ -6628,8 +7924,12 @@
       <c r="G169" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H169" s="2" t="n"/>
-      <c r="I169" s="2" t="n"/>
+      <c r="H169" s="2" t="inlineStr">
+        <is>
+          <t>Google AI 摘要未抓取到，請手動補充。</t>
+        </is>
+      </c>
+      <c r="I169" s="2" t="inlineStr"/>
     </row>
     <row r="170" ht="77.15000000000001" customHeight="1">
       <c r="A170" s="2" t="n">
@@ -6663,8 +7963,21 @@
       <c r="G170" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H170" s="2" t="n"/>
-      <c r="I170" s="2" t="n"/>
+      <c r="H170" s="2" t="inlineStr">
+        <is>
+          <t>事業單位若以違反規定單項（或單一事業）內容公告時，應於該違規之機具設備或場所公告。
+104學習
+相關公告規定對照
+單項/單一違規內容公告： 應公告於該違規之機具、設備或場所。
+104學習
+全部檢查結果通知書公告（符合下列場所之一即可）：
+事業單位管制勞工出勤之場所。
+餐廳、宿舍及各作業場所之公告場所。
+與工會或勞工代表協商同意之場所。
+104學習</t>
+        </is>
+      </c>
+      <c r="I170" s="2" t="inlineStr"/>
     </row>
     <row r="171" ht="92.59999999999999" customHeight="1">
       <c r="A171" s="2" t="n">
@@ -6698,8 +8011,18 @@
       <c r="G171" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H171" s="2" t="n"/>
-      <c r="I171" s="2" t="n"/>
+      <c r="H171" s="2" t="inlineStr">
+        <is>
+          <t>工作者如發現事業單位違反職業安全衛生法令時，其申訴的對象不包括目的事業主管機關。
+相關法規依據
+依據 職業安全衛生法 第 39 條規定，工作者發現事業單位違反本法或有關安全衛生之規定、疑似罹患職業病、或身體精神遭受侵害時，得向下列三個對象申訴：
+雇主
+主管機關（如勞動部或地方勞工主管機關）
+勞動檢查機構
+因此，申訴對象並不包含「目的事業主管機關」。</t>
+        </is>
+      </c>
+      <c r="I171" s="2" t="inlineStr"/>
     </row>
     <row r="172" ht="77.15000000000001" customHeight="1">
       <c r="A172" s="2" t="n">
@@ -6733,8 +8056,18 @@
       <c r="G172" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H172" s="2" t="n"/>
-      <c r="I172" s="2" t="n"/>
+      <c r="H172" s="2" t="inlineStr">
+        <is>
+          <t>答案為 「以上皆是」（選項 D）。
+依據《勞動檢查法》第 13 條規定，勞動檢查員執行職務，除下列事項外，不得事先通知事業單位：
+勞動檢查法第 26 條規定之審查或檢查（危險性工作場所）
+危險性機械或設備檢查
+職業災害檢查
+其他經勞動檢查機構或主管機關核准者
+臺北市勞動檢查處 因此，選項所列的三項皆屬於「例外可以事先通知」的事項，故題目問除下列何者外不得事先通知，答案即為包含上述所有項目的「以上皆是」。</t>
+        </is>
+      </c>
+      <c r="I172" s="2" t="inlineStr"/>
     </row>
     <row r="173" ht="77.15000000000001" customHeight="1">
       <c r="A173" s="2" t="n">
@@ -6768,8 +8101,20 @@
       <c r="G173" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H173" s="2" t="n"/>
-      <c r="I173" s="2" t="n"/>
+      <c r="H173" s="2" t="inlineStr">
+        <is>
+          <t>依勞動檢查法施行細則第34條規定，停工通知書不應記載復工日期。
+停工通知書應記載事項
+依規定，勞動檢查機構發出的停工通知書應載明下列要點：
+受處分單位與地址：受停工處分之事業單位、雇主名稱及地址。
+法令依據與停工理由。
+停工日期（起訖時間）與停工範圍。
+申請復工之條件及程序。
+執行停工處分之機構。
+臺北市政府全球資訊網 由於停工處分並無預先设定的特定期限，必須等事業單位完成改善並經主管機關查證原因消滅後才能申請復工，因此無法在剛勒令停工時預先填寫「復工日期」。「復工日期」是 später 在審查合格後發出的復工通知書上才需要記載的項目。</t>
+        </is>
+      </c>
+      <c r="I173" s="2" t="inlineStr"/>
     </row>
     <row r="174" ht="77.15000000000001" customHeight="1">
       <c r="A174" s="2" t="n">
@@ -6803,8 +8148,16 @@
       <c r="G174" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H174" s="2" t="n"/>
-      <c r="I174" s="2" t="n"/>
+      <c r="H174" s="2" t="inlineStr">
+        <is>
+          <t>依勞動檢查法規定，事業單位對未持勞動檢查證者，得拒絕檢查。
+相關法律規定
+法令依據：依據《勞動檢查法》第22條第1項規定：「勞動檢查員進入事業單位進行檢查時，應主動出示勞動檢查證，並告知雇主及工會。事業單位對未持勞動檢查證者，得拒絕檢查。」
+注意事項：勞動檢查員依法執行職務時必須出示證件；若對方未持證件，事業單位有權拒絕，以策安全並確認其合法身分。但若檢查員已主動出示證件，事業單位則不得無故拒絕、規避或妨礙，否則可能面臨罰鍰。
+104招募管理</t>
+        </is>
+      </c>
+      <c r="I174" s="2" t="inlineStr"/>
     </row>
     <row r="175" ht="92.59999999999999" customHeight="1">
       <c r="A175" s="2" t="n">
@@ -6838,8 +8191,13 @@
       <c r="G175" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H175" s="2" t="n"/>
-      <c r="I175" s="2" t="n"/>
+      <c r="H175" s="2" t="inlineStr">
+        <is>
+          <t>本題答案為：勞動檢查法。
+依據 勞動檢查法 第 26 條規定：「左列危險性工作場所，非經勞動檢查機構審查或檢查合格，事業單位不得使勞工在該場所作業。」</t>
+        </is>
+      </c>
+      <c r="I175" s="2" t="inlineStr"/>
     </row>
     <row r="176" ht="77.15000000000001" customHeight="1">
       <c r="A176" s="2" t="n">
@@ -6873,8 +8231,13 @@
       <c r="G176" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H176" s="2" t="n"/>
-      <c r="I176" s="2" t="n"/>
+      <c r="H176" s="2" t="inlineStr">
+        <is>
+          <t>依據危險性工作場所審查及檢查辦法第2條規定，從事製造、處置、使用危險物及有害物之數量達規定數量者，應申請甲類危險性工作場所審查及檢查。
+正確答案為：甲類。</t>
+        </is>
+      </c>
+      <c r="I176" s="2" t="inlineStr"/>
     </row>
     <row r="177" ht="92.59999999999999" customHeight="1">
       <c r="A177" s="2" t="n">
@@ -6908,8 +8271,12 @@
       <c r="G177" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H177" s="2" t="n"/>
-      <c r="I177" s="2" t="n"/>
+      <c r="H177" s="2" t="inlineStr">
+        <is>
+          <t>依據《危險性工作場所審查及檢查辦法》規定，甲類危險性工作場所須執行 (B) 製程安全評估。</t>
+        </is>
+      </c>
+      <c r="I177" s="2" t="inlineStr"/>
     </row>
     <row r="178" ht="92.59999999999999" customHeight="1">
       <c r="A178" s="2" t="n">
@@ -6937,8 +8304,15 @@
       <c r="G178" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H178" s="2" t="n"/>
-      <c r="I178" s="2" t="n"/>
+      <c r="H178" s="2" t="inlineStr">
+        <is>
+          <t>事業單位對經檢查機構審查合格之乙類危險性工作場所，應至少每 5 年重新評估一次。
+依據《危險性工作場所審查及檢查辦法》規定：
+事業單位對經檢查機構審查及檢查合格之工作場所，應於製程修改時或至少每五年重新評估一次。
+評估內容須為必要之更新並確實記錄。</t>
+        </is>
+      </c>
+      <c r="I178" s="2" t="inlineStr"/>
     </row>
     <row r="179" ht="92.59999999999999" customHeight="1">
       <c r="A179" s="2" t="n">
@@ -6972,8 +8346,17 @@
       <c r="G179" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H179" s="2" t="n"/>
-      <c r="I179" s="2" t="n"/>
+      <c r="H179" s="2" t="inlineStr">
+        <is>
+          <t>從事農藥原體合成之工作場所，應向勞動檢查機構申請乙類危險性工作場所審查與檢查。
+法源法律網
+依據危險性工作場所審查及檢查辦法第2條規定，危險性工作場所分為甲、乙、丙、丁四類：
+乙類包含：使用異氰酸甲酯、氯化氫、氨、甲醛、過氧化氫或吡啶，從事農藥原體合成之工作場所。
+申請規定：事業單位設置乙類工作場所時，應於使勞工在該場所作業四十五日前，向當地勞動檢查機構申請審查及檢查。
+高雄市政府全球資訊網 正確答案為：乙類（選項 B）。</t>
+        </is>
+      </c>
+      <c r="I179" s="2" t="inlineStr"/>
     </row>
     <row r="180" ht="77.15000000000001" customHeight="1">
       <c r="A180" s="2" t="n">
@@ -7007,8 +8390,23 @@
       <c r="G180" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H180" s="2" t="n"/>
-      <c r="I180" s="2" t="n"/>
+      <c r="H180" s="2" t="inlineStr">
+        <is>
+          <t>緊急沖淋設施非屬乙類危險性工作場所應檢查之火災爆炸危害預防設施。
+說明
+依「危險性工作場所審查及檢查辦法」相關規定（如乙類工作場所應檢查之火災爆炸危害預防設施），包含：
+危險物品倉庫之避雷裝置
+發火源之管制
+靜電危害預防措施
+危險性蒸氣、氣體及粉塵濃度測定及管理等
+而「緊急沖淋設施」屬於接觸腐蝕性或有害化學品時的急救沖洗設備，不屬於火災爆炸危害的預防設施。
+需要為您解說其他關於危險性工作場所的分類或法規嗎？
+甲類與乙類工作場所差異
+危害評估監督及管理規定
+職業安全衛生法規查詢</t>
+        </is>
+      </c>
+      <c r="I180" s="2" t="inlineStr"/>
     </row>
     <row r="181" ht="108" customHeight="1">
       <c r="A181" s="2" t="n">
@@ -7042,8 +8440,17 @@
       <c r="G181" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H181" s="2" t="n"/>
-      <c r="I181" s="2" t="n"/>
+      <c r="H181" s="2" t="inlineStr">
+        <is>
+          <t>依據《危險性工作場所審查及檢查辦法》規定，營造工程之危險性工作場所為丁類。
+相關分類說明
+甲類：製造石化基本原料、或製造、處置、使用危險物及有害物之工作場所。
+乙類：農藥製造等相關工作場所。
+丙類：具備一定規模以上之蒸汽鍋爐、高壓氣體壓力容器等工作場所。
+丁類：指特定規模之營造工程（如高度 80 公尺以上建築工程、採用壓氣施工作業之工程等）。</t>
+        </is>
+      </c>
+      <c r="I181" s="2" t="inlineStr"/>
     </row>
     <row r="182" ht="92.59999999999999" customHeight="1">
       <c r="A182" s="2" t="n">
@@ -7077,8 +8484,15 @@
       <c r="G182" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H182" s="2" t="n"/>
-      <c r="I182" s="2" t="n"/>
+      <c r="H182" s="2" t="inlineStr">
+        <is>
+          <t>依據危險性工作場所審查及檢查辦法規定，須執行施工安全評估是屬於丁類危險性工作場所（針對特定大規模之營造工程）。
+重點整理
+正確答案：丁類
+相關法條：依該辦法第五章「丁類工作場所之審查」第17條規定，事業單位申請審查丁類工作場所時，應檢附施工計畫書及施工安全評估報告書。</t>
+        </is>
+      </c>
+      <c r="I182" s="2" t="inlineStr"/>
     </row>
     <row r="183" ht="92.59999999999999" customHeight="1">
       <c r="A183" s="2" t="n">
@@ -7112,8 +8526,14 @@
       <c r="G183" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H183" s="2" t="n"/>
-      <c r="I183" s="2" t="n"/>
+      <c r="H183" s="2" t="inlineStr">
+        <is>
+          <t>正確答案是：(D) 變更主要分項工程施工方法。
+重點說明
+依據《危險性工作場所審查及檢查辦法》第20條規定，事業單位對於經檢查機構審查合格之丁類危險性工作場所，於施工過程中如有變更主要分項工程施工方法的情況時，應就變更部分重新評估，採取必要的預防措施，並更新施工計畫書及施工安全評估報告書等。</t>
+        </is>
+      </c>
+      <c r="I183" s="2" t="inlineStr"/>
     </row>
     <row r="184" ht="77.15000000000001" customHeight="1">
       <c r="A184" s="2" t="n">
@@ -7147,8 +8567,13 @@
       <c r="G184" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H184" s="2" t="n"/>
-      <c r="I184" s="2" t="n"/>
+      <c r="H184" s="2" t="inlineStr">
+        <is>
+          <t>依據《勞動檢查法》第34條規定，違反停工通知者，可處有期徒刑、拘役或科或併科罰金（最高可處3年以下有期徒刑、拘役或科或併科新臺幣15萬元以下罰金）。
+勞動部職業安全衛生署 因此，正確選項為：有期徒刑、拘役或科或併科罰金。</t>
+        </is>
+      </c>
+      <c r="I184" s="2" t="inlineStr"/>
     </row>
     <row r="185" ht="92.59999999999999" customHeight="1">
       <c r="A185" s="2" t="n">
@@ -7182,8 +8607,12 @@
       <c r="G185" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H185" s="2" t="n"/>
-      <c r="I185" s="2" t="n"/>
+      <c r="H185" s="2" t="inlineStr">
+        <is>
+          <t>Google AI 摘要未抓取到，請手動補充。</t>
+        </is>
+      </c>
+      <c r="I185" s="2" t="inlineStr"/>
     </row>
     <row r="186" ht="92.59999999999999" customHeight="1">
       <c r="A186" s="2" t="n">
@@ -7217,8 +8646,15 @@
       <c r="G186" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H186" s="2" t="n"/>
-      <c r="I186" s="2" t="n"/>
+      <c r="H186" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+依職業安全衛生設施規則規定，低壓係指 600 伏特以下之電壓。
+正確答案為：(D) 600 伏特（選項中對應的項目）。
+Quizlet</t>
+        </is>
+      </c>
+      <c r="I186" s="2" t="inlineStr"/>
     </row>
     <row r="187" ht="92.59999999999999" customHeight="1">
       <c r="A187" s="2" t="n">
@@ -7252,8 +8688,17 @@
       <c r="G187" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H187" s="2" t="n"/>
-      <c r="I187" s="2" t="n"/>
+      <c r="H187" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+依職業安全衛生設施規則第3條規定，高壓係指超過600伏特未滿22800伏特（超過六百伏特至二萬二千八百伏特）之電壓。
+電壓等級劃分標準
+低壓：600伏特以下之電壓。
+高壓：超過600伏特至22800伏特之電壓。
+特高壓：超過22800伏特之電壓。</t>
+        </is>
+      </c>
+      <c r="I187" s="2" t="inlineStr"/>
     </row>
     <row r="188" ht="92.59999999999999" customHeight="1">
       <c r="A188" s="2" t="n">
@@ -7287,8 +8732,17 @@
       <c r="G188" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H188" s="2" t="n"/>
-      <c r="I188" s="2" t="n"/>
+      <c r="H188" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+依職業安全衛生設施規則第3條規定，特高壓係指超過 22800 伏特之電壓。
+電壓等級劃分標準
+特高壓：超過 22800 伏特之電壓
+高壓：超過 600 伏特至 22800 伏特之電壓
+低壓：600 伏特以下之電壓</t>
+        </is>
+      </c>
+      <c r="I188" s="2" t="inlineStr"/>
     </row>
     <row r="189" ht="92.59999999999999" customHeight="1">
       <c r="A189" s="2" t="n">
@@ -7322,8 +8776,19 @@
       <c r="G189" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H189" s="2" t="n"/>
-      <c r="I189" s="2" t="n"/>
+      <c r="H189" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+依職業安全衛生設施規則規定，1萬伏特之電壓係屬高壓。
+法規電壓定義
+根據職業安全衛生設施規則第3條規定：
+低壓：係指 600 伏特以下之電壓。
+高壓：係指超過 600 伏特至 2 萬 2 千 8 百伏特之電壓。
+特高壓：係指超過 2 萬 2 千 8 百伏特之電壓。
+萬伏特介於 600 伏特與 2 萬 2 千 8 百伏特之間，因此屬於高壓。</t>
+        </is>
+      </c>
+      <c r="I189" s="2" t="inlineStr"/>
     </row>
     <row r="190" ht="92.59999999999999" customHeight="1">
       <c r="A190" s="2" t="n">
@@ -7357,8 +8822,16 @@
       <c r="G190" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H190" s="2" t="n"/>
-      <c r="I190" s="2" t="n"/>
+      <c r="H190" s="2" t="inlineStr">
+        <is>
+          <t>在職業安全衛生設施規則中，對於電壓的分類為「低壓」、「高壓」及「特高壓」三種，因此中壓與選項中的錯字「特高歷（特高壓）」皆非正式法定分類，但若以常見考題選項來看，「中壓」為法規中未涵蓋的分類名稱。
+依據職業安全衛生設施規則第3條規定，電壓分級如下：
+低壓：係指 600伏特以下 之電壓。
+高壓：係指 超過600伏特至2萬2千8百伏特 之電壓。
+特高壓：係指 超過2萬2千8百伏特 之電壓。</t>
+        </is>
+      </c>
+      <c r="I190" s="2" t="inlineStr"/>
     </row>
     <row r="191" ht="92.59999999999999" customHeight="1">
       <c r="A191" s="2" t="n">
@@ -7392,8 +8865,17 @@
       <c r="G191" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H191" s="2" t="n"/>
-      <c r="I191" s="2" t="n"/>
+      <c r="H191" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+依據職業安全衛生設施規則第12條規定，下列何者非屬著火性物質為：易燃液體。
+詳細說明
+著火性物質：依職業安全衛生設施規則第12條定義，包含金屬鋰/鈉/鉀、黃磷/赤磷、賽璐珞類、碳化鈣、鎂粉鋁粉、二亞硫磺酸鈉，以及其他易燃固體、自燃物質與禁水性物質（第8款）。
+易燃液體：屬於獨立的分類，載於同規則第13條規範（如汽油、乙醚、酒精等），因此不屬於著火性物質。
+行政院公報資訊網</t>
+        </is>
+      </c>
+      <c r="I191" s="2" t="inlineStr"/>
     </row>
     <row r="192" ht="92.59999999999999" customHeight="1">
       <c r="A192" s="2" t="n">
@@ -7427,8 +8909,22 @@
       <c r="G192" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H192" s="2" t="n"/>
-      <c r="I192" s="2" t="n"/>
+      <c r="H192" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+依《職業安全衛生設施規則》規定，硝化乙二醇非屬著火性物質（它屬於爆炸性物質），因此答案為硝化乙二醇。
+Facebook
+·工安百科 相關法規對照
+根據《職業安全衛生設施規則》第12條，著火性物質包含下列危險物：
+鎂粉、鋁粉、鐵粉及鎂粒等（部分金屬粉末）
+黃磷、赤磷、硫化磷等
+賽璐珞類
+金屬鋰、金屬鈉、金屬鉀
+碳化鈣、磷化鈣
+而「硝化乙二醇」則是被歸類在同規則中定義的爆炸性物質。</t>
+        </is>
+      </c>
+      <c r="I192" s="2" t="inlineStr"/>
     </row>
     <row r="193" ht="77.15000000000001" customHeight="1">
       <c r="A193" s="2" t="n">
@@ -7462,8 +8958,19 @@
       <c r="G193" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H193" s="2" t="n"/>
-      <c r="I193" s="2" t="n"/>
+      <c r="H193" s="2" t="inlineStr">
+        <is>
+          <t>黃磷、赤磷、硫化磷（題目常誤植為破化磷）等物質依《職業安全衛生設施規則》規定，屬著火性物質。
+根據《職業安全衛生設施規則》第12條規定，「著火性物質」包含：
+金屬鋰、金屬鈉、金屬鉀
+黃磷、赤磷、硫化磷等
+賽璐珞類
+碳化鈣、磷化鈣
+鎂粉、鋁粉
+如果還有其他職業安全衛生或消防法規的考題需要解答，</t>
+        </is>
+      </c>
+      <c r="I193" s="2" t="inlineStr"/>
     </row>
     <row r="194" ht="92.59999999999999" customHeight="1">
       <c r="A194" s="2" t="n">
@@ -7497,8 +9004,23 @@
       <c r="G194" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H194" s="2" t="n"/>
-      <c r="I194" s="2" t="n"/>
+      <c r="H194" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+硝化甘油不是著火性物質（它屬於爆炸性物質）。
+根據職業安全衛生設施規則第12條之規定，所稱著火性物質包含下列危險物：
+金屬鋰、金屬鈉、金屬鉀
+黃磷、赤磷、硫化磷等
+賽璐珞類
+碳化鈣、磷化鈣
+鎂粉、鋁粉
+鎂粉及鋁粉以外之金屬粉
+二亞硫磺酸鈉
+其他易燃固體、自燃物質、禁水性物質
+題目中的金屬鉀、碳化鈣與硫化磷皆名列其中，而硝化甘油則屬於爆炸性物質，因此答案為硝化甘油。</t>
+        </is>
+      </c>
+      <c r="I194" s="2" t="inlineStr"/>
     </row>
     <row r="195" ht="77.15000000000001" customHeight="1">
       <c r="A195" s="2" t="n">
@@ -7532,8 +9054,18 @@
       <c r="G195" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H195" s="2" t="n"/>
-      <c r="I195" s="2" t="n"/>
+      <c r="H195" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+依職業安全衛生設施規則規定，過氧化丁酮屬爆炸性物質。
+各選項說明
+過氧化丁酮：屬職業安全衛生設施規則規定的爆炸性物質。
+金屬鋰：屬禁水性物質（著火性物質之一）。
+過氧化鉀：屬氧化性物質。
+氯酸鈉：屬氧化性物質。</t>
+        </is>
+      </c>
+      <c r="I195" s="2" t="inlineStr"/>
     </row>
     <row r="196" ht="92.59999999999999" customHeight="1">
       <c r="A196" s="2" t="n">
@@ -7567,8 +9099,25 @@
       <c r="G196" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H196" s="2" t="n"/>
-      <c r="I196" s="2" t="n"/>
+      <c r="H196" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+錯誤敘述為：「得超過堆放地最大安全負荷」。
+依職業安全衛生設施規則第159條規定，雇主對物料之堆放應符合下列規定：
+不得超過堆放地最大安全負荷（正確應為不得超過）。
+不得影響照明。
+不得妨礙機械設備之操作。
+不得阻礙交通或出入口。
+不得減少自動灑水器及火警警報器有效功用。
+不得妨礙消防器具之緊急使用。
+以不倚靠牆壁或結構支柱堆放為原則（並不得超過其安全負荷）。
+需要我提供其他職安法規考古題或積垛作業高度限制的規定嗎？
+第159 條 - 勞動部-條文內容
+雇主對物料之堆放，應依下列規定： 一、不得超過堆放地最大安全負荷。 二、不得影響照明。 三、不得妨礙機械設備之操作。 四、不得阻礙交通或出入口。
+顯示全部 內容</t>
+        </is>
+      </c>
+      <c r="I196" s="2" t="inlineStr"/>
     </row>
     <row r="197" ht="108" customHeight="1">
       <c r="A197" s="2" t="n">
@@ -7602,8 +9151,17 @@
       <c r="G197" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H197" s="2" t="n"/>
-      <c r="I197" s="2" t="n"/>
+      <c r="H197" s="2" t="inlineStr">
+        <is>
+          <t>依據職業安全衛生設施規則第27條規定，安全門於勞工工作期間內不得上鎖，其通道不得堆置物品。
+正確選項為：安全門於勞工工作期間內不得上鎖，其通道不得堆置物品。
+相關規定重點
+安全門與安全梯：在工作期間內絕對不能上鎖，確保發生緊急狀況時能立即開啟與疏散。
+通道維護：通道應隨時保持暢通，嚴禁堆放任何雜物或物品，以免阻礙逃生。
+臺中市總工業會</t>
+        </is>
+      </c>
+      <c r="I197" s="2" t="inlineStr"/>
     </row>
     <row r="198" ht="108" customHeight="1">
       <c r="A198" s="2" t="n">
@@ -7637,8 +9195,19 @@
       <c r="G198" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H198" s="2" t="n"/>
-      <c r="I198" s="2" t="n"/>
+      <c r="H198" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+(D) 自路面起算2公尺高度範圍內，得有障礙物 為錯誤敘述。
+正確法規依據
+依職業安全衛生設施規則第31條：
+高度要求：自路面起算2公尺高度範圍內，不得有障礙物（因工作必要且採防護措施者不在此限）。選項(D)稱「得有」屬錯誤。
+主要人行道：不得小於1公尺。
+機械間通道：不得小於80公分。
+標示要求：主要人行道及有關安全門、安全梯應有明顯標示。</t>
+        </is>
+      </c>
+      <c r="I198" s="2" t="inlineStr"/>
     </row>
     <row r="199" ht="92.59999999999999" customHeight="1">
       <c r="A199" s="2" t="n">
@@ -7672,8 +9241,13 @@
       <c r="G199" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H199" s="2" t="n"/>
-      <c r="I199" s="2" t="n"/>
+      <c r="H199" s="2" t="inlineStr">
+        <is>
+          <t>依據職業安全衛生設施規則第237條規定，答案為 3公尺（選項3）。
+法規規定：雇主對於自高度在 3公尺 以上之場所投下物體（物料）有危害勞工之虞時，應設置適當之滑槽、承受設備，並指派監視人員。</t>
+        </is>
+      </c>
+      <c r="I199" s="2" t="inlineStr"/>
     </row>
     <row r="200" ht="108" customHeight="1">
       <c r="A200" s="2" t="n">
@@ -7707,8 +9281,24 @@
       <c r="G200" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H200" s="2" t="n"/>
-      <c r="I200" s="2" t="n"/>
+      <c r="H200" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+梯腳與地面之角度應在 75 度以上是錯誤的敘述。
+根據職業安全衛生設施規則第 230 條規定，合梯梯腳與地面之角度應在 75 度以內（而不是 75 度以上），以確保合梯站立時的穩定與安全。
+合法合梯的安全規定與要求
+法規規定事項
+梯腳角度：梯腳與地面之角度應在 75 度以內。
+結構與繫材：兩梯腳間應有金屬等硬質繫材扣牢。
+防滑絕緣：腳部應有防滑絕緣腳座套。
+梯面防滑：應有安全之防滑梯面。
+材質限制：合梯應具有堅固之構造，材質不得有顯著之損傷、腐蝕等。
+禁止行為與安全限制
+禁止當作上下設備：雇主不得使勞工以合梯當作二工作面之上下設備使用。
+禁止站立頂板：應禁止勞工站立於頂板作業。</t>
+        </is>
+      </c>
+      <c r="I200" s="2" t="inlineStr"/>
     </row>
     <row r="201" ht="108" customHeight="1">
       <c r="A201" s="2" t="n">
@@ -7742,8 +9332,22 @@
       <c r="G201" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H201" s="2" t="n"/>
-      <c r="I201" s="2" t="n"/>
+      <c r="H201" s="2" t="inlineStr">
+        <is>
+          <t>梯腳與地面夾角任何角度皆可，且兩梯腳間無需繫材扣牢此項敘述錯誤。
+根據《職業安全衛生設施規則》第230條規定，合梯梯腳與地面之角度應在 75度以內，且兩梯腳間應以金屬等硬質繫材扣牢。
+Facebook
+·桃園市政府勞動局
+合梯作業安全規定重點
+構造與材質：合梯應具有堅固之構造，材質不得有顯著之損傷或腐蝕。
+角度與繫材：梯腳與地面夾角須在 75度以內，並用金屬等硬質繫材將兩梯腳扣牢，腳部須有防滑絕緣腳座套。
+梯面防滑：應具有安全之防滑梯面。
+禁止事項：不得當作上下設備使用，且嚴禁勞工站立於頂板作業。
+Facebook
+·桃園市政府勞動局</t>
+        </is>
+      </c>
+      <c r="I201" s="2" t="inlineStr"/>
     </row>
     <row r="202" ht="92.59999999999999" customHeight="1">
       <c r="A202" s="2" t="n">
@@ -7777,8 +9381,18 @@
       <c r="G202" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H202" s="2" t="n"/>
-      <c r="I202" s="2" t="n"/>
+      <c r="H202" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+答案是 (A) 可夾著合梯移動（這是不安全、錯誤的方式）。
+安全合梯使用重點
+嚴禁移動：移動合梯時，人員應下至地面，絕對不可「夾著合梯」或利用兩梯腳開合方式進行橫向移動。
+高度限制：應於高度 2 公尺以下之作業使用。
+協同作業：合梯作業建議採 2 人協同作業（一人於梯上作業，另一人於下方扶持或看守）。
+單側限制：不可單側使用（應雙腳站立於安全梯面上，嚴禁站立於頂板或單邊跨坐）。</t>
+        </is>
+      </c>
+      <c r="I202" s="2" t="inlineStr"/>
     </row>
     <row r="203" ht="92.59999999999999" customHeight="1">
       <c r="A203" s="2" t="n">
@@ -7812,8 +9426,12 @@
       <c r="G203" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H203" s="2" t="n"/>
-      <c r="I203" s="2" t="n"/>
+      <c r="H203" s="2" t="inlineStr">
+        <is>
+          <t>Google AI 摘要未抓取到，請手動補充。</t>
+        </is>
+      </c>
+      <c r="I203" s="2" t="inlineStr"/>
     </row>
     <row r="204" ht="108" customHeight="1">
       <c r="A204" s="2" t="n">
@@ -7847,8 +9465,14 @@
       <c r="G204" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H204" s="2" t="n"/>
-      <c r="I204" s="2" t="n"/>
+      <c r="H204" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+依據職業安全衛生設施規則第37條規定，固定梯梯長連續超過6公尺時，應每隔 9 公尺以下設置一平台。因此正確答案為 9 公尺。
+（註：若未設置護籠或其他保護裝置，則規定應每隔6公尺以下設置一平台。）</t>
+        </is>
+      </c>
+      <c r="I204" s="2" t="inlineStr"/>
     </row>
     <row r="205" ht="108" customHeight="1">
       <c r="A205" s="2" t="n">
@@ -7882,8 +9506,18 @@
       <c r="G205" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H205" s="2" t="n"/>
-      <c r="I205" s="2" t="n"/>
+      <c r="H205" s="2" t="inlineStr">
+        <is>
+          <t>關於固定梯的規定，正確的答案是：「梯子頂端應凸出板面 60 公分以上」。
+根據台灣《職業安全衛生設施規則》第 37 條之規定，各選項的法規標準對照如下：
+原題目選項敘述	法規正確規定	結果
+踏條與牆壁間之淨距離不得超過15公分	踏條與牆壁間應保持 16.5 公分以上 之淨距。	❌ 錯誤
+梯子頂端應凸出板面 60 公分以上	梯之頂端應 突出板面 60 公分以上。	⭕ 正確
+梯長連續超過 6 公尺，應每隔 12 公尺以下設置平台	梯長連續超過 6 公尺時，應每隔 9 公尺以下 設一平台。	❌ 錯誤
+未設護籠或其他保護裝置...	未設置護籠或其他保護裝置時，應於每隔 6 公尺以下 設一平台。	❌ 錯誤</t>
+        </is>
+      </c>
+      <c r="I205" s="2" t="inlineStr"/>
     </row>
     <row r="206" ht="108" customHeight="1">
       <c r="A206" s="2" t="n">
@@ -7917,8 +9551,18 @@
       <c r="G206" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H206" s="2" t="n"/>
-      <c r="I206" s="2" t="n"/>
+      <c r="H206" s="2" t="inlineStr">
+        <is>
+          <t>固定梯之踏條與牆壁間應保持 16.5 公分 以上之淨距。
+根據台灣的《職業安全衛生設施規則》第 37 條規定，雇主設置之固定梯應符合下列重要規範：
+構造與設置： 應具有堅固之構造，並等間隔設置踏條。
+牆壁淨距： 踏條與牆壁間應保持 16.5 公分以上之淨距（以確保人員踩踏時有足夠腳部空間，避免碰撞牆面）。
+頂端突出： 梯之頂端應突出板面 60 公分 以上。
+防墜防護： 梯長連續超過 6 公尺 時，應每隔 9 公尺以下設一平台，並應於距梯底 2 公尺以上部分設置護籠或其他保護裝置。
+臺北市政府全球資訊網</t>
+        </is>
+      </c>
+      <c r="I206" s="2" t="inlineStr"/>
     </row>
     <row r="207" ht="108" customHeight="1">
       <c r="A207" s="2" t="n">
@@ -7952,8 +9596,14 @@
       <c r="G207" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H207" s="2" t="n"/>
-      <c r="I207" s="2" t="n"/>
+      <c r="H207" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+固定梯子梯長連續超過 6 公尺時，應於距離梯底 2 公尺以上部分設 護籠（(B) 護籠）。
+依據《職業安全衛生設施規則》第 37 條規定，雇主設置之固定梯子，若梯長連續超過 6 公尺，應每隔 9 公尺以下設一平台，並應於距梯底 2 公尺以上部分，設置護籠或其他保護裝置。</t>
+        </is>
+      </c>
+      <c r="I207" s="2" t="inlineStr"/>
     </row>
     <row r="208" ht="92.59999999999999" customHeight="1">
       <c r="A208" s="2" t="n">
@@ -7987,8 +9637,19 @@
       <c r="G208" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H208" s="2" t="n"/>
-      <c r="I208" s="2" t="n"/>
+      <c r="H208" s="2" t="inlineStr">
+        <is>
+          <t>有誤的敘述是 (B) 雙手拿工具。
+說明
+正確做法：攀爬梯子時應保持三點接觸（兩手一腳或兩腳一手），雙手必須空出來抓好梯階，絕不能雙手拿工具攀爬；工具與物品應利用吊繩或工具袋背負運送。
+正確敘述：
+檢查固定：使用前應檢查梯子是否穩固。
+使用捲揚式防墜器：高空作業或攀爬時應配合防墜設施保障安全。
+要全神貫注：操作與攀爬時必須專心，注意周遭狀況。
+高雄市政府全球資訊網</t>
+        </is>
+      </c>
+      <c r="I208" s="2" t="inlineStr"/>
     </row>
     <row r="209" ht="92.59999999999999" customHeight="1">
       <c r="A209" s="2" t="n">
@@ -8022,8 +9683,17 @@
       <c r="G209" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H209" s="2" t="n"/>
-      <c r="I209" s="2" t="n"/>
+      <c r="H209" s="2" t="inlineStr">
+        <is>
+          <t>正確答案是 30公分。
+根據台灣的《職業安全衛生設施規則》第 229 條規定，雇主對於使用之移動梯，應符合下列規定：
+構造與材質： 應具有堅固之構造，且材質不得有顯著之損傷、腐蝕等現象。
+寬度限制： 淨寬度（兩梯柱之間距）應在 30公分以上。
+防滑措施： 應採取防止滑溜或其他防止轉動之必要措施。
+慈濟大學</t>
+        </is>
+      </c>
+      <c r="I209" s="2" t="inlineStr"/>
     </row>
     <row r="210" ht="92.59999999999999" customHeight="1">
       <c r="A210" s="2" t="n">
@@ -8057,8 +9727,17 @@
       <c r="G210" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H210" s="2" t="n"/>
-      <c r="I210" s="2" t="n"/>
+      <c r="H210" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+依據《職業安全衛生設施規則》第155條規定，500公斤以上物品，應以以機動車輛或其他機械搬運為宜。
+相關重量搬運原則
+40公斤以上物品：以人力車輛或工具搬運為原則。
+500公斤以上物品：以機動車輛或其他機械搬運為宜。
+總體原則：物料搬運應儘量利用機械以代替人力，且運輸路線應妥善規劃並作標示。</t>
+        </is>
+      </c>
+      <c r="I210" s="2" t="inlineStr"/>
     </row>
     <row r="211" ht="92.59999999999999" customHeight="1">
       <c r="A211" s="2" t="n">
@@ -8092,8 +9771,16 @@
       <c r="G211" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H211" s="2" t="n"/>
-      <c r="I211" s="2" t="n"/>
+      <c r="H211" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+依職業安全衛生設施規則第155條規定，40 kg 以上物品，應以以人力車輛或工具搬運為原則。
+重物搬運重量與方式標準
+40公斤以上：以人力車輛或工具搬運為原則（應儘量利用機械以代替人力）。
+500公斤以上：以機動車輛或其他機械搬運為宜。</t>
+        </is>
+      </c>
+      <c r="I211" s="2" t="inlineStr"/>
     </row>
     <row r="212" ht="108" customHeight="1">
       <c r="A212" s="2" t="n">
@@ -8127,8 +9814,17 @@
       <c r="G212" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H212" s="2" t="n"/>
-      <c r="I212" s="2" t="n"/>
+      <c r="H212" s="2" t="inlineStr">
+        <is>
+          <t>依據《職業安全衛生設施規則》第 227 條規定，雇主對勞工於石綿板、瓦、木板、茅草等易踏穿材料構築之屋頂從事作業時，應設置寬度至少在 30 公分以上之踏板。
+正確答案為：30 公分（選項 D）。
+重點規範摘要
+安全通道設置：於屋架上設置適當強度，且寬度在 30 公分以上之踏板。
+防墜設施：於屋架下方可能墜落之範圍，裝設堅固格柵或安全網等設施。
+作業監督：應指定專人（屋頂作業主管）指揮或監督該作業。</t>
+        </is>
+      </c>
+      <c r="I212" s="2" t="inlineStr"/>
     </row>
     <row r="213" ht="92.59999999999999" customHeight="1">
       <c r="A213" s="2" t="n">
@@ -8162,8 +9858,17 @@
       <c r="G213" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H213" s="2" t="n"/>
-      <c r="I213" s="2" t="n"/>
+      <c r="H213" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+高差超過 1.5公尺 應設安全上下設備。
+iPEDIA 百科
+根據《職業安全衛生設施規則》第228條及《營造安全衛生設施標準》規定，雇主對勞工於高差超過 1.5 公尺以上之場所作業時，應設置能使勞工安全上下之設備（如工作用階梯、活動梯等）。
+正確選項為 1.5公尺。
+iPEDIA 百科</t>
+        </is>
+      </c>
+      <c r="I213" s="2" t="inlineStr"/>
     </row>
     <row r="214" ht="92.59999999999999" customHeight="1">
       <c r="A214" s="2" t="n">
@@ -8197,8 +9902,15 @@
       <c r="G214" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H214" s="2" t="n"/>
-      <c r="I214" s="2" t="n"/>
+      <c r="H214" s="2" t="inlineStr">
+        <is>
+          <t>二公尺以上之工作場所邊緣及開口部分，為防止勞工墜落應優先設置之適當強度防護設備係指設置護欄、護蓋。
+依據《職業安全衛生設施規則》第224條規定：
+雇主對於高度在二公尺以上之工作場所邊緣及開口部分，勞工有遭受墜落危險之虞者，應設有適當強度之護欄、護蓋等防護設備。
+只有在設置護欄、護蓋顯有困難，或因作業需要臨時拆除時，才改為採取使勞工佩掛安全帶等防止墜落之措施。</t>
+        </is>
+      </c>
+      <c r="I214" s="2" t="inlineStr"/>
     </row>
     <row r="215" ht="92.59999999999999" customHeight="1">
       <c r="A215" s="2" t="n">
@@ -8226,8 +9938,13 @@
       <c r="G215" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H215" s="2" t="n"/>
-      <c r="I215" s="2" t="n"/>
+      <c r="H215" s="2" t="inlineStr">
+        <is>
+          <t>依據職業安全衛生設施規則第226條規定，答案是 2 公尺。
+雇主對於高度在 2公尺以上 之作業場所，有遇強風、大雨等惡劣氣候致勞工有墜落危險時，應使勞工停止作業。</t>
+        </is>
+      </c>
+      <c r="I215" s="2" t="inlineStr"/>
     </row>
     <row r="216" ht="92.59999999999999" customHeight="1">
       <c r="A216" s="2" t="n">
@@ -8261,8 +9978,12 @@
       <c r="G216" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H216" s="2" t="n"/>
-      <c r="I216" s="2" t="n"/>
+      <c r="H216" s="2" t="inlineStr">
+        <is>
+          <t>依國家標準 CNS 9328「安全用顏色通則」規定，緊急停止按鈕表面應為紅色。紅色代表危險、停止及消防等緊急狀況。</t>
+        </is>
+      </c>
+      <c r="I216" s="2" t="inlineStr"/>
     </row>
     <row r="217" ht="108" customHeight="1">
       <c r="A217" s="2" t="n">
@@ -8296,8 +10017,23 @@
       <c r="G217" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H217" s="2" t="n"/>
-      <c r="I217" s="2" t="n"/>
+      <c r="H217" s="2" t="inlineStr">
+        <is>
+          <t>依據《職業安全衛生設施規則》第29-1條規定，非屬局限空間危害防止計畫應訂定之事項為「危害性化學品標示及通識」。
+局限空間危害防止計畫規定事項
+依據法規，危害防止計畫應訂定下列事項：
+局限空間內危害之確認
+局限空間內氧氣、危險物、有害物濃度之測定
+通風換氣實施方式
+電能、高溫、低溫與危害物質之隔離措施及各項防止措施
+作業方法及安全管制作法
+進入作業許可程序
+測定儀器、通風換氣、防護與救援設備之檢點及維護方法
+作業控制設施及作業安全檢點方法
+緊急應變處置措施</t>
+        </is>
+      </c>
+      <c r="I217" s="2" t="inlineStr"/>
     </row>
     <row r="218" ht="92.59999999999999" customHeight="1">
       <c r="A218" s="2" t="n">
@@ -8331,8 +10067,19 @@
       <c r="G218" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H218" s="2" t="n"/>
-      <c r="I218" s="2" t="n"/>
+      <c r="H218" s="2" t="inlineStr">
+        <is>
+          <t>依據職業安全衛生設施規則第178條第9款規定，對於輸送腐蝕性物質管線，無須標示部門名稱。
+相關法規重點
+應標示項目：根據規定，輸送腐蝕性物質之管線，應標示該物質之名稱、輸送方向及閥之開閉狀態。
+選項比較：
+(A) 物質名稱：須標示。
+(B) 輸送方向：須標示。
+(C) 閥之開閉狀態：須標示。
+(D) 部門名稱：無須標示。</t>
+        </is>
+      </c>
+      <c r="I218" s="2" t="inlineStr"/>
     </row>
     <row r="219" ht="92.59999999999999" customHeight="1">
       <c r="A219" s="2" t="n">
@@ -8366,8 +10113,17 @@
       <c r="G219" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H219" s="2" t="n"/>
-      <c r="I219" s="2" t="n"/>
+      <c r="H219" s="2" t="inlineStr">
+        <is>
+          <t>依據職業安全衛生設施規則第308條規定，除特殊情形外，勞工於坑內作業，其溫度應保持在攝氏37度以下。
+法規重點
+標準限制：坑內溫度應保持在 37度 以下。
+停止作業：溫度若達到 37度以上 時，雇主應使勞工停止作業。
+例外情形：已採取防止高溫危害人體之措施、從事救護或防止危害之搶救作業者，不在此限。
+正確答案為：(C) 37度。</t>
+        </is>
+      </c>
+      <c r="I219" s="2" t="inlineStr"/>
     </row>
     <row r="220" ht="77.15000000000001" customHeight="1">
       <c r="A220" s="2" t="n">
@@ -8401,8 +10157,19 @@
       <c r="G220" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H220" s="2" t="n"/>
-      <c r="I220" s="2" t="n"/>
+      <c r="H220" s="2" t="inlineStr">
+        <is>
+          <t>依據職業安全衛生設施規則第108條規定，可燃性氣體、有毒性氣體及氧氣（題目中的「氣氣」應為氧氣之誤繕）之鋼瓶，應全部分開儲存。
+因此正確答案為：全部分開。
+鋼瓶儲存重點規範
+分開貯存：可燃性氣體、有毒性氣體與氧氣鋼瓶彼此之間皆須分開存放，避免交互反應引起危險。
+分區放置：盛裝容器與空容器應分區放置。
+固定防傾倒：鋼瓶應安穩置放，加以固定，並裝妥護蓋。
+溫控與環境：容器應保持在 40℃ 以下，且貯存處須便於緊急時搬出。
+nantou.ardswc.gov.tw</t>
+        </is>
+      </c>
+      <c r="I220" s="2" t="inlineStr"/>
     </row>
     <row r="221" ht="77.15000000000001" customHeight="1">
       <c r="A221" s="2" t="n">
@@ -8436,8 +10203,14 @@
       <c r="G221" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H221" s="2" t="n"/>
-      <c r="I221" s="2" t="n"/>
+      <c r="H221" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+應防止翻倒災害。
+根據《職業安全衛生設施規則》第127條規定：「雇主對於堆高機之操作，不得超過該機械所能承受之最大荷重，且其載運之貨物應保持穩固狀態，防止翻倒。」</t>
+        </is>
+      </c>
+      <c r="I221" s="2" t="inlineStr"/>
     </row>
     <row r="222" ht="92.59999999999999" customHeight="1">
       <c r="A222" s="2" t="n">
@@ -8471,8 +10244,14 @@
       <c r="G222" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H222" s="2" t="n"/>
-      <c r="I222" s="2" t="n"/>
+      <c r="H222" s="2" t="inlineStr">
+        <is>
+          <t>依職業安全衛生設施規則規定，對於良導體設備內從事檢修作業使用之手提式照明燈，其電壓不得超過 24 伏特（二十四伏特）。
+正確選項為：24 伏特
+依據《職業安全衛生設施規則》相關條文規定，雇主對於良導體機器設備內之檢修工作所用之手提式照明燈，其使用電壓不得超過 24 伏特，且導線須為耐磨損及有良好絕緣，並不得有接頭。</t>
+        </is>
+      </c>
+      <c r="I222" s="2" t="inlineStr"/>
     </row>
     <row r="223" ht="108" customHeight="1">
       <c r="A223" s="2" t="n">
@@ -8506,8 +10285,24 @@
       <c r="G223" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H223" s="2" t="n"/>
-      <c r="I223" s="2" t="n"/>
+      <c r="H223" s="2" t="inlineStr">
+        <is>
+          <t>答案為 (D) 以上皆是。
+局限空間作業安全重點
+危害防止計畫：作業前應先確認危害並訂定計畫。
+濃度確認：應採取連續確認氧氣及危害物質濃度之措施。
+主管簽署：進入許可應經現場作業主管簽署後始得進入。
+需要了解更多關於局限空間的法規與防護措施嗎？
+職業安全衛生設施規則重點
+氣體偵測與通風換氣規定
+緊急救援設備設置標準
+資料來源：勞動部-職業安全衛生設施規則
+雇主使勞工於局限空間從事作業前，應先確認該局限空間內有無可能引起勞工缺氧、中毒、感電、塌陷、被夾、被捲及火災、爆炸等危害，有危害之虞者，應訂定危害防止計畫，並使現場作業主管、監視人員、作業勞工及相關承攬人依循辦理。 前項危害防止計畫，應依作業可能引起之危害訂定...
+顯示全部
+AI 回覆可能有誤。如需法律建議，請諮詢專業人士。 瞭解詳情</t>
+        </is>
+      </c>
+      <c r="I223" s="2" t="inlineStr"/>
     </row>
     <row r="224" ht="92.59999999999999" customHeight="1">
       <c r="A224" s="2" t="n">
@@ -8541,8 +10336,17 @@
       <c r="G224" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H224" s="2" t="n"/>
-      <c r="I224" s="2" t="n"/>
+      <c r="H224" s="2" t="inlineStr">
+        <is>
+          <t>依職業安全衛生法規定，雇主不得使未滿 18 歲者從事坑內工作等危險性或有害性工作。
+正確答案為：18 歲。
+相關法規重點
+年齡限制：未滿 18 歲的勞工，身心發育尚未完全，因此不能從事坑內作業、接觸危險化學物質或輻射等有害工作。
+法定要求：僱用未滿 18 歲青少年時，雇主必須先備妥法定代理人同意書及年齡證明文件。
+勞動部職業安全衛生署 如果想了解更多關於青少年打工的工時限制或禁忌工作種類，</t>
+        </is>
+      </c>
+      <c r="I224" s="2" t="inlineStr"/>
     </row>
     <row r="225" ht="92.59999999999999" customHeight="1">
       <c r="A225" s="2" t="n">
@@ -8576,8 +10380,13 @@
       <c r="G225" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H225" s="2" t="n"/>
-      <c r="I225" s="2" t="n"/>
+      <c r="H225" s="2" t="inlineStr">
+        <is>
+          <t>答案是 (D) 30 公厘。
+依據《職業安全衛生設施規則》規定，雇主架設之通道、通道路如用漏空格條製成，其縫間隙不得超過 3 公分（即 30 公厘）；如果超過這個間隙，就必須裝置鐵絲網防護，以避免人員踩空或工具掉落發生危險。</t>
+        </is>
+      </c>
+      <c r="I225" s="2" t="inlineStr"/>
     </row>
     <row r="226" ht="92.59999999999999" customHeight="1">
       <c r="A226" s="2" t="n">
@@ -8611,8 +10420,13 @@
       <c r="G226" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H226" s="2" t="n"/>
-      <c r="I226" s="2" t="n"/>
+      <c r="H226" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+依職業安全衛生設施規則規定，一般辦公場所之照明應為 300 米燭光（lux）以上（選項中的「300 米煙光」為筆誤）。</t>
+        </is>
+      </c>
+      <c r="I226" s="2" t="inlineStr"/>
     </row>
     <row r="227" ht="92.59999999999999" customHeight="1">
       <c r="A227" s="2" t="n">
@@ -8646,8 +10460,18 @@
       <c r="G227" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H227" s="2" t="n"/>
-      <c r="I227" s="2" t="n"/>
+      <c r="H227" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+依據職業安全衛生設施規則第313條規定，對於作業場所之走道照明，其照度至少應為 50 米燭光（50 lux）以上。因此正確答案為 (B) 50 米燭光。
+相關照度標準快速看
+50 米燭光以上：走道、樓梯、倉庫、堆置或搬運粗大物件處。
+100 米燭光以上：機械及鍋爐房、升降機、裝箱、更衣室、廁所。
+300 米燭光以上：一般辦公場所。
+JZTEK</t>
+        </is>
+      </c>
+      <c r="I227" s="2" t="inlineStr"/>
     </row>
     <row r="228" ht="92.59999999999999" customHeight="1">
       <c r="A228" s="2" t="n">
@@ -8681,8 +10505,12 @@
       <c r="G228" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H228" s="2" t="n"/>
-      <c r="I228" s="2" t="n"/>
+      <c r="H228" s="2" t="inlineStr">
+        <is>
+          <t>Google AI 摘要未抓取到，請手動補充。</t>
+        </is>
+      </c>
+      <c r="I228" s="2" t="inlineStr"/>
     </row>
     <row r="229" ht="92.59999999999999" customHeight="1">
       <c r="A229" s="2" t="n">
@@ -8716,8 +10544,19 @@
       <c r="G229" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H229" s="2" t="n"/>
-      <c r="I229" s="2" t="n"/>
+      <c r="H229" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+錯誤的敘述為：「焊接時得在容器上試焊」。
+說明
+依據《職業安全衛生設施規則》第106條規定，雇主對於儲存高壓氣體之容器（不論盛裝或空容器），應依下列規定辦理：
+正確做法：高壓氣體容器應標明所裝氣體之品名，不得任意灌裝或轉裝。
+正確做法：容器使用時應加固定。
+正確做法：確知容器之用途無誤者，方得使用。
+錯誤原因：嚴禁在高壓氣體容器上進行焊接或試焊，以免破壞容器結構、產生熱應力或引發爆炸危害。</t>
+        </is>
+      </c>
+      <c r="I229" s="2" t="inlineStr"/>
     </row>
     <row r="230" ht="92.59999999999999" customHeight="1">
       <c r="A230" s="2" t="n">
@@ -8751,8 +10590,19 @@
       <c r="G230" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H230" s="2" t="n"/>
-      <c r="I230" s="2" t="n"/>
+      <c r="H230" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+高壓氣體容器搬運時之注意事項，選項(A)「非與其他氣體混載不可時，應將容器之頭尾反方向或隔置相當間隔」為正確選項。
+詳細解析與法規依據
+依據《職業安全衛生設施規則》第107條規定，各選項的正誤如下：
+(A) 正確：儘量避免與其他氣體混載，非混載不可時，應將容器之頭尾反方向置放或隔置相當間隔。
+(B) 錯誤：以手移動容器，應確知護蓋旋緊後，方直立移動（非單純旋緊即可隨意移動）。
+(C) 錯誤：載運可燃性氣體時，應置備滅火器；載運毒性氣體時，才需置備吸收劑、中和劑、防毒面具等。
+(D) 錯誤：溫度應保持在攝氏四十度以下，而非五十度。</t>
+        </is>
+      </c>
+      <c r="I230" s="2" t="inlineStr"/>
     </row>
     <row r="231" ht="92.59999999999999" customHeight="1">
       <c r="A231" s="2" t="n">
@@ -8786,8 +10636,18 @@
       <c r="G231" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H231" s="2" t="n"/>
-      <c r="I231" s="2" t="n"/>
+      <c r="H231" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+「可燃性氣體、有毒性氣體及氧氣之鋼瓶，應合併貯存」這項敘述是錯誤的。
+根據職業安全衛生設施規則第 108 條規定，可燃性氣體、有毒性氣體及氧氣之鋼瓶，應分開貯存，而非合併貯存。
+相關正確規定
+溫度限制：容器應保持在攝氏 40 度以下。
+固定方式：應安穩置放並加固定及裝妥護蓋。
+防火安全：貯存場所應有適當之警戒標示，禁止煙火接近。</t>
+        </is>
+      </c>
+      <c r="I231" s="2" t="inlineStr"/>
     </row>
     <row r="232" ht="92.59999999999999" customHeight="1">
       <c r="A232" s="2" t="n">
@@ -8821,8 +10681,17 @@
       <c r="G232" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H232" s="2" t="n"/>
-      <c r="I232" s="2" t="n"/>
+      <c r="H232" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+依據《職業安全衛生設施規則》第309條規定，每一勞工原則上應有 10 立方公尺 以上之空間。
+臺北市政府全球資訊網
+相關規定重點
+空間計算：除設備及自地面算起高度超過 4 公尺以上之空間不予計入外，每一勞工原則上應有 10 立方公尺 以上的空間。
+正確選項：10 立方公尺。</t>
+        </is>
+      </c>
+      <c r="I232" s="2" t="inlineStr"/>
     </row>
     <row r="233" ht="92.59999999999999" customHeight="1">
       <c r="A233" s="2" t="n">
@@ -8848,8 +10717,17 @@
       <c r="G233" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H233" s="2" t="n"/>
-      <c r="I233" s="2" t="n"/>
+      <c r="H233" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+依據職業安全衛生設施規則第311條規定，直接與大氣相通之開口部分面積應為地板面積之二十分之一（1/20）以上（即選項中的 01:20:00，代表 1/20）。
+重點整理
+法規標準：窗戶及其他可直接與大氣相通之開口部分面積，須至少達室內作業場所地板面積的 1/20 以上。
+例外規定：若雇主已設置具備充分換氣能力的機械通風設備，則不受此比例限制。
+低溫限制：氣溫在攝氏 10 度以下進行換氣時，不得使勞工暴露於每秒 1 公尺以上之氣流中。</t>
+        </is>
+      </c>
+      <c r="I233" s="2" t="inlineStr"/>
     </row>
     <row r="234" ht="92.59999999999999" customHeight="1">
       <c r="A234" s="2" t="n">
@@ -8875,8 +10753,16 @@
       <c r="G234" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H234" s="2" t="n"/>
-      <c r="I234" s="2" t="n"/>
+      <c r="H234" s="2" t="inlineStr">
+        <is>
+          <t>依職業安全衛生設施規則第162條規定，答案是 10 公分以上。
+相關規定重點
+適用對象：草袋、麻袋、塑膠袋等袋裝容器構成之積垛。
+高度限制：高度在 2公尺以上。
+安全距離：積垛與積垛間下端之距離應保持在 10公分以上。</t>
+        </is>
+      </c>
+      <c r="I234" s="2" t="inlineStr"/>
     </row>
     <row r="235" ht="92.59999999999999" customHeight="1">
       <c r="A235" s="2" t="n">
@@ -8910,8 +10796,15 @@
       <c r="G235" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H235" s="2" t="n"/>
-      <c r="I235" s="2" t="n"/>
+      <c r="H235" s="2" t="inlineStr">
+        <is>
+          <t>依據職業安全衛生設施規則第38條規定，雇主如設置傾斜路代替樓梯時，傾斜路之斜度不得大於20度（二十度），因此正確答案為 20 度。
+相關法規重點
+斜度限制：不得大於 20 度。
+表面材質：表面應以粗糙不滑之材料製造。</t>
+        </is>
+      </c>
+      <c r="I235" s="2" t="inlineStr"/>
     </row>
     <row r="236" ht="92.59999999999999" customHeight="1">
       <c r="A236" s="2" t="n">
@@ -8939,8 +10832,17 @@
       <c r="G236" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H236" s="2" t="n"/>
-      <c r="I236" s="2" t="n"/>
+      <c r="H236" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+在原動機與鍋爐房中，或在機械四周通往工作台之工作用階梯，其寬度不得小於 56 公分。
+相關法規規定
+依據《職業安全衛生設施規則》第 29 條規定：
+寬度限制：工作用階梯之寬度不得小於 56 公分。
+斜度限制：斜度不得大於 60 度。</t>
+        </is>
+      </c>
+      <c r="I236" s="2" t="inlineStr"/>
     </row>
     <row r="237" ht="92.59999999999999" customHeight="1">
       <c r="A237" s="2" t="n">
@@ -8974,8 +10876,15 @@
       <c r="G237" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H237" s="2" t="n"/>
-      <c r="I237" s="2" t="n"/>
+      <c r="H237" s="2" t="inlineStr">
+        <is>
+          <t>辦理新進或調換一般勞工之職業安全衛生教育訓練時數不得少於 3 小時。
+勞動部職業安全衛生署
+根據《職業安全衛生教育訓練規則》附表十四規定，雇主對新僱勞工或在職勞工於變更工作前，應使其接受適於各該工作必要之一般安全衛生教育訓練，時數不得少於 3 小時。
+臺灣戲曲學院</t>
+        </is>
+      </c>
+      <c r="I237" s="2" t="inlineStr"/>
     </row>
     <row r="238" ht="108" customHeight="1">
       <c r="A238" s="2" t="n">
@@ -9009,8 +10918,18 @@
       <c r="G238" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H238" s="2" t="n"/>
-      <c r="I238" s="2" t="n"/>
+      <c r="H238" s="2" t="inlineStr">
+        <is>
+          <t>辦理新進或調換之缺氧作業勞工，其職業安全衛生教育訓練時數不得少於 6 小時。
+勞動部職業安全衛生署
+依據《職業安全衛生教育訓練規則》附表十四規定：
+一般安全衛生教育訓練基本時數：新僱勞工或在職勞工變更工作前應接受至少 3 小時 的一般安全衛生教育訓練。
+缺氧作業增列時數：從事缺氧作業（含局限空間作業）之勞工，須另外增列 3 小時 的特定作業課程。
+合計時數：基本 3 小時加上增列 3 小時，總計不得少於 6 小時。
+勞動部職業安全衛生署</t>
+        </is>
+      </c>
+      <c r="I238" s="2" t="inlineStr"/>
     </row>
     <row r="239" ht="92.59999999999999" customHeight="1">
       <c r="A239" s="2" t="n">
@@ -9044,8 +10963,13 @@
       <c r="G239" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H239" s="2" t="n"/>
-      <c r="I239" s="2" t="n"/>
+      <c r="H239" s="2" t="inlineStr">
+        <is>
+          <t>依據《職業安全衛生教育訓練規則》第 42-4 條規定，事業單位以數位方式經營商品交易或運送，且交付無僱傭關係之個人親自履行外送作業時，對於新加入者，應使其接受安全衛生教育訓練，時數至少 1 小時。
+正確答案為：1 小時。</t>
+        </is>
+      </c>
+      <c r="I239" s="2" t="inlineStr"/>
     </row>
     <row r="240" ht="92.59999999999999" customHeight="1">
       <c r="A240" s="2" t="n">
@@ -9079,8 +11003,22 @@
       <c r="G240" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H240" s="2" t="n"/>
-      <c r="I240" s="2" t="n"/>
+      <c r="H240" s="2" t="inlineStr">
+        <is>
+          <t>2 年至少 6 小時（選項 (B)）。
+中國勞工安全衛生管理學會 依據勞動部職業安全衛生教育訓練規則規定，雇主對擔任職業安全衛生業務主管之勞工，應使其接受每 2 年至少 6 小時之安全衛生在職教育訓練。
+中國生產力中心中區服務處
+重點整理
+正確答案：2 年至少 6 小時
+中國勞工安全衛生管理學會 法規依據：職業安全衛生教育訓練規則相關在職訓練規定
+常見對照：
+業務主管：每 2 年至少 6 小時
+管理人員（管理師/管理員）：每 2 年至少 12 小時
+時數與紀錄查詢平台：可至職業安全衛生教育訓練暨電腦測驗資訊網查詢。
+臺中市勞工局</t>
+        </is>
+      </c>
+      <c r="I240" s="2" t="inlineStr"/>
     </row>
     <row r="241" ht="92.59999999999999" customHeight="1">
       <c r="A241" s="2" t="n">
@@ -9114,8 +11052,13 @@
       <c r="G241" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H241" s="2" t="n"/>
-      <c r="I241" s="2" t="n"/>
+      <c r="H241" s="2" t="inlineStr">
+        <is>
+          <t>依職業安全衛生教育訓練規則規定，移動式起重機操作人員之在職教育訓練為每 3 年至少 3 小時。
+財團法人中國生產力中心線上商城</t>
+        </is>
+      </c>
+      <c r="I241" s="2" t="inlineStr"/>
     </row>
     <row r="242" ht="92.59999999999999" customHeight="1">
       <c r="A242" s="2" t="n">
@@ -9149,8 +11092,16 @@
       <c r="G242" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H242" s="2" t="n"/>
-      <c r="I242" s="2" t="n"/>
+      <c r="H242" s="2" t="inlineStr">
+        <is>
+          <t>辦理現場安全衛生監督人員的安全衛生教育訓練不必於事前報請當地主管機關備查。
+職業安全衛生管理證照題庫練習
+相關規定說明
+現場安全衛生監督人員之訓練通常屬於事業單位內部自行辦理或一般性訓練，依規定不需像有害作業主管、危險性機械/設備操作人員或職業安全衛生人員等訓練，須於事前報請當地主管機關核備或備查。
+職業安全衛生管理證照題庫練習</t>
+        </is>
+      </c>
+      <c r="I242" s="2" t="inlineStr"/>
     </row>
     <row r="243" ht="92.59999999999999" customHeight="1">
       <c r="A243" s="2" t="n">
@@ -9184,8 +11135,18 @@
       <c r="G243" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H243" s="2" t="n"/>
-      <c r="I243" s="2" t="n"/>
+      <c r="H243" s="2" t="inlineStr">
+        <is>
+          <t>依據《職業安全衛生教育訓練規則》規定，相關實施資料應保存 3 年。
+新竹縣政府-勞工處
+重點整理
+正確答案：3 年
+應保存資料：包含訓練計畫、受訓人員名冊、簽到紀錄、課程內容及訓練教材等。
+法規依據：依據法規，雇主或訓練單位辦理一般安全衛生教育訓練等相關實施資料，至少應保存三年，以備主管機關查核。
+新竹縣政府-勞工處</t>
+        </is>
+      </c>
+      <c r="I243" s="2" t="inlineStr"/>
     </row>
     <row r="244" ht="92.59999999999999" customHeight="1">
       <c r="A244" s="2" t="n">
@@ -9219,8 +11180,12 @@
       <c r="G244" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H244" s="2" t="n"/>
-      <c r="I244" s="2" t="n"/>
+      <c r="H244" s="2" t="inlineStr">
+        <is>
+          <t>Google AI 摘要未抓取到，請手動補充。</t>
+        </is>
+      </c>
+      <c r="I244" s="2" t="inlineStr"/>
     </row>
     <row r="245" ht="92.59999999999999" customHeight="1">
       <c r="A245" s="2" t="n">
@@ -9254,8 +11219,19 @@
       <c r="G245" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H245" s="2" t="n"/>
-      <c r="I245" s="2" t="n"/>
+      <c r="H245" s="2" t="inlineStr">
+        <is>
+          <t>電焊機操作人員無須接受職業安全衛生教育訓練規則規定的特殊作業安全衛生教育訓練（電焊作業屬於一般安全衛生教育訓練或變更工作前之增列時數課程，而非第14條所規範的特殊作業類別）。
+相關法規對照
+依據《職業安全衛生教育訓練規則》第 14 條規定，雇主應使下列人員接受特殊作業安全衛生教育訓練：
+小型鍋爐操作人員（應接受訓練）
+荷重在 1 公噸以上之堆高機操作人員（應接受訓練）
+使用起重機具從事吊掛作業人員（應接受訓練）
+電焊機操作人員：不屬於第 14 條規定的特殊作業訓練對象，電焊作業勞工係於新僱或變更工作時接受一般安全衛生教育訓練並增列相應時數。
+中國勞工安全衛生管理學會</t>
+        </is>
+      </c>
+      <c r="I245" s="2" t="inlineStr"/>
     </row>
     <row r="246" ht="92.59999999999999" customHeight="1">
       <c r="A246" s="2" t="n">
@@ -9289,8 +11265,22 @@
       <c r="G246" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H246" s="2" t="n"/>
-      <c r="I246" s="2" t="n"/>
+      <c r="H246" s="2" t="inlineStr">
+        <is>
+          <t>以乙炔熔接裝置或氣體集合裝置從事金屬熔接、切斷或加熱作業之人員，應接受特殊作業安全衛生教育訓練。
+職業安全衛生教育訓練
+依據《職業安全衛生教育訓練規則》規定，此類作業屬於特殊作業類別，訓練時數不得少於 18 小時，且從業人員應每 3 年接受至少 3 小時之在職教育訓練。
+中華民國職業安全衛生協會 需要了解該訓練的課程時數與大綱嗎？
+課程時數與內容
+在職回訓規定
+報名受訓資格
+職業安全衛生教育訓練
+常用法令資訊 - 職業安全衛生教育訓練暨電腦測驗資訊網
+依職業安全衛生教育訓練規則（下稱訓練規則）第14條第1項第8款規定，雇主對於以乙炔熔接裝置或氣體集合熔接裝置從事金屬之熔接、切斷或加熱作業人員，應使其接受特殊作業 ...
+顯示全部 內容</t>
+        </is>
+      </c>
+      <c r="I246" s="2" t="inlineStr"/>
     </row>
     <row r="247" ht="92.59999999999999" customHeight="1">
       <c r="A247" s="2" t="n">
@@ -9324,8 +11314,13 @@
       <c r="G247" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H247" s="2" t="n"/>
-      <c r="I247" s="2" t="n"/>
+      <c r="H247" s="2" t="inlineStr">
+        <is>
+          <t>依職業安全衛生教育訓練規則規定，職業安全衛生委員會成員之職業安全衛生在職教育訓練時數為每 3 年 3 小時（對應法規為第七款至第十三款之勞工，每三年至少三小時）。
+正確選項為：每 3 年 3 小時。</t>
+        </is>
+      </c>
+      <c r="I247" s="2" t="inlineStr"/>
     </row>
     <row r="248" ht="92.59999999999999" customHeight="1">
       <c r="A248" s="2" t="n">
@@ -9359,8 +11354,20 @@
       <c r="G248" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H248" s="2" t="n"/>
-      <c r="I248" s="2" t="n"/>
+      <c r="H248" s="2" t="inlineStr">
+        <is>
+          <t>有誤的敘述為：(A) 事業單位不具辦理資格，應指派勞工至職業訓練機構受訓。
+原因說明
+選項 (A) 的錯誤之處：依據職業安全衛生教育訓練規則第20條規定，安全衛生之教育訓練單位包含「事業單位」本身。因此，事業單位符合條件是可以自行辦理教育訓練的，並非「不具辦理資格」而一定得指派勞工至外面的職業訓練機構受訓。
+其他選項皆正確：
+(B) 對於已取得資格的勞工，應定期分別使其接受在職教育訓練（回訓）。
+(C) 訓練單位辦理相關作業（如鍋爐操作人員）教育訓練時，依法應向當地主管機關報備/核備。
+(D) 依同規則第14條，雇主對於小型鍋爐操作人員，應使其接受特殊作業安全衛生教育訓練。
+社團法人中華民國技能發展協會 .下列有關職業安全衛生教育訓練之辦理方式，下列敘述何者 ...
+2019年9月1日 — 32.下列有關職業安全衛生教育訓練之辦理方式，下列敘述何者有誤？ (A)對於已取得資格之不 同職類勞工，應定期分別使其接受在職教育訓練 (B)事業單位不具辦理資格，應指派勞工至職 業訓練機構受訓 (C)訓練單位辦理鍋爐操作人員教育訓練，應向當地主管機關報備 (</t>
+        </is>
+      </c>
+      <c r="I248" s="2" t="inlineStr"/>
     </row>
     <row r="249" ht="92.59999999999999" customHeight="1">
       <c r="A249" s="2" t="n">
@@ -9394,8 +11401,18 @@
       <c r="G249" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H249" s="2" t="n"/>
-      <c r="I249" s="2" t="n"/>
+      <c r="H249" s="2" t="inlineStr">
+        <is>
+          <t>勞工參加職業安全衛生教育訓練，缺課時數達課程總時數五分之一以上時，訓練單位應通知其退訓。
+正確答案為：五分之一。
+重點說明
+退訓標準：依據《職業安全衛生教育訓練規則》第33條規定，受訓學員缺課時數若達到課程總時數的 1/5 以上，訓練單位必須強制通知退訓。
+補課規定：學員若請假超過3小時或有曠課情形（但未達退訓的 1/5 標準），訓練單位應通知其補足全部缺課的課程與時數。
+Facebook
+·臺北市政府勞動局 - 勞動臺北</t>
+        </is>
+      </c>
+      <c r="I249" s="2" t="inlineStr"/>
     </row>
     <row r="250" ht="92.59999999999999" customHeight="1">
       <c r="A250" s="2" t="n">
@@ -9429,8 +11446,18 @@
       <c r="G250" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H250" s="2" t="n"/>
-      <c r="I250" s="2" t="n"/>
+      <c r="H250" s="2" t="inlineStr">
+        <is>
+          <t>依據相關法規（現行《勞工職業災害保險及保護法》第88條及原《職業災害勞工保護法》第29條規定），職業災害未認定前，勞工無法上班時，應先請普通傷病假。
+處理原則
+先請普通傷病假：勞工得依規定先請普通傷病假。
+後續留職停薪：若普通傷病假期滿仍須治療休養，申請留職停薪者，雇主應予留職停薪。
+追溯改為公傷病假：經後續認定結果確屬職業災害者，雇主應再將該段期間改以公傷病假處理。
+臺北市政府全球資訊網 因此，正確選項為：先請普通傷病假。
+桃園市政府勞動局</t>
+        </is>
+      </c>
+      <c r="I250" s="2" t="inlineStr"/>
     </row>
     <row r="251" ht="92.59999999999999" customHeight="1">
       <c r="A251" s="2" t="n">
@@ -9464,8 +11491,12 @@
       <c r="G251" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H251" s="2" t="n"/>
-      <c r="I251" s="2" t="n"/>
+      <c r="H251" s="2" t="inlineStr">
+        <is>
+          <t>Google AI 摘要未抓取到，請手動補充。</t>
+        </is>
+      </c>
+      <c r="I251" s="2" t="inlineStr"/>
     </row>
     <row r="252" ht="92.59999999999999" customHeight="1">
       <c r="A252" s="2" t="n">
@@ -9499,8 +11530,15 @@
       <c r="G252" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H252" s="2" t="n"/>
-      <c r="I252" s="2" t="n"/>
+      <c r="H252" s="2" t="inlineStr">
+        <is>
+          <t>依據《職業災害勞工保護法》第23條（現行相關規定亦見於《勞工職業災害保險及保護法》第84條）之規定，非有下列情形之一者，雇主不得預告終止與職業災害勞工之勞動契約：
+歇業或重大虧損，報經主管機關核定。
+職業災害勞工經醫療終止後，經公立醫療機構認定身心障礙（心神喪失或身體殘廢）不堪勝任工作者。
+因天災、事變或其他不可抗力因素，致事業不能繼續經營，報經主管機關核定。</t>
+        </is>
+      </c>
+      <c r="I252" s="2" t="inlineStr"/>
     </row>
     <row r="253" ht="92.59999999999999" customHeight="1">
       <c r="A253" s="2" t="n">
@@ -9534,8 +11572,14 @@
       <c r="G253" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H253" s="2" t="n"/>
-      <c r="I253" s="2" t="n"/>
+      <c r="H253" s="2" t="inlineStr">
+        <is>
+          <t>答案為：(D) 育嬰津貼。
+育嬰留職停薪津貼是依據《就業保險法》所提供的給付，而非屬《職業災害勞工保護法》（現相關規定多已納入《勞工職業災害保險及保護法》）之職業災害補助範圍。職業災害勞工保護法提供的補助包含生活津貼、看護補助、職業訓練生活津貼、失能及死亡補助等，並無「家屬補助」與「育嬰津貼」，但在該題選項中，育嬰津貼為就業保險範疇，且題目的標準答案為 (D) 育嬰津貼（註：部分舊法或考題中家屬津貼/補助亦不屬於，但此題典型考法之解答為育嬰津貼）。
+勞動力發展署技能檢定中心</t>
+        </is>
+      </c>
+      <c r="I253" s="2" t="inlineStr"/>
     </row>
     <row r="254" ht="92.59999999999999" customHeight="1">
       <c r="A254" s="2" t="n">
@@ -9569,8 +11613,14 @@
       <c r="G254" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H254" s="2" t="n"/>
-      <c r="I254" s="2" t="n"/>
+      <c r="H254" s="2" t="inlineStr">
+        <is>
+          <t>依職業災害勞工保護法規定，事業單位、職業訓練機構及相關團體辦理加強職業災害預防及職業災害勞工之重建事項，得向勞工保險局申請補助。
+相關法源依據
+職業災害勞工保護法第10條：為加強職業災害預防及職業災害勞工之重建，事業單位、職業訓練機構及相關團體辦理相關事項（如職業災害之研究、職業疾病之防治等），得向勞工保險局申請補助。</t>
+        </is>
+      </c>
+      <c r="I254" s="2" t="inlineStr"/>
     </row>
     <row r="255" ht="92.59999999999999" customHeight="1">
       <c r="A255" s="2" t="n">
@@ -9604,8 +11654,13 @@
       <c r="G255" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H255" s="2" t="n"/>
-      <c r="I255" s="2" t="n"/>
+      <c r="H255" s="2" t="inlineStr">
+        <is>
+          <t>依據舊版《職業災害勞工保護法》第8條第3項（相關法規及補助辦法）規定，罹患職業疾病喪失部分或所領取之各項生活津貼，合計以 5年 為限。
+花蓮縣勞工e網 正確答案為：(A) 5 年。</t>
+        </is>
+      </c>
+      <c r="I255" s="2" t="inlineStr"/>
     </row>
     <row r="256" ht="92.59999999999999" customHeight="1">
       <c r="A256" s="2" t="n">
@@ -9639,8 +11694,19 @@
       <c r="G256" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H256" s="2" t="n"/>
-      <c r="I256" s="2" t="n"/>
+      <c r="H256" s="2" t="inlineStr">
+        <is>
+          <t>✅ 照護補助
+💡 補助說明
+申請條件：
+因職業傷病致終身無工作能力
+喪失全部或部分生活自理能力
+經常需醫療護理及專人周密照護，或需他人扶助
+法律依據：
+《勞工職業災害保險及保護法》第80條第2款</t>
+        </is>
+      </c>
+      <c r="I256" s="2" t="inlineStr"/>
     </row>
     <row r="257" ht="77.15000000000001" customHeight="1">
       <c r="A257" s="2" t="n">
@@ -9674,8 +11740,12 @@
       <c r="G257" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H257" s="2" t="n"/>
-      <c r="I257" s="2" t="n"/>
+      <c r="H257" s="2" t="inlineStr">
+        <is>
+          <t>Google AI 摘要未抓取到，請手動補充。</t>
+        </is>
+      </c>
+      <c r="I257" s="2" t="inlineStr"/>
     </row>
     <row r="258" ht="92.59999999999999" customHeight="1">
       <c r="A258" s="2" t="n">
@@ -9709,8 +11779,16 @@
       <c r="G258" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H258" s="2" t="n"/>
-      <c r="I258" s="2" t="n"/>
+      <c r="H258" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+勞工於高度二公尺以上場所工作，未有合乎規定之工作臺或防護網等措施而導致傷害，其原因應歸類為不安全狀態。
+原因解析
+不安全狀態（Unsafe Condition）：指物體、設備、環境本身的缺陷，或缺乏必要的安全防護設施（如未設置合規的工作臺、護欄或防護網），屬於客觀環境與硬體上的不足。
+不安全動作：指人員自身的行為不當或違反作業規定（例如未佩戴安全帶）。</t>
+        </is>
+      </c>
+      <c r="I258" s="2" t="inlineStr"/>
     </row>
     <row r="259" ht="92.59999999999999" customHeight="1">
       <c r="A259" s="2" t="n">
@@ -9744,8 +11822,16 @@
       <c r="G259" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H259" s="2" t="n"/>
-      <c r="I259" s="2" t="n"/>
+      <c r="H259" s="2" t="inlineStr">
+        <is>
+          <t>未使用防護具屬不安全行為。
+原因解析
+不安全行為（人為缺失）：指因人員疏忽、未遵守規定或未採取防護措施所造成的狀況，例如未使用防護具、未依標準作業程序操作等。
+不安全狀況（環境或設備缺失）：指硬體或環境本身存在缺陷，如不適當的支撐或防護、不適當警告裝置以及有缺陷的設備，皆屬於不安全狀況（或稱不安全環境/狀態）。
+NTNU</t>
+        </is>
+      </c>
+      <c r="I259" s="2" t="inlineStr"/>
     </row>
     <row r="260" ht="92.59999999999999" customHeight="1">
       <c r="A260" s="2" t="n">
@@ -9779,8 +11865,17 @@
       <c r="G260" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H260" s="2" t="n"/>
-      <c r="I260" s="2" t="n"/>
+      <c r="H260" s="2" t="inlineStr">
+        <is>
+          <t>每一個人都有責任。
+在職業安全衛生（職安衛）的觀念中，安全不是某個特定職位的專屬工作，而是全員參與的共同責任。不同角色在廠區內承擔不同的職責：
+廠長（雇主/經營負責人）：承擔最終的法律與管理責任。負責編列安全預算、推動安全政策、提供安全的設備與工作環境。
+安全衛生管理人員：承擔規劃與擬訂的責任。負責規劃安全衛生管理計畫、提供專業諮詢、進行巡檢及職災統計分析，是「幕僚」與「協助者」。
+領班（現場指揮監督人員）：承擔現場指揮與監督的責任。負責確實執行安全管理、監督作業人員是否佩戴防護具、維持現場落實安全規定。
+每一個人（基層員工）：承擔確實遵守與執行的責任。必須遵守安全作業標準（SOP）、正確佩戴防護具、接受安全培訓，並主動回報現場的異常狀況。</t>
+        </is>
+      </c>
+      <c r="I260" s="2" t="inlineStr"/>
     </row>
     <row r="261" ht="92.59999999999999" customHeight="1">
       <c r="A261" s="2" t="n">
@@ -9814,8 +11909,14 @@
       <c r="G261" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H261" s="2" t="n"/>
-      <c r="I261" s="2" t="n"/>
+      <c r="H261" s="2" t="inlineStr">
+        <is>
+          <t>答案是噪音。
+粗心、遲鈍與不使用防護器具都屬於個人行為或心理、生理狀態所導致的不安全個人因素（不安全行為）。
+噪音則是外在工作環境中的物理性危害因子，並非由個人自身因素所造成。</t>
+        </is>
+      </c>
+      <c r="I261" s="2" t="inlineStr"/>
     </row>
     <row r="262" ht="92.59999999999999" customHeight="1">
       <c r="A262" s="2" t="n">
@@ -9849,8 +11950,13 @@
       <c r="G262" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H262" s="2" t="n"/>
-      <c r="I262" s="2" t="n"/>
+      <c r="H262" s="2" t="inlineStr">
+        <is>
+          <t>失能傷害（Disabling Injury）是指受傷工人損失時間超過 24 小時。
+在勞工安全衛生與職業災害統計中，失能傷害是指在工作時間內因工作原因導致的傷害，且其傷害程度使得受傷者在受傷翌日（隔天）起無法繼續工作，亦即損失工作時間達到一個工作日（通常以 24 小時計算）以上。</t>
+        </is>
+      </c>
+      <c r="I262" s="2" t="inlineStr"/>
     </row>
     <row r="263" ht="77.15000000000001" customHeight="1">
       <c r="A263" s="2" t="n">
@@ -9884,8 +11990,15 @@
       <c r="G263" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H263" s="2" t="n"/>
-      <c r="I263" s="2" t="n"/>
+      <c r="H263" s="2" t="inlineStr">
+        <is>
+          <t>根據我國《職業安全衛生法》等相關勞動法規，這題的正確答案是以上皆是。
+詳細的法規依據與說明如下：
+經依罰則處分之事業單位：根據《職業安全衛生法》第 49 條規定，對於違反該法規定受罰鍰、停工等行政處分的事業單位，主管機關「應」公布其事業單位、雇主或機構之名稱及姓名。
+事業單位發生重大職業災害 / 職業病：為了保障勞工知情權並促進公共安全，當事業單位發生重大職災（如死亡事故）或群聚性職業病時，主管機關通常會依法或依政府資訊公開原則，公布相關事業單位名稱，以督促企業改善並提醒社會大眾注意。</t>
+        </is>
+      </c>
+      <c r="I263" s="2" t="inlineStr"/>
     </row>
     <row r="264" ht="92.59999999999999" customHeight="1">
       <c r="A264" s="2" t="n">
@@ -9919,8 +12032,17 @@
       <c r="G264" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H264" s="2" t="n"/>
-      <c r="I264" s="2" t="n"/>
+      <c r="H264" s="2" t="inlineStr">
+        <is>
+          <t>人員進行機械設備維修保養時，最正確的安全程序是：關閉電源、掛牌、上鎖（這通常被稱為 LOTO，即 Lockout/Tagout 危害能量控制程序）。
+完整的安全步驟通常包括：
+辨識能源：確認設備的所有動力來源（如電能、氣壓、液壓等）。
+關閉電源：確實將設備停機並切斷所有能源供應。
+掛牌上鎖：在隔離裝置上鎖上個人安全鎖，並懸掛警告標牌（註明維修人員、時間與事由），防止他人誤開。
+確認零能狀態：釋放殘留能量（如管道餘壓、電容殘電），並測試啟動確認設備已完全無法運作，方可開始維護。</t>
+        </is>
+      </c>
+      <c r="I264" s="2" t="inlineStr"/>
     </row>
     <row r="265" ht="92.59999999999999" customHeight="1">
       <c r="A265" s="2" t="n">
@@ -9954,8 +12076,18 @@
       <c r="G265" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H265" s="2" t="n"/>
-      <c r="I265" s="2" t="n"/>
+      <c r="H265" s="2" t="inlineStr">
+        <is>
+          <t>「作業環境監測」為危害的(B) 評估方法。
+在職業衛生與安全管理中，處理職場危害主要分為四大步驟：
+認知：辨識、發現工作場所中有哪些潛在的危害因子（例如查閱化學品安全資料表、現場巡視）。
+評估：透過科學的作業環境監測、採樣與分析，測定有害因子的濃度或強度，並與法令容許標準比較，藉此確認勞工實際的暴露風險與嚴重程度。
+控制：根據評估結果採取改善措施（如工程控制、局部排氣、個人防護具等）以降低風險。
+偵測：通常指即時警報或偵檢裝置（如氣體外洩偵測器），而系統性的環境測量與暴露評估則歸類在評估階段。
+勞工作業環境監測及暴露危害管理</t>
+        </is>
+      </c>
+      <c r="I265" s="2" t="inlineStr"/>
     </row>
     <row r="266" ht="92.59999999999999" customHeight="1">
       <c r="A266" s="2" t="n">
@@ -9989,8 +12121,17 @@
       <c r="G266" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H266" s="2" t="n"/>
-      <c r="I266" s="2" t="n"/>
+      <c r="H266" s="2" t="inlineStr">
+        <is>
+          <t>職業災害的直接損失與間接損失相比較，正確答案為：直接損失小於間接損失。
+損失比較說明
+直接損失：指職災造成之金錢與實體直接損失，例如醫療費用及保險給付等。
+間接損失：指事故引發的後續無形成本，如生產中斷、調查成本、士氣低落及停工時間損失等。
+比例關係：依據工安統計經驗，間接損失通常約為直接損失的 4 到 5 倍（即直接損失小於間接損失）。
+iPEDIA 百科</t>
+        </is>
+      </c>
+      <c r="I266" s="2" t="inlineStr"/>
     </row>
     <row r="267" ht="92.59999999999999" customHeight="1">
       <c r="A267" s="2" t="n">
@@ -10024,8 +12165,17 @@
       <c r="G267" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H267" s="2" t="n"/>
-      <c r="I267" s="2" t="n"/>
+      <c r="H267" s="2" t="inlineStr">
+        <is>
+          <t>這題的正確答案是：以上皆是。
+在職業安全衛生領域中，「不安全的動作」（或稱不安全行為）是指人員因為自身的疏忽、貪圖方便或缺乏安全意識，而做出違反安全規範的舉動。
+選項中的三種行為都屬於典型的不安全的動作：
+擅入禁止進入之作業場所：違反現場安全管制，使自己暴露於未知的危險環境中。
+為操作便利，使設置之安全裝置失效：私自拆除、跨接或關閉安全開關、護罩等防護設施，極易導致嚴重外傷或捲夾事故。
+未著用應使用之必要防護具：未依規定配戴安全帽、護目鏡、防滑鞋或防墜安全帶等，一旦發生意外將失去最後一線保護。</t>
+        </is>
+      </c>
+      <c r="I267" s="2" t="inlineStr"/>
     </row>
     <row r="268" ht="92.59999999999999" customHeight="1">
       <c r="A268" s="2" t="n">
@@ -10059,8 +12209,14 @@
       <c r="G268" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H268" s="2" t="n"/>
-      <c r="I268" s="2" t="n"/>
+      <c r="H268" s="2" t="inlineStr">
+        <is>
+          <t>一般安全衛生之工作，下列何者為非？答案為 (C) 量測。
+Quizlet 工業衛生與職業安全的核心工作流程一般包含「認知（Recognition）、評估（Evaluation）、控制（Control）」三大主軸（部分會加入辨識），而「量測」並非基本四大程序中的標準概念或非其典型稱謂。
+Quizlet</t>
+        </is>
+      </c>
+      <c r="I268" s="2" t="inlineStr"/>
     </row>
     <row r="269" ht="92.59999999999999" customHeight="1">
       <c r="A269" s="2" t="n">
@@ -10094,8 +12250,15 @@
       <c r="G269" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H269" s="2" t="n"/>
-      <c r="I269" s="2" t="n"/>
+      <c r="H269" s="2" t="inlineStr">
+        <is>
+          <t>為加強及提升各級人員安全衛生意識，根本作法是(B) 加強教育訓練。
+說明
+教育訓練能直接建立人員對危害的認知、正確的安全觀念與防護技能，是提升安全衛生意識與形塑安全文化的根本方法。
+其他選項如環境管理、作業管理與稽核（查核）制度雖同為安全管理的重要環節，但多屬於制度面、環境面或監督面的控制手段，而非形塑人員內在意識的根本作法。</t>
+        </is>
+      </c>
+      <c r="I269" s="2" t="inlineStr"/>
     </row>
     <row r="270" ht="92.59999999999999" customHeight="1">
       <c r="A270" s="2" t="n">
@@ -10129,8 +12292,15 @@
       <c r="G270" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H270" s="2" t="n"/>
-      <c r="I270" s="2" t="n"/>
+      <c r="H270" s="2" t="inlineStr">
+        <is>
+          <t>答案是 (A) 機械防護措施之缺陷。
+原因解析
+不安全狀態（Unsafe Condition）：是指物體、機械設備或工作環境本身存在、可能導致災害的缺陷。「機械防護措施之缺陷」屬於客觀環境與設備本身的缺失，因此是不安全狀態。
+不安全行為（Unsafe Act）：是指人員因疏忽、便宜行事或違反規定而產生的行為。選項中的 錯誤的操作、使安全裝置失效 以及 使用指定外之機械，皆屬於人為操作不當或違規的「不安全行為」。</t>
+        </is>
+      </c>
+      <c r="I270" s="2" t="inlineStr"/>
     </row>
     <row r="271" ht="92.59999999999999" customHeight="1">
       <c r="A271" s="2" t="n">
@@ -10164,8 +12334,17 @@
       <c r="G271" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H271" s="2" t="n"/>
-      <c r="I271" s="2" t="n"/>
+      <c r="H271" s="2" t="inlineStr">
+        <is>
+          <t>因安全衛生管理不良而導致職業災害發生，屬於基本原因。
+職業災害原因分類
+基本原因 (Basic Causes)：指潛在管理系統的缺陷或管理上的缺失（如未訂定安全衛生政策、未提供適當防護、教育訓練不足等），進而導致不安全行為或不安全狀態。
+間接原因 (Indirect Causes)：指物體的不安全狀況（如設備故障、無防護設施）或人的不安全動作（如未依標準作業程序操作）。
+直接原因 (Direct Causes)：指人員直接接觸能量（如電能、機械能）或危害物，或發生墜落、撞擊等造成傷害的物理現象。
+iPEDIA 百科</t>
+        </is>
+      </c>
+      <c r="I271" s="2" t="inlineStr"/>
     </row>
     <row r="272" ht="92.59999999999999" customHeight="1">
       <c r="A272" s="2" t="n">
@@ -10199,8 +12378,16 @@
       <c r="G272" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H272" s="2" t="n"/>
-      <c r="I272" s="2" t="n"/>
+      <c r="H272" s="2" t="inlineStr">
+        <is>
+          <t>安全衛生管理不善是職業災害發生的基本原因，而非間接原因。
+Quizlet 職業災害原因分類說明
+直接原因：人體直接接觸能量或危害物（如機械能、電能、化學能等）。
+間接原因：屬於不安全動作（如未依標準作業程序操作）與不安全狀況（如未提供安全設備、未提供安全護具）。
+基本原因：屬於潛在管理系統的缺陷或缺失（如安全衛生管理不善）。</t>
+        </is>
+      </c>
+      <c r="I272" s="2" t="inlineStr"/>
     </row>
     <row r="273" ht="92.59999999999999" customHeight="1">
       <c r="A273" s="2" t="n">
@@ -10234,8 +12421,18 @@
       <c r="G273" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H273" s="2" t="n"/>
-      <c r="I273" s="2" t="n"/>
+      <c r="H273" s="2" t="inlineStr">
+        <is>
+          <t>「須在工作場所發生」非職業災害須具備之要件（正確答案選 C）。
+職業災害的三大核心要件
+具有工作者（勞工）身份：受僱或受指揮監督從事勞動獲得報酬。
+生理上的傷害（或疾病/失能/死亡）：造成身體健康的實質危害。
+職業上的原因：災害與工作活動、工作環境或職務執行具有因果關係。
+為什麼「須在工作場所發生」不是必要要件？
+職業災害不限於狹義的「工作場所（廠房、辦公室內）」。只要是在雇主指揮監督或勞務管理必要下，例如上下班通勤途中發生車禍、因公出差在外、或是前往特定作業地點的途中，符合職業上原因與職務關聯性，也常被認定為職業災害（公傷）。</t>
+        </is>
+      </c>
+      <c r="I273" s="2" t="inlineStr"/>
     </row>
     <row r="274" ht="92.59999999999999" customHeight="1">
       <c r="A274" s="2" t="n">
@@ -10269,8 +12466,71 @@
       <c r="G274" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H274" s="2" t="n"/>
-      <c r="I274" s="2" t="n"/>
+      <c r="H274" s="2" t="inlineStr">
+        <is>
+          <t>勞工不遵守安全衛生工作守則規定，屬於不安全行為。
+顯示更多
+網頁搜尋結果
+140. 勞工不遵守安全衛生工作手則規定，屬於下列何者? (A) ...
+› item-140.+勞工不遵守安全衛生工作...
+2024年6月18日 — 41.勞工不遵守安全衛生工作守則規定，屬於下列何者？(A)不安全環境(B)不安全行為(C)管理缺陷(D)不安全設備。
+7. 勞工不遵守安全衛生工作守則規定，屬於下列何者？ (A) ...
+› item-7.+勞工不遵守安全衛生工作守...
+2025年8月14日 — 7. 勞工不遵守安全衛生工作守則規定，屬於下列何者？ (A)不安全環境(B)不安全行為(C)管理缺陷(D)不安全設備。，包含題目內容、選項、詳解等， ...
+題庫/ 網頁設計(丙) / 01.職業安全衛生17300
+BLOCK 學習網
+› question
+勞工不遵守安全衛生工作守則規定，屬於下列何者？ A 不安全設備. B 不安全行為. C 不安全環境. D 管理缺陷. 答案. 本網站提供的試題，僅供自我練習，並不保証完全正確。
+缺少字詞： 公害 ‎| 必須包含以下字詞： 公害
+9.勞工不遵守安全衛生工作手則規定，屬於下列何者? (A) ...
+› item-9.勞工不遵守安全衛生工作手則...
+2024年5月14日 — 41.勞工不遵守安全衛生工作守則規定，屬於下列何者？(A)不安全環境(B)不安全行為(C)管理缺陷(D)不安全設備。
+一、法規與通識(四) 職業安全衛生概論545-600
+› document › 一-法規與通識-...
+勞工不遵守安全衛生工作守則規定,屬於下列何者?(1)不安全環境(2)公害(3)不安全. 行為(4)不安全設備。 (1) 568. 職業災害發生之原因可分為直接原因、間接原因及基本原因 ...
+相關問題
+勞工不遵守安全衛生工作守則規定,屬於哪一種行為?
+勞工不遵守安全衛生工作守則會受到什麼樣的處罰?
+勞工不遵守安全衛生工作守則 可處新臺幣多少元罰鍰？
+依 職業安全 衛生管理 辦法規定 下列 哪些 機械 設備 於 開始 使用 時 須 實施 重點 檢查？
+網頁搜尋結果
+87. 勞工不遵守安全衛生工作守則規定，屬於下列何者？ (A) ...
+› item-87.+勞工不遵守安全衛生工作守...
+2025年12月30日 — 9. 勞工不遵守安全衛生工作守則規定，屬於下列何者？ (A)不安全設備(B)管理缺陷(C)不安全環境(D)不安全行為。 ... 87. 勞工不遵守安全衛生工作守則規定， ...
+缺少字詞： 公害 ‎| 必須包含以下字詞： 公害
+工(職)業安全衛生教育題庫
+國立岡山高級農工職業學校
+› ...
+PDF
+762 ( A ) 勞工違反安全衛生工作守則者，可處新台幣(A)三仟元(B)六仟元(C). 九仟元以下罰鍰。 763 ( C ) 下列何者不是勞工的安全義務(A)遵守安全衛生規則(B)報告不安全情 ...
+題庫/ 照顧服務員(單) / 01.職業安全衛生 ...
+BLOCK 學習網
+› question
+勞工不遵守安全衛生工作守則規定，屬於下列何者？ A 不安全設備. B 不安全行為. C 不安全環境. D 管理缺陷. 答案. 8 88. 下列何者不屬於局限空間內作業場所應採取之缺氧 ...
+缺少字詞： 公害 ‎| 必須包含以下字詞： 公害
+30. 勞工不遵守安全衛生工作守則規定，屬於下列何者？ (A) ...
+› item-30.+勞工不遵守安全衛生工作守...
+2025年8月11日 — 30. 勞工不遵守安全衛生工作守則規定，屬於下列何者？ (A)不安全設備(B)管理缺陷(C)不安全行為(D)不安全環境。，包含題目內容、選項、詳解等， ...
+頁面導覽
+1
+2
+3
+4
+5
+6
+7
+下一頁
+頁尾連結
+台灣
+708 臺南市安平區 - 根據你的 IP 位址
+- 更新位置
+說明
+提供意見
+隱私權
+服務條款</t>
+        </is>
+      </c>
+      <c r="I274" s="2" t="inlineStr"/>
     </row>
     <row r="275" ht="92.59999999999999" customHeight="1">
       <c r="A275" s="2" t="n">
@@ -10304,8 +12564,17 @@
       <c r="G275" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H275" s="2" t="n"/>
-      <c r="I275" s="2" t="n"/>
+      <c r="H275" s="2" t="inlineStr">
+        <is>
+          <t>能量係屬職業災害發生的直接原因。
+職業災害原因分類
+直接原因：人體直接接觸能量或危害物（如機械能、電能、化學能、熱能等）。
+間接原因：包含不安全行為（人為缺失）與不安全狀況（環境缺失）。
+基本原因：源自管理上的缺陷（如教育訓練不足、未落實安全衛生管理系統等）。
+iPEDIA 百科</t>
+        </is>
+      </c>
+      <c r="I275" s="2" t="inlineStr"/>
     </row>
     <row r="276" ht="92.59999999999999" customHeight="1">
       <c r="A276" s="2" t="n">
@@ -10339,8 +12608,12 @@
       <c r="G276" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H276" s="2" t="n"/>
-      <c r="I276" s="2" t="n"/>
+      <c r="H276" s="2" t="inlineStr">
+        <is>
+          <t>Google AI 摘要未抓取到，請手動補充。</t>
+        </is>
+      </c>
+      <c r="I276" s="2" t="inlineStr"/>
     </row>
     <row r="277" ht="92.59999999999999" customHeight="1">
       <c r="A277" s="2" t="n">
@@ -10374,8 +12647,16 @@
       <c r="G277" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H277" s="2" t="n"/>
-      <c r="I277" s="2" t="n"/>
+      <c r="H277" s="2" t="inlineStr">
+        <is>
+          <t>交流電焊機未設置自動電擊防止裝置致勞工感電，其災害之間接原因是不安全設備（或稱不安全狀況）。
+原因解析
+不安全設備（Unsafe Equipment / Unsafe Condition）：電焊機本身屬於硬體與機械設備，未依規定裝設或提供防止感電的「自動電擊防止裝置」，屬於客觀物質條件上的缺失。
+不安全動作：指人員未依標準作業程序或疏忽操作，非機械本身未設置裝置之問題。
+中華民國勞工安全衛生教育協會</t>
+        </is>
+      </c>
+      <c r="I277" s="2" t="inlineStr"/>
     </row>
     <row r="278" ht="92.59999999999999" customHeight="1">
       <c r="A278" s="2" t="n">
@@ -10409,8 +12690,16 @@
       <c r="G278" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H278" s="2" t="n"/>
-      <c r="I278" s="2" t="n"/>
+      <c r="H278" s="2" t="inlineStr">
+        <is>
+          <t>設備安裝作業的潛在危害答案為(D)以上皆是（包含切割傷、倒塌、墜落等風險）。
+潛在危害說明
+切割傷：在搬運金屬設備、使用工具安裝或修邊時，容易發生割傷。
+倒塌：大型設備固定不當、臨時支撐失效或吊掛重心不穩時，可能發生傾斜倒塌。
+墜落：在高處、開口部分或施工架上進行設備安裝時，若防護不足容易發生墜落。</t>
+        </is>
+      </c>
+      <c r="I278" s="2" t="inlineStr"/>
     </row>
     <row r="279" ht="92.59999999999999" customHeight="1">
       <c r="A279" s="2" t="n">
@@ -10444,8 +12733,15 @@
       <c r="G279" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H279" s="2" t="n"/>
-      <c r="I279" s="2" t="n"/>
+      <c r="H279" s="2" t="inlineStr">
+        <is>
+          <t>造成事業單位形象受損屬間接損失。
+損失分類說明
+直接損失：包含保險賠償、醫療費用、法定補償及工資損失等金錢直接支出。
+間接損失：包含企業信譽與形象受損、員工士氣低落、生產力下降及管理成本增加等無形或連帶損失。</t>
+        </is>
+      </c>
+      <c r="I279" s="2" t="inlineStr"/>
     </row>
     <row r="280" ht="92.59999999999999" customHeight="1">
       <c r="A280" s="2" t="n">
@@ -10479,8 +12775,16 @@
       <c r="G280" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H280" s="2" t="n"/>
-      <c r="I280" s="2" t="n"/>
+      <c r="H280" s="2" t="inlineStr">
+        <is>
+          <t>關於樓地板開口（施工安全）的敘述，「拿模板蓋起來即可」是錯誤的（非）。
+根據營造安全衛生設施標準與勞安法規，針對樓地板開口的防護措施有嚴格規定：
+護欄要求： 開口應設置高度 90 公分以上之防護欄杆。
+安全網設置： 如果無法設置護欄，應裝設安全網或佩戴安全帶。
+護蓋規範： 若使用護蓋，材質必須堅固並確實固定，不得有滑動、移位或脫落之虞，且必須塗上警告漆或標示「構造物開口危險」等字樣，絕對不能只是「拿模板隨便蓋起來即可」。</t>
+        </is>
+      </c>
+      <c r="I280" s="2" t="inlineStr"/>
     </row>
     <row r="281" ht="92.59999999999999" customHeight="1">
       <c r="A281" s="2" t="n">
@@ -10514,8 +12818,15 @@
       <c r="G281" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H281" s="2" t="n"/>
-      <c r="I281" s="2" t="n"/>
+      <c r="H281" s="2" t="inlineStr">
+        <is>
+          <t>工作用電動器具突然不動時，應立即報告主管處理，避免自行拆解發生觸電或機械傷害等危險。
+處理原則
+正確做法：(B) 報告主管。交由專業維修人員或依公司規定處理。
+嚴禁行為：(A) 自行拆開修理。非專業維修人員擅自拆卸電器，容易導致觸電、短路或零件損壞加劇。</t>
+        </is>
+      </c>
+      <c r="I281" s="2" t="inlineStr"/>
     </row>
     <row r="282" ht="92.59999999999999" customHeight="1">
       <c r="A282" s="2" t="n">
@@ -10549,8 +12860,22 @@
       <c r="G282" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H282" s="2" t="n"/>
-      <c r="I282" s="2" t="n"/>
+      <c r="H282" s="2" t="inlineStr">
+        <is>
+          <t>進入大型攪拌槽內部清理結塊時，較不易發生下列何種危害？正確答案是：被撞。
+危害分析簡述
+被撞：因為進入靜止的槽內進行清理結塊，機具在作業時已斷電停機，通常不會有外來移動物體或車輛直接撞擊的情況，因此相較之下「被撞」是較不易發生的危害。
+被夾、被捲：若未確實切斷電源或上鎖標示，機械誤動時極易發生捲夾。
+墜落：槽體深且內部踏面不穩，容易發生高處或內部跌落。
+缺氧：大型攪拌槽常屬於局限空間，通風不良易導致缺氧。
+想了解更多局限空間作業安全的注意事項嗎？
+缺氧與中毒預防
+危害防止計畫與通風
+緊急救援設備規定
+一般業業務主管參考練習題112 08 20有解答 - (1)從事缺氧危險作業時之人員安排，下列何者較佳？①無論作業人數，應指派1 人以上之監視人員②避免與他人一起作業，以免他人不專業致干擾及妨礙作業安全之危害③若2 人以上同時進入該場所作業，則無須指派人員監視④若僅1 人作業，必須帶通訊設備. 墜落危害 1.(4...</t>
+        </is>
+      </c>
+      <c r="I282" s="2" t="inlineStr"/>
     </row>
     <row r="283" ht="92.59999999999999" customHeight="1">
       <c r="A283" s="2" t="n">
@@ -10584,8 +12909,13 @@
       <c r="G283" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H283" s="2" t="n"/>
-      <c r="I283" s="2" t="n"/>
+      <c r="H283" s="2" t="inlineStr">
+        <is>
+          <t>鋁錠熔解爐風險較高之危害為水蒸汽爆炸。
+當潮濕的鋁錠、含有水分的工具或雜質接觸到高溫熔融的鋁液時，水分會瞬間汽化並急劇膨脹，進而引發嚴重的物理性爆炸（水蒸汽爆炸）。</t>
+        </is>
+      </c>
+      <c r="I283" s="2" t="inlineStr"/>
     </row>
     <row r="284" ht="92.59999999999999" customHeight="1">
       <c r="A284" s="2" t="n">
@@ -10619,8 +12949,18 @@
       <c r="G284" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H284" s="2" t="n"/>
-      <c r="I284" s="2" t="n"/>
+      <c r="H284" s="2" t="inlineStr">
+        <is>
+          <t>美國工業安全專家韓立奇（H. W. Heinrich）提出的 1:29:300 法則中，比例為 1 係指重傷害（或死亡、重大傷亡）事故。
+Quizlet 韓立奇 1:29:300 法則解析
+1：指重傷害或死亡事故。
+29：指輕傷害（輕微傷亡）事故。
+300：指無傷害的虛驚事故（驚險事件/近乎失誤）。
+財團法人中華顧問工程司 這代表每發生 1 起嚴重傷害或死亡事故的背後，通常伴隨著 29 起輕傷事故，以及 300 起沒有造成人員受傷的虛驚事故。
+財團法人中華顧問工程司</t>
+        </is>
+      </c>
+      <c r="I284" s="2" t="inlineStr"/>
     </row>
     <row r="285" ht="92.59999999999999" customHeight="1">
       <c r="A285" s="2" t="n">
@@ -10654,8 +12994,19 @@
       <c r="G285" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H285" s="2" t="n"/>
-      <c r="I285" s="2" t="n"/>
+      <c r="H285" s="2" t="inlineStr">
+        <is>
+          <t>美國工業安全專家韓立奇（H. W. Heinrich）提出的骨牌理論（Domino theory）中，最後一張（第五張）骨牌為傷害。
+全民勞教e網 韓立奇五張骨牌順序
+第一張： 遺傳及社會環境（Ancestry and social environment）
+第二張： 個人缺陷（Fault of person）
+第三張： 不安全行為或狀況（Unsafe act or condition）
+第四張： 事故／災害（Accident）
+第五張： 傷害（Injury）
+MBA智库</t>
+        </is>
+      </c>
+      <c r="I285" s="2" t="inlineStr"/>
     </row>
     <row r="286" ht="92.59999999999999" customHeight="1">
       <c r="A286" s="2" t="n">
@@ -10689,8 +13040,13 @@
       <c r="G286" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H286" s="2" t="n"/>
-      <c r="I286" s="2" t="n"/>
+      <c r="H286" s="2" t="inlineStr">
+        <is>
+          <t>答案是：不安全行為。
+根據美國工業安全專家韓立奇（H. W. Heinrich）的事故統計與分析（如著名的 88:10:2 比例原則），職場上絕大多數的職業災害與事故，其根本原因多數是由於人的不安全行為（例如違反安全規定、未配戴防護具、分心或疏忽）所引起的，而非不可抗力或天災。您可以參考 取得更多相關考題解析。</t>
+        </is>
+      </c>
+      <c r="I286" s="2" t="inlineStr"/>
     </row>
     <row r="287" ht="92.59999999999999" customHeight="1">
       <c r="A287" s="2" t="n">
@@ -10725,8 +13081,19 @@
       <c r="G287" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H287" s="2" t="n"/>
-      <c r="I287" s="2" t="n"/>
+      <c r="H287" s="2" t="inlineStr">
+        <is>
+          <t>在安全防護的原則中，安全護罩所提供的主要功能為隔離危險。
+國立高雄師範大學 機械安全防護原則說明
+隔離危險：裝設護圍、護罩等實體設備，將人體與危險區域或危害源隔離開來。
+消除危險：屬於本質安全設計。
+遠離危險：採用自動進退料等方式。
+危險預警：設置光電感應式等警示或感應裝置。
+安全護圍所提供的主要功能為下列何者？ (A)消除危險(B)遠離 ...
+2020年1月21日 — 602. () 在安全防護的原則中，安全護圍所提供的主要功能為下列何者？ (A)消除危險(B)遠離危險(C)隔離危害源(D)危險預警 ，包含題目內容、選項、詳解等 ...</t>
+        </is>
+      </c>
+      <c r="I287" s="2" t="inlineStr"/>
     </row>
     <row r="288" ht="108" customHeight="1">
       <c r="A288" s="2" t="n">
@@ -10760,8 +13127,12 @@
       <c r="G288" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H288" s="2" t="n"/>
-      <c r="I288" s="2" t="n"/>
+      <c r="H288" s="2" t="inlineStr">
+        <is>
+          <t>Google AI 摘要未抓取到，請手動補充。</t>
+        </is>
+      </c>
+      <c r="I288" s="2" t="inlineStr"/>
     </row>
     <row r="289" ht="92.59999999999999" customHeight="1">
       <c r="A289" s="2" t="n">
@@ -10795,8 +13166,14 @@
       <c r="G289" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H289" s="2" t="n"/>
-      <c r="I289" s="2" t="n"/>
+      <c r="H289" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+為防止災害，應對人員及設備皆要採取適當對策或措施。
+在職業安全衛生與防災規範中，保障安全必須同時兼顧「人員」（如教育訓練、防護具、健康管理）與「設備」（如機械安全防護、器具檢點、環境維護），兩者缺一不可。</t>
+        </is>
+      </c>
+      <c r="I289" s="2" t="inlineStr"/>
     </row>
     <row r="290" ht="92.59999999999999" customHeight="1">
       <c r="A290" s="2" t="n">
@@ -10830,8 +13207,18 @@
       <c r="G290" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H290" s="2" t="n"/>
-      <c r="I290" s="2" t="n"/>
+      <c r="H290" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+在各類災害防止基本對策中，屬於強化安全管理之措施為確立安全作業標準。
+相關選項解析
+確立安全作業標準：屬於管理層面的措施，透過制定與落實標準作業程序（SOP）來強化安全管理。
+設備安全化：屬於工程控制或硬體本質安全化之措施。
+設置局部排氣裝置：屬於改善作業環境與衛生條件的工程控制措施。
+安全連鎖裝置：屬於機械設備防護的工程安全裝置。</t>
+        </is>
+      </c>
+      <c r="I290" s="2" t="inlineStr"/>
     </row>
     <row r="291" ht="92.59999999999999" customHeight="1">
       <c r="A291" s="2" t="n">
@@ -10865,8 +13252,12 @@
       <c r="G291" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H291" s="2" t="n"/>
-      <c r="I291" s="2" t="n"/>
+      <c r="H291" s="2" t="inlineStr">
+        <is>
+          <t>Google AI 摘要未抓取到，請手動補充。</t>
+        </is>
+      </c>
+      <c r="I291" s="2" t="inlineStr"/>
     </row>
     <row r="292" ht="108" customHeight="1">
       <c r="A292" s="2" t="n">
@@ -10900,8 +13291,17 @@
       <c r="G292" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H292" s="2" t="n"/>
-      <c r="I292" s="2" t="n"/>
+      <c r="H292" s="2" t="inlineStr">
+        <is>
+          <t>從事維修污水儲槽作業，正確的敘述為：「攪拌設施未停電掛牌維修，易產生感電及因誤動作造成人員被夾、被捲等傷害」。
+各選項解析
+(A) 攪拌設施未停電掛牌維修，易產生感電及因誤動作造成人員被夾、被捲等傷害：正確。 進入具有機械設備的儲槽維修前，必須確實切斷電源並加掛標示牌（Lockout/Tagout，LOTO），否則設備突然啟動會造成嚴重夾捲或感電事故。
+(B) 只要實施一次通風，人員進入就不會造成缺氧、中毒等危害：錯誤。 局限空間內的有害氣體或氧氣濃度可能隨時間變化或因作業而釋放，不能僅憑一次通風就認定全程安全，必須持續監測與通風。
+(C) 應實施作業環境監測，則可免除派人監視之責任：錯誤。 作業環境監測與設置局限空間監視人員（作業主管/監視人）是兩種不同的安全防護要求，實施監測不能免除派人監視的法定義務。
+(D) 應單獨完成維修作作業，以避免遭主管績效考評之危害：錯誤。 局限空間作業嚴禁單獨一人進入（應有監視人員及救援機制在外部戒備），以確保發生危故時能即時搶救。</t>
+        </is>
+      </c>
+      <c r="I292" s="2" t="inlineStr"/>
     </row>
     <row r="293" ht="108" customHeight="1">
       <c r="A293" s="2" t="n">
@@ -10935,8 +13335,19 @@
       <c r="G293" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H293" s="2" t="n"/>
-      <c r="I293" s="2" t="n"/>
+      <c r="H293" s="2" t="inlineStr">
+        <is>
+          <t>工作場所發生死亡職業災害時，「馬上復原現場，並加以隔離」非雇主應有之作為。
+依據《職業安全衛生法》第37條規定，發生職業災害時，正確的處理方式與規範如下：
+雇主應採取之作為
+必要急救：立即對受傷勞工進行必要的急救措施。
+必要搶救：採取防止災害擴大的搶救措施。
+實施調查、分析：會同勞工代表實施調查、分析及作成紀錄。
+保持現場完整：除必要之急救、搶救外，非經司法機關或勞動檢查機構許可，不得移動或破壞現場，以免影響後續的災害調查與責任釐清。
+104 職場力</t>
+        </is>
+      </c>
+      <c r="I293" s="2" t="inlineStr"/>
     </row>
     <row r="294" ht="77.15000000000001" customHeight="1">
       <c r="A294" s="2" t="n">
@@ -10970,8 +13381,19 @@
       <c r="G294" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H294" s="2" t="n"/>
-      <c r="I294" s="2" t="n"/>
+      <c r="H294" s="2" t="inlineStr">
+        <is>
+          <t>其災害之間接原因為不安全動作。
+說明
+在職業安全衛生中：
+不安全動作（Unsafe Act）：指人員未遵守作業規定、擅自高速行駛或採用不安全的方法操作機械，屬於人為疏失或違規行為。
+不安全設備：指機械本身有故障或防護裝置失效。
+不安全環境：指工作場所地面不平、照明不足等客觀環境缺陷。
+天災：指不可抗力的自然災害。
+本題中勞工擅自以高速行駛堆高機且未遵守規定，屬於人為的不安全動作。</t>
+        </is>
+      </c>
+      <c r="I294" s="2" t="inlineStr"/>
     </row>
     <row r="295" ht="108" customHeight="1">
       <c r="A295" s="2" t="n">
@@ -11005,8 +13427,22 @@
       <c r="G295" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H295" s="2" t="n"/>
-      <c r="I295" s="2" t="n"/>
+      <c r="H295" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+有誤的選項為：
+考量企業之營運模式與國際佈局
+解析說明
+在職業安全衛生與風險評估的規範中，進行危害辨識（Hazard Identification）時，應針對實際的作業活動、工作環境及其潛在危害進行實質考量，包括：
+考量作業危害之規模與特性等因素（正確）
+考量工作環境之規模與特性等因素（正確）
+應明確規範執行及檢討修正之時機（正確）
+而「企業之營運模式與國際佈局」屬於商業策略、市場定位與企業管理的範疇，與現場作業安全、工作環境之危害辨識無直接相關，因此以此作為危害辨識的考量因素是有誤的。
+下列何者有誤？(A)考量作業危害之規模與特性等因素(B)考量 ...
+2018年9月30日 — 24.有關危害辨識之考量，下列何者有誤？ (A)考量作業危害之規模與特性等因素 (B)考量企業之營運 模式與國際佈局 (C)考量工作環境之規模與特性等因素 (D)應明確規範執行及檢討修正之時機。 答案：登入後查看 統計： A(7), B(808), C(13)</t>
+        </is>
+      </c>
+      <c r="I295" s="2" t="inlineStr"/>
     </row>
     <row r="296" ht="92.59999999999999" customHeight="1">
       <c r="A296" s="2" t="n">
@@ -11040,8 +13476,20 @@
       <c r="G296" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H296" s="2" t="n"/>
-      <c r="I296" s="2" t="n"/>
+      <c r="H296" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+下列選項中以「生理性」有誤（為非）。
+在職業安全衛生與危害辨識工作中，職場危害因子一般正確區分為五大類：
+物理性危害（如噪音、振動、極端溫濕度、輻射等）
+化學性危害（如粉塵、有機溶劑、毒性氣體、重金屬等）
+生物性危害（如細菌、病毒、黴菌等微生物或寄生蟲）
+人因性危害（或稱人因工程危害，如不當姿勢、重複性動作、負重等）
+心理性危害（或稱社會心理性危害，如工作壓力、過勞等）
+台灣大學醫學院附設醫院 選項中的「生理性」並非正式的五大分類之一，故為錯誤選項。</t>
+        </is>
+      </c>
+      <c r="I296" s="2" t="inlineStr"/>
     </row>
     <row r="297" ht="108" customHeight="1">
       <c r="A297" s="2" t="n">
@@ -11075,8 +13523,17 @@
       <c r="G297" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H297" s="2" t="n"/>
-      <c r="I297" s="2" t="n"/>
+      <c r="H297" s="2" t="inlineStr">
+        <is>
+          <t>最不適當的措施是：立即徒手進入救人出來，以求時效。
+原因說明
+局限空間危害大：半密閉或局限空間（如污水槽）內部常有缺氧、硫化氫或其他有毒氣體累積的問題。
+嚴禁貿然進入：未佩戴適當防護具（如空氣呼吸器）而徒手進入，往往會造成救援者也隨之中毒或缺氧倒地，導致傷亡擴大。
+正確做法：應先實施通風換氣、打 119 求救、並佩戴妥善的防護裝備（如空氣呼吸器）再進行救援。
+勞動部職業安全衛生署</t>
+        </is>
+      </c>
+      <c r="I297" s="2" t="inlineStr"/>
     </row>
     <row r="298" ht="92.59999999999999" customHeight="1">
       <c r="A298" s="2" t="n">
@@ -11110,8 +13567,15 @@
       <c r="G298" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H298" s="2" t="n"/>
-      <c r="I298" s="2" t="n"/>
+      <c r="H298" s="2" t="inlineStr">
+        <is>
+          <t>在降低風險的控制措施中，以低電壓電氣設備取代高電壓電氣設備，屬於取代。
+說明
+取代 (Substitution)：指將具有高風險的設備、程序或材料，更換為風險較低的替代品（例如將高電壓設備改為低電壓設備）。
+這屬於職業安全衛生風險控制階層中較優先的本質安全改善方法。</t>
+        </is>
+      </c>
+      <c r="I298" s="2" t="inlineStr"/>
     </row>
     <row r="299" ht="92.59999999999999" customHeight="1">
       <c r="A299" s="2" t="n">
@@ -11145,8 +13609,19 @@
       <c r="G299" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H299" s="2" t="n"/>
-      <c r="I299" s="2" t="n"/>
+      <c r="H299" s="2" t="inlineStr">
+        <is>
+          <t>在降低風險的控制措施中，連鎖停機系統屬於工程控制措施。
+中小企業安全衛生資訊網
+職業安全衛生控制措施層級
+依據風險控制順序（由高至低），常見的危害控制方法包含：
+消除：從源頭直接移除危害（例如：不使用有害化學品）。
+取代：改用較低風險的物質、製程或設備。
+工程控制措施：透過物理裝置或設備來降低風險或減輕後果，例如連鎖停機系統、釋壓裝置、護欄與警報系統。
+管理控制措施：透過訂定工作守則、教育訓練或輪班來減少暴露時間。</t>
+        </is>
+      </c>
+      <c r="I299" s="2" t="inlineStr"/>
     </row>
     <row r="300" ht="92.59999999999999" customHeight="1">
       <c r="A300" s="2" t="n">
@@ -11180,8 +13655,14 @@
       <c r="G300" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H300" s="2" t="n"/>
-      <c r="I300" s="2" t="n"/>
+      <c r="H300" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+在降低風險的控制措施中，完全「不使用危害物質」屬於消除。
+Quizlet</t>
+        </is>
+      </c>
+      <c r="I300" s="2" t="inlineStr"/>
     </row>
     <row r="301" ht="92.59999999999999" customHeight="1">
       <c r="A301" s="2" t="n">
@@ -11215,8 +13696,18 @@
       <c r="G301" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H301" s="2" t="n"/>
-      <c r="I301" s="2" t="n"/>
+      <c r="H301" s="2" t="inlineStr">
+        <is>
+          <t>職業災害預防工作中對於危害控制，首先應考慮的為 (B) 危害源控制。
+危害控制的優先順序
+在職業安全衛生管理中，危害控制的原則通常遵循階層順序：
+優先考量：危害源控制（如消除、取代危害源，或進行工程控制如隔離與密閉）。
+其次考量：危害路徑控制（如設置通風設備、阻絕傳播途徑）。
+再次考量：危害場所控制（如管制區域、標示警告）。
+最後防線：勞工之控制（如使用個人防護具如耳塞、口罩等，這是效果最低、勞工負擔最大的方式）。</t>
+        </is>
+      </c>
+      <c r="I301" s="2" t="inlineStr"/>
     </row>
     <row r="302" ht="92.59999999999999" customHeight="1">
       <c r="A302" s="2" t="n">
@@ -11250,8 +13741,14 @@
       <c r="G302" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H302" s="2" t="n"/>
-      <c r="I302" s="2" t="n"/>
+      <c r="H302" s="2" t="inlineStr">
+        <is>
+          <t>下列何者屬有害物質作業？答案為 特定化學物質作業。
+特定化學物質作業：屬於特別危害健康作業中的有害物相關作業（如有機溶劑、特定化學物質等）。
+其他選項如高溫作業、潛水（異常氣壓）作業則屬於物理性或特殊環境危害作業。</t>
+        </is>
+      </c>
+      <c r="I302" s="2" t="inlineStr"/>
     </row>
     <row r="303" ht="92.59999999999999" customHeight="1">
       <c r="A303" s="2" t="n">
@@ -11285,8 +13782,12 @@
       <c r="G303" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H303" s="2" t="n"/>
-      <c r="I303" s="2" t="n"/>
+      <c r="H303" s="2" t="inlineStr">
+        <is>
+          <t>Google AI 摘要未抓取到，請手動補充。</t>
+        </is>
+      </c>
+      <c r="I303" s="2" t="inlineStr"/>
     </row>
     <row r="304" ht="108" customHeight="1">
       <c r="A304" s="2" t="n">
@@ -11320,8 +13821,18 @@
       <c r="G304" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H304" s="2" t="n"/>
-      <c r="I304" s="2" t="n"/>
+      <c r="H304" s="2" t="inlineStr">
+        <is>
+          <t>錯誤的選項為：「精確計算事故發生的可能性，作為無須保險之依據」。
+錯誤原因說明
+無法免除保險：危害辨識及風險評估是用來預防災害、降低風險的管理工具，並不能完全排除所有意外，也無法作為「不需要投保勞工保險或其他商業保險」的法定或實質依據。
+正確功能：
+協助事業單位建置良好的職業安全衛生管理系統。
+有效控制危害及風險，預防與削減災害。
+提升職業安全衛生管理績效，進而達到永續經營之目的。</t>
+        </is>
+      </c>
+      <c r="I304" s="2" t="inlineStr"/>
     </row>
     <row r="305" ht="92.59999999999999" customHeight="1">
       <c r="A305" s="2" t="n">
@@ -11355,8 +13866,13 @@
       <c r="G305" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H305" s="2" t="n"/>
-      <c r="I305" s="2" t="n"/>
+      <c r="H305" s="2" t="inlineStr">
+        <is>
+          <t>調查及分析災害原因之最重要目的，是為了防止災害再度發生。
+進行職業災害調查的核心價值在於找出流程、設備或管理上的根本缺失（Root Cause），並據此採取修正與預防措施，以確保未來的勞工安全，而非流於行政應酬或應付法規。</t>
+        </is>
+      </c>
+      <c r="I305" s="2" t="inlineStr"/>
     </row>
     <row r="306" ht="92.59999999999999" customHeight="1">
       <c r="A306" s="2" t="n">
@@ -11390,8 +13906,17 @@
       <c r="G306" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H306" s="2" t="n"/>
-      <c r="I306" s="2" t="n"/>
+      <c r="H306" s="2" t="inlineStr">
+        <is>
+          <t>正確的敘述為：「無任一物質為絕對安全」。
+原因說明
+無任一物質為絕對安全：在毒物學與日常觀念中，任何物質（包含水、氧氣、陽光等維持生命的必需元素）只要過量或劑量不當，都可能對人體造成危害，因此沒有絕對安全的物質（呼應「劑量決定毒性」的概念）。
+過量之陽光對人體無害：錯誤，過量陽光會導致晒傷、皮膚老化，甚至增加罹患皮膚癌的風險。
+過量睡眠對人體無害：錯誤，長期過量睡眠（嗜睡）可能與憂鬱症、心血管疾病、糖尿病等健康問題有關。
+過量之氧氣對人體無害：錯誤，吸入過高濃度的氧氣會產生大量自由基，導致氧中毒，對肺部及中樞神經造成傷害。</t>
+        </is>
+      </c>
+      <c r="I306" s="2" t="inlineStr"/>
     </row>
     <row r="307" ht="92.59999999999999" customHeight="1">
       <c r="A307" s="2" t="n">
@@ -11425,8 +13950,12 @@
       <c r="G307" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H307" s="2" t="n"/>
-      <c r="I307" s="2" t="n"/>
+      <c r="H307" s="2" t="inlineStr">
+        <is>
+          <t>Google AI 摘要未抓取到，請手動補充。</t>
+        </is>
+      </c>
+      <c r="I307" s="2" t="inlineStr"/>
     </row>
     <row r="308" ht="77.15000000000001" customHeight="1">
       <c r="A308" s="2" t="n">
@@ -11454,8 +13983,13 @@
       <c r="G308" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H308" s="2" t="n"/>
-      <c r="I308" s="2" t="n"/>
+      <c r="H308" s="2" t="inlineStr">
+        <is>
+          <t>依據職業安全衛生設施規則第 170 條規定，雇主對於高煙囟及高度在三公尺以上並作為危險物品倉庫使用之建築物，均應裝設適當避雷裝置。
+正確答案為：3 公尺（選項 A）</t>
+        </is>
+      </c>
+      <c r="I308" s="2" t="inlineStr"/>
     </row>
     <row r="309" ht="92.59999999999999" customHeight="1">
       <c r="A309" s="2" t="n">
@@ -11489,8 +14023,15 @@
       <c r="G309" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H309" s="2" t="n"/>
-      <c r="I309" s="2" t="n"/>
+      <c r="H309" s="2" t="inlineStr">
+        <is>
+          <t>避雷裝置（或避雷器）的接地電阻規定應在 10Ω（歐姆）以下（選項 B）。
+重點說明
+標準要求：防雷與避雷系統的接地電阻必須小於或等於 10Ω，以確保遭受雷擊時能迅速將巨大電流導入大地，避免電位過高而擊穿設備。
+選項對照：(A) 5Ω、(C) 15Ω、(D) 20Ω 均不符合標準上限規定。</t>
+        </is>
+      </c>
+      <c r="I309" s="2" t="inlineStr"/>
     </row>
     <row r="310" ht="92.59999999999999" customHeight="1">
       <c r="A310" s="2" t="n">
@@ -11524,8 +14065,15 @@
       <c r="G310" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H310" s="2" t="n"/>
-      <c r="I310" s="2" t="n"/>
+      <c r="H310" s="2" t="inlineStr">
+        <is>
+          <t>答案是雇主的利益。
+說明
+安全衛生運動的核心是以人為本，核心理念包含尊重生命、關懷安全、以及保障勞工的生命安全與健康。
+雇主的利益屬於商業或經營考量，並非職業安全衛生運動設計的本意與核心理念。</t>
+        </is>
+      </c>
+      <c r="I310" s="2" t="inlineStr"/>
     </row>
     <row r="311" ht="92.59999999999999" customHeight="1">
       <c r="A311" s="2" t="n">
@@ -11559,8 +14107,16 @@
       <c r="G311" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H311" s="2" t="n"/>
-      <c r="I311" s="2" t="n"/>
+      <c r="H311" s="2" t="inlineStr">
+        <is>
+          <t>發揮安全衛生組織功能的主要關鍵為良好溝通與協調。
+關鍵原因
+促進共識：安全衛生需要全體員工配合，透過雙向溝通才能落實政策。
+解決衝突：良好的協調能減少工作場所中因安全與生產效率產生的摩擦。
+活化成效：溝通比單純的課堂講授更能深入現場，提升整體安全意識。</t>
+        </is>
+      </c>
+      <c r="I311" s="2" t="inlineStr"/>
     </row>
     <row r="312" ht="92.59999999999999" customHeight="1">
       <c r="A312" s="2" t="n">
@@ -11594,8 +14150,17 @@
       <c r="G312" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H312" s="2" t="n"/>
-      <c r="I312" s="2" t="n"/>
+      <c r="H312" s="2" t="inlineStr">
+        <is>
+          <t>下列何者不為溝通協調之主要目的的正確答案是：(D) 安全器材。
+題目解析
+(A) 安全協調：屬於溝通協調的互動與實施方式。
+(B) 安全接談：屬於人員之間面對面溝通、交換安全意見的作法。
+(C) 安全會議：屬於透過集體討論與溝通達成共識的管道。
+(D) 安全器材：屬於具體的硬體設備或防護工具，並非透過溝通協調所達成的「溝通目的」或「溝通項目」。</t>
+        </is>
+      </c>
+      <c r="I312" s="2" t="inlineStr"/>
     </row>
     <row r="313" ht="92.59999999999999" customHeight="1">
       <c r="A313" s="2" t="n">
@@ -11629,8 +14194,15 @@
       <c r="G313" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H313" s="2" t="n"/>
-      <c r="I313" s="2" t="n"/>
+      <c r="H313" s="2" t="inlineStr">
+        <is>
+          <t>安全衛生教育訓練之時機，與薪資調整時無關。
+相關說明
+薪資調整時：屬於人事及財務薪酬範疇，與勞工在工作場所中的作業安全、危害預防及職安法規要求沒有直接關係。
+組織或職掌變更、事故頻傳、增辦業務或推行新工作：這些狀況都伴隨著工作環境、作業內容或人員職務的改變，或是潛在風險的提高，因此皆是需要立即實施或加強安全衛生教育訓練的重要時機。</t>
+        </is>
+      </c>
+      <c r="I313" s="2" t="inlineStr"/>
     </row>
     <row r="314" ht="92.59999999999999" customHeight="1">
       <c r="A314" s="2" t="n">
@@ -11664,8 +14236,16 @@
       <c r="G314" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H314" s="2" t="n"/>
-      <c r="I314" s="2" t="n"/>
+      <c r="H314" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+這種溝通方式為 (B) 同理心。
+同理心：指隨時設身處地站在對方的立場思考問題，理解並感受對方的觀點與需求，而非死守自己的立場，因此能促進良好的溝通。
+.人性化管理組織注重隨時設身處地站在對方立場思考問題 ...
+2022年3月15日 — 10.人性化管理組織注重隨時設身處地站在對方立場思考問題，而不是嚴守本身立場，所以大家容易溝通，此種為下列何種溝通方式? (A)威權式 (B)同理心 (C)指揮 ...</t>
+        </is>
+      </c>
+      <c r="I314" s="2" t="inlineStr"/>
     </row>
     <row r="315" ht="92.59999999999999" customHeight="1">
       <c r="A315" s="2" t="n">
@@ -11699,8 +14279,16 @@
       <c r="G315" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H315" s="2" t="n"/>
-      <c r="I315" s="2" t="n"/>
+      <c r="H315" s="2" t="inlineStr">
+        <is>
+          <t>自己喜歡又能勝任的情況最容易表現敬業精神。
+Quizlet
+原因說明
+熱情與動力：因為自己喜歡（有興趣），所以會有高度的內在動機去投入工作。
+能力與成就：因為能夠勝任（有能力），所以能夠把工作做好，並從中獲得成就感，進而持續保持良好且專業的工作表現。</t>
+        </is>
+      </c>
+      <c r="I315" s="2" t="inlineStr"/>
     </row>
     <row r="316" ht="92.59999999999999" customHeight="1">
       <c r="A316" s="2" t="n">
@@ -11734,8 +14322,12 @@
       <c r="G316" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H316" s="2" t="n"/>
-      <c r="I316" s="2" t="n"/>
+      <c r="H316" s="2" t="inlineStr">
+        <is>
+          <t>Google AI 摘要未抓取到，請手動補充。</t>
+        </is>
+      </c>
+      <c r="I316" s="2" t="inlineStr"/>
     </row>
     <row r="317" ht="92.59999999999999" customHeight="1">
       <c r="A317" s="2" t="n">
@@ -11769,8 +14361,16 @@
       <c r="G317" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H317" s="2" t="n"/>
-      <c r="I317" s="2" t="n"/>
+      <c r="H317" s="2" t="inlineStr">
+        <is>
+          <t>這題的答案是 (B) 負數。
+影響解析
+負數：有高度專業能力卻沒有責任感和工作倫理的人，往往會對團隊合作、組織信譽或內部管理造成破壞與損耗，因此對長久經營而言是負面影響（如同一顆未爆彈或負資產）。
+其他選項：不符合工作倫理與專業倫理在組織管理中的評估概念。
+您可以參考 的詳細討論與答題統計。</t>
+        </is>
+      </c>
+      <c r="I317" s="2" t="inlineStr"/>
     </row>
     <row r="318" ht="92.59999999999999" customHeight="1">
       <c r="A318" s="2" t="n">
@@ -11804,8 +14404,17 @@
       <c r="G318" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H318" s="2" t="n"/>
-      <c r="I318" s="2" t="n"/>
+      <c r="H318" s="2" t="inlineStr">
+        <is>
+          <t>與人相處發生衝突時，宜採取 (C) 思考各種解決方式。
+原因解析
+(C) 思考各種解決方式：面對衝突時，保持理性、積極尋找雙方都能接受的方案，才是化解矛盾、維系良好人際關係的正確做法。
+(A) 要求別人尊重自己的意見和感受：這屬於過度強調自我中心的單向要求，容易讓對立加劇。
+(B) 提出破壞性的批評：會傷害彼此情感，無助於問題解決。
+(D) 惡言相向、提高聲勢：會使衝突升級，甚至造成不可挽回的傷害。</t>
+        </is>
+      </c>
+      <c r="I318" s="2" t="inlineStr"/>
     </row>
     <row r="319" ht="92.59999999999999" customHeight="1">
       <c r="A319" s="2" t="n">
@@ -11839,8 +14448,19 @@
       <c r="G319" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H319" s="2" t="n"/>
-      <c r="I319" s="2" t="n"/>
+      <c r="H319" s="2" t="inlineStr">
+        <is>
+          <t>答案為 (C) 守紀。
+Quizlet
+解析
+守紀：指遵守紀律與規範。服從單位制定的安全規範、維護工作安全及預防意外，屬於遵守工作紀律的表現。
+敬業：對工作盡心盡責。
+協同：與他人合作配合。
+服務：提供協助或滿足他人需求。
+Quizlet</t>
+        </is>
+      </c>
+      <c r="I319" s="2" t="inlineStr"/>
     </row>
     <row r="320" ht="92.59999999999999" customHeight="1">
       <c r="A320" s="2" t="n">
@@ -11874,8 +14494,12 @@
       <c r="G320" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H320" s="2" t="n"/>
-      <c r="I320" s="2" t="n"/>
+      <c r="H320" s="2" t="inlineStr">
+        <is>
+          <t>Google AI 摘要未抓取到，請手動補充。</t>
+        </is>
+      </c>
+      <c r="I320" s="2" t="inlineStr"/>
     </row>
     <row r="321" ht="77.15000000000001" customHeight="1">
       <c r="A321" s="2" t="n">
@@ -11909,8 +14533,15 @@
       <c r="G321" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H321" s="2" t="n"/>
-      <c r="I321" s="2" t="n"/>
+      <c r="H321" s="2" t="inlineStr">
+        <is>
+          <t>這題的答案是 (A) 忠誠。
+解析
+忠誠義務：勞工在勞動契約存續期間及結束前後，應對雇主負誠實及信用基礎上的忠誠行為，包含不兼職、完整履行契約、妥善交接業務，以及離職後不作營業競爭等。
+選項對照：題幹所述之行為皆屬於勞工對雇主應盡的「忠誠」範疇。</t>
+        </is>
+      </c>
+      <c r="I321" s="2" t="inlineStr"/>
     </row>
     <row r="322" ht="92.59999999999999" customHeight="1">
       <c r="A322" s="2" t="n">
@@ -11944,8 +14575,19 @@
       <c r="G322" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H322" s="2" t="n"/>
-      <c r="I322" s="2" t="n"/>
+      <c r="H322" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+「需要的物品要能很快的拿到」是指 5S（或題目中的選項概念）中的 整頓。
+S 核心含義簡述
+整頓（Set in order）：將需要的物品妥善定位、定量擺放，並加上明確標示，讓大家不需要尋找、用後能物歸原位，快速拿到。
+整理（Sort）：區分要用與不要用的物品，把不需要的清除。
+清掃（Shine）：清除工作場所的髒污。
+清潔（Standardize）：將前三者制度化與規範化，維持成果。
+维基百科</t>
+        </is>
+      </c>
+      <c r="I322" s="2" t="inlineStr"/>
     </row>
     <row r="323" ht="92.59999999999999" customHeight="1">
       <c r="A323" s="2" t="n">
@@ -11979,8 +14621,12 @@
       <c r="G323" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H323" s="2" t="n"/>
-      <c r="I323" s="2" t="n"/>
+      <c r="H323" s="2" t="inlineStr">
+        <is>
+          <t>Google AI 摘要未抓取到，請手動補充。</t>
+        </is>
+      </c>
+      <c r="I323" s="2" t="inlineStr"/>
     </row>
     <row r="324" ht="92.59999999999999" customHeight="1">
       <c r="A324" s="2" t="n">
@@ -12014,8 +14660,19 @@
       <c r="G324" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H324" s="2" t="n"/>
-      <c r="I324" s="2" t="n"/>
+      <c r="H324" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+將要與不要的物品加以區分、不要的加以清除，是指 5S 中的整理（Seiri）。
+S 簡要對照
+整理（Seiri）：區分要與不要的物品，清除不需要的東西。
+整頓（Seiton）：需要的物品定位、定量的擺放整齊。
+清掃（Seiso）：清除職場內的髒污與垃圾。
+清潔（Seiketsu）：維持前三項的成果，使其制度化。
+新文明管理顧問有限公司</t>
+        </is>
+      </c>
+      <c r="I324" s="2" t="inlineStr"/>
     </row>
     <row r="325" ht="108" customHeight="1">
       <c r="A325" s="2" t="n">
@@ -12049,8 +14706,16 @@
       <c r="G325" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H325" s="2" t="n"/>
-      <c r="I325" s="2" t="n"/>
+      <c r="H325" s="2" t="inlineStr">
+        <is>
+          <t>安全衛生工作能否落實有效，最根本且最關鍵的是 (C) 企業是否有正確的安全衛生理念。
+為什麼是企業的理念最關鍵？
+決策與資源分配：企業（雇主）擁有工作場所的實質控制權與資源分配權。唯有企業具備正確的工安意識，願意主動投資安全設備、改善作業環境並落實教育訓練，安全衛生政策才能真正扎根。
+法規與檢查的輔助：政府法規與勞動檢查屬於「外部監督」力量，雖然必要，但若企業缺乏自發性的正確理念，往往容易流於形式或僅在面對檢查時應付，難以達到全面且長遠的落實效果。
+勞動部職業安全衛生署</t>
+        </is>
+      </c>
+      <c r="I325" s="2" t="inlineStr"/>
     </row>
     <row r="326" ht="92.59999999999999" customHeight="1">
       <c r="A326" s="2" t="n">
@@ -12084,8 +14749,12 @@
       <c r="G326" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H326" s="2" t="n"/>
-      <c r="I326" s="2" t="n"/>
+      <c r="H326" s="2" t="inlineStr">
+        <is>
+          <t>Google AI 摘要未抓取到，請手動補充。</t>
+        </is>
+      </c>
+      <c r="I326" s="2" t="inlineStr"/>
     </row>
     <row r="327" ht="92.59999999999999" customHeight="1">
       <c r="A327" s="2" t="n">
@@ -12119,8 +14788,12 @@
       <c r="G327" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H327" s="2" t="n"/>
-      <c r="I327" s="2" t="n"/>
+      <c r="H327" s="2" t="inlineStr">
+        <is>
+          <t>Google AI 摘要未抓取到，請手動補充。</t>
+        </is>
+      </c>
+      <c r="I327" s="2" t="inlineStr"/>
     </row>
     <row r="328" ht="92.59999999999999" customHeight="1">
       <c r="A328" s="2" t="n">
@@ -12154,8 +14827,13 @@
       <c r="G328" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H328" s="2" t="n"/>
-      <c r="I328" s="2" t="n"/>
+      <c r="H328" s="2" t="inlineStr">
+        <is>
+          <t>答案是：愈大。
+工作能讓人增進專業知識、技術、實務經驗與個人能力，並提升身分與地位。在這個過程中，個人成長越多，所獲得的肯定通常也會愈大。這是因為能力的提升與績效的展現，會直接反映在主管、同事、客戶或社會大眾對你的評價與信任度上。</t>
+        </is>
+      </c>
+      <c r="I328" s="2" t="inlineStr"/>
     </row>
     <row r="329" ht="92.59999999999999" customHeight="1">
       <c r="A329" s="2" t="n">
@@ -12189,8 +14867,17 @@
       <c r="G329" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H329" s="2" t="n"/>
-      <c r="I329" s="2" t="n"/>
+      <c r="H329" s="2" t="inlineStr">
+        <is>
+          <t>在組織中，不是心理或行為所引起協調與溝通不良的原因是飲食差異。
+原因解析
+飲食差異：屬於生理需求或生活習慣的差異，與組織內部的心理偏誤、行為模式或溝通障礙無直接相關。
+刻板印象：屬於心理與認知上的偏差，容易因特定群體印象而影響對個人的正確判斷。
+文化差異：屬於價值觀與行為規範的不同，容易導致溝通時的誤解。
+知覺差異：屬於心理歷程的不同，每個人對同一件事物的解讀與接收方式不一致，進而引發溝通不良。</t>
+        </is>
+      </c>
+      <c r="I329" s="2" t="inlineStr"/>
     </row>
     <row r="330" ht="92.59999999999999" customHeight="1">
       <c r="A330" s="2" t="n">
@@ -12224,8 +14911,16 @@
       <c r="G330" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H330" s="2" t="n"/>
-      <c r="I330" s="2" t="n"/>
+      <c r="H330" s="2" t="inlineStr">
+        <is>
+          <t>這個現象是由安全衛生文化（安衛文化）所形成的。
+解析與原因：
+安全衛生文化：是指組織內全體員工共同擁有的價值觀、態度、信念和行為模式。當這種文化內化到每個人心中時，員工不論是否在自己的職責範圍內，都會自發性地維護環境、注意安全，把「看到紙屑就撿起來」當作一種理所當然的習慣，這屬於最高層次的「全員參與」與內化表現。
+其他選項為何不符：
+安全衛生檢查、計畫和組織：大多屬於制度、法規、被動的管理或特定區域的責任劃分（如題目所述的「負責區域」），通常只能做到「各人自掃門前雪」，無法達到讓「任何人、在任何區域」都自發性維護的境界。</t>
+        </is>
+      </c>
+      <c r="I330" s="2" t="inlineStr"/>
     </row>
     <row r="331" ht="92.59999999999999" customHeight="1">
       <c r="A331" s="2" t="n">
@@ -12259,8 +14954,20 @@
       <c r="G331" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H331" s="2" t="n"/>
-      <c r="I331" s="2" t="n"/>
+      <c r="H331" s="2" t="inlineStr">
+        <is>
+          <t>正確的流程排列為 e-b-c-a-d。
+溝通流程解析
+溝通的過程模式順序如下：
+e. 傳送者：溝通的發起人，負責構思與發送想法。
+b. 編碼：傳送者將心中的想法或訊息轉換成符號、語言或文字。
+c. 管道：傳送訊息所經由的媒介或傳遞途徑（如口頭、書面、電子郵件）。
+a. 解碼：接收者對收到的訊息符號進行解釋與理解。
+d. 接收者：訊息的接收與解讀對象。
+高點文化</t>
+        </is>
+      </c>
+      <c r="I331" s="2" t="inlineStr"/>
     </row>
     <row r="332" ht="92.59999999999999" customHeight="1">
       <c r="A332" s="2" t="n">
@@ -12294,8 +15001,13 @@
       <c r="G332" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H332" s="2" t="n"/>
-      <c r="I332" s="2" t="n"/>
+      <c r="H332" s="2" t="inlineStr">
+        <is>
+          <t>安全衛生政策由事業經營負責人擬訂、簽署並頒發。
+根據《職業安全衛生管理辦法》及相關勞安法規，安全衛生政策代表一個企業對勞工安全健康的最高承諾與決心。因此，必須由企業的最高首長（如董事長、總經理或廠長等事業經營負責人）親自簽署並發布，才能展現經營階層的重視，並有效推動全公司各部門遵行。</t>
+        </is>
+      </c>
+      <c r="I332" s="2" t="inlineStr"/>
     </row>
     <row r="333" ht="92.59999999999999" customHeight="1">
       <c r="A333" s="2" t="n">
@@ -12329,8 +15041,15 @@
       <c r="G333" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H333" s="2" t="n"/>
-      <c r="I333" s="2" t="n"/>
+      <c r="H333" s="2" t="inlineStr">
+        <is>
+          <t>勞動環境的本質是以 (A) 人 為中心。
+詳細說明
+核心價值：勞動環境與職業安全衛生的根本目的，在於保護勞動者的安全與健康，因此一切規範與環境營造皆以人（工作者）為出發點。
+法源依據：依據《職業安全衛生法》第一條規定，立法宗旨即是為了防止職業災害，並保障工作者的安全與健康。</t>
+        </is>
+      </c>
+      <c r="I333" s="2" t="inlineStr"/>
     </row>
     <row r="334" ht="108" customHeight="1">
       <c r="A334" s="2" t="n">
@@ -12364,8 +15083,17 @@
       <c r="G334" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H334" s="2" t="n"/>
-      <c r="I334" s="2" t="n"/>
+      <c r="H334" s="2" t="inlineStr">
+        <is>
+          <t>專業訓練互異（題目誤植為互虧），缺乏共同語言（或事業訓練互異）構成組織溝通協調之阻力。
+解析與選項說明
+專業訓練互異，缺乏共同語言（正確答案）：不同部門或專業背景的人員，因學經歷與專業術語不同，常導致彼此無法理解對方的觀點與需求，形成溝通障礙與協調阻力。
+高階主管的支持與認同：有助於推動溝通與協調，屬於促進因素而非阻力。
+相似的資源、目標及需要：彼此目標與需求一致，能降低衝突、增進合作。
+利益大於成本：當預期利益大於付出成本時，各方更有意願進行協商與溝通。</t>
+        </is>
+      </c>
+      <c r="I334" s="2" t="inlineStr"/>
     </row>
     <row r="335" ht="92.59999999999999" customHeight="1">
       <c r="A335" s="2" t="n">
@@ -12399,8 +15127,16 @@
       <c r="G335" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H335" s="2" t="n"/>
-      <c r="I335" s="2" t="n"/>
+      <c r="H335" s="2" t="inlineStr">
+        <is>
+          <t>下列何者因素不致造成組織的衝突？
+共識不致造成組織的衝突。
+為什麼是「共識」？
+共識（Consensus）：指成員或部門之間意見一致、目標相同、彼此配合，這會減少摩擦與對立，因此不會引發衝突。
+意見分歧、對立、難容：這些都是指彼此想法不同、立場相左或無法互相容忍，因此容易在日常運作或決策中造成組織內部的衝突。</t>
+        </is>
+      </c>
+      <c r="I335" s="2" t="inlineStr"/>
     </row>
     <row r="336" ht="92.59999999999999" customHeight="1">
       <c r="A336" s="2" t="n">
@@ -12434,8 +15170,15 @@
       <c r="G336" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H336" s="2" t="n"/>
-      <c r="I336" s="2" t="n"/>
+      <c r="H336" s="2" t="inlineStr">
+        <is>
+          <t>答案是：資源分配平均。
+解析
+資源分配平均代表資源分配公平、合理，通常能減少摩擦與不滿，因此不會是組織衝突的起因。
+其他選項如「執掌、權責等不明確」、「權力與利益遭受瓜分」以及「溝通不良」都是常見導致組織內部產生對立與衝突的原因。</t>
+        </is>
+      </c>
+      <c r="I336" s="2" t="inlineStr"/>
     </row>
     <row r="337" ht="92.59999999999999" customHeight="1">
       <c r="A337" s="2" t="n">
@@ -12469,8 +15212,19 @@
       <c r="G337" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H337" s="2" t="n"/>
-      <c r="I337" s="2" t="n"/>
+      <c r="H337" s="2" t="inlineStr">
+        <is>
+          <t>答案是：安全文化。
+Quizlet
+解析
+安全文化：指組織成員共同持有的安全價值、信念與規範，並透過個人與組織的行動、態度、政策及程序表現出來，強調大家對安全的共同認知與感受。
+職業災害調查：是在職業災害發生後，為了查明原因、防止類似災害再度發生所進行的調查程序。
+職業災害防止計畫：是雇主為預防職業災害、保障勞工安全健康而訂定並執行的具體規劃。
+自動檢查計畫：是針對機械、設備等實施自主性定期檢查的作業安排。
+Quizlet</t>
+        </is>
+      </c>
+      <c r="I337" s="2" t="inlineStr"/>
     </row>
     <row r="338" ht="92.59999999999999" customHeight="1">
       <c r="A338" s="2" t="n">
@@ -12504,8 +15258,17 @@
       <c r="G338" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H338" s="2" t="n"/>
-      <c r="I338" s="2" t="n"/>
+      <c r="H338" s="2" t="inlineStr">
+        <is>
+          <t>主觀不屬於雙向溝通之條件。
+詳細說明
+講述：表達自己的想法與訊息，屬於溝通的必要過程。
+傾聽：接收並重視對方的意見，是雙向互動的基礎。
+瞭解：雙方互相理解意涵，達成共識。
+主觀：過度堅持自己的立場與偏見，會阻礙彼此的理解與交流，因此不屬於良好雙向溝通的條件。</t>
+        </is>
+      </c>
+      <c r="I338" s="2" t="inlineStr"/>
     </row>
     <row r="339" ht="92.59999999999999" customHeight="1">
       <c r="A339" s="2" t="n">
@@ -12539,8 +15302,16 @@
       <c r="G339" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H339" s="2" t="n"/>
-      <c r="I339" s="2" t="n"/>
+      <c r="H339" s="2" t="inlineStr">
+        <is>
+          <t>下列何者非勞工義務？答案是 (C) 提供安全衛生設備及措施。
+說明
+依據《職業安全衛生法》規定：
+提供安全衛生設備及措施是雇主的責任與義務，而非勞工。
+接受健康檢查、接受安全衛生教育訓練、遵守工作守則（安全衛生工作守則）皆屬於勞工應配合的法定義務。</t>
+        </is>
+      </c>
+      <c r="I339" s="2" t="inlineStr"/>
     </row>
     <row r="340" ht="92.59999999999999" customHeight="1">
       <c r="A340" s="2" t="n">
@@ -12574,8 +15345,18 @@
       <c r="G340" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H340" s="2" t="n"/>
-      <c r="I340" s="2" t="n"/>
+      <c r="H340" s="2" t="inlineStr">
+        <is>
+          <t>職業道德必須具備合法性（選項C）。
+職業道德的核心特點
+合法性：職業行為與規範必須符合國家法律與法規的最低要求，這是從事任何職業的基礎底線。
+其他選項分析：
+利己性：追求個人利益並非道德規範的核心與必須具備條件。
+唯物性：屬於哲學範疇，與職業道德規範無直接關聯。
+機會性：指視機會而定的投機行為，與穩定且具約束力的道德相違背。</t>
+        </is>
+      </c>
+      <c r="I340" s="2" t="inlineStr"/>
     </row>
     <row r="341" ht="92.59999999999999" customHeight="1">
       <c r="A341" s="2" t="n">
@@ -12609,8 +15390,15 @@
       <c r="G341" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H341" s="2" t="n"/>
-      <c r="I341" s="2" t="n"/>
+      <c r="H341" s="2" t="inlineStr">
+        <is>
+          <t>職業災害發生時，下列何者為無形的影響：公共形象損失。
+影響分析
+有形損失：包含財產損失（如設備毀損）、醫療損失（如醫療與賠償費用）以及雜項損失等，這些都可以用金錢直接計算。
+無形損失：包含公共形象損失、員工士氣低落、社會觀感變差等，這些無法直接用金錢衡量。</t>
+        </is>
+      </c>
+      <c r="I341" s="2" t="inlineStr"/>
     </row>
     <row r="342" ht="92.59999999999999" customHeight="1">
       <c r="A342" s="2" t="n">
@@ -12644,8 +15432,15 @@
       <c r="G342" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H342" s="2" t="n"/>
-      <c r="I342" s="2" t="n"/>
+      <c r="H342" s="2" t="inlineStr">
+        <is>
+          <t>有立即發生危險之虞，工作場所負責人下令停止作業並讓勞工退避至安全場所，屬於(A) 強制性溝通協調（或稱強制性協調溝通）。
+解析重點
+依據：依據《職業安全衛生法》第18條規定，工作場所有立即發生危險之虞時，雇主或工作場所負責人應即令停止作業，並使勞工退避至安全場所。
+性質：因為這是法律強制規定且具備強制執行力、不容許勞資雙方討價還價的緊急安全處置，故在管理學或工安溝通分類上屬於強制性溝通協調。</t>
+        </is>
+      </c>
+      <c r="I342" s="2" t="inlineStr"/>
     </row>
     <row r="343" ht="92.59999999999999" customHeight="1">
       <c r="A343" s="2" t="n">
@@ -12679,8 +15474,13 @@
       <c r="G343" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H343" s="2" t="n"/>
-      <c r="I343" s="2" t="n"/>
+      <c r="H343" s="2" t="inlineStr">
+        <is>
+          <t>這項特色屬於強制性。
+根據台灣的《職業安全衛生法》相關法規，事業單位和勞工都必須遵守相關的法規規範。雇主有義務為員工辦理安全衛生教育訓練，而員工同樣有接受該教育訓練的義務。若員工拒絕參加，不僅事業單位可以依內部規定進行懲戒，依法也可能面臨行政罰鍰，這充分體現了法令的強制性特色。</t>
+        </is>
+      </c>
+      <c r="I343" s="2" t="inlineStr"/>
     </row>
     <row r="344" ht="92.59999999999999" customHeight="1">
       <c r="A344" s="2" t="n">
@@ -12714,8 +15514,19 @@
       <c r="G344" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H344" s="2" t="n"/>
-      <c r="I344" s="2" t="n"/>
+      <c r="H344" s="2" t="inlineStr">
+        <is>
+          <t>安全衛生協調與溝通不屬於其特色的是 (A) 分歧性（或稱擴大思想差異性）。
+國立岡山高級農工職業學校 安全衛生協調與溝通的特色
+強制性：為了保障勞工安全與符合法規，必須依法強制執行或配合。
+權威性：依循法規與管理權責，具有規範與指導的約束力。
+專業性：需具備職業安全衛生的專業知識與技術來進行正確判斷與改善。
+花職訓
+協調與溝通的目的是建立共識、傳達觀念與分享意見，而非造成分歧。
+國立岡山高級農工職業學校</t>
+        </is>
+      </c>
+      <c r="I344" s="2" t="inlineStr"/>
     </row>
     <row r="345" ht="92.59999999999999" customHeight="1">
       <c r="A345" s="2" t="n">
@@ -12749,8 +15560,17 @@
       <c r="G345" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H345" s="2" t="n"/>
-      <c r="I345" s="2" t="n"/>
+      <c r="H345" s="2" t="inlineStr">
+        <is>
+          <t>這種逢迎、試著取悅別人或看似向人道歉，但讓人感受不到真心與誠意的溝通模式稱為討好型。
+這是心理學家薩提爾（Virginia Satir）提出的四大溝通順應模式之一。以下是這四種型態的簡要對比：
+討好型：壓抑自己的感受，以取悅他人、道歉或逢迎的方式來維持和諧，但內心往往感到委屈或並非真心。
+責備型：習慣將錯誤歸咎於他人，用控制和批評來掩飾自己的脆弱。
+電腦型：極度理智、冷靜且講求邏輯，完全切斷情感連結，只談客觀數據與道理。
+打岔型：面對壓力時習慣轉移話題、開玩笑或逃避面對核心問題。</t>
+        </is>
+      </c>
+      <c r="I345" s="2" t="inlineStr"/>
     </row>
     <row r="346" ht="92.59999999999999" customHeight="1">
       <c r="A346" s="2" t="n">
@@ -12784,8 +15604,19 @@
       <c r="G346" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H346" s="2" t="n"/>
-      <c r="I346" s="2" t="n"/>
+      <c r="H346" s="2" t="inlineStr">
+        <is>
+          <t>亞伯拉罕·馬斯洛（Abraham Maslow）的需求層級理論由低到高的正確順序為 DBAEC（生理需求 → 安全需求 → 愛的需求 → 尊嚴需求 → 自我實現需求）。
+考古豹 需求層級順序說明
+D. 生理需求（最底層：食物、水、空氣、睡眠）
+B. 安全需求（第二層：人身安全、健康、資源保障）
+E. 愛的需求（第三層：愛與歸屬感、友情、愛情）
+A. 尊嚴需求（第四層：自尊、尊重他人、成就感）
+C. 自我實現需求（最高層：發揮個人潛能、實現理想）
+翰林雲端學院</t>
+        </is>
+      </c>
+      <c r="I346" s="2" t="inlineStr"/>
     </row>
     <row r="347" ht="108" customHeight="1">
       <c r="A347" s="2" t="n">
@@ -12819,8 +15650,23 @@
       <c r="G347" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H347" s="2" t="n"/>
-      <c r="I347" s="2" t="n"/>
+      <c r="H347" s="2" t="inlineStr">
+        <is>
+          <t>正確的選項是：消除 → 取代 → 隔離 → 行政管理（對應題目中的第二個選項或常見考題中的 (B) 選項）。
+解析
+依據職業安全衛生法規與「危害控制階層（Hierarchy of Control）」原則，當我們面對職場危害時，必須由效益最高、最優先的源頭減災做起，依序為：
+消除（Elimination）：從源頭直接拿掉危害或風險。
+亞東醫院 取代（Substitution）：用較低危害的物質或方式替代。
+亞東醫院
+工程控制／隔離（Engineering Controls / Isolation）：透過設備修改、加裝護欄或隔離設施降低風險。
+中小企業安全衛生資訊網
+行政管理（Administrative Controls）：如教育訓練、縮短工時或輪班等管理措施。
+國立岡山高級農工職業學校
+個人防護具（PPE）：最後防線，佩戴安全帽、耳塞或防護衣等。
+因此選項中合乎由前到後邏輯的正確順序為「消除 → 取代 → 隔離 → 行政管理」。</t>
+        </is>
+      </c>
+      <c r="I347" s="2" t="inlineStr"/>
     </row>
     <row r="348" ht="92.59999999999999" customHeight="1">
       <c r="A348" s="2" t="n">
@@ -12854,8 +15700,19 @@
       <c r="G348" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H348" s="2" t="n"/>
-      <c r="I348" s="2" t="n"/>
+      <c r="H348" s="2" t="inlineStr">
+        <is>
+          <t>消除或降低危害最優先考慮的方法為 (B) 工程改善。
+職業安全衛生控制原則（控制階層）
+依據職業安全衛生管理與風險控制的優先順序（從最優先到最後手段）：
+消除/替代：從源頭移除危害或以無害/低害物質、設備取代。
+工程改善（工程控制）：如隔離、封閉、自動化或設置局部排氣裝置，以降低暴露程度。
+教育訓練/行政管理（管理控制）：如限制暴露時間、輪班或加強安全衛生教育訓練。
+使用防護具（個人防護具）：屬於最後不得已的防護手段（因防護具可能因佩戴不實而失效）。
+因此，在選項「健康管理、工程改善、教育訓練、使用防護具」之中，最優先考慮的為工程改善。</t>
+        </is>
+      </c>
+      <c r="I348" s="2" t="inlineStr"/>
     </row>
     <row r="349" ht="92.59999999999999" customHeight="1">
       <c r="A349" s="2" t="n">
@@ -12889,8 +15746,25 @@
       <c r="G349" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H349" s="2" t="n"/>
-      <c r="I349" s="2" t="n"/>
+      <c r="H349" s="2" t="inlineStr">
+        <is>
+          <t>✅ 答案：財務控制
+在職業安全衛生的風險控制層級（危害控制階層）中，正確的常用優先順序與措施為：消除 &gt; 取代 &gt; 工程控制 &gt; 管理控制（行政管制） &gt; 個人防護具。因此選項中的「財務控制」並非職業安全風險評估與控制的標準措施，是有誤的選項。
+考古豹 📊 常見風險控制措施層級
+🔄 消除或取代
+消除：從源頭移除危害（如改用無毒物質）。
+取代：以較低風險者替換（如改用低壓設備）。
+中小企業安全衛生資訊網
+🛠️ 工程控制
+設置實體防護設施（如護欄、隔音、排氣裝置）。
+中小企業安全衛生資訊網
+📋 管理控制
+透過規章與訓練降低暴露（如輪班制、教育訓練）。
+🦺 個人防護具
+最後防線（如安全帽、耳塞）。</t>
+        </is>
+      </c>
+      <c r="I349" s="2" t="inlineStr"/>
     </row>
     <row r="350" ht="108" customHeight="1">
       <c r="A350" s="2" t="n">
@@ -12924,8 +15798,17 @@
       <c r="G350" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H350" s="2" t="n"/>
-      <c r="I350" s="2" t="n"/>
+      <c r="H350" s="2" t="inlineStr">
+        <is>
+          <t>危害辨識→風險評估→風險控制為正確之風險管理順序。
+風險管理步驟說明
+危害辨識：找出工作場所中所有可能導致人員受傷或健康受損的潛在原因。
+風險評估：分析與評估已辨識危害發生機率及其嚴重性，判定風險等級。
+風險控制：針對不可接受之風險，採取消除、取代、工程控制、管理控制或個人防護具等對策。
+中小企業安全衛生資訊網</t>
+        </is>
+      </c>
+      <c r="I350" s="2" t="inlineStr"/>
     </row>
     <row r="351" ht="92.59999999999999" customHeight="1">
       <c r="A351" s="2" t="n">
@@ -12959,8 +15842,16 @@
       <c r="G351" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H351" s="2" t="n"/>
-      <c r="I351" s="2" t="n"/>
+      <c r="H351" s="2" t="inlineStr">
+        <is>
+          <t>在建立安全衛生工作環境時，領導風格（或選項中的採購管理，視常見題庫標準，領導風格屬於組織管理與文化層面）較屬於組織管理層面。
+常見的健康與安全工作環境分類中：
+組織管理層面：包含領導風格、團隊互助、人際關係等。
+健康服務層面：包含預防注射、健康檢查等。
+個人行為／人因工程層面：包含工作姿勢等。</t>
+        </is>
+      </c>
+      <c r="I351" s="2" t="inlineStr"/>
     </row>
     <row r="352" ht="92.59999999999999" customHeight="1">
       <c r="A352" s="2" t="n">
@@ -12994,8 +15885,12 @@
       <c r="G352" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H352" s="2" t="n"/>
-      <c r="I352" s="2" t="n"/>
+      <c r="H352" s="2" t="inlineStr">
+        <is>
+          <t>輪班作業係針對接受者（暴露者）進行控制。藉由調整工作時間、縮短單一勞工連續暴露於有害環境（如噪音、化學物質、高溫或夜間工作壓力）之時間，來降低個人受害的風險。</t>
+        </is>
+      </c>
+      <c r="I352" s="2" t="inlineStr"/>
     </row>
     <row r="353" ht="108" customHeight="1">
       <c r="A353" s="2" t="n">
@@ -13029,8 +15924,19 @@
       <c r="G353" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H353" s="2" t="n"/>
-      <c r="I353" s="2" t="n"/>
+      <c r="H353" s="2" t="inlineStr">
+        <is>
+          <t>有關實施控制方法之敘述，正確的選項為：「應維持管制方法之必要條件，以確保該方法的持續有效性」。
+詳細解析
+正確選項：應維持管制方法之必要條件，以確保該方法的持續有效性。
+控制方法或管制措施實施後，必須持續維持其必要的運作條件與效能，才能真正達到預防與控制危害的目的。
+錯誤選項說明：
+既訂定控制方法，就無需再發展新的作業程序：當環境、設備或風險改變時，仍可能需要檢討並發展或更新作業程序。
+輕微變動無須告知員工，以避免訓練成本增加：作業內容或條件若有變動（甚至是輕微變動），為了安全與合規，仍應讓相關員工知悉並進行必要的宣導或訓練。
+除管理者外，應全員訓練：控制方法的落實需要實際操作或接觸的全員配合，而非僅排除管理者或僅訓練特定人員。</t>
+        </is>
+      </c>
+      <c r="I353" s="2" t="inlineStr"/>
     </row>
     <row r="354" ht="92.59999999999999" customHeight="1">
       <c r="A354" s="2" t="n">
@@ -13064,8 +15970,15 @@
       <c r="G354" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H354" s="2" t="n"/>
-      <c r="I354" s="2" t="n"/>
+      <c r="H354" s="2" t="inlineStr">
+        <is>
+          <t>正確答案為：職業安全衛生教育訓練。
+原因說明
+職業安全衛生教育訓練之主要目的，即在於對勞工灌輸與訓練正確的安全衛生觀念及標準作業程序，進而提升安全知能，防止勞工因不安全行為而引發職業災害。
+臺北市勞動檢查處 其餘選項（危險性機械設備之定期檢查、機械器具之型式檢定、作業環境測定）則分別側重於硬體設備安全檢查、器具合格驗證及作業環境有害物濃度之檢測，均非以「訓練勞工觀念與行為」為直接目的。</t>
+        </is>
+      </c>
+      <c r="I354" s="2" t="inlineStr"/>
     </row>
     <row r="355" ht="92.59999999999999" customHeight="1">
       <c r="A355" s="2" t="n">
@@ -13099,8 +16012,15 @@
       <c r="G355" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H355" s="2" t="n"/>
-      <c r="I355" s="2" t="n"/>
+      <c r="H355" s="2" t="inlineStr">
+        <is>
+          <t>答案是：工時縮短所致之危害。
+原因解析
+擴充產能的影響：當事業單位為了提高產量而擴充產能時，往往會增加原物料或有害物質的使用（如有害物增加逸散之危害）、招聘新員工但教育訓練跟不上（如新進人員訓練不足所致之危害），或是因為產量大增導致廠區擁擠（如製品堆置場所不足所致之危害），這些都容易衍生意外或職業衛生危害。
+工時縮短：工時縮短通常代表勞動時間減少、休息增加，反而較不可能直接引起擴產所帶來的突發性意外災害（相對地，若是延長工時或過勞，才較容易引發過勞或意外）。</t>
+        </is>
+      </c>
+      <c r="I355" s="2" t="inlineStr"/>
     </row>
     <row r="356" ht="92.59999999999999" customHeight="1">
       <c r="A356" s="2" t="n">
@@ -13134,8 +16054,20 @@
       <c r="G356" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H356" s="2" t="n"/>
-      <c r="I356" s="2" t="n"/>
+      <c r="H356" s="2" t="inlineStr">
+        <is>
+          <t>百貨公司櫃台之勞工，最容易產生的職場健康危害是易因久站，造成下肢靜脈曲張。
+💡 危害解析與原因
+下肢靜脈曲張：百貨專櫃人員因為工作需要長期站立，下肢血液長時間受到地心引力影響，容易造成血液淤積在腿部靜脈，進而導致靜脈瓣膜受損、血管變形，是常見的職業病。
+其他選項皆不符合科學與職業醫學根據：學歷高低與暴力傾向無正當因果關係；職場人際關係因人而異，非普遍性健康危害；飲食習慣屬於個人生活選擇，不屬於專櫃工作的必然職業特徵。
+如果想了解更多，我可以為您提供：
+預防下肢靜脈曲張的日常伸展動作
+專櫃勞工相關的勞動法規權益（如：雇主是否應提供椅凳）
+其他常見的專櫃職業肌肉骨骼疾病
+請問您想深入了解哪一部分呢？ 內容</t>
+        </is>
+      </c>
+      <c r="I356" s="2" t="inlineStr"/>
     </row>
     <row r="357" ht="92.59999999999999" customHeight="1">
       <c r="A357" s="2" t="n">
@@ -13169,8 +16101,15 @@
       <c r="G357" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H357" s="2" t="n"/>
-      <c r="I357" s="2" t="n"/>
+      <c r="H357" s="2" t="inlineStr">
+        <is>
+          <t>在災害防止基本對策中，非屬去除不安全環境之方式為「遵守安全標準作業程序」。
+原因解析
+不安全環境（硬體/環境層面）： 指工作場所、設備、環境本身的缺陷。如設備更新、改善作業環境、設備安全化等，都是針對硬體設施與環境進行改善的工程或管理對策，屬於去除「不安全環境」的方式。
+不安全行為與規範（軟體/人的層面）： 遵守安全標準作業程序是規範人的操作行為、要求勞工配合遵守的措施，因此屬於去除「不安全行為」或教育訓練與管理範疇，而非直接去除不安全環境。</t>
+        </is>
+      </c>
+      <c r="I357" s="2" t="inlineStr"/>
     </row>
     <row r="358" ht="92.59999999999999" customHeight="1">
       <c r="A358" s="2" t="n">
@@ -13204,8 +16143,19 @@
       <c r="G358" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H358" s="2" t="n"/>
-      <c r="I358" s="2" t="n"/>
+      <c r="H358" s="2" t="inlineStr">
+        <is>
+          <t>防止事故發生之安全作業要領通常不包括長時間集會討論。
+重點解析
+不包括的項目：
+長時間集會討論：安全作業要領強調的是實際現場的執行動作與預防措施，冗長的集會討論無助於即時防止作業事故。
+通常包括的項目：
+實施自動檢查
+推行廠場整潔、美化
+徹底做好安全確認（題目中的「役底」為「徹底」之筆誤）</t>
+        </is>
+      </c>
+      <c r="I358" s="2" t="inlineStr"/>
     </row>
     <row r="359" ht="92.59999999999999" customHeight="1">
       <c r="A359" s="2" t="n">
@@ -13239,8 +16189,16 @@
       <c r="G359" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H359" s="2" t="n"/>
-      <c r="I359" s="2" t="n"/>
+      <c r="H359" s="2" t="inlineStr">
+        <is>
+          <t>製程變更之目的，通常不包括(A) 提高風險。
+解析
+通常包括的目的：企業進行製程變更是為了追求最佳效益，包含提高產品品質、降低生產成本以及提高生產效率（或提高產率）。
+不包括的目的：製程變更雖然有時可能「伴隨」或「衍生」出未預期的風險，但其本身的目的絕對不是去「提高風險」。相反地，企業在進行變更時必須透過危害辨識與風險評估，盡力去降低或控制風險。
+iPEDIA 百科</t>
+        </is>
+      </c>
+      <c r="I359" s="2" t="inlineStr"/>
     </row>
     <row r="360" ht="108" customHeight="1">
       <c r="A360" s="2" t="n">
@@ -13274,8 +16232,81 @@
       <c r="G360" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H360" s="2" t="n"/>
-      <c r="I360" s="2" t="n"/>
+      <c r="H360" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+較不恰當的敘述是：應常使用誇大性之專業術語。
+說明
+在職業安全衛生的溝通與協調中，應力求清晰、具體、易懂，並避免使用過度誇大或艱澀難懂的專業術語，以免造成接收訊息者的誤解或溝通障礙。其他選項（保持雙向溝通、對象涵蓋員工與承攬商、建立暢通機制）皆為有效溝通的正確作法。
+想進一步了解其他職業安全衛生管理的相關考題或觀念嗎？
+需不需要補充工作安全分析或安全觀察的實務原則？
+承攬人員、外界相關單位(C)有可確保溝通管道暢通之機制(D)應 ...
+2025年4月23日 — 21. 有關有效的安全衛生協調與溝通之敘述，下列何項較不恰當？(A)有可確保溝通管道暢通之機制(B) 對象應包含員工、承攬人員、外界相關單位(C)應保持雙向溝通管道(D)應常使用誇大性之專業術語。 #2281167 · 45. 有關有效的安全衛生協調與溝通之敘...
+顯示更多
+網頁搜尋結果
+21. 有關有效的安全衛生協調與溝通之敘述，下列何項較不 ...
+› item-21.++有關有效的安全衛生協調...
+2020年5月4日 — 45. 有關有效的安全衛生協調與溝通之敘述，下列何者較不恰當？ (A)應保持雙向溝通管道(B)對象應包含員工、承攬人員、外界相關單位(C)有可確保溝通管道暢通 ...
+缺少字詞： 承 ‎措
+20. 有關有效的安全衛生協調與溝通之敘述，下列何項較不 ...
+› item-20.+有關有效的安全衛生協調與...
+2020年4月27日 — 20. 有關有效的安全衛生協調與溝通之敘述，下列何項較不恰當？ (A)對象應包含員工、承攬人員、外 界相關單位 (B)應常使用誇大性之專業術語 (C)應保持雙向 ...
+缺少字詞： 承 ‎措
+有關有效的安全衛生協調與溝通之敘述，下列何項較不恰當？
+職業安全衛生管理證照題庫練習
+› content › qbDetail
+有關有效的安全衛生協調與溝通之敘述，下列何項較不恰當？ · A 應保持雙向溝通管道 · B 對象應包含員工、承攬人員、外界相關單位 · C 有可確保溝通管道暢通之機制 · D 應常使用 ...
+1 個答案
+·
+最佳解答:
+正確答案：D
+缺少字詞： 何者 ‎承 ‎措
+22100 -職業衛生管理學科| PDF
+› document › 22100-職業衛生...
+(4) 有關有效的安全衛生協調與溝通之敘述，下列何項較不恰當？ ①應保持雙向溝通管道②對象應包含員工、承攬人員、外界相關單位③有可確保溝通管道暢通之機制④應常 ...
+[題庫][職業安全衛生管理(乙)][03：專業課程] BLOCK 學習網
+BLOCK 學習網
+› question
+2 342. 溝通協調可以活化安全教育成效，比課堂上的講授更具功效，下列何者非屬溝通協調之主要項目？ ... 有下列何種情況，則會有溝通障礙的產生？ A 環境干擾. B 距離 ...
+缺少字詞： 有效 ‎敘述, ‎恰當 ? ‎應 ‎保持 ‎對象 ‎員工、 ‎承 ‎措 ‎外界 ‎單位 ‎確保
+國防部軍備局生產製造中心第209廠「聘三等職業安全(衛生) ...
+中華民國國防部- 全球資訊網
+› File
+PDF
+486. 有關有效的安全衛生協調與溝通之敘述，下列何項較不恰當？①有可確保溝通管道暢通. 之機制②對象應包含員工、承攬人員、外界相關單位③應保持雙向溝通管道④應常使用.
+【解答】「職場霸凌防治」@e等公務園+e學中心+學習平臺解答
+› 勤嬉軒 › 票根盒子
+2025年11月26日 — 公務人員執行職務安全及衛生諮詢會的召開，以下哪些敘述是正確的？ 公務人員就安全及衛生防護事項提出建議後，機關應於接到建議後60日內回覆辦理情形。 高 ...
+缺少字詞： 協調 ‎溝通 ‎恰當 ? ‎保持 ‎雙向 ‎管道 ‎對象 ‎承 ‎措 ‎外界 ‎單位 ‎確保
+TAIWAN ROTARY
+taiwan-rotary.org
+› upload › monthly
+PDF
+扶輪簡史. 保羅．哈理斯於1905 年2 月23 日在美國. 伊利諾州芝加哥組織成立了第一個扶輪社。當. 時是一名年輕律師的保羅．哈理斯，為了追求.
+116 頁
+頁面導覽
+1
+2
+3
+4
+5
+6
+7
+8
+9
+10
+下一頁
+頁尾連結
+台灣
+708 臺南市安平區 - 根據你的 IP 位址
+- 更新位置
+說明
+提供意見
+隱私權
+服務條款</t>
+        </is>
+      </c>
+      <c r="I360" s="2" t="inlineStr"/>
     </row>
     <row r="361" ht="92.59999999999999" customHeight="1">
       <c r="A361" s="2" t="n">
@@ -13309,8 +16340,13 @@
       <c r="G361" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H361" s="2" t="n"/>
-      <c r="I361" s="2" t="n"/>
+      <c r="H361" s="2" t="inlineStr">
+        <is>
+          <t>過失之舉證責任為雇主。
+依原《職業災害勞工保護法》第7條（現行相關規定已納入《勞工職業災害保險及保護法》）規定，勞工因職業災害所致之損害，雇主應負賠償責任；但雇主能證明無過失者，不在此限。因此，舉證責任在於雇主必須證明自己沒有過失。</t>
+        </is>
+      </c>
+      <c r="I361" s="2" t="inlineStr"/>
     </row>
     <row r="362" ht="92.59999999999999" customHeight="1">
       <c r="A362" s="2" t="n">
@@ -13344,8 +16380,17 @@
       <c r="G362" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H362" s="2" t="n"/>
-      <c r="I362" s="2" t="n"/>
+      <c r="H362" s="2" t="inlineStr">
+        <is>
+          <t>以上皆是（選項 D）。
+依據《職業安全衛生管理辦法》第12條之2規定，下列事業單位均應參照中央主管機關所定之職業安全衛生管理系統指引，建置適合該事業單位之職業安全衛生管理系統：
+宜蘭縣勞工教育協進會 第一類事業勞工人數在二百人以上者
+有從事石油裂解之石化工業工作場所者
+有從事製造、處置或使用危害性之化學品，數量達中央主管機關規定量以上之工作場所者
+法律百科Legispedia</t>
+        </is>
+      </c>
+      <c r="I362" s="2" t="inlineStr"/>
     </row>
     <row r="363" ht="108" customHeight="1">
       <c r="A363" s="2" t="n">
@@ -13379,8 +16424,16 @@
       <c r="G363" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H363" s="2" t="n"/>
-      <c r="I363" s="2" t="n"/>
+      <c r="H363" s="2" t="inlineStr">
+        <is>
+          <t>依據《職業安全衛生管理辦法》第12-2條規定，電力供應業（屬於第一類事業單位）勞工人數達到 200 人以上者，應參照中央主管機關所定之職業安全衛生管理系統指引，建立及推動職業安全衛生管理系統（TOSHMS）。
+重點整理
+適用對象：電力供應業。
+人數門檻：勞工人數達 200 人以上。
+法規要求：應建立及推動適合該事業單位之 TOSHMS（或同等以上之國家標準 CNS 45001 / ISO 45001 相關管理系統）。</t>
+        </is>
+      </c>
+      <c r="I363" s="2" t="inlineStr"/>
     </row>
     <row r="364" ht="92.59999999999999" customHeight="1">
       <c r="A364" s="2" t="n">
@@ -13414,8 +16467,16 @@
       <c r="G364" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H364" s="2" t="n"/>
-      <c r="I364" s="2" t="n"/>
+      <c r="H364" s="2" t="inlineStr">
+        <is>
+          <t>答案是：(B) ISO 9001
+解析說明
+ISO 9001 是「品質管理系統」（Quality Management System）標準，負責管理產品與服務的品質，不屬於職業安全衛生管理系統。
+OHSAS 18001、ILO-OSH 以及 TOSHMS 均為專門推動與規範工作者安全與健康的職業安全衛生管理系統。
+臺北市政府全球資訊網</t>
+        </is>
+      </c>
+      <c r="I364" s="2" t="inlineStr"/>
     </row>
     <row r="365" ht="92.59999999999999" customHeight="1">
       <c r="A365" s="2" t="n">
@@ -13449,8 +16510,18 @@
       <c r="G365" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H365" s="2" t="n"/>
-      <c r="I365" s="2" t="n"/>
+      <c r="H365" s="2" t="inlineStr">
+        <is>
+          <t>職業安全衛生管理系統所強調的 P-D-C-A 管理循環，係指 規劃 - 實施 - 查核（或檢查） - 改進。
+P-D-C-A 管理循環解析
+P（Plan，規劃）：政策擬定、危害辨識與風險評估、訂定目標及管理方案。
+D（Do，實施／執行）：建立組織架構、實施教育訓練、作業管制與溝通。
+C（Check，查核／檢查）：監督與量測、事故調查、內部稽查與效能評估。
+A（Act，改進／行動）：檢討缺失、矯正與預防措施、持續改善。
+中華檢驗科技有限公司</t>
+        </is>
+      </c>
+      <c r="I365" s="2" t="inlineStr"/>
     </row>
     <row r="366" ht="92.59999999999999" customHeight="1">
       <c r="A366" s="2" t="n">
@@ -13484,8 +16555,18 @@
       <c r="G366" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H366" s="2" t="n"/>
-      <c r="I366" s="2" t="n"/>
+      <c r="H366" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+職業安全衛生管理系統所強調的 P-D-C-A 管理循環中，P 代表的意義是 Plan（計畫／規劃）。
+PDCA 循環四大階段
+Plan（計畫）：辨識工作場所危害、評估風險，並制定安全衛生政策、目標與管理方案。
+Do（執行）：落實執行所規劃的安全衛生計畫、教育訓練與控制措施。
+Check（查核）：檢查、監測及評估作業環境與執行成果，確認是否符合預期目標。
+Act（行動／改善）：依據查核結果進行檢討，採取矯正與預防措施以持續改善系統。</t>
+        </is>
+      </c>
+      <c r="I366" s="2" t="inlineStr"/>
     </row>
     <row r="367" ht="92.59999999999999" customHeight="1">
       <c r="A367" s="2" t="n">
@@ -13519,8 +16600,18 @@
       <c r="G367" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H367" s="2" t="n"/>
-      <c r="I367" s="2" t="n"/>
+      <c r="H367" s="2" t="inlineStr">
+        <is>
+          <t>職業安全衛生管理系統所強調的 P-D-C-A 管理循環中，其 C 代表的意義為 Check（檢查／查核）。
+PDCA 管理循環架構
+P (Plan)：規劃／計畫
+D (Do)：實施／執行
+C (Check)：檢查／查核（評估執行成果與目標是否一致）
+A (Act)：改進／行動（對異常或缺失進行矯正與持續改善）
+職業安全衛生管理資訊平台</t>
+        </is>
+      </c>
+      <c r="I367" s="2" t="inlineStr"/>
     </row>
     <row r="368" ht="92.59999999999999" customHeight="1">
       <c r="A368" s="2" t="n">
@@ -13554,8 +16645,15 @@
       <c r="G368" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H368" s="2" t="n"/>
-      <c r="I368" s="2" t="n"/>
+      <c r="H368" s="2" t="inlineStr">
+        <is>
+          <t>為落實職業安全衛生管理系統中之採購管理，對於請購、採購及驗收人員應提供安全衛生教育訓練必要之措施。
+說明
+正確答案：(A) 安全衛生教育訓練。
+原因：為了確保採購的機械、設備、器具、物料、原料或工程、勞務等符合安全衛生法規與實際需求，相關的請購、採購及驗收人員必須具備相應的職安知識，因此事業單位應給予必要的安全衛生教育訓練。</t>
+        </is>
+      </c>
+      <c r="I368" s="2" t="inlineStr"/>
     </row>
     <row r="369" ht="92.59999999999999" customHeight="1">
       <c r="A369" s="2" t="n">
@@ -13589,8 +16687,19 @@
       <c r="G369" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H369" s="2" t="n"/>
-      <c r="I369" s="2" t="n"/>
+      <c r="H369" s="2" t="inlineStr">
+        <is>
+          <t>臺灣職業安全衛生管理系統中之預防與控制措施項目中，第一優先採行的措施為消除危害及風險。
+危害控制階層（Hierarchy of Controls）
+根據職業安全衛生管理原則，風險控制與預防必須依循由高至低的優先順序：
+消除危害及風險（第一優先：從源頭直接移除危害，如停用有毒化學品或消除高處作業需求）
+替代（第二優先：以危害較低的事物取代，如用水性漆取代溶劑漆）
+工程控制（第三優先：設置隔音、護欄、局部排氣等隔離或機械防護設施）
+行政管理（第四優先：實施教育訓練、輪班制、工作守則等管理措施）
+個人防護具（最後防線：提供安全帽、耳塞、防護面具等個人裝備，為最低優先順序）</t>
+        </is>
+      </c>
+      <c r="I369" s="2" t="inlineStr"/>
     </row>
     <row r="370" ht="92.59999999999999" customHeight="1">
       <c r="A370" s="2" t="n">
@@ -13624,8 +16733,16 @@
       <c r="G370" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H370" s="2" t="n"/>
-      <c r="I370" s="2" t="n"/>
+      <c r="H370" s="2" t="inlineStr">
+        <is>
+          <t>下列何者不是推動臺灣職業安全衛生管理系統 (TOSHMS) 之主要目的的正確答案為：維護環境生態。
+說明
+主要目的：臺灣職業安全衛生管理系統（TOSHMS）的核心目的在於「強化組織自主管理」、「持續改善安全衛生管理績效」以及「降低（防止）職業災害」，保障工作者的安全與健康。
+非主要目的：「維護環境生態」屬於環境管理系統（如 ISO 14001）的主要範疇，而非職業安全衛生管理系統的主要目的。
+中小企業安全衛生資訊網</t>
+        </is>
+      </c>
+      <c r="I370" s="2" t="inlineStr"/>
     </row>
     <row r="371" ht="108" customHeight="1">
       <c r="A371" s="2" t="n">
@@ -13659,8 +16776,15 @@
       <c r="G371" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H371" s="2" t="n"/>
-      <c r="I371" s="2" t="n"/>
+      <c r="H371" s="2" t="inlineStr">
+        <is>
+          <t>依據臺灣職業安全衛生管理系統指引，危害的定義係指對人體的健康造成傷害或損害的潛在因素。
+相關說明
+正確選項：對人體的健康造成傷害或損害的潛在因素（或稱能對人體造成傷害或有損健康的潛在因素）。
+法規依據：參照勞動部頒布之臺灣職業安全衛生管理系統指引第3.7節明訂，「危害」即指能對人體造成傷害或有損健康的潛在因素。</t>
+        </is>
+      </c>
+      <c r="I371" s="2" t="inlineStr"/>
     </row>
     <row r="372" ht="92.59999999999999" customHeight="1">
       <c r="A372" s="2" t="n">
@@ -13694,8 +16818,78 @@
       <c r="G372" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H372" s="2" t="n"/>
-      <c r="I372" s="2" t="n"/>
+      <c r="H372" s="2" t="inlineStr">
+        <is>
+          <t>職業安全衛生活動的最高指導原則為「職業安全衛生政策」。
+正確選項為：職業安全衛生政策
+一般業（重要資料）重新排序版112.07.22 (1465題) (27-52)
+(3)職業安全衛生管理系統之主要架構運作，職業安全衛生活動的最高指導原則為下列何者？①職業安全衛生方案②職業安全衛生計畫③職業安全衛生政策④職業安全衛生指針職業安全衛生政策最高指導原則 6.(3)職業安全衛生政策是企業職業安全衛生管理的最高指導原則，所以下列何...
+網頁搜尋結果
+1.職業安全衛生管理系統之主要架構運作
+› item-1.職業安全衛生管理系統之主要...
+2018年9月30日 — 22.職業安全衛生管理系統之主要架構運作，職業安全衛生活動的最高指導原則為下列何者？(A)職業 安全衛生計畫(B)職業安全衛生政策(C)職業安全衛生指針(D) ...
+22.職業安全衛生管理系統之主要架構運作
+› item-22.職業安全衛生管理系統之主...
+2018年9月30日 — 22.職業安全衛生管理系統之主要架構運作，職業安全衛生活動的最高指導原則為下列何者？ (A)職業 安全衛生計畫 (B)職業安全衛生政策 (C)職業安全衛生指針 ( ...
+1.職業安全衛生管理系統之主要架構運作
+› item-1.職業安全衛生管理系統之主要...
+2024年5月29日 — 22.職業安全衛生管理系統之主要架構運作，職業安全衛生活動的最高指導原則為下列何者？(A)職業 安全衛生計畫(B)職業安全衛生政策(C)職業安全衛生指針(D) ...
+一般業（重要資料）重新排序版112.07.22 (1465題) (27-52)
+› document › 一般業-重要資料...
+... 架構運作，職業安全衛生活動的最高指導原則為下列何者？①職業安全衛生方案②職業安全衛生計畫③職業安全衛生政策④職業安全衛生指針職業安全衛生政策最高指導原則 6 ...
+​【你知道嗎？職安快問快答】 ​❓ 考考你：職業安全衛生管理 ...
+Threads
+› @osh_flourishing
+2026年6月9日 — ... 管理系統之主要架構運作，職業安全衛生活動的最高指導原則為下列何者？ 職業安全衛生計畫. 39%. 職業安全衛生方案. 3%. 職業安全衛生指針. 3%. 職業安全 ...
+職業安全衛生管理規章及職業安全衛生管理計畫指導原則
+勞動部職業安全衛生署
+› media › 職業安全衛...
+PDF
+職業安全衛生管理規章指事業單位為有效防止職業災害，促進. 勞工安全與健康，所訂定要求各級主管及管理、指揮、監督等有關. 人員執行與職業安全衛生有關之內部管理程序、 ...
+14 頁
+缺少字詞： 何者 ? ‎方案
+324. 職業安全衛生管理系統之主要架構運作
+› item-324.++職業安全衛生管理系統之...
+2022年12月11日 — 324. 職業安全衛生管理系統之主要架構運作，職業安全衛生活動的最高 指導原則為下列何者？ (A)職業安全衛生方案 (B)職業安全衛生計畫 (C)職業安全衛生政策
+缺少字詞： 事業 ‎| 必須包含以下字詞： 事業
+相關問題
+職業安全衛生管理規章的架構是什麼?
+職業安全衛生管理系統包括哪五個主要項目？
+職業安全衛生管理單位「專責」、一級的意思為何？
+職業病診斷的五大原則是什麼?
+網頁搜尋結果
+職業安全衛生管理規章及職業安全衛生管理計畫指導原則
+› FLAW › PrintFLAWDAT0202
+（一）規章之架構如下： 1.制定目的：制定規章預定達到之目的，如降低職災、維護勞工安全及健康等。 2.適用範圍：依規章所適用之相關人員、業務或工作場所等。 3.規章內容 ...
+缺少字詞： 何者 ? ‎方案
+113年TOSHMS 臺灣職業安全衛生管理系統介紹
+財團法人職業災害預防及重建中心
+› files
+PDF
+2024年7月10日 — 一、應實施檢查之事業單位. (二)職業安全衛生部分：. 1.發生死亡或重傷之職業災害及應追蹤改善情形者。 2.年度防災重點輔導對象，不配合改善職業安全 ...
+頁面導覽
+1
+2
+3
+4
+5
+6
+7
+8
+9
+10
+下一頁
+頁尾連結
+台灣
+708 臺南市安平區 - 根據你的 IP 位址
+- 更新位置
+說明
+提供意見
+隱私權
+服務條款</t>
+        </is>
+      </c>
+      <c r="I372" s="2" t="inlineStr"/>
     </row>
     <row r="373" ht="92.59999999999999" customHeight="1">
       <c r="A373" s="2" t="n">
@@ -13729,8 +16923,19 @@
       <c r="G373" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H373" s="2" t="n"/>
-      <c r="I373" s="2" t="n"/>
+      <c r="H373" s="2" t="inlineStr">
+        <is>
+          <t>臺灣職業安全衛生管理系統之簡稱為 TOSHMS。
+財團法人全國認證基金會
+相關名詞對照
+TOSHMS：臺灣職業安全衛生管理系統（Taiwan Occupational Safety and Health Management System）。
+OHSAS 18001：過去國際通用的職業安全衛生管理系統規範（已被 ISO 45001 取代）。
+VPP：自主安全衛生管理優良單位（Voluntary Protection Program）。
+TS：台灣規格或驗證相關規範（Taiwan Specification）。
+財團法人全國認證基金會</t>
+        </is>
+      </c>
+      <c r="I373" s="2" t="inlineStr"/>
     </row>
     <row r="374" ht="92.59999999999999" customHeight="1">
       <c r="A374" s="2" t="n">
@@ -13764,8 +16969,16 @@
       <c r="G374" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H374" s="2" t="n"/>
-      <c r="I374" s="2" t="n"/>
+      <c r="H374" s="2" t="inlineStr">
+        <is>
+          <t>「增加客戶對產品品質的抱怨」是有誤的選項。
+原因說明
+職業安全衛生管理系統（如 OHSMS、TOSHMS 等）的核心目的是保護工作者的安全與健康、預防職業災害。
+它可以降低職災、減少災害善後支出並避免經營中斷。
+產品品質屬於品質管理系統（如 ISO 9000 系列）的範疇，與職業安全衛生管理系統無直接關聯。</t>
+        </is>
+      </c>
+      <c r="I374" s="2" t="inlineStr"/>
     </row>
     <row r="375" ht="92.59999999999999" customHeight="1">
       <c r="A375" s="2" t="n">
@@ -13799,8 +17012,15 @@
       <c r="G375" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H375" s="2" t="n"/>
-      <c r="I375" s="2" t="n"/>
+      <c r="H375" s="2" t="inlineStr">
+        <is>
+          <t>為執行職業安全衛生管理系統的績效監督與量測，被動指標通常會選用職業傷病統計資料。
+指標說明
+被動指標（Reactive Indicators）：指用來追蹤、量測與調查已經發生的不良事件（如事故、職業病、傷害）的指標，例如職業傷病統計資料、失能頻率及失能嚴重率等。
+主動指標（Proactive Indicators）：指在事故發生前，用來監督與評估安全衛生管理活動及預防措施落實情形的指標，例如教育訓練人數、安衛提案件數、機械設備數量等。</t>
+        </is>
+      </c>
+      <c r="I375" s="2" t="inlineStr"/>
     </row>
     <row r="376" ht="92.59999999999999" customHeight="1">
       <c r="A376" s="2" t="n">
@@ -13834,8 +17054,15 @@
       <c r="G376" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H376" s="2" t="n"/>
-      <c r="I376" s="2" t="n"/>
+      <c r="H376" s="2" t="inlineStr">
+        <is>
+          <t>依臺灣職業安全衛生管理系統指引之規定，採取矯正措施的目的是(A) 預防事故再度發生。
+說明
+矯正措施（Corrective Action）：是用來消除已發現的不符合事項、事故或其他不安全情況之「根本原因」，以預防其再次發生。
+其核心精神在於系統性改善與風險控制，而非針對個人進行懲處或行政程序。</t>
+        </is>
+      </c>
+      <c r="I376" s="2" t="inlineStr"/>
     </row>
     <row r="377" ht="92.59999999999999" customHeight="1">
       <c r="A377" s="2" t="n">
@@ -13869,8 +17096,17 @@
       <c r="G377" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H377" s="2" t="n"/>
-      <c r="I377" s="2" t="n"/>
+      <c r="H377" s="2" t="inlineStr">
+        <is>
+          <t>答案為 (A) 製程技術修改。
+解析與說明
+製程技術修改：屬於職業安全衛生管理中「變更管理」（Management of Change, MOC）或「製程變更管理」的範疇，涉及操作條件、方法、技術、化學品或設備調整，需進行安全評估。
+健康檢查：屬於勞工健康保護與醫學管理範疇。
+組織調整、薪資結構變動：屬於公司的人事行政與人力資源管理範疇，不屬於製程技術與安全變更管理。
+高雄市政府全球資訊網</t>
+        </is>
+      </c>
+      <c r="I377" s="2" t="inlineStr"/>
     </row>
     <row r="378" ht="92.59999999999999" customHeight="1">
       <c r="A378" s="2" t="n">

--- a/salf/丙種職業安全衛生業務主管題庫.xlsx
+++ b/salf/丙種職業安全衛生業務主管題庫.xlsx
@@ -17140,8 +17140,15 @@
       <c r="G378" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H378" s="2" t="n"/>
-      <c r="I378" s="2" t="n"/>
+      <c r="H378" s="2" t="inlineStr">
+        <is>
+          <t>高風險事業單位已實施職業安全衛生管理系統，其所設置之職業安全衛生管理單位須由管理績效報經中央主管機關認可，才得以免除一級專責的限制。
+Quizlet
+正確答案為：管理績效報經中央主管機關認可。
+Quizlet</t>
+        </is>
+      </c>
+      <c r="I378" s="2" t="inlineStr"/>
     </row>
     <row r="379" ht="92.59999999999999" customHeight="1">
       <c r="A379" s="2" t="n">
@@ -17175,8 +17182,13 @@
       <c r="G379" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H379" s="2" t="n"/>
-      <c r="I379" s="2" t="n"/>
+      <c r="H379" s="2" t="inlineStr">
+        <is>
+          <t>執行計畫。
+根據職業安全衛生管理辦法及相關指引規定，企業或事業單位在訂定整體的「職業安全衛生管理計畫」後，為了能落實推動，應再依據計畫內容制訂詳細的執行計畫，以明確規範各項措施的實施步驟、期程、負責部門及資源配置。</t>
+        </is>
+      </c>
+      <c r="I379" s="2" t="inlineStr"/>
     </row>
     <row r="380" ht="92.59999999999999" customHeight="1">
       <c r="A380" s="2" t="n">
@@ -17210,8 +17222,12 @@
       <c r="G380" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H380" s="2" t="n"/>
-      <c r="I380" s="2" t="n"/>
+      <c r="H380" s="2" t="inlineStr">
+        <is>
+          <t>職業安全衛生管理計畫訂定完成後，對於中小事業單位無安全衛生委員會者，可由安全衛生業務主管擬定職業安全衛生管理計畫後，送請雇主核定後實施。</t>
+        </is>
+      </c>
+      <c r="I380" s="2" t="inlineStr"/>
     </row>
     <row r="381" ht="92.59999999999999" customHeight="1">
       <c r="A381" s="2" t="n">
@@ -17245,8 +17261,17 @@
       <c r="G381" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H381" s="2" t="n"/>
-      <c r="I381" s="2" t="n"/>
+      <c r="H381" s="2" t="inlineStr">
+        <is>
+          <t>職業安全衛生管理計畫是年度性的。
+依據勞動部頒定的職業安全衛生管理規章及職業安全衛生管理計畫指導原則，職業安全衛生管理計畫應以「年度計畫」為週期進行系統性規劃與滾動式修正。
+勞動部職業安全衛生署
+重點說明
+年度週期：每年重新檢討、擬定與執行，並配合績效考核與定期檢查（至少每季一次）。
+核心內容：包含政策發布、安全目標、各級權責、具體計畫項目（如機械管理、化學品管理、教育訓練等）及經費編列。</t>
+        </is>
+      </c>
+      <c r="I381" s="2" t="inlineStr"/>
     </row>
     <row r="382" ht="92.59999999999999" customHeight="1">
       <c r="A382" s="2" t="n">
@@ -17280,8 +17305,13 @@
       <c r="G382" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H382" s="2" t="n"/>
-      <c r="I382" s="2" t="n"/>
+      <c r="H382" s="2" t="inlineStr">
+        <is>
+          <t>事業單位年度職業安全衛生管理計畫，職業安全衛生管理單位應彙整報請事業單位負責人（或雇主）核定後確實實施。
+國立臺北商業大學</t>
+        </is>
+      </c>
+      <c r="I382" s="2" t="inlineStr"/>
     </row>
     <row r="383" ht="92.59999999999999" customHeight="1">
       <c r="A383" s="2" t="n">
@@ -17315,8 +17345,15 @@
       <c r="G383" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H383" s="2" t="n"/>
-      <c r="I383" s="2" t="n"/>
+      <c r="H383" s="2" t="inlineStr">
+        <is>
+          <t>下列何者為職業安全衛生管理計畫之經常性工作項目：職業安全衛生教育訓練計畫。
+職業安全衛生管理計畫項目解析
+經常性工作項目：如職業安全衛生教育訓練計畫、安全衛生作業標準、定期檢查與現場巡視等，屬於事業單位需持續、例行推動的安全衛生管理核心項目。
+非經常性或專案/階段性項目：如申請自護制度計畫、推行並通過 OHSAS 18000/ISO 45001 認證、計畫危險性工作場所審查申請等，多屬於特定階段或目標導向的專案工作。</t>
+        </is>
+      </c>
+      <c r="I383" s="2" t="inlineStr"/>
     </row>
     <row r="384" ht="108" customHeight="1">
       <c r="A384" s="2" t="n">
@@ -17350,8 +17387,19 @@
       <c r="G384" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H384" s="2" t="n"/>
-      <c r="I384" s="2" t="n"/>
+      <c r="H384" s="2" t="inlineStr">
+        <is>
+          <t>在職業安全衛生管理計畫中，「設備本質安全改善及作業程序更新計畫」屬於非經常性工作項目。
+📊 經常性與非經常性工作對照
+為了方便您理解，以下將選項中的工作項目進行分類比較：
+工作項目	性質分類	說明
+設備本質安全改善及作業程序更新計畫	❌ 非經常性工作	通常屬於專案型或階段性工作。當設備需要汰舊換新、製程改變、發生事故或法規修訂時，才會特別進行的改善與更新。
+防護具使用、管理及採購計畫	⭕ 經常性工作	屬於日常或定期維護的庶務。防護具需要持續發放、定期檢查、盤點並依消耗狀況常態性採購。
+局限空間作業災害防止計畫	⭕ 經常性工作	屬於日常作業的安全管理。只要廠內有局限空間作業，就必須持續執行許可證申請、氣體偵測及現場監督。
+安全衛生稽核計畫	⭕ 經常性工作	屬於管理制度中的定期稽核（如每月、每季或每年定期辦理），是維持管理系統運作的例行性工作。</t>
+        </is>
+      </c>
+      <c r="I384" s="2" t="inlineStr"/>
     </row>
     <row r="385" ht="92.59999999999999" customHeight="1">
       <c r="A385" s="2" t="n">
@@ -17385,8 +17433,13 @@
       <c r="G385" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H385" s="2" t="n"/>
-      <c r="I385" s="2" t="n"/>
+      <c r="H385" s="2" t="inlineStr">
+        <is>
+          <t>依據《職業安全衛生法》及《職業安全衛生管理辦法》規定，事業單位之職業安全衛生管理應由各部門主管依其職責指揮、監督所屬人員執行之責（而整體安全衛生管理則由雇主、工作場所負責人綜理）。
+因此，本題正確選項為：各部門主管。</t>
+        </is>
+      </c>
+      <c r="I385" s="2" t="inlineStr"/>
     </row>
     <row r="386" ht="92.59999999999999" customHeight="1">
       <c r="A386" s="2" t="n">
@@ -17420,8 +17473,13 @@
       <c r="G386" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H386" s="2" t="n"/>
-      <c r="I386" s="2" t="n"/>
+      <c r="H386" s="2" t="inlineStr">
+        <is>
+          <t>事業單位安全衛生管理政策應由雇主制定。
+依據《職業安全衛生管理辦法》及相關法規，安全衛生政策是企業經營最高指導原則，必須由最高決策者即雇主親自擬定與頒布，再由各級主管與管理人員推動執行。</t>
+        </is>
+      </c>
+      <c r="I386" s="2" t="inlineStr"/>
     </row>
     <row r="387" ht="92.59999999999999" customHeight="1">
       <c r="A387" s="2" t="n">
@@ -17455,8 +17513,15 @@
       <c r="G387" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H387" s="2" t="n"/>
-      <c r="I387" s="2" t="n"/>
+      <c r="H387" s="2" t="inlineStr">
+        <is>
+          <t>一般而言，變更管理計畫通常不包括 (A) 組織架構 變更。
+詳細說明
+根據勞動部變更管理技術指引之規定，職業安全衛生或製程中的「變更管理」主要是針對製程、活動或服務中各項作業的調整，包含作業之條件、方法、原物料、機械或設備等。而「組織架構調整」或人員異動等，通常屬於行政組織與人事管理範疇，並未直接涵蓋在作業與製程的變更管理計畫中。
+植根法律網</t>
+        </is>
+      </c>
+      <c r="I387" s="2" t="inlineStr"/>
     </row>
     <row r="388" ht="92.59999999999999" customHeight="1">
       <c r="A388" s="2" t="n">
@@ -17490,8 +17555,20 @@
       <c r="G388" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H388" s="2" t="n"/>
-      <c r="I388" s="2" t="n"/>
+      <c r="H388" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+緊急應變演練非系統架構建置期的工作。
+職業安全衛生管理系統建置期說明
+系統架構建置期包含的工作：
+先期審查（Initial Review）：了解現況與法規符合度。
+風險評估（Risk Assessment）：辨識危害並評估風險等級。
+目標與方案（Objectives and Programs）：擬定安衛目標及執行方案。
+非建置期工作：
+緊急應變演練屬於系統實際運作與執行階段（實施與運作期）的具體落實與驗證工作，而不是架構建置規畫期的主要項目。</t>
+        </is>
+      </c>
+      <c r="I388" s="2" t="inlineStr"/>
     </row>
     <row r="389" ht="92.59999999999999" customHeight="1">
       <c r="A389" s="2" t="n">
@@ -17525,8 +17602,15 @@
       <c r="G389" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H389" s="2" t="n"/>
-      <c r="I389" s="2" t="n"/>
+      <c r="H389" s="2" t="inlineStr">
+        <is>
+          <t>安全衛生稽核是職業安全衛生管理系統之主動式評鑑資料。
+說明
+主動式評鑑（Proactive monitoring）：指在發生事故或危害顯現之前，主動對工作環境、設備、作業程序及安全衛生管理系統執行情況進行檢查與評估，例如安全衛生稽核、安全巡檢、健康檢查等。
+被動式評鑑（Reactive monitoring）：指在事故、危害或缺失發生後才進行調查與檢討的資料，如虛驚事故、職災發生、附近居民抗議或主管機關的糾正等。</t>
+        </is>
+      </c>
+      <c r="I389" s="2" t="inlineStr"/>
     </row>
     <row r="390" ht="108" customHeight="1">
       <c r="A390" s="2" t="n">
@@ -17560,8 +17644,19 @@
       <c r="G390" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H390" s="2" t="n"/>
-      <c r="I390" s="2" t="n"/>
+      <c r="H390" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+系統架構建置期主要完成的项目是 (A) 召開啟始會議、安衛風險評估。
+根據職業安全衛生管理系統（如 TOSHMS）建置實務與相關考題對照：
+(A) 召開啟始會議、安衛風險評估：對應系統架構建置與準備規劃階段的核心事項。
+(B) 先期審查、系統運作及記錄
+(C) 法規鑑別查核、安衛風險評估
+(D) 政策目標及方案、系統運作及記錄
+詳細歷程與考古題解析可參考 Yamol 考試題庫。</t>
+        </is>
+      </c>
+      <c r="I390" s="2" t="inlineStr"/>
     </row>
     <row r="391" ht="92.59999999999999" customHeight="1">
       <c r="A391" s="2" t="n">
@@ -17595,8 +17690,16 @@
       <c r="G391" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H391" s="2" t="n"/>
-      <c r="I391" s="2" t="n"/>
+      <c r="H391" s="2" t="inlineStr">
+        <is>
+          <t>這種教育訓練需求分析是屬於 (A) 組織層級的分析。
+分析原因
+組織層級分析（Organizational Analysis）： 從整個企業或組織的方針、政策、安全衛生指標及整體目標出發，來評估哪些部門或整體需要何種訓練，以確保安全衛生計畫符合組織的政策方向。
+工作層級分析（Task/Job Analysis）： 著重於特定工作內容與操作步驟所需的技能與知識。
+個人層級分析（Individual Analysis）： 針對個別員工的表現與能力差距來決定培訓需求。</t>
+        </is>
+      </c>
+      <c r="I391" s="2" t="inlineStr"/>
     </row>
     <row r="392" ht="108" customHeight="1">
       <c r="A392" s="2" t="n">
@@ -17630,8 +17733,20 @@
       <c r="G392" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H392" s="2" t="n"/>
-      <c r="I392" s="2" t="n"/>
+      <c r="H392" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+錯誤的敘述為：(A) 職業安全衛生業務主管綜理職業安全衛生管理之責。
+錯誤原因說明
+依據《職業安全衛生法施行細則》規定，事業單位的職業安全衛生管理，負綜理之責的是「雇主」（或對事業具管理權限之雇主代理人），而不是職業安全衛生業務主管。職業安全衛生業務主管或管理人員的職責是協助雇主規劃、辦理或督導安全衛生管理相關業務，而非「綜理」。
+正確對照
+(A) 錯誤：應由雇主綜理，非業務主管。
+(B) 正確：各級主管就其各部門內，執行與其有關之職業安全衛生事項。
+(C) 正確：領班督導所屬勞工，注意安全衛生。
+(D) 正確：現場勞工遵守安全衛生有關規定，防止職業災害。</t>
+        </is>
+      </c>
+      <c r="I392" s="2" t="inlineStr"/>
     </row>
     <row r="393" ht="92.59999999999999" customHeight="1">
       <c r="A393" s="2" t="n">
@@ -17665,8 +17780,18 @@
       <c r="G393" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H393" s="2" t="n"/>
-      <c r="I393" s="2" t="n"/>
+      <c r="H393" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+零災害運動四階段演練之第四階段為 設定行動目標（即決定行動計畫／設定目標、濃縮集中）。
+零災害四階段演練內容
+第一階段：抓住事實（掌握現狀），使用 腦力激盪。
+第二階段：尋找真因（追究真相），進行濃縮集中（質）。
+第三階段：建立對策，使用 腦力激盪。
+第四階段：設定行動目標（決定行動計畫），進行濃縮集中（量）。</t>
+        </is>
+      </c>
+      <c r="I393" s="2" t="inlineStr"/>
     </row>
     <row r="394" ht="92.59999999999999" customHeight="1">
       <c r="A394" s="2" t="n">
@@ -17700,8 +17825,16 @@
       <c r="G394" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H394" s="2" t="n"/>
-      <c r="I394" s="2" t="n"/>
+      <c r="H394" s="2" t="inlineStr">
+        <is>
+          <t>零災害運動的 3 大原則通常不包括 (A) 要求完美。
+零災害運動（Zero Disaster Campaign）的三大原則為：
+以零為目標（無災害、無疾病、無傷亡）
+先知先制（預先發現潛在危險並採取對策）
+全員參加（從最高主管到基層勞工全面參與）</t>
+        </is>
+      </c>
+      <c r="I394" s="2" t="inlineStr"/>
     </row>
     <row r="395" ht="92.59999999999999" customHeight="1">
       <c r="A395" s="2" t="n">
@@ -17735,8 +17868,15 @@
       <c r="G395" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H395" s="2" t="n"/>
-      <c r="I395" s="2" t="n"/>
+      <c r="H395" s="2" t="inlineStr">
+        <is>
+          <t>變更管理之所謂變更，通常不包括 商標變更。
+說明
+商標變更：屬於商業、智慧財產權或品牌行銷範疇，與工安、製程技術、設備或物料等操作安全性無關，因此不屬於職業安全衛生或製程安全中「變更管理（Management of Change, MOC）」的管轄範圍。
+製程變更、材料變更、設備變更：皆會直接影響操作安全、物化性質或生產環境，屬於變更管理必須嚴格評估與控制的技術性項目。</t>
+        </is>
+      </c>
+      <c r="I395" s="2" t="inlineStr"/>
     </row>
     <row r="396" ht="92.59999999999999" customHeight="1">
       <c r="A396" s="2" t="n">
@@ -17770,8 +17910,15 @@
       <c r="G396" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H396" s="2" t="n"/>
-      <c r="I396" s="2" t="n"/>
+      <c r="H396" s="2" t="inlineStr">
+        <is>
+          <t>臺灣職業安全衛生管理系統涵蓋的項目為採購管理。
+選項分析：
+(B) 採購管理：屬於臺灣職業安全衛生管理系統及職業安全衛生管理計畫中規範的重要事項。
+(A) 環境影響評估、(C) 6 個標準差、(D) 廢水處理：皆不屬於職業安全衛生管理系統所涵蓋之核心項目。</t>
+        </is>
+      </c>
+      <c r="I396" s="2" t="inlineStr"/>
     </row>
     <row r="397" ht="92.59999999999999" customHeight="1">
       <c r="A397" s="2" t="n">
@@ -17805,8 +17952,16 @@
       <c r="G397" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H397" s="2" t="n"/>
-      <c r="I397" s="2" t="n"/>
+      <c r="H397" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+依據變更管理技術指引之要求，變更管理之作業流程中應最先執行的是界定變更管制範圍。
+變更管理作業流程重點
+界定變更管制範圍：為流程的第一步，應明確定義出變更管制的適用範圍（如建築物、設備、化學品、標準作業程序等之新增與變更）。
+後續步驟依序包含研訂變更管理制度、諮詢、變更之申請、危害評估與成效確認等。</t>
+        </is>
+      </c>
+      <c r="I397" s="2" t="inlineStr"/>
     </row>
     <row r="398" ht="92.59999999999999" customHeight="1">
       <c r="A398" s="2" t="n">
@@ -17840,8 +17995,29 @@
       <c r="G398" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H398" s="2" t="n"/>
-      <c r="I398" s="2" t="n"/>
+      <c r="H398" s="2" t="inlineStr">
+        <is>
+          <t>正確答案為：OHSAS18001 已包含 TOSHMS 之所有規定是不對的，等等，看題目與選項：
+選項分析：
+(A) OHSAS18001 已包含 TOSHMS 之所有規定（錯誤，TOSHMS 包含國內法規與特定稽核重點）
+(B) 兩者均非 ISO 國際標準（OHSAS 18001 是英國標準 BS OHSAS 18001，早期也非正式 ISO 國際標準，但通常這題的正確答案是什麼？讓我們看題庫解析）
+查閱考古題發現此題正確答案為「兩者均非 ISO 國際標準」（OHSAS 18001 是 BS 協會標準，TOSHMS 是我國臺灣本土規範，兩者嚴格來說都不是 ISO 組織發布的 ISO 國際標準，如 ISO 45001 才屬於 ISO 國際標準）。
+匯續永續股份有限公司 OHSAS 18001 與 TOSHMS 之差異
+OHSAS 18001：
+屬早期由英國標準協會（BSI）等國際機構所發布的民間驗證標準，並非 ISO 國際標準。
+ORIGO森維國際認證集團 TOSHMS（臺灣職業安全衛生管理系統）：
+由我國勞動部（前勞委會）主導推動，結合國家標準與我國在地法規要求（加入特定稽核重點事項），亦非 ISO 國際標準。
+臺灣職業安全衛生管理系統資訊網 正確選項解析
+正確答案：兩者均非 ISO 國際標準。
+其他選項錯誤原因：
+OHSAS18001 已包含 TOSHMS 之所有規定：錯誤，OHSAS 18001 未涵蓋臺灣在地職業安全衛生法規的特定稽核重點。
+兩者均向勞動部申請驗證：錯誤，OHSAS 18001 是由民間認可的第三方驗證機構執行，並非直接向勞動部申請。
+兩者之驗證內容完全一致：錯誤，TOSHMS 額外包含國內法規要求及特定查核重點。
+Facebook
+·JENO Int.傑諾國際標準驗證有限公司</t>
+        </is>
+      </c>
+      <c r="I398" s="2" t="inlineStr"/>
     </row>
     <row r="399" ht="92.59999999999999" customHeight="1">
       <c r="A399" s="2" t="n">
@@ -17875,8 +18051,19 @@
       <c r="G399" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H399" s="2" t="n"/>
-      <c r="I399" s="2" t="n"/>
+      <c r="H399" s="2" t="inlineStr">
+        <is>
+          <t>針對職業安全衛生管理系統稽核所發現的不符合事項，應採取矯正措施。
+正確答案：矯正措施（用於消除不符合事項之原因，並防止其再次發生）。
+需要了解更多關於職業安全衛生管理系統的相關規定嗎？
+內部稽核與改善流程
+危害辨識與風險評估
+職業安全衛生法規重點
+針對職業安全衛生管理系統稽核所發現不符合事項，應採取何 ...
+2022年4月20日 — 13針對職業安全衛生管理系統稽核所發現不符合事項，應採取何種措施？ (A)矯正措施 (B)鑑別措施 (C)防護措施 (D)控制措施。 答案：登入後查看</t>
+        </is>
+      </c>
+      <c r="I399" s="2" t="inlineStr"/>
     </row>
     <row r="400" ht="92.59999999999999" customHeight="1">
       <c r="A400" s="2" t="n">
@@ -17910,8 +18097,20 @@
       <c r="G400" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H400" s="2" t="n"/>
-      <c r="I400" s="2" t="n"/>
+      <c r="H400" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+答案是 ISO 9001。
+詳細說明
+ISO 9001 是國際標準組織（ISO）所制定的品質管理系統（Quality Management System, QMS）標準，著重於顧客滿意與產品/服務品質，不屬於職業安全衛生管理系統。
+OHSAS 18001（題目中常寫作 OHSASI8001 / OHSAS18001）為過去廣泛使用的職業安全衛生管理系統標準（現已被 ISO 45001 取代）。
+ISO 45001 是現行國際通用的職業安全衛生管理系統標準。
+臺灣職業安全衛生管理系統資訊網
+TOSHMS 是我國勞動部職業安全衛生署推動的臺灣職業安全衛生管理系統（Taiwan Occupational Safety and Health Management System）。
+勞動部全球資訊網</t>
+        </is>
+      </c>
+      <c r="I400" s="2" t="inlineStr"/>
     </row>
     <row r="401" ht="92.59999999999999" customHeight="1">
       <c r="A401" s="2" t="n">
@@ -17945,8 +18144,12 @@
       <c r="G401" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H401" s="2" t="n"/>
-      <c r="I401" s="2" t="n"/>
+      <c r="H401" s="2" t="inlineStr">
+        <is>
+          <t>依臺灣職業安全衛生管理系統（TOSHMS）驗證指導要點之定義，執行事業單位職業安全衛生管理系統稽核、驗證之機構，在舊版或部分條文中稱為認可驗證機構（或依最新條文定義為「驗證機構」或「TOSHMS驗證機構」）。在選項中正確答案為認可驗證機構。</t>
+        </is>
+      </c>
+      <c r="I401" s="2" t="inlineStr"/>
     </row>
     <row r="402" ht="92.59999999999999" customHeight="1">
       <c r="A402" s="2" t="n">
@@ -17980,8 +18183,15 @@
       <c r="G402" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H402" s="2" t="n"/>
-      <c r="I402" s="2" t="n"/>
+      <c r="H402" s="2" t="inlineStr">
+        <is>
+          <t>答案是 安全衛生輔導手冊。
+說明
+安全衛生輔導手冊 並非中央主管機關（勞動部職業安全衛生署）所發布之臺灣職業安全衛生管理系統（TOSHMS）正式相關管理文件。
+其他三項（TOSHMS 指引、TOSHMS 驗證規範、TOSHMS 指導綱領）皆屬於中央主管機關針對 TOSHMS 所發布的官方推動與驗證相關規範文件。</t>
+        </is>
+      </c>
+      <c r="I402" s="2" t="inlineStr"/>
     </row>
     <row r="403" ht="92.59999999999999" customHeight="1">
       <c r="A403" s="2" t="n">
@@ -18015,8 +18225,20 @@
       <c r="G403" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H403" s="2" t="n"/>
-      <c r="I403" s="2" t="n"/>
+      <c r="H403" s="2" t="inlineStr">
+        <is>
+          <t>下列有誤的選項是：須向勞動檢查機構報備。
+解析
+正確的動機或目的：
+提升安全衛生管理水準：藉由系統化運作降低職業災害。
+希望透過第三者的稽核，瞭解是否符合系統要求：透過外部獨立驗證來檢視管理成效與盲點。
+客戶在貿易上的要求：許多國際供應鏈或大型企業會要求合作廠商取得相關安衛驗證。
+錯誤的原因：
+職業安全衛生管理系統（如 TOSHMS / ISO 45001）的驗證主要是企業自主管理、提升競爭力或因應客戶與社會責任的自願性或市場所趨行為，並非「須向勞動檢查機構報備」的法定強制義務。勞檢機構僅對特定重大職災、危險性機械設備或職災月報有通報及備查要求，而非針對管理系統驗證結果進行報備。
+臺北市勞動檢查處</t>
+        </is>
+      </c>
+      <c r="I403" s="2" t="inlineStr"/>
     </row>
     <row r="404" ht="92.59999999999999" customHeight="1">
       <c r="A404" s="2" t="n">
@@ -18050,8 +18272,18 @@
       <c r="G404" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H404" s="2" t="n"/>
-      <c r="I404" s="2" t="n"/>
+      <c r="H404" s="2" t="inlineStr">
+        <is>
+          <t>「安全衛生績效競賽實施要點」不屬於職業安全衛生管理規章中之政策與組織規定。
+根據勞動部訂定之「職業安全衛生管理規章及職業安全衛生管理計畫指導原則」，職業安全衛生管理規章中之「政策與組織」規章主要包含：
+安全衛生政策及目標
+安全衛生權責劃分標準
+職業安全衛生委員會組織規程
+職業安全衛生管理單位設置及職責等相關規定
+勞動部職業安全衛生署 而「安全衛生績效競賽實施要點」則通常歸類在獎懲或推行激勵相關之管理規定，而非政策與組織架構本身。</t>
+        </is>
+      </c>
+      <c r="I404" s="2" t="inlineStr"/>
     </row>
     <row r="405" ht="108" customHeight="1">
       <c r="A405" s="2" t="n">
@@ -18085,8 +18317,21 @@
       <c r="G405" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H405" s="2" t="n"/>
-      <c r="I405" s="2" t="n"/>
+      <c r="H405" s="2" t="inlineStr">
+        <is>
+          <t>有誤的敘述為：「僅涉及設備或材料等硬體變更事項，未必須再實施風險評估」。
+錯誤原因解析
+在臺灣職業安全衛生管理系統指引的變更管理規範中，無論變更事項是屬於硬體（如設備、機械、材料、原料等）還是軟體/程序（如作業流程、組織變更、法規調整等），只要進行變更，事前均必須重新實施危害辨識與風險評估，以確保不會因變更而衍生新的安全衛生風險或疏漏。
+正確觀念對照
+事前風險評估：任何變更實施前，皆須進行風險評估。
+告知與訓練：與變更有關之人員均須被充分告知相關資訊並給予必要訓練。
+文件修正：與變更有關的作業程序、安全守則或相關文件均須進行檢討與修正。
+是否需要我為您整理 職業安全衛生管理系統中「變更管理」的完整執行步驟 或其他相關的考題解析？
+. () 有關臺灣職業安全衛生管理系統指引中之敘述
+977. () 有關臺灣職業安全衛生管理系統指引中之敘述，下列何者有誤？ (A)事前應實施風險評估 (B)與變更有關人員均 須被告知或訓練 (C)僅涉及設備或材料 等硬體變更事項， 未必須再實施風險 評估 (D)與變更有關文件均 須被檢討修正. 答案：登入後查...</t>
+        </is>
+      </c>
+      <c r="I405" s="2" t="inlineStr"/>
     </row>
     <row r="406" ht="92.59999999999999" customHeight="1">
       <c r="A406" s="2" t="n">
@@ -18120,8 +18365,19 @@
       <c r="G406" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H406" s="2" t="n"/>
-      <c r="I406" s="2" t="n"/>
+      <c r="H406" s="2" t="inlineStr">
+        <is>
+          <t>下列何者不包含在內：(D) 逾期罰款。
+依據《加強公共工程職業安全衛生管理作業要點》第13點規定，機關於工程規劃、設計時，應要求規劃、設計單位依職業安全衛生法規規劃及提供的資料包含：
+安全衛生注意事項
+安全衛生圖說
+施工安全衛生規範
+安全衛生經費明細表
+機關規定之其他安全衛生規劃、設計資料
+因此，選項中的「職業安全衛生法規」、「規劃安全衛生注意事項、圖說」及「施工安全衛生規範」皆包含在內，僅有「逾期罰款」不屬於安全衛生規劃設計應納入之項目。</t>
+        </is>
+      </c>
+      <c r="I406" s="2" t="inlineStr"/>
     </row>
     <row r="407" ht="108" customHeight="1">
       <c r="A407" s="2" t="n">
@@ -18155,8 +18411,15 @@
       <c r="G407" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H407" s="2" t="n"/>
-      <c r="I407" s="2" t="n"/>
+      <c r="H407" s="2" t="inlineStr">
+        <is>
+          <t>錯誤的敘述為：「風險係指危害事故對人員造成傷害或危害健康之嚴重度」。
+解析與正確定義
+「風險（Risk）」的正確定義：在職業安全衛生管理系統（如 TOSHMS / ISO 45001）中，風險是指「特定危險事件發生的可能性（Probability）」與「其對人員造成傷害或危害健康嚴重度（Severity）」之結合度（或稱組合），不能僅偏頗地定義為僅代表嚴重度。
+其他選項（雇主定義、員工定義、與工作有關的傷病和不健康）在國家級職業安全衛生管理系統指引中皆屬於正確的標準名詞定義。</t>
+        </is>
+      </c>
+      <c r="I407" s="2" t="inlineStr"/>
     </row>
     <row r="408" ht="92.59999999999999" customHeight="1">
       <c r="A408" s="2" t="n">
@@ -18190,8 +18453,16 @@
       <c r="G408" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H408" s="2" t="n"/>
-      <c r="I408" s="2" t="n"/>
+      <c r="H408" s="2" t="inlineStr">
+        <is>
+          <t>安全衛生管理系統內部稽核之執行的正確答案為 以上皆是 (D)。
+依據《臺灣職業安全衛生管理系統指導綱領》與相關法規規定，組織執行內部稽核的目的是為了決定安全衛生管理系統是否達成以下事項：
+符合安全衛生管理所規劃之安排事項（包括規範要求事項）
+已經適當的實施與維持
+有效達到組織之政策與目標</t>
+        </is>
+      </c>
+      <c r="I408" s="2" t="inlineStr"/>
     </row>
     <row r="409" ht="92.59999999999999" customHeight="1">
       <c r="A409" s="2" t="n">
@@ -18225,8 +18496,13 @@
       <c r="G409" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H409" s="2" t="n"/>
-      <c r="I409" s="2" t="n"/>
+      <c r="H409" s="2" t="inlineStr">
+        <is>
+          <t>以上皆是（選項D）。
+依據《臺灣職業安全衛生管理系統指引》及相關職業安全衛生規定，雇主（或屋主/組織）所訂定之書面職業安全衛生政策，應傳達給員工、承攬商及利害相關者。</t>
+        </is>
+      </c>
+      <c r="I409" s="2" t="inlineStr"/>
     </row>
     <row r="410" ht="92.59999999999999" customHeight="1">
       <c r="A410" s="2" t="n">
@@ -18260,8 +18536,20 @@
       <c r="G410" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H410" s="2" t="n"/>
-      <c r="I410" s="2" t="n"/>
+      <c r="H410" s="2" t="inlineStr">
+        <is>
+          <t>組織對現有安全衛生管理系統及相關作法進行先期審查時，「先期審查工作由部門主管進行」是有誤的。
+先期審查的正確觀念
+職責歸屬：先期審查是組織整體（包含雇主、安全衛生專業人員、勞工及相關代表共同參與）的系統性評估，而非僅由個別「部門主管」單獨負責。
+應辦事項：
+審查結果應予以文件化。
+須分析員工健康監控資料。
+須辨識、預測和評估作業環境的危害及風險。
+審查結果應傳達給員工及利害相關者。
+植根法律網</t>
+        </is>
+      </c>
+      <c r="I410" s="2" t="inlineStr"/>
     </row>
     <row r="411" ht="108" customHeight="1">
       <c r="A411" s="2" t="n">
@@ -18295,8 +18583,19 @@
       <c r="G411" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H411" s="2" t="n"/>
-      <c r="I411" s="2" t="n"/>
+      <c r="H411" s="2" t="inlineStr">
+        <is>
+          <t>自動檢查發現之危害狀況必須予以控制，其控制對策優先順序為：a. 本質安全 b. 安全裝置 c. 警告裝置 d. 安全標準與教育訓練
+正確選項為最後一個：
+a. 本質安全
+b. 安全裝置
+c. 警告裝置
+d. 安全標準與教育訓練
+其控制對策優先順序為(A)1.安全裝置2.本質安全3.警告裝置4 ...
+2022年3月15日 — 自動檢查發現之危害狀況必須予以控制,其控制對策優先順序為(A)1.安全裝置2. 包含題目內容、選項、詳解等,幫助學生提升學習效果。</t>
+        </is>
+      </c>
+      <c r="I411" s="2" t="inlineStr"/>
     </row>
     <row r="412" ht="92.59999999999999" customHeight="1">
       <c r="A412" s="2" t="n">
@@ -18330,8 +18629,24 @@
       <c r="G412" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H412" s="2" t="n"/>
-      <c r="I412" s="2" t="n"/>
+      <c r="H412" s="2" t="inlineStr">
+        <is>
+          <t>甲、丙須建置職業安全衛生管理系統。
+依據《職業安全衛生管理辦法》第12條之2規定，第一類事業（如食品製造業）之事業單位勞工人數在二百人以上者，應建置職業安全衛生管理系統。另外同辦法第3條之2規定，事業設有總機構（甲公司）者，其勞工人數之計算包含所屬各地區事業單位（乙、丙工廠）作業勞工之人數，因此總機構甲之總人數為
+3
+3
++
+2
+8
+0
+=
+3
+1
+3
+人，已達200人以上門檻，故總機構甲與勞工人數280人之丙工廠均須建置。因此選項對應為「甲、丙」。</t>
+        </is>
+      </c>
+      <c r="I412" s="2" t="inlineStr"/>
     </row>
     <row r="413" ht="92.59999999999999" customHeight="1">
       <c r="A413" s="2" t="n">
@@ -18365,8 +18680,13 @@
       <c r="G413" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H413" s="2" t="n"/>
-      <c r="I413" s="2" t="n"/>
+      <c r="H413" s="2" t="inlineStr">
+        <is>
+          <t>答案為 (B) 從事業石油裂解之石化工業。
+依據《職業安全衛生法》第 12 條及《職業安全衛生管理辦法》規定，除達一定規模（如第一類事業勞工人數達 200 人以上等）之事業單位應建置職業安全衛生管理系統外，具有顯著風險之特定行業，如從事石油裂解之石化工業，無論規模大小，亦強制要求建置適合之職業安全衛生管理系統。</t>
+        </is>
+      </c>
+      <c r="I413" s="2" t="inlineStr"/>
     </row>
     <row r="414" ht="108" customHeight="1">
       <c r="A414" s="2" t="n">
@@ -18400,8 +18720,15 @@
       <c r="G414" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H414" s="2" t="n"/>
-      <c r="I414" s="2" t="n"/>
+      <c r="H414" s="2" t="inlineStr">
+        <is>
+          <t>錯誤的選項是：「績效考核屬於人資業務，不應納入」。
+原因說明
+根據《職業安全衛生管理規章及職業安全衛生管理計畫指導原則》規定，職業安全衛生管理計畫係指事業單位為執行職業安全衛生事項，所據以訂定之工作目標、執行方法、期程、資源需求及績效考核等具體實施內容。因此，「績效考核」屬於職業安全衛生管理計畫中不可或缺的具體實施內容之一，而非僅屬於人資業務而不納入。
+勞動部職業安全衛生署</t>
+        </is>
+      </c>
+      <c r="I414" s="2" t="inlineStr"/>
     </row>
     <row r="415" ht="92.59999999999999" customHeight="1">
       <c r="A415" s="2" t="n">
@@ -18435,8 +18762,16 @@
       <c r="G415" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H415" s="2" t="n"/>
-      <c r="I415" s="2" t="n"/>
+      <c r="H415" s="2" t="inlineStr">
+        <is>
+          <t>ISO 45001 職業安全衛生管理系統標準是在 2018年3月12日 正式發布並用以取代 OHSAS 18001。正確選項為 2018年3月12日（對應常見考題中的選項 B）。
+相關轉版資訊
+正式公告日：2018年3月12日
+轉換期限：持 OHSAS 18001 證書的組織有 3 年的轉換期（原定至 2021年3月11日，後因疫情延長至 2021年9月30日），期限過後 OHSAS 18001 正式失效。
+環球國際驗證</t>
+        </is>
+      </c>
+      <c r="I415" s="2" t="inlineStr"/>
     </row>
     <row r="416" ht="92.59999999999999" customHeight="1">
       <c r="A416" s="2" t="n">
@@ -18470,8 +18805,17 @@
       <c r="G416" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H416" s="2" t="n"/>
-      <c r="I416" s="2" t="n"/>
+      <c r="H416" s="2" t="inlineStr">
+        <is>
+          <t>為達到零災害目標，在訂定職業安全衛生管理計畫時，可運用訂定－執行－檢討－修正的循環機制。
+職業安全衛生管理循環
+訂定：依據事業單位規模與風險評估結果，規劃安全衛生目標與實施內容。
+執行：落實各項標準作業程序與推動事項。
+檢討：透過查核與稽核機制評估執行成效、發掘潛在問題。
+修正：即時採取矯正與預防措施，滾動式提升安全績效。</t>
+        </is>
+      </c>
+      <c r="I416" s="2" t="inlineStr"/>
     </row>
     <row r="417" ht="92.59999999999999" customHeight="1">
       <c r="A417" s="2" t="n">
@@ -18505,8 +18849,18 @@
       <c r="G417" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H417" s="2" t="n"/>
-      <c r="I417" s="2" t="n"/>
+      <c r="H417" s="2" t="inlineStr">
+        <is>
+          <t>依職業安全衛生管理辦法規定，事業單位勞工人數在 100 人以上時，應另訂定職業安全衛生管理規章。
+正確答案為：100 人。
+重點整理
+100 人以上：除應訂定職業安全衛生管理計畫外，應另訂定管理規章。
+30 人至 100 人以下：應訂定職業安全衛生管理計畫。
+30 人以下：得以安全衛生管理執行紀錄或文件代替管理計畫。
+yicheng.net.tw</t>
+        </is>
+      </c>
+      <c r="I417" s="2" t="inlineStr"/>
     </row>
     <row r="418" ht="92.59999999999999" customHeight="1">
       <c r="A418" s="2" t="n">
@@ -18540,8 +18894,12 @@
       <c r="G418" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H418" s="2" t="n"/>
-      <c r="I418" s="2" t="n"/>
+      <c r="H418" s="2" t="inlineStr">
+        <is>
+          <t>Google AI 摘要未抓取到，請手動補充。</t>
+        </is>
+      </c>
+      <c r="I418" s="2" t="inlineStr"/>
     </row>
     <row r="419" ht="92.59999999999999" customHeight="1">
       <c r="A419" s="2" t="n">
@@ -18575,8 +18933,15 @@
       <c r="G419" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H419" s="2" t="n"/>
-      <c r="I419" s="2" t="n"/>
+      <c r="H419" s="2" t="inlineStr">
+        <is>
+          <t>實施安全衛生檢查以後，必須採取務實確實改善（或務使確實改善）措施，才能達到防止職業災害、保障勞工安全與健康之目的。
+原因說明
+落實改善：檢查的根本目的在於發現工作場所中的潛在危害與缺失，若僅停留在紙上談兵或形式上的報告，而未針對缺失進行實質與確實的改善，則無法發揮防災效果。
+核心目的：唯有切實執行改善行動、消除危害根源，才能真正保護工作者的安全與健康。</t>
+        </is>
+      </c>
+      <c r="I419" s="2" t="inlineStr"/>
     </row>
     <row r="420" ht="92.59999999999999" customHeight="1">
       <c r="A420" s="2" t="n">
@@ -18610,8 +18975,12 @@
       <c r="G420" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H420" s="2" t="n"/>
-      <c r="I420" s="2" t="n"/>
+      <c r="H420" s="2" t="inlineStr">
+        <is>
+          <t>Google AI 摘要未抓取到，請手動補充。</t>
+        </is>
+      </c>
+      <c r="I420" s="2" t="inlineStr"/>
     </row>
     <row r="421" ht="92.59999999999999" customHeight="1">
       <c r="A421" s="2" t="n">
@@ -18645,8 +19014,15 @@
       <c r="G421" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H421" s="2" t="n"/>
-      <c r="I421" s="2" t="n"/>
+      <c r="H421" s="2" t="inlineStr">
+        <is>
+          <t>答案是 提供勞工危險津貼。
+原因說明
+提供勞工危險津貼 屬於金錢補償或福利措施，並不能實質降低或預防工作場所中的有害危害暴露，因此不是危害預防的行政管理方法。
+其他選項（縮短勞工暴露時間、輪換勞工之工作、教導勞工正確使用防護具）皆是透過調整工作安排或管理規範來減少實質危害的有效行政管理手段。</t>
+        </is>
+      </c>
+      <c r="I421" s="2" t="inlineStr"/>
     </row>
     <row r="422" ht="108" customHeight="1">
       <c r="A422" s="2" t="n">
@@ -18680,8 +19056,16 @@
       <c r="G422" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H422" s="2" t="n"/>
-      <c r="I422" s="2" t="n"/>
+      <c r="H422" s="2" t="inlineStr">
+        <is>
+          <t>答案是：修訂（延長）下年度有機溶劑依法應實施作業環境測定的頻率。
+為什麼選這個？
+法規是固定的：像有機溶劑這類的有害作業環境測定（監測）頻率，法規（如《職業安全衛生設施規則》或相關作業環境監測辦法）都有明確規定，不能由企業自己隨便在「檢討上年度計畫」時短暫修訂或任意延長。
+檢討計畫的真正目的：主要是為了評估過去一年的成效、決定哪些既有工作要持續、評估是否要新增項目，以及看看過去做得有沒有達到效果。
+如果還有其他職安法規或是考古題需要解析，隨時告訴我！</t>
+        </is>
+      </c>
+      <c r="I422" s="2" t="inlineStr"/>
     </row>
     <row r="423" ht="92.59999999999999" customHeight="1">
       <c r="A423" s="2" t="n">

--- a/salf/丙種職業安全衛生業務主管題庫.xlsx
+++ b/salf/丙種職業安全衛生業務主管題庫.xlsx
@@ -19099,8 +19099,16 @@
       <c r="G423" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H423" s="2" t="n"/>
-      <c r="I423" s="2" t="n"/>
+      <c r="H423" s="2" t="inlineStr">
+        <is>
+          <t>企業內部安全衛生管理工作的最高指導原則是指安全衛生政策。
+Shihlin Electric 說明
+安全衛生政策（Safety and Health Policy）：由企業最高管理階層所簽署與頒布的正式承諾與方向，確立了組織對工安與健康的整體意向，是所有安全衛生管理制度與目標的最高指導原則。
+其他選項如計畫、目標、管理作為，則是在政策架構下所展開的具體實施步驟或階段性成果。
+財團法人職業災害預防及重建中心</t>
+        </is>
+      </c>
+      <c r="I423" s="2" t="inlineStr"/>
     </row>
     <row r="424" ht="92.59999999999999" customHeight="1">
       <c r="A424" s="2" t="n">
@@ -19134,8 +19142,12 @@
       <c r="G424" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H424" s="2" t="n"/>
-      <c r="I424" s="2" t="n"/>
+      <c r="H424" s="2" t="inlineStr">
+        <is>
+          <t>Google AI 摘要未抓取到，請手動補充。</t>
+        </is>
+      </c>
+      <c r="I424" s="2" t="inlineStr"/>
     </row>
     <row r="425" ht="92.59999999999999" customHeight="1">
       <c r="A425" s="2" t="n">
@@ -19169,8 +19181,12 @@
       <c r="G425" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H425" s="2" t="n"/>
-      <c r="I425" s="2" t="n"/>
+      <c r="H425" s="2" t="inlineStr">
+        <is>
+          <t>Google AI 摘要未抓取到，請手動補充。</t>
+        </is>
+      </c>
+      <c r="I425" s="2" t="inlineStr"/>
     </row>
     <row r="426" ht="92.59999999999999" customHeight="1">
       <c r="A426" s="2" t="n">
@@ -19204,8 +19220,18 @@
       <c r="G426" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H426" s="2" t="n"/>
-      <c r="I426" s="2" t="n"/>
+      <c r="H426" s="2" t="inlineStr">
+        <is>
+          <t>下列有關實施風險評估之步驟，為非的是 (C) 績效審查。
+解析與步驟說明
+辨識危害及後果：屬於風險評估的基礎核心步驟，用以找出潛在危害。
+評估危害之風險：分析危害發生的可能性與嚴重度，屬於評估步驟。
+決定控制設施：針對辨識與評估後的結果，規劃並決定應採取的降低風險控制措施。
+績效審查：屬於事後的監督、量測與管理審查機制，不屬於實施風險評估本身的分析步驟。
+中小企業安全衛生資訊網</t>
+        </is>
+      </c>
+      <c r="I426" s="2" t="inlineStr"/>
     </row>
     <row r="427" ht="92.59999999999999" customHeight="1">
       <c r="A427" s="2" t="n">
@@ -19239,8 +19265,17 @@
       <c r="G427" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H427" s="2" t="n"/>
-      <c r="I427" s="2" t="n"/>
+      <c r="H427" s="2" t="inlineStr">
+        <is>
+          <t>風險控制的完整程序包含危害辨識、評估風險、採取適當控制措施以及定期或不定時審查控制程序。因此，這題的正確答案是以上皆是。
+一個完整的風險管理流程通常包括以下四個核心步驟：
+危害辨識：找出工作環境或流程中所有潛在的危險源。
+風險評估：分析這些危害發生的機率以及可能造成的嚴重程度。
+控制措施：依據風險高低，採用消除、替代、工程控制、行政管理或個人防護具等方法來降低風險。
+審查與更新：隨時因應環境改變或法規更新，進行定期或不定時審查，確保控制措施持續有效。</t>
+        </is>
+      </c>
+      <c r="I427" s="2" t="inlineStr"/>
     </row>
     <row r="428" ht="108" customHeight="1">
       <c r="A428" s="2" t="n">
@@ -19274,8 +19309,16 @@
       <c r="G428" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H428" s="2" t="n"/>
-      <c r="I428" s="2" t="n"/>
+      <c r="H428" s="2" t="inlineStr">
+        <is>
+          <t>正確的敘述為：事業單位應依職業安全衛生法規要求，選擇適合方法執行危害辨識。
+錯誤選項原因解析
+無須參考作業環境監測之結果：錯誤。執行危害辨識時，必須參考作業環境測定及監測結果，以全面掌握真實危害。
+應指定勞工單獨限時完成：錯誤。危害辨識通常需要團隊合作、實地評估與充分討論，而非由單一勞工倉促、單獨限時完成。
+以往事故已經發生過者無須再辨識：錯誤。以往發生過的事故或潛在事件更需要納入辨識與檢討，並持續採取對應的預防控制措施。</t>
+        </is>
+      </c>
+      <c r="I428" s="2" t="inlineStr"/>
     </row>
     <row r="429" ht="92.59999999999999" customHeight="1">
       <c r="A429" s="2" t="n">
@@ -19309,8 +19352,15 @@
       <c r="G429" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H429" s="2" t="n"/>
-      <c r="I429" s="2" t="n"/>
+      <c r="H429" s="2" t="inlineStr">
+        <is>
+          <t>工商普查無法幫助我們實施危害辨識。
+原因說明
+工商普查：屬於政府統計調查企業之基本經濟活動、營業額、從業員工人數等總體經濟數據，與工作場所的物理、化學或人為危害無關。
+員工討論及意外事故調查、工作安全分析、安全資料表 (SDS)：皆是用於辨識工作環境中潛在危險、化學品特性及作業安全風險的有效工具。</t>
+        </is>
+      </c>
+      <c r="I429" s="2" t="inlineStr"/>
     </row>
     <row r="430" ht="92.59999999999999" customHeight="1">
       <c r="A430" s="2" t="n">
@@ -19344,8 +19394,17 @@
       <c r="G430" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H430" s="2" t="n"/>
-      <c r="I430" s="2" t="n"/>
+      <c r="H430" s="2" t="inlineStr">
+        <is>
+          <t>危害辨識係指 (A) 辨識工作場所的潛在危害。
+相關概念解析
+危害辨識：找出工作場所中所有可能造成人員傷害、疾病或環境損害的潛在因素（危害源）。
+選項 (B)（考量危害後果的嚴重度與發生的可能性）屬於 風險評估 的範疇。
+選項 (C)（評估其風險等級）屬於 風險決定與評量。
+選項 (D)（採取降低風險的控制設施）屬於 風險控制措施。</t>
+        </is>
+      </c>
+      <c r="I430" s="2" t="inlineStr"/>
     </row>
     <row r="431" ht="92.59999999999999" customHeight="1">
       <c r="A431" s="2" t="n">
@@ -19379,8 +19438,16 @@
       <c r="G431" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H431" s="2" t="n"/>
-      <c r="I431" s="2" t="n"/>
+      <c r="H431" s="2" t="inlineStr">
+        <is>
+          <t>危害辨識非降低風險的控制措施。
+說明
+危害辨識：是用來找出工作場所中潛在危害的步驟，屬於風險評估與管理的前置分析階段，在採取控制風險之前進行。
+降低風險的控制措施：包含教育訓練、個人防護具以及工作許可等管理或防護手段，目的是在辨識出危害後加以消除或減少其風險。
+職安一點通服務網</t>
+        </is>
+      </c>
+      <c r="I431" s="2" t="inlineStr"/>
     </row>
     <row r="432" ht="92.59999999999999" customHeight="1">
       <c r="A432" s="2" t="n">
@@ -19414,8 +19481,90 @@
       <c r="G432" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H432" s="2" t="n"/>
-      <c r="I432" s="2" t="n"/>
+      <c r="H432" s="2" t="inlineStr">
+        <is>
+          <t>這題的正確答案是 以上皆是。
+說明
+在職業安全衛生與風險管控中，消除或降低作業危害的方法包含多個層面：
+儘量不讓勞工從事高處危險性工作：屬於從源頭或作業規劃上消除/避免危害（Elimination/Avoidance）。
+設置適當的防護設施及設備：屬於工程控制（Engineering controls），利用物理屏障或設備隔離風險。
+提供適當防護裝備：屬於個人防護具（Personal Protective Equipment, PPE），作為最後一道防線來降低勞工受傷的風險。
+因此，這三項皆是有效的方法。
+如果還有其他職業安全衛生或法規考試相關的題目需要解答，歡迎隨時提出！
+AI 回覆可能有誤。如需法律建議，請諮詢專業人士。 瞭解詳情
+網頁搜尋結果
+678. 下述何者是消除或降低作業時所可能面對的危險源的 ...
+› item-678.+下述何者是消除或降低作...
+2024年10月7日 — 678. 下述何者是消除或降低作業時所可能面對的危險源的有效方法? (A)儘量不讓勞工從事高處危險性工作 (B)設置適當的防護設施及設備 (C)提供適當防護裝備 ( ...
+危險性工作場所審查及檢查辦法 - 全國法規資料庫
+全國法規資料庫
+› LawClass › LawAll
+沒有這個頁面的資訊。
+瞭解原因
+222002-1安衛乙學1093(春)單詞卡
+Quizlet
+› 222002-1安衛乙學1093春-flash-c...
+僱用勞工從事作業時，於各項職業安全衛生管理措施中，應報請勞動檢查機構備查者為何？ ①實施勞工體格檢查結果②新僱勞工之安全衛生教育訓練③職業安全衛生管理計畫④ ...
+共用共同科目一職業安全衛生@測驗結果
+育才國際文化事業有限公司
+› exam › result10254
+2025年8月16日 — 有立即發生墜落危險情事， 在於高差二公尺以上之工作場所邊緣及開口部分，設置符合規定之護欄、護蓋、安全網或配掛安全帶之防墜設施。
+營造安全衛生設施標準(民國115 年06 月30 日修正)
+› FLAW › FLAWDAT0202
+雇主使勞工於屋頂從事作業時，應指派專人督導，並依下列規定辦理： 一、因屋頂斜度、屋面性質或天候等因素，致勞工有墜落、滾落之虞者， 應採取適當安全措施。 二、於斜度 ...
+缺少字詞： 何者 ‎是
+職業安全衛生相關法規1. (4) 依勞動檢查法之規定
+花職訓
+› uploads › 2023/10 › 2...
+PDF
+(2). 工作場所有立即發生危險之虞時，何人應即令停止作業，並使勞工退避. 至安全場所？ ①業主或雇主②雇主或工作場所負責人③工作場所負責. 人或部門主管④部門主管或作業 ...
+49 頁
+職場夜間工作安全衛生指引
+勞動部職業安全衛生署
+› media › 職場夜間工...
+PDF
+2. 調查、蒐集或分析可能的暴力攻擊情境，檢討現有防護設施之. 有效性，運用現有科技能力、可用資源及結合多元策略或方. 法，盡可能降低或消除暴力事件之風險。 3. 安全 ...
+職業安全衛生1. (2) 對於核計勞工所得有無低於
+社團法人台灣美容產業技能協會
+› item › download
+PDF
+類於下列何種職業危害？ ①物理性②化學性③社會心理性④生物性。 98. (1) 有關高風險或高負荷、夜間工作之安排或防護措施，下列何者不恰當？ ①. 若受威脅或加害時，在 ...
+法規新訊-修正「職業安全衛生設施規則」(2026-06-30)
+法源法律網
+› news › NewsContent_print
+2026年6月30日 — 第57 條雇主對於機械、設備及其相關配件之掃除、上油、檢查、修理或調整有導致危害勞工之虞者，應採取下列措施： 一、停止相關機械運轉及送料。 二、上鎖 ...
+缺少字詞： 何者 ‎是 ‎降低 ‎面 ‎儘量 ‎讓
+其他人也搜尋了以下項目
+危險性工作場所審查及檢查辦法施行細則
+危險性工作場所施行細則
+危險性工作場所施行細則附表一
+甲乙丙丁類危險性工作場所
+危險性工作場所分類
+危險性工作場所定義
+乙類危險性工作場所
+甲類危險性工作場所附表二
+頁面導覽
+1
+2
+3
+4
+5
+6
+7
+8
+9
+下一頁
+頁尾連結
+台灣
+708 臺南市安平區 - 根據你的 IP 位址
+- 更新位置
+說明
+提供意見
+隱私權
+服務條款</t>
+        </is>
+      </c>
+      <c r="I432" s="2" t="inlineStr"/>
     </row>
     <row r="433" ht="92.59999999999999" customHeight="1">
       <c r="A433" s="2" t="n">
@@ -19449,8 +19598,16 @@
       <c r="G433" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H433" s="2" t="n"/>
-      <c r="I433" s="2" t="n"/>
+      <c r="H433" s="2" t="inlineStr">
+        <is>
+          <t>安全作業標準的功能包含以上皆是。
+安全作業標準（SOP）在職場安全管理中扮演非常重要的角色，其核心功能涵蓋了以下幾個面向：
+確定工作場所所需的設備或器具：在制定標準時，會明確列出該項作業必須使用的防護具、工具及安全設備，確保人員在正確的配備下工作。
+作為安全教導的參考：它是新進人員訓練或在職教育訓練的標準教材，能讓員工明確了解正確且安全的作業步驟。
+作為安全觀察的參考：主管在進行現場安全巡檢或「安全觀察」時，是以安全作業標準為依據，用來評估現場人員的操作是否符合規範、有無不安全行為，進而予以糾正或改善。 內容</t>
+        </is>
+      </c>
+      <c r="I433" s="2" t="inlineStr"/>
     </row>
     <row r="434" ht="92.59999999999999" customHeight="1">
       <c r="A434" s="2" t="n">
@@ -19485,8 +19642,18 @@
       <c r="G434" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H434" s="2" t="n"/>
-      <c r="I434" s="2" t="n"/>
+      <c r="H434" s="2" t="inlineStr">
+        <is>
+          <t>製作安全作業標準時的首要步驟是確認實際工作步驟。
+製作安全作業標準的步驟重點
+確認實際工作步驟：首先要將工作分解為基本的動作或步驟。
+尋找不安全因素：接著針對各個步驟檢視潛在的危險與風險。
+評估可能造成之傷害：分析可能發生的意外與嚴重程度。
+訂定安全對策與方法：提出預防災害及事故處理的方法。
+NTNU</t>
+        </is>
+      </c>
+      <c r="I434" s="2" t="inlineStr"/>
     </row>
     <row r="435" ht="108" customHeight="1">
       <c r="A435" s="2" t="n">
@@ -19520,8 +19687,19 @@
       <c r="G435" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H435" s="2" t="n"/>
-      <c r="I435" s="2" t="n"/>
+      <c r="H435" s="2" t="inlineStr">
+        <is>
+          <t>答案為：健康管理計劃可以此資料為基礎預作規劃。
+📝 解析
+「安全作業標準」（Job Safety Standards / Standard Operating Procedures）的核心目的在於規範作業流程、消除環境與行為危害、提升工作效率與職場安全。
+各選項分析如下：
+❌ 健康管理計劃可以此資料為基礎預作規劃：此敘述錯誤（本題選此）。健康管理計畫（如健康檢查、四大指引、選工復工等）主要是依據「勞工作業環境監測結果」或「健康檢查結果」來進行預作規劃，而非依據安全作業標準。
+⭕ 藉以改善勞工不安全行為及施工設備、現場作業環境：安全作業標準確立後，能作為檢視並修正現場不安全行為與環境的依據。
+⭕ 可明確規定工作人員職掌，以強化管理能力：標準中會明確定義各崗位人員的操作步驟與職責。
+⭕ 可使工作更具效率，人員、環境、設備更具安全性：這是實施安全作業標準最主要的終極目標。</t>
+        </is>
+      </c>
+      <c r="I435" s="2" t="inlineStr"/>
     </row>
     <row r="436" ht="92.59999999999999" customHeight="1">
       <c r="A436" s="2" t="n">
@@ -19555,8 +19733,17 @@
       <c r="G436" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H436" s="2" t="n"/>
-      <c r="I436" s="2" t="n"/>
+      <c r="H436" s="2" t="inlineStr">
+        <is>
+          <t>以上均正確。
+安全作業標準（Safe Operation Standard）的主要功能與功用包含：
+防範工作場所職業災害發生：明確規定正確的作業步驟與方法，避免危害產生。
+作為安全教導的參考：提供教育訓練與現場指導時的依據，使工作人員明瞭正確作法。
+增進工作人員的參與感：在制定與檢討過程中透過討論與分析，提高員工對作業安全的認知與參與。
+此外，其功能還包括確定所需設備器具、作為安全觀察及事故調查之參考等。</t>
+        </is>
+      </c>
+      <c r="I436" s="2" t="inlineStr"/>
     </row>
     <row r="437" ht="92.59999999999999" customHeight="1">
       <c r="A437" s="2" t="n">
@@ -19590,8 +19777,17 @@
       <c r="G437" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H437" s="2" t="n"/>
-      <c r="I437" s="2" t="n"/>
+      <c r="H437" s="2" t="inlineStr">
+        <is>
+          <t>安全作業標準係經由「以上皆是」的方式建立的作業方法與步驟。
+相關概念說明
+工作安全分析 (JSA)：藉由分解工作步驟、辨識潛在危害並決定安全的工作方法，來建立安全作業標準的核心工具。
+作業步驟：將一項工作拆解為連續且基礎的操作步驟，是分析與標準化的基礎。
+安全工法：在工程與作業實務中，為確保安全而採行的正確施工或操作方法。
+中華民國工業安全衛生協會</t>
+        </is>
+      </c>
+      <c r="I437" s="2" t="inlineStr"/>
     </row>
     <row r="438" ht="92.59999999999999" customHeight="1">
       <c r="A438" s="2" t="n">
@@ -19625,8 +19821,20 @@
       <c r="G438" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H438" s="2" t="n"/>
-      <c r="I438" s="2" t="n"/>
+      <c r="H438" s="2" t="inlineStr">
+        <is>
+          <t>這個定義指的是工作安全分析（Job Safety Analysis, 簡稱 JSA）。
+為什麼是工作安全分析？
+核心概念：工作安全分析（JSA）是一種系統化的程序，它將一項工作或作業拆解成每一個作業步驟，接著參酌安全衛生法令規定，指明每個步驟的潛在危害，並將安全措施結合至每一作業步驟中。
+事故處理：在分析的過程中，除了預防措施，也會同時規劃當該步驟發生事故或緊急狀況時的具體處理與應變方式。
+其他選項的差異
+項目	核心定義與差異
+🛡️ 安全作業標準 (SOP)	依據工作安全分析（JSA）的結果，所制定出的一套標準化標準作業程序。它是分析後的「產出結果」，而非結合與分析的「過程或行為本身」。
+📜 安全衛生工作守則	雇主依據《職業安全衛生法》會同勞工代表制定的一般性、通則性規範（如：勞工應盡之義務、通用防護具配戴等），屬於全廠或各部門適用的基本規範，不會針對「每一作業步驟」進行細化拆解。
+📋 安全衛生管理計畫	屬於高層級的行政管理文件，內容涵蓋組織權責、安全衛生教育訓練、自動檢查、防災計畫等整體營運管理方針，並非針對單一作業步驟的技術性分析。</t>
+        </is>
+      </c>
+      <c r="I438" s="2" t="inlineStr"/>
     </row>
     <row r="439" ht="92.59999999999999" customHeight="1">
       <c r="A439" s="2" t="n">
@@ -19660,8 +19868,18 @@
       <c r="G439" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H439" s="2" t="n"/>
-      <c r="I439" s="2" t="n"/>
+      <c r="H439" s="2" t="inlineStr">
+        <is>
+          <t>違反安全作業標準規定時非安全作業標準修訂的時機。
+刷題王
+原因說明
+應修訂標準的時機：當發生事故（代表原標準可能有漏洞）、製程改變，或是風險評估發現有不可忍受的風險時，代表既有標準或防護措施已不足夠，必須進行修訂。
+刷題王
+違反規定的處理方式：人員「違反規定」通常是因為未落實執行或遵守現行規定，這屬於人員遵循與現場管理的範疇，應透過加強教育訓練、稽查與懲戒來改善，而非直接修訂安全作業標準。
+刷題王</t>
+        </is>
+      </c>
+      <c r="I439" s="2" t="inlineStr"/>
     </row>
     <row r="440" ht="92.59999999999999" customHeight="1">
       <c r="A440" s="2" t="n">
@@ -19695,8 +19913,18 @@
       <c r="G440" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H440" s="2" t="n"/>
-      <c r="I440" s="2" t="n"/>
+      <c r="H440" s="2" t="inlineStr">
+        <is>
+          <t>安全作業標準之製作程序不包括(C) 實施自動檢查。
+說明
+安全作業標準（如工作安全分析 JSA）的製作程序主要包含：
+確認實際工作步驟
+辨識不安全因素（危害辨識）
+規劃事故之處理 / 研擬對策與控制措施
+而「實施自動檢查」屬於現場設備與作業安全管理的執行項目，並非安全作業標準本身的製作程序。</t>
+        </is>
+      </c>
+      <c r="I440" s="2" t="inlineStr"/>
     </row>
     <row r="441" ht="92.59999999999999" customHeight="1">
       <c r="A441" s="2" t="n">
@@ -19730,8 +19958,17 @@
       <c r="G441" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H441" s="2" t="n"/>
-      <c r="I441" s="2" t="n"/>
+      <c r="H441" s="2" t="inlineStr">
+        <is>
+          <t>事業單位發生職業災害時，以 (B) 安全作業標準 為較好之事故調查參考。
+事故調查參考依據解析
+(B) 安全作業標準（SOP）：記錄正常操作的步驟與安全要求。調查時可藉此比對實際操作，判斷當下行為是否偏離標準、找出潛在原因與不安全動作，是釐清事故主因最重要的依據。
+(A) 緊急應變計畫：主要用於災害發生後的通報、急救與疏散應變，與分析事故發生的根本原因關聯較小。
+(C) 教育訓練紀錄：僅能確認勞工是否受過相關訓練，無法直接反映或還原災害發生當下的實際操作狀況。
+(D) 自動檢查表：屬於設備或環境的日常維護與巡檢紀錄，雖有助於排除設備異常，但不如安全作業標準直接貼近作業過程與人為操作行為。</t>
+        </is>
+      </c>
+      <c r="I441" s="2" t="inlineStr"/>
     </row>
     <row r="442" ht="92.59999999999999" customHeight="1">
       <c r="A442" s="2" t="n">
@@ -19765,8 +20002,16 @@
       <c r="G442" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H442" s="2" t="n"/>
-      <c r="I442" s="2" t="n"/>
+      <c r="H442" s="2" t="inlineStr">
+        <is>
+          <t>工作安全分析（Job Safety Analysis, JSA）的分析者通常為(D) 領班（或其他現場主管人員）。
+相關職責分工說明
+分析者：領班或現場主管（最熟悉實際作業流程與第一線操作）。
+審核者：安全管理人員（職業安全衛生人員）。
+批准者：最高主管或事業經營負責人、廠長等。</t>
+        </is>
+      </c>
+      <c r="I442" s="2" t="inlineStr"/>
     </row>
     <row r="443" ht="92.59999999999999" customHeight="1">
       <c r="A443" s="2" t="n">
@@ -19800,8 +20045,16 @@
       <c r="G443" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H443" s="2" t="n"/>
-      <c r="I443" s="2" t="n"/>
+      <c r="H443" s="2" t="inlineStr">
+        <is>
+          <t>工作安全分析的初核者為職業安全衛生人員。
+工作安全分析的權責分工
+分析者：領班或其他直接主管人員（負責實際執行步驟拆解與危害辨識）。
+初核／審核者：職業安全衛生人員（負責審查分析內容是否合乎安全規範）。
+批准者：事業經營負責人或廠長等最高主管（負責最終批准公告實施）。</t>
+        </is>
+      </c>
+      <c r="I443" s="2" t="inlineStr"/>
     </row>
     <row r="444" ht="92.59999999999999" customHeight="1">
       <c r="A444" s="2" t="n">
@@ -19835,8 +20088,17 @@
       <c r="G444" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H444" s="2" t="n"/>
-      <c r="I444" s="2" t="n"/>
+      <c r="H444" s="2" t="inlineStr">
+        <is>
+          <t>工作安全分析（Job Safety Analysis, JSA）的批准者最適合由廠長（或事業單位的最高主管／高級主管）擔任。
+應用化學及材料科學系 原因說明
+廠長：具備廠區內製程與資源調度之權責，適合作為工作安全分析結果的最終核准與負責人。
+領班：通常為工作安全分析的「分析者」或實際執行者。
+職業安全衛生人員：通常負責提供專業諮詢、協助或審查，而非最終批准者。
+事業經營負責人：層級過高，一般廠務及作業安全分析多授權由廠長批准。</t>
+        </is>
+      </c>
+      <c r="I444" s="2" t="inlineStr"/>
     </row>
     <row r="445" ht="92.59999999999999" customHeight="1">
       <c r="A445" s="2" t="n">
@@ -19870,8 +20132,14 @@
       <c r="G445" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H445" s="2" t="n"/>
-      <c r="I445" s="2" t="n"/>
+      <c r="H445" s="2" t="inlineStr">
+        <is>
+          <t>答案是 (D) 工作安全分析。
+題目解析
+工作安全分析 (Job Safety Analysis, JSA)：通常是由相關主管或作業主管，結合其專業知識、現場常識，並透過集思廣益與腦力激盪的方式，針對特定工作步驟拆解、辨識潛在危害，進而制定安全的工作方法與程序。</t>
+        </is>
+      </c>
+      <c r="I445" s="2" t="inlineStr"/>
     </row>
     <row r="446" ht="92.59999999999999" customHeight="1">
       <c r="A446" s="2" t="n">
@@ -19905,8 +20173,12 @@
       <c r="G446" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H446" s="2" t="n"/>
-      <c r="I446" s="2" t="n"/>
+      <c r="H446" s="2" t="inlineStr">
+        <is>
+          <t>Google AI 摘要未抓取到，請手動補充。</t>
+        </is>
+      </c>
+      <c r="I446" s="2" t="inlineStr"/>
     </row>
     <row r="447" ht="92.59999999999999" customHeight="1">
       <c r="A447" s="2" t="n">
@@ -19940,8 +20212,15 @@
       <c r="G447" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H447" s="2" t="n"/>
-      <c r="I447" s="2" t="n"/>
+      <c r="H447" s="2" t="inlineStr">
+        <is>
+          <t>正確答案是：發現及杜絕工作危害。
+解析
+在工作安全分析（Job Safety Analysis, JSA）的過程中，透過詳細觀察與記錄作業中的各項危害，並針對這些危害採取適當的工作方法與程序來防止其發生，其最直接且核心的目的就是為了發現及杜絕工作危害，進而降低職災風險。
+中華民國工業安全衛生協會</t>
+        </is>
+      </c>
+      <c r="I447" s="2" t="inlineStr"/>
     </row>
     <row r="448" ht="92.59999999999999" customHeight="1">
       <c r="A448" s="2" t="n">
@@ -19975,8 +20254,18 @@
       <c r="G448" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H448" s="2" t="n"/>
-      <c r="I448" s="2" t="n"/>
+      <c r="H448" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+正確答案為 (B) 作為安全教導的參考。
+工作安全分析（Job Safety Analysis, JSA）的功能
+安全教導與訓練：分析結果可作為新進員工訓練、教育講授及現場作業指導的標準教材。
+危害辨識：找出作業流程中的潛在危險與意外風險。
+訂定安全作業標準：建立正確、安全的工作步驟與防範對策。
+iPEDIA 百科</t>
+        </is>
+      </c>
+      <c r="I448" s="2" t="inlineStr"/>
     </row>
     <row r="449" ht="92.59999999999999" customHeight="1">
       <c r="A449" s="2" t="n">
@@ -20010,8 +20299,18 @@
       <c r="G449" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H449" s="2" t="n"/>
-      <c r="I449" s="2" t="n"/>
+      <c r="H449" s="2" t="inlineStr">
+        <is>
+          <t>答案是 「懲罰犯錯的員工」。
+工作安全分析（Job Safety Analysis, JSA）的目的
+發現並杜絕工作危害：找出作業流程中的潛在危險與風險。
+確立工作安全所需工具與設備：評估並準備適當的防護具與機械設施。
+作為員工在職訓練的參考：將正確的安全步驟納入標準作業程序（SOP）與教育訓練。
+中華民國工業安全衛生協會 工作安全分析的重點在於預防事故與改善工作環境，而非事後歸責或懲處員工。
+中華民國工業安全衛生協會</t>
+        </is>
+      </c>
+      <c r="I449" s="2" t="inlineStr"/>
     </row>
     <row r="450" ht="92.59999999999999" customHeight="1">
       <c r="A450" s="2" t="n">
@@ -20045,8 +20344,15 @@
       <c r="G450" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H450" s="2" t="n"/>
-      <c r="I450" s="2" t="n"/>
+      <c r="H450" s="2" t="inlineStr">
+        <is>
+          <t>在工作安全分析（Job Safety Analysis, JSA）中，應考慮的不安全主體為 (D) 人。
+重點解析
+人：工作安全分析主要強調辨識與消除作業過程中人的不安全行為與操作疏失。
+核心目的：透過分解工作步驟，找出潛在危害並建立正確的安全標準程序，防範工安事故。</t>
+        </is>
+      </c>
+      <c r="I450" s="2" t="inlineStr"/>
     </row>
     <row r="451" ht="92.59999999999999" customHeight="1">
       <c r="A451" s="2" t="n">
@@ -20080,8 +20386,15 @@
       <c r="G451" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H451" s="2" t="n"/>
-      <c r="I451" s="2" t="n"/>
+      <c r="H451" s="2" t="inlineStr">
+        <is>
+          <t>產品品質不列入工作安全分析（JSA）的考慮項目。
+工作安全分析（JSA）說明
+主要目的：辨識工作步驟中的潛在危害，並採取預防措施來保護人（勞工安全）、改善環境與控管材料或機械設備。
+不列入考量：產品品質屬於生產管理與品質保證（QA/QC）的範疇，不屬於工作安全與危害辨識的直接考慮項目。</t>
+        </is>
+      </c>
+      <c r="I451" s="2" t="inlineStr"/>
     </row>
     <row r="452" ht="92.59999999999999" customHeight="1">
       <c r="A452" s="2" t="n">
@@ -20115,8 +20428,18 @@
       <c r="G452" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H452" s="2" t="n"/>
-      <c r="I452" s="2" t="n"/>
+      <c r="H452" s="2" t="inlineStr">
+        <is>
+          <t>成本分析通常非為工作安全分析表（Job Safety Analysis, JSA）內應有之項目。
+工作安全分析表的核心項目
+工作安全分析主要聚焦於作業過程中的安全與危害控制，標準欄位或核心項目通常包含：
+工作步驟：將一項工作拆解為連續的具體動作或步驟。
+潛在危險：辨識每個步驟中可能導致人員受傷或設備損壞的危害。
+安全工作方法：針對潛在危險提出預防與對應的安全作業對策。
+而「成本分析」屬於財務或工程預算評估的範疇，與作業安全危害辨識無直接關係。</t>
+        </is>
+      </c>
+      <c r="I452" s="2" t="inlineStr"/>
     </row>
     <row r="453" ht="92.59999999999999" customHeight="1">
       <c r="A453" s="2" t="n">
@@ -20150,8 +20473,12 @@
       <c r="G453" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H453" s="2" t="n"/>
-      <c r="I453" s="2" t="n"/>
+      <c r="H453" s="2" t="inlineStr">
+        <is>
+          <t>Google AI 摘要未抓取到，請手動補充。</t>
+        </is>
+      </c>
+      <c r="I453" s="2" t="inlineStr"/>
     </row>
     <row r="454" ht="92.59999999999999" customHeight="1">
       <c r="A454" s="2" t="n">
@@ -20185,8 +20512,20 @@
       <c r="G454" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H454" s="2" t="n"/>
-      <c r="I454" s="2" t="n"/>
+      <c r="H454" s="2" t="inlineStr">
+        <is>
+          <t>答案：(D) 天災
+說明
+工作安全分析（JSA）聚焦於人為與作業環境中可預防、可控制的危害因素。
+中華民國工業安全衛生協會
+潛在危險包含：
+不安全行為（人員操作失誤、未戴防護具等）
+不安全設備（機械故障、無防護罩等）
+不安全環境（照明不良、地面濕滑、噪音過高等）
+天災屬於不可抗力之外力事件，非屬工作安全分析中針對特定作業步驟檢討與控制的主要潛在危險類別。</t>
+        </is>
+      </c>
+      <c r="I454" s="2" t="inlineStr"/>
     </row>
     <row r="455" ht="92.59999999999999" customHeight="1">
       <c r="A455" s="2" t="n">
@@ -20220,8 +20559,16 @@
       <c r="G455" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H455" s="2" t="n"/>
-      <c r="I455" s="2" t="n"/>
+      <c r="H455" s="2" t="inlineStr">
+        <is>
+          <t>這題的答案是 安全作業標準。
+詳細說明
+安全作業標準：是指透過工作安全分析（Job Safety Analysis, JSA）的結果，將安全的工作步驟、方法與規定明確訂定出來，作為現場作業遵循的標準，用來消除不安全的行為、設備與環境。
+工作安全分析：是一種評估與辨識工作流程中潛在危害的手法，它是「建立」安全作業標準的過程或手段，而不是最後產出的「標準」本身。
+台灣永續網</t>
+        </is>
+      </c>
+      <c r="I455" s="2" t="inlineStr"/>
     </row>
     <row r="456" ht="92.59999999999999" customHeight="1">
       <c r="A456" s="2" t="n">
@@ -20255,8 +20602,20 @@
       <c r="G456" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H456" s="2" t="n"/>
-      <c r="I456" s="2" t="n"/>
+      <c r="H456" s="2" t="inlineStr">
+        <is>
+          <t>答案是 工作安全分析。
+說明
+工作安全分析（Job Safety Analysis, JSA）是將「工作分析」與「預知危險」相結合的一種簡單定性風險管理方法。
+它的核心步驟包含：
+決定要分析的工作。
+將工作分解成各個基本步驟。
+辨識每一個步驟中的潛在危害。
+決定適當的安全與預防方法。
+中華民國工業安全衛生協會</t>
+        </is>
+      </c>
+      <c r="I456" s="2" t="inlineStr"/>
     </row>
     <row r="457" ht="92.59999999999999" customHeight="1">
       <c r="A457" s="2" t="n">
@@ -20290,8 +20649,16 @@
       <c r="G457" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H457" s="2" t="n"/>
-      <c r="I457" s="2" t="n"/>
+      <c r="H457" s="2" t="inlineStr">
+        <is>
+          <t>工作場所風險安全評估的第一步驟是危害辨識。
+風險評估的主要步驟
+危害辨識：找出工作場所中所有潛在的作業、工程、環境危害與災害情境。
+風險評估：評估危害發生的可能性及嚴重程度，決定風險等級。
+風險控制決策：研擬並決定降低風險的控制措施與管理方案。</t>
+        </is>
+      </c>
+      <c r="I457" s="2" t="inlineStr"/>
     </row>
     <row r="458" ht="92.59999999999999" customHeight="1">
       <c r="A458" s="2" t="n">
@@ -20325,8 +20692,34 @@
       <c r="G458" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H458" s="2" t="n"/>
-      <c r="I458" s="2" t="n"/>
+      <c r="H458" s="2" t="inlineStr">
+        <is>
+          <t>d-e-a-b-c（即 d. 工作步驟
+→
+→
+e. 不安全因素
+→
+→
+a. 安全措施
+→
+→
+b. 工作方法
+→
+→
+c. 事故處理）。
+職安一點通服務網 說明與排序邏輯
+d. 工作步驟：先拆解作業流程的先後順序。
+e. 不安全因素：針對每個步驟找出潛在危害或不安全狀況。
+a. 安全措施：針對不安全因素擬定防範對策與設施。
+b. 工作方法：確立該步驟正確執行的具體操作方法。
+c. 事故處理：預先規畫萬一發生意外時的應變與善後處置。
+需要我提供這五要素在工作安全分析（JSA）或具體作業範例中的實際填寫對照嗎？
+職安一點通服務網
+106-1 學科試題 - 職安一點通服務網
+( 4 ) 設安全作業標準表須包含5 要素：a. 安全措施；b. 工作方法；c. 事故處理；d. 工. 作步驟；e. 不安全因素，製作此表時應按下列何種順序說明探討此5 要素？ ① ...</t>
+        </is>
+      </c>
+      <c r="I458" s="2" t="inlineStr"/>
     </row>
     <row r="459" ht="92.59999999999999" customHeight="1">
       <c r="A459" s="2" t="n">
@@ -20360,8 +20753,18 @@
       <c r="G459" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H459" s="2" t="n"/>
-      <c r="I459" s="2" t="n"/>
+      <c r="H459" s="2" t="inlineStr">
+        <is>
+          <t>將工作方法或程序分解為各細項或步驟，以了解可能具有之危害，並訂出安全作業的需求，係指工作安全分析（Job Safety Analysis, JSA）。
+工作安全分析的4個主要步驟
+選擇工作：挑選具潛在危險或曾發生事故的工作進行分析。
+步驟分解：將工作程序拆解成依序進行的各個細項或步驟。
+辨識危害：找出每一個步驟中可能發生的潛在危害或意外事故。
+訂定對策：提出安全作業方法與需求，預防災害發生。
+iPEDIA 百科</t>
+        </is>
+      </c>
+      <c r="I459" s="2" t="inlineStr"/>
     </row>
     <row r="460" ht="92.59999999999999" customHeight="1">
       <c r="A460" s="2" t="n">
@@ -20395,8 +20798,20 @@
       <c r="G460" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H460" s="2" t="n"/>
-      <c r="I460" s="2" t="n"/>
+      <c r="H460" s="2" t="inlineStr">
+        <is>
+          <t>下列何者非工作分析（工作安全分析）要件？
+答案是：確定工作費用。
+📌 為什麼？
+工作安全分析（Job Safety Analysis, JSA）的核心目的是為了預防職業災害與確保人員安全。它的四大核心步驟與要件包括：
+確定工作內容：明確知道要做什麼職務或工程項目。
+確定工作人員：了解執行該工作的人員資格、編組與職責。
+確定工作方法：將工作流程拆解為具體的步驟。
+辨識危害與擬定對策：分析每個步驟可能帶來的風險，並訂定對應的安全防護措施。
+工作費用屬於工程財務與成本管理的範疇，與施工現場的「安全作業標準」擬定並無直接關係。</t>
+        </is>
+      </c>
+      <c r="I460" s="2" t="inlineStr"/>
     </row>
     <row r="461" ht="92.59999999999999" customHeight="1">
       <c r="A461" s="2" t="n">
@@ -20430,8 +20845,16 @@
       <c r="G461" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H461" s="2" t="n"/>
-      <c r="I461" s="2" t="n"/>
+      <c r="H461" s="2" t="inlineStr">
+        <is>
+          <t>這題 market-leading 的正確答案是：以上皆是。
+在進行工作安全分析（JSA）或作業拆解時，通常會包含以下幾個核心核心要素：
+分項作業（作業名稱）：明確界定要分析的特定工作項目。
+作業程序（工作步驟）：將該作業依先後順序，拆解成數個具體的主要步驟。
+作業方法（工作方法）：說明每一個步驟應該如何執行、使用什麼工具，進而找出潛在危害並設定安全對策。</t>
+        </is>
+      </c>
+      <c r="I461" s="2" t="inlineStr"/>
     </row>
     <row r="462" ht="92.59999999999999" customHeight="1">
       <c r="A462" s="2" t="n">
@@ -20465,8 +20888,18 @@
       <c r="G462" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H462" s="2" t="n"/>
-      <c r="I462" s="2" t="n"/>
+      <c r="H462" s="2" t="inlineStr">
+        <is>
+          <t>預知危險四階段的第四階段（3R. 樹立對策及？）答案是 (D) 4R 設定目標。
+預知危險四階段（4R）內容
+1R. 掌握現狀：觀察並了解工作場所或作業程序中的實際狀況。
+2R. 追究真相：找出潛在的危險與危害發生的根本原因。
+3R. 樹立對策：研擬改善作業程序、設備或防護具的具體解決方法。
+4R. 設定目標：確立安全的工作方法與實施目標。
+臺中市政府全球資訊網</t>
+        </is>
+      </c>
+      <c r="I462" s="2" t="inlineStr"/>
     </row>
     <row r="463" ht="92.59999999999999" customHeight="1">
       <c r="A463" s="2" t="n">
@@ -20500,8 +20933,19 @@
       <c r="G463" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H463" s="2" t="n"/>
-      <c r="I463" s="2" t="n"/>
+      <c r="H463" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+答案是 低風險性工作。
+工作安全分析優先選擇項目說明
+工作安全分析（Job Safety Analysis, JSA）應用於找出潛在危害並採取對策，其優先順序為高風險或高潛在危機的工作：
+傷害頻率高的工作：容易發生意外、頻繁造成人員受傷的工作需優先改善。
+傷害嚴重率高的工作：可能導致失能、重傷或死亡的高嚴重性工作。
+新工作 / 變更後的工作：因缺乏操作經驗或尚未建立完整安全防護，具備潛在的高風險。
+低風險性工作：發生災害機率低且危害程度輕微，不是工作安全分析需要優先考慮的對象。</t>
+        </is>
+      </c>
+      <c r="I463" s="2" t="inlineStr"/>
     </row>
     <row r="464" ht="92.59999999999999" customHeight="1">
       <c r="A464" s="2" t="n">
@@ -20535,8 +20979,16 @@
       <c r="G464" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H464" s="2" t="n"/>
-      <c r="I464" s="2" t="n"/>
+      <c r="H464" s="2" t="inlineStr">
+        <is>
+          <t>下列何者非危害的根源？答案是 (A) 訓練。
+工作安全分析（JSA）重點
+危害根源：工作安全分析在分解工作步驟、辨識潛在危害時，主要考量的根源包含人員、方法、材料（以及機械設備/環境等），這些是直接產生風險的要素。
+訓練的角色：訓練是用來預防、降低或控制危害的手段與教育措施，而非危害本身的「根源」。
+職安一點通服務網</t>
+        </is>
+      </c>
+      <c r="I464" s="2" t="inlineStr"/>
     </row>
     <row r="465" ht="92.59999999999999" customHeight="1">
       <c r="A465" s="2" t="n">
@@ -20570,8 +21022,19 @@
       <c r="G465" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H465" s="2" t="n"/>
-      <c r="I465" s="2" t="n"/>
+      <c r="H465" s="2" t="inlineStr">
+        <is>
+          <t>主管人員藉由觀察屬下工作步驟與分析作業實況來建立安全工作方法，稱為工作安全分析。
+相關名詞解析
+工作安全分析（Job Safety Analysis, JSA）：結合工作分析與預知危險，透過觀察、討論與修正，找出潛在危害並建立安全作業程序。
+安全觀察：側重於現場對人員行為或環境的檢視與回饋，但未包含完整的工作步驟分解與方法建立流程。
+安全作業標準：是工作安全分析完成後所產出的具體規範成果。
+風險管理：涵蓋整體組織危害辨識、評估與控制的宏觀管理機制。
+Facebook
+·工安百科</t>
+        </is>
+      </c>
+      <c r="I465" s="2" t="inlineStr"/>
     </row>
     <row r="466" ht="92.59999999999999" customHeight="1">
       <c r="A466" s="2" t="n">
@@ -20605,8 +21068,17 @@
       <c r="G466" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H466" s="2" t="n"/>
-      <c r="I466" s="2" t="n"/>
+      <c r="H466" s="2" t="inlineStr">
+        <is>
+          <t>答案是教育訓練實施紀錄。
+原因解析
+教育訓練實施紀錄：主要記錄勞工參加安全衛生教育訓練的課程名稱、時數及簽到表等，屬於法規遵循與授課證明，較無法直接反映工作場所具體的機械設備、作業環境或現場操作的危害因素。
+自動檢查紀錄：記錄現場設備、機具的檢點與異常狀態，能直接呈現現場硬體危害。
+工作安全分析單（JSA）：針對特定作業步驟逐一分析潛在危害與控制方法，能明確了解現場作業危害。
+安全觀察紀錄表：記錄現場人員的不安全行為或環境狀況，直接對應現場實際動態危害。</t>
+        </is>
+      </c>
+      <c r="I466" s="2" t="inlineStr"/>
     </row>
     <row r="467" ht="108" customHeight="1">
       <c r="A467" s="2" t="n">
@@ -20640,8 +21112,17 @@
       <c r="G467" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H467" s="2" t="n"/>
-      <c r="I467" s="2" t="n"/>
+      <c r="H467" s="2" t="inlineStr">
+        <is>
+          <t>(A) 尋求避免危害及可能發生事故的方法為工作安全分析（JSA）的最後一個程序。
+工作安全分析的四大程序順序
+決定要分析的工作（第一步：選定對象）
+將工作分解成若干步驟（第二步：拆解流程）
+找出危害及可能發生的事故（第三步：辨識風險）
+尋求避免危害及可能發生事故的方法（最後一步：研擬對策與改善措施）</t>
+        </is>
+      </c>
+      <c r="I467" s="2" t="inlineStr"/>
     </row>
     <row r="468" ht="92.59999999999999" customHeight="1">
       <c r="A468" s="2" t="n">
@@ -20675,8 +21156,20 @@
       <c r="G468" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H468" s="2" t="n"/>
-      <c r="I468" s="2" t="n"/>
+      <c r="H468" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+下列何者非製作工作安全分析程序之要項？答案是 (B) 製作安全衛生作業標準。
+解析
+工作安全分析（Job Safety Analysis, 簡稱 JSA）主要是針對工作步驟進行拆解與風險控制，其主要步驟與要項包含：
+中華民國工業安全衛生協會 選擇需要分析的工作
+將工作步驟分解
+辨識出潛在的危害
+決定安全的工作方法（或研擬改善與控制對策）
+中華民國工業安全衛生協會 而「製作安全衛生作業標準」通常是工作安全分析完成、確定安全工作方法後延伸的後續產出或應用，並非直接屬於「製作工作安全分析程序」本身的拆解要項。</t>
+        </is>
+      </c>
+      <c r="I468" s="2" t="inlineStr"/>
     </row>
     <row r="469" ht="108" customHeight="1">
       <c r="A469" s="2" t="n">
@@ -20710,8 +21203,18 @@
       <c r="G469" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H469" s="2" t="n"/>
-      <c r="I469" s="2" t="n"/>
+      <c r="H469" s="2" t="inlineStr">
+        <is>
+          <t>正確的敘述為：「風險評估係指辨識、分析及評量風險之過程」。
+相關選項解析
+正確選項：風險評估係指辨識、分析及評量風險之過程（符合職業安全衛生風險評估之定義與風險評估技術指引規範）。
+桃園市政府 不正確選項：
+風險評估是用以自主管理與預防災害之機制，而非僅供認證單位稽核之工具。
+風險評估不一定「一律」以具體量化數字計算，亦可採用相對風險等級之定性或半定量評估。
+風險評估涵蓋全面性危害鑑別與評量，不侷限於僅依歷年職災實錄來辨識主要危害類型。</t>
+        </is>
+      </c>
+      <c r="I469" s="2" t="inlineStr"/>
     </row>
     <row r="470" ht="108" customHeight="1">
       <c r="A470" s="2" t="n">
@@ -20745,8 +21248,17 @@
       <c r="G470" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H470" s="2" t="n"/>
-      <c r="I470" s="2" t="n"/>
+      <c r="H470" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+運營風險矩陣方式評估風險可能性時，正確的評量方式為極有可能：3，有可能：2，可能性低：1。
+風險可能性評量選項對照
+極有可能：3 分
+有可能：2 分
+可能性低：1 分</t>
+        </is>
+      </c>
+      <c r="I470" s="2" t="inlineStr"/>
     </row>
     <row r="471" ht="92.59999999999999" customHeight="1">
       <c r="A471" s="2" t="n">
@@ -20780,8 +21292,15 @@
       <c r="G471" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H471" s="2" t="n"/>
-      <c r="I471" s="2" t="n"/>
+      <c r="H471" s="2" t="inlineStr">
+        <is>
+          <t>答案是 (C) 緊急應變措施。
+原因解析
+緊急應變措施是當危害已經發生或災害擴大時的應變與處置作為，而非在事前用來「辨識」作業環境危害的方法。
+作業場所巡視、檢查虛驚事故與員工健康檢查紀錄、以及查詢安全資料表（物質安全資料表），皆屬於事前調查、收集資訊或尋找潛在危險源以進行危害辨識的有效方法。</t>
+        </is>
+      </c>
+      <c r="I471" s="2" t="inlineStr"/>
     </row>
     <row r="472" ht="92.59999999999999" customHeight="1">
       <c r="A472" s="2" t="n">
@@ -20815,8 +21334,31 @@
       <c r="G472" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H472" s="2" t="n"/>
-      <c r="I472" s="2" t="n"/>
+      <c r="H472" s="2" t="inlineStr">
+        <is>
+          <t>風險是危害事件發生的可能性與嚴重性兩者之 (C) 乘積。
+重點說明
+定義：在職業安全衛生與風險評估中，風險（Risk）通常表示為事件發生的可能性（機率）與其後果嚴重性的組合，計算方式為兩者相乘的綜合指標（
+風
+險
+=
+可
+能
+性
+×
+嚴
+重
+性
+）。
+龍華科技大學
+選項對照：
+(A) 和
+(B) 差
+(C) 乘積
+(D) 除</t>
+        </is>
+      </c>
+      <c r="I472" s="2" t="inlineStr"/>
     </row>
     <row r="473" ht="92.59999999999999" customHeight="1">
       <c r="A473" s="2" t="n">
@@ -20850,8 +21392,20 @@
       <c r="G473" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H473" s="2" t="n"/>
-      <c r="I473" s="2" t="n"/>
+      <c r="H473" s="2" t="inlineStr">
+        <is>
+          <t>風險評估
+相關說明
+定義：對危害發生的機率與造成的損失進行評估與判斷，藉此提出因應對策以修正作業計畫，即為職業安全衛生管理中的「風險評估」。
+核心步驟：
+辨識危害及後果
+評估危害發生的機率與嚴重度（風險）
+決定與採取降低風險的控制措施
+中小企業安全衛生資訊網 甲種職業安全衛生業務主管_第二篇第二章風險評估#106913
+2021年12月31日 — 對危害發生之機率與危害所造成損失進行評估與判斷，最後評估危害發生造成之損失、範圍及發生機率，並提出因應對策，藉以修正作業計畫，稱之為(A)計畫評估 ...</t>
+        </is>
+      </c>
+      <c r="I473" s="2" t="inlineStr"/>
     </row>
     <row r="474" ht="92.59999999999999" customHeight="1">
       <c r="A474" s="2" t="n">
@@ -20885,8 +21439,16 @@
       <c r="G474" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H474" s="2" t="n"/>
-      <c r="I474" s="2" t="n"/>
+      <c r="H474" s="2" t="inlineStr">
+        <is>
+          <t>工作場所安全衛生風險評估的第一個步驟是危害辨識。
+產業本質安全推動網站
+說明
+危害辨識：尋找每個工作場所中，所有可能造成人體傷害或物質損害的潛在因素。這是後續進行風險分析與評估的基礎。
+產業本質安全推動網站</t>
+        </is>
+      </c>
+      <c r="I474" s="2" t="inlineStr"/>
     </row>
     <row r="475" ht="92.59999999999999" customHeight="1">
       <c r="A475" s="2" t="n">
@@ -20920,8 +21482,19 @@
       <c r="G475" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H475" s="2" t="n"/>
-      <c r="I475" s="2" t="n"/>
+      <c r="H475" s="2" t="inlineStr">
+        <is>
+          <t>勞工的素質 不是危害辨識分類基本的元素之一。
+說明
+在職業安全衛生與營造安全風險評估的危害辨識分類中，基本的元素通常包含：
+工作設備的使用
+工程施工方法
+施工程序變更
+物理媒介的接觸、作業與廠房規劃等
+「勞工的素質」屬於人員特性或管理範疇，並非直接用來作為危害辨識分類的硬體、程序或物理性基本元素分類。</t>
+        </is>
+      </c>
+      <c r="I475" s="2" t="inlineStr"/>
     </row>
     <row r="476" ht="92.59999999999999" customHeight="1">
       <c r="A476" s="2" t="n">
@@ -20955,8 +21528,15 @@
       <c r="G476" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H476" s="2" t="n"/>
-      <c r="I476" s="2" t="n"/>
+      <c r="H476" s="2" t="inlineStr">
+        <is>
+          <t>根據我國《職業安全衛生管理辦法》及風險評估（危害辨識與風險評估）的相關指引，答案是：須指定。
+詳細說明如下：
+法規與實務要求： 對於評估出屬於「不可接受風險（重大風險）」的危害項目，事業單位必須採取減輕或控制風險的降低風險對策。
+執行關鍵： 為了確保對策能夠切實執行，管理計畫中必須明確指定負責人員（權責單位）並訂定完成期限，否則對策往往會流於形式，無法達到追蹤與改善的效果。</t>
+        </is>
+      </c>
+      <c r="I476" s="2" t="inlineStr"/>
     </row>
     <row r="477" ht="92.59999999999999" customHeight="1">
       <c r="A477" s="2" t="n">
@@ -20990,8 +21570,12 @@
       <c r="G477" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H477" s="2" t="n"/>
-      <c r="I477" s="2" t="n"/>
+      <c r="H477" s="2" t="inlineStr">
+        <is>
+          <t>依勞動部風險評估技術指引，適用於勞工人數 29 人以下之事業單位所需的風險評估表單是基本版。</t>
+        </is>
+      </c>
+      <c r="I477" s="2" t="inlineStr"/>
     </row>
     <row r="478" ht="92.59999999999999" customHeight="1">
       <c r="A478" s="2" t="n">
@@ -21025,8 +21609,13 @@
       <c r="G478" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H478" s="2" t="n"/>
-      <c r="I478" s="2" t="n"/>
+      <c r="H478" s="2" t="inlineStr">
+        <is>
+          <t>依勞動部風險評估指引，適用於勞工人數30～299人之事業單位所需表單是標準版。
+中小企業安全衛生資訊網</t>
+        </is>
+      </c>
+      <c r="I478" s="2" t="inlineStr"/>
     </row>
     <row r="479" ht="92.59999999999999" customHeight="1">
       <c r="A479" s="2" t="n">
@@ -21060,8 +21649,19 @@
       <c r="G479" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H479" s="2" t="n"/>
-      <c r="I479" s="2" t="n"/>
+      <c r="H479" s="2" t="inlineStr">
+        <is>
+          <t>依據勞動部職業安全衛生署公布的「風險評估技術指引」，適用於勞工人數 300 人以上之事業單位所需表單是系統版。
+中小企業安全衛生資訊網
+指引中針對不同規模的事業單位所建議的表單區分如下：
+中小企業安全衛生資訊網
+基本版：適用於勞工人數 29 人以下之事業單位或已知之高風險作業。
+標準版：適用於勞工人數 30～299 人之事業單位。
+系統版：適用於勞工人數 300 人以上及依規定須推動職業安全衛生管理系統之事業單位。
+中小企業安全衛生資訊網</t>
+        </is>
+      </c>
+      <c r="I479" s="2" t="inlineStr"/>
     </row>
     <row r="480" ht="92.59999999999999" customHeight="1">
       <c r="A480" s="2" t="n">
@@ -21095,8 +21695,19 @@
       <c r="G480" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H480" s="2" t="n"/>
-      <c r="I480" s="2" t="n"/>
+      <c r="H480" s="2" t="inlineStr">
+        <is>
+          <t>風險等級中無須採取行動，無須保存任何文件紀錄屬於微不足道的風險（選項A）。
+宏國德霖科技大學圖書館
+風險等級對照
+微不足道的風險：無須採取行動，無須保存任何文件紀錄。
+可忍受的風險：無須進一步預防動作，但須隨時監控確保控制措施維持。
+中等程度風險：必須採取動作以降低風險，並在規定時間內完成。
+顯著的風險：在危害風險降低前，不得使勞工進行工作。
+宏國德霖科技大學圖書館</t>
+        </is>
+      </c>
+      <c r="I480" s="2" t="inlineStr"/>
     </row>
     <row r="481" ht="92.59999999999999" customHeight="1">
       <c r="A481" s="2" t="n">
@@ -21130,8 +21741,17 @@
       <c r="G481" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H481" s="2" t="n"/>
-      <c r="I481" s="2" t="n"/>
+      <c r="H481" s="2" t="inlineStr">
+        <is>
+          <t>這題的答案是 顯著的風險。
+職業安全衛生風險等級說明
+在危害風險評估中，「顯著的風險」代表該危害相當嚴重，必須採取以下嚴格措施：
+禁止作業：在危害風險降低之前，不得使勞工進行工作。
+投入成本：必須花費相當成本在預防與控制措施上，以降低風險。
+限期改善：若涉及進行中之工程，其危害必須在更短的時間內予以改善。</t>
+        </is>
+      </c>
+      <c r="I481" s="2" t="inlineStr"/>
     </row>
     <row r="482" ht="92.59999999999999" customHeight="1">
       <c r="A482" s="2" t="n">

--- a/salf/丙種職業安全衛生業務主管題庫.xlsx
+++ b/salf/丙種職業安全衛生業務主管題庫.xlsx
@@ -21785,8 +21785,12 @@
       <c r="G482" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H482" s="2" t="n"/>
-      <c r="I482" s="2" t="n"/>
+      <c r="H482" s="2" t="inlineStr">
+        <is>
+          <t>Google AI 摘要未抓取到，請手動補充。</t>
+        </is>
+      </c>
+      <c r="I482" s="2" t="inlineStr"/>
     </row>
     <row r="483" ht="92.59999999999999" customHeight="1">
       <c r="A483" s="2" t="n">
@@ -21820,8 +21824,19 @@
       <c r="G483" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H483" s="2" t="n"/>
-      <c r="I483" s="2" t="n"/>
+      <c r="H483" s="2" t="inlineStr">
+        <is>
+          <t>依勞動部風險評估技術指引，常見矩陣組合可將風險等級區分（如常見之半定量矩陣配合嚴重度與可能性評分組合出不同等級，如營造或一般指引常用 4 級或 5 級，例如風險值對應或矩陣常見 1~5 級或不同對應區間。以一般常見矩陣如嚴重度4級與可能性4級交叉或對應範例中常見 4 級分類，但亦有分5級者）。
+看選項：4 級、5 級、6 級、7 級。依勞動部常見半定量或矩陣範例（如可能性與嚴重度級距乘積或矩陣對應），實務上常見為 5 級（例如嚴重度5級、可能性5級交乘或分5個風險等級如可接受/待改善/不可接受）或部分指引對應4級。不過多數職安矩陣對應常見評分。根據常見勞動部職業安全衛生署相關指引與說明（例如常見矩陣對應或常見選項），標準矩陣常見 5 級或對應級別。
+讓我們先精簡回答：
+依勞動部相關職業安全衛生風險評估實務與矩陣對應，通常採 5 級（部分指引或矩陣對應亦見 4 級，如常見矩陣最高到 5 級評分或分級）。若以選擇題標準或常見矩陣（如嚴重度1-5、可能性1-5交乘後分級），通常對應 5 級（或看特定表格分類）。
+重新核對選項：4 級 5 級 6 級 7 級。
+依常見勞動部指引矩陣（如可能性5等級、嚴重度5等級交叉，對應出不同風險區間或等級），通常總共分 5 級（如不可接受、顯著等或1~5級風險值區間）。
+精準重點：
+正確選項：5 級（常見如風險矩陣將風險值或組合成 5 個等級，例如不可接受風險、須改善等）。</t>
+        </is>
+      </c>
+      <c r="I483" s="2" t="inlineStr"/>
     </row>
     <row r="484" ht="92.59999999999999" customHeight="1">
       <c r="A484" s="2" t="n">
@@ -21855,8 +21870,14 @@
       <c r="G484" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H484" s="2" t="n"/>
-      <c r="I484" s="2" t="n"/>
+      <c r="H484" s="2" t="inlineStr">
+        <is>
+          <t>依勞動部風險評估分級，造成一人以上死亡之嚴重度屬於 (A) 重大 等級。
+根據勞動部相關職業安全衛生風險評估規範，嚴重度分級通常分為四級（S4 重大、S3 高度、S2 中度、S1 輕度），其中「造成一人以上死亡、三人以上受傷，或可能發生無法復原之職業病」被歸類在最高級的 重大（S4）。
+中小企業安全衛生資訊網</t>
+        </is>
+      </c>
+      <c r="I484" s="2" t="inlineStr"/>
     </row>
     <row r="485" ht="92.59999999999999" customHeight="1">
       <c r="A485" s="2" t="n">
@@ -21890,8 +21911,23 @@
       <c r="G485" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H485" s="2" t="n"/>
-      <c r="I485" s="2" t="n"/>
+      <c r="H485" s="2" t="inlineStr">
+        <is>
+          <t>預期危害事件每年發生一次以上之可能性屬於極可能等級。
+中小企業安全衛生資訊網 依據勞動部相關職業安全衛生風險評估技術指引與可能性分級標準（如 P4 級）：
+極可能 (P4)：每年發生 1 次（含）以上（或每年發生
+≥
+3
+≥
+3
+次，視各行業/範本參考細節而定，但頻率達每年一次以上皆歸類於最高可能性分級）。
+較有可能 (P3)：每 1 至 10 年發生 1 次（或每年 1 至 2 次）。
+有可能 (P2)：每 10 至 100 年發生 1 次。
+不太可能 (P1)：100 年以上發生 1 次。
+學校安全衛生資訊網</t>
+        </is>
+      </c>
+      <c r="I485" s="2" t="inlineStr"/>
     </row>
     <row r="486" ht="92.59999999999999" customHeight="1">
       <c r="A486" s="2" t="n">
@@ -21925,8 +21961,22 @@
       <c r="G486" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H486" s="2" t="n"/>
-      <c r="I486" s="2" t="n"/>
+      <c r="H486" s="2" t="inlineStr">
+        <is>
+          <t>根據我國《職業安全衛生法》及《職業安全衛生管理辦法》規定，事業單位執行或檢討風險評估時，應由安全衛生人員、各級主管及熟悉該作業的員工共同參與，並應有工會或勞工代表參與。
+在您列出的選項中，最符合法規強制要求必須參與的內部人員是「工會（或勞工代表）」與「熟悉該作業的員工」。
+核心參與人員說明
+內部核心團隊（法規強制）：
+工會或勞工代表：法規明確規定，風險評估的程序與過程應有勞工代表參與。
+熟悉該作業的員工：第一線作業人員最清楚實際操作時的危害與潛在風險，是評估準確性的關鍵。
+工作場所負責人 / 各級主管：負責指揮監督，並擁有改善資源的權限。
+職業安全衛生人員：負責規劃、協調、提供專業指引並統籌評估作業。
+外部單位（非固定編組人員）：
+當地勞檢機構：屬於外部監督與執法單位，不會直接參與事業單位內部的風險評估執行。
+安全衛生協會：屬於外部法人或顧問機構，若事業單位內部專業能力不足，可自費邀請其進行技術諮詢或輔導，但非編組內必定參與的法定成員。</t>
+        </is>
+      </c>
+      <c r="I486" s="2" t="inlineStr"/>
     </row>
     <row r="487" ht="92.59999999999999" customHeight="1">
       <c r="A487" s="2" t="n">
@@ -21960,8 +22010,19 @@
       <c r="G487" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H487" s="2" t="n"/>
-      <c r="I487" s="2" t="n"/>
+      <c r="H487" s="2" t="inlineStr">
+        <is>
+          <t>降低風險控制措施的首要考量為消除。職業安全衛生的風險管控順序（控制階層 Hierarchy of Control）中，最高優先順序與最首要考量是從源頭直接將危險根源完全移除。
+中小企業安全衛生資訊網 依據危害控制的優先順序，其完整排列為：
+消除（首要考量）
+取代
+工程控制
+管理控制
+個人防護具（最後防線）
+新竹市消防局</t>
+        </is>
+      </c>
+      <c r="I487" s="2" t="inlineStr"/>
     </row>
     <row r="488" ht="92.59999999999999" customHeight="1">
       <c r="A488" s="2" t="n">
@@ -21995,8 +22056,18 @@
       <c r="G488" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H488" s="2" t="n"/>
-      <c r="I488" s="2" t="n"/>
+      <c r="H488" s="2" t="inlineStr">
+        <is>
+          <t>這個問題的答案是 初步危害分析（Preliminary Hazard Analysis, PHA）。
+為什麼是初步危害分析？
+初步危害分析 (PHA)：主要用於製程或作業開發初期或規劃階段。它的目的就是對系統中的主要作業項目、危險物質及潛在危害進行先期、初步的評估，藉此識別出高風險領域，以決定後續是否需要採取更細部的評估方法（如 HAZOP、FTA 等）。
+其他選項的用途
+檢核表分析 (Checklist Analysis)：利用預先編製好的清單（Checklist）來逐項檢查設備或作業是否符合安全標準，屬於對照式的經驗評估。
+危害及可操作性分析 (HAZOP)：屬於細部評估方法，利用引導詞（如流量過大、無壓力等）系統化地探討製程偏離設計意圖時可能產生的危害。
+故障樹分析 (FTA)：屬於定性與定量的細部評估方法，從一個已知的系統故障結果（頂上事件）開始，由上而下尋找導致該故障的所有潛在原因。</t>
+        </is>
+      </c>
+      <c r="I488" s="2" t="inlineStr"/>
     </row>
     <row r="489" ht="92.59999999999999" customHeight="1">
       <c r="A489" s="2" t="n">
@@ -22030,8 +22101,16 @@
       <c r="G489" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H489" s="2" t="n"/>
-      <c r="I489" s="2" t="n"/>
+      <c r="H489" s="2" t="inlineStr">
+        <is>
+          <t>這題的答案是可以。
+核心觀念解析
+風險矩陣當然可以採取動態的設計。在現代安全管理與風險控制（如南工組等系統化架構）中，推動「動態風險評估」是提升安全績效的關鍵趨勢。
+即時回饋與更新：當系統化蒐集到現場的績效量測結果、異常事件或設備狀態時，這些數據可以即時回饋並動態調整風險矩陣中的發生機率（Likelihood）或後果嚴重度（Consequence），進而自動更新風險等級。
+評估實施地點：這種動態回饋雖然依賴系統（如總公司或中央控制系統）進行數據運算與矩陣更新，但其核心數據源自於現場實際狀況與評估。動態風險矩陣的目的正是為了讓管理階層與現場人員能即時掌握最新的動態風險，而不是將風險評估硬性限縮在只能於特定地點（如僅在總公司內）進行靜態審查。</t>
+        </is>
+      </c>
+      <c r="I489" s="2" t="inlineStr"/>
     </row>
     <row r="490" ht="123.45" customHeight="1">
       <c r="A490" s="2" t="n">
@@ -22065,8 +22144,15 @@
       <c r="G490" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H490" s="2" t="n"/>
-      <c r="I490" s="2" t="n"/>
+      <c r="H490" s="2" t="inlineStr">
+        <is>
+          <t>錯誤的敘述為：「機具設備設計製造以產能為導向，操作安全應由使用者依各自之工作內容進行風險評估，與製造者無關」。
+原因說明
+製造者的責任：機具設備的操作安全與本質安全設計，在源頭上與製造者密不可分。製造商有責任在設計與製造階段進行風險評估，提供安全的設備與使用說明，而不是全部推給使用者負責。
+正確做法：其他選項如主辦機關應合理設定需求與工期、施工規劃及設計階段皆應實施風險評估，均為正確的風險管理與職業安全衛生要求。</t>
+        </is>
+      </c>
+      <c r="I490" s="2" t="inlineStr"/>
     </row>
     <row r="491" ht="92.59999999999999" customHeight="1">
       <c r="A491" s="2" t="n">
@@ -22100,8 +22186,15 @@
       <c r="G491" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H491" s="2" t="n"/>
-      <c r="I491" s="2" t="n"/>
+      <c r="H491" s="2" t="inlineStr">
+        <is>
+          <t>錯誤的敘述為：「列入自主檢查缺失統計」（通常對應選項 (C) 或 ③）。
+解析
+風險評估成果的追蹤管制主要是針對潛在危害預防與對策實施成效進行管理與檢討，例如列入工地協議組織會議中列管追蹤、提報公司管理審查會議檢討、以及由相關部門主管追蹤對策處置人員辦理情形。
+它屬於風險管理與危害控制的預防追蹤機制，並不直接「列入自主檢查缺失統計」中（自主檢查通常針對施工當下的具體設施設備或作業環境符合性進行缺失統計）。</t>
+        </is>
+      </c>
+      <c r="I491" s="2" t="inlineStr"/>
     </row>
     <row r="492" ht="92.59999999999999" customHeight="1">
       <c r="A492" s="2" t="n">
@@ -22135,8 +22228,19 @@
       <c r="G492" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H492" s="2" t="n"/>
-      <c r="I492" s="2" t="n"/>
+      <c r="H492" s="2" t="inlineStr">
+        <is>
+          <t>依據製程安全評估定期實施辦法規定，事業單位成立之製程評估小組成員應包含 工作場所負責人。
+製程評估小組必要成員
+依規定，評估小組應由下列人員組成：
+工作場所負責人
+製程安全評估人員（曾受專業訓練或具專業能力並經認可者）
+職業安全衛生人員
+工作場所作業主管
+熟悉該場所作業之勞工</t>
+        </is>
+      </c>
+      <c r="I492" s="2" t="inlineStr"/>
     </row>
     <row r="493" ht="92.59999999999999" customHeight="1">
       <c r="A493" s="2" t="n">
@@ -22170,8 +22274,15 @@
       <c r="G493" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H493" s="2" t="n"/>
-      <c r="I493" s="2" t="n"/>
+      <c r="H493" s="2" t="inlineStr">
+        <is>
+          <t>在製程安全管理（PSM）中，蒐集製程安全資訊（PSI）的主要目的是為了辨識和評估製程中的潛在危害，因此該資訊一般可應用於製程危害分析（PHA）。
+為什麼是製程危害分析？
+核心依據：製程安全資訊（如化學品危害特性、製程設計基礎、設備管線圖等）是執行製程危害分析的最重要基礎。沒有完整的資訊，就無法準確評估潛在的風險與危害。
+其他選項不相關：訂定請假規則、操作人員家庭財務分析、以及同業間之產品價格定價，皆屬於人力資源、個人隱私或商業市場策略的範疇，與製程安全工程無關。 內容</t>
+        </is>
+      </c>
+      <c r="I493" s="2" t="inlineStr"/>
     </row>
     <row r="494" ht="92.59999999999999" customHeight="1">
       <c r="A494" s="2" t="n">
@@ -22205,8 +22316,22 @@
       <c r="G494" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H494" s="2" t="n"/>
-      <c r="I494" s="2" t="n"/>
+      <c r="H494" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+依「製程安全評估定期實施辦法」規定，答案是 (B) 為何樹分析（不包括在內，法規規定的是「故障樹分析」）。
+相關法規說明
+依據 製程安全評估定期實施辦法 第 5 條規定，製程安全評估應使用下列一種以上之安全評估方法：
+如果-結果分析
+檢核表
+如果-結果分析／檢核表
+危害及可操作性分析
+失誤模式及影響分析
+故障樹分析（選項中的「為何樹分析」為錯誤名稱）
+其他經中央主管機關認可具有同等功能之安全評估方法</t>
+        </is>
+      </c>
+      <c r="I494" s="2" t="inlineStr"/>
     </row>
     <row r="495" ht="92.59999999999999" customHeight="1">
       <c r="A495" s="2" t="n">
@@ -22240,8 +22365,19 @@
       <c r="G495" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H495" s="2" t="n"/>
-      <c r="I495" s="2" t="n"/>
+      <c r="H495" s="2" t="inlineStr">
+        <is>
+          <t>FTA 為故障樹分析（Fault Tree Analysis）之縮寫。
+相關評估方法簡介
+FTA（故障樹分析）：採用「由上而下（Top-Down）」的演繹邏輯，從不希望發生的頂端事件開始，推導出導致該事件發生的各種系統故障或人為失誤原因。
+HAZOP（危害及可操作性分析）：透過引導詞系統性地分析製程操作參數的偏差所引起的危害。
+勞動部職業安全衛生署
+FMEA（失誤模式與影響分析）：採用「由下而上（Bottom-Up）」的方式，逐一分析系統中各個零組件的失效模式及其對整個系統造成的影響。
+Threads
+·osh_flourishing</t>
+        </is>
+      </c>
+      <c r="I495" s="2" t="inlineStr"/>
     </row>
     <row r="496" ht="92.59999999999999" customHeight="1">
       <c r="A496" s="2" t="n">
@@ -22275,8 +22411,16 @@
       <c r="G496" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H496" s="2" t="n"/>
-      <c r="I496" s="2" t="n"/>
+      <c r="H496" s="2" t="inlineStr">
+        <is>
+          <t>FMEA 為失誤模式與影響分析（Failure Mode and Effects Analysis，又譯失效模式與效應分析）之縮寫。
+製造新觀點 簡介
+定義：一種結構化與預防式的風險評估工具。
+目的：用來系統性辨識產品、製程或系統中可能發生的失誤，並評估其影響程度與發生機率，以事先採取改善措施。
+SG Systems Global</t>
+        </is>
+      </c>
+      <c r="I496" s="2" t="inlineStr"/>
     </row>
     <row r="497" ht="92.59999999999999" customHeight="1">
       <c r="A497" s="2" t="n">
@@ -22310,8 +22454,21 @@
       <c r="G497" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H497" s="2" t="n"/>
-      <c r="I497" s="2" t="n"/>
+      <c r="H497" s="2" t="inlineStr">
+        <is>
+          <t>事業單位設置甲類工作場所向檢查機構申請審查時，應檢附之「製程安全評估報告書」內容不包括【安全衛生人員報備書】。
+S-link 電子六法全書
+製程安全評估報告書包含項目
+依據《危險性工作場所審查及檢查辦法》附件二規定，製程安全評估報告書主要包括：
+製程說明（如流程圖、設計規範、設備規格、操作手冊與維修保養制度等）
+實施初步危害分析以分析發掘重大潛在危害，並針對重大潛在危害依規定方法實施安全評估
+製程危害控制
+參與評估人員具名簽認
+S-link 電子六法全書
+而「安全衛生人員報備書」屬於安全衛生管理基本資料或設置報備事項，並非製程安全評估報告書之組成內容。</t>
+        </is>
+      </c>
+      <c r="I497" s="2" t="inlineStr"/>
     </row>
     <row r="498" ht="92.59999999999999" customHeight="1">
       <c r="A498" s="2" t="n">
@@ -22345,8 +22502,19 @@
       <c r="G498" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H498" s="2" t="n"/>
-      <c r="I498" s="2" t="n"/>
+      <c r="H498" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+依據《製程安全評估定期實施辦法》規定，事業單位實施製程安全評估及報告內容不包括「急救搶救」。
+重點整理
+不包括的項目：急救搶救（屬於緊急應變或現場救護範疇，非製程安全評估報告規定應涵蓋之項目）。
+包括的項目：
+製程安全資訊
+機械完整性
+原料改變等相關變更管理與評估事項（如製程修改時亦適用）</t>
+        </is>
+      </c>
+      <c r="I498" s="2" t="inlineStr"/>
     </row>
     <row r="499" ht="92.59999999999999" customHeight="1">
       <c r="A499" s="2" t="n">
@@ -22380,8 +22548,17 @@
       <c r="G499" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H499" s="2" t="n"/>
-      <c r="I499" s="2" t="n"/>
+      <c r="H499" s="2" t="inlineStr">
+        <is>
+          <t>依據《職業安全衛生法》第15條規定，應定期實施製程安全評估的工作場所為從事石油裂解之石化工業。故正確選項為(A)從事石油裂解之石化工業（題目中常寫作「從事石油製解」）。
+相關法規重點
+規範對象：
+從事石油裂解之石化工業。
+從事製造、處置或使用危害性之化學品數量達中央主管機關規定量以上之工作場所。
+應辦事項：事業單位應定期實施製程安全評估，製作評估報告並報請勞動檢查機構備查，製程修改時亦同。</t>
+        </is>
+      </c>
+      <c r="I499" s="2" t="inlineStr"/>
     </row>
     <row r="500" ht="108" customHeight="1">
       <c r="A500" s="2" t="n">
@@ -22415,8 +22592,15 @@
       <c r="G500" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H500" s="2" t="n"/>
-      <c r="I500" s="2" t="n"/>
+      <c r="H500" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+答案為：各級主管人員應於報告書中具名簽認。
+說明
+依據「危險性工作場所審查及檢查辦法」及相關規定，申請甲類、乙類、丙類危險性工作場所審查或檢查所檢附之製程安全評估報告書，其內容主要包含製程說明、實施初步危害分析並針對重大潛在危害實施規定之安全評估方法、製程危害控制等項目，並沒有「各級主管人員應於報告書中具名簽認」之強制條文內容要求。</t>
+        </is>
+      </c>
+      <c r="I500" s="2" t="inlineStr"/>
     </row>
     <row r="501" ht="92.59999999999999" customHeight="1">
       <c r="A501" s="2" t="n">
@@ -22450,8 +22634,79 @@
       <c r="G501" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H501" s="2" t="n"/>
-      <c r="I501" s="2" t="n"/>
+      <c r="H501" s="2" t="inlineStr">
+        <is>
+          <t>，請稍後再試。
+網頁搜尋結果
+157. 製程安全評估定期實施辦法所稱製程修改
+› item-157.+製程安全評估定期實施辦...
+2025年4月7日 — 158.製程安全評估定期實施辦法所稱製程修改，不包括下列何者？ (A)對適用 工作場所之製程化學品之變更(B)製程操作程序之變更(C)製程操作人員 異動(D)製程 ...
+39. 製程安全評估定期實施辦法所稱製程修改
+› item-39.++製程安全評估定期實施辦...
+2019年12月2日 — 39. 製程安全評估定期實施辦法所稱製程修改，不包括下列何者？ (A)對適用工作場所之製程化學品之 變更 (B)製程操作人員異動 (C)製程設備之變更 (D)製程 ...
+[題庫][職業安全衛生管理(乙)][01
+BLOCK 學習網
+› question
+製程安全評估定期實施辦法所稱製程修改，不包括下列何者？ A 對適用工作場所之製程化學品之變更. B 製程操作程序之變更. C 製程操作人員異動. D 製程設備之變更. 答案. 9 ...
+製程安全評估定期實施辦法所稱製程修改，不包括下列何者？
+職業安全衛生管理證照題庫練習
+› content › qbDetail
+製程安全評估定期實施辦法所稱製程修改，不包括下列何者？ · A 對適用工作場所之製程化學品之變更 · B 製程操作程序之變更 · C 製程操作人員異動 · D 製程設備之變更.
+1 個答案
+·
+最佳解答:
+正確答案：C。依製程安全評估定期實施辦法 本辦法所稱製程修改，指前條工作場所既有安全防護措施未能控制新淺 ...
+製程安全評估定期實施辦法(民國109 年07 月17 日修正)
+› flaw › FLAWDAT0202
+本辦法所稱製程安全評估，指利用結構化、系統化方式，辨識、分析前條工作場所潛在危害，而採取必要預防措施之評估。 本辦法所稱製程修改，指前條工作場所既有安全防護措施 ...
+缺少字詞： 對 ‎異動
+製程安全評估定期實施辦法部分條文修正總說明
+行政院公報資訊網
+› type1 › num28 › images
+PDF
+第三條本辦法所稱製 程安全評估,指利用結 構化、系統化方式,辨 識、分析前條… 本辦法所稱製程修改,指對前條工作場 所之製程化學品、技 術、設備、操作程序、 規模或影響製 ...
+4 頁
+缺少字詞： 不 ‎何者 ? ‎異動
+製程安全評估定期實施辦法第3 條- 2026 最新全國法規資料庫
+› 製程安全評估定期實施辦法
+1.本辦法所稱製程安全評估,指利用結構化、系統化方式,辨識、分析前條工作場所潛在危害,而採取必要預防措施之評估。 2.本辦法所稱製程修改,指前條工作場所既有安全防護措施 ...
+缺少字詞： 包括 ‎何者 ? ‎對 ‎適用 ‎人員 ‎異動
+114年- 22200 職業安全衛生管理乙級工作項目01
+› exam-114年+ +職業安全衛生...
+2024年12月31日 — 157. 製程安全評估定期實施辦法所稱製程修改，不包括下列何者？ (A)對適用工作場所之製程化學品之變更(B)製程操作程序之變更(C)製程操作人員異動(D)製程 ...
+法規新訊-修正「製程安全評估定期實施辦法」(2020-07-17)
+法源法律網
+› news › NewsContent
+2020年7月17日 — 本辦法所稱製程修改，指前條工作場所既有安全防護措施未能控制新潛在危害之製程化學品、技術、設備、操作程序或規模之變更。 第6 條 第四條所定每五年 ...
+缺少字詞： 不 ‎包括 ‎何者 ? ‎對 ‎適用 ‎異動
+其他人也搜尋了以下項目
+依營造安全衛生設施標準規定下列有關施工架之敘述何者正確
+依營造安全衛生設施標準規定防止人員墜落所設置之護欄下列何者錯誤
+依機械類產品型式驗證實施及監督管理辦法規定報驗義務人申請產品型式驗證時所檢附之構造圖說包括下列何者
+高壓氣體勞工安全規則於液化氣體定義所稱壓力原則上概指下列何者
+依危害性化學品標示及通識規則規定安全資料表中不包括下列何者
+下列敘述何者非為高壓氣體之製造
+從事局限空間作業如有危害勞工之虞應於作業場所顯而易見處公告注意事項公告內容不包括下列何者
+依缺氧症預防規則規定於缺氧危險作業場所入口之公告不包括下列何者
+頁面導覽
+1
+2
+3
+4
+5
+6
+下一頁
+頁尾連結
+台灣
+708 臺南市安平區 - 根據你的 IP 位址
+- 更新位置
+說明
+提供意見
+隱私權
+服務條款</t>
+        </is>
+      </c>
+      <c r="I501" s="2" t="inlineStr"/>
     </row>
     <row r="502" ht="92.59999999999999" customHeight="1">
       <c r="A502" s="2" t="n">
@@ -22485,8 +22740,20 @@
       <c r="G502" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H502" s="2" t="n"/>
-      <c r="I502" s="2" t="n"/>
+      <c r="H502" s="2" t="inlineStr">
+        <is>
+          <t>答案：公司之業務概況
+依據《危險性工作場所審查及檢查辦法》附件四「緊急應變計畫」之規定，緊急應變計畫的內容至少應包含下列事項：
+緊急應變運作流程與組織（包含應變組織架構與權責、緊急應變控制中心位置與設施、緊急應變運作流程與說明）。
+緊急應變設備之置備與外援單位之聯繫。
+緊急應變演練計畫與演練記錄（演練模擬一般及最嚴重危害之狀況）。
+緊急應變計畫之修正。
+因此，公司之業務概況並不屬於緊急應變計畫應涵蓋的規定內容。
+附件四緊急應變計畫
+附件四緊急應變計畫. 緊急應變計畫至少應含下列事項：. 一、緊急應變運作流程與組織：. 應變組織架構與權責。 緊急應變控制中心位置與設施。 緊急應變運作流程與說明。 二、緊急應變設備之置備與外援單位之聯繫。 三、緊急應變演練計畫與演練記錄（演練模擬一般及最嚴重...</t>
+        </is>
+      </c>
+      <c r="I502" s="2" t="inlineStr"/>
     </row>
     <row r="503" ht="92.59999999999999" customHeight="1">
       <c r="A503" s="2" t="n">
@@ -22520,8 +22787,16 @@
       <c r="G503" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H503" s="2" t="n"/>
-      <c r="I503" s="2" t="n"/>
+      <c r="H503" s="2" t="inlineStr">
+        <is>
+          <t>這類契約在法律上稱為雇傭契約（依據民法第482條規定）。
+法務部主管法規查詢系統 相關概念對照
+雇傭契約：一方於一定或不定之期限內為他方服勞務，他方給付報酬之契約（著重於勞務給付之過程）。
+承攬契約：一方為他方完成一定之工作，他方俟工作完成，給付報酬之契約（著重於工作成果）。
+新竹縣政府全球資訊網</t>
+        </is>
+      </c>
+      <c r="I503" s="2" t="inlineStr"/>
     </row>
     <row r="504" ht="92.59999999999999" customHeight="1">
       <c r="A504" s="2" t="n">
@@ -22555,8 +22830,13 @@
       <c r="G504" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H504" s="2" t="n"/>
-      <c r="I504" s="2" t="n"/>
+      <c r="H504" s="2" t="inlineStr">
+        <is>
+          <t>答案是 承攬。
+依據我國《民法》第 490 條第 1 項規定：「稱承攬者，謂當事人約定，一方為他方完成一定之工作，他方俟工作完成，給付報酬之契約。」</t>
+        </is>
+      </c>
+      <c r="I504" s="2" t="inlineStr"/>
     </row>
     <row r="505" ht="92.59999999999999" customHeight="1">
       <c r="A505" s="2" t="n">
@@ -22586,8 +22866,13 @@
       <c r="G505" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H505" s="2" t="n"/>
-      <c r="I505" s="2" t="n"/>
+      <c r="H505" s="2" t="inlineStr">
+        <is>
+          <t>這個定義指的是勞動契約。
+根據我國《勞動基準法》規定，勞動契約是指約定雇主與勞工關係的契約。其核心特徵在於勞工在一定期間內，接受雇主的指揮監督（指示），提供勞務（從事一定種類之活動）以獲取報酬。</t>
+        </is>
+      </c>
+      <c r="I505" s="2" t="inlineStr"/>
     </row>
     <row r="506" ht="92.59999999999999" customHeight="1">
       <c r="A506" s="2" t="n">

--- a/salf/丙種職業安全衛生業務主管題庫.xlsx
+++ b/salf/丙種職業安全衛生業務主管題庫.xlsx
@@ -22906,8 +22906,12 @@
       <c r="G506" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H506" s="2" t="n"/>
-      <c r="I506" s="2" t="n"/>
+      <c r="H506" s="2" t="inlineStr">
+        <is>
+          <t>Google AI 摘要未抓取到，請手動補充。</t>
+        </is>
+      </c>
+      <c r="I506" s="2" t="inlineStr"/>
     </row>
     <row r="507" ht="92.59999999999999" customHeight="1">
       <c r="A507" s="2" t="n">
@@ -22941,8 +22945,13 @@
       <c r="G507" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H507" s="2" t="n"/>
-      <c r="I507" s="2" t="n"/>
+      <c r="H507" s="2" t="inlineStr">
+        <is>
+          <t>二個或二個以上承攬人基於資金、人力組配等之實際需要，而以約定方式從事承攬一事業稱為共同承攬。
+威宏儀器科技有限公司</t>
+        </is>
+      </c>
+      <c r="I507" s="2" t="inlineStr"/>
     </row>
     <row r="508" ht="92.59999999999999" customHeight="1">
       <c r="A508" s="2" t="n">
@@ -22976,8 +22985,12 @@
       <c r="G508" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H508" s="2" t="n"/>
-      <c r="I508" s="2" t="n"/>
+      <c r="H508" s="2" t="inlineStr">
+        <is>
+          <t>Google AI 摘要未抓取到，請手動補充。</t>
+        </is>
+      </c>
+      <c r="I508" s="2" t="inlineStr"/>
     </row>
     <row r="509" ht="92.59999999999999" customHeight="1">
       <c r="A509" s="2" t="n">
@@ -23011,8 +23024,19 @@
       <c r="G509" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H509" s="2" t="n"/>
-      <c r="I509" s="2" t="n"/>
+      <c r="H509" s="2" t="inlineStr">
+        <is>
+          <t>勞動給付。
+承攬契約是以「勞動結果」（完成一定之工作）為目的[1]；而僱傭契約則是以「勞動給付」（提供勞務本身）為目的[1]。
+由於您的題目文字為「承措契約」，通常是「承攬契約」的常見打字錯別字：
+如果題目是在問承攬契約，其目的是勞動結果[1]。
+如果題目是在問僱傭契約，其目的是勞動給付[1]。
+您可以幫我確認以下資訊，以便為您精準解答：
+這題是出自哪一個考試科目或法規考題（例如：民法、勞基法）？
+題目是否有完整的前後文或多選題選項說明？ 內容</t>
+        </is>
+      </c>
+      <c r="I509" s="2" t="inlineStr"/>
     </row>
     <row r="510" ht="92.59999999999999" customHeight="1">
       <c r="A510" s="2" t="n">
@@ -23046,8 +23070,18 @@
       <c r="G510" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H510" s="2" t="n"/>
-      <c r="I510" s="2" t="n"/>
+      <c r="H510" s="2" t="inlineStr">
+        <is>
+          <t>依政府採購法第 65 條第 2 項規定，稱為轉包。
+相關概念區別
+轉包（採購法第 65 條）：
+指將原契約中應自行履行之全部或其主要部分，由其他廠商代為履行，這是法律所禁止的行為。
+新北市政府採購處 分包（採購法第 67 條）：
+指得標廠商非轉包，而將契約之部分（非主要部分）由其他廠商代為履行，基於專業分工，在合乎規定下是允許的。
+臺中市政府秘書處</t>
+        </is>
+      </c>
+      <c r="I510" s="2" t="inlineStr"/>
     </row>
     <row r="511" ht="92.59999999999999" customHeight="1">
       <c r="A511" s="2" t="n">
@@ -23081,8 +23115,19 @@
       <c r="G511" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H511" s="2" t="n"/>
-      <c r="I511" s="2" t="n"/>
+      <c r="H511" s="2" t="inlineStr">
+        <is>
+          <t>非屬轉包情形，而將契約部分由其他廠商代為履行稱為分包。
+臺北市政府採購業務資訊網
+相關概念解析
+分包：依據《政府採購法》第67條第1項規定，指非轉包而將契約之部分由其他廠商代為履行（通常為非主要部分或次要部分），此行為合法且被允許。
+轉包：依據同法第65條規定，指將原契約中應自行履行之全部或其主要部分，交由其他廠商代為履行，屬於違法行為。
+承包：指廠商直接向業主承接工程或勞務契約。
+並包：非法律或採購法規中規範的標準名詞。
+永然聯合法律事務所</t>
+        </is>
+      </c>
+      <c r="I511" s="2" t="inlineStr"/>
     </row>
     <row r="512" ht="92.59999999999999" customHeight="1">
       <c r="A512" s="2" t="n">
@@ -23116,8 +23161,17 @@
       <c r="G512" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H512" s="2" t="n"/>
-      <c r="I512" s="2" t="n"/>
+      <c r="H512" s="2" t="inlineStr">
+        <is>
+          <t>應由原事業單位指定工作場所負責人，擔任統一指揮及協調工作。
+相關法規說明
+依據《職業安全衛生法》第27條規定：
+事業單位以其事業交付承攬，並與承攬人、再承攬人之工作者共同作業時，原事業單位應設置協議組織，並指定工作場所負責人，擔任指揮、監督及協調之工作。
+此規範旨在防止共同作業時發生職業災害，明確由原事業單位負起統籌管理與聯繫調整的責任。
+新北市政府電子法規查詢系統</t>
+        </is>
+      </c>
+      <c r="I512" s="2" t="inlineStr"/>
     </row>
     <row r="513" ht="123.45" customHeight="1">
       <c r="A513" s="2" t="n">
@@ -23151,8 +23205,18 @@
       <c r="G513" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H513" s="2" t="n"/>
-      <c r="I513" s="2" t="n"/>
+      <c r="H513" s="2" t="inlineStr">
+        <is>
+          <t>「以上皆是」。
+依據《職業安全衛生法》第27條規定，事業單位（原事業單位）以其事業交付承攬，並與承攬人、再承攬人之工作者共同作業時，為防止職業災害，應採取下列必要措施：
+設置協議組織，並指定工作場所負責人，擔任指揮、監督及協調之工作
+工作之連繫及調整
+工作場所之巡視
+其他如安全衛生教育訓練指導、機械設備器具及人員進場管制等事項
+因此，選項中所提及的各項措施皆包含在內。</t>
+        </is>
+      </c>
+      <c r="I513" s="2" t="inlineStr"/>
     </row>
     <row r="514" ht="108" customHeight="1">
       <c r="A514" s="2" t="n">
@@ -23186,8 +23250,19 @@
       <c r="G514" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H514" s="2" t="n"/>
-      <c r="I514" s="2" t="n"/>
+      <c r="H514" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+協助承攬人遵守職業安全衛生相關法令為職業安全衛生法規定原事業單位應盡之義務。
+說明
+原事業單位義務：依據職業安全衛生法相關規定（如共同作業時的巡視、指導及協助等），原事業單位有責任協助承攬人遵守職業安全衛生相關法令。
+其他選項錯誤原因：
+承攬人雖就承攬部分負雇主責任，但原事業單位基於安全管理仍須依法介入、協調與指導，不能完全不介入。
+原事業單位是負指揮、監督或協調之責，而非「接受」承攬人之工作指示。
+協助通過勞動檢查並非法規規定的具體義務。</t>
+        </is>
+      </c>
+      <c r="I514" s="2" t="inlineStr"/>
     </row>
     <row r="515" ht="92.59999999999999" customHeight="1">
       <c r="A515" s="2" t="n">
@@ -23221,8 +23296,16 @@
       <c r="G515" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H515" s="2" t="n"/>
-      <c r="I515" s="2" t="n"/>
+      <c r="H515" s="2" t="inlineStr">
+        <is>
+          <t>依職業安全衛生法規定，應由原事業單位指定工作場所負責人，擔任統一指揮及協調工作。
+相關法規重點
+依據：《職業安全衛生法》第27條規定。
+實施方式：原事業單位以其事業交付承攬，並與承攬人、再承攬人之工作者共同作業時，應設置協議組織，並指定工作場所負責人，擔任指揮、監督及協調之工作。
+目的：防止不同單位的勞工因作業干擾、動線重疊而發生職業災害。</t>
+        </is>
+      </c>
+      <c r="I515" s="2" t="inlineStr"/>
     </row>
     <row r="516" ht="92.59999999999999" customHeight="1">
       <c r="A516" s="2" t="n">
@@ -23256,8 +23339,12 @@
       <c r="G516" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H516" s="2" t="n"/>
-      <c r="I516" s="2" t="n"/>
+      <c r="H516" s="2" t="inlineStr">
+        <is>
+          <t>Google AI 摘要未抓取到，請手動補充。</t>
+        </is>
+      </c>
+      <c r="I516" s="2" t="inlineStr"/>
     </row>
     <row r="517" ht="92.59999999999999" customHeight="1">
       <c r="A517" s="2" t="n">
@@ -23291,8 +23378,14 @@
       <c r="G517" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H517" s="2" t="n"/>
-      <c r="I517" s="2" t="n"/>
+      <c r="H517" s="2" t="inlineStr">
+        <is>
+          <t>原事業單位應設置協議組織，並指定工作場所負責人擔任指揮及協調之工作。
+根據《職業安全衛生法》第27條規定，當原事業單位與承攬人、再承攬人共同作業時，應採取設置協議組織並指定工作場所負責人等必要安全衛生管理措施。
+第27 條 - 勞動部事業單位以其事業交付承攬，並與承攬人、再承攬人之工作者共同作業時，原事業單位應採取下列必要措施： 一、設置協議組織，並指定工作場所負責人，擔任指揮、監督及協調之工作。 二、工作之連繫及調整。 三、工作場所之巡視。 四、相關承攬人安全衛生教育訓練之指導及協助。</t>
+        </is>
+      </c>
+      <c r="I517" s="2" t="inlineStr"/>
     </row>
     <row r="518" ht="92.59999999999999" customHeight="1">
       <c r="A518" s="2" t="n">
@@ -23326,8 +23419,18 @@
       <c r="G518" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H518" s="2" t="n"/>
-      <c r="I518" s="2" t="n"/>
+      <c r="H518" s="2" t="inlineStr">
+        <is>
+          <t>正確答案是調整薪資。
+在營建工程或專案管理中，「協議組織」（通常依據《職業安全衛生法》第26、27條規定，原事業單位與承攬人、再承攬人共同成立）的運作機制主要聚焦於職業安全衛生管理、共同作業之指揮協調、巡視、連繫與調整等安全管理作為。
+以下為各選項的分類與解析：
+❌ 調整薪資（不屬於）：薪資屬於承攬商內部的勞動人事管理或勞資契約範圍，並非原事業單位協議組織用來協調共同作業或約束承攬商安全行為的運作機制。
+✅ 扣款、罰款（屬於）：屬於協議組織或契約管理中，針對承攬商違反安全衛生規定時的懲罰與經濟制裁機制。
+✅ 危險作業之管制（屬於）：這是協議組織的核心功能，包含動火作業、高架作業、局限空間作業等高風險作業的許可與管制。
+✅ 停止計價或解約（屬於）：屬於最嚴格的合同約束手段，當承攬商嚴重違反安全規範且屢勸不聽時，原事業單位可採取暫停估驗計價或解除契約。</t>
+        </is>
+      </c>
+      <c r="I518" s="2" t="inlineStr"/>
     </row>
     <row r="519" ht="92.59999999999999" customHeight="1">
       <c r="A519" s="2" t="n">
@@ -23361,8 +23464,18 @@
       <c r="G519" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H519" s="2" t="n"/>
-      <c r="I519" s="2" t="n"/>
+      <c r="H519" s="2" t="inlineStr">
+        <is>
+          <t>正確答案是 (A) 體格或健康檢查。
+完整句子為：「承攬廠商之勞工於入場施工前，應要求先接受職業安全衛生教育訓練並參加勞工保險及體格或健康檢查。」
+核心法規與要求
+職業安全衛生教育訓練：勞工進場前須接受適於工作必要的安全衛生教育訓練。
+勞工保險：確認勞工已依法加保，保障工作安全與權益。
+體格或健康檢查：確認勞工身體狀況是否適合從事該項作業。
+新北勞動雲</t>
+        </is>
+      </c>
+      <c r="I519" s="2" t="inlineStr"/>
     </row>
     <row r="520" ht="92.59999999999999" customHeight="1">
       <c r="A520" s="2" t="n">
@@ -23396,8 +23509,16 @@
       <c r="G520" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H520" s="2" t="n"/>
-      <c r="I520" s="2" t="n"/>
+      <c r="H520" s="2" t="inlineStr">
+        <is>
+          <t>依職業安全衛生法施行細則第38條第3款規定，協議組織應協議之危險作業管制事項，包含「從事動火、高架、開挖、爆破、高壓電活線等危險作業之管制」。題目中的「關挖作業」為「開挖作業」之筆誤，因此上述四項（動火作業、高架作業、開挖作業、活線/高壓電活線作業）皆屬於協議組織應協議的危險作業管理範圍，若為選擇題，通常此類題目應選「以上皆是」或題目本身有誤。
+如果這是某份考題中的選項，可以告訴我該題的其他選項（如 (A)(B)(C)(D) 全貌）或正確答案為何，我來幫你詳細解析該題的判斷邏輯。
+職業安全衛生法施行細則 - 勞動部-所有條文
+職業安全衛生法施行細則 (民國115 年06 月26 日修正) 英. 第一章總則. 第1 條. 本細則依職業安全衛生法（以下簡稱本法）第五十四條規定訂定之。 第2 條. 本法第二條第一款、第六款、第十條第二項及第五十一條第一項所稱自營作業者，指獨立從事勞動或技...
+顯示全部 內容</t>
+        </is>
+      </c>
+      <c r="I520" s="2" t="inlineStr"/>
     </row>
     <row r="521" ht="108" customHeight="1">
       <c r="A521" s="2" t="n">
@@ -23431,8 +23552,18 @@
       <c r="G521" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H521" s="2" t="n"/>
-      <c r="I521" s="2" t="n"/>
+      <c r="H521" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+承攬在安全衛生法規之責任包含(A) 共同作業時原事業單位應有之作為與(B) 職業災害賠償（或補償）責任。
+依據台灣現行《職業安全衛生法》規定：
+共同作業時原事業單位之作為：依據職安法第27條，原事業單位與承攬人、再承攬人分別僱用勞工共同作業時，應採取設置協議組織、工作聯繫與調整、工作場所巡視等必要措施。
+學校安全衛生資訊網
+職業災害賠償／補償責任：依據職安法第25條，事業單位以其事業招人承攬時，承攬人就承攬部分負雇主責任；原事業單位就職業災害補償仍應與承攬人負連帶責任，若違反安衛規定致發生職災亦須負連帶賠償責任。
+國立臺灣科技大學</t>
+        </is>
+      </c>
+      <c r="I521" s="2" t="inlineStr"/>
     </row>
     <row r="522" ht="92.59999999999999" customHeight="1">
       <c r="A522" s="2" t="n">
@@ -23466,8 +23597,18 @@
       <c r="G522" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H522" s="2" t="n"/>
-      <c r="I522" s="2" t="n"/>
+      <c r="H522" s="2" t="inlineStr">
+        <is>
+          <t>以上皆是。
+根據職業安全衛生法第26條規定，事業單位以其事業之全部或一部分交付承攬時，應於事前告知該承攬人有關其：
+事業工作環境
+危害因素
+本法及有關安全衛生規定應採取之措施
+學校安全衛生資訊網
+因此，選項所提及的內容皆屬於事業單位在交付承攬時應負的事前告知義務（危害告知）。</t>
+        </is>
+      </c>
+      <c r="I522" s="2" t="inlineStr"/>
     </row>
     <row r="523" ht="92.59999999999999" customHeight="1">
       <c r="A523" s="2" t="n">
@@ -23501,8 +23642,13 @@
       <c r="G523" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H523" s="2" t="n"/>
-      <c r="I523" s="2" t="n"/>
+      <c r="H523" s="2" t="inlineStr">
+        <is>
+          <t>依職業安全衛生法第26條規定，事業單位以其事業之全部或一部分交付承攬時，應於事前告知承攬人有關其事業工作環境、危害因素，以及本法及有關安全衛生規定應採取之措施，未包括「人員薪資」。
+因此正確答案為：人員薪資。</t>
+        </is>
+      </c>
+      <c r="I523" s="2" t="inlineStr"/>
     </row>
     <row r="524" ht="92.59999999999999" customHeight="1">
       <c r="A524" s="2" t="n">
@@ -23536,8 +23682,15 @@
       <c r="G524" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H524" s="2" t="n"/>
-      <c r="I524" s="2" t="n"/>
+      <c r="H524" s="2" t="inlineStr">
+        <is>
+          <t>原事業單位對於承攬人之危害告知方式，依規定應以書面告知（或透過合約、備忘錄、協議紀錄、安全衛生日誌等任何形式之書面文件）為之。
+Quizlet 相關法規重點
+法定要求：依據《職業安全衛生法施行細則》規定，危害告知必須有明確的佐證資料，通常以書面為之或召開協商會議並作成紀錄。
+實務認定：勞動檢查時，口頭或現場告知若無相應的書面或會議紀錄佐證，無法被認定為符合事前告知義務。因此，在考試或標準答案中，應選擇以書面告知為主。</t>
+        </is>
+      </c>
+      <c r="I524" s="2" t="inlineStr"/>
     </row>
     <row r="525" ht="92.59999999999999" customHeight="1">
       <c r="A525" s="2" t="n">
@@ -23571,8 +23724,15 @@
       <c r="G525" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H525" s="2" t="n"/>
-      <c r="I525" s="2" t="n"/>
+      <c r="H525" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+答案為 (B) 原事業單位。
+法律依據
+依據職業安全衛生法第27條規定，事業單位以其事業交付承攬，並與承攬人、再承攬人之工作者共同作業時，應由 原事業單位 採取必要防範措施（如設置協議組織、工作聯繫與調整、巡視等），以防止職業災害發生。</t>
+        </is>
+      </c>
+      <c r="I525" s="2" t="inlineStr"/>
     </row>
     <row r="526" ht="92.59999999999999" customHeight="1">
       <c r="A526" s="2" t="n">
@@ -23606,8 +23766,16 @@
       <c r="G526" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H526" s="2" t="n"/>
-      <c r="I526" s="2" t="n"/>
+      <c r="H526" s="2" t="inlineStr">
+        <is>
+          <t>答案為 (D) 連帶賠償責任。
+依據《職業安全衛生法》第25條第2項規定：「原事業單位違反本法或有關安全衛生規定，致承攬人所僱勞工發生職業災害時，與承攬人負連帶賠償責任。」
+重點解析
+連帶補償責任：若原事業單位未違反安全衛生規定，僅因承攬關係，原事業單位仍須就承攬人之勞工負職業災害的「連帶補償責任」。
+連帶賠償責任：若原事業單位本身有違反職業安全衛生法或相關安全衛生規定，因而導致承攬人所僱勞工發生職災，則須加重負起「連帶賠償責任」。</t>
+        </is>
+      </c>
+      <c r="I526" s="2" t="inlineStr"/>
     </row>
     <row r="527" ht="92.59999999999999" customHeight="1">
       <c r="A527" s="2" t="n">
@@ -23641,8 +23809,17 @@
       <c r="G527" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H527" s="2" t="n"/>
-      <c r="I527" s="2" t="n"/>
+      <c r="H527" s="2" t="inlineStr">
+        <is>
+          <t>勞工保險條例未規定承攬管理有關事項。
+相關法律說明
+勞工保險條例：主要規範勞工保險的投保、保險費與保險給付等事項，並未對工作場所的「承攬作業管理」或安全衛生責任做規範。
+職業安全衛生法：明文規定事業單位交付承攬時的雇主責任、協議組織設置與共同作業安全衛生管理（如第25條至第27條）。
+勞動基準法：對事業單位招人承攬或轉包時的職業災害補償責任有所規定（如第62條及第63條）。
+職業災害勞工保護法：針對未加入勞保之職災勞工相關補助及承攬人、再承攬人與最後承攬人的職災補償連帶責任也有規範。</t>
+        </is>
+      </c>
+      <c r="I527" s="2" t="inlineStr"/>
     </row>
     <row r="528" ht="123.45" customHeight="1">
       <c r="A528" s="2" t="n">
@@ -23676,8 +23853,19 @@
       <c r="G528" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H528" s="2" t="n"/>
-      <c r="I528" s="2" t="n"/>
+      <c r="H528" s="2" t="inlineStr">
+        <is>
+          <t>正確的敘述為：原事業單位交付廠商承攬，如不幸發生承攬廠商所僱勞工墜落致死職業災害，原事業單位應與承攬廠商負連帶補償及賠償責任。
+相關法律依據與說明
+連帶責任：依據《勞動基準法》第25條規定，事業單位以其事業招人承攬時，原事業單位就職業災害補償應與承攬人負連帶責任。
+共同作業與安全衛生責任：若原事業單位與承攬人共同作業，原事業單位亦負有防止職業災害的指揮、協調與協議組織設置義務。
+sf-personalinjurylawyer.com 請問您是否需要了解更多關於職業安全衛生法或是承攬管理的其他相關規定呢？
+sf-personalinjurylawyer.com
+外包商勞工發生職業災害，原事業單位、承攬人 - 車禍事故專業律師
+2026年6月30日 — 此外，第18條更規定，當原事業單位與承攬人、再承攬人分別僱用之勞工於同一工作場所共同作業時，原事業單位應設置協議組織，指定工作場所負責人，負責工作協調、危害防止、工作場所巡視、安全衛生教育指導及其他防止職業災害之必要事項。</t>
+        </is>
+      </c>
+      <c r="I528" s="2" t="inlineStr"/>
     </row>
     <row r="529" ht="92.59999999999999" customHeight="1">
       <c r="A529" s="2" t="n">
@@ -23711,8 +23899,13 @@
       <c r="G529" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H529" s="2" t="n"/>
-      <c r="I529" s="2" t="n"/>
+      <c r="H529" s="2" t="inlineStr">
+        <is>
+          <t>事業單位與承攬人、再承攬人所選用之勞工於同一期間、同一工作場所從事工作，稱為共同作業。
+依據《職業安全衛生法施行細則》第37條規定，共同作業係指事業單位與承攬人、再承攬人之工作者，於「同一期間」及「同一工作場所」從事工作。此時原事業單位須採取設置協議組織、工作聯繫與調整等必要安全衛生措施，以防止職業災害發生。</t>
+        </is>
+      </c>
+      <c r="I529" s="2" t="inlineStr"/>
     </row>
     <row r="530" ht="108" customHeight="1">
       <c r="A530" s="2" t="n">
@@ -23746,8 +23939,18 @@
       <c r="G530" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H530" s="2" t="n"/>
-      <c r="I530" s="2" t="n"/>
+      <c r="H530" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+職業安全衛生法所稱之共同作業為：事業單位與承攬人、再承攬人所雇用之勞工於同一時間、同一工作場所從事工作。
+共同作業重點解析
+法規定義：依據《職業安全衛生法施行細則》第37條規定，共同作業係指原事業單位、承攬人或再承攬人之工作者，在同一期間且在同一工作場所中從事工作。
+選項對照：
+事業單位與承攬人、再承攬人所雇用之勞工於同一時間、同一工作場所從事工作：正確，符合法規對共同作業的定義。
+其餘選項（僅於完工後驗收、空地無相互打擾、各自獨立作業且無危害相關聯）因無時間與空間上的重疊交錯及危害相關性，不構成共同作業。</t>
+        </is>
+      </c>
+      <c r="I530" s="2" t="inlineStr"/>
     </row>
     <row r="531" ht="92.59999999999999" customHeight="1">
       <c r="A531" s="2" t="n">
@@ -23781,8 +23984,13 @@
       <c r="G531" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H531" s="2" t="n"/>
-      <c r="I531" s="2" t="n"/>
+      <c r="H531" s="2" t="inlineStr">
+        <is>
+          <t>承攬人使用之機械、設備或器具係由原事業單位提供者，該機械、設備或器具應由原事業單位實施定期檢查及重點檢查。
+根據《職業安全衛生管理辦法》第84條規定，事業單位將事業交付承攬或再承攬時，若機具是由原事業單位所提供，原則上即應由原事業單位負擔該機械、設備或器具的定期檢查與重點檢查責任（必要時得由承攬人或再承攬人會同實施，或具備能力的承攬人以書面約定辦理）。</t>
+        </is>
+      </c>
+      <c r="I531" s="2" t="inlineStr"/>
     </row>
     <row r="532" ht="92.59999999999999" customHeight="1">
       <c r="A532" s="2" t="n">
@@ -23816,8 +24024,18 @@
       <c r="G532" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H532" s="2" t="n"/>
-      <c r="I532" s="2" t="n"/>
+      <c r="H532" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+承攬人發生職業災害時，可能產生的責任是前三者都有可能。
+責任說明
+行政責任：違反《職業安全衛生法》等相關規定時，主管機關可處以罰鍰或勒令停工。
+刑事責任：若因過失或違反安全衛生規定導致勞工傷亡，負責人或相關人員可能涉犯《刑法》過失傷害、過失致死罪，或《職業安全衛生法》之刑責。
+民事責任：須負擔勞基法規定的職業災害補償責任，以及民事侵權行為損害賠償責任。
+勞資爭議專業律師</t>
+        </is>
+      </c>
+      <c r="I532" s="2" t="inlineStr"/>
     </row>
     <row r="533" ht="92.59999999999999" customHeight="1">
       <c r="A533" s="2" t="n">
@@ -23851,8 +24069,15 @@
       <c r="G533" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H533" s="2" t="n"/>
-      <c r="I533" s="2" t="n"/>
+      <c r="H533" s="2" t="inlineStr">
+        <is>
+          <t>根據台灣的《職業安全衛生法》及相關安全管理實務規定，正確答案是：原事業單位。
+核心原因
+指揮協調責任：當原事業單位將工程交付承攬時，若同一工作場所有多家廠商共同作業，原事業單位負有設置協議組織、指揮、協調及巡視等共同職業災害防止責任。
+主導角色：為了提升所有承攬人的綜合管理實效，「安全施工循環」（如每日開工前的工具箱會議、危害告知、點檢等）必須由原事業單位來主導、推動與監督，承攬人及再承攬人則負責配合執行。</t>
+        </is>
+      </c>
+      <c r="I533" s="2" t="inlineStr"/>
     </row>
     <row r="534" ht="108" customHeight="1">
       <c r="A534" s="2" t="n">
@@ -23886,8 +24111,21 @@
       <c r="G534" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H534" s="2" t="n"/>
-      <c r="I534" s="2" t="n"/>
+      <c r="H534" s="2" t="inlineStr">
+        <is>
+          <t>正確答案是：須以書面或電子文件或召開協商會議並作成紀錄為之。
+重點解析
+正確做法：危害告知不能只用講的（口頭無效），依規定必須透過書面、電子文件，或是召開協商會議並作成紀錄來辦理。
+再承攬規定：承攬人如果把全部或部分工作交給別人（再承攬）時，一樣要負起危害告知的責任，不能免除。
+不得替代：安全承諾書是承攬人對安全衛生的承諾，不能替代事業單位或承攬人應盡的危害告知義務。
+學校安全衛生資訊網 想不想順便看這題的相關法條（職業安全衛生法第26條），或者需要更多職安乙/甲級的歷屆考題解析？
+學校安全衛生資訊網
+承攬管理 - 學校安全衛生資訊網
+▫ 承攬人就其承攬之全部或一部分交付再. 承攬時，承攬人亦應依前項規定告知再 ... 事業之全部或一部分交付承攬時，即應負危害告知之. 責任。 ▫ 以其事業交付承攬 ...
+顯示全部 內容</t>
+        </is>
+      </c>
+      <c r="I534" s="2" t="inlineStr"/>
     </row>
     <row r="535" ht="108" customHeight="1">
       <c r="A535" s="2" t="n">
@@ -23921,8 +24159,19 @@
       <c r="G535" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H535" s="2" t="n"/>
-      <c r="I535" s="2" t="n"/>
+      <c r="H535" s="2" t="inlineStr">
+        <is>
+          <t>依據職業安全衛生法第27條規定，敘述錯誤的選項為：指定承攬工程金額最多之承攬人為工作場所負責人。
+正確法規解析
+錯誤原因：依職業安全衛生法第27條第1項第1款規定，原事業單位應「設置協議組織，並指定工作場所負責人，擔任指揮、監督及協調之工作」，而不是依承攬工程金額多寡來指定。
+其它正確選項（皆為法規明定之必要措施）：
+工作之聯繫及調整
+工作場所之巡視
+相關承攬人之安全衛生教育之指導及協助（或安全衛生教育訓練之指導及協助）
+第27 條 - 勞動部查詢系統每月週期更新，如需查詢最新資料，請點閱「最新動態」。 法規名稱：. 職業安全衛生法 (民國114 年12 月19 日修正) 英. 第27 條. 事業單位以其事業交付承攬，並與承攬人、再承攬人之工作者共同作業時，原事業單位應採取下列必要措施： 一、設置協... 內容</t>
+        </is>
+      </c>
+      <c r="I535" s="2" t="inlineStr"/>
     </row>
     <row r="536" ht="108" customHeight="1">
       <c r="A536" s="2" t="n">
@@ -23956,8 +24205,16 @@
       <c r="G536" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H536" s="2" t="n"/>
-      <c r="I536" s="2" t="n"/>
+      <c r="H536" s="2" t="inlineStr">
+        <is>
+          <t>錯誤的敘述為：「屬承攬人之設備，原事業單位不能管制」。
+解析說明
+依據《職業安全衛生法》及相關承攬管理規定，事業單位以其事業交付承攬並與承攬人共同作業時，對於工作場所中有關承攬人所使用之機械、設備或器具（包含屬承攬人之設備），原事業單位負有指揮、監督、協調及採取必要安全衛生防護措施之責任，並非不能管制。因此，選項「屬承攬人之設備，原事業單位不能管制」是錯誤的敘述。
+職業安全衛生法第27 條- 2026 最新全國法規資料庫 - .事業單位以其事業交付承攬，並與承攬人、再承攬人之工作者共同作業時，原事業單位應採取下列必要措施： 一、設置協議組織，並指定工作場所負責人，擔任指揮、監督及協調之工作。 二、工作之連繫及調整。
+顯示全部 內容</t>
+        </is>
+      </c>
+      <c r="I536" s="2" t="inlineStr"/>
     </row>
     <row r="537" ht="92.59999999999999" customHeight="1">
       <c r="A537" s="2" t="n">
@@ -23991,8 +24248,22 @@
       <c r="G537" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H537" s="2" t="n"/>
-      <c r="I537" s="2" t="n"/>
+      <c r="H537" s="2" t="inlineStr">
+        <is>
+          <t>依職業安全衛生管理辦法第12-5條規定，非屬承攬管理計畫相關執行紀錄應登載之內容為職業安全衛生政策。
+承攬管理計畫規定解析
+依據法規，承攬管理計畫應登載與執行的事項包含：
+承攬人之安全衛生管理能力
+職業災害與事故通報（即職業災害通報）
+危險作業管制
+教育訓練
+進場管制
+緊急應變
+安全衛生績效評估
+而職業安全衛生政策係屬於雇主整體職業安全衛生管理目標與方針（參照同辦法第12條），並非直接作為「承攬管理計畫」執行紀錄應登載之特定項目。</t>
+        </is>
+      </c>
+      <c r="I537" s="2" t="inlineStr"/>
     </row>
     <row r="538" ht="92.59999999999999" customHeight="1">
       <c r="A538" s="2" t="n">
@@ -24026,8 +24297,21 @@
       <c r="G538" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H538" s="2" t="n"/>
-      <c r="I538" s="2" t="n"/>
+      <c r="H538" s="2" t="inlineStr">
+        <is>
+          <t>受害勞工可以向原事業單位請求 民事賠償。
+Quizlet
+原因解析
+民事賠償責任：依據《職業安全衛生法》第26條規定，原事業單位將工作場所交付承攬時，有義務將工作場所的危害因素告知承攬人。若因未盡告知義務而導致承攬人之勞工發生職業災害，原事業單位違反保護他人之法律（具過失），受害勞工或其家屬可依《民法》侵權行為規定向原事業單位請求民事損害賠償。
+其他選項差異：
+職業災害補償：通常由直接雇主（承攬人）負擔勞基法上的職災補償責任。
+勞工保險給付：向勞動部勞工保險局申請，非向原事業單位請求。
+國家賠償：適用於公務員違法侵害人民權利，本題原事業單位若為一般企業或私人單位則不適用。
+您可以參考 營造業務主管參考練習題 獲取更多相關考題與解析。
+Quizlet</t>
+        </is>
+      </c>
+      <c r="I538" s="2" t="inlineStr"/>
     </row>
     <row r="539" ht="92.59999999999999" customHeight="1">
       <c r="A539" s="2" t="n">
@@ -24061,8 +24345,14 @@
       <c r="G539" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H539" s="2" t="n"/>
-      <c r="I539" s="2" t="n"/>
+      <c r="H539" s="2" t="inlineStr">
+        <is>
+          <t>分包商篩選屬承攬管理中之 (A) 作業前管理。
+在三階段承攬管理項目中，作業前管理包含發包前的管理（如分包商篩選與建置三級管理機制）及進場前的準備作業。
+臺中市總工業會</t>
+        </is>
+      </c>
+      <c r="I539" s="2" t="inlineStr"/>
     </row>
     <row r="540" ht="92.59999999999999" customHeight="1">
       <c r="A540" s="2" t="n">
@@ -24096,8 +24386,13 @@
       <c r="G540" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H540" s="2" t="n"/>
-      <c r="I540" s="2" t="n"/>
+      <c r="H540" s="2" t="inlineStr">
+        <is>
+          <t>每日作業前預知危險活動屬承攬管理中之作業中管理（施工安全循環的一部分）。
+學校安全衛生資訊網</t>
+        </is>
+      </c>
+      <c r="I540" s="2" t="inlineStr"/>
     </row>
     <row r="541" ht="92.59999999999999" customHeight="1">
       <c r="A541" s="2" t="n">
@@ -24131,8 +24426,14 @@
       <c r="G541" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H541" s="2" t="n"/>
-      <c r="I541" s="2" t="n"/>
+      <c r="H541" s="2" t="inlineStr">
+        <is>
+          <t>承攬作業完成後之離場管理屬承攬管理中之作業後管理。
+依據相關安全衛生與承攬管理技術指引，承攬管理通常劃分為作業前、作業中與作業後管理三大階段，其中每日人員離場管控及完工後的撤場、環境復原與離場確認，皆屬於作業後管理的範疇。
+學校安全衛生資訊網</t>
+        </is>
+      </c>
+      <c r="I541" s="2" t="inlineStr"/>
     </row>
     <row r="542" ht="108" customHeight="1">
       <c r="A542" s="2" t="n">

--- a/salf/丙種職業安全衛生業務主管題庫.xlsx
+++ b/salf/丙種職業安全衛生業務主管題庫.xlsx
@@ -24467,8 +24467,18 @@
       <c r="G542" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H542" s="2" t="n"/>
-      <c r="I542" s="2" t="n"/>
+      <c r="H542" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+正確答案為：承攬人履約過程出現重大瑕疵，無法繼續履行契約時。
+選項解析
+承攬人履約過程出現重大瑕疵，無法繼續履行契約時：屬於契約根本無法履行或無法補救改善的嚴重狀況，因此必須終止或解除契約並令其退場。
+發生虛驚事故時：虛驚事故（Near Miss）是指未造成人員傷亡、疾病或財物損失的異常事件，通常作為改善安全防護與預防災害的警訊，而非直接退場之時機。
+安全衛生缺失計點達罰款上限額度時：通常依合約規定會先進行罰款、限期改善或停工，未必直接達到「無法改善必須退場」的絕對條件（視各事業單位內規而定，但相較於C選項的根本無法履行，C更符合標準答案）。
+分項工程作業計畫於危險性工作場所審查時未通過：審查未通過可以針對計畫書內容進行修正、補件後重新送審，屬於可以改善的階段。</t>
+        </is>
+      </c>
+      <c r="I542" s="2" t="inlineStr"/>
     </row>
     <row r="543" ht="92.59999999999999" customHeight="1">
       <c r="A543" s="2" t="n">
@@ -24502,8 +24512,18 @@
       <c r="G543" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H543" s="2" t="n"/>
-      <c r="I543" s="2" t="n"/>
+      <c r="H543" s="2" t="inlineStr">
+        <is>
+          <t>敘述不正確的選項是：屬再承攬人之勞工，與原事業單位無關。
+解析
+不正確的敘述 (A)：屬再承攬人之勞工，與原事業單位無關。當原事業單位與承攬人、再承攬人分別僱用勞工在同一工作場所共同作業時，原事業單位依法負有指揮、協調、管制及防止職業災害的責任，不能認為與原事業單位無關。
+新北市政府電子法規查詢系統 正確的敘述：
+(B) 原事業單位應負起管制責任，對於未接受安全衛生教育訓練的勞工不得准其進入工作場所。
+(C) 再承攬人未讓勞工接受訓練即進場作業，其雇主確實違反了職業安全衛生法相關規定。
+(D) 原事業單位在共同作業時有義務與責任協助或要求承攬與再承攬人之勞工符合相關勞工安全衛生法令。</t>
+        </is>
+      </c>
+      <c r="I543" s="2" t="inlineStr"/>
     </row>
     <row r="544" ht="92.59999999999999" customHeight="1">
       <c r="A544" s="2" t="n">
@@ -24537,8 +24557,22 @@
       <c r="G544" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H544" s="2" t="n"/>
-      <c r="I544" s="2" t="n"/>
+      <c r="H544" s="2" t="inlineStr">
+        <is>
+          <t>不屬承攬關係之特徵為：(A) 只負責出工，不負責損益。
+承攬關係的真正特徵
+為損益計算對象：承攬人自負盈虧，提供工作成果以獲取報酬。
+具備雇主性質：承攬人對其雇用之勞工具備雇主地位。
+工作不受約束：工作指派與執行方法不受定作人指揮拘束。
+獨立營運自主：有獨立的營業主體性與自主權。
+僅「負責出工、不負責損益」屬於僱傭或單純「僱工」型態，不符合承攬。
+sdd.nat.gov.tw 參考勞動部。
+需要我補充承攬與僱傭在職安法上的責任區別嗎？
+.下列敘述中，何者不屬承攬關係之特徵？(A)只負責出工
+2018年9月30日 — 7.下列敘述中，何者不屬承攬關係之特徵？(A)只負責出工，不負責損益(B) 承攬人具備「雇主之特性」(C)工作指派不受他人所約束(D)有獨立營運之自 主權。 # ...</t>
+        </is>
+      </c>
+      <c r="I544" s="2" t="inlineStr"/>
     </row>
     <row r="545" ht="92.59999999999999" customHeight="1">
       <c r="A545" s="2" t="n">
@@ -24572,8 +24606,12 @@
       <c r="G545" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H545" s="2" t="n"/>
-      <c r="I545" s="2" t="n"/>
+      <c r="H545" s="2" t="inlineStr">
+        <is>
+          <t>Google AI 摘要未抓取到，請手動補充。</t>
+        </is>
+      </c>
+      <c r="I545" s="2" t="inlineStr"/>
     </row>
     <row r="546" ht="92.59999999999999" customHeight="1">
       <c r="A546" s="2" t="n">
@@ -24607,8 +24645,17 @@
       <c r="G546" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H546" s="2" t="n"/>
-      <c r="I546" s="2" t="n"/>
+      <c r="H546" s="2" t="inlineStr">
+        <is>
+          <t>使用權的移轉不正確的選項是採購狹義的意義。
+觀念解析
+採購狹義的意義：指以購買的方式取得物品的所有權，屬於所有權的移轉，而非單純的使用權移轉。
+採購廣義的意義：除了購買所有權外，也包含取得物品的使用權（如租賃、借貸等）。
+租賃：支付租金來取得他人物品的使用權。
+徵收：政府依法取得私有土地之所有權或他項權利，在職安主管與採購管理題庫中常被歸類在廣義採購或使用權／權利取得的範疇。</t>
+        </is>
+      </c>
+      <c r="I546" s="2" t="inlineStr"/>
     </row>
     <row r="547" ht="92.59999999999999" customHeight="1">
       <c r="A547" s="2" t="n">
@@ -24642,8 +24689,21 @@
       <c r="G547" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H547" s="2" t="n"/>
-      <c r="I547" s="2" t="n"/>
+      <c r="H547" s="2" t="inlineStr">
+        <is>
+          <t>3 年以上 是最符合現行法規邏輯的選項。
+在台灣的法規實務中，採購管理記錄與文件的保存年限通常有以下規定：
+政府採購與檔案法規：過去《採購文件保存作業準則》規定未達巨額之採購文件保存期限至少為 3年；現行依《檔案法》及各機關共通性檔案保存年限基準，一般採購管理與契約文件之定期保存年限也多設定在 3年、5年、10年或15年以上。
+法務部主管法規查詢系統 商業與稅法會計憑證：若採購紀錄涉及會計憑證（如發票、收據、合約），依《商業會計法》與稅法規定，至少需保存 5年以上；會計帳簿則需保存 10年以上。
+財政部稅務入口網
+因此不論是哪一種採購管理紀錄，法定或實務上的保存期限基本上都要求在 3年以上（通常為 3、5 或 10 年）。
+請問這題是出自哪一個特定證照或考試（例如：採購專業人員、企業內部稽核、ISO認證、或是商業檢定）的題庫嗎？如果能提供考試類別，我可以幫您查出該官方教材內定義的精確標準答案！
+採購文件保存作業準則第5 條- 2026 最新全國法規資料庫 - 採購文件之保存期限如下，機關(構) 並得視需要延長之： 一、未達巨額或為轉售或供製造成品以供轉售之採購，自驗收之日起三年。 二、前款以外之採購，自驗收之日起五年。 三 ...
+顯示全部
+AI 回覆可能有誤。如需法律建議，請諮詢專業人士。 瞭解詳情</t>
+        </is>
+      </c>
+      <c r="I547" s="2" t="inlineStr"/>
     </row>
     <row r="548" ht="108" customHeight="1">
       <c r="A548" s="2" t="n">
@@ -24677,8 +24737,16 @@
       <c r="G548" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H548" s="2" t="n"/>
-      <c r="I548" s="2" t="n"/>
+      <c r="H548" s="2" t="inlineStr">
+        <is>
+          <t>敘述有誤的是：「安全衛生為施工廠商應自行注意事項，業主單位無權介入」（選項 D）。
+原因說明
+業主有責與權限：在職業安全衛生法規與承攬管理規範中，業主（事業單位）對於委外或工程採購負有告知、協調、指導及監督的責任，並非「無權介入」。
+正確做法：業主單位不僅有權利也有義務在契約中規範安全衛生要求、監督施工廠商執行，並落實安全衛生費用的編列與驗收。
+國立臺東專科學校</t>
+        </is>
+      </c>
+      <c r="I548" s="2" t="inlineStr"/>
     </row>
     <row r="549" ht="92.59999999999999" customHeight="1">
       <c r="A549" s="2" t="n">
@@ -24712,8 +24780,16 @@
       <c r="G549" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H549" s="2" t="n"/>
-      <c r="I549" s="2" t="n"/>
+      <c r="H549" s="2" t="inlineStr">
+        <is>
+          <t>採購管理的正確答案是 以上皆是（D）。
+在職業安全衛生管理（例如業務主管訓練課程）中，採購管理範疇包含：
+採購管理：設備、原料、機械等採購時的安全衛生管制。
+變更管理：製程、設備、原料或作業程序變更時的風險評估與預防。
+修繕管理：廠房、機械、設備維修與修繕作業的安全規範與監督。</t>
+        </is>
+      </c>
+      <c r="I549" s="2" t="inlineStr"/>
     </row>
     <row r="550" ht="92.59999999999999" customHeight="1">
       <c r="A550" s="2" t="n">
@@ -24747,8 +24823,15 @@
       <c r="G550" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H550" s="2" t="n"/>
-      <c r="I550" s="2" t="n"/>
+      <c r="H550" s="2" t="inlineStr">
+        <is>
+          <t>技術、服務、工程發包屬於無形物品（勞務與工程無形之委外性質）。
+採購類型說明
+無形物品：在職業安全衛生與採購管理分類中，技術服務、顧問諮詢、專業服務及工程發包等均被歸類為無形服務或無形勞務（非直接購買有形貨品設備）。
+選項對應：依據相關職業安全衛生業務主管與採購管理題庫標準答案，此題正解為 (B) 無形物品。</t>
+        </is>
+      </c>
+      <c r="I550" s="2" t="inlineStr"/>
     </row>
     <row r="551" ht="92.59999999999999" customHeight="1">
       <c r="A551" s="2" t="n">
@@ -24782,8 +24865,17 @@
       <c r="G551" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H551" s="2" t="n"/>
-      <c r="I551" s="2" t="n"/>
+      <c r="H551" s="2" t="inlineStr">
+        <is>
+          <t>這題的答案是 以上皆是。
+為什麼是「以上皆是」？
+要同時發揮採購效益、降低經營風險，並落實品質與安衛管理，企業必須將管理思維貫穿於整個供應鏈流程中，這三個選項缺一不可：
+採購過程：從供應商的評選、合約談判到交期管理，健全的過程能確保交易符合法令規範（如勞安法規），防範舞弊與違約風險。
+採購資訊：明確且透明的資訊（如產品規格、安全資料表 SDS、品質標準）是溝通的基礎。資訊錯誤會直接導致買錯東西或違反安衛標準。
+所購產品之查證：進料檢驗與查證是最後一道防線。確保到貨的成品或原料符合預期的品質與安全衛生標準，避免劣質品流入生產線引發職業災害或商譽受損。</t>
+        </is>
+      </c>
+      <c r="I551" s="2" t="inlineStr"/>
     </row>
     <row r="552" ht="92.59999999999999" customHeight="1">
       <c r="A552" s="2" t="n">
@@ -24817,8 +24909,16 @@
       <c r="G552" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H552" s="2" t="n"/>
-      <c r="I552" s="2" t="n"/>
+      <c r="H552" s="2" t="inlineStr">
+        <is>
+          <t>答案是「以上皆是」。
+依據職業安全衛生有關法規及採購管理技術指引，事業單位在制定採購管理時，上述各項均為應包含之核心規範與流程：
+文化大學 建立、實施及維持可符合安全衛生管理制度、程序及計劃：確保採購流程有系統性能遵循。
+以契約內容要求應有符合安全衛生法規及實際需要之安全衛生具體規範：在採購與租賃契約中明確規範安全衛生要求。
+對於請購、採購及輸收等相關人員應予必要之安全衛生教育訓練：提升相關職務人員對危害辨識與安全採購的認知。</t>
+        </is>
+      </c>
+      <c r="I552" s="2" t="inlineStr"/>
     </row>
     <row r="553" ht="92.59999999999999" customHeight="1">
       <c r="A553" s="2" t="n">
@@ -24852,8 +24952,20 @@
       <c r="G553" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H553" s="2" t="n"/>
-      <c r="I553" s="2" t="n"/>
+      <c r="H553" s="2" t="inlineStr">
+        <is>
+          <t>答案是：(D) 以上皆是。
+詳細說明
+(A) 事業單位請購前，應先確認並將所需之安全衛生具體規範，作為請購、採購及驗收之依據：
+事業單位在進行工程、財物或勞務請購前，必須先評估相關的安全衛生法規與實際需求，將規格寫入契約或需求說明書中。
+(B) 對工程之施工、規劃、設計、監造等契約內容，應有防止職業災害之具體規範，並列為履約要件：
+營繕工程在發包或委託時，契約必須包含明確的防範職業災害規範，並嚴格列為履約條件。
+(C) 有關工程採購案，安全衛生項目所需之費用應有一定的比例，並要求廠商編列：
+為確保工安設施與防護落實，工程採購案中必須規劃安全衛生經費比例，要求廠商確實編列並依規定執行。
+你可以至勞動部查閱相關職業安全衛生採購管理規定。</t>
+        </is>
+      </c>
+      <c r="I553" s="2" t="inlineStr"/>
     </row>
     <row r="554" ht="108" customHeight="1">
       <c r="A554" s="2" t="n">
@@ -24887,8 +24999,17 @@
       <c r="G554" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H554" s="2" t="n"/>
-      <c r="I554" s="2" t="n"/>
+      <c r="H554" s="2" t="inlineStr">
+        <is>
+          <t>答案是 (A) 委外輔導建置職業安全衛生管理系統。
+選項解析
+委外輔導建置職業安全衛生管理系統：屬於專業顧問服務與技術支援，沒有實體商品，因此屬於 無形勞務。
+租賃機具及設備：屬於設備與器具的使用權租賃，不屬於無形勞務。
+購買安全鞋：屬於實體個人防護具商品。
+購買瓦斯：屬於實體物料與燃料商品。</t>
+        </is>
+      </c>
+      <c r="I554" s="2" t="inlineStr"/>
     </row>
     <row r="555" ht="92.59999999999999" customHeight="1">
       <c r="A555" s="2" t="n">
@@ -24922,8 +25043,12 @@
       <c r="G555" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H555" s="2" t="n"/>
-      <c r="I555" s="2" t="n"/>
+      <c r="H555" s="2" t="inlineStr">
+        <is>
+          <t>Google AI 摘要未抓取到，請手動補充。</t>
+        </is>
+      </c>
+      <c r="I555" s="2" t="inlineStr"/>
     </row>
     <row r="556" ht="92.59999999999999" customHeight="1">
       <c r="A556" s="2" t="n">
@@ -24957,8 +25082,18 @@
       <c r="G556" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H556" s="2" t="n"/>
-      <c r="I556" s="2" t="n"/>
+      <c r="H556" s="2" t="inlineStr">
+        <is>
+          <t>當災害發生時，為了減少人員傷亡，急救處置平常應作好的工作是預定罹災者送醫的醫療機構。
+以下為您解析各個選項的正確性：
+預定罹災者送醫的醫療機構（正確）：事先規劃好送醫路線與特約、鄰近醫療機構，能在災害發生時省去慌亂找醫院的時間，黃金救援時間一分一秒都不能浪費。
+將單位急救用具放置在隱密地方，以避免人員亂用（錯誤）：急救用具和藥品必須放在顯眼、易取得且標示明確的地方，不能藏起來，否則緊急時會找不到。
+為免造成人員工作上之困擾，可不用定期實行演練（錯誤）：必須定期實施防災與急救演練，人員才能在災害發生時臨危不亂、熟練操作。
+各作業場所配置之急救人員只要有配置就好（錯誤）：急救人員不僅要依法配置，還必須取得合格證書並定期接受複訓，確保具備實質救護能力。
+為了幫助您更好地準備相關測驗，請問您這是勞安（職安）證照考試的模擬題嗎？如果是的話，我可以為您提供更多職業安全衛生急救編組的常考重點。 內容</t>
+        </is>
+      </c>
+      <c r="I556" s="2" t="inlineStr"/>
     </row>
     <row r="557" ht="92.59999999999999" customHeight="1">
       <c r="A557" s="2" t="n">
@@ -24992,8 +25127,12 @@
       <c r="G557" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H557" s="2" t="n"/>
-      <c r="I557" s="2" t="n"/>
+      <c r="H557" s="2" t="inlineStr">
+        <is>
+          <t>Google AI 摘要未抓取到，請手動補充。</t>
+        </is>
+      </c>
+      <c r="I557" s="2" t="inlineStr"/>
     </row>
     <row r="558" ht="92.59999999999999" customHeight="1">
       <c r="A558" s="2" t="n">
@@ -25027,8 +25166,17 @@
       <c r="G558" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H558" s="2" t="n"/>
-      <c r="I558" s="2" t="n"/>
+      <c r="H558" s="2" t="inlineStr">
+        <is>
+          <t>「應最短跑離（或應最短距離）」非緊急應變疏散路線之要求。
+緊急應變疏散路線之正確要求
+至少 2 條：事業單位至少應規劃二條疏散路線及二處集合地點。
+應事先規劃：必須於事前做好完善規劃。
+應保持通暢：應定期檢查以保持通暢可用。
+說明：疏散路線需要求至少規劃二條、保持通暢並事前規劃，但不強制要求必須是最短距離（因最短距離可能潛藏危險或災害阻礙）。</t>
+        </is>
+      </c>
+      <c r="I558" s="2" t="inlineStr"/>
     </row>
     <row r="559" ht="92.59999999999999" customHeight="1">
       <c r="A559" s="2" t="n">
@@ -25062,8 +25210,22 @@
       <c r="G559" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H559" s="2" t="n"/>
-      <c r="I559" s="2" t="n"/>
+      <c r="H559" s="2" t="inlineStr">
+        <is>
+          <t>答案是以上皆是（選項D）。
+急救的三大主要目的
+挽救生命：維持患者呼吸與血液循環，避免生命徵象消失。
+防止病情惡化：避免傷勢擴大、防止繼續失血或感染。
+使傷患及早獲得治療：在專業救護人員或醫療資源抵達前給予初步處置，減輕痛苦。
+NTNU 想了解更多關於基本急救原則或CPR步驟嗎？
+CPR壓胸步驟
+異物梗塞處理
+外傷止血方法
+.下列有關急救的目的，何者為是？(A)挽救生命(B)防止病情 ...
+2020年9月6日 — 8.下列有關急救的目的，何者為是？(A)挽救生命(B)防止病情惡化(C)使傷患及早獲得 治療(D)以上皆是。 ，包含題目內容、選項、詳解等，幫助學生提升學習 ...</t>
+        </is>
+      </c>
+      <c r="I559" s="2" t="inlineStr"/>
     </row>
     <row r="560" ht="92.59999999999999" customHeight="1">
       <c r="A560" s="2" t="n">
@@ -25097,8 +25259,22 @@
       <c r="G560" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H560" s="2" t="n"/>
-      <c r="I560" s="2" t="n"/>
+      <c r="H560" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+答案是 施予治療。
+解析
+急救的目的：主要是挽救生命、維持傷患的呼吸與血液循環功能，以及防止傷情或病情繼續惡化。
+為什麼不是「施予治療」：急救（First Aid）屬於黃金時間內的緊急救護與處置，目的是在專業醫療人員或醫療機構到達前「維持生命與防止惡化」，而不是由旁觀者或急救員對傷患進行診斷與「施予治療」。治療是醫師在醫院或專業醫療行為中進行的步驟。
+NTNU 想了解更多急救原則或CPR操作步驟嗎？
+職業安全衛生管理證照題庫練習
+下列何者不是急救的目的？ - 職業安全衛生管理證照題庫練習
+下列何者不是急救的目的？ 做記號. 244 / 472. A 維持呼吸功能; B 維持血液循環功能; C 防止傷情惡化; D 施予治療. 答案：D 說明：急救主要為了維持生命(Preserve life)， ...
+顯示全部
+AI 回覆可能有誤。這項資訊僅供參考，如需醫療建議或診斷，請諮詢專業人士。 瞭解詳情</t>
+        </is>
+      </c>
+      <c r="I560" s="2" t="inlineStr"/>
     </row>
     <row r="561" ht="92.59999999999999" customHeight="1">
       <c r="A561" s="2" t="n">
@@ -25132,8 +25308,14 @@
       <c r="G561" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H561" s="2" t="n"/>
-      <c r="I561" s="2" t="n"/>
+      <c r="H561" s="2" t="inlineStr">
+        <is>
+          <t>答案是 (A) 災害現場證人。
+解析
+設立急救人員的主要目的是在工作場所發生事故或突發疾病時，能夠及時採取急救處理、幫助勞工維持生命以及避免不必要傷亡。擔任「災害現場證人」並非設置急救人員的職責或目的。</t>
+        </is>
+      </c>
+      <c r="I561" s="2" t="inlineStr"/>
     </row>
     <row r="562" ht="92.59999999999999" customHeight="1">
       <c r="A562" s="2" t="n">
@@ -25167,8 +25349,18 @@
       <c r="G562" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H562" s="2" t="n"/>
-      <c r="I562" s="2" t="n"/>
+      <c r="H562" s="2" t="inlineStr">
+        <is>
+          <t>正確答案是：1 人（選項 A）
+重點解析
+依據現行《勞工健康保護規則》規定：
+基本配置：每一輪班次之勞工人數應至少置 1 名合格急救人員。
+遞增規定：每一輪班次勞工人數如果超過 50 人，每增加 50 人（以此類推），就必須再增置 1 人。
+依勞工健康保護規則 - 勞動部-所有條文
+查詢系統每月週期更新，如需查詢最新資料，請點閱「最新動態」。 法規名稱：. 勞工健康保護規則 (民國115 年06 月26 日修正). 生效狀態：. ※本法規部分或全部條文尚未生效，最後生效日期：民國117 年01 月01 日 一百十五年六月二十六日修正之全文...</t>
+        </is>
+      </c>
+      <c r="I562" s="2" t="inlineStr"/>
     </row>
     <row r="563" ht="92.59999999999999" customHeight="1">
       <c r="A563" s="2" t="n">
@@ -25202,8 +25394,22 @@
       <c r="G563" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H563" s="2" t="n"/>
-      <c r="I563" s="2" t="n"/>
+      <c r="H563" s="2" t="inlineStr">
+        <is>
+          <t>日班應設置 4人。
+Quizlet
+計算方式
+依據《勞工健康保護規則》規定，每一輪班次勞工人數超過50人者，每增加50人應再增置1名急救人員。
+勞工人數 160 人：
+前 50 人：1 人
+51 至 100 人：第 2 人
+101 至 150 人：第 3 人
+151 至 160 人（超過 150 人）：第 4 人
+因此總共需要設置 4人。
+Quizlet</t>
+        </is>
+      </c>
+      <c r="I563" s="2" t="inlineStr"/>
     </row>
     <row r="564" ht="92.59999999999999" customHeight="1">
       <c r="A564" s="2" t="n">
@@ -25237,8 +25443,19 @@
       <c r="G564" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H564" s="2" t="n"/>
-      <c r="I564" s="2" t="n"/>
+      <c r="H564" s="2" t="inlineStr">
+        <is>
+          <t>依勞工健康保護規則第15條規定，急救人員不得有失聰、色盲、心臟病、兩眼裸視或矯正視力後均在0.6以下、失能及健康不良等足以妨礙急救的情形，因此選項中「高血壓」不在法規限制不得有的列舉項目中（即不包括高血壓）。
+法規重點整理
+依據《勞工健康保護規則》第15條，急救人員不得有的身體與健康不良因素包含：
+失聰（耳聾）
+色盲
+心臟病
+兩眼裸視或矯正視力後均在0.6以下
+失能及其他足以妨礙急救之健康不良情形</t>
+        </is>
+      </c>
+      <c r="I564" s="2" t="inlineStr"/>
     </row>
     <row r="565" ht="92.59999999999999" customHeight="1">
       <c r="A565" s="2" t="n">
@@ -25272,8 +25489,13 @@
       <c r="G565" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H565" s="2" t="n"/>
-      <c r="I565" s="2" t="n"/>
+      <c r="H565" s="2" t="inlineStr">
+        <is>
+          <t>急救藥品與器材應至少每 6 個月定期檢查並保持清潔。
+根據《勞工健康保護規則》規定，事業單位備置的急救藥品與器材，應置於適當固定處所及保持清潔，至少每六個月定期檢查一次；遭污染或失效的物品則應隨時更換與補充。</t>
+        </is>
+      </c>
+      <c r="I565" s="2" t="inlineStr"/>
     </row>
     <row r="566" ht="92.59999999999999" customHeight="1">
       <c r="A566" s="2" t="n">
@@ -25307,8 +25529,17 @@
       <c r="G566" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H566" s="2" t="n"/>
-      <c r="I566" s="2" t="n"/>
+      <c r="H566" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+選項中的「脈搏快而強慢慢轉快而弱」屬於中暑的徵狀。
+原因解析
+中暑徵狀：患者通常會出現皮膚乾熱與潮紅（而非濕冷）、體溫調節功能失效使體溫飆高（通常超過 40 度，選項 C 的 38 度偏低），而脈搏變化在嚴重中暑或惡化時常表現為脈搏快而強，隨後慢慢轉為快而弱。
+熱衰竭徵狀：臉色蒼白、皮膚表面濕冷、脈搏微弱等通常是熱衰竭的表現。
+考古豹</t>
+        </is>
+      </c>
+      <c r="I566" s="2" t="inlineStr"/>
     </row>
     <row r="567" ht="92.59999999999999" customHeight="1">
       <c r="A567" s="2" t="n">
@@ -25342,8 +25573,17 @@
       <c r="G567" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H567" s="2" t="n"/>
-      <c r="I567" s="2" t="n"/>
+      <c r="H567" s="2" t="inlineStr">
+        <is>
+          <t>對於發生中暑之勞工最優先的急救方法為儘快有效降溫。
+中暑急救原則
+儘快降溫：迅速降低患者核心體溫是決定預後的關鍵。
+移至陰涼：將勞工移至陰涼、通風良好的地方。
+鬆脫衣物：移除不必要的外衣以協助散熱。
+www.hpa.gov.tw</t>
+        </is>
+      </c>
+      <c r="I567" s="2" t="inlineStr"/>
     </row>
     <row r="568" ht="108" customHeight="1">
       <c r="A568" s="2" t="n">
@@ -25377,8 +25617,22 @@
       <c r="G568" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H568" s="2" t="n"/>
-      <c r="I568" s="2" t="n"/>
+      <c r="H568" s="2" t="inlineStr">
+        <is>
+          <t>答案是：檢討肇事原因及提出防災對策。
+解析
+屬於急救步驟：
+切掉電源並使受災者脫離電路（第一步，確保救援安全）。
+將患者送到通風良好的地方，解開緊束的衣物，使患者仰臥，必要時實施急救（如 CPR）。
+送醫治療（後續醫療處置）。
+不屬於急救步驟：
+「檢討肇事原因及提出防災對策」屬於事後的工安檢討與預防措施，不屬於當下對傷患執行的「急救」步驟。
+yamol.tw
+17.下列何者不屬於電擊傷害的急救步驟?(A)切掉電源並使罹災 ...
+2018年10月1日 — 901. () 下列何者不屬於電擊傷害的急救步驟？ (A)切掉電源並使罹災者 脫離電路 (B)檢討肇事原因及提 出防災對策 (C)將患者送到通風良 好的地方，解開緊 束的衣物，使患者 仰臥，必要時實施 急救 (D)送醫治療. #2165106 · 17.下列何... 內容</t>
+        </is>
+      </c>
+      <c r="I568" s="2" t="inlineStr"/>
     </row>
     <row r="569" ht="92.59999999999999" customHeight="1">
       <c r="A569" s="2" t="n">
@@ -25412,8 +25666,18 @@
       <c r="G569" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H569" s="2" t="n"/>
-      <c r="I569" s="2" t="n"/>
+      <c r="H569" s="2" t="inlineStr">
+        <is>
+          <t>民眾版簡易 CPR 口訣「叫叫壓」的主要施作內容不包括人工呼吸。
+說明
+叫：檢查患者意識（拍打、呼叫）。
+叫：大聲呼救、撥打 119 求援並取得 AED。
+壓：持續進行胸部按壓。
+簡易版（壓胸為主）鼓勵民眾第一時間持續壓胸，不強制要求非專業民眾做人工呼吸。
+www.nhi.gov.tw</t>
+        </is>
+      </c>
+      <c r="I569" s="2" t="inlineStr"/>
     </row>
     <row r="570" ht="92.59999999999999" customHeight="1">
       <c r="A570" s="2" t="n">
@@ -25447,8 +25711,19 @@
       <c r="G570" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H570" s="2" t="n"/>
-      <c r="I570" s="2" t="n"/>
+      <c r="H570" s="2" t="inlineStr">
+        <is>
+          <t>「叫叫 CAB」中的第 1 個「叫」是確認患者的意識及呼吸。
+叫叫 CAB 步驟說明
+第 1 個叫：確認患者的意識及呼吸。
+第 2 個叫：求救（大聲呼救並指定旁人打 119、拿 AED）。
+C：胸部按壓（Compressions）。
+A：暢通呼吸道（Airway）。
+B：人工呼吸（Breathing）。
+元氣網</t>
+        </is>
+      </c>
+      <c r="I570" s="2" t="inlineStr"/>
     </row>
     <row r="571" ht="92.59999999999999" customHeight="1">
       <c r="A571" s="2" t="n">
@@ -25482,8 +25757,19 @@
       <c r="G571" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H571" s="2" t="n"/>
-      <c r="I571" s="2" t="n"/>
+      <c r="H571" s="2" t="inlineStr">
+        <is>
+          <t>急救「叫叫 CAB」口訣中的第 2 個「叫」為求救。
+叫叫 CAB 順序解析
+第 1 個叫：確認患者意識與呼吸
+第 2 個叫：求救（撥打 119、尋求旁人協助並取得 AED）
+C：胸部按壓（Compressions）
+A：暢通呼吸道（Airway）
+B：人工呼吸（Breathing）
+Hello 醫師</t>
+        </is>
+      </c>
+      <c r="I571" s="2" t="inlineStr"/>
     </row>
     <row r="572" ht="92.59999999999999" customHeight="1">
       <c r="A572" s="2" t="n">
@@ -25517,8 +25803,20 @@
       <c r="G572" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H572" s="2" t="n"/>
-      <c r="I572" s="2" t="n"/>
+      <c r="H572" s="2" t="inlineStr">
+        <is>
+          <t>急救叫叫 CAB 中的 C 為胸部按壓（Compressions）。
+叫叫 CABD 流程說明
+第 1 個叫：確認患者有無意識與呼吸。
+第 2 個叫：向旁人求救或撥打 119、取得 AED。
+C（Compressions）：胸部按壓。
+A（Airway）：暢通呼吸道。
+B（Breathing）：人工呼吸。
+D（Defibrillation）：使用 AED 去顫。
+凱樂斯AED</t>
+        </is>
+      </c>
+      <c r="I572" s="2" t="inlineStr"/>
     </row>
     <row r="573" ht="92.59999999999999" customHeight="1">
       <c r="A573" s="2" t="n">
@@ -25552,8 +25850,19 @@
       <c r="G573" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H573" s="2" t="n"/>
-      <c r="I573" s="2" t="n"/>
+      <c r="H573" s="2" t="inlineStr">
+        <is>
+          <t>急救口訣「叫叫 CAB」中的 A 代表的是暢通呼吸道（Airway）。
+叫叫 CAB 流程簡介
+叫（第一個叫）：確認患者意識與呼吸。
+叫（第二個叫）：大聲求救並撥打 119、取得 AED。
+C（Compressions）：胸部按壓。
+A（Airway）：暢通呼吸道（如壓額抬下巴）。
+B（Breathing）：人工呼吸。
+Hello 醫師</t>
+        </is>
+      </c>
+      <c r="I573" s="2" t="inlineStr"/>
     </row>
     <row r="574" ht="92.59999999999999" customHeight="1">
       <c r="A574" s="2" t="n">
@@ -25587,8 +25896,19 @@
       <c r="G574" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H574" s="2" t="n"/>
-      <c r="I574" s="2" t="n"/>
+      <c r="H574" s="2" t="inlineStr">
+        <is>
+          <t>急救口訣「叫叫 CAB」中的 B 指的是 進行人工呼吸（Breathing）。
+臺灣慧行志工救生游泳協會 叫叫 CAB 流程重點
+叫：確認患者意識與呼吸。
+叫：大聲求救、撥打 119 並取得 AED。
+C (Compressions)：胸部按壓（建立血液循環）。
+A (Airway)：暢通呼吸道。
+B (Breathing)：進行人工呼吸（給予 2 次吹氣）。
+思傑夢想AED</t>
+        </is>
+      </c>
+      <c r="I574" s="2" t="inlineStr"/>
     </row>
     <row r="575" ht="92.59999999999999" customHeight="1">
       <c r="A575" s="2" t="n">
@@ -25622,8 +25942,20 @@
       <c r="G575" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H575" s="2" t="n"/>
-      <c r="I575" s="2" t="n"/>
+      <c r="H575" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+燒傷急救之口訣為「沖脫泡蓋送」。
+燒燙傷急救五步驟
+沖：用流動的冷水沖洗傷口15至30分鐘，降低皮膚表面熱度。
+脫：在水中小心除去衣物，避免直接扯破水泡。
+泡：持續在冷水中浸泡數分鐘，以減輕疼痛。
+蓋：用乾淨或無菌的清潔布料覆蓋傷口。
+送：儘速將傷患送往醫院接受治療。
+中國醫藥大學附設醫院</t>
+        </is>
+      </c>
+      <c r="I575" s="2" t="inlineStr"/>
     </row>
     <row r="576" ht="92.59999999999999" customHeight="1">
       <c r="A576" s="2" t="n">
@@ -25657,8 +25989,24 @@
       <c r="G576" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H576" s="2" t="n"/>
-      <c r="I576" s="2" t="n"/>
+      <c r="H576" s="2" t="inlineStr">
+        <is>
+          <t>皮膚燒傷至感覺消失，屬於三級燒傷（(C)三）。
+燒傷特徵對照
+一度燒傷：表皮淺層，發紅腫脹、明顯觸痛感。
+淺二度燒傷：表皮與真皮淺層，紅腫起水泡、劇烈疼痛。
+深二度燒傷：表皮與真皮深層，白色大水泡、較不感覺疼痛（但仍有知覺）。
+三級燒傷：全層皮膚受損，焦黑硬如皮革或蒼白，神經破壞、感覺消失。
+四級燒傷：傷及肌肉、肌腱或骨骼。
+陽光社會福利基金會 關鍵應對與處理
+立即送醫：三級燒傷無法自行癒合，必須接受清創與植皮手術。
+急救口訣：沖、脫、泡、蓋、送（若皮膚焦硬緊繃或黏住，衣物不可強行脫除，直接送醫）。
+陽光社會福利基金會
+更進一步的深層分類與病理資訊可參考陽光社會福利基金會。
+如果這是真實發生的急救狀況，</t>
+        </is>
+      </c>
+      <c r="I576" s="2" t="inlineStr"/>
     </row>
     <row r="577" ht="108" customHeight="1">
       <c r="A577" s="2" t="n">
@@ -25693,8 +26041,19 @@
       <c r="G577" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H577" s="2" t="n"/>
-      <c r="I577" s="2" t="n"/>
+      <c r="H577" s="2" t="inlineStr">
+        <is>
+          <t>敘述有誤的是：「其他利害相關者非廠內員工，無須邀請其參與緊急應變之訓練及演練」（此為錯誤選項）。
+原因說明
+法規要求：依據相關職業安全衛生法規（如職業安全衛生設施規則），事業單位應定期演練緊急應變計畫，並且在必要時應邀請利害相關者參與，而非無須邀請。
+其他選項皆正確：
+緊急應變訓練與演練形式通常包含講解、沙盤推演、單元訓練及實地演習四種。
+演練與訓練確實能有效提升人員的應變能力。
+演練可用以測試計畫適用性，並確認單位、設施與人員能安全應付狀況。
+高雄市政府全球資訊網</t>
+        </is>
+      </c>
+      <c r="I577" s="2" t="inlineStr"/>
     </row>
     <row r="578" ht="92.59999999999999" customHeight="1">
       <c r="A578" s="2" t="n">
@@ -25728,8 +26087,18 @@
       <c r="G578" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H578" s="2" t="n"/>
-      <c r="I578" s="2" t="n"/>
+      <c r="H578" s="2" t="inlineStr">
+        <is>
+          <t>對於處理大量漏洩氮氣之緊急應變人員，應著 B 級防護裝備（若無高濃度皮膚危害，但有嚴重缺氧或呼吸危害時需搭配 SCBA）或依現場未知高風險選用 A 級，但在一般考試與法規題庫標準中，面對大量氣體（如窒息性氣體氮氣）大量外洩時，主要考量為防止缺氧，應使用自攜式空氣呼吸器（SCBA），若皮膚無直接劇毒或經皮吸收危害，則防護衣等級對應為 B 級（若為全面氣密未知則為 A 級）。
+氮氣危害與防護等級
+主要危害：氮氣本身無毒，但大量外洩會排擠空氣中的氧氣，造成缺氧。
+tsem.blob.core.windows.net 呼吸防護：必須配備正壓全面式自攜式空氣呼吸器（SCBA）。
+環境部主管法規共用系統 防護衣選擇：
+A 級：適用於未知濃度、具最高皮膚與呼吸危害之環境。
+B 級：適用於呼吸防護要求最高（需用 SCBA），但皮膚無顯著立即致命危害或不需氣密保護之大量氣體外洩環境。</t>
+        </is>
+      </c>
+      <c r="I578" s="2" t="inlineStr"/>
     </row>
     <row r="579" ht="108" customHeight="1">
       <c r="A579" s="2" t="n">
@@ -25763,8 +26132,19 @@
       <c r="G579" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H579" s="2" t="n"/>
-      <c r="I579" s="2" t="n"/>
+      <c r="H579" s="2" t="inlineStr">
+        <is>
+          <t>緊急應變總指揮之工作職責為「掌握各應變編組運作, 瞭解災害之發展狀況, 授權及督導各組應變」。
+工作職責解析
+正確選項：掌握各應變編組運作，瞭解災害之發展狀況，授權及督導各組應變。
+其他選項之職責歸屬：
+代表事業單位對外發佈和說明災變處理情形：通常由發言人或事業單位高階主管／公關部門負責。
+負責消防水及緊急電源之正常供應：通常由後勤支援組、營繕組或機電相關防救編組負責。
+負責現場搶救工作：通常由現場指揮官或搶救組負責執行。
+高雄市政府全球資訊網</t>
+        </is>
+      </c>
+      <c r="I579" s="2" t="inlineStr"/>
     </row>
     <row r="580" ht="108" customHeight="1">
       <c r="A580" s="2" t="n">
@@ -25798,8 +26178,19 @@
       <c r="G580" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H580" s="2" t="n"/>
-      <c r="I580" s="2" t="n"/>
+      <c r="H580" s="2" t="inlineStr">
+        <is>
+          <t>有關緊急應變組織架構及權責的敘述，「假日及夜間均有人值班，所以不須另定假日及夜間之應變組織架構」這項敘述是錯誤的。
+錯誤原因分析
+人力配置與功能不同：假日及夜間的留守值班人力通常比平日白天少，且常態值班人員的權限與專業分工無法完全取代正式的緊急應變小組。
+應變啟動機制調整：當假日或夜間發生重大突發事件時，必須有專門的「假日夜間緊急通報與召回架構」，明確規劃第一時間由誰代理指揮官、如何通知外部支援，以及如何召回其他留守或休假主管。如果沒有另定架構，容易在事故發生時陷入指揮真空。
+其他正確觀念
+應訂定應變組織各階層人員的職掌：正確。各級人員（如指揮官、安全官、各工作小組組長）必須有明確的任務分工，才不會在災時權責不清。
+應變組織各工作小組應有編組名冊：正確。名冊須包含正職與代理人，並定期更新聯絡電話，以確保災時能隨時取得聯繫。
+不同應變等級應有不同應變組織架構：正確。企業應根據災害嚴重程度（如輕微、中度、重大）啟動對應規模的應變架構，避免小事故過度動員，或大事故動員不足。</t>
+        </is>
+      </c>
+      <c r="I580" s="2" t="inlineStr"/>
     </row>
     <row r="581" ht="92.59999999999999" customHeight="1">
       <c r="A581" s="2" t="n">
@@ -25833,8 +26224,18 @@
       <c r="G581" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H581" s="2" t="n"/>
-      <c r="I581" s="2" t="n"/>
+      <c r="H581" s="2" t="inlineStr">
+        <is>
+          <t>這題的正確答案是：只要是閒置不用之場所即可。這個敘述是錯誤的。
+答案解析
+緊急應變場所（如指揮所、避難安置處所）的設置關係到救援效率與人員安全，絕不能只因為空間「閒置不用」就直接選定，必須經過嚴格的風險與功能評估。
+以下為其他正確選項的考量重點：
+考量結構安全性：場所必須能抵禦二次災害（如餘震、風災），確保內部人員與設施的安全。
+遠離危害物之危害與污染區域：必須設在安全區域（通常為冷區），避免人員遭受有毒氣體、化學品洩漏、火災或輻射等二次傷害。
+考量人員緊急疏散等問題：動線必須順暢，方便受災人員進出、傷患運送以及救援物資與車輛的調配。</t>
+        </is>
+      </c>
+      <c r="I581" s="2" t="inlineStr"/>
     </row>
     <row r="582" ht="108" customHeight="1">
       <c r="A582" s="2" t="n">
@@ -25868,8 +26269,19 @@
       <c r="G582" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H582" s="2" t="n"/>
-      <c r="I582" s="2" t="n"/>
+      <c r="H582" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+敘述有誤的是：不論分級為何，緊急應變指揮官都是同一人。
+原因說明
+指揮官會隨級別與規模調整：當緊急狀況的等級升高（例如從廠內小型災害擴大為需要外界支援的大型災害或三級災害時），應變組織與指揮層級（如現場指揮官、總指揮官或外部支援單位進駐）會依規模進行調整或權責轉移，並非「不論分級為何都由同一人擔任」。
+正確觀念：
+應依事故之損害特性及後果嚴重度進行分級。
+應依分級規劃對應的處理程序與對策。
+當災害超出自身能力無法控制時，必須迅速聯絡外界支援。</t>
+        </is>
+      </c>
+      <c r="I582" s="2" t="inlineStr"/>
     </row>
     <row r="583" ht="123.45" customHeight="1">
       <c r="A583" s="2" t="n">
@@ -25903,8 +26315,15 @@
       <c r="G583" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H583" s="2" t="n"/>
-      <c r="I583" s="2" t="n"/>
+      <c r="H583" s="2" t="inlineStr">
+        <is>
+          <t>敘述有誤的是：「選擇緊急應變計畫參與之成員以安全衛生管理人員為主，其他技術或生產部門人員可以不必納入」。
+錯誤原因說明
+正確做法：緊急應變計畫之成員選擇，除了安全衛生管理人員外，必須納入相關的技術、生產、維修、總務或各級主管等跨部門人員，因為實際現場應變需要各部門的專業知識與實務操作配合，不能僅靠安衛人員。
+其他選項：皆符合勞動部職業安全衛生署之「緊急應變措施技術指引」中關於危害辨識、資源評估及應變指引制定之正確程序與基本原則。</t>
+        </is>
+      </c>
+      <c r="I583" s="2" t="inlineStr"/>
     </row>
     <row r="584" ht="92.59999999999999" customHeight="1">
       <c r="A584" s="2" t="n">
@@ -25938,8 +26357,21 @@
       <c r="G584" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H584" s="2" t="n"/>
-      <c r="I584" s="2" t="n"/>
+      <c r="H584" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+事業單位應採取 (C) 緊急應變管理，使災害發生後得有效控制並減少損失。
+管理措施解析
+緊急應變管理：
+目的：在災害或突發事故發生時，迅速啟動應變程序、進行搶救與疏散，以有效控制災情並減少人員傷亡與財產損失。
+常見作法：規劃疏散路線、設置集合地點、定期實施防救災演練及發布事故應變資訊等。
+其他選項說明：
+風險評估：用於事前辨識危害、評估風險等級並採取預防措施。
+變更管理：用於製程、設備或作業改變時的事前審查與控制，防止因改變引發災害。
+自動檢查：由事業單位定期對機械、設備等實施自我檢查，屬於預防設備失效的手段。</t>
+        </is>
+      </c>
+      <c r="I584" s="2" t="inlineStr"/>
     </row>
     <row r="585" ht="108" customHeight="1">
       <c r="A585" s="2" t="n">
@@ -25973,8 +26405,15 @@
       <c r="G585" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H585" s="2" t="n"/>
-      <c r="I585" s="2" t="n"/>
+      <c r="H585" s="2" t="inlineStr">
+        <is>
+          <t>敘述有誤的是：「對於已由廠內自行處理完畢之事故可不通報」。
+原因說明
+法規要求：只要符合法定通報要件（如重大職業災害、一定規模以上的危害物質洩漏、火災爆炸或勞工住院等），即使在廠內初步處理完畢或控制，依據職業安全衛生法規及相關主管機關規定，仍須在法定時限內向主管機關（如勞動檢查機構）通報，不能逕自隱匿或不通報。
+正確做法：其他選項如應訂定通報流程與電話一覽表、明訂法定應通報事項、以及規劃假日與夜間的通報聯絡體系，皆為緊急應變計畫中正確且必要的規定。</t>
+        </is>
+      </c>
+      <c r="I585" s="2" t="inlineStr"/>
     </row>
     <row r="586" ht="108" customHeight="1">
       <c r="A586" s="2" t="n">
@@ -26008,8 +26447,17 @@
       <c r="G586" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H586" s="2" t="n"/>
-      <c r="I586" s="2" t="n"/>
+      <c r="H586" s="2" t="inlineStr">
+        <is>
+          <t>執行應變能力及資源評估時，敘述有誤的是「對於必要的搶救設備如成本太高可不必購置，災害發生時再向鄰廠借用」。
+事業單位應依規定自行備妥必要的緊急應變與搶救設施及器材，不能以成本過高為由而不予購置、僅依賴災時向鄰廠借用。
+應變能力與資源評估重點
+應變器材：應評估種類及數量是否充足。
+醫療救護：應評估單位內部是否有足夠的醫療救護能力。
+電力系統：應評估是否有足夠的緊急供電系統。</t>
+        </is>
+      </c>
+      <c r="I586" s="2" t="inlineStr"/>
     </row>
     <row r="587" ht="92.59999999999999" customHeight="1">
       <c r="A587" s="2" t="n">
@@ -26044,8 +26492,18 @@
       <c r="G587" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H587" s="2" t="n"/>
-      <c r="I587" s="2" t="n"/>
+      <c r="H587" s="2" t="inlineStr">
+        <is>
+          <t>有關緊急應變之程序，通報應最優先執行。
+在面對突發災害或緊急狀況時，正確的處理順序通常是先進行通報（向內部主管、相關單位或外部救援如119求救），以便儘快啟動整體救援資源與應變機制。
+各選項在程序中的特性：
+通報：最優先執行，爭取救援時間。
+成立應變小組：通常依通報後續或按既定編組啟動。
+CPR：視現場有無傷病員需要急救而定，但若以整體行政/標準應變程序考量，「通報」為首要步驟；若有人命危急，現場急救與通報亦常同步或緊接進行，但在多數安衛考古題標準答案中為通報最優先。
+調查災害原因：屬於事件結束後的復原或檢討階段，絕對是最後才執行。</t>
+        </is>
+      </c>
+      <c r="I587" s="2" t="inlineStr"/>
     </row>
     <row r="588" ht="108" customHeight="1">
       <c r="A588" s="2" t="n">
@@ -26080,8 +26538,14 @@
       <c r="G588" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H588" s="2" t="n"/>
-      <c r="I588" s="2" t="n"/>
+      <c r="H588" s="2" t="inlineStr">
+        <is>
+          <t>敘述有誤的選項為：「相關資料已保存於電腦，無須保留紙本備份」。
+原因說明
+紙本備份必要性：在緊急應變狀況發生時（如廠區斷電、網路中斷或電腦設備損壞），電腦資料可能無法順利讀取。因此，相關緊急應變資訊與配置圖等必要資料，仍須妥善保留紙本備份以供隨時查閱與應變使用，不能僅依賴電子檔。</t>
+        </is>
+      </c>
+      <c r="I588" s="2" t="inlineStr"/>
     </row>
     <row r="589" ht="108" customHeight="1">
       <c r="A589" s="2" t="n">
@@ -26115,8 +26579,15 @@
       <c r="G589" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H589" s="2" t="n"/>
-      <c r="I589" s="2" t="n"/>
+      <c r="H589" s="2" t="inlineStr">
+        <is>
+          <t>下列敘述有誤的是：「救人第一，搶救時應不顧一切全力搶救。」
+原因說明
+安全第一原則：緊急應變與搶救時，首要條件是確保自身及救援人員的安全。若環境本身存在立即危害（如未斷電、有毒氣體外洩、局限空間危害未排除且防護不足），貿然不顧一切進入救人，往往會造成救援者傷亡、擴大災害，因此「不可貿然進行」。
+其他選項（進行搶救前應先考量自身安全、感電災害應先切斷電源、局限空間應先做好個人防護與通風/救援準備）皆為正確且安全的標準應變程序。</t>
+        </is>
+      </c>
+      <c r="I589" s="2" t="inlineStr"/>
     </row>
     <row r="590" ht="108" customHeight="1">
       <c r="A590" s="2" t="n">
@@ -26150,8 +26621,15 @@
       <c r="G590" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H590" s="2" t="n"/>
-      <c r="I590" s="2" t="n"/>
+      <c r="H590" s="2" t="inlineStr">
+        <is>
+          <t>敘述有誤的選項為：「人口、道路、醫院 等客觀環境改變時，因與廠內運作無關，無須修改計畫」。
+說明
+正確觀念：當廠外周邊的客觀環境（如人口分布、周遭道路、鄰近醫院或支援單位）發生改變時，會直接影響外部支援、疏散路線及救援效率，因此必須將這些外在環境變動納入考量並檢討修正緊急應變計畫，不能以「與廠內運作無關」為由而不修改。
+其他選項（如緊急狀況發生後、設計製程等變更時、演練檢討結果確認時）皆為需要進行不定期檢討與修訂的正確時機。</t>
+        </is>
+      </c>
+      <c r="I590" s="2" t="inlineStr"/>
     </row>
     <row r="591" ht="108" customHeight="1">
       <c r="A591" s="2" t="n">
@@ -26185,8 +26663,18 @@
       <c r="G591" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H591" s="2" t="n"/>
-      <c r="I591" s="2" t="n"/>
+      <c r="H591" s="2" t="inlineStr">
+        <is>
+          <t>敘述有誤的是：「緊急應變計畫係備而不用，無須考慮人員之訓練」。
+正確觀念說明
+必須實施訓練與演練：緊急應變計畫絕非「備而不用」，為了確保在災害發生時人員能正確反應、降低損害，計畫中必須明確規範相關的教育訓練及定期應變演練。
+應包含之核心要素：
+明確辨識危害性物質及其存量。
+明確界定應變組織各階層人員的職掌。
+訂定緊急狀況之處理方法（包含指揮權移轉等）。</t>
+        </is>
+      </c>
+      <c r="I591" s="2" t="inlineStr"/>
     </row>
     <row r="592" ht="92.59999999999999" customHeight="1">
       <c r="A592" s="2" t="n">
@@ -26220,8 +26708,18 @@
       <c r="G592" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H592" s="2" t="n"/>
-      <c r="I592" s="2" t="n"/>
+      <c r="H592" s="2" t="inlineStr">
+        <is>
+          <t>答案是 (A) 臉色潮紅。
+休克常見症狀說明
+臉色蒼白：休克時因血管收縮、血液集中重要器官，患者通常會臉色蒼白或發紺，而非臉色潮紅。
+自訴寒冷，甚至發抖：因體溫調節與末梢循環不良，患者常感覺寒冷、發抖。
+噁心、嘔吐：腸胃道血流減少常引起噁心感或嘔吐。
+呼吸快而淺：身體缺氧或代償反應會使呼吸變得急促而淺快。
+榮民總醫院</t>
+        </is>
+      </c>
+      <c r="I592" s="2" t="inlineStr"/>
     </row>
     <row r="593" ht="92.59999999999999" customHeight="1">
       <c r="A593" s="2" t="n">
@@ -26255,8 +26753,20 @@
       <c r="G593" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H593" s="2" t="n"/>
-      <c r="I593" s="2" t="n"/>
+      <c r="H593" s="2" t="inlineStr">
+        <is>
+          <t>骨折急救時，衣服不可充當護木（副木）使用。
+原因說明
+護木（副木）的條件：必須具有足夠的硬度與支撐力，才能有效固定受傷的肢體、防止骨折處二次受傷。
+選項比較：
+木板、雨傘、拐杖：皆具備堅硬的長條狀結構，可以作為臨時固定的支撐物。
+衣服：屬於柔軟材質，缺乏剛性支撐，因此無法當作護木使用。
+職業安全衛生管理證照題庫練習
+骨折急救時，下列何者不可充當副木使用？
+骨折急救時，下列何者不可充當副木使用？ 做記號. 263 / 472. A 木板; B 雨傘; C 枴杖; D 衣服. 答案：D 說明：副木應為固定式支架，強度需要足夠。 答案隱藏中. 內容</t>
+        </is>
+      </c>
+      <c r="I593" s="2" t="inlineStr"/>
     </row>
     <row r="594" ht="92.59999999999999" customHeight="1">
       <c r="A594" s="2" t="n">
@@ -26290,8 +26800,18 @@
       <c r="G594" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H594" s="2" t="n"/>
-      <c r="I594" s="2" t="n"/>
+      <c r="H594" s="2" t="inlineStr">
+        <is>
+          <t>正確答案為 (C) DBCA。
+作業流程順序
+依據勞動部職業安全衛生相關指引與法規規範，緊急應變計畫之規劃與研訂步驟如下：
+D. 選擇參與計畫之成員：先指派具不同技術背景之人員組成規劃小組。
+B. 危害辨識及風險評估：確認須採取應變措施控制的危害與情境。
+C. 應變能力及資源評估：評估現有能力、裝備及後勤支援。
+A. 研訂緊急應變計畫：綜合前述評估結果正式規劃與編修計畫。</t>
+        </is>
+      </c>
+      <c r="I594" s="2" t="inlineStr"/>
     </row>
     <row r="595" ht="77.15000000000001" customHeight="1">
       <c r="A595" s="2" t="n">
@@ -26325,8 +26845,19 @@
       <c r="G595" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H595" s="2" t="n"/>
-      <c r="I595" s="2" t="n"/>
+      <c r="H595" s="2" t="inlineStr">
+        <is>
+          <t>下列何者不是自衛消防編組常用的班別名稱答案是 (B) 安全救護班。
+自衛消防編組常見班別
+滅火班：負責初期滅火、操作滅火器或室內消防栓。
+通報班（或稱通報聯絡班概念）：負責向內部人員及消防機關通報。
+避難引導班：負責引導人員安全疏散與避難。
+安全防護班 與 救護班：依規定於員工人數達50人以上時增編。
+題目中的「安全救護班」並非標準正式名稱，正確的分法為「安全防護班」與「救護班」或單獨的「救護班」。
+中華都市安全推廣協會</t>
+        </is>
+      </c>
+      <c r="I595" s="2" t="inlineStr"/>
     </row>
     <row r="596" ht="77.15000000000001" customHeight="1">
       <c r="A596" s="2" t="n">

--- a/salf/丙種職業安全衛生業務主管題庫.xlsx
+++ b/salf/丙種職業安全衛生業務主管題庫.xlsx
@@ -26891,8 +26891,19 @@
       <c r="G596" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H596" s="2" t="n"/>
-      <c r="I596" s="2" t="n"/>
+      <c r="H596" s="2" t="inlineStr">
+        <is>
+          <t>一氧化碳中毒時，不宜採取「頻繁詢問患者」（選項 C）這一項措施。
+原因說明
+不宜頻繁詢問（C）：一氧化碳中毒患者常伴隨頭痛、頭暈、意識不清或腦部缺氧，頻繁干擾或詢問患者會增加其精神與腦部負擔，應讓患者安靜休息、減少耗氧。
+正確急救措施：
+保持呼吸道暢通（A）：確保患者呼吸順暢，必要時清除口鼻異物。
+多給予保暖（B）：維持患者體溫，防止失溫。
+儘早給予吸入氧氣（D）：提供高濃度氧氣加速一氧化碳排出，降低組織缺氧傷害。
+榮民總醫院</t>
+        </is>
+      </c>
+      <c r="I596" s="2" t="inlineStr"/>
     </row>
     <row r="597" ht="92.59999999999999" customHeight="1">
       <c r="A597" s="2" t="n">
@@ -26926,8 +26937,17 @@
       <c r="G597" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H597" s="2" t="n"/>
-      <c r="I597" s="2" t="n"/>
+      <c r="H597" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+答案是 15 分鐘（選項 C）。
+說明與現今觀念
+傳統考試題庫解答：在舊有的急救考題中，通常標準答案為每隔 15 分鐘鬆開一次（或依部分題庫為 15 分鐘）。
+現代急救醫學觀念：現代戰傷與民間急救指引（如 TCCC、黑熊學院等）已不建議在送醫途中自行將止血帶定時鬆開，因為鬆開會導致再次大出血或引發嚴重併發症；一旦綁上合格的止血帶並記錄時間後，應直接送醫交由專業醫療人員處理。但在標準考試中仍以傳統選項為準。
+黑熊學院</t>
+        </is>
+      </c>
+      <c r="I597" s="2" t="inlineStr"/>
     </row>
     <row r="598" ht="77.15000000000001" customHeight="1">
       <c r="A598" s="2" t="n">
@@ -26961,8 +26981,17 @@
       <c r="G598" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H598" s="2" t="n"/>
-      <c r="I598" s="2" t="n"/>
+      <c r="H598" s="2" t="inlineStr">
+        <is>
+          <t>勞工發生一氧化碳中毒時，應立即供給氧氣呼吸。
+急救重點
+供給氧氣：高濃度氧氣能幫助加速排除體內血紅素結合的一氧化碳，減輕中毒危害。
+移至通風處：迅速將患者移到空氣清新的地方，並鬆解衣物。
+實施CPR：若患者失去意識、無呼吸心跳，應立即施以人工呼吸與心肺復甦術，並盡速撥打119送醫。
+需要了解更多一氧化碳中毒的預防方法或其他急救常識嗎？</t>
+        </is>
+      </c>
+      <c r="I598" s="2" t="inlineStr"/>
     </row>
     <row r="599" ht="77.15000000000001" customHeight="1">
       <c r="A599" s="2" t="n">
@@ -26996,8 +27025,23 @@
       <c r="G599" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H599" s="2" t="n"/>
-      <c r="I599" s="2" t="n"/>
+      <c r="H599" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+眼睛化學性傷害以流動之水沖洗時，正確的做法是由眼內角往眼外角沖洗。
+www.cych.org.tw
+正確處理方式
+沖洗方向：應從靠近鼻子的眼內角（內眥）向耳朵方向的眼外角沖洗。
+核心原因：這樣可以防止化學物質流向並汙染另一隻健康的眼睛，或積聚在淚管中。
+www.cych.org.tw
+急救重點
+持續時間：應使用大量流動的清水或生理食鹽水持續沖洗至少 20 至 30 分鐘。
+輔助動作：沖洗時應將眼皮撐開，並轉動眼球，確保化學物質完全被洗淨。
+切忌搓揉：千萬不要用手搓揉眼睛，也不要隨便使用中和劑，以免產生熱量造成二次傷害。
+恆春旅遊醫院</t>
+        </is>
+      </c>
+      <c r="I599" s="2" t="inlineStr"/>
     </row>
     <row r="600" ht="108" customHeight="1">
       <c r="A600" s="2" t="n">
@@ -27031,8 +27075,19 @@
       <c r="G600" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H600" s="2" t="n"/>
-      <c r="I600" s="2" t="n"/>
+      <c r="H600" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+「截肢不必處理，連同患者送醫」是不適當的處理方式。
+說明
+不適當的選項：(C) 截肢（斷肢）必須妥善處理，切勿直接丟棄或隨意放置，應保持清潔、以濕紗布包裹並配合正確冷藏（避免直接接觸冰塊），與患者一同送醫以爭取顯微接合手術的機會。
+適當的處理：
+控制患者傷口出血情形。
+預防與注意傷口感染。
+將斷肢以生理食鹽水濕潤的紗布包住，再放入塑膠袋中，外側可放置冰塊冷藏（避免斷肢直接接觸冰塊或浸泡在水中），連同病患一同送醫。</t>
+        </is>
+      </c>
+      <c r="I600" s="2" t="inlineStr"/>
     </row>
     <row r="601" ht="108" customHeight="1">
       <c r="A601" s="2" t="n">
@@ -27066,8 +27121,12 @@
       <c r="G601" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H601" s="2" t="n"/>
-      <c r="I601" s="2" t="n"/>
+      <c r="H601" s="2" t="inlineStr">
+        <is>
+          <t>Google AI 摘要未抓取到，請手動補充。</t>
+        </is>
+      </c>
+      <c r="I601" s="2" t="inlineStr"/>
     </row>
     <row r="602" ht="92.59999999999999" customHeight="1">
       <c r="A602" s="2" t="n">
@@ -27101,8 +27160,17 @@
       <c r="G602" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H602" s="2" t="n"/>
-      <c r="I602" s="2" t="n"/>
+      <c r="H602" s="2" t="inlineStr">
+        <is>
+          <t>在緊急應變時，事故區域之擬定，通常將指揮區設置於冷區。
+事故區域劃分說明
+冷區（安全區 / 支援區）：未受污染或已完成除污的區域。通常設置指揮站與支援設施，並應位於上風處。
+溫區（影響區 / 除污區）：熱區與冷區之間的緩衝區，主要進行人員與設備除污。
+熱區（污染區 / 禁區）：事故發生地點或直接遭受污染的危險區域，僅限配備適當防護裝備之搶救人員進入。
+消防法令查詢系統</t>
+        </is>
+      </c>
+      <c r="I602" s="2" t="inlineStr"/>
     </row>
     <row r="603" ht="92.59999999999999" customHeight="1">
       <c r="A603" s="2" t="n">
@@ -27136,8 +27204,18 @@
       <c r="G603" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H603" s="2" t="n"/>
-      <c r="I603" s="2" t="n"/>
+      <c r="H603" s="2" t="inlineStr">
+        <is>
+          <t>災害搶救後，搶救人員清洗與除污的地方設在溫區（又稱除污區或黃區）。
+消防法令查詢系統 災害現場區域劃分說明
+熱區（紅區／污染區）：危害物質濃度最高或事故發生之區域，僅允許穿著適當防護裝備的專業人員進入。
+溫區（黃區／除污區）：位於熱區與冷區之間的緩衝區域，主要功能為設立除污通道（除污走廊），供自熱區撤離的搶救人員與傷病患進行清洗與清除污染物，以防止污染擴散。
+冷區（綠區／安全區）：未受污染的安全支援區，指揮站、待命人員及多數救護處置均設於此區。
+禁區：通常為熱區的別稱或指嚴格禁止進入的危險範圍。
+新竹縣環境保護局</t>
+        </is>
+      </c>
+      <c r="I603" s="2" t="inlineStr"/>
     </row>
     <row r="604" ht="108" customHeight="1">
       <c r="A604" s="2" t="n">
@@ -27171,8 +27249,14 @@
       <c r="G604" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H604" s="2" t="n"/>
-      <c r="I604" s="2" t="n"/>
+      <c r="H604" s="2" t="inlineStr">
+        <is>
+          <t>答案為：緊急應變器材之數量及價格。
+說明
+在擬定緊急應變計畫的過程中，應著重於整體危害與風險的分析、應變能力的評估，以及相關安全與歷史資訊的檢討。而器材的「數量及價格」屬於後續資源配置、採購與預算編列的實務考量，並非在「訂定應變計畫過程」中評估的核心考慮事項。</t>
+        </is>
+      </c>
+      <c r="I604" s="2" t="inlineStr"/>
     </row>
     <row r="605" ht="108" customHeight="1">
       <c r="A605" s="2" t="n">
@@ -27206,8 +27290,16 @@
       <c r="G605" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H605" s="2" t="n"/>
-      <c r="I605" s="2" t="n"/>
+      <c r="H605" s="2" t="inlineStr">
+        <is>
+          <t>依據高架作業勞工保護措施標準規定，未設置平台、護欄等設備而已採取必要安全措施，其高度在 2 公尺 以上者稱為高架作業。
+選項正確答案為 2 公尺。
+相關高度規定重點
+無平台、護欄：高度在 2 公尺 以上。
+已設置平台、護欄：高度在 5 公尺 以上。</t>
+        </is>
+      </c>
+      <c r="I605" s="2" t="inlineStr"/>
     </row>
     <row r="606" ht="108" customHeight="1">
       <c r="A606" s="2" t="n">
@@ -27241,8 +27333,21 @@
       <c r="G606" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H606" s="2" t="n"/>
-      <c r="I606" s="2" t="n"/>
+      <c r="H606" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+依據《高架作業勞工保護措施標準》規定，已依規定設置平台、護欄等設備，並採取防止墜落之必要安全措施，其高度在 5 公尺（5公尺） 以上者稱為高架作業。因此答案為 5 公尺。
+國立臺灣師範大學－環境安全衛生中心
+(註：若「未」設置平台、護欄等設備但已採取必要安全措施，其高度在 2 公尺以上者即稱為高架作業。)
+iPEDIA 百科
+需要我幫你整理其他勞工安全衛生法規或職業安全的相關考題嗎？
+國立臺灣師範大學－環境安全衛生中心
+高架作業相關法規 - 環境安全衛生中心
+2021年8月21日 — 二、已依規定設置平台、護欄等設備，並採取防止墜落之必要安全措施，其高度在五公. 尺以上者。 前項高度之計算方式依下列規定：. 一、露天作業場所，自 ...
+顯示全部 內容</t>
+        </is>
+      </c>
+      <c r="I606" s="2" t="inlineStr"/>
     </row>
     <row r="607" ht="108" customHeight="1">
       <c r="A607" s="2" t="n">
@@ -27276,8 +27381,14 @@
       <c r="G607" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H607" s="2" t="n"/>
-      <c r="I607" s="2" t="n"/>
+      <c r="H607" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+依據高架作業勞工保護措施標準第3條規定，露天作業場所的高度計算，為自勞工站立位置，半徑 3 公尺範圍內最低點之地面或水面起至勞工立足點平面間之垂直距離。
+因此，正確答案為 3 公尺。</t>
+        </is>
+      </c>
+      <c r="I607" s="2" t="inlineStr"/>
     </row>
     <row r="608" ht="108" customHeight="1">
       <c r="A608" s="2" t="n">
@@ -27305,8 +27416,22 @@
       <c r="G608" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H608" s="2" t="n"/>
-      <c r="I608" s="2" t="n"/>
+      <c r="H608" s="2" t="inlineStr">
+        <is>
+          <t>答案是 20 分鐘。
+依照《高架作業勞工保護措施標準》規定，高架作業每連續作業 2 小時的休息時間為：
+公尺以上未滿 5 公尺：至少休息 20分鐘
+5 公尺以上未滿 20 公尺：至少休息 25分鐘
+20 公尺以上：至少休息 35分鐘
+需要了解其他高度的高架作業休息規定嗎？
+5公尺至未滿20公尺
+20公尺以上
+高架作業定義說明
+高架作業勞工保護措施標準 - 勞動部-所有條文
+雇主使勞工從事高架作業時，應減少工作時間，每連續作業二小時，應給予作業勞工下列休息時間： 一、高度在二公尺以上未滿五公尺者，至少有二十分鐘休息。 二、高度在五公尺以上未滿二十公尺者，至少有二十五分鐘休息。 三、高度在二十公尺以上者，至少有三十五分鐘休息。 內容</t>
+        </is>
+      </c>
+      <c r="I608" s="2" t="inlineStr"/>
     </row>
     <row r="609" ht="108" customHeight="1">
       <c r="A609" s="2" t="n">
@@ -27334,8 +27459,12 @@
       <c r="G609" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H609" s="2" t="n"/>
-      <c r="I609" s="2" t="n"/>
+      <c r="H609" s="2" t="inlineStr">
+        <is>
+          <t>Google AI 摘要未抓取到，請手動補充。</t>
+        </is>
+      </c>
+      <c r="I609" s="2" t="inlineStr"/>
     </row>
     <row r="610" ht="108" customHeight="1">
       <c r="A610" s="2" t="n">
@@ -27363,8 +27492,16 @@
       <c r="G610" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H610" s="2" t="n"/>
-      <c r="I610" s="2" t="n"/>
+      <c r="H610" s="2" t="inlineStr">
+        <is>
+          <t>高度在 20 公尺以上之高架作業，每連續作業 2 小時，應給予至少 35 分鐘的休息時間。
+根據高架作業勞工保護措施標準規定，每連續作業 2 小時的休息時間標準如下：
+2 公尺以上未滿 5 公尺：至少 20 分鐘。
+5 公尺以上未滿 20 公尺：至少 25 分鐘。
+20 公尺以上：至少 35 分鐘。</t>
+        </is>
+      </c>
+      <c r="I610" s="2" t="inlineStr"/>
     </row>
     <row r="611" ht="108" customHeight="1">
       <c r="A611" s="2" t="n">
@@ -27398,8 +27535,17 @@
       <c r="G611" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H611" s="2" t="n"/>
-      <c r="I611" s="2" t="n"/>
+      <c r="H611" s="2" t="inlineStr">
+        <is>
+          <t>正確答案是 以上皆是（通常對應考試選項中的 (D) 或最後一項）。
+相關法規依據
+依據《高架作業勞工保護措施標準》第 8 條規定，勞工有下列情事之一者，雇主不得使其從事高架作業：
+酒醉或有酒醉之虞者
+身體虛弱，經醫師診斷認為身體狀況不良者或勞工自覺不適從事工作者
+情緒不穩定，有安全顧慮者或其他經主管人員認定者</t>
+        </is>
+      </c>
+      <c r="I611" s="2" t="inlineStr"/>
     </row>
     <row r="612" ht="92.59999999999999" customHeight="1">
       <c r="A612" s="2" t="n">
@@ -27433,8 +27579,18 @@
       <c r="G612" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H612" s="2" t="n"/>
-      <c r="I612" s="2" t="n"/>
+      <c r="H612" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+答案是以上皆是（選項D）。
+墜落危險場所說明
+高架作業：高度在2公尺或5公尺以上、具備高度差的高處作業，若未有完善防護容易發生危險。
+施工架開口處：施工鷹架邊緣或工作台與構造物間的開口，防護不足時容易踩空墜落。
+屋頂：斜屋頂、鐵皮屋頂或維修作業時，常因踏穿或邊緣無防墜設施而發生事故。
+您可以在 Yamol 題庫網 查看更多相關職業安全衛生（職安卡）考古題與統計。</t>
+        </is>
+      </c>
+      <c r="I612" s="2" t="inlineStr"/>
     </row>
     <row r="613" ht="108" customHeight="1">
       <c r="A613" s="2" t="n">
@@ -27468,8 +27624,16 @@
       <c r="G613" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H613" s="2" t="n"/>
-      <c r="I613" s="2" t="n"/>
+      <c r="H613" s="2" t="inlineStr">
+        <is>
+          <t>高架作業主要可能引起的危害是暈眩導致墜落。
+危害解析
+暈眩導致墜落：在高處作業時，勞工容易因高度感、平衡感失調、身體狀況不佳或強風而產生暈眩，進而導致墜落、崩塌或跌落等嚴重職災，這是高架作業最核心且常見的危險。
+熱中暑 / 虛脫：這屬於在高溫、戶外曝曬或通風不良環境下作業常見的熱危害，雖然高架作業若在室外也可能遇到，但並非高架作業特有的本質危害。
+減壓症：俗稱潛水夫病，通常發生於異常氣壓作業（如潛水、沉箱作業），與高架（高處）作業無關。</t>
+        </is>
+      </c>
+      <c r="I613" s="2" t="inlineStr"/>
     </row>
     <row r="614" ht="92.59999999999999" customHeight="1">
       <c r="A614" s="2" t="n">
@@ -27503,8 +27667,15 @@
       <c r="G614" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H614" s="2" t="n"/>
-      <c r="I614" s="2" t="n"/>
+      <c r="H614" s="2" t="inlineStr">
+        <is>
+          <t>依據《營造安全衛生設施標準》第 11-1 條規定，正確答案為：(C) 營繕工程工作場所
+重點說明
+法令依據：《營造安全衛生設施標準》第 11-1 條明定：「雇主對於進入營繕工程工作場所作業人員，應提供適當安全帽，並使其正確戴用。」
+其他選項：如員工休息室、辦公室或工地事務所等非直接施工的相對安全區域，則無強制規定需配戴安全帽。</t>
+        </is>
+      </c>
+      <c r="I614" s="2" t="inlineStr"/>
     </row>
     <row r="615" ht="92.59999999999999" customHeight="1">
       <c r="A615" s="2" t="n">
@@ -27538,8 +27709,15 @@
       <c r="G615" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H615" s="2" t="n"/>
-      <c r="I615" s="2" t="n"/>
+      <c r="H615" s="2" t="inlineStr">
+        <is>
+          <t>從事電梯井吊料作業時，應先掛安全帶再進行開門等後續動作。正確答案為 (B) 先掛安全帶。
+依據營造安全衛生設施標準及相關作業安全程序，在高處或電梯井開口旁作業時，防墜措施與個人防護具的配掛絕對優先於其他操作：
+正確順序：先將安全帶確實勾掛於安全母索或指定的牢固扣環上，確認安全無虞後，才可以打開電梯井護欄或門扇進行吊料。
+新北捷運工程局</t>
+        </is>
+      </c>
+      <c r="I615" s="2" t="inlineStr"/>
     </row>
     <row r="616" ht="108" customHeight="1">
       <c r="A616" s="2" t="n">
@@ -27573,8 +27751,16 @@
       <c r="G616" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H616" s="2" t="n"/>
-      <c r="I616" s="2" t="n"/>
+      <c r="H616" s="2" t="inlineStr">
+        <is>
+          <t>屋頂作業敘述正確的選項是 (A) 要聽主管指揮。
+屋頂作業安全重點
+服從指揮：作業時務必遵循現場主管或屋頂作業主管的監督與安全指示。
+配戴防護：確實使用安全帶、安全帽等個人防護具。
+留意環境：隨時注意屋面材質強度及天候狀況，防止踏穿或墜落。</t>
+        </is>
+      </c>
+      <c r="I616" s="2" t="inlineStr"/>
     </row>
     <row r="617" ht="108" customHeight="1">
       <c r="A617" s="2" t="n">
@@ -27608,8 +27794,18 @@
       <c r="G617" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H617" s="2" t="n"/>
-      <c r="I617" s="2" t="n"/>
+      <c r="H617" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+正確答案是 「以上皆是」（選項 D）。
+在進行斜屋頂或屋頂相關作業時，為了防止勞工發生墜落與踏穿等職業災害，上述各項安全衛生規定都必須同時符合：
+要鋪設安全通道（如針對易踏穿屋頂鋪設踏板、防墜網等）
+開口要設護欄（防止人員自邊緣或開口處墜落）
+要有主管監視作業（指派專人或作業主管在場督導）
+勞動部職業安全衛生署</t>
+        </is>
+      </c>
+      <c r="I617" s="2" t="inlineStr"/>
     </row>
     <row r="618" ht="108" customHeight="1">
       <c r="A618" s="2" t="n">
@@ -27643,8 +27839,12 @@
       <c r="G618" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H618" s="2" t="n"/>
-      <c r="I618" s="2" t="n"/>
+      <c r="H618" s="2" t="inlineStr">
+        <is>
+          <t>Google AI 摘要未抓取到，請手動補充。</t>
+        </is>
+      </c>
+      <c r="I618" s="2" t="inlineStr"/>
     </row>
     <row r="619" ht="92.59999999999999" customHeight="1">
       <c r="A619" s="2" t="n">
@@ -27678,8 +27878,18 @@
       <c r="G619" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H619" s="2" t="n"/>
-      <c r="I619" s="2" t="n"/>
+      <c r="H619" s="2" t="inlineStr">
+        <is>
+          <t>高處作業安全帶應該要扣在 (C) 安全母索。
+安全重點整理
+正確扣法：安全帶的鉤環應確實鉤掛在牢固的安全母索（或上方錨錠點）上，以發揮防墜落保護功能。
+高科大
+錯誤示範：
+不可扣在合梯或移動梯上，因為梯子本身不具備承受人體墜落衝擊的錨錠強度，若發生墜落，梯子容易跟著傾倒或斷裂。
+更不能扣在身上。</t>
+        </is>
+      </c>
+      <c r="I619" s="2" t="inlineStr"/>
     </row>
     <row r="620" ht="108" customHeight="1">
       <c r="A620" s="2" t="n">
@@ -27713,8 +27923,16 @@
       <c r="G620" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H620" s="2" t="n"/>
-      <c r="I620" s="2" t="n"/>
+      <c r="H620" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+在高處作業人員之管理對策方面，不包括 「設置無墜落之虞的通路、樓梯、升降設備等設施」。
+解析與說明
+人員管理對策：包含選擇適合高架作業之勞工、限制身體精神狀況不良勞工之作業、以及培養從事高處作業之安全態度等，屬於針對「人」的健康、適性與心理安全管理。
+工程/硬體設施對策：設置無墜落之虞的通路、樓梯、升降設備等設施，是屬於工作環境與硬體改善的工程對策，而非人員的管理對策。</t>
+        </is>
+      </c>
+      <c r="I620" s="2" t="inlineStr"/>
     </row>
     <row r="621" ht="108" customHeight="1">
       <c r="A621" s="2" t="n">
@@ -27748,8 +27966,19 @@
       <c r="G621" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H621" s="2" t="n"/>
-      <c r="I621" s="2" t="n"/>
+      <c r="H621" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+不正確的選項是：物料應儘量緊臨護欄。
+原因說明
+物料不可緊臨護欄：在護欄附近堆積物料時，若物料緊臨護欄，會導致勞工踩踏物料時高度相對增加、失去護欄防護效果，甚至可能因物料崩塌或推擠破壞護欄而造成墜落危險。因此物料應與護欄保持適當安全距離，不可儘量緊臨護欄。
+其他正確做法：
+應有墜落警告標示：提醒人員注意高處或開口危險。
+應將護欄適度加高：配合堆積物高度，避免人員翻落。
+不可使用合梯作業：高處邊緣或危險開口附近使用合梯容易發生傾倒與墜落，應禁止使用。</t>
+        </is>
+      </c>
+      <c r="I621" s="2" t="inlineStr"/>
     </row>
     <row r="622" ht="92.59999999999999" customHeight="1">
       <c r="A622" s="2" t="n">
@@ -27783,8 +28012,17 @@
       <c r="G622" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H622" s="2" t="n"/>
-      <c r="I622" s="2" t="n"/>
+      <c r="H622" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+預防樓地板開口墜落最有效的防護方式為設置足夠強度的覆蓋（選項 A）。
+防護重點說明
+工程控制優先：依據職業安全衛生法規，對於開口部分應優先設置護欄、護蓋（覆蓋）等實體工程防護設施，這是最直接且有效的源頭防範方式。
+次要防護：若因作業臨時需要拆除護蓋或設置確有困難時，才退而求其次讓勞工使用安全帶或張掛安全網。
+輔助措施：拉警示帶或設警語僅具警告效果，無法實體阻止人員墜落。</t>
+        </is>
+      </c>
+      <c r="I622" s="2" t="inlineStr"/>
     </row>
     <row r="623" ht="108" customHeight="1">
       <c r="A623" s="2" t="n">
@@ -27818,8 +28056,13 @@
       <c r="G623" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H623" s="2" t="n"/>
-      <c r="I623" s="2" t="n"/>
+      <c r="H623" s="2" t="inlineStr">
+        <is>
+          <t>答案是 2 公尺。
+依據《職業安全衛生設施規則》第 225 條規定，雇主對於在高度 2 公尺以上之處所進行作業，勞工有墜落之虞者，應以架設施工架或其他方法設置工作台。</t>
+        </is>
+      </c>
+      <c r="I623" s="2" t="inlineStr"/>
     </row>
     <row r="624" ht="108" customHeight="1">
       <c r="A624" s="2" t="n">
@@ -27853,8 +28096,98 @@
       <c r="G624" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H624" s="2" t="n"/>
-      <c r="I624" s="2" t="n"/>
+      <c r="H624" s="2" t="inlineStr">
+        <is>
+          <t>以上皆是（正確答案為 D）。
+載入中...
+顯示更多
+網頁搜尋結果
+939. 施工架上應設置何種設施,以免勞工墜落?(A)踏板(B)護欄 ...
+› item-939.+施工架上應設置何種設施...
+2024年10月7日 — 施工架上應設置何種設施,以免勞工墜落? (A)踏板 (B)護欄 (C)交叉拉桿 (D)以上皆是。 答案：登入後查看 統計： A(6), B(23), C(6), D(752), E(0) ...
+以避免勞工墜落？(A)踏板(B)護欄(C)交叉拉桿(D)以上皆是
+› item-30.施工架上應設置何種設備，...
+2022年3月15日 — 30.施工架上應設置何種設備，以避免勞工墜落？(A)踏板(B)護欄(C)交叉拉桿(D)以上皆是，包含題目內容、選項、詳解等，幫助學生提升學習效果。
+施工架作業安全檢查重點及注意事項
+勞動部職業安全衛生署
+› media › rojjkges › 施...
+PDF
+2.為防止施工架作業墜落，高度2 公尺以上應依營造安全衛生設施標準第19 條. 及國家標準CNS 4750 規定，於內、外側設置交叉拉桿及下拉桿，以及於兩. 端立架、轉角處及上下 ...
+59 頁
+缺少字詞： 皆 ‎| 必須包含以下字詞： 皆
+勞動部-所有條文
+› FLAW › FLAWDAT0202
+... 交叉拉桿上方應設置適當護欄（詳照片2）。 ... 為防止施工架作業墜落，高度2 公尺以上應依營造│ │ │ 安全衛生設施標準第19 條及國家標準CNS 4750 規│ │ │ 定 ...
+缺少字詞： 以免 ‎皆 ‎是
+相關問題
+施工架有哪些種類?
+雇主 對於 高度 5 公尺 以上 施工 架 之 組 配 及 拆除 作業 應 指派 何人 於 現場 督導 施工？
+施工架上的踏板法規是什麼?
+請問護欄設置的規定是什麼?
+網頁搜尋結果
+高架作業相關法規
+國立臺灣師範大學－環境安全衛生中心
+› news_file › 2021-...
+PDF
+2021年8月21日 — 第225 條. 雇主對於在高度二公尺以上之處所進行作業，勞工有墜落之虞者，應以架. 設施工架或其他方法設置工作台。但工作台之邊緣及開口部分等，不在此. 限 ...
+20 頁
+落實工地職業安全衛生管理作業手冊
+高雄市政府都市發展局
+› KDAN030101
+PDF
+施安§3. 高度≧2m 之施工架組立及拆除作業，應設置防止作業勞工. 墜落之設備，如扶手先行工法。 施安§4. □施工架內外側應設置交叉拉桿. □施工架高度≧2m，內外側增設下 ...
+施工架作業安全檢查重點及注意事項
+桃園市政府
+› Document › 18施工架...
+PDF
+說明：. 1.國人平均胸膛厚度約23 公分，勞工於施工架工作台上作業，設置補助踏板或長條型防墜網使. 其與構造物間之寬度保持在20 公分以下，可避免勞工墜落及方便於構造物外 ...
+6 頁
+缺少字詞： 以免 ‎皆 ‎是
+框式施工架作業安全指引及檢查重點
+mail.ncku.edu.tw
+› var › file › img
+PDF
+2.為防止施工架作業墜落，高度2 公尺以上應依營造安全衛生設施標準第19 條及國家. 標準規定，內、外側設置交叉拉桿及下拉桿，兩端立架及轉角處應設護欄。 五、 高度2 公尺 ...
+53 頁
+缺少字詞： 踏板 ‎皆
+職業安全衛生設施規則
+高雄市大寮區忠義國民小學
+› upload › 校園常見職...
+PDF
+雇主對於在高度二公尺以上之處所進行作業，勞工有. 墜落之虞者，應以架設施工架或其他方法設置工作. 台。但工作台之邊緣及開口部分等，不在此限。 雇主依前項規定設置工作 ...
+缺少字詞： 以免 ‎皆 ‎是
+其他人也搜尋了以下項目
+施工架法規
+施工架作業安全檢查重點及注意事項
+施工架最新規定
+施工架壁拉桿法規
+框式施工架
+施工架圖說
+施工架交叉拉桿
+施工架上下設備規定
+頁面導覽
+1
+2
+3
+4
+5
+6
+7
+8
+9
+10
+下一頁
+頁尾連結
+台灣
+708 臺南市安平區 - 根據你的 IP 位址
+- 更新位置
+說明
+提供意見
+隱私權
+服務條款</t>
+        </is>
+      </c>
+      <c r="I624" s="2" t="inlineStr"/>
     </row>
     <row r="625" ht="92.59999999999999" customHeight="1">
       <c r="A625" s="2" t="n">
@@ -27888,8 +28221,27 @@
       <c r="G625" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H625" s="2" t="n"/>
-      <c r="I625" s="2" t="n"/>
+      <c r="H625" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+強風係指 10 分鐘間的平均風速達每秒 10 公尺以上者。
+Instagram
+·ninebridgesenterprise
+相關規定
+依據職業安全衛生相關法規，高度在 2 公尺以上之作業場所，遇強風、大雨等惡劣氣候致勞工有墜落危險時，雇主應使勞工停止作業：
+強風定義：指 10 分鐘間之平均風速達每秒 10 公尺以上。
+大雨定義：指相當於雨量
+𝑅
+10
+𝑅
+1
+0
+達 10 公釐以上之降雨（通常指 10 分鐘內雨量達 10 公釐以上，或依實際視能與現場狀況判定）。
+Instagram
+·ninebridgesenterprise</t>
+        </is>
+      </c>
+      <c r="I625" s="2" t="inlineStr"/>
     </row>
     <row r="626" ht="92.59999999999999" customHeight="1">
       <c r="A626" s="2" t="n">
@@ -27923,8 +28275,13 @@
       <c r="G626" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H626" s="2" t="n"/>
-      <c r="I626" s="2" t="n"/>
+      <c r="H626" s="2" t="inlineStr">
+        <is>
+          <t>高度 2 公尺以上作業遇強風大雨而有墜落之虞應停止作業時，所謂之大雨係指日降雨量（或一次降雨量）達 50 公釐以上。
+正確選項為：50 公釐。</t>
+        </is>
+      </c>
+      <c r="I626" s="2" t="inlineStr"/>
     </row>
     <row r="627" ht="108" customHeight="1">
       <c r="A627" s="2" t="n">
@@ -27958,8 +28315,26 @@
       <c r="G627" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H627" s="2" t="n"/>
-      <c r="I627" s="2" t="n"/>
+      <c r="H627" s="2" t="inlineStr">
+        <is>
+          <t>🎯 答案：20 公分
+依據台灣的《營造安全衛生設施標準》第 40 條等相關勞安法規規定，施工架與結構體外緣之開口間隙超過 20 公分時，為防止人員墜落或物體飛落，應應置備防護網（長條型安全網）或採取其他防墜落之防護措施。
+💡 考試速記與陷阱提醒
+20 公分法規線：只要看到「施工架內側與結構體間隙」的防護門檻，請直接連結 20 公分。
+常見陷阱：題目常會混淆 30 公分（通常是其他走道寬度或特定防護鷹架間距的干擾選項），記得 20 公分以上就必須「拉網防護」。
+為了幫您徹底鎖定這個單元的法規分數，要不要試試看下面這題常見的延伸考古題？
+延伸練習題
+依勞工安全衛生相關法規規定，施工架之工作台寬度不得少於多少公分，且工作台間隙不得大於 3 公分？
+(A) 30 公分
+(B) 40 公分
+(C) 50 公分
+(D) 60 公分
+您可以直接回覆選項字母（如：A 或 B），我立刻幫您對答案！
+如果想直接看詳解或需要其他營造法規的重點整理，也請隨時告訴我。
+顯示更多</t>
+        </is>
+      </c>
+      <c r="I627" s="2" t="inlineStr"/>
     </row>
     <row r="628" ht="92.59999999999999" customHeight="1">
       <c r="A628" s="2" t="n">
@@ -27993,8 +28368,13 @@
       <c r="G628" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H628" s="2" t="n"/>
-      <c r="I628" s="2" t="n"/>
+      <c r="H628" s="2" t="inlineStr">
+        <is>
+          <t>依據職業安全衛生設施規則第36條第4款規定，雇主架設之通道，在有墜落之虞之場所，應置備高度75公分以上之堅固扶手。
+正確答案為：75 公分。</t>
+        </is>
+      </c>
+      <c r="I628" s="2" t="inlineStr"/>
     </row>
     <row r="629" ht="108" customHeight="1">
       <c r="A629" s="2" t="n">
@@ -28028,8 +28408,19 @@
       <c r="G629" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H629" s="2" t="n"/>
-      <c r="I629" s="2" t="n"/>
+      <c r="H629" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+題目中有誤的敘述是「作業人員上下應使用谷梯（應為合梯或內梯）」，正確用詞或概念應避免使用不合規定的梯子，且依勞安規範上下應使用合梯或固定內梯，而題目中的「谷梯」為錯別字或錯誤說法（多數題庫原貌作「合梯」或「內梯」）。
+勞動部職業安全衛生署 移動式施工架安全重點
+固定腳輪：施工架上有人員施工時，應確實固定煞車或腳輪以防滑動。
+人員離開：移動施工架時，絕對禁止人員留在架上，應要求作業人員先行離開。
+設置護欄：頂層或工作平台周邊須依規定設置安全護欄，防止墜落。
+Facebook
+·勞動部</t>
+        </is>
+      </c>
+      <c r="I629" s="2" t="inlineStr"/>
     </row>
     <row r="630" ht="108" customHeight="1">
       <c r="A630" s="2" t="n">
@@ -28063,8 +28454,16 @@
       <c r="G630" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H630" s="2" t="n"/>
-      <c r="I630" s="2" t="n"/>
+      <c r="H630" s="2" t="inlineStr">
+        <is>
+          <t>施工架與結構體間開口應設置 (A) 安全網。
+詳細說明
+正確答案：(A) 安全網（或長條型防墜網、補助踏板）。
+法規依據：依據相關營造安全衛生設施標準與檢查重點，高度 2 公尺以上之施工架工作臺與構造物（結構體）間之開口寬度超過 20 公分時，若因作業需要拆除內側交叉拉桿及下拉桿，應先設置具有防墜強度之補助踏板或長條型防墜網（安全網）以防止人員墜落。
+勞動部職業安全衛生署</t>
+        </is>
+      </c>
+      <c r="I630" s="2" t="inlineStr"/>
     </row>
     <row r="631" ht="108" customHeight="1">
       <c r="A631" s="2" t="n">
@@ -28098,8 +28497,14 @@
       <c r="G631" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H631" s="2" t="n"/>
-      <c r="I631" s="2" t="n"/>
+      <c r="H631" s="2" t="inlineStr">
+        <is>
+          <t>依據《營造安全衛生設施標準》規定，雇主構築施工架時，若有鄰近結構物之周遭或跨越工作走道者，應於其下方設置斜籬及防護網。
+桃園市政府 因此，您的選項中正確答案為：斜籬及防護網（題目選項中誤植為「倖秀及防護網」）。
+桃園市政府</t>
+        </is>
+      </c>
+      <c r="I631" s="2" t="inlineStr"/>
     </row>
     <row r="632" ht="108" customHeight="1">
       <c r="A632" s="2" t="n">
@@ -28133,8 +28538,14 @@
       <c r="G632" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H632" s="2" t="n"/>
-      <c r="I632" s="2" t="n"/>
+      <c r="H632" s="2" t="inlineStr">
+        <is>
+          <t>依據營造安全衛生設施標準第39條規定，雇主對於不能藉梯子、高空工作車或其他方法安全完成之2公尺以上高處營造作業，應設置適當之施工架。
+正確答案
+施工架</t>
+        </is>
+      </c>
+      <c r="I632" s="2" t="inlineStr"/>
     </row>
     <row r="633" ht="108" customHeight="1">
       <c r="A633" s="2" t="n">
@@ -28168,8 +28579,18 @@
       <c r="G633" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H633" s="2" t="n"/>
-      <c r="I633" s="2" t="n"/>
+      <c r="H633" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+安全施工架作業應注意的規定答案為以上皆是（選項D）。
+安全施工架作業重點規定
+樓板與施工架間設置防墜網：防止人員自開口處墜落。
+鋪設補助板料：維持工作臺與構造物間的安全寬度與強度。
+樓板與施工架間距要小於 20 公分：保持開口寬度在 20 公分以下，以避免勞工墜落。
+勞動部職業安全衛生署</t>
+        </is>
+      </c>
+      <c r="I633" s="2" t="inlineStr"/>
     </row>
     <row r="634" ht="108" customHeight="1">
       <c r="A634" s="2" t="n">
@@ -28203,8 +28624,16 @@
       <c r="G634" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H634" s="2" t="n"/>
-      <c r="I634" s="2" t="n"/>
+      <c r="H634" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+於電梯開口部進行作業時，有誤的選項為：作業人員應將所需零件及工具插於褲袋中。
+錯誤原因說明
+工具放置規定：作業人員在高度或開口部附近作業時，手工具與零件應放置於專用工具袋、工具箱或妥善固定，不可直接插在褲袋中，以免因彎腰或移動時工具滑落墜落，砸傷下方人員或造成作業危險。
+正確做法：其餘選項包括電梯直井工作平台下方設安全網、於對面或側邊牆壁裝設防墜設施與安全帶掛勾，以及安全帶確實鉤掛，均為符合規定的安全防護措施。</t>
+        </is>
+      </c>
+      <c r="I634" s="2" t="inlineStr"/>
     </row>
     <row r="635" ht="108" customHeight="1">
       <c r="A635" s="2" t="n">
@@ -28238,8 +28667,19 @@
       <c r="G635" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H635" s="2" t="n"/>
-      <c r="I635" s="2" t="n"/>
+      <c r="H635" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+選項「5公尺以上仍應使用合梯作業」是有誤的（應為高度2公尺以下作業才適用合梯）。
+合梯使用安全規定重點
+高度限制：合梯僅適用於高度 2 公尺以下 之作業，超過高度時應搭設鷹架或使用其他安全工作台。
+梯腳角度：合梯兩梯腳完全撐開時，梯腳與地面之角度應在 75 度以內（4:1之比）。
+結構與防滑：需具有堅固構造，兩梯腳間應有金屬等硬質繫材扣牢，腳部有防滑絕緣腳座套，並具備安全之防滑梯面。
+使用限制：單人使用時，禁止登上最上一層頂板，且不得當作上下設備使用。
+高雄市政府全球資訊網</t>
+        </is>
+      </c>
+      <c r="I635" s="2" t="inlineStr"/>
     </row>
     <row r="636" ht="108" customHeight="1">
       <c r="A636" s="2" t="n">
@@ -28273,8 +28713,21 @@
       <c r="G636" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H636" s="2" t="n"/>
-      <c r="I636" s="2" t="n"/>
+      <c r="H636" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+錯誤的做法是：「在施工架上適當位置設置合梯以作為上下設備」。
+原因解析
+禁止以合梯作為上下設備：依據職業安全衛生設施規則及相關營造安全規定，雇主不得使勞工以合梯當作兩個工作面之間的上下設備使用，且禁止勞工站立於合梯頂板作業。施工架應設置專用且安全的上下設備（如樓梯、斜道或踏條等），而不是使用合梯。
+iPEDIA 百科
+正確做法：
+組搭施工架時應採用扶手先行工法以保護作業人員。
+施工架工作台與構造物間之開口寬度應保持小於 20 公分，避免人員踏空墜落。
+應於施工架兩端立架及轉角處設置護欄。
+勞動部職業安全衛生署</t>
+        </is>
+      </c>
+      <c r="I636" s="2" t="inlineStr"/>
     </row>
     <row r="637" ht="92.59999999999999" customHeight="1">
       <c r="A637" s="2" t="n">
@@ -28308,8 +28761,17 @@
       <c r="G637" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H637" s="2" t="n"/>
-      <c r="I637" s="2" t="n"/>
+      <c r="H637" s="2" t="inlineStr">
+        <is>
+          <t>正確的優先順序為 d-c-b-a（即 預防 -&gt; 阻止 -&gt; 消除 -&gt; 警告 或是依職業安全控制邏輯：由高階至低階或依題意標準答案為 d-c-b-a）。詳細資訊可參閱相關題庫說明與解析 [線上 營造業甲種職業安全衛生業務主管測驗。
+控制方式與優先順序
+d. 預防 (PREVENT)：優先採取工程或結構預防。
+c. 阻止 (ARREST)：設置安全網或防墜器等阻止墜落。
+b. 消除 (ELIMLNATE)：從源頭取消高空作業。
+a. 警告 (WARN)：設置警示線或告示，為最低階防護。</t>
+        </is>
+      </c>
+      <c r="I637" s="2" t="inlineStr"/>
     </row>
     <row r="638" ht="108" customHeight="1">
       <c r="A638" s="2" t="n">
@@ -28343,8 +28805,15 @@
       <c r="G638" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H638" s="2" t="n"/>
-      <c r="I638" s="2" t="n"/>
+      <c r="H638" s="2" t="inlineStr">
+        <is>
+          <t>指派專人於現場指揮監督不屬於防止人員墜落的「設施」，而是一種「管理或督導」措施。
+詳細說明
+防墜設施：如設置適當強度踏板、張掛安全母索、張掛安全網或設置護欄等，是用來直接阻擋或支撐人員避免墜落的物理硬體。
+現場監督：指派專人於現場指揮監督（如屋頂作業主管）屬於作業安全管理與監督事項，並非物理防墜設施。</t>
+        </is>
+      </c>
+      <c r="I638" s="2" t="inlineStr"/>
     </row>
     <row r="639" ht="92.59999999999999" customHeight="1">
       <c r="A639" s="2" t="n">
@@ -28378,8 +28847,18 @@
       <c r="G639" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H639" s="2" t="n"/>
-      <c r="I639" s="2" t="n"/>
+      <c r="H639" s="2" t="inlineStr">
+        <is>
+          <t>施工架設置壁連座與施工架於地面預組皆屬於施工架構造穩定或組配作業方式，但在職安法規與考試題庫中，施工架設置壁連座（或視具體題庫標準，通常壁連座是用來防止施工架倒塌/傾倒之構造設施；而「施工架於地面預組」則是預防高空組配危害的作業方式）——等等，讓我們看一般題庫對此題的正解是哪一個。壁連座是用於防止施工架倒塌，而開口邊緣護欄與安全網是直接防止人體墜落。不過在多數營造安全試題中，「施工架設置壁連座」屬於防止施工架倒塌（構造倒塌災害防止），而非直接針對勞工「人體墜落」的防墜設施。
+答案解析
+開口邊緣設置護欄：屬於直接防止人員墜落的防護設施。
+開口邊緣張掛安全網：屬於發生墜落時的二次防墜（緩衝）設施。
+施工架設置壁連座：屬於防止施工架本身傾倒、崩塌的構造穩定設施，而非人體墜落災害防止設施。
+施工架於地面預組：屬於減少高空作業時間的預組工法（廣義安全作業程序）。
+正確答案為：施工架設置壁連座（非直接防止人體墜落之防墜設施）。</t>
+        </is>
+      </c>
+      <c r="I639" s="2" t="inlineStr"/>
     </row>
     <row r="640" ht="92.59999999999999" customHeight="1">
       <c r="A640" s="2" t="n">
@@ -28413,8 +28892,13 @@
       <c r="G640" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H640" s="2" t="n"/>
-      <c r="I640" s="2" t="n"/>
+      <c r="H640" s="2" t="inlineStr">
+        <is>
+          <t>有墜落危險時，高度 2 公尺以上高處作業應確實使用安全帶、安全帽。
+根據《職業安全衛生設施規則》第 281 條規定，雇主對於在高度二公尺以上之高處作業，勞工有墜落之虞者，應使勞工確實使用安全帶、安全帽及其他必要之防護具。</t>
+        </is>
+      </c>
+      <c r="I640" s="2" t="inlineStr"/>
     </row>
     <row r="641" ht="92.59999999999999" customHeight="1">
       <c r="A641" s="2" t="n">
@@ -28448,8 +28932,17 @@
       <c r="G641" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H641" s="2" t="n"/>
-      <c r="I641" s="2" t="n"/>
+      <c r="H641" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+使勞工穿反光背心非屬墜落災害防止之設施。
+相關說明
+墜落災害防止設施：包含設置護欄、護蓋、張掛安全網以及使勞工佩掛安全帶等，是用於直接防止人員從高處墜落或發生墜落時提供攔截與保護的硬體設施。
+反光背心：主要用於提高能見度、防止車禍或視線不良引起的碰撞災害，並非直接防止高處墜落的防護設施。
+營造業職業安全衛生管理系統</t>
+        </is>
+      </c>
+      <c r="I641" s="2" t="inlineStr"/>
     </row>
     <row r="642" ht="92.59999999999999" customHeight="1">
       <c r="A642" s="2" t="n">
@@ -28483,8 +28976,15 @@
       <c r="G642" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H642" s="2" t="n"/>
-      <c r="I642" s="2" t="n"/>
+      <c r="H642" s="2" t="inlineStr">
+        <is>
+          <t>正確答案為：(A) 設置安全柵門並上鎖及實施作業管制，作業時確實要求使用安全帶（註：部分類似題庫或考試系統對此題標準答案設定為 A 或 以上皆是，依勞安職安法規與相關題庫標準，防止電梯口開口墜落主要著重於設置安全柵門、上鎖管制與佩掛安全帶）。您可以參考 Yamol 題庫討論區 取得更多細節。
+yamol.tw
+963. 工地為防止電梯口作業人員墜落,應要求採取下列何項設施 ...
+2024年10月7日 — 963. 工地為防止電梯口作業人員墜落,應要求採取下列何項設施? (A)設置安全柵門並上鎖及實施作業管制,作業時確實要求使用安全帶 (B)設置上橫檔及下橫檔 (C)設置輔助繩、開口危險警示標誌及充分之照明 (D)以上皆是。 答案：登入後查看 統計： A(7), 內容</t>
+        </is>
+      </c>
+      <c r="I642" s="2" t="inlineStr"/>
     </row>
     <row r="643" ht="108" customHeight="1">
       <c r="A643" s="2" t="n">
@@ -28518,8 +29018,18 @@
       <c r="G643" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H643" s="2" t="n"/>
-      <c r="I643" s="2" t="n"/>
+      <c r="H643" s="2" t="inlineStr">
+        <is>
+          <t>下列有關墜落防護應注意事項中，敘述有誤的是：「上工前為充實精神，所以要喝具有提神的酒精性飲料」。
+💡 錯誤原因與正確觀念
+工作前與工時中嚴禁飲酒：酒精會影響中樞神經系統，導致反應遲鈍、平衡感變差、注意力不集中。在進行高處作業（2公尺以上）時飲酒，會大幅增加墜落的危險。依據勞工安全衛生相關法規，雇主不得讓酒精濃度超過規定或有酒醉之虞的勞工從事高空作業。
+正確的墜落防護注意事項
+設置防墜設施：雇主對於高度 2 公尺以上之作業場所，有墜落之虞者，應確實設置護欄、護蓋或安全網等防護設施。
+教育訓練：雇主應對勞工施予必要的安全衛生教育訓練，確保勞工了解高處作業的風險與防護具（如安全帶、安全帽）的正確使用方法。
+自動檢查：落實安全衛生自動檢查，每日上工前檢查防墜設施及個人防護具是否完整無損。</t>
+        </is>
+      </c>
+      <c r="I643" s="2" t="inlineStr"/>
     </row>
     <row r="644" ht="108" customHeight="1">
       <c r="A644" s="2" t="n">
@@ -28553,8 +29063,18 @@
       <c r="G644" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H644" s="2" t="n"/>
-      <c r="I644" s="2" t="n"/>
+      <c r="H644" s="2" t="inlineStr">
+        <is>
+          <t>針對這道職業安全衛生考題，在所列出的選項中，以 「高度 2 公尺以上之開口處應設護欄或安全網」 較為妥適。
+敘述解析與比較
+高度 2 公尺以上之開口處應設護欄或安全網：依據法規，高度在 2 公尺以上之工作場所邊緣及開口部分，勞工有遭受墜落危險之虞時，應設有適當強度之護欄、護蓋或安全網等防護設備，此敘述符合法規要求。
+在外牆施工架等高處作業，應盡量使用背腰式安全帶：實務與法規上，高處作業應優先使用全身背負式（Full-body harness）安全帶，而非僅固定腰部的繫腰式安全帶，以避免墜落時衝擊力集中腰椎造成二次傷害。
+高度 2 公尺以上之中斷開口部分處應圍起警示帶：開口處僅圍警示帶強度不足以防止人員墜落，仍需依規定設置實體護欄、護蓋或安全網。
+安全帶應確實佩掛在低於足下之堅固點：安全帶的掛點應盡可能高掛在「高於足下甚至胸高以上」的堅固點，若掛在低於足下處，會拉大墜落距離並增加衝擊力。
+為了提供更精準的實務建議，想了解您是正在準備職安相關證照考試（如甲乙種職業安全衛生業務主管、勞安士等），還是需要了解具體的營造作業墜落防護法規細節呢？</t>
+        </is>
+      </c>
+      <c r="I644" s="2" t="inlineStr"/>
     </row>
     <row r="645" ht="92.59999999999999" customHeight="1">
       <c r="A645" s="2" t="n">
@@ -28588,8 +29108,15 @@
       <c r="G645" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H645" s="2" t="n"/>
-      <c r="I645" s="2" t="n"/>
+      <c r="H645" s="2" t="inlineStr">
+        <is>
+          <t>「撬開電梯門」是錯誤的敘述（選項有誤）。
+原因解析
+危險行為：當電梯發生故障或受困時，絕對不可以自行撬開電梯門，這樣非常容易導致失足墜落深井或遭受嚴重夾傷，引發致命意外。
+正確做法：應留在車廂內冷靜等待救援、使用緊急對講機或按求救鈴，聽從專業人員的指揮。</t>
+        </is>
+      </c>
+      <c r="I645" s="2" t="inlineStr"/>
     </row>
     <row r="646" ht="108" customHeight="1">
       <c r="A646" s="2" t="n">
@@ -28623,8 +29150,18 @@
       <c r="G646" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H646" s="2" t="n"/>
-      <c r="I646" s="2" t="n"/>
+      <c r="H646" s="2" t="inlineStr">
+        <is>
+          <t>下列何者非屬施工架與建物間距過大時，應採取之措施的答案是裝設防塵網。
+施工架與建物間距過大之正確因應措施
+當施工架與建築物之間的間距過大而產生墜落風險時，應採取下列安全防護：
+於施工架與建物間裝設防墜網：防止人員自間距空隙墜落。
+確實使用安全帶：高處作業之基本防護。
+增設延伸踏板：縮小施工架與建物間的距離與開口。
+防塵網是用來阻擋飛塵與雜物飄散，不屬於防止間距過大造成墜落的結構或安全支撐措施。</t>
+        </is>
+      </c>
+      <c r="I646" s="2" t="inlineStr"/>
     </row>
     <row r="647" ht="92.59999999999999" customHeight="1">
       <c r="A647" s="2" t="n">
@@ -28658,8 +29195,15 @@
       <c r="G647" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H647" s="2" t="n"/>
-      <c r="I647" s="2" t="n"/>
+      <c r="H647" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+答案是以上皆是（選項 D）。
+依據職業安全衛生設施規則第 281 條規定：「雇主對於在高度二公尺以上之高處作業，勞工有墜落之虞者，應使勞工確實使用安全帶、安全帽及其他必要之防護具。」
+因此，題目中所提及的安全帶、安全帽以及其他必要之防護具皆包含在內。</t>
+        </is>
+      </c>
+      <c r="I647" s="2" t="inlineStr"/>
     </row>
     <row r="648" ht="77.15000000000001" customHeight="1">
       <c r="A648" s="2" t="n">
@@ -28693,8 +29237,13 @@
       <c r="G648" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H648" s="2" t="n"/>
-      <c r="I648" s="2" t="n"/>
+      <c r="H648" s="2" t="inlineStr">
+        <is>
+          <t>應採用的防止墜落等措施之一為使勞工佩帶 安全帶（同時也包含安全帽與全身背負式安全帶）。在選項中正確答案為 安全帶。
+依據《起重升降機具安全規則》規定，以搭乘設備乘載或吊升勞工時，需設置安全母索或防墜設施，並使勞工佩戴安全帽及符合規定之全身背負式安全帶。</t>
+        </is>
+      </c>
+      <c r="I648" s="2" t="inlineStr"/>
     </row>
     <row r="649" ht="92.59999999999999" customHeight="1">
       <c r="A649" s="2" t="n">
@@ -28728,8 +29277,17 @@
       <c r="G649" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H649" s="2" t="n"/>
-      <c r="I649" s="2" t="n"/>
+      <c r="H649" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+依勞動部統計分析報告顯示，墜落災害占全體重大（含死亡）職業傷害之 第一名。
+主要原因：高處墜落與滾落事故長期為各行業（特別是營造業）中造成勞工重大傷亡與死亡的最高風險類型。
+相關資訊：您可參考 Yamol 題庫詳解 了解更多考試相關細節。
+勞動部全球資訊網 . 依勞動部對近十年來職業傷害發生類型進行統計分析之 ...
+2024年10月7日 — 971. 依勞動部對近十年來職業傷害發生類型進行統計分析之報告顯示,墜落災害占全體重大(含死亡)職業傷害? (A)第一名 (B)第二名 (C)第三名 (D)第四。</t>
+        </is>
+      </c>
+      <c r="I649" s="2" t="inlineStr"/>
     </row>
     <row r="650" ht="92.59999999999999" customHeight="1">
       <c r="A650" s="2" t="n">
@@ -28763,8 +29321,14 @@
       <c r="G650" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H650" s="2" t="n"/>
-      <c r="I650" s="2" t="n"/>
+      <c r="H650" s="2" t="inlineStr">
+        <is>
+          <t>高差超過二層樓或 7.5 公尺以上之鋼構建築，未張設安全網，且其下方未具有足夠淨空及工作面與安全網間具有障礙物。
+正確答案為：7.5 公尺。
+依據《勞動檢查法第二十八條所定勞工有立即發生危險之虞認定標準》規定，高差超過二層樓或七點五公尺以上之鋼構建築物若未依規定張設安全網，且下方淨空不足或工作面與安全網間有障礙物，會被認定有立即發生危險之虞。</t>
+        </is>
+      </c>
+      <c r="I650" s="2" t="inlineStr"/>
     </row>
     <row r="651" ht="108" customHeight="1">
       <c r="A651" s="2" t="n">
@@ -28798,8 +29362,23 @@
       <c r="G651" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H651" s="2" t="n"/>
-      <c r="I651" s="2" t="n"/>
+      <c r="H651" s="2" t="inlineStr">
+        <is>
+          <t>正確答案為 (B) 梯子之頂端應突出板面 60 公分以上。
+依據《職業安全衛生設施規則》第 37 條規定，固定梯子的各項正確標準如下：
+Facebook
+·Diy小王子X信昌鐵工
+頂端高度：梯子之頂端應突出板面 60 公分以上（選項 B 正確）。
+踏條與牆壁淨距：應保持 16.5 公分以上 之淨距，而非不得超過 15 公分（選項 A 錯誤）。
+平台設置（有護籠時）：梯長連續超過 6 公尺時，應每隔 9 公尺以下 設一平台（選項 C 錯誤）。
+平台設置（未設護籠時）：未設護籠或其他保護裝置時，應每隔 6 公尺以下 設一平台（選項 D 錯誤）。
+需要了解更多職業安全衛生設施規則的相關規定嗎？
+施工架安全標準
+墜落災害預防原則
+安全帶使用規範</t>
+        </is>
+      </c>
+      <c r="I651" s="2" t="inlineStr"/>
     </row>
     <row r="652" ht="92.59999999999999" customHeight="1">
       <c r="A652" s="2" t="n">
@@ -28833,8 +29412,23 @@
       <c r="G652" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H652" s="2" t="n"/>
-      <c r="I652" s="2" t="n"/>
+      <c r="H652" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+(D) 地面作業較少發生人體墜落災害。
+答案解析
+地面作業：在平面或無高低落差的環境進行，不具高處或臨邊風險，因此最少發生墜落。
+高架作業：高度達2公尺以上，具高處墜落風險。
+合梯作業：梯面或梯腳移動不慎易傾倒墜落。
+配戴安全帶：是用來預防或減輕墜落傷害的防護措施，但本身屬於高處/危險作業中的保護動作，情境對比下以「地面作業」最無墜落可能。
+您可以參考 勞動部了解高架作業定義。
+需要我幫你整理更多職業安全衛生乙/丙級學科的常考題目嗎？
+高架作業勞工保護措施標準 - 勞動部-所有條文
+本標準所稱高架作業，係指雇主使勞工從事之下列作業： 一、未設置平台、護欄等設備而已採取必要安全措施，其高度在二公尺以上者。 二、已依規定設置平台、護欄等設備，並採取防止墜落之必要安全措施， 其高度在五公尺以上者。
+顯示全部 內容</t>
+        </is>
+      </c>
+      <c r="I652" s="2" t="inlineStr"/>
     </row>
     <row r="653" ht="92.59999999999999" customHeight="1">
       <c r="A653" s="2" t="n">
@@ -28868,8 +29462,19 @@
       <c r="G653" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H653" s="2" t="n"/>
-      <c r="I653" s="2" t="n"/>
+      <c r="H653" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+人體墜落屬於 物理性 危害因子。
+危害因子說明
+物理性危害因子：指作業環境中各種形式的能量或機械性能造成人員傷害的因素，包含機械動能引起的人體墜落、感電、噪音、振動、極端溫濕條件與輻射等。
+化學性：如粉塵、有機溶劑、有毒氣體等。
+生物性：如細菌、病毒、黴菌等微生物或寄生蟲。
+人因工程：如姿勢不良、重複性動作、過度施力或長期負重造成的肌肉骨骼傷害。
+台灣大學醫學院附設醫院</t>
+        </is>
+      </c>
+      <c r="I653" s="2" t="inlineStr"/>
     </row>
     <row r="654" ht="92.59999999999999" customHeight="1">
       <c r="A654" s="2" t="n">
@@ -28903,8 +29508,12 @@
       <c r="G654" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H654" s="2" t="n"/>
-      <c r="I654" s="2" t="n"/>
+      <c r="H654" s="2" t="inlineStr">
+        <is>
+          <t>依據《營造安全衛生設施標準》規定，臨時性開口處使用之覆蓋（護蓋），表面應漆成黃色並書以「開口注意」等警告訊息。</t>
+        </is>
+      </c>
+      <c r="I654" s="2" t="inlineStr"/>
     </row>
     <row r="655" ht="92.59999999999999" customHeight="1">
       <c r="A655" s="2" t="n">
@@ -28938,8 +29547,22 @@
       <c r="G655" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H655" s="2" t="n"/>
-      <c r="I655" s="2" t="n"/>
+      <c r="H655" s="2" t="inlineStr">
+        <is>
+          <t>於合梯上作業非《職業安全衛生設施規則》第281條規定強制指定需使用 CNS-14253-1 全身背負式安全帶及捲揚式防墜器的高處作業項目。
+依據《職業安全衛生設施規則》第281條規定，須採用符合國家標準 CNS 14253-1 全身背負式安全帶及捲揚式防墜器的作業包含：
+鋼構懸臂突出物
+斜籬
+二公尺以上未設護籠等保護裝置之垂直固定梯
+局限空間
+屋頂
+施工架組拆
+工作台組拆
+管線維修作業等高處或傾斜面移動
+而「於合梯上作業」法規另有規範其高度、梯腳角度及防滑等構造要求（同規則第230條），但未在此項強制規定之列。</t>
+        </is>
+      </c>
+      <c r="I655" s="2" t="inlineStr"/>
     </row>
     <row r="656" ht="108" customHeight="1">
       <c r="A656" s="2" t="n">
@@ -28973,8 +29596,16 @@
       <c r="G656" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H656" s="2" t="n"/>
-      <c r="I656" s="2" t="n"/>
+      <c r="H656" s="2" t="inlineStr">
+        <is>
+          <t>施工架組配作業應使勞工配戴符合國家標準 CNS 14253-1 同等以上規定之全身背負式安全帶。
+高雄市政府都市發展局
+正確選項：CNS 14253-1（個人防墜落系統－全身背負式安全帶）
+CNS 4750：係指鋼管施工架之國家標準。
+勞動部職業安全衛生署</t>
+        </is>
+      </c>
+      <c r="I656" s="2" t="inlineStr"/>
     </row>
     <row r="657" ht="108" customHeight="1">
       <c r="A657" s="2" t="n">
@@ -29008,8 +29639,12 @@
       <c r="G657" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H657" s="2" t="n"/>
-      <c r="I657" s="2" t="n"/>
+      <c r="H657" s="2" t="inlineStr">
+        <is>
+          <t>Google AI 摘要未抓取到，請手動補充。</t>
+        </is>
+      </c>
+      <c r="I657" s="2" t="inlineStr"/>
     </row>
     <row r="658" ht="92.59999999999999" customHeight="1">
       <c r="A658" s="2" t="n">
@@ -29043,8 +29678,13 @@
       <c r="G658" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H658" s="2" t="n"/>
-      <c r="I658" s="2" t="n"/>
+      <c r="H658" s="2" t="inlineStr">
+        <is>
+          <t>保護勞工的最後一道防線是個人防護具（PPE）。
+在職業安全衛生的「危害控制控制層級」（Hierarchy of Controls）中，消除危害、取代、工程控制和管理控制都屬於優先採取的手段。當上述前面所有防護措施都無法完全消除風險時，才需要依賴個人防護具（如安全帽、防護口罩、安全鞋等）作為最後的防守界線。</t>
+        </is>
+      </c>
+      <c r="I658" s="2" t="inlineStr"/>
     </row>
     <row r="659" ht="108" customHeight="1">
       <c r="A659" s="2" t="n">
@@ -29078,8 +29718,13 @@
       <c r="G659" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H659" s="2" t="n"/>
-      <c r="I659" s="2" t="n"/>
+      <c r="H659" s="2" t="inlineStr">
+        <is>
+          <t>避免身體因墜落而受到撞擊傷害。
+背負式安全帶與捲揚式防墜器（防墜王）的核心功能，是當勞工在進行高處作業不慎跌落時，能夠在極短的時間與距離內煞車鎖定，並透過安全帶將衝擊力均勻分散至全身，從而防止人體掉落地面或撞擊下方障礙物，保障生命安全。</t>
+        </is>
+      </c>
+      <c r="I659" s="2" t="inlineStr"/>
     </row>
     <row r="660" ht="92.59999999999999" customHeight="1">
       <c r="A660" s="2" t="n">
@@ -29113,8 +29758,16 @@
       <c r="G660" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H660" s="2" t="n"/>
-      <c r="I660" s="2" t="n"/>
+      <c r="H660" s="2" t="inlineStr">
+        <is>
+          <t>「以上皆是」是正確答案。
+這三個敘述完全符合高空作業安全與懸掛創傷（Suspension Trauma，又稱安全帶綜合症）的學理：
+懸掛創傷與一個人健康水平無關：不論受困者的體格多麼強健、平時多健康，只要在安全帶中懸吊靜止不動，人體因重力血液滯留下肢的生理反應都是一樣的。
+下擺、盪回都會造成傷害：當人員高空墜落時，若錨點不是在正上方，就會產生像鐘擺一樣的「下擺」與「盪回」效應，這會導致身體撞擊周邊的結構物（如牆壁、鋼架），造成嚴重的二次傷害。
+吊在全身背負式安全帶中靜止時，會造成懸掛創傷：當人體長時間垂直懸掛且缺乏雙腿活動時，下肢肌肉無法協助血液回流，會導致深層靜脈血液大量淤積在腿部。這會使體內有效循環血容量驟降，引發暈厥、休克甚至短時間內死亡。</t>
+        </is>
+      </c>
+      <c r="I660" s="2" t="inlineStr"/>
     </row>
     <row r="661" ht="92.59999999999999" customHeight="1">
       <c r="A661" s="2" t="n">
@@ -29148,8 +29801,17 @@
       <c r="G661" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H661" s="2" t="n"/>
-      <c r="I661" s="2" t="n"/>
+      <c r="H661" s="2" t="inlineStr">
+        <is>
+          <t>正確答案是：(D) 以上皆是。
+為什麼是以上皆是？
+固定良好：懸掛或安裝防墜器的錨錠點必須牢固、強度足夠（需大於 10kN 以上），以防受力時脫落。
+使用距離：要注意淨空高度和作業半徑是否足夠，避免因距離不足或角度太大（超過 30 度）而產生致命的鐘擺效應。
+伸縮良好：鋼索或織帶必須能順暢拉出與收回，確保發生墜落時能即時發揮制動作用。
+梯老闆</t>
+        </is>
+      </c>
+      <c r="I661" s="2" t="inlineStr"/>
     </row>
     <row r="662" ht="108" customHeight="1">
       <c r="A662" s="2" t="n">
@@ -29183,8 +29845,17 @@
       <c r="G662" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H662" s="2" t="n"/>
-      <c r="I662" s="2" t="n"/>
+      <c r="H662" s="2" t="inlineStr">
+        <is>
+          <t>不正確的選項是：為提高合梯的穩定性，合梯的角應儘量加大。
+正確觀念與法規說明
+合梯角度限制：依據《職業安全衛生設施規則》規定，合梯梯腳與地面之角度應在 75度以內（即兩梯腳張開的角度不能過大或過平），且兩梯腳間必須用金屬等硬質繫材扣牢。若角度過大、過度撐開反而容易導致結構不穩或滑動崩塌，因此不能「儘量加大」。
+護蓋柵狀構造：設置之護蓋為柵狀構造者，柵條間隔不得大於 3 公分，以防人員踩空或物品掉落。
+防止開口墜落：對於廢止使用之開口部分應予封閉或採取防護措施，防止勞工發生墜落。
+合梯高度限制：合梯高度以頂部之梯面至梯腳間之垂直距離計算，高度不得超過 2 公尺。</t>
+        </is>
+      </c>
+      <c r="I662" s="2" t="inlineStr"/>
     </row>
     <row r="663" ht="108" customHeight="1">
       <c r="A663" s="2" t="n">
@@ -29218,8 +29889,15 @@
       <c r="G663" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H663" s="2" t="n"/>
-      <c r="I663" s="2" t="n"/>
+      <c r="H663" s="2" t="inlineStr">
+        <is>
+          <t>依據營造安全衛生設施標準第 17 條規定，答案應填訂定：墜落災害防止計畫。
+相關規定重點
+適用對象：高度 2 公尺以上之工作場所，且勞工作業有墜落之虞者。
+辦理方式：雇主應依風險控制之先後順序進行規劃，並採取適當之墜落災害防止設施。</t>
+        </is>
+      </c>
+      <c r="I663" s="2" t="inlineStr"/>
     </row>
     <row r="664" ht="108" customHeight="1">
       <c r="A664" s="2" t="n">
@@ -29253,8 +29931,39 @@
       <c r="G664" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H664" s="2" t="n"/>
-      <c r="I664" s="2" t="n"/>
+      <c r="H664" s="2" t="inlineStr">
+        <is>
+          <t>依營造安全衛生設施標準第 17 條規定，正確的墜落災害防止採取先後優先順序為 d.e.f.c.a.b.g（或部分版本選項為 d.e.f.c.a.b.g / d.f.c.a.e.b.g 等，依最新條文順序對應為：d
+→
+→
+f
+→
+→
+c
+→
+→
+a
+→
+→
+e
+→
+→
+b
+→
+→
+g，或各款依序排列）。
+營造業職業安全衛生管理系統 依據法規條號之風險控制先後順序：
+d. 經由設計或工法之選擇，儘量使勞工於地面完成作業，減少高處作業項目。
+f. 經由施工程序之變更，優先施作永久構造物之上下設備或防墜設施。
+c. 設置護欄、護蓋。
+a. 張掛安全網。
+e. 設置警示線系統。
+b. 限制作業人員進入管制區。
+g. 使勞工佩掛安全帶。
+營造業職業安全衛生管理系統</t>
+        </is>
+      </c>
+      <c r="I664" s="2" t="inlineStr"/>
     </row>
     <row r="665" ht="108" customHeight="1">
       <c r="A665" s="2" t="n">
@@ -29288,8 +29997,17 @@
       <c r="G665" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H665" s="2" t="n"/>
-      <c r="I665" s="2" t="n"/>
+      <c r="H665" s="2" t="inlineStr">
+        <is>
+          <t>依據《營造安全衛生設施標準》第18條規定，勞工於屋頂作業時，其屋頂斜度大於 34 度（即高底比為二比三以上）或為滑溜之屋頂時，應設置適當之護欄。
+正確答案為：34 度。
+屋頂作業安全重點規定
+護欄與工作臺：斜度大於 34 度或滑溜之屋頂，應設置適當護欄、寬度在 40 公分以上之工作臺及充分之梯子。
+踏板設置：在易踏穿材料（如石綿板、FRP採光板等）構築之屋頂作業，應裝設寬度在 30 公分以上之安全步道或踏板。
+人員督導：雇主使勞工從事屋頂作業時，應指派專人（屋頂作業主管）在場督導。</t>
+        </is>
+      </c>
+      <c r="I665" s="2" t="inlineStr"/>
     </row>
     <row r="666" ht="108" customHeight="1">
       <c r="A666" s="2" t="n">
@@ -29323,8 +30041,13 @@
       <c r="G666" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H666" s="2" t="n"/>
-      <c r="I666" s="2" t="n"/>
+      <c r="H666" s="2" t="inlineStr">
+        <is>
+          <t>依營造安全衛生設施標準規定，於易踏穿材料構築之屋頂作業時，雇主應指派 (C) 屋頂作業主管 於現場辦理規定事項。
+行政院公報資訊網</t>
+        </is>
+      </c>
+      <c r="I666" s="2" t="inlineStr"/>
     </row>
     <row r="667" ht="108" customHeight="1">
       <c r="A667" s="2" t="n">
@@ -29358,8 +30081,18 @@
       <c r="G667" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H667" s="2" t="n"/>
-      <c r="I667" s="2" t="n"/>
+      <c r="H667" s="2" t="inlineStr">
+        <is>
+          <t>依《營造安全衛生設施標準》規定，於易踏穿材料構築之屋頂作業時，雇主應指派屋頂作業主管於現場辦理規定事項。
+相關法規重點
+指派人員：依據 營造安全衛生設施標準第18條 之規定，於易踏穿材料（如石綿板、塑膠浪板、採光罩等）構築之屋頂作業時，雇主應指派「屋頂作業主管」於現場坐鎮指揮。
+勞動部職業安全衛生署 現場辦理事項：
+決定作業方法，指揮勞工作業。
+實施檢點，檢查材料、工具、器具等，並汰換不良品。
+監督勞工確實使用個人防護具等安全措施。</t>
+        </is>
+      </c>
+      <c r="I667" s="2" t="inlineStr"/>
     </row>
     <row r="668" ht="108" customHeight="1">
       <c r="A668" s="2" t="n">
@@ -29393,8 +30126,12 @@
       <c r="G668" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H668" s="2" t="n"/>
-      <c r="I668" s="2" t="n"/>
+      <c r="H668" s="2" t="inlineStr">
+        <is>
+          <t>Google AI 摘要未抓取到，請手動補充。</t>
+        </is>
+      </c>
+      <c r="I668" s="2" t="inlineStr"/>
     </row>
     <row r="669" ht="108" customHeight="1">
       <c r="A669" s="2" t="n">
@@ -29428,8 +30165,13 @@
       <c r="G669" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H669" s="2" t="n"/>
-      <c r="I669" s="2" t="n"/>
+      <c r="H669" s="2" t="inlineStr">
+        <is>
+          <t>依據營造安全衛生設施標準第18條規定，於斜度大於三十四度或滑溜之屋頂從事作業時，所設置之適當工作臺寬度應在 40 公分以上。
+正確答案為：40 公分。</t>
+        </is>
+      </c>
+      <c r="I669" s="2" t="inlineStr"/>
     </row>
     <row r="670" ht="77.15000000000001" customHeight="1">
       <c r="A670" s="2" t="n">
@@ -29463,8 +30205,15 @@
       <c r="G670" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H670" s="2" t="n"/>
-      <c r="I670" s="2" t="n"/>
+      <c r="H670" s="2" t="inlineStr">
+        <is>
+          <t>依據營造安全衛生設施標準第18條規定，於易踏穿材料構築之屋頂作業時，應設置寬度在 30 公分以上之踏板。因此正確選項為 30 公分。
+重點摘述
+法規依據：營造安全衛生設施標準第18條
+規定要求：應先規劃安全通道，於屋架上設置適當強度，且寬度在 30 公分以上之踏板，並於下方適當範圍裝設堅固格柵或安全網等防墜設施。</t>
+        </is>
+      </c>
+      <c r="I670" s="2" t="inlineStr"/>
     </row>
     <row r="671" ht="108" customHeight="1">
       <c r="A671" s="2" t="n">
@@ -29498,8 +30247,13 @@
       <c r="G671" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H671" s="2" t="n"/>
-      <c r="I671" s="2" t="n"/>
+      <c r="H671" s="2" t="inlineStr">
+        <is>
+          <t>下列何者為非的答案是：降落傘。
+依據《營造安全衛生設施標準》規定，勞工有遭受墜落危險之虞者，應於該處設置護欄、護蓋或安全網等防護設備，「降落傘」並非規定設置的防護設備。</t>
+        </is>
+      </c>
+      <c r="I671" s="2" t="inlineStr"/>
     </row>
     <row r="672" ht="108" customHeight="1">
       <c r="A672" s="2" t="n">
@@ -29533,8 +30287,13 @@
       <c r="G672" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H672" s="2" t="n"/>
-      <c r="I672" s="2" t="n"/>
+      <c r="H672" s="2" t="inlineStr">
+        <is>
+          <t>正確答案是 (D) 以上皆是。
+根據《營造安全衛生設施標準》第20條規定，護欄前方 2 公尺內之樓板、地板，不得堆放任何物料、設備，並不得使用梯子、合梯、踏凳作業及停放車輛機械供勞工使用。因此，堆放鋼筋、使用合梯以及停放貨車下貨，在護欄旁 2 公尺內都是被禁止的行為。</t>
+        </is>
+      </c>
+      <c r="I672" s="2" t="inlineStr"/>
     </row>
     <row r="673" ht="108" customHeight="1">
       <c r="A673" s="2" t="n">
@@ -29568,8 +30327,17 @@
       <c r="G673" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H673" s="2" t="n"/>
-      <c r="I673" s="2" t="n"/>
+      <c r="H673" s="2" t="inlineStr">
+        <is>
+          <t>施作護欄前，最優先且正確的注意事項是先做防墜設施。
+在營造工地或高處作業中，拆除或施作任何防護構造物時，人員都會暴露於墜落風險中。因此，必須在確保人員有安全帶、母索或其他防墜設施保護的前提下，才能開始進行施作或拆改。
+為了幫助您確認相關法規與實務細節，請問：
+這是屬於職業安全衛生管理師/衛生成員的考試題庫嗎？
+您需要了解特定作業環境（如：施工架、鋼構作業或電梯井）的護欄施作規範嗎？
+我可以為您提供更詳細的法規依據與解題說明。 內容</t>
+        </is>
+      </c>
+      <c r="I673" s="2" t="inlineStr"/>
     </row>
     <row r="674" ht="108" customHeight="1">
       <c r="A674" s="2" t="n">
@@ -29603,8 +30371,13 @@
       <c r="G674" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H674" s="2" t="n"/>
-      <c r="I674" s="2" t="n"/>
+      <c r="H674" s="2" t="inlineStr">
+        <is>
+          <t>開口護欄應設置 (A) 上中欄杆及腳趾板。
+根據《營造安全衛生設施標準》規定，雇主設置之防護護欄應包含高度 90 公分以上之上欄杆、中間欄杆（中欄杆）、腳趾板及杆柱等構材，以防止人員與物體墜落。</t>
+        </is>
+      </c>
+      <c r="I674" s="2" t="inlineStr"/>
     </row>
     <row r="675" ht="108" customHeight="1">
       <c r="A675" s="2" t="n">
@@ -29638,8 +30411,14 @@
       <c r="G675" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H675" s="2" t="n"/>
-      <c r="I675" s="2" t="n"/>
+      <c r="H675" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+依據[營造安全衛生設施標準]第20條規定，設置之護欄高度應在 90公分 以上。
+正確答案為：90 公分。</t>
+        </is>
+      </c>
+      <c r="I675" s="2" t="inlineStr"/>
     </row>
     <row r="676" ht="108" customHeight="1">
       <c r="A676" s="2" t="n">
@@ -29673,8 +30452,16 @@
       <c r="G676" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H676" s="2" t="n"/>
-      <c r="I676" s="2" t="n"/>
+      <c r="H676" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+依營造安全衛生設施標準規定，設置之護欄其上欄杆、中欄杆及地盤面與樓板面間之上下開口距離，應不大於 55 公分（正確選項為 55 公分）。
+相關法規重點
+法規依據：依據勞動部中《營造安全衛生設施標準》第 20 條規定辦理。
+高度與開口：護欄應具有高度 90 公分以上之上欄杆、中間欄杆（或等效設備）、腳趾板及杆柱等構材；其上欄杆、中欄杆及地盤面與樓板面間之上下開口距離，均應不大於 55 公分。</t>
+        </is>
+      </c>
+      <c r="I676" s="2" t="inlineStr"/>
     </row>
     <row r="677" ht="108" customHeight="1">
       <c r="A677" s="2" t="n">
@@ -29708,8 +30495,16 @@
       <c r="G677" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H677" s="2" t="n"/>
-      <c r="I677" s="2" t="n"/>
+      <c r="H677" s="2" t="inlineStr">
+        <is>
+          <t>依營造安全衛生設施標準規定，設置護欄之腳趾板高度應在 10 公分以上。
+正確選項為：10 公分。
+相關法規重點
+法規依據：依據《營造安全衛生設施標準》第 20 條規定。
+規格限制：以木材構成之腳趾板，其高度應在 10 公分以上、厚度在 1 公分以上，並須密接於地盤面或樓板面舖設。</t>
+        </is>
+      </c>
+      <c r="I677" s="2" t="inlineStr"/>
     </row>
     <row r="678" ht="108" customHeight="1">
       <c r="A678" s="2" t="n">
@@ -29743,8 +30538,13 @@
       <c r="G678" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H678" s="2" t="n"/>
-      <c r="I678" s="2" t="n"/>
+      <c r="H678" s="2" t="inlineStr">
+        <is>
+          <t>依據營造安全衛生設施標準第20條規定，護欄以木材構成者，其上欄杆應平整，且其斷面應在 30 平方公分 以上。
+正確答案為：30 平方公分。</t>
+        </is>
+      </c>
+      <c r="I678" s="2" t="inlineStr"/>
     </row>
     <row r="679" ht="108" customHeight="1">
       <c r="A679" s="2" t="n">
@@ -29778,8 +30578,18 @@
       <c r="G679" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H679" s="2" t="n"/>
-      <c r="I679" s="2" t="n"/>
+      <c r="H679" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+依營造安全衛生設施標準第20條規定，護欄以木材構成者，其上欄杆斷面應在30平方公分以上，而題目所指的中欄杆斷面應在25平方公分以上。因此正確答案為 25 平方公分。
+木材護欄規格重點
+上欄杆：應平整，斷面在 30 平方公分以上。
+中欄杆：斷面在 25 平方公分以上。
+腳趾板：高度在 10 公分以上，厚度在 1 公分以上。
+杆柱：斷面在 30 平方公分以上，相鄰間距不得超過 2 公尺。</t>
+        </is>
+      </c>
+      <c r="I679" s="2" t="inlineStr"/>
     </row>
     <row r="680" ht="108" customHeight="1">
       <c r="A680" s="2" t="n">
@@ -29813,8 +30623,19 @@
       <c r="G680" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H680" s="2" t="n"/>
-      <c r="I680" s="2" t="n"/>
+      <c r="H680" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+依營造安全衛生設施標準規定，護欄以木材構成者，其杆柱相鄰間距不得超過 2 公尺。
+根據勞動部之《營造安全衛生設施標準》第20條規定，以木材構成之護欄規格：
+上欄杆斷面應在 30 平方公分以上。
+中欄杆斷面應在 25 平方公分以上。
+腳趾板高度應在 10 公分以上。
+杆柱斷面應在 30 平方公分以上，相鄰間距不得超過 2 公尺。
+法源法律網</t>
+        </is>
+      </c>
+      <c r="I680" s="2" t="inlineStr"/>
     </row>
     <row r="681" ht="108" customHeight="1">
       <c r="A681" s="2" t="n">
@@ -29848,8 +30669,19 @@
       <c r="G681" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H681" s="2" t="n"/>
-      <c r="I681" s="2" t="n"/>
+      <c r="H681" s="2" t="inlineStr">
+        <is>
+          <t>以上皆是（正確答案為 (D)）。
+護欄構件說明
+依據營造安全衛生設施標準第20條，合格護欄應包含下列構材：
+上欄杆：高度應在90公分以上。
+中間欄杆（中欄杆）：高度在35公分以上、55公分以下，或等效設備；上下開口距離不大於55公分。
+腳趾板：防止物料滾落或人員足部滑出開口。
+杆柱：支撐整體結構之直立桿件（如鋼管直徑須達3.8公分以上，間距不大於2.5公尺）。
+相關法規全文與細節可參閱勞動部。</t>
+        </is>
+      </c>
+      <c r="I681" s="2" t="inlineStr"/>
     </row>
     <row r="682" ht="108" customHeight="1">
       <c r="A682" s="2" t="n">
@@ -29883,8 +30715,15 @@
       <c r="G682" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H682" s="2" t="n"/>
-      <c r="I682" s="2" t="n"/>
+      <c r="H682" s="2" t="inlineStr">
+        <is>
+          <t>依營造安全衛生設施標準第20條規定，設置之護欄如以鋼管製成者，其上欄杆、中欄杆及杆柱之直徑均不得小於 3.8 公分（正確選項為 3.8 公分）。
+相關規定重點
+直徑限制：以鋼管構成之護欄，上欄杆、中欄杆及杆柱直徑皆不得小於 3.8 公分。
+間距限制：杆柱相鄰間距不得超過 2.5 公尺。</t>
+        </is>
+      </c>
+      <c r="I682" s="2" t="inlineStr"/>
     </row>
     <row r="683" ht="108" customHeight="1">
       <c r="A683" s="2" t="n">
@@ -29918,8 +30757,16 @@
       <c r="G683" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H683" s="2" t="n"/>
-      <c r="I683" s="2" t="n"/>
+      <c r="H683" s="2" t="inlineStr">
+        <is>
+          <t>依「營造安全衛生設施標準」規定，以鋼管製成之護欄，其杆柱相鄰間距不得超過 2.5 公尺。
+相關法規重點
+法規依據：《營造安全衛生設施標準》第20條第3款。
+直徑限制：上欄杆、中欄杆及杆柱之直徑均不得小於 3.8 公分。
+間距限制：杆柱相鄰間距不得超過 2.5 公尺。</t>
+        </is>
+      </c>
+      <c r="I683" s="2" t="inlineStr"/>
     </row>
     <row r="684" ht="108" customHeight="1">
       <c r="A684" s="2" t="n">
@@ -29953,8 +30800,18 @@
       <c r="G684" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H684" s="2" t="n"/>
-      <c r="I684" s="2" t="n"/>
+      <c r="H684" s="2" t="inlineStr">
+        <is>
+          <t>鋼管施工架頂層設置的護欄高度應在 90 公分 以上。
+正確選項為：(C) 90 公分。
+相關法規重點
+依據《營造安全衛生設施標準》第 20 條規定：
+高度規定：護欄高度應在 90 公分 以上。
+必備構材：應包括上欄杆、中欄杆（或等效設備）、腳趾板及杆柱（丁柱）等構材。
+開口距離：上欄杆、中欄杆與地盤面或樓板面間的上下開口距離，應不大於 55 公分。詳細法規內容可參考全國法規資料庫。</t>
+        </is>
+      </c>
+      <c r="I684" s="2" t="inlineStr"/>
     </row>
     <row r="685" ht="108" customHeight="1">
       <c r="A685" s="2" t="n">
@@ -29988,8 +30845,13 @@
       <c r="G685" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H685" s="2" t="n"/>
-      <c r="I685" s="2" t="n"/>
+      <c r="H685" s="2" t="inlineStr">
+        <is>
+          <t>依據營造安全衛生設施標準第20條規定，設置之護欄應使整個護欄具有抵抗於上欄杆之任何一點，於任何方向加以 75 公斤之荷重，而無顯著（明顯）變形之強度。
+正確答案為：(A) 75 公斤。</t>
+        </is>
+      </c>
+      <c r="I685" s="2" t="inlineStr"/>
     </row>
     <row r="686" ht="108" customHeight="1">
       <c r="A686" s="2" t="n">
@@ -30023,8 +30885,17 @@
       <c r="G686" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H686" s="2" t="n"/>
-      <c r="I686" s="2" t="n"/>
+      <c r="H686" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+依據營造安全衛生設施標準規定，空格應填入「上欄杆」。
+高雄市政府勞工局勞動檢查處
+完整的條文規定為：任何型式之護欄，其杆柱、杆件之強度及錨錠，應使整個護欄具有抵抗於上欄杆之任何一點，於任何方向加以 75 公斤之荷重，而無顯著變形之強度。
+高雄市政府勞工局勞動檢查處
+您可以參考全國法規資料庫以獲得更詳細的法規資訊。</t>
+        </is>
+      </c>
+      <c r="I686" s="2" t="inlineStr"/>
     </row>
     <row r="687" ht="108" customHeight="1">
       <c r="A687" s="2" t="n">
@@ -30058,8 +30929,14 @@
       <c r="G687" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H687" s="2" t="n"/>
-      <c r="I687" s="2" t="n"/>
+      <c r="H687" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+依營造安全衛生設施標準第20條規定，以金屬網、塑膠網遮覆上欄杆、中欄杆與樓板或地板間之空隙者，其網目大小不得超過 15平方公分。
+正確選項為：15 平方公分。</t>
+        </is>
+      </c>
+      <c r="I687" s="2" t="inlineStr"/>
     </row>
     <row r="688" ht="108" customHeight="1">
       <c r="A688" s="2" t="n">
@@ -30093,8 +30970,13 @@
       <c r="G688" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H688" s="2" t="n"/>
-      <c r="I688" s="2" t="n"/>
+      <c r="H688" s="2" t="inlineStr">
+        <is>
+          <t>答案是 15 度。
+根據《營造安全衛生設施標準》第 24 條規定：雇主對於坡度小於 15 度之勞工作業區域，距離開口部分、開放邊線或其他有墜落之虞之地點超過 2 公尺時，得設置警示線、管制通行區，代替護欄、護蓋或安全網之設置。</t>
+        </is>
+      </c>
+      <c r="I688" s="2" t="inlineStr"/>
     </row>
     <row r="689" ht="108" customHeight="1">
       <c r="A689" s="2" t="n">
@@ -30128,8 +31010,14 @@
       <c r="G689" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H689" s="2" t="n"/>
-      <c r="I689" s="2" t="n"/>
+      <c r="H689" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+依據[營造安全衛生設施標準]第24條規定，雇主設置警示線、管制通行區以代替護欄、護蓋或安全網時，應每隔 2.5 公尺以下設置高度 90 公分以上之杆柱（丁柱）。
+正確答案為：2.5 公尺。</t>
+        </is>
+      </c>
+      <c r="I689" s="2" t="inlineStr"/>
     </row>
     <row r="690" ht="108" customHeight="1">
       <c r="A690" s="2" t="n">
@@ -30163,8 +31051,13 @@
       <c r="G690" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H690" s="2" t="n"/>
-      <c r="I690" s="2" t="n"/>
+      <c r="H690" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+依據營造安全衛生設施標準第24條規定，警示繩、帶之最小張力強度至少應在 225 公斤以上。</t>
+        </is>
+      </c>
+      <c r="I690" s="2" t="inlineStr"/>
     </row>
     <row r="691" ht="108" customHeight="1">
       <c r="A691" s="2" t="n">
@@ -30198,8 +31091,12 @@
       <c r="G691" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H691" s="2" t="n"/>
-      <c r="I691" s="2" t="n"/>
+      <c r="H691" s="2" t="inlineStr">
+        <is>
+          <t>依據營造安全衛生設施標準第21條規定，臨時性開口處使用之護蓋，表面應漆以黃色並書以警告訊息。</t>
+        </is>
+      </c>
+      <c r="I691" s="2" t="inlineStr"/>
     </row>
     <row r="692" ht="108" customHeight="1">
       <c r="A692" s="2" t="n">
@@ -30233,8 +31130,12 @@
       <c r="G692" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H692" s="2" t="n"/>
-      <c r="I692" s="2" t="n"/>
+      <c r="H692" s="2" t="inlineStr">
+        <is>
+          <t>依據《營造安全衛生設施標準》第21條規定，設置之護蓋為柵狀構造者，柵條間距不得大於 3 公分。正確答案為 3 公分。</t>
+        </is>
+      </c>
+      <c r="I692" s="2" t="inlineStr"/>
     </row>
     <row r="693" ht="108" customHeight="1">
       <c r="A693" s="2" t="n">
@@ -30269,8 +31170,21 @@
       <c r="G693" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H693" s="2" t="n"/>
-      <c r="I693" s="2" t="n"/>
+      <c r="H693" s="2" t="inlineStr">
+        <is>
+          <t>依營造安全衛生設施標準第 21 條規定，正確的選項組合為 a.b.c.d.e。
+各項敘述解析：
+a. 正確：應具有能使人員及車輛安全通過之強度。
+b. 正確：應以有效方法防止滑溜、掉落、掀出或移動。
+c. 正確：供車輛通行者，得以車輛後軸載重之 2 倍設計之，並不得妨礙車輛之正常通行。
+d. 正確：為柵狀構造者，柵條間隔不得大於 3 公分。
+e. 正確：上面不得放置機動設備或超過其設計強度之重物。
+f. 錯誤：依規定臨時性開口處使用之護蓋，表面應漆以黃色（而非綠色），並書以警告訊息。
+mail.ncku.edu.tw . 依營造安全衛生設施標準21 條規定,有關下列護蓋之敘述 ...
+2024年10月7日 — 依營造安全衛生設施標準21 條規定,有關下列護蓋之敘述,何者正確?a.應具有能使人員及車輛安全通過之強度b.應以有效方法防止滑溜、掉落、掀出或移動c.供車輛通行者,得以車輛後軸載重之2倍設計之,並不得妨礙車輛之正常通行d.為柵狀構造者,柵條間隔不得大於3 公分...</t>
+        </is>
+      </c>
+      <c r="I693" s="2" t="inlineStr"/>
     </row>
     <row r="694" ht="92.59999999999999" customHeight="1">
       <c r="A694" s="2" t="n">

--- a/salf/丙種職業安全衛生業務主管題庫.xlsx
+++ b/salf/丙種職業安全衛生業務主管題庫.xlsx
@@ -31218,8 +31218,13 @@
       <c r="G694" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H694" s="2" t="n"/>
-      <c r="I694" s="2" t="n"/>
+      <c r="H694" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+設置安全網時，其工作面至安全網架設平面之攔截高度，不得超過 7 公尺（依據營造安全衛生設施標準第22條規定）。因此正確答案為 7 公尺。</t>
+        </is>
+      </c>
+      <c r="I694" s="2" t="inlineStr"/>
     </row>
     <row r="695" ht="92.59999999999999" customHeight="1">
       <c r="A695" s="2" t="n">
@@ -31253,8 +31258,16 @@
       <c r="G695" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H695" s="2" t="n"/>
-      <c r="I695" s="2" t="n"/>
+      <c r="H695" s="2" t="inlineStr">
+        <is>
+          <t>根據台灣《營造安全衛生設施標準》及相關職業安全衛生法令規定，設置之安全網及其組件應每天在作業前進行檢查。
+安全網檢查時機
+每天作業前：由工地主管或作業主管進行目視檢查，確認無破損、鬆脫或移位。
+強風、大雨或地震後：屬於特別檢查，必須在重新作業前全面確認結構安全。
+物體掉落衝擊後：若有大型物體或人員掉落至網上，不論時間長短，都必須立即檢查並汰換受損組件。</t>
+        </is>
+      </c>
+      <c r="I695" s="2" t="inlineStr"/>
     </row>
     <row r="696" ht="108" customHeight="1">
       <c r="A696" s="2" t="n">
@@ -31288,8 +31301,18 @@
       <c r="G696" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H696" s="2" t="n"/>
-      <c r="I696" s="2" t="n"/>
+      <c r="H696" s="2" t="inlineStr">
+        <is>
+          <t>有誤的選項是：發現安全網有破損時，應即刻以防塵網修補後才能繼續使用。
+錯誤原因說明
+正確做法：安全網若發生破損，應予更換新品或依規定修繕至符合強度標準，而不是使用無結構強度的「防塵網」來修補。
+其他選項皆正確：
+安全網之材料及張掛方式應符合國家標準之規定。
+攔截高度在 1.5 公尺以下者，至少應延伸 2.5 公尺（防止拋物線效應）。
+工作面至安全網架設平面之攔截高度不得超過 7 公尺。</t>
+        </is>
+      </c>
+      <c r="I696" s="2" t="inlineStr"/>
     </row>
     <row r="697" ht="92.59999999999999" customHeight="1">
       <c r="A697" s="2" t="n">
@@ -31323,8 +31346,18 @@
       <c r="G697" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H697" s="2" t="n"/>
-      <c r="I697" s="2" t="n"/>
+      <c r="H697" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+以上皆是為正確答案。
+依據《營造安全衛生設施標準》第22條規定，使用於結構物四周之安全網，為足以涵蓋勞工墜落時之拋物線預測路徑範圍，應依下列規定延伸適當之距離：
+攔截高度在 1.5 公尺以下者，至少應延伸 2.5 公尺。
+攔截高度超過 1.5 公尺且在 3 公尺以下者，至少應延伸 3 公尺。
+攔截高度超過 3 公尺者，至少應延伸 4 公尺。
+選項中的各項敘述皆符合法規標準。</t>
+        </is>
+      </c>
+      <c r="I697" s="2" t="inlineStr"/>
     </row>
     <row r="698" ht="92.59999999999999" customHeight="1">
       <c r="A698" s="2" t="n">
@@ -31358,8 +31391,13 @@
       <c r="G698" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H698" s="2" t="n"/>
-      <c r="I698" s="2" t="n"/>
+      <c r="H698" s="2" t="inlineStr">
+        <is>
+          <t>安全網如遇有「顏色不均勻者」的情形，得繼續使用。
+依據相關營造安全衛生標準，若安全網有「經測試強度未達規定者」、「經電焊火花、銳利物切割者」或「強度標示不明確者」等情形，皆應停止使用並廢棄；而顏色不均勻並不影響安全網的結構強度，因此符合得繼續使用的條件。</t>
+        </is>
+      </c>
+      <c r="I698" s="2" t="inlineStr"/>
     </row>
     <row r="699" ht="108" customHeight="1">
       <c r="A699" s="2" t="n">
@@ -31393,8 +31431,13 @@
       <c r="G699" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H699" s="2" t="n"/>
-      <c r="I699" s="2" t="n"/>
+      <c r="H699" s="2" t="inlineStr">
+        <is>
+          <t>安全母索不得以麻繩為之構成。
+依據《營造安全衛生設施標準》第23條規定，安全母索得由鋼索、尼龍繩索或合成纖維之材質構成，其最小斷裂強度應在二千三百公斤以上。天然材質如麻繩強度不足且易受潮腐朽，因此不得使用。</t>
+        </is>
+      </c>
+      <c r="I699" s="2" t="inlineStr"/>
     </row>
     <row r="700" ht="108" customHeight="1">
       <c r="A700" s="2" t="n">
@@ -31428,8 +31471,15 @@
       <c r="G700" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H700" s="2" t="n"/>
-      <c r="I700" s="2" t="n"/>
+      <c r="H700" s="2" t="inlineStr">
+        <is>
+          <t>安全母索的最小斷裂強度為 2300 公斤以上。
+根據台灣勞動部《營造安全衛生設施標準第 23 條》之規定：
+安全母索材質與強度：可由鋼索、尼龍繩索或合成纖維之材質構成，其最小斷裂強度應在二千三百公斤以上。
+錨錠承載力：安全帶或安全母索繫固之錨錠，至少應能承受每人二千三百公斤之拉力。</t>
+        </is>
+      </c>
+      <c r="I700" s="2" t="inlineStr"/>
     </row>
     <row r="701" ht="108" customHeight="1">
       <c r="A701" s="2" t="n">
@@ -31463,8 +31513,13 @@
       <c r="G701" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H701" s="2" t="n"/>
-      <c r="I701" s="2" t="n"/>
+      <c r="H701" s="2" t="inlineStr">
+        <is>
+          <t>正確答案是：3.8 公尺。
+根據台灣的《營造安全衛生設施標準》第 23 條規定，水平安全母索之設置應辦理事項第一款明確指出：「水平安全母索之設置高度應大於三點八公尺」。</t>
+        </is>
+      </c>
+      <c r="I701" s="2" t="inlineStr"/>
     </row>
     <row r="702" ht="108" customHeight="1">
       <c r="A702" s="2" t="n">
@@ -31498,8 +31553,17 @@
       <c r="G702" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H702" s="2" t="n"/>
-      <c r="I702" s="2" t="n"/>
+      <c r="H702" s="2" t="inlineStr">
+        <is>
+          <t>相鄰兩中間支柱間（或錨錠點間）之安全母索僅能繫掛 1 條安全帶。
+根據《營造安全衛生設施標準》規定：
+支柱與另一繫掛點間、相鄰二支柱間或母索支柱間之安全母索僅能繫掛一條安全帶。
+每條安全母索能繫掛安全帶之條數，應標示於母索錨錠端。
+桃園市政府
+正確答案為：1 條。</t>
+        </is>
+      </c>
+      <c r="I702" s="2" t="inlineStr"/>
     </row>
     <row r="703" ht="108" customHeight="1">
       <c r="A703" s="2" t="n">
@@ -31533,8 +31597,15 @@
       <c r="G703" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H703" s="2" t="n"/>
-      <c r="I703" s="2" t="n"/>
+      <c r="H703" s="2" t="inlineStr">
+        <is>
+          <t>本題答案為：相鄰兩中間杆柱間之母索可繫掛兩條安全帶（此選項有誤）。
+根據我國《營造安全衛生設施標準》及高處作業安全指引，關於屋頂作業垂直或水平母索的設置與使用規範如下：
+❌ 錯誤原因：相鄰兩中間杆柱間的每條母索，只能繫掛一條安全帶。因為若同時繫掛兩條（或以上）安全帶，當其中一人墜落時，產生的拉力與衝擊波會導致母索劇烈晃動或斷裂，進而將另一名人員一併拉下，造成更嚴重的二次災害。
+⭕ 其他選項皆正確：母索確實應於適當間隔設置中間杆柱以維持張力與強度；各項構件（如母索、錨錠、安全帶等）必須定期檢查；在屋頂等高處移動時，應採用全身背負式安全帶配合捲揚式防墜器以確保萬無一失。</t>
+        </is>
+      </c>
+      <c r="I703" s="2" t="inlineStr"/>
     </row>
     <row r="704" ht="108" customHeight="1">
       <c r="A704" s="2" t="n">
@@ -31568,8 +31639,15 @@
       <c r="G704" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H704" s="2" t="n"/>
-      <c r="I704" s="2" t="n"/>
+      <c r="H704" s="2" t="inlineStr">
+        <is>
+          <t>答案為以上皆是。
+根據《營造安全衛生設施標準》規定，垂直安全母索之設置應符合下列事項：
+安全母索之下端應有防止安全帶鎖扣自尾端脫落之設施。
+每條安全母索應僅提供一名勞工使用，但勞工作業或爬昇位置之水平間距在1公尺以下者，得二人共用一條安全母索。</t>
+        </is>
+      </c>
+      <c r="I704" s="2" t="inlineStr"/>
     </row>
     <row r="705" ht="108" customHeight="1">
       <c r="A705" s="2" t="n">
@@ -31603,8 +31681,18 @@
       <c r="G705" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H705" s="2" t="n"/>
-      <c r="I705" s="2" t="n"/>
+      <c r="H705" s="2" t="inlineStr">
+        <is>
+          <t>「錨錠強度需在 800 kg 以上」是不正確的敘述。
+根據營造安全衛生設施標準第 23 條規定，安全帶或安全母索繫固之錨錠，至少應能承受每人 2300 公斤之拉力，而不是 800 公斤。
+心瓦佐料庫 各項設置規定解析
+最小斷裂強度：安全母索的最小斷裂強度應在 2300 公斤以上（正確）。
+錨錠強度：繫固之錨錠至少應能承受每人 2300 公斤之拉力（選項寫 800 kg，故不正確）。
+共用母索限制：每條安全母索原則上僅供 1 人使用；但作業或爬升位置之水平間距在 1 公尺以下者，得 2 人共用一條（正確）。
+末端防脫落設施：垂直安全母索下端應有防止安全帶鎖扣自尾端脫落之設施（正確）。</t>
+        </is>
+      </c>
+      <c r="I705" s="2" t="inlineStr"/>
     </row>
     <row r="706" ht="77.15000000000001" customHeight="1">
       <c r="A706" s="2" t="n">
@@ -31638,8 +31726,22 @@
       <c r="G706" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H706" s="2" t="n"/>
-      <c r="I706" s="2" t="n"/>
+      <c r="H706" s="2" t="inlineStr">
+        <is>
+          <t>「高空工作車」非屬職業安全衛生法中所稱之具有危險性之機械。
+Facebook
+·百禾智庫粉絲團【職業安全衛生管理數位學習領導品牌】 依據《職業安全衛生法施行細則》第22條規定，具危險性之機械包含：
+固定式起重機
+移動式起重機
+人字臂起重桿
+營建用升降機
+營建用提升機
+吊籠
+立法院全球資訊網
+選項中的起重機、營建用升降機、吊籠均名列其中，而高空工作車則屬於車輛系營建機械或經公告之「其他特定機械」，並非傳統法規定義之「危險性機械」。</t>
+        </is>
+      </c>
+      <c r="I706" s="2" t="inlineStr"/>
     </row>
     <row r="707" ht="77.15000000000001" customHeight="1">
       <c r="A707" s="2" t="n">
@@ -31673,8 +31775,14 @@
       <c r="G707" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H707" s="2" t="n"/>
-      <c r="I707" s="2" t="n"/>
+      <c r="H707" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+危險性機械所定一定容量以上斯達卡式起重機為一公噸。
+依據《危險性機械及設備安全檢查規則》規定，固定式起重機中之斯達卡式起重機，其危險性機械之一定容量標準為吊升荷重在一公噸以上。</t>
+        </is>
+      </c>
+      <c r="I707" s="2" t="inlineStr"/>
     </row>
     <row r="708" ht="77.15000000000001" customHeight="1">
       <c r="A708" s="2" t="n">
@@ -31708,8 +31816,17 @@
       <c r="G708" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H708" s="2" t="n"/>
-      <c r="I708" s="2" t="n"/>
+      <c r="H708" s="2" t="inlineStr">
+        <is>
+          <t>是的，這題的答案為「以上皆是」（或該選項所敘述的定義完全正確）。
+根據勞動部《起重升降機具安全規則》中的定義，人字臂起重桿係指：
+以動力吊升貨物為目的
+具有主柱、吊桿
+另行裝置原動機，並以鋼索操作升降之機械裝置
+此定義完全符合您題目的敘述內容。</t>
+        </is>
+      </c>
+      <c r="I708" s="2" t="inlineStr"/>
     </row>
     <row r="709" ht="77.15000000000001" customHeight="1">
       <c r="A709" s="2" t="n">
@@ -31743,8 +31860,12 @@
       <c r="G709" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H709" s="2" t="n"/>
-      <c r="I709" s="2" t="n"/>
+      <c r="H709" s="2" t="inlineStr">
+        <is>
+          <t>Google AI 摘要未抓取到，請手動補充。</t>
+        </is>
+      </c>
+      <c r="I709" s="2" t="inlineStr"/>
     </row>
     <row r="710" ht="77.15000000000001" customHeight="1">
       <c r="A710" s="2" t="n">
@@ -31778,8 +31899,14 @@
       <c r="G710" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H710" s="2" t="n"/>
-      <c r="I710" s="2" t="n"/>
+      <c r="H710" s="2" t="inlineStr">
+        <is>
+          <t>危險性機械及設備安全檢查規則中所適用之營建用提升機，係指導軌或升降路之高度在 20 公尺以上之營建用提升機。
+正確答案為：20 公尺。
+依據《危險性機械及設備安全檢查規則》第3條規定，營建用提升機係指其導軌或升降路之垂直高度達 20 公尺以上的設備。</t>
+        </is>
+      </c>
+      <c r="I710" s="2" t="inlineStr"/>
     </row>
     <row r="711" ht="77.15000000000001" customHeight="1">
       <c r="A711" s="2" t="n">
@@ -31813,8 +31940,20 @@
       <c r="G711" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H711" s="2" t="n"/>
-      <c r="I711" s="2" t="n"/>
+      <c r="H711" s="2" t="inlineStr">
+        <is>
+          <t>依危險性機械及設備安全檢查規則規定，型式檢定非屬鍋爐之檢查種類。
+鍋爐的檢查種類
+依規定，鍋爐之安全檢查項目包含：
+構造檢查
+定期檢查
+重新檢查
+其他如型式檢查、竣工檢查、變更檢查、熔接檢查等
+「型式檢定」係針對特定機械、器具之產品品質與安全標準所實施之檢定，非危險性設備（鍋爐）之法定檢查種類。
+iPEDIA 百科</t>
+        </is>
+      </c>
+      <c r="I711" s="2" t="inlineStr"/>
     </row>
     <row r="712" ht="92.59999999999999" customHeight="1">
       <c r="A712" s="2" t="n">
@@ -31848,8 +31987,17 @@
       <c r="G712" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H712" s="2" t="n"/>
-      <c r="I712" s="2" t="n"/>
+      <c r="H712" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+下列何者不是具有危險性之設備之檢查種類，答案是 (C) 型式檢定。
+說明
+型式檢定：通常適用於「具有危險性之機械」（如固定式起重機、移動式起重機、吊籠等）或特定防爆電氣設備等的合格證明程序。
+構造檢查、型式檢查與定期檢查均屬於「具有危險性之設備」（如鍋爐、壓力容器、高壓氣體特定設備、高壓氣體容器）之法定檢查種類。
+iPEDIA 百科</t>
+        </is>
+      </c>
+      <c r="I712" s="2" t="inlineStr"/>
     </row>
     <row r="713" ht="77.15000000000001" customHeight="1">
       <c r="A713" s="2" t="n">
@@ -31883,8 +32031,16 @@
       <c r="G713" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H713" s="2" t="n"/>
-      <c r="I713" s="2" t="n"/>
+      <c r="H713" s="2" t="inlineStr">
+        <is>
+          <t>依據《危險性機械及設備安全檢查規則》規定，雇主於鍋爐設置完成時，應向檢查機構申請竣工檢查；未經竣工檢查合格，不得使用。
+相關規定重點
+檢查項目：竣工檢查
+法源依據：危險性機械及設備安全檢查規則第81條：「雇主於鍋爐設置完成時，應向檢查機構申請竣工檢查；未經竣工檢查合格，不得使用。」
+注意事項：檢查機構實施竣工檢查時，雇主或其指派人員應在場。</t>
+        </is>
+      </c>
+      <c r="I713" s="2" t="inlineStr"/>
     </row>
     <row r="714" ht="92.59999999999999" customHeight="1">
       <c r="A714" s="2" t="n">
@@ -31918,8 +32074,22 @@
       <c r="G714" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H714" s="2" t="n"/>
-      <c r="I714" s="2" t="n"/>
+      <c r="H714" s="2" t="inlineStr">
+        <is>
+          <t>「起重機」與「給水償」（應為給水閥）非鍋爐常用之安全裝置。
+若這是一題選擇題，最明顯的錯誤選項是起重機（起重機屬於物料搬運機械，並非鍋爐的安全防護裝置）。
+以下為您整理鍋爐常見的安全裝置與常見字詞修正：
+鍋爐常用之安全裝置
+安全閥（題目錯字：安全閱）：當鍋爐內壓力超過規定值時，會自動開啟洩壓，防止鍋爐因超壓而爆炸。
+水位高低警報器：當鍋爐水位過高或過低時會發出警報，提醒操作人員，防止滿水或缺水導致燒乾爆炸。
+壓力錶：用來指示鍋爐內部的實際蒸汽壓力。
+易熔塞：當鍋爐嚴重缺水、溫度過高時會熔化，讓蒸汽噴出滅火並降壓，保護鍋爐。
+題目中的其他名詞辨析
+吹洩閥 / 吹絀閥（題目錯字：吹混閱）：用於排出鍋爐底部的泥沙、水垢及濃縮水，維持鍋爐水質。
+給水閥（題目錯字：給水償）：控制進入鍋爐內水量的閥門。</t>
+        </is>
+      </c>
+      <c r="I714" s="2" t="inlineStr"/>
     </row>
     <row r="715" ht="108" customHeight="1">
       <c r="A715" s="2" t="n">
@@ -31953,8 +32123,15 @@
       <c r="G715" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H715" s="2" t="n"/>
-      <c r="I715" s="2" t="n"/>
+      <c r="H715" s="2" t="inlineStr">
+        <is>
+          <t>在高壓電線周圍附近從事吊掛作業、施工架組配作業或使用高空工作車而有碰觸高壓電線之虞時，雇主應於施工前協調台電安裝絕緣防護套管（或採取移開電路、斷電停電等預防感電之安全設施）。
+作業安全重點
+保持安全距離：應依規定保持接近界限距離，設置防護裝備或監視人員。
+預防感電災害：施工前務必通報並協調 台灣電力公司進行斷電、移設或加裝絕緣保護。</t>
+        </is>
+      </c>
+      <c r="I715" s="2" t="inlineStr"/>
     </row>
     <row r="716" ht="77.15000000000001" customHeight="1">
       <c r="A716" s="2" t="n">
@@ -31988,8 +32165,14 @@
       <c r="G716" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H716" s="2" t="n"/>
-      <c r="I716" s="2" t="n"/>
+      <c r="H716" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+依據《起重升降機具安全規則》第5條之規定，固定式起重機、移動式起重機、人字臂起重桿等之構造及材質，所能吊升之最大荷重稱為吊升荷重。
+因此，正確答案為：吊升荷重。</t>
+        </is>
+      </c>
+      <c r="I716" s="2" t="inlineStr"/>
     </row>
     <row r="717" ht="77.15000000000001" customHeight="1">
       <c r="A717" s="2" t="n">
@@ -32023,8 +32206,18 @@
       <c r="G717" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H717" s="2" t="n"/>
-      <c r="I717" s="2" t="n"/>
+      <c r="H717" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+依據《起重升降機具安全規則》規定，扣除吊鉤、抓斗等吊具重量後所得之荷重稱為額定荷重。正確答案為 額定荷重。
+Facebook
+·工安百科
+重點解析
+額定荷重：指依起重機構造、材質、伸臂傾斜角、長度及吊運車位置等，決定其足以承受之最大荷重，再扣除吊鉤、抓斗等吊具重量後的淨荷重。
+吊升荷重：指機械構造與材質所能吊升之最大總荷重（未扣除吊具重量）。</t>
+        </is>
+      </c>
+      <c r="I717" s="2" t="inlineStr"/>
     </row>
     <row r="718" ht="77.15000000000001" customHeight="1">
       <c r="A718" s="2" t="n">
@@ -32058,8 +32251,15 @@
       <c r="G718" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H718" s="2" t="n"/>
-      <c r="I718" s="2" t="n"/>
+      <c r="H718" s="2" t="inlineStr">
+        <is>
+          <t>雇主對於移動式起重機之使用，不得超過其額定荷重（答案選「額定荷重」）。
+危險性機械及設備代檢機構
+依據《起重升降機具安全規則》第23條規定：「雇主對於移動式起重機之使用，不得超過額定荷重。」
+危險性機械及設備代檢機構</t>
+        </is>
+      </c>
+      <c r="I718" s="2" t="inlineStr"/>
     </row>
     <row r="719" ht="77.15000000000001" customHeight="1">
       <c r="A719" s="2" t="n">
@@ -32093,8 +32293,13 @@
       <c r="G719" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H719" s="2" t="n"/>
-      <c r="I719" s="2" t="n"/>
+      <c r="H719" s="2" t="inlineStr">
+        <is>
+          <t>依《職業安全衛生管理辦法》規定，正確答案為：檢點。
+根據 職業安全衛生管理辦法第 53 條 規定：「雇主對移動式起重機，應於每日作業前對過捲預防裝置、過負荷警報裝置、制動器、離合器、控制裝置及其他警報裝置之性能，實施檢點。」</t>
+        </is>
+      </c>
+      <c r="I719" s="2" t="inlineStr"/>
     </row>
     <row r="720" ht="77.15000000000001" customHeight="1">
       <c r="A720" s="2" t="n">
@@ -32128,8 +32333,17 @@
       <c r="G720" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H720" s="2" t="n"/>
-      <c r="I720" s="2" t="n"/>
+      <c r="H720" s="2" t="inlineStr">
+        <is>
+          <t>根據台灣的勞安相關法規與安全操作標準，開始進行吊掛作業時，起吊掛物離開地面約 30 公分 時必須暫停下來檢查。
+這個步驟通常被稱為「試吊」或「微起吊」，目的在於確認以下安全事項：
+吊掛物的重心是否穩定、有無傾斜。
+吊具（如鋼索、吊帶）是否有滑脫或受力不均的狀況。
+起重機的剎車系統是否正常運作。
+確定一切安全無誤後，才可以繼續向上提升並進行移動。</t>
+        </is>
+      </c>
+      <c r="I720" s="2" t="inlineStr"/>
     </row>
     <row r="721" ht="108" customHeight="1">
       <c r="A721" s="2" t="n">

--- a/salf/丙種職業安全衛生業務主管題庫.xlsx
+++ b/salf/丙種職業安全衛生業務主管題庫.xlsx
@@ -32377,8 +32377,17 @@
       <c r="G721" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H721" s="2" t="n"/>
-      <c r="I721" s="2" t="n"/>
+      <c r="H721" s="2" t="inlineStr">
+        <is>
+          <t>不正確的敘述為：「可供人員搭乘、吊升或降落」。
+依據《職業安全衛生設施規則》第 155-1 條規定，雇主使勞工以捲揚機等吊運物料時，嚴禁以該等設備供人員搭乘、吊升或降落。
+相關正確規定
+安裝作業：安裝前須核對並確認設計資料及強度計算書。
+荷重與裝置：吊掛重量不得超過設備最高負荷，並應設有防止過捲及防止超過負荷裝置。
+安全距離：禁止人員進入吊掛物下方，以防墜落物砸傷。</t>
+        </is>
+      </c>
+      <c r="I721" s="2" t="inlineStr"/>
     </row>
     <row r="722" ht="77.15000000000001" customHeight="1">
       <c r="A722" s="2" t="n">
@@ -32412,8 +32421,15 @@
       <c r="G722" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H722" s="2" t="n"/>
-      <c r="I722" s="2" t="n"/>
+      <c r="H722" s="2" t="inlineStr">
+        <is>
+          <t>一般情況下，起重機吊運物件時，吊物上不可載人。
+安全規範重點
+以吊物為限：依據相關職業安全衛生法規（如起重升降機具安全規則），固定式或移動式起重機在一般作業時，僅能用來吊運物件與貨物。
+嚴禁違規搭乘：除符合特定例外規定（如無其他安全作業替代方法而使用專用合格「搭乘設備」進行短暫、臨時性作業外），一般吊物上嚴禁站立或乘坐任何人員。</t>
+        </is>
+      </c>
+      <c r="I722" s="2" t="inlineStr"/>
     </row>
     <row r="723" ht="92.59999999999999" customHeight="1">
       <c r="A723" s="2" t="n">
@@ -32447,8 +32463,19 @@
       <c r="G723" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H723" s="2" t="n"/>
-      <c r="I723" s="2" t="n"/>
+      <c r="H723" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+一般所謂的吊車是屬於起重機。
+機械類別說明
+起重機：專門用來垂直吊升與水平移動重物的機械，常見的移動式吊車便屬於此類。
+堆高機：用於廠房或倉庫中裝卸、堆疊貨物的搬運機械。
+昇空車（升空車）：又稱高空工作車，是用來載運人員至高處進行作業的機械。
+搬運車：主要用於平面或短距離搬運貨物的車輛。
+myMKC管理知識中心</t>
+        </is>
+      </c>
+      <c r="I723" s="2" t="inlineStr"/>
     </row>
     <row r="724" ht="77.15000000000001" customHeight="1">
       <c r="A724" s="2" t="n">
@@ -32482,8 +32509,17 @@
       <c r="G724" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H724" s="2" t="n"/>
-      <c r="I724" s="2" t="n"/>
+      <c r="H724" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+應確認起重機具之額定荷重，並使所吊荷物之重量在此荷重值以下。正確答案為：(B) 額定荷重。
+依據《起重升降機具安全規則》第63條規定，雇主對於使用起重機具從事吊掛作業之勞工，應使其辦理下列事項：
+確認起重機具之額定荷重，使所吊荷物之重量在額定荷重值以下。
+檢視荷物之形狀、大小及材質等特性，以估算荷物重量，或查明其實際重量，並選用適當吊掛用具及採取正確吊掛方法。
+估測荷物重心位置，以決定吊具懸掛位置。</t>
+        </is>
+      </c>
+      <c r="I724" s="2" t="inlineStr"/>
     </row>
     <row r="725" ht="77.15000000000001" customHeight="1">
       <c r="A725" s="2" t="n">
@@ -32519,8 +32555,15 @@
       <c r="G725" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H725" s="2" t="n"/>
-      <c r="I725" s="2" t="n"/>
+      <c r="H725" s="2" t="inlineStr">
+        <is>
+          <t>答案是：破裂板（選項 D）。
+原因說明
+破裂板（Bursting disc）：是用來防止壓力容器或管線內部壓力過高而發生爆炸的壓力容器安全裝置（屬於鍋爐及壓力容器的安全配件），而非起重機的安全裝置。
+過負荷預防裝置、過捲預防裝置與防滑舌片（防止吊鉤上的吊掛物脫落的防脫舌片）皆為起重機常見或規定的安全／防護裝置。</t>
+        </is>
+      </c>
+      <c r="I725" s="2" t="inlineStr"/>
     </row>
     <row r="726" ht="77.15000000000001" customHeight="1">
       <c r="A726" s="2" t="n">
@@ -32554,8 +32597,15 @@
       <c r="G726" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H726" s="2" t="n"/>
-      <c r="I726" s="2" t="n"/>
+      <c r="H726" s="2" t="inlineStr">
+        <is>
+          <t>吊掛用鋼索之張角愈大，則張力亦愈大。
+原因解析
+當吊掛角度（張角）變大時，鋼索分擔垂直重力的分力會減小，導致鋼索所承受的實際張力（Tension）反而顯著增加。
+因此，在進行吊掛作業時，應盡量保持較小的張角，以避免鋼索張力過大而發生斷裂危險。</t>
+        </is>
+      </c>
+      <c r="I726" s="2" t="inlineStr"/>
     </row>
     <row r="727" ht="77.15000000000001" customHeight="1">
       <c r="A727" s="2" t="n">
@@ -32589,8 +32639,18 @@
       <c r="G727" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H727" s="2" t="n"/>
-      <c r="I727" s="2" t="n"/>
+      <c r="H727" s="2" t="inlineStr">
+        <is>
+          <t>根據勞動部職業安全衛生相關法規與安全操作指引，吊掛材料移動時，必須保持離開地面 2 公尺以上的高度，確認移動路徑上沒有障礙物、架空電線等安全威脅後，才可開始移動。
+因此，正確答案應該選擇 2 公尺。
+如果想進一步了解，我可以為您提供：
+吊掛作業的完整安全檢查步驟
+遇到架空電線時的安全距離規範
+相關法規的處罰與責任規定
+請問您需要哪方面的詳細資訊呢？ 內容</t>
+        </is>
+      </c>
+      <c r="I727" s="2" t="inlineStr"/>
     </row>
     <row r="728" ht="77.15000000000001" customHeight="1">
       <c r="A728" s="2" t="n">
@@ -32624,8 +32684,16 @@
       <c r="G728" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H728" s="2" t="n"/>
-      <c r="I728" s="2" t="n"/>
+      <c r="H728" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+從事吊掛作業時，吊掛物的重心應在吊鉤正下方。
+作業注意事項
+防止傾斜：吊掛物必須垂直起吊，不可斜向拉升，因此吊鉤必須引導至物品重心的正上方。
+保持平衡：確實估測貨物重心位置並選用適當吊具，確保吊舉物平穩、不晃動。</t>
+        </is>
+      </c>
+      <c r="I728" s="2" t="inlineStr"/>
     </row>
     <row r="729" ht="77.15000000000001" customHeight="1">
       <c r="A729" s="2" t="n">
@@ -32659,8 +32727,13 @@
       <c r="G729" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H729" s="2" t="n"/>
-      <c r="I729" s="2" t="n"/>
+      <c r="H729" s="2" t="inlineStr">
+        <is>
+          <t>應至少保持 0.25 公尺 距離。
+根據《職業安全衛生設施規則》第 91 條規定，雇主對於起重機具之吊鉤或吊具，為防止與吊架或捲揚胴接觸、碰撞，應有至少保持 0.25 公尺距離之過捲預防裝置（如為直動式過捲預防裝置者，應保持 0.05 公尺以上）。</t>
+        </is>
+      </c>
+      <c r="I729" s="2" t="inlineStr"/>
     </row>
     <row r="730" ht="92.59999999999999" customHeight="1">
       <c r="A730" s="2" t="n">
@@ -32694,8 +32767,17 @@
       <c r="G730" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H730" s="2" t="n"/>
-      <c r="I730" s="2" t="n"/>
+      <c r="H730" s="2" t="inlineStr">
+        <is>
+          <t>過捲預防裝置如為直動式，其限制尺寸為 0.05 公尺。
+💡 核心法規與說明
+根據台灣《起重升降機具安全規則》相關規定：
+直動式過捲預防裝置：吊鉤等上載裝置與捲揚機鼓輪、槽輪、桁架、橫樑等頂部可能造成碰撞之物件間的距離，應調整在 0.05 公尺以上（即 5 公分以上）。
+間接式（其他式）過捲預防裝置：其安全距離則規定在 0.25 公尺以上（即 25 公分以上）。
+若需要進一步了解起重機安全裝置的相關法規計算或考古題解析，</t>
+        </is>
+      </c>
+      <c r="I730" s="2" t="inlineStr"/>
     </row>
     <row r="731" ht="92.59999999999999" customHeight="1">
       <c r="A731" s="2" t="n">
@@ -32729,8 +32811,17 @@
       <c r="G731" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H731" s="2" t="n"/>
-      <c r="I731" s="2" t="n"/>
+      <c r="H731" s="2" t="inlineStr">
+        <is>
+          <t>這個問題的正確答案是：以上皆是。
+根據職業安全衛生相關法規與安全操作標準，吊帶（安全帶或起重吊帶）屬於保護勞工生命安全與防止物體飛落的重要工具。為了確保作業安全，只要出現以下任何一種情形，都應立即停止使用並予以汰換：
+縫合部分的絲線截斷者：這會嚴重損害吊帶的結構強度與承重能力，增加斷裂風險。
+吊帶的毛刺甚多者：毛刺多代表纖維已經過度磨損、老化或受化學品侵蝕，其強度已大幅降低。
+有顯著的損傷者：任何明顯的割傷、燒灼傷或嚴重變形，都會讓吊帶隨時有斷裂的危險。
+為了工作安全，使用前務必落實檢查，只要符合上述任一條件就絕不能繼續使用。</t>
+        </is>
+      </c>
+      <c r="I731" s="2" t="inlineStr"/>
     </row>
     <row r="732" ht="77.15000000000001" customHeight="1">
       <c r="A732" s="2" t="n">
@@ -32764,8 +32855,16 @@
       <c r="G732" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H732" s="2" t="n"/>
-      <c r="I732" s="2" t="n"/>
+      <c r="H732" s="2" t="inlineStr">
+        <is>
+          <t>這題的正確答案是 以上皆是。
+依據台灣的《起重升降機具安全規則》與職業安全衛生相關檢定規範，雇主與操作人員在進行起重吊掛作業時，必須落實以下安全措施：
+測出荷物重心位置：依規定應「估測荷物重心位置，以決定吊具懸掛荷物之適當位置」，避免起吊時因重心不穩發生傾斜或滑落。
+吊掛物離地 30 公分停下檢查：此為業界常規與考題標準（法規定義為「荷物剛離地面時暫停動作」，實務與學科常考「離地 30 公分暫停」），主要目的是確認吊索強度、剎車制動力及起重機的穩定度。
+檢查鋼索：起吊作業前及日常檢點中，必須確認鋼索是否有斷絲、變形、腐蝕或扭結等不良情形，汰換不合格品以確保安全。</t>
+        </is>
+      </c>
+      <c r="I732" s="2" t="inlineStr"/>
     </row>
     <row r="733" ht="77.15000000000001" customHeight="1">
       <c r="A733" s="2" t="n">
@@ -32799,8 +32898,18 @@
       <c r="G733" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H733" s="2" t="n"/>
-      <c r="I733" s="2" t="n"/>
+      <c r="H733" s="2" t="inlineStr">
+        <is>
+          <t>危險性機械進入工地前，不須檢附的文件是司機駕照。
+📌 說明原因
+根據《職業安全衛生法》及工地安全管理規定，危險性機械（如移動式起重機/吊車）進場時，著重審查的是設備本身的安全性以及專業作業人員的資格：
+危險性之機械檢查合格證：證明該機械符合國家安全標準，屬於必備文件。
+操作人員證照：證明操作吊車等機械的人員具備法定專業技術，屬於必備文件。
+吊掛人員證照：證明協助捆綁、指揮吊掛物品的人員受過專業訓練，屬於必備文件。
+❌ 司機駕照：屬於普通公路行駛的資格，非工地現場特定危險作業的審查重點（由交通法規規範，且部分機械於場內作業不涉及公路行駛，故進場安衛審查主要查驗上述三項）。</t>
+        </is>
+      </c>
+      <c r="I733" s="2" t="inlineStr"/>
     </row>
     <row r="734" ht="77.15000000000001" customHeight="1">
       <c r="A734" s="2" t="n">
@@ -32826,8 +32935,18 @@
       <c r="G734" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H734" s="2" t="n"/>
-      <c r="I734" s="2" t="n"/>
+      <c r="H734" s="2" t="inlineStr">
+        <is>
+          <t>答案是 0.07（即 7%）。
+根據台灣的《職業安全衛生設施規則》第 99 條以及《起重升降機具安全規則》第 68 條規定，雇主不得使用「直徑減少達公稱直徑百分之七以上」之鋼索作為起重機具的吊掛用具。因此，鋼索的直徑磨損以不減少超過 7%（0.07）為限。
+💡 補充起重吊掛鋼索的汰換標準：
+鋼索一撚間有 10% 以上素線截斷者。
+直徑減少達公稱直徑 7% 以上者。
+有顯著變形或腐蝕者。
+已扭結者。</t>
+        </is>
+      </c>
+      <c r="I734" s="2" t="inlineStr"/>
     </row>
     <row r="735" ht="92.59999999999999" customHeight="1">
       <c r="A735" s="2" t="n">
@@ -32861,8 +32980,16 @@
       <c r="G735" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H735" s="2" t="n"/>
-      <c r="I735" s="2" t="n"/>
+      <c r="H735" s="2" t="inlineStr">
+        <is>
+          <t>鋼索日常使用保養時，應注意的事項為以上皆是（選項D）。
+保養注意事項
+塗油：定期塗抹適當潤滑油以防止生鏽並減少摩擦損壞。
+雨水浸淋時塗油：淋雨後水分容易導致鋼索生鏽，應即時擦乾並塗油防護。
+灰塵多之場所以油布擦拭：在粉塵較多的環境下，使用油布擦拭可清除髒污並維持適度潤滑。</t>
+        </is>
+      </c>
+      <c r="I735" s="2" t="inlineStr"/>
     </row>
     <row r="736" ht="77.15000000000001" customHeight="1">
       <c r="A736" s="2" t="n">
@@ -32896,8 +33023,18 @@
       <c r="G736" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H736" s="2" t="n"/>
-      <c r="I736" s="2" t="n"/>
+      <c r="H736" s="2" t="inlineStr">
+        <is>
+          <t>以上皆是。
+在進行吊掛作業時，為了確保工地與人員安全，法規與安全指引對於機械、操作手及吊掛手都有嚴格的資格限制：
+起重機或吊運卡車：必須具備檢查合格的證明文件（如經代檢機構檢查合格之「機具檢查合格證」），確保機械結構與安全裝置正常。
+操作人員：必須依法取得吊升荷重符合該機具規格的「操作人員訓練結業證書」或「技術士證」。
+吊掛人員：必須受過「吊掛作業人員安全衛生訓練」並取得結業證書，才能負責指揮與綁紮。
+這三者缺一不可，共同構成安全的吊掛作業環境。
+請問您目前是在準備職業安全衛生相關考試，還是需要了解特定吊升荷重（如 3公噸以上或以下）的具體法規與證照資格呢？ 內容</t>
+        </is>
+      </c>
+      <c r="I736" s="2" t="inlineStr"/>
     </row>
     <row r="737" ht="77.15000000000001" customHeight="1">
       <c r="A737" s="2" t="n">
@@ -32931,8 +33068,17 @@
       <c r="G737" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H737" s="2" t="n"/>
-      <c r="I737" s="2" t="n"/>
+      <c r="H737" s="2" t="inlineStr">
+        <is>
+          <t>不用警戒圈圍工作區域是錯誤的選項。
+吊掛作業安全規定
+警告標誌：應設置適當的警告標示或標誌，提醒人員注意危險。
+警戒圈圍：必須圈圍工作區域或設置柵欄，防止無關人員進入危險半徑內。
+派專人指揮：作業時應指派專人進行交通引導與現場指揮。
+禁止人員進入：嚴禁人員進入機械動作迴轉半徑內及吊掛物下方。</t>
+        </is>
+      </c>
+      <c r="I737" s="2" t="inlineStr"/>
     </row>
     <row r="738" ht="92.59999999999999" customHeight="1">
       <c r="A738" s="2" t="n">
@@ -32966,8 +33112,18 @@
       <c r="G738" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H738" s="2" t="n"/>
-      <c r="I738" s="2" t="n"/>
+      <c r="H738" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+依據《職業安全衛生設施規則》第99條規定，雇主不得以下列情況之吊掛鋼索作為起重升降機具之吊掛用具：
+鋼索一撚間有百分之十以上素線截斷者
+直徑減少達公稱直徑百分之七以上者
+有顯著變形或腐蝕者
+已扭結者
+因此，在你提到的選項中，「一撚間有 10%以上束線（素線）截斷」是屬於不得使用的法定情況之一（而直徑減少的標準為達公稱直徑 7% 以上，並非 5%；延伸長度超過 5% 與斷面直徑減少 10% 以上則是適用於吊鏈的規定）。</t>
+        </is>
+      </c>
+      <c r="I738" s="2" t="inlineStr"/>
     </row>
     <row r="739" ht="92.59999999999999" customHeight="1">
       <c r="A739" s="2" t="n">
@@ -33001,8 +33157,18 @@
       <c r="G739" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H739" s="2" t="n"/>
-      <c r="I739" s="2" t="n"/>
+      <c r="H739" s="2" t="inlineStr">
+        <is>
+          <t>正確答案是 (A) 一撚間有10%以上素線截斷。
+法規依據
+依據勞動部的《起重升降機具安全規則》第99條規定，雇主不得以「鋼索一撚間有百分之十以上素線截斷者」之吊掛鋼索作為起重升降機具之吊掛用具。
+其他不得使用的情況還包含：
+直徑減少達公稱直徑百分之七以上者。
+有顯著變形或腐蝕者。
+已扭結者。</t>
+        </is>
+      </c>
+      <c r="I739" s="2" t="inlineStr"/>
     </row>
     <row r="740" ht="77.15000000000001" customHeight="1">
       <c r="A740" s="2" t="n">
@@ -33028,8 +33194,20 @@
       <c r="G740" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H740" s="2" t="n"/>
-      <c r="I740" s="2" t="n"/>
+      <c r="H740" s="2" t="inlineStr">
+        <is>
+          <t>斷面直徑減少 0.1（即百分之十，10%）以上者之吊鏈不得作為起重升降機具之吊掛用具。
+根據《職業安全衛生設施規則》第98條規定，雇主不得以斷面直徑減少百分之十以上之吊鏈作為起重升降機具之吊掛用具。
+您是否需要了解其他起重吊掛用具（如鋼索）的淘汰標準？
+鋼索斷線標準
+吊鉤開口變大標準
+纖維索損壞限制
+第98 條 - 勞動部-條文內容
+雇主不得以下列任何一種情況之吊鏈作為起重升降機具之吊掛用具： 一、延伸長度超過百分之五以上者。 二、斷面直徑減少百分之十以上者。 三、有龜裂者。 顯示立法理由.
+顯示全部 內容</t>
+        </is>
+      </c>
+      <c r="I740" s="2" t="inlineStr"/>
     </row>
     <row r="741" ht="77.15000000000001" customHeight="1">
       <c r="A741" s="2" t="n">
@@ -33055,8 +33233,18 @@
       <c r="G741" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H741" s="2" t="n"/>
-      <c r="I741" s="2" t="n"/>
+      <c r="H741" s="2" t="inlineStr">
+        <is>
+          <t>延伸長度超過百分之五（0.05）以上者之吊鏈，不得作為起重升降機具之吊掛用具。因此正確選項為 0.05（即 5%）。
+相關法規規定
+依據《職業安全衛生設施規則》第98條及《起重升降機具安全規則》第69條規定，雇主不得以有下列情形之一之吊鏈，供起重吊掛作業或作為吊掛用具：
+延伸長度：超過原製造時（或製造時長度）百分之五以上者。
+斷面直徑：減少百分之十（0.1）以上者。
+其他：有龜裂或已扭結者。
+新竹市文化局</t>
+        </is>
+      </c>
+      <c r="I741" s="2" t="inlineStr"/>
     </row>
     <row r="742" ht="92.59999999999999" customHeight="1">
       <c r="A742" s="2" t="n">
@@ -33090,8 +33278,13 @@
       <c r="G742" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H742" s="2" t="n"/>
-      <c r="I742" s="2" t="n"/>
+      <c r="H742" s="2" t="inlineStr">
+        <is>
+          <t>墊物。
+當鋼索直接接觸物體的銳角時，鋼索在受力時容易因集中應力或摩擦而遭受剪切、磨損或斷裂。為了保護鋼索並確保吊掛作業安全，必須在銳角處墊物（例如使用橡膠墊、木板、專用護角或角鐵）來緩衝並分散壓力。</t>
+        </is>
+      </c>
+      <c r="I742" s="2" t="inlineStr"/>
     </row>
     <row r="743" ht="92.59999999999999" customHeight="1">
       <c r="A743" s="2" t="n">
@@ -33119,8 +33312,14 @@
       <c r="G743" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H743" s="2" t="n"/>
-      <c r="I743" s="2" t="n"/>
+      <c r="H743" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+搭乘設備之懸吊用鋼索或鋼線之安全係數應在 10 以上。
+根據起重升降機具安全規則規定，搭乘設備之懸吊用鋼索或鋼線安全係數應在十以上；而吊鏈、吊帶及其支點之安全係數則應在五以上。</t>
+        </is>
+      </c>
+      <c r="I743" s="2" t="inlineStr"/>
     </row>
     <row r="744" ht="92.59999999999999" customHeight="1">
       <c r="A744" s="2" t="n">
@@ -33148,8 +33347,14 @@
       <c r="G744" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H744" s="2" t="n"/>
-      <c r="I744" s="2" t="n"/>
+      <c r="H744" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+搭乘設備之吊鏈、吊帶等及其支點之安全係數應在 5 以上。
+依據相關安全規則（如起重機吊掛搭乘設備相關注意事項），搭乘設備之懸吊用鋼索或鋼線之安全係數應在 10 以上，而吊鏈、吊帶、馬鞍環等及其支點之安全係數則應在 5 以上。</t>
+        </is>
+      </c>
+      <c r="I744" s="2" t="inlineStr"/>
     </row>
     <row r="745" ht="77.15000000000001" customHeight="1">
       <c r="A745" s="2" t="n">
@@ -33177,8 +33382,16 @@
       <c r="G745" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H745" s="2" t="n"/>
-      <c r="I745" s="2" t="n"/>
+      <c r="H745" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+起重機具所使用之鉤環，其安全係數應在 4 以上。
+經濟部標準檢驗局
+依據《職業安全衛生設施規則》及《起重升降機具安全規則》規定，起重機具所使用之吊鉤或鉤環及附屬零件，其斷裂荷重與所承受之最大荷重比之安全係數，應在 4 以上。
+正確選項為：4（即選項 C）。</t>
+        </is>
+      </c>
+      <c r="I745" s="2" t="inlineStr"/>
     </row>
     <row r="746" ht="77.15000000000001" customHeight="1">
       <c r="A746" s="2" t="n">
@@ -33212,8 +33425,13 @@
       <c r="G746" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H746" s="2" t="n"/>
-      <c r="I746" s="2" t="n"/>
+      <c r="H746" s="2" t="inlineStr">
+        <is>
+          <t>起重機載人作業前應保持 5 分鐘以上。
+依據《起重升降機具安全規則》第 38 條規定，起重機載人作業前，應先以預期最大荷重之荷物進行試吊測試，將測試荷物置於搭乘設備上，吊升至最大作業高度，保持 5 分鐘以上，以確認其平衡性及安全性無異常。</t>
+        </is>
+      </c>
+      <c r="I746" s="2" t="inlineStr"/>
     </row>
     <row r="747" ht="92.59999999999999" customHeight="1">
       <c r="A747" s="2" t="n">
@@ -33247,8 +33465,14 @@
       <c r="G747" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H747" s="2" t="n"/>
-      <c r="I747" s="2" t="n"/>
+      <c r="H747" s="2" t="inlineStr">
+        <is>
+          <t>垂直高度超過 20 公尺之高處作業，禁止使用直結式搭乘設備。正確答案為 20 公尺。
+產業本質安全推動網站
+依據《起重升降機具安全規則》第 35 條規定，移動式起重機之搭乘設備若從事垂直高度超過 20 公尺的高處作業，因指揮與操控不易，使用直結式搭乘設備容易因碰撞導致翻轉而發生災害，因此原則上禁止使用（但設有無線電通訊聯絡及作業監視或預防碰撞警報裝置者，不在此限）。</t>
+        </is>
+      </c>
+      <c r="I747" s="2" t="inlineStr"/>
     </row>
     <row r="748" ht="92.59999999999999" customHeight="1">
       <c r="A748" s="2" t="n">
@@ -33282,8 +33506,28 @@
       <c r="G748" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H748" s="2" t="n"/>
-      <c r="I748" s="2" t="n"/>
+      <c r="H748" s="2" t="inlineStr">
+        <is>
+          <t>這題的答案是：「當兩輛起重機共同作業時，無須訂定施工協調事究及統一指揮」是錯誤的（為非）。
+💡 答案解析
+當兩輛或兩輛以上起重機共同作業（即俗稱的「雙機合吊」或「多機合吊」）時，危險性極高，非常需要訂定施工協調事項，並且必須指定統一的指揮人員來負責協調與發號施令，以防動作不協調導致重心偏移而發生倒塌或斷裂意外。
+🏗️ 起重機的常見型式分類
+起重機具（吊車）依據其結構、外觀及移動方式，主要可以分為以下幾大類：
+移動式起重機（Mobile Cranes）
+輪胎式吊車（All Terrain / Rough Terrain Cranes）： 移動速度快，可在一般道路行駛，常用於營建工地。
+履帶式吊車（Crawler Cranes）： 使用履帶移動，接地面積大、穩定性高，適合鬆軟地面或超重型吊掛。
+卡車隨車吊車（Truck Cranes）： 安裝於一般載貨卡車後方的吊臂，方便運輸與小規模吊裝。
+固定式起重機（Stationary Cranes）
+塔式起重機（Tower Cranes）： 俗稱「塔吊」，高聳於高樓建築工地，專門負責高空吊運。
+人字臂起重桿（Derrick Cranes）： 由主桿和斜撐組成，常用於碼頭、造船廠或大樓頂部。
+架空式起重機（Overhead Traveling Cranes）
+固定天車（Bridge Cranes）： 常見於工廠或倉庫廠房頂部，沿著高架軌道左右、前後移動。
+龍門吊車（Gantry Cranes）： 吊車架在地面軌道上的門形支架上，常見於貨櫃碼頭或露天鋼材場。
+請問您目前正在準備起重機操作人員的證照考試（如固定式或移動式起重機操作），還是這屬於工地現場的安全宣導（Toolbox Talk）內容呢？如果有特定型式的起重機安全法規需要深入了解，我可以為您提供更詳細的資料！
+顯示更多</t>
+        </is>
+      </c>
+      <c r="I748" s="2" t="inlineStr"/>
     </row>
     <row r="749" ht="77.15000000000001" customHeight="1">
       <c r="A749" s="2" t="n">
@@ -33317,8 +33561,13 @@
       <c r="G749" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H749" s="2" t="n"/>
-      <c r="I749" s="2" t="n"/>
+      <c r="H749" s="2" t="inlineStr">
+        <is>
+          <t>正確答案是 (D) 以上皆是。
+卡車式起重機、積載型起重機（俗稱吊卡車）與履帶式起重機，皆屬於移動式起重機常見的型式分類。</t>
+        </is>
+      </c>
+      <c r="I749" s="2" t="inlineStr"/>
     </row>
     <row r="750" ht="77.15000000000001" customHeight="1">
       <c r="A750" s="2" t="n">
@@ -33352,8 +33601,16 @@
       <c r="G750" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H750" s="2" t="n"/>
-      <c r="I750" s="2" t="n"/>
+      <c r="H750" s="2" t="inlineStr">
+        <is>
+          <t>正確答案是 (D) 以上皆是。
+起重機具運轉注意事項
+吊鉤或吊具防脫裝置：應具備防止吊舉中所吊物體脫落之裝置。
+過捲預防裝置：應與吊架或捲揚胴保持至少 25公分（0.25公尺） 以上之距離，以防碰撞損傷。
+防止人員進入下方：運轉時應採取有效措施，防止人員進入吊掛物下方或通過人員上方。</t>
+        </is>
+      </c>
+      <c r="I750" s="2" t="inlineStr"/>
     </row>
     <row r="751" ht="77.15000000000001" customHeight="1">
       <c r="A751" s="2" t="n">
@@ -33387,8 +33644,15 @@
       <c r="G751" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H751" s="2" t="n"/>
-      <c r="I751" s="2" t="n"/>
+      <c r="H751" s="2" t="inlineStr">
+        <is>
+          <t>操作者與吊掛者之間能確實保持確實之連絡時，操作者仍需聽從指揮者的指揮。
+重點整理
+正確選項為：(B) 仍需聽從指揮者的指揮（或類似選項「能須聽從指揮者的指揮」）。
+即使通訊無礙，起重與吊掛作業仍須依循統一指揮，以維護現場安全。</t>
+        </is>
+      </c>
+      <c r="I751" s="2" t="inlineStr"/>
     </row>
     <row r="752" ht="77.15000000000001" customHeight="1">
       <c r="A752" s="2" t="n">
@@ -33422,8 +33686,81 @@
       <c r="G752" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H752" s="2" t="n"/>
-      <c r="I752" s="2" t="n"/>
+      <c r="H752" s="2" t="inlineStr">
+        <is>
+          <t>，請稍後再試。
+網頁搜尋結果
+1040. 吊掛用吊索於作業前需做何檢查,下列敘述何者錯誤? ...
+› item-1040.+吊掛用吊索於作業前...
+2024年10月7日 — 1040. 吊掛用吊索於作業前需做何檢查,下列敘述何者錯誤? (A)吊索是否有扭結 (B)目視觀察吊索 (C)索線是否有截斷者 (D)是否有顯著變形或腐蝕者. 答案 ...
+1038. 對起重機具之運轉應注意事項(A)吊鉤或吊具應有防脫 ...
+› item-1038.+對起重機具之運轉應注意...
+2024年10月7日 — 吊掛用吊索於作業前需做何檢查,下列敘述何者錯誤?(A)吊索是否有扭結(B)目視觀察吊索(C)索線是否有截斷者(D)是否有顯著變形或腐蝕者. #3327038 · 1041. 吊 ...
+常見問答-吊掛作業在安全上應注意那些事項？
+臺北市勞動檢查處
+› News_Content
+應由合格之操作人員操作且於吊掛作業前需了解吊舉物的重量和起重升降機具的額定荷重及吊舉物的重心，物料的重心宜低，吊鉤應在重心的正上方。 2. 吊掛作業時除應穿戴 ...
+技術士技能檢定固定式起重機操作單一級學科測試 ...
+臺中市總工業會
+› download_file › 固定...
+PDF
+... 作業程序、工作方法不用歸入。 51. (1) 吊掛用鋼索以下何者可以使用？ ①一撚間有百分之七素線裁斷者②已扭. 結者③直徑減少達公稱直徑百分之七以上者④嚴重鏽蝕。 52 ...
+相關問題
+吊掛作業的一機三證 指的是什麼項目？
+吊掛鋼索的規定是什麼?
+吊掛作業時,人員可以進入吊掛物正下方嗎?
+吊掛作業的標準作業程序是什麼?
+網頁搜尋結果
+第五章起重吊掛作業安全管理
+› flaw › FLAWDAT0201
+雇主對於使用起重機具從事吊掛作業之勞工，應使其辦理下列事項： 一、確認起重機具之額定荷重，使所吊荷物之重量在額定荷重值以下。 二、檢視荷物之形狀、大小及材質等特性 ...
+缺少字詞： 做 ‎錯誤 ? ‎目視 ‎觀察
+起重機及吊掛作業在職教育訓練講義
+桃園市幼獅產業協進會
+› proimage › images
+PDF
+使用鋼索作為吊掛用具時、應注意不得有下列之情形(設施則99). (1) 鋼索一撚間有百分之十以上素線截斷者。 (2) 直徑減少達公稱直徑百分之七以上者。 (3) 有顯著變形或腐蝕者 ...
+缺少字詞： 檢查, ‎敘述 ‎何者 ‎錯誤 ? ‎目視 ‎觀察
+吊掛用具作業前檢查表
+中原大學Chung Yuan Christian University
+› 吊掛用具作業前檢查...
+PDF
+說明:1.作業前檢查1. 檢查結果正常狀態打v，異常狀態打x，並向單位反應故障狀況。2. 檢查表檢查完後，正本原單位留存備查，影本繳交環安中心。 實驗場所負責人簽名 ...
+缺少字詞： 用 ‎於 ‎做 ‎下列 ‎何者 ‎錯誤 ? ‎觀察
+06100 固定式起重機操作單一級工作項目01:作業之準備與檢點
+金屬中心樂齡學苑
+› banner › 固定式起...
+PDF
+26. (1) 荷件掛上吊索拉緊準備起吊時首先應查看①每條吊索的緊度是否相同②起吊荷件上面是否載人③吊索是否在. 吊鉤中心④荷件的重量。 27. (4) 凡形狀複雜或重心不明之荷 ...
+缺少字詞： 扭結 ‎觀察
+【觀念隨身卡】- 吊掛作業安全實務：讓吊掛不再提心吊膽
+iPEDIA 百科
+› 部落格
+· 吊掛事故預防 · 1. 操作及吊掛人員需有證照。 · 2. 吊掛作業的運搬路線應妥為規劃，選用適當的吊掛方法，避免吊具斷損，物體飛落。 · 3. 人員禁止進入吊物下方；若人員要於 ...
+缺少字詞： 前 ‎做 ‎檢查, ‎敘述 ‎扭結 ‎目視 ‎觀察 ‎線 ‎截斷
+頁面導覽
+1
+2
+3
+4
+5
+6
+7
+8
+9
+10
+下一頁
+頁尾連結
+台灣
+708 臺南市安平區 - 根據你的 IP 位址
+- 更新位置
+說明
+提供意見
+隱私權
+服務條款</t>
+        </is>
+      </c>
+      <c r="I752" s="2" t="inlineStr"/>
     </row>
     <row r="753" ht="77.15000000000001" customHeight="1">
       <c r="A753" s="2" t="n">
@@ -33457,8 +33794,12 @@
       <c r="G753" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H753" s="2" t="n"/>
-      <c r="I753" s="2" t="n"/>
+      <c r="H753" s="2" t="inlineStr">
+        <is>
+          <t>Google AI 摘要未抓取到，請手動補充。</t>
+        </is>
+      </c>
+      <c r="I753" s="2" t="inlineStr"/>
     </row>
     <row r="754" ht="92.59999999999999" customHeight="1">
       <c r="A754" s="2" t="n">
@@ -33492,8 +33833,18 @@
       <c r="G754" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H754" s="2" t="n"/>
-      <c r="I754" s="2" t="n"/>
+      <c r="H754" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+斷面直徑減少超過製造時之百分之十者，不可使用為正確的敘述。
+根據起重升降機具安全規則之規定，雇主不得以有下列情形之一的吊鏈，供起重吊掛作業使用：
+延伸長度超過製造時長度百分之五以上者
+斷面直徑減少超過製造時之百分之十者
+有龜裂者（有龜裂即不可使用，故「有龜裂仍可使用」為錯誤）
+另外，吊鏈若有顯著腐蝕亦不得使用（故「有腐蝕仍可使用」為錯誤）；而「直徑減少達公稱直徑百分之七以上者」則是針對鋼索（Wire rope）的規定，對於吊鏈（Chain）的斷面直徑減少標準則是超過 百分之十。</t>
+        </is>
+      </c>
+      <c r="I754" s="2" t="inlineStr"/>
     </row>
     <row r="755" ht="92.59999999999999" customHeight="1">
       <c r="A755" s="2" t="n">
@@ -33527,8 +33878,14 @@
       <c r="G755" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H755" s="2" t="n"/>
-      <c r="I755" s="2" t="n"/>
+      <c r="H755" s="2" t="inlineStr">
+        <is>
+          <t>吊運長度超過 5 公尺之鋼筋時，應在適當距離之二端以吊鏈鈎住或拉索捆紮拉緊，保持平穩以防擺動。
+正確答案為：5 公尺。
+依據營造安全衛生設施標準第 129 條規定辦理。</t>
+        </is>
+      </c>
+      <c r="I755" s="2" t="inlineStr"/>
     </row>
     <row r="756" ht="92.59999999999999" customHeight="1">
       <c r="A756" s="2" t="n">
@@ -33562,8 +33919,18 @@
       <c r="G756" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H756" s="2" t="n"/>
-      <c r="I756" s="2" t="n"/>
+      <c r="H756" s="2" t="inlineStr">
+        <is>
+          <t>錯誤的敘述為：「安放鋼構時，應由側方或交叉方向完全支稱」。
+錯誤原因解析
+依據勞動部《營造安全衛生設施標準》第 148 條規定：
+正確規定：安放鋼構時，應由「側方及交叉方向」進行「安全支撐」（或稱安全撐住），而非「側方或交叉方向」且用詞為「完全支稱」。
+另外，針對長度超過 6 公尺之構架吊運，法規要求應在適當距離之「二端」以拉索捆紮拉緊，有些選項若寫成「一端」亦屬錯誤（但以此題選項比較，安放鋼構的語意與法規不符為標準考題的常見錯誤選項）。
+第148 條 - 勞動部-條文內容
+營造安全衛生設施標準 (民國115 年06 月30 日修正). 生效狀態：. ※本法規部分或全部條文尚未生效，最後生效日期：民國116 年07 月01 日 一百十五年六月三十日增訂之第 11-2 條，自一百十六年七月一日施行。 第148 條. 雇主對於鋼構吊運...</t>
+        </is>
+      </c>
+      <c r="I756" s="2" t="inlineStr"/>
     </row>
     <row r="757" ht="77.15000000000001" customHeight="1">
       <c r="A757" s="2" t="n">
@@ -33597,8 +33964,12 @@
       <c r="G757" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H757" s="2" t="n"/>
-      <c r="I757" s="2" t="n"/>
+      <c r="H757" s="2" t="inlineStr">
+        <is>
+          <t>Google AI 摘要未抓取到，請手動補充。</t>
+        </is>
+      </c>
+      <c r="I757" s="2" t="inlineStr"/>
     </row>
     <row r="758" ht="92.59999999999999" customHeight="1">
       <c r="A758" s="2" t="n">
@@ -33632,8 +34003,18 @@
       <c r="G758" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H758" s="2" t="n"/>
-      <c r="I758" s="2" t="n"/>
+      <c r="H758" s="2" t="inlineStr">
+        <is>
+          <t>正確的敘述為：強風、大雨等惡劣氣候，塔式起重機應停止作業。
+相關法規與說明
+依據《起重升降機具安全規則》及相關職業安全衛生規定：
+惡劣氣候處理：遇有強風、大雨等惡劣氣候致生危險之虞時，應立即停止塔式起重機的吊運作業。
+額定荷重標示：起重機具應明顯標示額定荷重，不得超出規定。
+吊運管制：吊舉物應盡量避免通過人員上方，且作業區域應設置管制與警告標示，禁止無關人員進入。
+半徑與荷重：操作時必須嚴格依照起重機荷重表規定之作業半徑及容許荷重進行作業。</t>
+        </is>
+      </c>
+      <c r="I758" s="2" t="inlineStr"/>
     </row>
     <row r="759" ht="92.59999999999999" customHeight="1">
       <c r="A759" s="2" t="n">
@@ -33667,8 +34048,19 @@
       <c r="G759" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H759" s="2" t="n"/>
-      <c r="I759" s="2" t="n"/>
+      <c r="H759" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+「可供人員搭乘、吊升或降落」為不正確的敘述。
+詳細說明
+依據《職業安全衛生設施規則》第 155-1 條規定，雇主使勞工以捲揚機等吊運物料時，應依下列規定辦理：
+不得供人員搭乘、吊升或降落。
+應禁止人員進入吊掛物下方。
+安裝前須核對並確認設計資料及強度計算書。
+吊掛之重量不得超過該設備所能承受之最高負荷，並應設有防止過捲裝置或其他安全裝置。</t>
+        </is>
+      </c>
+      <c r="I759" s="2" t="inlineStr"/>
     </row>
     <row r="760" ht="77.15000000000001" customHeight="1">
       <c r="A760" s="2" t="n">
@@ -33702,8 +34094,17 @@
       <c r="G760" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H760" s="2" t="n"/>
-      <c r="I760" s="2" t="n"/>
+      <c r="H760" s="2" t="inlineStr">
+        <is>
+          <t>吊鉤防滑舌片彈性鬆弛是不正確的措施，因為吊鉤防滑舌片彈性鬆弛或失效時，吊掛物容易脫鉤掉落，應立即更換或維修，不能任其鬆弛。
+正確措施說明
+吊掛物使用吊耳時：吊耳的位置與數量必須確保確實平衡，防止傾斜或翻轉。
+吊掛用具：必須具備足夠的強度與安全係數。
+運轉時：應採取防止吊掛物通過人員上方及人員進入下方的設備或措施。
+桃園市幼獅產業協進會</t>
+        </is>
+      </c>
+      <c r="I760" s="2" t="inlineStr"/>
     </row>
     <row r="761" ht="92.59999999999999" customHeight="1">
       <c r="A761" s="2" t="n">
@@ -33737,8 +34138,18 @@
       <c r="G761" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H761" s="2" t="n"/>
-      <c r="I761" s="2" t="n"/>
+      <c r="H761" s="2" t="inlineStr">
+        <is>
+          <t>在吊掛長條形吊物時，吊掛人員應該在吊物上綁牽引繩，並由人員用手拉繩控制（選項B）。
+安全作法說明
+正確做法：應使用牽引繩（導引繩）保持安全距離來控制吊物方向與旋轉，避免直接接觸。
+iPEDIA 百科
+錯誤做法：
+徒手去扶吊物容易因吊物晃動、碰撞或掉落而造成手部夾傷或砸傷。
+站在吊物下方或上方隨之移動，極易因吊物滑落、翻覆或斷索而引發重大職業災害。</t>
+        </is>
+      </c>
+      <c r="I761" s="2" t="inlineStr"/>
     </row>
     <row r="762" ht="77.15000000000001" customHeight="1">
       <c r="A762" s="2" t="n">
@@ -33772,8 +34183,18 @@
       <c r="G762" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H762" s="2" t="n"/>
-      <c r="I762" s="2" t="n"/>
+      <c r="H762" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+依危險性機械及設備安全檢查規則規定，雇主變更固定式起重機之桁架、伸臂、腳、塔等構造部分時，應向檢查機構申請變更檢查。
+相關規定重點
+申請項目：變更檢查
+應備文件：
+固定式起重機變更檢查申請書
+變更部分之圖件</t>
+        </is>
+      </c>
+      <c r="I762" s="2" t="inlineStr"/>
     </row>
     <row r="763" ht="92.59999999999999" customHeight="1">
       <c r="A763" s="2" t="n">
@@ -33807,8 +34228,17 @@
       <c r="G763" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H763" s="2" t="n"/>
-      <c r="I763" s="2" t="n"/>
+      <c r="H763" s="2" t="inlineStr">
+        <is>
+          <t>依起重升降機具安全規則第40條規定，錯誤的敘述為：移動式起重機之操作，得以搖撼伸臂或拖拉物件等方式從事起重作業。
+正確法規規定
+禁止不當操作：移動式起重機之操作，應依原設計功能之操作方法吊升荷物，不得以搖撼伸臂或拖拉物件等不當方式從事起重作業。
+檢修與調整：從事檢修、調整作業時，應指定作業監督人員，從事監督指揮工作（但無虞危險或採其他安全措施，確無危險之虞者不在此限）。
+吊有荷重：操作人員於起重機吊有荷重時，不得擅離操作位置或駕駛室。
+組配與拆卸：組配、拆卸時，應選用適當人員擔任，作業區內禁止無關人員進入，必要時並設置警告標示。</t>
+        </is>
+      </c>
+      <c r="I763" s="2" t="inlineStr"/>
     </row>
     <row r="764" ht="77.15000000000001" customHeight="1">
       <c r="A764" s="2" t="n">
@@ -33842,8 +34272,15 @@
       <c r="G764" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H764" s="2" t="n"/>
-      <c r="I764" s="2" t="n"/>
+      <c r="H764" s="2" t="inlineStr">
+        <is>
+          <t>答案為 過熱預防裝置。
+解析
+過熱預防裝置：屬於馬達或電氣機械本身的溫升保護，不列入法規定義的「固定式起重機安全裝置」名目中。
+防脫落裝置、過捲預防裝置（題目筆誤作「過描預防裝置」）及過負荷警報裝置（或過負荷預防裝置）皆為法規規定的固定式起重機標準安全裝置。</t>
+        </is>
+      </c>
+      <c r="I764" s="2" t="inlineStr"/>
     </row>
     <row r="765" ht="92.59999999999999" customHeight="1">
       <c r="A765" s="2" t="n">
@@ -33877,8 +34314,12 @@
       <c r="G765" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H765" s="2" t="n"/>
-      <c r="I765" s="2" t="n"/>
+      <c r="H765" s="2" t="inlineStr">
+        <is>
+          <t>Google AI 摘要未抓取到，請手動補充。</t>
+        </is>
+      </c>
+      <c r="I765" s="2" t="inlineStr"/>
     </row>
     <row r="766" ht="77.15000000000001" customHeight="1">
       <c r="A766" s="2" t="n">
@@ -33906,8 +34347,15 @@
       <c r="G766" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H766" s="2" t="n"/>
-      <c r="I766" s="2" t="n"/>
+      <c r="H766" s="2" t="inlineStr">
+        <is>
+          <t>依職業安全衛生設施規則規定，固定式起重機所設非直動式過捲預防裝置，應使吊鉤或吊具之捲揚用槽輪之上方，與捲胴、槽輪或桁架等之下方之間隔，至少保持 25 公分（即 0.25 公尺）。因此正確答案為 25。
+重點整理
+非直動式過捲預防裝置：至少保持 25 公分（0.25公尺）。
+直動式過捲預防裝置：至少保持 5 公分（0.05公尺）以上。</t>
+        </is>
+      </c>
+      <c r="I766" s="2" t="inlineStr"/>
     </row>
     <row r="767" ht="92.59999999999999" customHeight="1">
       <c r="A767" s="2" t="n">
@@ -33941,8 +34389,18 @@
       <c r="G767" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H767" s="2" t="n"/>
-      <c r="I767" s="2" t="n"/>
+      <c r="H767" s="2" t="inlineStr">
+        <is>
+          <t>固定式起重機
+相關定義說明
+依據《起重升降機具安全規則》第2條規定：
+固定式起重機：指在特定場所使用動力將貨物吊升並將其作水平搬運為目的之機械裝置。
+移動式起重機：指能自行移動於非特定場所並具有起重動力之起重機。
+人字臂起重桿：指以動力吊升貨物為目的，具有主柱、吊桿，另行裝置原動機，並以鋼索操作升降之機械裝置。
+升降機：指乘載人員及（或）貨物於搬器上，而該搬器順沿軌道鉛直升降，並以動力從事搬運之機械裝置。</t>
+        </is>
+      </c>
+      <c r="I767" s="2" t="inlineStr"/>
     </row>
     <row r="768" ht="108" customHeight="1">
       <c r="A768" s="2" t="n">
@@ -33976,8 +34434,19 @@
       <c r="G768" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H768" s="2" t="n"/>
-      <c r="I768" s="2" t="n"/>
+      <c r="H768" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+使用吊籠時，有誤的選項是 「應使用全身式安全帶並鉤掛於吊籠的欄杆上」。
+錯誤原因說明
+安全帶鉤掛位置：安全帶應鉤掛於獨立的安全母索（或專用固定點）上，不得直接鉤掛於吊籠的欄杆上。如果吊籠本身發生傾斜、結構損壞或墜落，鉤掛在欄杆上將無法發揮防墜保護作用。
+其他選項正確性
+需檢查合格才能使用：正確，使用前須確認各項安全裝置與機具檢查合格。
+不得超過積載荷重使用：正確，嚴禁超載以維持結構安全 [6.8]。
+下方應做適當管制及淨空：正確，應防止無關人員進入下方或遭受落物砸傷。</t>
+        </is>
+      </c>
+      <c r="I768" s="2" t="inlineStr"/>
     </row>
     <row r="769" ht="77.15000000000001" customHeight="1">
       <c r="A769" s="2" t="n">
@@ -34007,8 +34476,14 @@
       <c r="G769" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H769" s="2" t="n"/>
-      <c r="I769" s="2" t="n"/>
+      <c r="H769" s="2" t="inlineStr">
+        <is>
+          <t>固定式起重機係指在特定場所使用動力將貨物吊升並將其作水平搬運為目的之機械裝置。
+根據《起重升降機具安全規則》第2條之規定，固定式起重機的定義即包含以「水平搬運」為目的。因此選項中的正確答案為 水平。
+myMKC管理知識中心</t>
+        </is>
+      </c>
+      <c r="I769" s="2" t="inlineStr"/>
     </row>
     <row r="770" ht="77.15000000000001" customHeight="1">
       <c r="A770" s="2" t="n">
@@ -34042,8 +34517,17 @@
       <c r="G770" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H770" s="2" t="n"/>
-      <c r="I770" s="2" t="n"/>
+      <c r="H770" s="2" t="inlineStr">
+        <is>
+          <t>積載型油壓起重機俗稱「秤仔車」（亦常被稱為吊卡車）。
+Instagram
+·ninebridgesenterprise 詳細說明
+積載型油壓起重機：指在卡車貨物平台上裝設油壓起重機（吊桿通常裝在駕駛台與貨物台之間），同時具備載貨與吊裝功能。
+特點：機動性高、應用範圍廣，吊升荷重通常在十公噸以下，僅具兩支外伸撐座。
+危險性機械及設備代檢機構</t>
+        </is>
+      </c>
+      <c r="I770" s="2" t="inlineStr"/>
     </row>
     <row r="771" ht="92.59999999999999" customHeight="1">
       <c r="A771" s="2" t="n">
@@ -34069,8 +34553,14 @@
       <c r="G771" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H771" s="2" t="n"/>
-      <c r="I771" s="2" t="n"/>
+      <c r="H771" s="2" t="inlineStr">
+        <is>
+          <t>吊升荷重未滿 3 公噸之移動式或固定式起重機操作人員，應使其接受特殊作業安全衛生教育訓練。
+依據《職業安全衛生教育訓練規則》規定，吊升荷重在 0.5 公噸以上未滿 3 公噸之移動式或固定式起重機操作人員，雇主應安排其接受 18 小時的特殊作業安全衛生教育訓練。而 3 公噸以上者則另規範須具備技術士技能檢定合格資格。
+法源法律網</t>
+        </is>
+      </c>
+      <c r="I771" s="2" t="inlineStr"/>
     </row>
     <row r="772" ht="77.15000000000001" customHeight="1">
       <c r="A772" s="2" t="n">
@@ -34104,8 +34594,15 @@
       <c r="G772" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H772" s="2" t="n"/>
-      <c r="I772" s="2" t="n"/>
+      <c r="H772" s="2" t="inlineStr">
+        <is>
+          <t>危險性機械或設備之定期檢查係由代行檢查機構（或勞動檢查機構）來檢查。
+勞動部職業安全衛生署 說明
+代行檢查機構：依據《勞動檢查法》規定，中央主管機關（勞動部）對於危險性機械或設備之檢查，除由勞動檢查機構派員實施外，必要時得指定代行檢查機構派代行檢查員實施。目前多數的危險性機械與設備之定期檢查（約97%）皆委由民間之代行檢查機構來執行。
+選項中對應的正確答案為：代行檢查機構（或檢查機構）。</t>
+        </is>
+      </c>
+      <c r="I772" s="2" t="inlineStr"/>
     </row>
     <row r="773" ht="77.15000000000001" customHeight="1">
       <c r="A773" s="2" t="n">
@@ -34131,8 +34628,14 @@
       <c r="G773" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H773" s="2" t="n"/>
-      <c r="I773" s="2" t="n"/>
+      <c r="H773" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+移動式起重機捲揚用鋼索，當吊具置於最低位置時，應至少有 2 捲以上鋼索留置於吊升裝置之捲胴上。
+根據《移動式起重機安全檢查構造標準》第45條規定，對於捲揚用鋼索，當吊具置於最低位置時，應有二捲以上鋼索留置於吊升裝置之捲胴上。因此正確答案為 2。</t>
+        </is>
+      </c>
+      <c r="I773" s="2" t="inlineStr"/>
     </row>
     <row r="774" ht="92.59999999999999" customHeight="1">
       <c r="A774" s="2" t="n">
@@ -34166,8 +34669,15 @@
       <c r="G774" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H774" s="2" t="n"/>
-      <c r="I774" s="2" t="n"/>
+      <c r="H774" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+依據《起重升降機具安全規則》規定，答案為 積載荷重。
+相關法規說明
+積載荷重：依據起重升降機具安全規則第7條，在升降機、簡易提升機、營建用提升機或未具吊臂之吊籠，指依其構造及材質，於搬器上乘載人員或荷物上升之最大荷重。</t>
+        </is>
+      </c>
+      <c r="I774" s="2" t="inlineStr"/>
     </row>
     <row r="775" ht="108" customHeight="1">
       <c r="A775" s="2" t="n">
@@ -34201,8 +34711,15 @@
       <c r="G775" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H775" s="2" t="n"/>
-      <c r="I775" s="2" t="n"/>
+      <c r="H775" s="2" t="inlineStr">
+        <is>
+          <t>依據《起重升降機具安全規則》第2條規定，答案是吊籠（題目中的「吊委」應為「吊籠」之誤繕或字形誤植）。
+名詞定義
+吊籠：指由懸吊式施工架、升降裝置、支撐裝置、工作台及其附屬裝置所構成，專供勞工（人員）升降施工之設備（例如常見的洗窗機）。
+中華民國工業安全衛生協會</t>
+        </is>
+      </c>
+      <c r="I775" s="2" t="inlineStr"/>
     </row>
     <row r="776" ht="92.59999999999999" customHeight="1">
       <c r="A776" s="2" t="n">
@@ -34236,8 +34753,15 @@
       <c r="G776" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H776" s="2" t="n"/>
-      <c r="I776" s="2" t="n"/>
+      <c r="H776" s="2" t="inlineStr">
+        <is>
+          <t>依據職業安全衛生設施規則第93條規定，正確的安全連鎖作用為停止上下（或使升降機不能開動、開動中能停止上下）。
+相關法規重點
+法規依據：職業安全衛生設施規則第93條。
+規定內容：雇主對於升降機之升降路各樓出入口，應裝置構造堅固平滑之門，並應有安全裝置，使升降搬器及升降路出入口之任一門開啟時，升降機不能開動，及升降機在開動中任一門開啟時，能停止上下。</t>
+        </is>
+      </c>
+      <c r="I776" s="2" t="inlineStr"/>
     </row>
     <row r="777" ht="92.59999999999999" customHeight="1">
       <c r="A777" s="2" t="n">
@@ -34263,8 +34787,15 @@
       <c r="G777" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H777" s="2" t="n"/>
-      <c r="I777" s="2" t="n"/>
+      <c r="H777" s="2" t="inlineStr">
+        <is>
+          <t>依職業安全衛生設施規則第95條規定，答案是 7.5公分。
+相關規定重點
+法條依據：職業安全衛生設施規則第95條。
+規定內容：雇主對於升降機之升降路各樓出入口門，應有連鎖裝置，使搬器地板與樓板相差 七．五公分 以上時，升降路出入口門不能開啟之。</t>
+        </is>
+      </c>
+      <c r="I777" s="2" t="inlineStr"/>
     </row>
     <row r="778" ht="92.59999999999999" customHeight="1">
       <c r="A778" s="2" t="n">
@@ -34298,8 +34829,14 @@
       <c r="G778" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H778" s="2" t="n"/>
-      <c r="I778" s="2" t="n"/>
+      <c r="H778" s="2" t="inlineStr">
+        <is>
+          <t>在萬不得已的情況下使用堆高機搭載人員作業時，錯誤的作法是：「堆高機行駛中仍可進行人員在上面作業」。
+根據職業安全衛生相關法規，堆高機原則上不得搭載人員作業。若在萬不得已的特殊情況下落實安全防護（如使用合格工作台、配戴安全帶、操作人員受訓等）進行高處作業時，堆高機在行駛、移動過程中，上方絕對嚴禁載人或進行作業，以防劇烈搖晃或緊急煞車導致人員墜落。
+為了幫您確認更詳細的安全規範，請問您目前是在準備堆高機操作證照考試，還是需要規劃工廠內部的安全作業守則呢？ 內容</t>
+        </is>
+      </c>
+      <c r="I778" s="2" t="inlineStr"/>
     </row>
     <row r="779" ht="77.15000000000001" customHeight="1">
       <c r="A779" s="2" t="n">
@@ -34333,8 +34870,15 @@
       <c r="G779" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H779" s="2" t="n"/>
-      <c r="I779" s="2" t="n"/>
+      <c r="H779" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+依《職業安全衛生設施規則》第127條規定，答案為 翻倒。
+相關法規內容：雇主對於堆高機之操作，不得超過該機械所能承受之最大荷重，且其載運之貨物應保持穩固狀態，防止翻倒。
+正確選項：翻倒（或翻覆）</t>
+        </is>
+      </c>
+      <c r="I779" s="2" t="inlineStr"/>
     </row>
     <row r="780" ht="77.15000000000001" customHeight="1">
       <c r="A780" s="2" t="n">
@@ -34362,8 +34906,12 @@
       <c r="G780" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H780" s="2" t="n"/>
-      <c r="I780" s="2" t="n"/>
+      <c r="H780" s="2" t="inlineStr">
+        <is>
+          <t>Google AI 摘要未抓取到，請手動補充。</t>
+        </is>
+      </c>
+      <c r="I780" s="2" t="inlineStr"/>
     </row>
     <row r="781" ht="77.15000000000001" customHeight="1">
       <c r="A781" s="2" t="n">
@@ -34397,8 +34945,16 @@
       <c r="G781" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H781" s="2" t="n"/>
-      <c r="I781" s="2" t="n"/>
+      <c r="H781" s="2" t="inlineStr">
+        <is>
+          <t>動力堆高機的乘坐席最多可載1人（即駕駛本人）。
+台灣省工礦安全衛生技師公會
+詳細說明
+乘坐席限制：堆高機的駕駛座（乘坐席）設計僅供單一駕駛操作使用，依法僅限1人乘坐。
+其他部位禁止載人：除了駕駛座之外，嚴禁讓任何人搭乘於堆高機的貨叉、載物架、托板或其他非乘坐席部分。</t>
+        </is>
+      </c>
+      <c r="I781" s="2" t="inlineStr"/>
     </row>
     <row r="782" ht="77.15000000000001" customHeight="1">
       <c r="A782" s="2" t="n">
@@ -34432,8 +34988,17 @@
       <c r="G782" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H782" s="2" t="n"/>
-      <c r="I782" s="2" t="n"/>
+      <c r="H782" s="2" t="inlineStr">
+        <is>
+          <t>照度足夠時就不用開啟前燈。
+在職安衛生與堆高機相關考題中，針對「為安全起見，於室內行駛動力堆高機是否要開前燈？」的標準答案為 (C) 照度夠就不用。
+Would you like to review more forklift safety quiz questions?
+Load capacity &amp; stability rules
+Ramps &amp; turning safety guidelines
+Daily pre-operation inspection items</t>
+        </is>
+      </c>
+      <c r="I782" s="2" t="inlineStr"/>
     </row>
     <row r="783" ht="77.15000000000001" customHeight="1">
       <c r="A783" s="2" t="n">
@@ -34467,8 +35032,13 @@
       <c r="G783" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H783" s="2" t="n"/>
-      <c r="I783" s="2" t="n"/>
+      <c r="H783" s="2" t="inlineStr">
+        <is>
+          <t>堆高機作業較常發生之危害為被撞（如被堆高機撞擊或擦撞）。
+臺中市勞動檢查處</t>
+        </is>
+      </c>
+      <c r="I783" s="2" t="inlineStr"/>
     </row>
     <row r="784" ht="92.59999999999999" customHeight="1">
       <c r="A784" s="2" t="n">
@@ -34502,8 +35072,15 @@
       <c r="G784" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H784" s="2" t="n"/>
-      <c r="I784" s="2" t="n"/>
+      <c r="H784" s="2" t="inlineStr">
+        <is>
+          <t>高空工作車桿臂之型式，何者為非？答案是 (C) 吊掛式。
+說明
+伸縮臂式、屈折臂式與垂直升降式皆為法規及業界常見的高空工作車作業臂（升降裝置）型式。
+吊掛式不屬於高空工作車桿臂的基本型式。</t>
+        </is>
+      </c>
+      <c r="I784" s="2" t="inlineStr"/>
     </row>
     <row r="785" ht="92.59999999999999" customHeight="1">
       <c r="A785" s="2" t="n">
@@ -34537,8 +35114,16 @@
       <c r="G785" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H785" s="2" t="n"/>
-      <c r="I785" s="2" t="n"/>
+      <c r="H785" s="2" t="inlineStr">
+        <is>
+          <t>答案為：(A) 伸縮臂式
+高空工作車桿臂型式說明
+伸縮臂式：藉由作業臂伸縮長度及底座旋轉方式，移動作業平台到達位置。
+屈折臂式：作業臂各節長度固定，藉由各節關節旋轉而移動作業平台到達作業位置。
+垂直升降式：作業平台為垂直升降方式移動。</t>
+        </is>
+      </c>
+      <c r="I785" s="2" t="inlineStr"/>
     </row>
     <row r="786" ht="92.59999999999999" customHeight="1">
       <c r="A786" s="2" t="n">
@@ -34572,8 +35157,25 @@
       <c r="G786" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H786" s="2" t="n"/>
-      <c r="I786" s="2" t="n"/>
+      <c r="H786" s="2" t="inlineStr">
+        <is>
+          <t>這是一段非常正確且重要的安全觀念！使用高空作業車（如高空工作車）時，因為作業高度高、環境多變，確實常伴隨墜落、翻覆、感電或夾夾等重大風險。
+為了維護勞工作業安全，以下為您整理出必須特別重視的核心危害風險以及應遵循的安全規範重點：
+主要危害風險
+墜落風險：勞工自工作台邊緣或開口處墜落。
+翻覆與傾倒：因地盤不穩、超載、強風或未確實伸出支撐架（Outrigger）導致整車翻覆。
+感電危害：工作台或臂桿誤觸高壓電線。
+被夾、被卷：作業人員被結構物與工作台之間夾傷。
+物體飛落：上方工具或材料掉落擊中下方人員。
+應遵循的安全防護與規範
+落實法規與標準：依循職業安全衛生設施規則等相關法規，確認機具具備合格檢驗與自動檢查紀錄。
+依循說明書與標示：嚴格遵守製造廠商規定的載重限制、操作限制與警示標示。
+落實作業前檢點：使用前必須檢查煞車、制動裝置、液壓系統、防墜及警報裝置是否正常。
+個人防護具：作業人員應正確佩戴安全帽及符合規定之安全帶與全身背負式安全索，並確實鉤掛於指定之安全母索或固定點。
+合格操作人員：應由接受過專業訓練並取得合格證照之人員進行操作。</t>
+        </is>
+      </c>
+      <c r="I786" s="2" t="inlineStr"/>
     </row>
     <row r="787" ht="108" customHeight="1">
       <c r="A787" s="2" t="n">
@@ -34607,8 +35209,15 @@
       <c r="G787" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H787" s="2" t="n"/>
-      <c r="I787" s="2" t="n"/>
+      <c r="H787" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+「使用高空工作車從事作業時，於該高空工作車工作台上之勞工無須佩戴安全帶」此敘述為非。
+國立臺灣師範大學－環境安全衛生中心 根據《職業安全衛生設施規則》規定，使用高空工作車從事作業時，雇主應使該高空工作車工作台上之勞工佩戴安全帶等防護具，以防止墜落災害發生。
+農村發展及水土保持署</t>
+        </is>
+      </c>
+      <c r="I787" s="2" t="inlineStr"/>
     </row>
     <row r="788" ht="92.59999999999999" customHeight="1">
       <c r="A788" s="2" t="n">
@@ -34642,8 +35251,19 @@
       <c r="G788" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H788" s="2" t="n"/>
-      <c r="I788" s="2" t="n"/>
+      <c r="H788" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+使用高空工作車進行作業時，有誤的選項為：「可作為人員上下設備使用」。
+相關規範重點說明
+有誤選項：高空工作車的工作台不可作為人員上下建築物或結構物等其他設備的進出通道或上下工具使用。
+正確做法：
+作業區間內應限制人員進入：應設置標示或管制，防止無關人員進入發生危險。
+工作台應設 90 公分以上之護欄：以防止勞工墜落。
+不可超過積載荷重：應嚴格遵守載重限制，確保作業安全。</t>
+        </is>
+      </c>
+      <c r="I788" s="2" t="inlineStr"/>
     </row>
     <row r="789" ht="92.59999999999999" customHeight="1">
       <c r="A789" s="2" t="n">
@@ -34677,8 +35297,15 @@
       <c r="G789" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H789" s="2" t="n"/>
-      <c r="I789" s="2" t="n"/>
+      <c r="H789" s="2" t="inlineStr">
+        <is>
+          <t>使用高空工作車，應於每日作業前就其制動裝置、操作裝置及作業裝置之性能實施檢點。
+依據《職業安全衛生管理辦法》規定：
+每日作業前：應實施檢點，確認制動裝置、操作裝置及作業裝置之性能有無異常。
+每月定期檢查：應定期實施檢查一次，項目包含制動裝置、離合器、操作裝置、作業裝置、油壓裝置及安全裝置等。</t>
+        </is>
+      </c>
+      <c r="I789" s="2" t="inlineStr"/>
     </row>
     <row r="790" ht="92.59999999999999" customHeight="1">
       <c r="A790" s="2" t="n">
@@ -34712,8 +35339,13 @@
       <c r="G790" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H790" s="2" t="n"/>
-      <c r="I790" s="2" t="n"/>
+      <c r="H790" s="2" t="inlineStr">
+        <is>
+          <t>正確答案為 以上皆是（即包含制動裝置、操作裝置及作業裝置）。
+根據《職業安全衛生設施規則》及相關法規規定，雇主對高空工作車，應於每日作業前就其制動裝置、操作裝置及作業裝置之性能實施檢點，以維持應有性能並保障作業安全。</t>
+        </is>
+      </c>
+      <c r="I790" s="2" t="inlineStr"/>
     </row>
     <row r="791" ht="92.59999999999999" customHeight="1">
       <c r="A791" s="2" t="n">
@@ -34747,8 +35379,13 @@
       <c r="G791" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H791" s="2" t="n"/>
-      <c r="I791" s="2" t="n"/>
+      <c r="H791" s="2" t="inlineStr">
+        <is>
+          <t>使用高空工作車時，不得超過其(C) 積載荷重。
+依據台灣《職業安全衛生設施規則》規定，雇主對於高空工作車之使用，應注意不得超過其積載荷重及能力。</t>
+        </is>
+      </c>
+      <c r="I791" s="2" t="inlineStr"/>
     </row>
     <row r="792" ht="92.59999999999999" customHeight="1">
       <c r="A792" s="2" t="n">
@@ -34782,8 +35419,13 @@
       <c r="G792" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H792" s="2" t="n"/>
-      <c r="I792" s="2" t="n"/>
+      <c r="H792" s="2" t="inlineStr">
+        <is>
+          <t>高空工作車從事作業時，操作者與工作台上勞工間之連絡方式應該要採用統一指揮信號。
+為了確保作業安全、防止溝通誤解引發職業災害，法規與安全操作指引皆規定必須建立明確、統一的指揮信號（如手勢、無線電通訊或口令），而絕非隨意或不用連絡。</t>
+        </is>
+      </c>
+      <c r="I792" s="2" t="inlineStr"/>
     </row>
     <row r="793" ht="92.59999999999999" customHeight="1">
       <c r="A793" s="2" t="n">
@@ -34817,8 +35459,18 @@
       <c r="G793" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H793" s="2" t="n"/>
-      <c r="I793" s="2" t="n"/>
+      <c r="H793" s="2" t="inlineStr">
+        <is>
+          <t>錯誤的選項是「(B) 可使用 A 字梯」。
+在高空作業車（高空工作車）的工作台上，嚴禁使用 A 字梯、合梯或站立於箱子等物品上增加高度，否則極易因重心不穩而發生嚴重墜落災害。
+農村發展及水土保持署
+正確觀念與規範
+穩定與防傾：應站立於堅硬地或設置其他防傾、防倒塌設施。
+護欄限制：不可爬出護欄外作業，亦不得在護欄上增放工作踏板。
+外觀維護：設備外觀與結構應完好無損壞、無生鏽現象。</t>
+        </is>
+      </c>
+      <c r="I793" s="2" t="inlineStr"/>
     </row>
     <row r="794" ht="92.59999999999999" customHeight="1">
       <c r="A794" s="2" t="n">
@@ -34852,8 +35504,19 @@
       <c r="G794" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H794" s="2" t="n"/>
-      <c r="I794" s="2" t="n"/>
+      <c r="H794" s="2" t="inlineStr">
+        <is>
+          <t>使用手持砂輪機敘述正確的是 (B) 先試運轉。
+各選項解析
+(A) 拆除護罩：錯誤。防護罩（護罩）絕對不可拆除、反裝或任意改裝，以免碎屑或破裂的砂輪片飛出傷人。
+(B) 先試運轉：正確。使用前應先開機空轉數秒（或依規定試轉），確認沒有異音、劇烈晃動或偏擺後再進行作業。
+(C) 敲擊砂輪片：錯誤。嚴禁敲擊砂輪片，這容易造成內部產生肉眼看不見的裂紋，運轉時發生爆裂危險。
+(D) 單手握持：錯誤。操作時必須雙手緊握砂輪機（主握把與側邊輔助把手），避免單手操作導致機身失控發生危險。
+frtoolsman.easy.co 使用手持砂輪機敘述何者正確？(A)拆除護罩。(B)先試運轉 ...
+2024年6月18日 — 290 使用手持砂輪機敘述何者正確？ (A)拆除護罩。 (B)先試運轉。 (C)敲擊砂輪片。 (D)單手握持。 答案：登入後查看 統計： A(4), B(395), C(4), D(3), E(0) #3256980 ...</t>
+        </is>
+      </c>
+      <c r="I794" s="2" t="inlineStr"/>
     </row>
     <row r="795" ht="108" customHeight="1">
       <c r="A795" s="2" t="n">
@@ -34887,8 +35550,15 @@
       <c r="G795" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H795" s="2" t="n"/>
-      <c r="I795" s="2" t="n"/>
+      <c r="H795" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+選項 「車輛系營建機械作業時，人員可進入操作半徑內或附近有危險之虞之場所」 為非（錯誤的敘述）。
+說明
+依據《職業安全衛生設施規則》第116條規定，車輛系營建機械作業時，禁止人員進入操作半徑內或附近有危險之虞之場所（但駕駛者依規定就位者或另採安全措施者，不在此限），而非允許人員隨意進入。其餘選項皆符合該法規要求之正確執行事項。</t>
+        </is>
+      </c>
+      <c r="I795" s="2" t="inlineStr"/>
     </row>
     <row r="796" ht="92.59999999999999" customHeight="1">
       <c r="A796" s="2" t="n">
@@ -34922,8 +35592,13 @@
       <c r="G796" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H796" s="2" t="n"/>
-      <c r="I796" s="2" t="n"/>
+      <c r="H796" s="2" t="inlineStr">
+        <is>
+          <t>以上皆是。
+根據職業安全衛生設施規則相關法規，為了防止車輛機械（如堆高機、推土機、挖掘機等）在作業或移動時發生碰撞、危害勞工，雇主應依據不同的車輛類型與作業環境，裝設倒車燈、倒車蜂鳴器（警報裝置）及旋轉警示燈（閃光燈）等安全防護措施。</t>
+        </is>
+      </c>
+      <c r="I796" s="2" t="inlineStr"/>
     </row>
     <row r="797" ht="108" customHeight="1">
       <c r="A797" s="2" t="n">
@@ -34957,8 +35632,17 @@
       <c r="G797" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H797" s="2" t="n"/>
-      <c r="I797" s="2" t="n"/>
+      <c r="H797" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+機械操作時若發生安全裝置失效或損壞，正確的處置方式為應予維修完成確認安全後再使用。
+安全處置原則
+停止運轉：立即停止機械運作，避免發生意外。
+禁止便宜行事：絕對不可減少使用頻率、小心繼續勉強使用，或自行修改安全迴路將線路跳過。
+確認安全：必須完全修復、經過安全檢查與確認無虞後，才可以重新開啟或操作機械。</t>
+        </is>
+      </c>
+      <c r="I797" s="2" t="inlineStr"/>
     </row>
     <row r="798" ht="92.59999999999999" customHeight="1">
       <c r="A798" s="2" t="n">
@@ -34992,8 +35676,15 @@
       <c r="G798" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H798" s="2" t="n"/>
-      <c r="I798" s="2" t="n"/>
+      <c r="H798" s="2" t="inlineStr">
+        <is>
+          <t>以連桿、彈簧等控制離合器或油壓管路等動力傳動裝置，該連鎖裝置稱為機械連鎖（選項 D）。
+相關概念
+機械連鎖：利用實體機械零件（如連桿、凸輪、彈簧或油壓管路）直接連動或限制機構，使防護裝置與機械動作之間產生互相牽制的安全構造。
+其他如電氣連鎖、光電連鎖則是透過電氣信號或光電感應來達成控制與保護的目的。</t>
+        </is>
+      </c>
+      <c r="I798" s="2" t="inlineStr"/>
     </row>
     <row r="799" ht="92.59999999999999" customHeight="1">
       <c r="A799" s="2" t="n">
@@ -35027,8 +35718,13 @@
       <c r="G799" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H799" s="2" t="n"/>
-      <c r="I799" s="2" t="n"/>
+      <c r="H799" s="2" t="inlineStr">
+        <is>
+          <t>齒輪與齒條之傳動裝置，較易造成的危害是 (D) 被夾、被捲。
+當齒輪與齒條（或齒輪與齒輪）轉動時，兩者嚙合處會形成一個會夾入或捲入物體的危險點。如果人員的衣物、頭髮或手指靠近，極易發生被夾傷或捲入的嚴重工安意外。</t>
+        </is>
+      </c>
+      <c r="I799" s="2" t="inlineStr"/>
     </row>
     <row r="800" ht="92.59999999999999" customHeight="1">
       <c r="A800" s="2" t="n">
@@ -35062,8 +35758,20 @@
       <c r="G800" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H800" s="2" t="n"/>
-      <c r="I800" s="2" t="n"/>
+      <c r="H800" s="2" t="inlineStr">
+        <is>
+          <t>造紙廠於滾胴接紙作業時，較易發生被夾、被捲危害。
+正確答案：被夾、被捲
+原因：滾胴（或捲紙機、複捲機）在進行接紙或高速運轉時，旋轉的滾輪與紙帶之間存在極大的夾點與捲入點，人員若不慎接觸極易遭到機械捲入。
+勞動部職業安全衛生署 需要為您整理更多機械安全衛生的相關考題或防護重點嗎？
+勞工安全衛生法規題庫
+機械捲夾危害預防措施
+製造業常見職業災害類型
+較易發生下列何種危害？ (A)被切(B)墜落(C)感電(D)被夾
+2022年12月11日 — 56. 造紙廠於滾胴接紙作業時，較易發生下列何種危害？ (A)被切 (B)墜落 (C)感電 (D)被夾、被捲. 答案：登入後查看 統計： A(389), B(28), C(22), D ...</t>
+        </is>
+      </c>
+      <c r="I800" s="2" t="inlineStr"/>
     </row>
     <row r="801" ht="92.59999999999999" customHeight="1">
       <c r="A801" s="2" t="n">
@@ -35097,8 +35805,19 @@
       <c r="G801" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H801" s="2" t="n"/>
-      <c r="I801" s="2" t="n"/>
+      <c r="H801" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+「這台機械購置成本」不是辨識機械危害所需思考的因素。
+解析
+在進行職業安全衛生的機械危害辨識時，主要需評估機械的物理動作、加工方式、操作環境及對人員可能造成的實質威脅：
+(A) 預期機械會產生什麼旋轉、來回運動或上下移動：屬於機械運動部件帶來的夾、捲、割等實體危害評估。
+(C) 產生什麼廢料：加工過程產生的碎屑、粉塵或廢料可能伴隨飛散、中毒或割傷等危害需要一併考量。
+(D) 這台機械處理什麼原料、如何處理加工：原料特性與加工方式決定了操作時的危險點（如高溫、衝壓、切削）。
+(B) 這台機械購置成本：屬於經濟與採購預算考量，與現場作業安全、機械本身的物理危害辨識無關。</t>
+        </is>
+      </c>
+      <c r="I801" s="2" t="inlineStr"/>
     </row>
     <row r="802" ht="92.59999999999999" customHeight="1">
       <c r="A802" s="2" t="n">
@@ -35132,8 +35851,68 @@
       <c r="G802" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H802" s="2" t="n"/>
-      <c r="I802" s="2" t="n"/>
+      <c r="H802" s="2" t="inlineStr">
+        <is>
+          <t>，請稍後再試。
+網頁搜尋結果
+186. 進入混凝土預拌廠之拌合機內部清除結塊時，預防捲夾災害的 ...
+› item-186.++進入混凝土預拌廠之拌合...
+186. 進入混凝土預拌廠之拌合機內部清除結塊時，預防捲夾災害的最有 效方法為下列何者？ (A)設置寸動開關 (B)門蓋加裝連鎖裝置 (C)實施通風 (D)穿戴防護具. 答案：登入 ...
+182. () 危險性工作場所審查暨檢查辦法規定，須執行施工 ...
+› ...
+2020年1月21日 — () 進入混凝土預拌廠之拌合機內部清除結塊時，預防捲夾災害的最有 效方法為下列何者？ (A)設置寸動開關(B)門蓋加裝連鎖裝置(C)實施通風(D)穿戴防護具.
+勞委會呼籲，預拌混凝土拌合機入槽清理作業應依規定做好 ...
+勞動部全球資訊網
+› ...
+勞委會呼籲業者應確實依法令規定設置符合規定必要之安全設施，如拌合機、泥水分離設備及預拌混凝土車入槽作業時加鎖及設置連鎖裝置等，及加強安全作業程序之落實與內部控管 ...
+缺少字詞： 進入 ‎結 ‎塊 ‎夾 ‎有效 ‎方法 ‎何者？ ‎寸 ‎動 ‎門 ‎蓋 ‎裝
+一般甲業考題| PDF
+› document › 一般甲業考題
+( 2 ) 進入混凝土預拌廠之拌合機內部清除結塊時，預防捲夾災害的最有① 設置寸動開關② 門蓋加裝連鎖裝置③ 實施通風④ 穿戴防護具 效方法為下列何者？ 187. ( 2 ) ...
+從事混凝土拌合機下料口疏通清理作業時發生被夾災害
+勞動部職業安全衛生署
+› ...
+PDF
+說明：礦泉水瓶倒下壓到混凝土拌合機下料口夾頭「寸動關門」按鈕開關，致混凝. 土拌合機下料口夾頭關閉(夾住)。
+缺少字詞： 進入 ‎廠 ‎結 ‎塊 ‎預防 ‎捲 ‎最 ‎有效 ‎方法 ‎何者？ ‎蓋 ‎加 ‎裝 ‎連鎖
+從事水泥砂漿攪拌機之清洗作業發生被捲致死災害
+桃園市政府
+› Download
+PDF
+從事水泥砂漿攪拌機之清洗作業發生被捲致死災害. 一、 行業分類：其他專門營造業(4390)。 二、 災害類型：被夾、被捲(07)。 三、 媒介物：混合機及粉碎機(157)。
+缺少字詞： 進入 ‎混凝土 ‎預 ‎廠 ‎清除 ‎結 ‎塊 ‎預防 ‎最 ‎有效 ‎方法 ‎何者？ ‎寸 ‎動 ‎開關 ‎門 ‎蓋 ‎加 ‎裝 ‎連鎖
+【⚠注意】小心被「捲入」事端！保命措施不可少！ 常常在新聞 ...
+Facebook · 經濟部產業發展署
+超過 80 個回應 · 7 年前
+注意】小心被「捲入」事端！保命措施不可少！ 常常在新聞上看到勞工發生「被捲、被夾」 甚至是「感電」等職業災害 為了讓勞工的作業環境更 ...
+衛工職安小學堂－機械捲夾不只發生在工廠，小心誤「捲」事端
+臺北市政府全球資訊網
+› News_Content
+衛工處品管及職安科長盧師琁表示，工廠防止機械捲夾危害的方式，包括在易發生熱區設置「安全護罩」、熱區附近設置「緊急停止按鈕」、要求操作員維修保養時斷電停機，與操作 ...
+(最新版)甲種職業安全衛生業務主管_甲業主管人員151-200# ...
+› exam-112年++(最新版)甲種職業安全...
+2022年12月31日 — () 進入混凝土預拌廠之拌合機內部清除結塊時，預防捲夾災害的最有 效方法為下列何者？ (A)設置寸動開關(B)門蓋加裝連鎖裝置(C)實施通風(D)穿戴防護具.
+頁面導覽
+1
+2
+3
+4
+5
+6
+7
+8
+下一頁
+頁尾連結
+台灣
+708 臺南市安平區 - 根據你的 IP 位址
+- 更新位置
+說明
+提供意見
+隱私權
+服務條款</t>
+        </is>
+      </c>
+      <c r="I802" s="2" t="inlineStr"/>
     </row>
     <row r="803" ht="92.59999999999999" customHeight="1">
       <c r="A803" s="2" t="n">
@@ -35167,8 +35946,16 @@
       <c r="G803" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H803" s="2" t="n"/>
-      <c r="I803" s="2" t="n"/>
+      <c r="H803" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+答案是 變速裝置。
+說明
+變速裝置是用來調整輸送帶運轉速度或動力傳遞的機械結構，不屬於保護人員安全的防護或安全裝置。
+緊急停止開關、頭尾輪護罩（或護圍）以及啟動前之警報裝置皆是防止人員遭受夾捲、即時切斷動力或提醒周遭人員注意運轉的常見常設安全裝置。</t>
+        </is>
+      </c>
+      <c r="I803" s="2" t="inlineStr"/>
     </row>
     <row r="804" ht="92.59999999999999" customHeight="1">
       <c r="A804" s="2" t="n">
@@ -35202,8 +35989,16 @@
       <c r="G804" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H804" s="2" t="n"/>
-      <c r="I804" s="2" t="n"/>
+      <c r="H804" s="2" t="inlineStr">
+        <is>
+          <t>機械之連鎖式的防護原則上應該是防護失效時機械不能啟動。
+機械連鎖防護重點說明
+核心目的：當安全防護裝置失效、損壞或未正確閉合時，機械應無法被啟動或會立即停止運作。
+安全性設計：連鎖防護是為了防止防護未裝上或失效時造成人員傷害，屬於自動化安全機制，不依賴人工配合。
+多樣化應用：不限於光電裝置，還包含安全門開關、機械式連動及接近感應等形式。</t>
+        </is>
+      </c>
+      <c r="I804" s="2" t="inlineStr"/>
     </row>
     <row r="805" ht="92.59999999999999" customHeight="1">
       <c r="A805" s="2" t="n">
@@ -35237,8 +36032,14 @@
       <c r="G805" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H805" s="2" t="n"/>
-      <c r="I805" s="2" t="n"/>
+      <c r="H805" s="2" t="inlineStr">
+        <is>
+          <t>正確答案是 (D) 擠夾。
+原因說明
+擠夾危險：當機械的往復機件（來回移動的部件，例如活塞、滑塊）與周遭的固定物（如機身、牆壁或其他靜止設備）互相接近或碰撞時，其間的空隙會變小，容易將人員的肢體夾在中間，造成嚴重傷害。</t>
+        </is>
+      </c>
+      <c r="I805" s="2" t="inlineStr"/>
     </row>
     <row r="806" ht="92.59999999999999" customHeight="1">
       <c r="A806" s="2" t="n">
@@ -35266,8 +36067,15 @@
       <c r="G806" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H806" s="2" t="n"/>
-      <c r="I806" s="2" t="n"/>
+      <c r="H806" s="2" t="inlineStr">
+        <is>
+          <t>若有 6 名員工參與機械設備之維修工作，則最少需使用 6 把鎖進行上鎖作業。
+在進行 LOTO（Lockout/Tagout，上鎖掛牌）安全程序時，每一位參與維修的員工都必須各自擁有並鎖上自己的專屬掛鎖，以確保在自身工作完成並親自解鎖之前，設備無法被任何人誤啟動，因此人數與最少用鎖數是 1 對 1 的關係。
+Facebook
+·經濟部產業發展署</t>
+        </is>
+      </c>
+      <c r="I806" s="2" t="inlineStr"/>
     </row>
     <row r="807" ht="92.59999999999999" customHeight="1">
       <c r="A807" s="2" t="n">
@@ -35301,8 +36109,12 @@
       <c r="G807" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H807" s="2" t="n"/>
-      <c r="I807" s="2" t="n"/>
+      <c r="H807" s="2" t="inlineStr">
+        <is>
+          <t>Google AI 摘要未抓取到，請手動補充。</t>
+        </is>
+      </c>
+      <c r="I807" s="2" t="inlineStr"/>
     </row>
     <row r="808" ht="108" customHeight="1">
       <c r="A808" s="2" t="n">
@@ -35336,8 +36148,12 @@
       <c r="G808" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H808" s="2" t="n"/>
-      <c r="I808" s="2" t="n"/>
+      <c r="H808" s="2" t="inlineStr">
+        <is>
+          <t>Google AI 摘要未抓取到，請手動補充。</t>
+        </is>
+      </c>
+      <c r="I808" s="2" t="inlineStr"/>
     </row>
     <row r="809" ht="92.59999999999999" customHeight="1">
       <c r="A809" s="2" t="n">
@@ -35365,8 +36181,15 @@
       <c r="G809" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H809" s="2" t="n"/>
-      <c r="I809" s="2" t="n"/>
+      <c r="H809" s="2" t="inlineStr">
+        <is>
+          <t>依職業安全衛生設施規則規定，為防止勞工自粉碎機及混合機之開口部分墜落，高度應在 90 公分以上。
+相關法規重點
+必要設備：雇主應設有覆蓋、護圍或高度至少在 90公分以上之圍柵等防護設備。
+例外規定：若設置覆蓋、護圍或圍柵會阻礙作業，且從事該項作業之勞工已佩戴安全帶或安全索以防止墜落者，不在此限。</t>
+        </is>
+      </c>
+      <c r="I809" s="2" t="inlineStr"/>
     </row>
     <row r="810" ht="92.59999999999999" customHeight="1">
       <c r="A810" s="2" t="n">
@@ -35400,8 +36223,15 @@
       <c r="G810" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H810" s="2" t="n"/>
-      <c r="I810" s="2" t="n"/>
+      <c r="H810" s="2" t="inlineStr">
+        <is>
+          <t>依據《職業安全衛生設施規則》規定，答案為：良導體機器設備內之狹小空間。
+相關法規重點
+法規條號：《職業安全衛生設施規則》第250條。
+規定內容：雇主對勞工於良導體機器設備內之狹小空間，或於鋼架等致有觸及高導電性接地物之虞之場所，作業時所使用之交流電焊機，為防止感電，應設有自動電擊防止裝置（但採自動式焊接者，不在此限）。</t>
+        </is>
+      </c>
+      <c r="I810" s="2" t="inlineStr"/>
     </row>
     <row r="811" ht="92.59999999999999" customHeight="1">
       <c r="A811" s="2" t="n">
@@ -35435,8 +36265,20 @@
       <c r="G811" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H811" s="2" t="n"/>
-      <c r="I811" s="2" t="n"/>
+      <c r="H811" s="2" t="inlineStr">
+        <is>
+          <t>紅色且為凸出型
+依據勞動部之機械設備器具安全標準第21條規定：
+衝壓機械緊急停止裝置之操作部，應符合下列規定：
+紅色之凸出型按鈕或其他簡易操作、可明顯辨識及迅速有效之人為操作裝置。
+設置於各操作區。
+需要我整理更多機械安全法規常見考題或衝壓機械防護裝置的重點嗎？
+第21 條 - 勞動部-條文內容
+衝壓機械緊急停止裝置之操作部，應符合下列規定： 一、紅色之凸出型按鈕或其他簡易操作、可明顯辨識及迅速有效之人為操作裝置。 二、設置於各操作區。
+顯示全部 內容</t>
+        </is>
+      </c>
+      <c r="I811" s="2" t="inlineStr"/>
     </row>
     <row r="812" ht="92.59999999999999" customHeight="1">
       <c r="A812" s="2" t="n">
@@ -35470,8 +36312,16 @@
       <c r="G812" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H812" s="2" t="n"/>
-      <c r="I812" s="2" t="n"/>
+      <c r="H812" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+依職業安全衛生設施規則第43條規定，應設 護罩、護圍（選項中常表述為「護罩、護圍」或「護踢、護圍」之相近詞，正確法條原文為護罩、護圍、套胴、跨橋等設備）。
+重點整理
+應設設備：護罩、護圍。
+目的：防止原動機、轉軸、齒輪、傳動輪、傳動帶等高速轉動部位造成勞工夾捲危害。</t>
+        </is>
+      </c>
+      <c r="I812" s="2" t="inlineStr"/>
     </row>
     <row r="813" ht="92.59999999999999" customHeight="1">
       <c r="A813" s="2" t="n">
@@ -35505,8 +36355,16 @@
       <c r="G813" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H813" s="2" t="n"/>
-      <c r="I813" s="2" t="n"/>
+      <c r="H813" s="2" t="inlineStr">
+        <is>
+          <t>「裝設接地線」無法有效防止捲胴捲夾危害。
+原因解析
+裝設接地線：主要用於防止感電（觸電）危害或排除靜電，與機械轉動部位的夾捲、捲入危險無關。
+使用摩擦輪或惰輪、設置護圍及設置防護條（隔離捲夾點）等，均為機械防護設計或實體隔離方法，能有效預防或降低捲胴作業的捲夾風險。
+桃園市政府</t>
+        </is>
+      </c>
+      <c r="I813" s="2" t="inlineStr"/>
     </row>
     <row r="814" ht="92.59999999999999" customHeight="1">
       <c r="A814" s="2" t="n">
@@ -35540,8 +36398,15 @@
       <c r="G814" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H814" s="2" t="n"/>
-      <c r="I814" s="2" t="n"/>
+      <c r="H814" s="2" t="inlineStr">
+        <is>
+          <t>依據機械設備器具安全標準規定，該選項正確答案為 緊急停止裝置。
+相關名詞定義
+緊急停止裝置：指衝剪機械發生危險或異常時，以人為操作而使滑塊等動作緊急停止之裝置。
+快速停止機構：指衝剪機械檢出危險或異常時，能自動停止滑塊、刀具或撞錘動作之機構。</t>
+        </is>
+      </c>
+      <c r="I814" s="2" t="inlineStr"/>
     </row>
     <row r="815" ht="92.59999999999999" customHeight="1">
       <c r="A815" s="2" t="n">
@@ -35575,8 +36440,12 @@
       <c r="G815" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H815" s="2" t="n"/>
-      <c r="I815" s="2" t="n"/>
+      <c r="H815" s="2" t="inlineStr">
+        <is>
+          <t>Google AI 摘要未抓取到，請手動補充。</t>
+        </is>
+      </c>
+      <c r="I815" s="2" t="inlineStr"/>
     </row>
     <row r="816" ht="92.59999999999999" customHeight="1">
       <c r="A816" s="2" t="n">
@@ -35610,8 +36479,16 @@
       <c r="G816" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H816" s="2" t="n"/>
-      <c r="I816" s="2" t="n"/>
+      <c r="H816" s="2" t="inlineStr">
+        <is>
+          <t>依據《職業安全衛生設施規則》第73條規定，雇主對於離心機械，應裝置護蓋及連鎖裝置（即選項中的「連鎖裝置」）。
+財團法人職業災害預防及重建中心 相關規定重點
+裝置要求：離心機械必須裝置護蓋與連鎖裝置。
+連鎖功能：該連鎖裝置必須確保在護蓋未完全關閉時，機械無法啟動。
+財團法人職業災害預防及重建中心</t>
+        </is>
+      </c>
+      <c r="I816" s="2" t="inlineStr"/>
     </row>
     <row r="817" ht="92.59999999999999" customHeight="1">
       <c r="A817" s="2" t="n">
@@ -35645,8 +36522,15 @@
       <c r="G817" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H817" s="2" t="n"/>
-      <c r="I817" s="2" t="n"/>
+      <c r="H817" s="2" t="inlineStr">
+        <is>
+          <t>機器設置緊急按鈕的目的是 緊急停止。
+💡 核心功能說明
+即時切斷動力：當機器發生異常、操作人員受夾被捲，或有立即危險時，按下緊急按鈕可以馬上升降或切斷電源，使機器以最快速度停止運轉，防止災害擴大或人員受傷。
+醒目且易操作：通常設計為紅色圓頭（菇頭狀）並配有黃色底色，便於在危險發生的瞬間直覺地拍下。</t>
+        </is>
+      </c>
+      <c r="I817" s="2" t="inlineStr"/>
     </row>
     <row r="818" ht="92.59999999999999" customHeight="1">
       <c r="A818" s="2" t="n">
@@ -35680,8 +36564,12 @@
       <c r="G818" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H818" s="2" t="n"/>
-      <c r="I818" s="2" t="n"/>
+      <c r="H818" s="2" t="inlineStr">
+        <is>
+          <t>Google AI 摘要未抓取到，請手動補充。</t>
+        </is>
+      </c>
+      <c r="I818" s="2" t="inlineStr"/>
     </row>
     <row r="819" ht="92.59999999999999" customHeight="1">
       <c r="A819" s="2" t="n">
@@ -35715,8 +36603,15 @@
       <c r="G819" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H819" s="2" t="n"/>
-      <c r="I819" s="2" t="n"/>
+      <c r="H819" s="2" t="inlineStr">
+        <is>
+          <t>應設置的安全裝置為連鎖裝置。
+依據《職業安全衛生設施規則》第 73 條規定：
+雇主對於離心機械，應裝置覆蓋及連鎖裝置。
+前項連鎖裝置，應使覆蓋未完全關閉時無法啟動。</t>
+        </is>
+      </c>
+      <c r="I819" s="2" t="inlineStr"/>
     </row>
     <row r="820" ht="92.59999999999999" customHeight="1">
       <c r="A820" s="2" t="n">
@@ -35750,8 +36645,18 @@
       <c r="G820" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H820" s="2" t="n"/>
-      <c r="I820" s="2" t="n"/>
+      <c r="H820" s="2" t="inlineStr">
+        <is>
+          <t>墜落防止裝置不屬於塑膠射出成型機的安全裝置。
+說明
+塑膠射出成型機常見的安全防護設施包含：
+安全門裝置：具有非關閉狀態即無法啟動機械的性能。
+安全連鎖裝置（互鎖裝置）。
+安全護罩。
+Airiti Library 華藝線上圖書館 墜落防止裝置主要是用來防止人員從高處墜落的防護設施（例如高空作業、鷹架或安全帶相關裝置），因此不屬於操作平面上的塑膠射出成型機機械安全裝置。</t>
+        </is>
+      </c>
+      <c r="I820" s="2" t="inlineStr"/>
     </row>
     <row r="821" ht="92.59999999999999" customHeight="1">
       <c r="A821" s="2" t="n">
@@ -35785,8 +36690,17 @@
       <c r="G821" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H821" s="2" t="n"/>
-      <c r="I821" s="2" t="n"/>
+      <c r="H821" s="2" t="inlineStr">
+        <is>
+          <t>答案：(D) 爆炸
+解析
+衝剪機械（如沖床、剪床）主要進行金屬的衝壓、剪切、成型加工。
+作業過程主要機械危害包含：切斷、割傷、剪斷、夾/擠壓等。
+爆炸通常與化學品逸散、氣體/粉塵燃燒、壓力容器過壓等有關，非衝剪機械操作之主要機械性危害。
+需要我提供更多職業安全衛生管理或衝剪機械安全裝置（如光電式、雙手操作式）的考試重點嗎？</t>
+        </is>
+      </c>
+      <c r="I821" s="2" t="inlineStr"/>
     </row>
     <row r="822" ht="92.59999999999999" customHeight="1">
       <c r="A822" s="2" t="n">
@@ -35820,8 +36734,15 @@
       <c r="G822" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H822" s="2" t="n"/>
-      <c r="I822" s="2" t="n"/>
+      <c r="H822" s="2" t="inlineStr">
+        <is>
+          <t>設備上裝有雙手啟動之 2 個按鈕，一般應兩手同時各按 1 個安全操作。
+安全操作要點
+兩手同時按壓：勞工必須同時以雙手按壓左右 2 個啟動按鈕，才能啟動機械，藉此強迫雙手離開危險區域，防止手部遭機械夾傷或切割。
+嚴禁單手或固定操作：絕對不可使用膠帶、繩索或物件固定其中 1 個按鈕來企圖用單手操作，這會失去安全防護功能而容易發生職業災害。</t>
+        </is>
+      </c>
+      <c r="I822" s="2" t="inlineStr"/>
     </row>
     <row r="823" ht="92.59999999999999" customHeight="1">
       <c r="A823" s="2" t="n">
@@ -35855,8 +36776,12 @@
       <c r="G823" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H823" s="2" t="n"/>
-      <c r="I823" s="2" t="n"/>
+      <c r="H823" s="2" t="inlineStr">
+        <is>
+          <t>Google AI 摘要未抓取到，請手動補充。</t>
+        </is>
+      </c>
+      <c r="I823" s="2" t="inlineStr"/>
     </row>
     <row r="824" ht="92.59999999999999" customHeight="1">
       <c r="A824" s="2" t="n">
@@ -35890,8 +36815,15 @@
       <c r="G824" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H824" s="2" t="n"/>
-      <c r="I824" s="2" t="n"/>
+      <c r="H824" s="2" t="inlineStr">
+        <is>
+          <t>對外露動力傳動裝置或機件轉動裝置之防護效果最佳的是護罩（選項 C）。
+原因說明
+護罩（Guard）屬於固定式或實體物理隔離防護，能直接完全阻隔人員接觸轉動中的機械部位（如皮帶輪、齒輪、轉軸等），從源頭防止捲入與夾傷，是安全防護中效果最直接且最佳的實體措施。
+光電式安全裝置、掃除式安全裝置及拉回式安全裝置多屬於依賴感應、動作連動或干預操作的動態安全裝置，容易因零件老化、調整不當或失效而產生風險，因此在傳動裝置的直接防護上以固定護罩為最優先及最佳防護。</t>
+        </is>
+      </c>
+      <c r="I824" s="2" t="inlineStr"/>
     </row>
     <row r="825" ht="92.59999999999999" customHeight="1">
       <c r="A825" s="2" t="n">
@@ -35925,8 +36857,15 @@
       <c r="G825" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H825" s="2" t="n"/>
-      <c r="I825" s="2" t="n"/>
+      <c r="H825" s="2" t="inlineStr">
+        <is>
+          <t>破裂盤為壓力容器之安全裝置。
+破裂盤簡介
+功能：防止密閉容器或配管因內部壓力過大而損壞。
+原理：當內部壓力異常上升時，薄金屬板會破裂釋放氣體或流體，使壓力下降。</t>
+        </is>
+      </c>
+      <c r="I825" s="2" t="inlineStr"/>
     </row>
     <row r="826" ht="92.59999999999999" customHeight="1">
       <c r="A826" s="2" t="n">
@@ -35960,8 +36899,13 @@
       <c r="G826" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H826" s="2" t="n"/>
-      <c r="I826" s="2" t="n"/>
+      <c r="H826" s="2" t="inlineStr">
+        <is>
+          <t>飛輪、轉軸之轉動物體作業點的危險狀況，主要是捲入。
+當機械的轉軸、飛輪、齒輪或皮帶輪等旋轉組件在運動時，容易將作業人員的衣服、頭髮、手指或手套捲入旋轉件與固定件之間的間隙，造成嚴重的夾傷或捲入傷害。</t>
+        </is>
+      </c>
+      <c r="I826" s="2" t="inlineStr"/>
     </row>
     <row r="827" ht="92.59999999999999" customHeight="1">
       <c r="A827" s="2" t="n">
@@ -35995,8 +36939,16 @@
       <c r="G827" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H827" s="2" t="n"/>
-      <c r="I827" s="2" t="n"/>
+      <c r="H827" s="2" t="inlineStr">
+        <is>
+          <t>輸送帶尾輪之清潔作業，較常發生被夾、被捲災害。
+原因說明
+旋轉機械危害：輸送帶尾輪（Tail Pulley）在運轉時，皮帶與滾輪之間會形成夾點（Nip point）。
+清理風險：若在機械未完全停止運轉或未斷電上鎖的情況下進行擦拭、清理異物，衣物、手套或手指極易遭到旋轉的滾輪與皮帶被夾、被捲入，造成嚴重傷害甚至死亡。
+財團法人職業災害預防及重建中心</t>
+        </is>
+      </c>
+      <c r="I827" s="2" t="inlineStr"/>
     </row>
     <row r="828" ht="92.59999999999999" customHeight="1">
       <c r="A828" s="2" t="n">
@@ -36030,8 +36982,16 @@
       <c r="G828" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H828" s="2" t="n"/>
-      <c r="I828" s="2" t="n"/>
+      <c r="H828" s="2" t="inlineStr">
+        <is>
+          <t>操作鑽床時，不可穿戴棉手套。
+原因說明
+捲入風險：鑽床屬於旋轉機械，若配戴棉手套或任何寬鬆的手套，旋轉中的鑽頭極易將手套捲入，導致手指或手臂嚴重傷害。
+正確做法：操作鑽床時應禁止戴手套，並應配戴安全眼鏡防止切屑飛入眼睛，以及穿戴安全鞋保護足部。
+臺中市政府教育局</t>
+        </is>
+      </c>
+      <c r="I828" s="2" t="inlineStr"/>
     </row>
     <row r="829" ht="92.59999999999999" customHeight="1">
       <c r="A829" s="2" t="n">
@@ -36065,8 +37025,21 @@
       <c r="G829" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H829" s="2" t="n"/>
-      <c r="I829" s="2" t="n"/>
+      <c r="H829" s="2" t="inlineStr">
+        <is>
+          <t>正確答案是：繼續運轉。
+當物料夾在輸送帶的滾輪與皮帶之間時，這是非常危險的機械夾捲情境。絕對不可以繼續運轉，必須立即停機並執行安全鎖定程序（LOTO），以防止人員在排除故障時發生嚴重夾傷或斷肢意外。
+標準的安全故障排除步驟包括：
+🛑 停止運轉：第一時間切斷機械動力來源。
+🏷️ 掛牌公告：在啟動開關處懸掛「正在維修、禁止開機」的警告牌。
+🔒 多重上鎖裝置：執行上鎖（Lockout），確保多位維修人員各自擁有自己的鎖，防止不知情的人誤開電源。
+為了協助您進行安全訓練或考試複習，我可以提供以下協助：
+提供更多關於輸送帶安全作業標準（SOP）的法規說明。
+列出其他常見的機械夾捲預防題目與解析。
+請問您需要哪一方面的補充資料呢？ 內容</t>
+        </is>
+      </c>
+      <c r="I829" s="2" t="inlineStr"/>
     </row>
     <row r="830" ht="92.59999999999999" customHeight="1">
       <c r="A830" s="2" t="n">
@@ -36100,8 +37073,16 @@
       <c r="G830" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H830" s="2" t="n"/>
-      <c r="I830" s="2" t="n"/>
+      <c r="H830" s="2" t="inlineStr">
+        <is>
+          <t>答案是 (D) 安全護具。
+解析
+機械本質安全化是指從機械本身的設計、構造著手，縱使發生誤操作或零件故障，也不會導致災害，或將風險降到最低。
+(A) 連鎖裝置、(B) 安全係數之考量、(C) 安全閥 均屬於機械本質安全設計的作為或防護裝置。
+(D) 安全護具（如安全帽、護目鏡、安全鞋等）屬於個人防護具，是在無法完全靠機械本質安全解決時，作為最後防線的外在配備，不屬於機械本質安全化之作為或裝置。</t>
+        </is>
+      </c>
+      <c r="I830" s="2" t="inlineStr"/>
     </row>
     <row r="831" ht="92.59999999999999" customHeight="1">
       <c r="A831" s="2" t="n">
@@ -36135,8 +37116,16 @@
       <c r="G831" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H831" s="2" t="n"/>
-      <c r="I831" s="2" t="n"/>
+      <c r="H831" s="2" t="inlineStr">
+        <is>
+          <t>答案：戴用手套是非必要措施（實際上在旋轉機械或有夾捲風險的作業中，嚴禁戴手套，以免手套被機械捲入導致嚴重傷害）。
+防範機械夾傷、捲傷重點
+必要防護措施：
+實施點檢、修理、清掃時應予上鎖並設置「點檢中」、「危險勿近」等警示標示，防止他人誤動機械。
+操作或接近轉動機械時，應禁止勞工戴用手套或穿著寬鬆衣物，以防遭轉軸或齒輪捲入。</t>
+        </is>
+      </c>
+      <c r="I831" s="2" t="inlineStr"/>
     </row>
     <row r="832" ht="92.59999999999999" customHeight="1">
       <c r="A832" s="2" t="n">
@@ -36171,8 +37160,16 @@
       <c r="G832" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H832" s="2" t="n"/>
-      <c r="I832" s="2" t="n"/>
+      <c r="H832" s="2" t="inlineStr">
+        <is>
+          <t>答案是 (D) 滾胴間的捲入點。
+原因說明：
+滾胴間的捲入點（如輪軸、滾筒與滾筒之間夾入物品或肢體的機械危害）通常常見於滾壓機、印刷機、輸送帶等機械設備，而不屬於雷射加工機（以光束熱加工為主）的常見特有危害。
+其他選項（雷射光束誤照射人體、光束間接反射／折射／繞射發射、非游離輻射所引起的危害）皆為雷射加工機運作時常見的光學與輻射危害。
+Tailift Group</t>
+        </is>
+      </c>
+      <c r="I832" s="2" t="inlineStr"/>
     </row>
     <row r="833" ht="92.59999999999999" customHeight="1">
       <c r="A833" s="2" t="n">
@@ -36206,8 +37203,15 @@
       <c r="G833" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H833" s="2" t="n"/>
-      <c r="I833" s="2" t="n"/>
+      <c r="H833" s="2" t="inlineStr">
+        <is>
+          <t>該裝置為 (2) 全自動出料（或選項 B）。
+詳細說明
+全自動出料：利用壓縮空氣、機械手臂或其它自動化機構將成品從模具中吹出或取出，過程中完全不需要人工進行取料動作。
+與半自動或進料裝置的區分在於，此處強調的是「出料（取料）」動作已達到「全自動」化。</t>
+        </is>
+      </c>
+      <c r="I833" s="2" t="inlineStr"/>
     </row>
     <row r="834" ht="77.15000000000001" customHeight="1">
       <c r="A834" s="2" t="n">
@@ -36241,8 +37245,18 @@
       <c r="G834" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H834" s="2" t="n"/>
-      <c r="I834" s="2" t="n"/>
+      <c r="H834" s="2" t="inlineStr">
+        <is>
+          <t>汽油等易燃液體與液化石油氣等可燃性氣體引起的火災屬於 B 類（油類火災）。
+火災分類簡介
+A 類（普通火災）：木材、紙張、布料、塑膠等固體可燃物引起的火災。
+B 類（油類火災）：石油類、油脂類、有機溶劑等可燃性液體，以及液化石油氣、乙炔等可燃性氣體引起的火災。
+C 類（電氣火災）：通電中的電氣設備、變壓器或電線等引起的火災。
+D 類（金屬火災）：鎂、鉀、鋰等活性金屬引起的火災。
+苗栗縣政府全球資訊網</t>
+        </is>
+      </c>
+      <c r="I834" s="2" t="inlineStr"/>
     </row>
     <row r="835" ht="92.59999999999999" customHeight="1">
       <c r="A835" s="2" t="n">
@@ -36276,8 +37290,19 @@
       <c r="G835" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H835" s="2" t="n"/>
-      <c r="I835" s="2" t="n"/>
+      <c r="H835" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+下列何者不是乾粉滅火系統所用之滅火原理？答案是 冷卻。
+乾粉滅火原理說明
+抑制（抑制法）：為乾粉滅火最主要的機制，藉由化學藥劑破壞燃燒的連鎖反應。
+隔離（隔離法）：乾粉覆蓋於可燃物表面，具有隔離氧氣與火源的部份效果。
+窒息（窒息法）：乾粉受熱分解時會產生微量二氧化碳等氣體，具備輕微的遮斷氧氣效果。
+冷卻（冷卻法）：乾粉本身沒有顯著的冷卻降溫能力（相對而言，水系統才是利用冷卻原理）。
+桃園防災館</t>
+        </is>
+      </c>
+      <c r="I835" s="2" t="inlineStr"/>
     </row>
     <row r="836" ht="92.59999999999999" customHeight="1">
       <c r="A836" s="2" t="n">
@@ -36311,8 +37336,19 @@
       <c r="G836" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H836" s="2" t="n"/>
-      <c r="I836" s="2" t="n"/>
+      <c r="H836" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+毒化不是乾粉滅火系統所用之滅火原理。
+乾粉滅火原理說明
+隔離（隔離法）： 乾粉覆蓋在可燃物表面，阻絕空氣與氧氣。
+窒息（窒息法）： 乾粉受熱分解可能產生微量的二氧化碳或形成粉霧屏障，減少氧氣助燃。
+冷卻（冷卻法）： 乾粉噴入火場時會吸收部分熱能，具有微弱的冷卻效果（雖然主要機制是化學抑制）。
+抑制（抑制法/負觸媒）： 乾粉分解產生的金屬或銨根離子會捕捉燃燒連鎖反應中的活性自由基，為其最主要的滅火機制。
+萬安消防 題目中的「毒化」並非消防學或職業安全衛生中的正規滅火原理。</t>
+        </is>
+      </c>
+      <c r="I836" s="2" t="inlineStr"/>
     </row>
     <row r="837" ht="77.15000000000001" customHeight="1">
       <c r="A837" s="2" t="n">
@@ -36346,8 +37382,18 @@
       <c r="G837" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H837" s="2" t="n"/>
-      <c r="I837" s="2" t="n"/>
+      <c r="H837" s="2" t="inlineStr">
+        <is>
+          <t>一般可燃性固體如木材、紙張、紡織品等引起之火災稱為 A 類（普通火災）。
+火災分類簡介
+A 類（普通火災）：由木材、紙張、布料、塑膠等一般可燃性固體引起，燃燒後通常會產生灰燼或餘燼。
+B 類（油類火災）：由汽油、柴油、油漆或可燃性液體引起。
+C 類（電氣火災）：由通電中的電氣設備（如電線、配電盤、變壓器）引起。
+D 類（金屬火災）：由活性金屬（如鎂、鈉、鉀）引起。
+新竹市消防局</t>
+        </is>
+      </c>
+      <c r="I837" s="2" t="inlineStr"/>
     </row>
     <row r="838" ht="77.15000000000001" customHeight="1">
       <c r="A838" s="2" t="n">
@@ -36381,8 +37427,16 @@
       <c r="G838" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H838" s="2" t="n"/>
-      <c r="I838" s="2" t="n"/>
+      <c r="H838" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+紫燄乾粉對火場火災連鎖反應中之游離基之抑制效果最佳。
+滅火原理說明
+負催化作用（抑制連鎖反應）：乾粉滅火劑（特別是以碳酸氫鉀為主體的紫燄乾粉）在火場高溫下會分解，產生大量的活性基或捕捉游離基（自由基），阻斷燃燒的化學連鎖反應。
+效果比較：紫燄乾粉（鉀鹽乾粉）抑制游離基的效率高於普通乾粉（鈉鹽乾粉），而水與泡沫主要依靠冷卻與窒息（隔絕氧氣）作用。</t>
+        </is>
+      </c>
+      <c r="I838" s="2" t="inlineStr"/>
     </row>
     <row r="839" ht="92.59999999999999" customHeight="1">
       <c r="A839" s="2" t="n">

--- a/salf/丙種職業安全衛生業務主管題庫.xlsx
+++ b/salf/丙種職業安全衛生業務主管題庫.xlsx
@@ -37470,8 +37470,19 @@
       <c r="G839" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H839" s="2" t="n"/>
-      <c r="I839" s="2" t="n"/>
+      <c r="H839" s="2" t="inlineStr">
+        <is>
+          <t>泡沫滅火器不適用於電氣火災。
+中華都市安全推廣協會
+原因說明
+泡沫滅火器：主要成分包含水分，水能導電，因此用在通電的電器設備上可能會導致觸電危險或擴大短路。
+BC 乾粉滅火器：適用於 B 類（油類）與 C 類（電氣）火災。
+ABC 乾粉滅火器：適用於 A 類（普通）、B 類（油類）與 C 類（電氣）火災。
+二氧化碳滅火器（題目筆誤為二氣化碘）：適用於 B 類與 C 類火災，且不導電。
+消防防災館</t>
+        </is>
+      </c>
+      <c r="I839" s="2" t="inlineStr"/>
     </row>
     <row r="840" ht="108" customHeight="1">
       <c r="A840" s="2" t="n">
@@ -37505,8 +37516,17 @@
       <c r="G840" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H840" s="2" t="n"/>
-      <c r="I840" s="2" t="n"/>
+      <c r="H840" s="2" t="inlineStr">
+        <is>
+          <t>下列敘述中沒有不正確的選項，這題原本的完整考題選項（如 Yamol 題庫）通常包含「密閉燃燒空間使火自然熄滅為窒息法」等，而您列出的各項敘述在消防學理上皆為正確的滅火原理：
+隔離法：油料漏油引起火災時，關閉進口、停止輸送燃料，屬於移除可燃物的隔離滅火。
+冷卻法：以水降低火場溫度，使其低於燃燒點。
+窒息法：排除、隔絕或稀釋氧氣。
+抑制法（抑制連鎖反應）：以不燃性泡沫等覆蓋或透過化學干擾破壞燃燒連鎖反應。
+新竹市消防局</t>
+        </is>
+      </c>
+      <c r="I840" s="2" t="inlineStr"/>
     </row>
     <row r="841" ht="77.15000000000001" customHeight="1">
       <c r="A841" s="2" t="n">
@@ -37540,8 +37560,17 @@
       <c r="G841" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H841" s="2" t="n"/>
-      <c r="I841" s="2" t="n"/>
+      <c r="H841" s="2" t="inlineStr">
+        <is>
+          <t>油類發生火災不可用水澆滅。
+為什麼不能用水？
+油水不相容：水的密度比油大，水會沉到油的下方。
+高溫汽化：水接觸高溫油後會瞬間汽化成水蒸氣，體積膨脹約 1700 倍。
+引發爆燃：膨脹的水蒸氣會把帶火的高溫油帶向四周飛濺，導致火勢瞬間擴大甚至灼傷人員。
+大光明消防有限公司</t>
+        </is>
+      </c>
+      <c r="I841" s="2" t="inlineStr"/>
     </row>
     <row r="842" ht="77.15000000000001" customHeight="1">
       <c r="A842" s="2" t="n">
@@ -37575,8 +37604,18 @@
       <c r="G842" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H842" s="2" t="n"/>
-      <c r="I842" s="2" t="n"/>
+      <c r="H842" s="2" t="inlineStr">
+        <is>
+          <t>硫、磷、鉀、鈉、蠟燭、瀝青等可燃固體受熱先熔融蒸發、再與氧氣燃燒的形式屬於蒸發燃燒。
+燃燒類型說明
+蒸發燃燒：可燃固體加熱後先熔化、蒸發，蒸氣與氧氣混合後燃燒（如硫、磷、鉀、鈉、蠟燭、瀝青）。
+分解燃燒：可燃固體受熱分解出可燃氣體後再與氧氣燃燒（如木材、紙張）。
+表面燃燒：氧氣直接在固體表面進行無焰燃燒（如焦炭）。
+擴散燃燒：可燃氣體從噴口出來邊擴散邊與空氣混合燃燒。
+三民補習班</t>
+        </is>
+      </c>
+      <c r="I842" s="2" t="inlineStr"/>
     </row>
     <row r="843" ht="77.15000000000001" customHeight="1">
       <c r="A843" s="2" t="n">
@@ -37610,8 +37649,17 @@
       <c r="G843" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H843" s="2" t="n"/>
-      <c r="I843" s="2" t="n"/>
+      <c r="H843" s="2" t="inlineStr">
+        <is>
+          <t>易燃液體如酒精、汽油等的燃燒方式屬於蒸發燃燒。
+燃燒過程說明
+蒸發：酒精等易燃液體受熱或接觸火源後，液體表面會先汽化蒸發，產生可燃性蒸氣。
+著火：這些蒸氣與空氣中的氧氣混合，達到燃燒濃度後點燃並產生火焰。
+持續燃燒：火焰釋放的熱量會回頭加熱液體表面，促使更多蒸氣持續蒸發，形成循環。
+三民補習班</t>
+        </is>
+      </c>
+      <c r="I843" s="2" t="inlineStr"/>
     </row>
     <row r="844" ht="92.59999999999999" customHeight="1">
       <c r="A844" s="2" t="n">
@@ -37641,8 +37689,17 @@
       <c r="G844" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H844" s="2" t="n"/>
-      <c r="I844" s="2" t="n"/>
+      <c r="H844" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+沸騰液體膨脹蒸氣爆炸（BLEVE，題目筆誤為「肝脾巷氣」）是屬於 (3) 物理化學混合之爆炸。
+詳細原因
+物理性過程：起初是因為容器內部蒸氣壓力急劇升高，導致容器本身發生物理性破裂。
+化學性過程：若內容物為可燃性液體（如液化石油氣 LPG），噴發出的蒸氣接觸到外部火源後，會進一步引發劇烈的燃燒或蒸氣雲爆炸（VCE），因此兼具物理破裂與化學燃燒，屬於物理化學混合之爆炸。
+資料</t>
+        </is>
+      </c>
+      <c r="I844" s="2" t="inlineStr"/>
     </row>
     <row r="845" ht="77.15000000000001" customHeight="1">
       <c r="A845" s="2" t="n">
@@ -37676,8 +37733,21 @@
       <c r="G845" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H845" s="2" t="n"/>
-      <c r="I845" s="2" t="n"/>
+      <c r="H845" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+引火性物質表面有充分空氣遇到火種燃燒，持續燃燒時間達5秒以上，此時該物質之最低溫度稱為該物質之著火點。
+-三民輔考
+正確答案：著火點（又稱燃點）
+-三民輔考
+相關名詞區別
+引火點（閃火點）：液體表面產生足夠可燃蒸氣、接觸火源會「閃出火花」但無法持續燃燒的最低溫度。
+著火點（燃點）：接觸火源後，能持續燃燒達 5 秒以上的最低溫度。
+發火溫度（自燃點）：不需要外部火源，僅靠周遭環境高溫加熱就能自行起火燃燒的最低溫度。
+www.wunan.com.tw</t>
+        </is>
+      </c>
+      <c r="I845" s="2" t="inlineStr"/>
     </row>
     <row r="846" ht="77.15000000000001" customHeight="1">
       <c r="A846" s="2" t="n">
@@ -37711,8 +37781,16 @@
       <c r="G846" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H846" s="2" t="n"/>
-      <c r="I846" s="2" t="n"/>
+      <c r="H846" s="2" t="inlineStr">
+        <is>
+          <t>易燃液體表面若有充分空氣遇到火源立即燃燒，且歷久不滅（持續燃燒），此時該物質之最低溫度為著火點（又稱燃點）。
+名詞對照說明
+著火點：液體表面蒸氣濃度足夠，遇火源能持續燃燒不熄滅（歷久不滅）的最低溫度。
+閃火點 / 引火點：指液體表面蒸氣遇火源只能瞬間閃燃、隨即熄滅（無法持續燃燒）的最低溫度。
+發火溫度：指物質不需要外部火源引燃，就能自行在空氣中起火燃燒的最低溫度（又稱自燃溫度）。</t>
+        </is>
+      </c>
+      <c r="I846" s="2" t="inlineStr"/>
     </row>
     <row r="847" ht="77.15000000000001" customHeight="1">
       <c r="A847" s="2" t="n">
@@ -37746,8 +37824,17 @@
       <c r="G847" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H847" s="2" t="n"/>
-      <c r="I847" s="2" t="n"/>
+      <c r="H847" s="2" t="inlineStr">
+        <is>
+          <t>易燃液體產生足夠的蒸氣，在其容器內或與其近鄰空氣形成可被點燃的混合氣時之最低溫度，稱為閃火點。
+名詞小常識
+閃火點（Flash Point）：液體蒸氣接觸火源「瞬間閃燃、一閃即滅」的最低溫度。
+著火點（Fire Point / Ignition Point）：液體蒸氣接觸火源後，能「持續燃燒一段時間不熄滅」的最低溫度（通常高於閃火點）。
+沸點（Boiling Point）：液體沸騰變成氣體的溫度。
+熔點（Melting Point）：固體變成液體的溫度。</t>
+        </is>
+      </c>
+      <c r="I847" s="2" t="inlineStr"/>
     </row>
     <row r="848" ht="77.15000000000001" customHeight="1">
       <c r="A848" s="2" t="n">
@@ -37781,8 +37868,24 @@
       <c r="G848" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H848" s="2" t="n"/>
-      <c r="I848" s="2" t="n"/>
+      <c r="H848" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+(B) 閃火點（又稱 (C) 引火點）。
+關鍵名詞比較
+名詞	定義
+閃火點 / 引火點	蒸氣達燃燒下限、遇火源「一閃即滅」的最低溫度。
+著火點（燃點）	物質持續燃燒一段時間的最低溫度。
+發火溫（自燃點）	不需要外部火源就能自己起火的最低溫度。
+註：在多數消防與考試語境中，閃火點與引火點為同義詞（選項 (B) 與 (C) 皆符合，但單選題標準答案通常指向 (B) 閃火點 或視題庫給分）。
+维基百科 需要我補充 閃火點常見危險品級距（如一類、二類易燃液體） 嗎？
+. 可燃性液體揮發出的蒸氣在與空氣混合 ... - 年10月7日 — 18.可燃性液體揮發出的蒸氣在與空氣混合形成可燃性混合物並達到一定濃 度後，遇一定的溫度下時能夠閃爍起火的最低溫度？(A)著火點(B)閃火點 (C)引火點(D) ...
+维基百科
+閃燃點- ，自由的百科全書
+閃火點（又稱引火點，英語：flash point）是指揮發性物質所揮發出的氣體達到燃燒下限，與火源接觸下產生閃火（一閃即逝）的液體最低溫度。 一個較常見的例子是，燃料在低溫的冬天如果接近或等於這個溫度，引擎點火很可能就會點不起來。</t>
+        </is>
+      </c>
+      <c r="I848" s="2" t="inlineStr"/>
     </row>
     <row r="849" ht="92.59999999999999" customHeight="1">
       <c r="A849" s="2" t="n">
@@ -37816,8 +37919,18 @@
       <c r="G849" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H849" s="2" t="n"/>
-      <c r="I849" s="2" t="n"/>
+      <c r="H849" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+可燃性物質不自他處獲得火燄或電氣火花等火種引燃，而可自行在空氣燃燒之最低溫度稱為發火溫度（或稱發火點、自燃溫度）。故正確選項為 發火溫度。
+相關名詞區分
+引火點（閃點）：液體表面產生可燃蒸氣，接觸外部火源會閃火的最低溫度。
+著火點（燃點）：可燃物接觸外部火源後，能持續燃燒一定時間以上的最低溫度。
+發火溫度（自燃點）：不需要外部火源（明火、火花），僅靠自身受熱達到一定溫度就在空氣中自行燃燒的最低溫度。
+www.wunan.com.tw</t>
+        </is>
+      </c>
+      <c r="I849" s="2" t="inlineStr"/>
     </row>
     <row r="850" ht="77.15000000000001" customHeight="1">
       <c r="A850" s="2" t="n">
@@ -37851,8 +37964,14 @@
       <c r="G850" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H850" s="2" t="n"/>
-      <c r="I850" s="2" t="n"/>
+      <c r="H850" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+使易燃氣體之蒸氣、可燃性氣體著火所需最低能量，係指最小著火能量（或稱最小點火能量、最小著火能）。
+選項「最小善火能量」為筆誤（正確為最小著火能量/最小點火能）。</t>
+        </is>
+      </c>
+      <c r="I850" s="2" t="inlineStr"/>
     </row>
     <row r="851" ht="77.15000000000001" customHeight="1">
       <c r="A851" s="2" t="n">
@@ -37886,8 +38005,39 @@
       <c r="G851" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H851" s="2" t="n"/>
-      <c r="I851" s="2" t="n"/>
+      <c r="H851" s="2" t="inlineStr">
+        <is>
+          <t>，請稍後再試。
+網頁搜尋結果
+23 對於火災或爆炸之危險性敘述，何者正確？ (A)燃燒下 ...
+› item-23+對於火災或爆炸之危險性敘...
+2014年6月11日 — 23 對於火災或爆炸之危險性敘述，何者正確？ (A)燃燒下限值越大越危險(B)導電性越大越危險 (C)最小著火能量越大越危險(D)蒸氣壓越大越危險 ，包含題目 ...
+缺少字詞： 最低 ‎爆燃 ‎壓低
+工安ABC
+NTNU
+› ...
+何謂「爆炸上限」與「爆炸下限」？ Ans: 爆炸界限的大小與範圍是評估及控制火災危害的重要參數，一般而言，爆炸下限愈低或爆炸範圍愈大，則火災爆炸的危險性愈高。例如 ...
+缺少字詞： 態 ‎爆燃 ‎壓低
+嘗試還原-考古題115.1/5 今天at 115.1 ...
+Facebook · 職業安全衛生交流園地
+8 則留言 · 8 個月前
+(題目是溫度由低至高)答案是否為：「熔點」 &lt;「閃火點」&lt;「著火點」&lt;「沸點」&lt;「自燃溫 度」? 36w. OCR: at 115.1/5鳳 ...
+火災爆炸防止
+wunan.com.tw
+› download › preview
+PDF
+( )7. 何種物質若與可燃性物質或還原性物質接觸，並遇到衝擊、摩擦或火源就. 有發火、爆炸的危險？ 氧化性物質. 還原性物質. 液態物質. 毒性氣體。 ( )8. 泡沫 ...
+10 頁
+缺少字詞： 爆燃 ‎壓低
+什麼是可燃性氣體及爆炸極限？圖文解說1 次看懂
+iPEDIA 百科
+› 部落格
+2024年7月4日 — ◾ 爆炸下限在百分之 10 以下◾ 爆炸上限與下限之差在百分之 20 以上之氣體。 ◾ 包含： ▫ 氨、氫、苯、氰化氫、硫化氫、一氧化碳、二硫化碳▫ 甲烷、甲 ...
+缺少字詞： 壓低 ‎| 必須包含以下字詞： 壓低
+資料</t>
+        </is>
+      </c>
+      <c r="I851" s="2" t="inlineStr"/>
     </row>
     <row r="852" ht="77.15000000000001" customHeight="1">
       <c r="A852" s="2" t="n">
@@ -37921,8 +38071,83 @@
       <c r="G852" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H852" s="2" t="n"/>
-      <c r="I852" s="2" t="n"/>
+      <c r="H852" s="2" t="inlineStr">
+        <is>
+          <t>無法有效避免靜電火花產生之方式為 (A)利用惰性氣體充填。
+原理說明
+利用惰性氣體充填：屬於防止燃燒/爆炸（窒息法或濃度控制）的措施，它不能阻止靜電的產生或放電，只是讓周遭沒有氧氣助燃。
+接地與等電位連結：導引電荷流散，避免電位差與放電。
+增加溼度：增進表面導電性，加速電荷洩漏。
+穿戴導電器具：防止人體蓄積電荷。
+註：在部分職業安全衛生考題中，此題亦有被列為「本題刪題」之紀錄，但核心考義在於辨識「消除靜電」與「抑制燃燒氣體」的區別。
+載入中...
+顯示更多
+網頁搜尋結果
+41. 靜電為引發火災爆炸之重要火源之一，下列防護方式何者 ...
+› item-41.+靜電為引發火災爆炸之重要...
+2025年10月30日 — 41. 靜電為引發火災爆炸之重要火源之一，下列防護方式何者較無法避免靜電火花之產生？ (A)利用惰性氣體充填 (B)接地 (C)增加溼度 (D)穿戴導電器具。
+缺少字詞： 情 ‎性
+1202. 靜電為引發火災爆炸之重要火源之一，下列防護方式 ...
+› item-1202.+靜電為引發火災爆炸之重...
+2024年10月7日 — 41. 靜電為引發火災爆炸之重要火源之一，下列防護方式何者較無法避免靜電火花之產生？ (A)利用惰性氣體充填(B)接地(C)增加溼度(D)穿戴導電器具。
+缺少字詞： 情 ‎| 必須包含以下字詞： 情
+31.靜電為引發火災爆炸之重要火源之一，下列防護方式何者 ...
+› item-31.靜電為引發火災爆炸之重要...
+2024年5月14日 — 31.靜電為引發火災爆炸之重要火源之一，下列防護方式何者較無法避免靜電火花之產生？ (A)利用惰性氣體充填 (B)接地 (C)增加溼度 (D)穿戴導電器具。 答案 ...
+缺少字詞： 情 ‎| 必須包含以下字詞： 情
+[題庫][職業安全衛生管理(乙)][03：專業課程] BLOCK 學習網
+BLOCK 學習網
+› question
+1 111. 靜電為引發火災爆炸之重要火源之一，下列防護方式何者較無法避免靜電火花之產生？ A 利用惰性氣體充填. B 接地. C 增加溼度. D 穿戴導電器具.
+缺少字詞： 情 ‎| 必須包含以下字詞： 情
+(本題刪題)靜電為引發火災爆炸之重要火源之一
+職業安全衛生管理證照題庫練習
+› content › qbDetail
+(本題刪題)靜電為引發火災爆炸之重要火源之一，下列防護方式何者較無法避免靜電火花之產生？ · A 利用惰性氣體充填 · B 接地 · C 增加溼度 · D 穿戴導電器具.
+1 個答案
+·
+最佳解答:
+正確答案：A。靜電危害防制方法可分為接地、增加溼度、限制速度、抗靜電材料、與靜電消除器等五種。工業製造過程中 ...
+缺少字詞： 有效 ‎情 ‎性 ‎電位 ‎連結
+111. 靜電為引發火災爆炸之重要火源之一，下列防護方式 ...
+› item-111.+靜電為引發火災爆炸之重...
+2020年2月10日 — 41. 靜電為引發火災爆炸之重要火源之一，下列防護方式何者較無法避免靜電火花之產生？ (A)利用惰性氣體充填(B)接地(C)增加溼度(D)穿戴導電器具。
+缺少字詞： 情 ‎| 必須包含以下字詞： 情
+國防部軍備局生產製造中心第二0五廠「雇七等沖壓作業員」筆 ...
+中華民國國防部- 全球資訊網
+› File
+PDF
+靜電為引發火災爆炸之重要火源之一，下列防護方式何者較無法避免靜電火花之. 產生？①利用惰性氣體充填②接地③增加溼度④穿戴導電器具。 110. 依職業安全衛生管理辦法 ...
+丙種職業安全衛生業務主管筆記4版| PDF
+› document › 丙種職業安全衛...
+12 靜電爲引發火災爆炸之重要火源之一，下列防護方式何者較無法避免靜電火花之產生？ A (A)利用惰性氣體充塡(B)接地(C)增加溼度(D)穿戴導電器具。 12-1 電氣安全中 ...
+5.0(12)
+57.靜電為引發火災爆炸之重要火源之一，下列防護方式何者 ...
+› item-57.靜電為引發火災爆炸之重要...
+2022年3月16日 — 41. 靜電為引發火災爆炸之重要火源之一，下列防護方式何者較無法避免靜電火花之產生？ (A)利用惰性氣體充填(B)接地(C)增加溼度(D)穿戴導電器具。
+缺少字詞： 情 ‎| 必須包含以下字詞： 情
+頁面導覽
+1
+2
+3
+4
+5
+6
+7
+8
+9
+下一頁
+頁尾連結
+台灣
+708 臺南市安平區 - 根據你的 IP 位址
+- 更新位置
+說明
+提供意見
+隱私權
+服務條款</t>
+        </is>
+      </c>
+      <c r="I852" s="2" t="inlineStr"/>
     </row>
     <row r="853" ht="77.15000000000001" customHeight="1">
       <c r="A853" s="2" t="n">
@@ -37956,8 +38181,13 @@
       <c r="G853" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H853" s="2" t="n"/>
-      <c r="I853" s="2" t="n"/>
+      <c r="H853" s="2" t="inlineStr">
+        <is>
+          <t>正確答案是 氧化性物質。
+根據《職業安全衛生設施規則》第 184 條規定，為防止爆炸與火災，針對氧化性物質的處置規範為：「不得使其接觸促進其分解之物質，並不得予以加熱、摩擦或撞擊」。</t>
+        </is>
+      </c>
+      <c r="I853" s="2" t="inlineStr"/>
     </row>
     <row r="854" ht="92.59999999999999" customHeight="1">
       <c r="A854" s="2" t="n">
@@ -37991,8 +38221,16 @@
       <c r="G854" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H854" s="2" t="n"/>
-      <c r="I854" s="2" t="n"/>
+      <c r="H854" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+以氧乙炔熔接裝置切割型鋼時，連接切割器之橡皮管竄出火苗，應優先採行措施為關閉氧氣、乙炔鋼瓶。
+處理重點
+切斷氣源：橡皮管竄火或發生回火時，第一要務是立即關閉氣體供應源（氧氣與乙炔鋼瓶閥門），阻止可燃氣體繼續輸出，防止氣爆擴大。
+錯誤處置：若盲目使用滅火器或取水，並無法阻絕管路內部持續泄漏與燃燒的高壓氣體，反而延誤切斷源頭的黃金時間。</t>
+        </is>
+      </c>
+      <c r="I854" s="2" t="inlineStr"/>
     </row>
     <row r="855" ht="92.59999999999999" customHeight="1">
       <c r="A855" s="2" t="n">
@@ -38026,8 +38264,19 @@
       <c r="G855" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H855" s="2" t="n"/>
-      <c r="I855" s="2" t="n"/>
+      <c r="H855" s="2" t="inlineStr">
+        <is>
+          <t>使用氧乙炔熔接裝置作業時，應設置的安全設施為 (B) 滅火器。
+原因說明
+滅火器：氧乙炔作業會產生高溫火焰（約 3,000°C 以上），容易引起火災，因此作業現場必須備有滅火器以防萬一。
+Facebook
+其他選項：
+防止自動電擊防止裝置是用於「交流電焊機」作業。
+避雷針與氧乙炔氣體熔接作業無直接相關。
+漏電斷路器是用於電動機具或電氣設備防範觸電的裝置，非氣體熔接本身的必備安全設施。</t>
+        </is>
+      </c>
+      <c r="I855" s="2" t="inlineStr"/>
     </row>
     <row r="856" ht="92.59999999999999" customHeight="1">
       <c r="A856" s="2" t="n">
@@ -38061,8 +38310,17 @@
       <c r="G856" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H856" s="2" t="n"/>
-      <c r="I856" s="2" t="n"/>
+      <c r="H856" s="2" t="inlineStr">
+        <is>
+          <t>油漆桶發生火災屬於B類（油類）火災，不宜使用水作為滅火劑。
+Facebook
+·臺中市政府消防局第六救災救護大隊黎明分隊 原因說明
+水：油的密度比水小，若直接用水灌救，油會浮在水面上隨著水流四處流動，反而會讓火勢擴大蔓延。
+乾粉、二氧化碳與泡沫：均適用於B類油類火災的撲滅（其中乾粉與泡沫可覆蓋油面隔絕空氣，二氧化碳則能達到窒息與冷卻效果）。
+中華都市安全推廣協會</t>
+        </is>
+      </c>
+      <c r="I856" s="2" t="inlineStr"/>
     </row>
     <row r="857" ht="92.59999999999999" customHeight="1">
       <c r="A857" s="2" t="n">
@@ -38096,8 +38354,13 @@
       <c r="G857" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H857" s="2" t="n"/>
-      <c r="I857" s="2" t="n"/>
+      <c r="H857" s="2" t="inlineStr">
+        <is>
+          <t>切割瓦斯管線時，最重要的注意事項是 (D) 確定無瓦斯殘留。
+這是一道常見的職安卡（職業安全衛生教育訓練）考試題目。在進行任何可能產生火花或高熱的切割、焊接作業（如使用氧乙炔、砂輪機、電焊機等）之前，若管線內仍有殘留瓦斯，極易引起嚴重的燃燒與爆炸事故。因此，施工前務必先切斷氣源、排空並檢測確認管線內完全無瓦斯殘留，才能確保作業安全。</t>
+        </is>
+      </c>
+      <c r="I857" s="2" t="inlineStr"/>
     </row>
     <row r="858" ht="92.59999999999999" customHeight="1">
       <c r="A858" s="2" t="n">
@@ -38131,8 +38394,13 @@
       <c r="G858" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H858" s="2" t="n"/>
-      <c r="I858" s="2" t="n"/>
+      <c r="H858" s="2" t="inlineStr">
+        <is>
+          <t>當電線溫度太高，最可能發生的是 (B) 火災。
+這是一道常見的職業安全衛生（職安卡/業務主管）考試題目。當電線因為過載、短路或接觸不良導致溫度持續升高時，外層的絕緣皮會融化或燃燒，進而引發電氣火災。</t>
+        </is>
+      </c>
+      <c r="I858" s="2" t="inlineStr"/>
     </row>
     <row r="859" ht="92.59999999999999" customHeight="1">
       <c r="A859" s="2" t="n">
@@ -38166,8 +38434,16 @@
       <c r="G859" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H859" s="2" t="n"/>
-      <c r="I859" s="2" t="n"/>
+      <c r="H859" s="2" t="inlineStr">
+        <is>
+          <t>金屬鋰、金屬鈉與金屬鉀的最佳保存方式為儲存於石油醚中（題目中的「石油酚」應為「石油醚」之筆誤）。
+原因說明
+活性極高：鋰、鈉、鉀等鹼金屬化學活性非常強，極易與空氣中的氧氣反應而氧化。
+禁水性物質：這些金屬與水接觸會劇烈反應，甚至釋出氫氣引發燃燒或爆炸。
+石油醚隔離：石油醚（或礦物油、煤油）不含氧且不與這些金屬反應，能有效隔絕空氣與水分，是安全的浸泡保存液。</t>
+        </is>
+      </c>
+      <c r="I859" s="2" t="inlineStr"/>
     </row>
     <row r="860" ht="92.59999999999999" customHeight="1">
       <c r="A860" s="2" t="n">
@@ -38201,8 +38477,18 @@
       <c r="G860" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H860" s="2" t="n"/>
-      <c r="I860" s="2" t="n"/>
+      <c r="H860" s="2" t="inlineStr">
+        <is>
+          <t>將燃燒中的物質移開或斷絕供應以削弱火勢的方法是隔離法。
+滅火原理說明
+隔離法（移除法）：將可燃物移開或斷絕供應，使燃燒面積減少或使火勢無法延燒。
+窒息法：阻絕空氣或氧氣，使助燃物無法供應。
+冷卻法：降低溫度至燃點以下（例如用水滅火）。
+抑制法（負催化法）：中斷燃燒的連鎖反應。
+公職王</t>
+        </is>
+      </c>
+      <c r="I860" s="2" t="inlineStr"/>
     </row>
     <row r="861" ht="92.59999999999999" customHeight="1">
       <c r="A861" s="2" t="n">
@@ -38236,8 +38522,18 @@
       <c r="G861" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H861" s="2" t="n"/>
-      <c r="I861" s="2" t="n"/>
+      <c r="H861" s="2" t="inlineStr">
+        <is>
+          <t>紙張引起之火災（屬 A 類普通火災）以惰性氣體（如二氧化碳）的滅火效果較差。
+滅火效果分析
+惰性氣體：主要透過降低氧氣濃度來達到窒息滅火效果，但對紙張、木材等會深入內部悶燒的 A 類火災，無法有效降溫且容易復燃。
+水：具備極佳的冷卻降溫效果，是撲滅紙張火災最有效的方式。
+泡沫：能覆蓋表面隔絕氧氣並同時冷卻，適用於 A 類火災。
+ABC 類乾粉：可抑制燃燒連鎖反應，適用於 A、B、C 類火災。
+正德防火</t>
+        </is>
+      </c>
+      <c r="I861" s="2" t="inlineStr"/>
     </row>
     <row r="862" ht="77.15000000000001" customHeight="1">
       <c r="A862" s="2" t="n">
@@ -38271,8 +38567,17 @@
       <c r="G862" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H862" s="2" t="n"/>
-      <c r="I862" s="2" t="n"/>
+      <c r="H862" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+消防水系統所用之滅火原理是冷卻。
+滅火原理說明
+冷卻法：利用水吸收大量的熱能，有效降低燃燒物的溫度，使其降至燃點以下，進而達到滅火的效果。
+水的作用：水是日常中最經濟、實用且具強大冷卻能力的滅火介質。
+桃園防災館</t>
+        </is>
+      </c>
+      <c r="I862" s="2" t="inlineStr"/>
     </row>
     <row r="863" ht="77.15000000000001" customHeight="1">
       <c r="A863" s="2" t="n">
@@ -38306,8 +38611,16 @@
       <c r="G863" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H863" s="2" t="n"/>
-      <c r="I863" s="2" t="n"/>
+      <c r="H863" s="2" t="inlineStr">
+        <is>
+          <t>磷發生之火災不屬於 A 類火災。
+火災分類說明
+A 類火災（普通火災）： 指木製品、紙類、纖維、棉毛、橡膠、塑膠等普通可燃物所引起之火災。因此，橡膠、紙和木製品都屬於 A 類火災。
+D 類火災（金屬火災）： 指鉀、鈉、鎂、鈦、鋰、鋯及磷（黃磷/白磷等禁水性物質或特定金屬/化學物質）等物質引起之火災。
+基隆市消防局</t>
+        </is>
+      </c>
+      <c r="I863" s="2" t="inlineStr"/>
     </row>
     <row r="864" ht="77.15000000000001" customHeight="1">
       <c r="A864" s="2" t="n">
@@ -38341,8 +38654,18 @@
       <c r="G864" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H864" s="2" t="n"/>
-      <c r="I864" s="2" t="n"/>
+      <c r="H864" s="2" t="inlineStr">
+        <is>
+          <t>針對此選擇題，較佳的敘述為「應確認適用之滅火器措施」。
+原因解析
+應確認適用之滅火器措施：不同的火災類型（如A類普通火災、B類油類火災、C類電氣火災）需要使用不同種類的滅火器。例如電氣火災或油類火災若直接用水灌救，可能導致觸電或火勢擴大，因此必須先確認並採取適當的滅火方式。
+其他選項為什麼較不恰當：
+盡速用水灌救：若遇到油類（B類）或電氣（C類）火災，用水灌救非常危險。
+盡速逃離現場：雖然人身安全至關重要，但若在火災初期且火勢很小、自身安全無虞的情況下，應優先進行初期滅火或應變，而非一概而論「直接逃離」。
+不論火勢大小，先使用手提滅火器：如果火勢已經擴大失控，盲目使用小型滅火器不僅無效，還會延誤逃生時機。</t>
+        </is>
+      </c>
+      <c r="I864" s="2" t="inlineStr"/>
     </row>
     <row r="865" ht="92.59999999999999" customHeight="1">
       <c r="A865" s="2" t="n">
@@ -38376,8 +38699,15 @@
       <c r="G865" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H865" s="2" t="n"/>
-      <c r="I865" s="2" t="n"/>
+      <c r="H865" s="2" t="inlineStr">
+        <is>
+          <t>依據蒙特婁公約（Montreal Protocol）停止生產之滅火劑是指 海龍（Halon）滅火劑。
+原因簡述
+海龍滅火劑 含有會破壞地球臭氧層的氟氯碳化物（CFCs）及海龍成分。
+國際社會透過《蒙特婁公約》規範並逐步淘汰這類消耗臭氧層物質，因此全面停止生產海龍滅火劑。</t>
+        </is>
+      </c>
+      <c r="I865" s="2" t="inlineStr"/>
     </row>
     <row r="866" ht="77.15000000000001" customHeight="1">
       <c r="A866" s="2" t="n">
@@ -38411,8 +38741,15 @@
       <c r="G866" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H866" s="2" t="n"/>
-      <c r="I866" s="2" t="n"/>
+      <c r="H866" s="2" t="inlineStr">
+        <is>
+          <t>4°C。
+觀念解析
+閃火點的定義：閃火點（Flash Point）是指可燃性液體表面產生的蒸氣與空氣混合後，達到爆炸下限（LEL）且能被外部火源引燃的最低溫度。
+題目分析：題目已經明確指出，甲苯在常壓下且溫度為 4°C 時，其飽和蒸氣壓「剛好達到其爆炸下限」，這完全符合閃火點的物理定義。因此，該溫度即為甲苯的閃火點。</t>
+        </is>
+      </c>
+      <c r="I866" s="2" t="inlineStr"/>
     </row>
     <row r="867" ht="92.59999999999999" customHeight="1">
       <c r="A867" s="2" t="n">
@@ -38447,8 +38784,16 @@
       <c r="G867" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H867" s="2" t="n"/>
-      <c r="I867" s="2" t="n"/>
+      <c r="H867" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+氧乙炔焊接作業完畢時，其正確的關機程序是先關乙炔，再關氧氣。
+正確操作原因
+避免回火：先關閉乙炔可以切斷可燃氣體供應，防止殘留的氣體混和導致火焰倒灌或發生爆炸。
+熄滅火焰：操作時先將火炬上的乙炔閥門關閉使火熄滅，再關閉氧氣閥門。</t>
+        </is>
+      </c>
+      <c r="I867" s="2" t="inlineStr"/>
     </row>
     <row r="868" ht="108" customHeight="1">
       <c r="A868" s="2" t="n">
@@ -38482,8 +38827,17 @@
       <c r="G868" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H868" s="2" t="n"/>
-      <c r="I868" s="2" t="n"/>
+      <c r="H868" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+提高空氣中氧氣濃度，對易燃液體蒸汽之爆炸範圍影響為擴大。
+原因說明
+爆炸下限降低：氧氣濃度增加時，可燃性增強，使原本無法燃燒的較低氣體濃度也能達到燃燒條件（降低爆炸下限）。
+爆炸上限提高：同時，更高的氧氣量也能支援更高濃度的燃料蒸氣燃燒（提高爆炸上限）。
+範圍擴大：因此，爆炸上下限之間的區間（爆炸範圍）會變寬、擴大，增加火災與爆炸風險。</t>
+        </is>
+      </c>
+      <c r="I868" s="2" t="inlineStr"/>
     </row>
     <row r="869" ht="92.59999999999999" customHeight="1">
       <c r="A869" s="2" t="n">
@@ -38517,8 +38871,14 @@
       <c r="G869" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H869" s="2" t="n"/>
-      <c r="I869" s="2" t="n"/>
+      <c r="H869" s="2" t="inlineStr">
+        <is>
+          <t>大於音速。
+在氣體動力學與燃流學中，爆轟（Detonation）是一種極為劇烈的燃燒形式。它的燃燒波（反應前鋒）是以超音速（大於音速）在介質中傳播，通常可達每秒數公里，並會產生強烈的衝擊波。
+相較之下，一般常見的火災或瓦斯燃燒稱為「爆燃（Deflagration）」，其反應速度則「小於音速」。</t>
+        </is>
+      </c>
+      <c r="I869" s="2" t="inlineStr"/>
     </row>
     <row r="870" ht="108" customHeight="1">
       <c r="A870" s="2" t="n">
@@ -38552,8 +38912,16 @@
       <c r="G870" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H870" s="2" t="n"/>
-      <c r="I870" s="2" t="n"/>
+      <c r="H870" s="2" t="inlineStr">
+        <is>
+          <t>在缺氧危險而無火災、爆炸之虞的場所，不得戴用防毒面罩。
+原因說明
+防毒面罩（濾罐式）僅能過濾或吸附空氣中的有害氣體或蒸氣，無法提供氧氣。
+在缺氧環境中，空氣中的氧氣濃度不足（低於 18%），使用防毒面罩無法解決缺氧問題，會導致使用者窒息。
+應該使用能自主或外接供應氧氣/空氣的裝備，如空氣呼吸器、氧氣呼吸器或輸氣管面罩。</t>
+        </is>
+      </c>
+      <c r="I870" s="2" t="inlineStr"/>
     </row>
     <row r="871" ht="92.59999999999999" customHeight="1">
       <c r="A871" s="2" t="n">
@@ -38587,8 +38955,17 @@
       <c r="G871" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H871" s="2" t="n"/>
-      <c r="I871" s="2" t="n"/>
+      <c r="H871" s="2" t="inlineStr">
+        <is>
+          <t>高壓氣體在絕熱環境下吹洩，其溫度變化為下降。
+原因解析
+絕熱膨脹：高壓氣體快速向外噴出（吹洩）時，體積會瞬間膨脹。
+消耗內能：因為環境是絕熱的（沒有外界熱量補充），氣體膨脹對外作功所需的能量必須由自身的內部能量提供。
+溫度降低：內部能量消耗後，表現出來的結果就是氣體溫度下降，例如幫輪胎放氣或打開高壓氣瓶時會感覺噴嘴變冷。
+科技大觀園</t>
+        </is>
+      </c>
+      <c r="I871" s="2" t="inlineStr"/>
     </row>
     <row r="872" ht="92.59999999999999" customHeight="1">
       <c r="A872" s="2" t="n">
@@ -38616,8 +38993,19 @@
       <c r="G872" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H872" s="2" t="n"/>
-      <c r="I872" s="2" t="n"/>
+      <c r="H872" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+依據高壓氣體勞工安全規則第71條規定，將液化氣體灌注於儲槽時，應控制該液化氣體之容量不得超過在常用溫度下該槽內容積之 90 百分比（即 90%）。
+正確答案為：90。
+需要了解更多關於高壓氣體灌裝作業的其他安全規定嗎？
+可燃性與氧氣灌裝場距離限制
+容器定期檢查頻率與項目
+灌裝作業的禁煙火與防護規定
+第71 條 - 勞動部從事高壓氣體製造中之灌裝作業，應依下列規定辦理： 一、將液化氣體灌注於儲槽時，應控制該液化氣體之容量不得超過在常用溫度下該槽內容積之百分之九十；對液化毒性 ...</t>
+        </is>
+      </c>
+      <c r="I872" s="2" t="inlineStr"/>
     </row>
     <row r="873" ht="77.15000000000001" customHeight="1">
       <c r="A873" s="2" t="n">
@@ -38645,8 +39033,14 @@
       <c r="G873" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H873" s="2" t="n"/>
-      <c r="I873" s="2" t="n"/>
+      <c r="H873" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+依「危險性機械及設備安全檢查規則」規定，高壓氣體容器係指供灌裝高壓氣體之容器中，相對於地面可移動，其內容積在 500 公升以上。
+因此，正確答案為 500。</t>
+        </is>
+      </c>
+      <c r="I873" s="2" t="inlineStr"/>
     </row>
     <row r="874" ht="77.15000000000001" customHeight="1">
       <c r="A874" s="2" t="n">
@@ -38680,8 +39074,16 @@
       <c r="G874" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H874" s="2" t="n"/>
-      <c r="I874" s="2" t="n"/>
+      <c r="H874" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+置放於高溫或劇烈摩擦下易產生爆炸的物質為氧化性物質。
+答案解析
+氧化性物質：本身可能不一定會直接燃燒，但加熱、摩擦或撞擊時容易分解釋放出氧氣，並與可燃物劇烈反應甚至引發燃燒與爆炸。
+其他選項：還原性物質、水溶性物質或中性物質在高溫或摩擦下的物理/化學特性，並不像氧化性物質那樣具有顯著受熱或摩擦即易爆炸的危險特性。</t>
+        </is>
+      </c>
+      <c r="I874" s="2" t="inlineStr"/>
     </row>
     <row r="875" ht="77.15000000000001" customHeight="1">
       <c r="A875" s="2" t="n">

--- a/salf/丙種職業安全衛生業務主管題庫.xlsx
+++ b/salf/丙種職業安全衛生業務主管題庫.xlsx
@@ -39117,8 +39117,18 @@
       <c r="G875" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H875" s="2" t="n"/>
-      <c r="I875" s="2" t="n"/>
+      <c r="H875" s="2" t="inlineStr">
+        <is>
+          <t>這題的答案是 二甲苯（題目中的「二甲菜」為錯字）。
+以下為您解析各選項物質的性質：
+二甲苯（二甲菜）：屬於易燃液體（有機溶劑），它本身具有可燃性，不屬於氧化性物質。
+次氯酸鈣（欽氣酸鈣）：為強效的無機氧化劑，屬於氧化性物質。
+硝酸鉀（硝酸甸）：屬於氧化性物質，常作為火藥的助燃劑。
+氯酸鉀（氣酸甸）：屬於氧化性物質，常作為強氧化劑。
+揚程實業有限公司 請問這題是屬於職業安全衛生、消防法規還是基礎化學的考題呢？</t>
+        </is>
+      </c>
+      <c r="I875" s="2" t="inlineStr"/>
     </row>
     <row r="876" ht="77.15000000000001" customHeight="1">
       <c r="A876" s="2" t="n">
@@ -39152,8 +39162,18 @@
       <c r="G876" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H876" s="2" t="n"/>
-      <c r="I876" s="2" t="n"/>
+      <c r="H876" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+硝化甘油不是氧化性物質，它是爆炸性物質（第五類公共危險物品）。
+相關物質分類
+氯酸鈉：屬於氧化性物質（第一類）。
+過氯酸鈉：屬於氧化性物質（第一類）。
+硝酸鈉：屬於氧化性物質（第一類，硝酸鹽類）。
+硝化甘油：屬於具爆炸性質的爆炸性物質。</t>
+        </is>
+      </c>
+      <c r="I876" s="2" t="inlineStr"/>
     </row>
     <row r="877" ht="77.15000000000001" customHeight="1">
       <c r="A877" s="2" t="n">
@@ -39187,8 +39207,17 @@
       <c r="G877" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H877" s="2" t="n"/>
-      <c r="I877" s="2" t="n"/>
+      <c r="H877" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+鹽不會產生粉塵爆炸。
+原因說明
+可燃性差異：麵粉、糖和奶粉都是有機碳水化合物，屬於可燃性粉塵。當這些細小粉末懸浮在空氣中達到特定濃度時，遇到火源就容易引發劇烈的燃燒與爆炸。
+不可燃物質：鹽（氯化鈉）屬於不可燃物質，無法參與燃燒反應，因此不會產生粉塵爆炸。
+樹德家商</t>
+        </is>
+      </c>
+      <c r="I877" s="2" t="inlineStr"/>
     </row>
     <row r="878" ht="77.15000000000001" customHeight="1">
       <c r="A878" s="2" t="n">
@@ -39222,8 +39251,16 @@
       <c r="G878" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H878" s="2" t="n"/>
-      <c r="I878" s="2" t="n"/>
+      <c r="H878" s="2" t="inlineStr">
+        <is>
+          <t>大理石粉不會產生粉塵爆炸。
+原因說明
+不可燃性：大理石粉屬於無機礦石粉末，本身不具備可燃性，無法進行氧化連鎖反應。
+其他物質：穀粉（有機物）、鋁粉（金屬）、塑膠粉（合成物）皆具有可燃性，在空氣中達到特定濃度並遇火源時，皆可能引發粉塵爆炸。
+中華民國工業安全衛生協會 你可以參考詳細的 Yamol 題庫討論。</t>
+        </is>
+      </c>
+      <c r="I878" s="2" t="inlineStr"/>
     </row>
     <row r="879" ht="77.15000000000001" customHeight="1">
       <c r="A879" s="2" t="n">
@@ -39257,8 +39294,17 @@
       <c r="G879" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H879" s="2" t="n"/>
-      <c r="I879" s="2" t="n"/>
+      <c r="H879" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+粉塵爆炸係屬固相與氣相反應。
+原因說明
+固相：懸浮在空氣中的可燃性固體微粒（如麵粉、煤塵、金屬粉末等）。
+氣相：空氣中的氧氣或其他助燃氣體。
+當微細的固體粉塵均勻懸浮於氣體中，接觸到火源時會與氧氣發生極為劇烈的非均勻相燃燒反應，並在短時間內釋放大量熱能與氣體，進而引發爆炸。</t>
+        </is>
+      </c>
+      <c r="I879" s="2" t="inlineStr"/>
     </row>
     <row r="880" ht="77.15000000000001" customHeight="1">
       <c r="A880" s="2" t="n">
@@ -39292,8 +39338,19 @@
       <c r="G880" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H880" s="2" t="n"/>
-      <c r="I880" s="2" t="n"/>
+      <c r="H880" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+電腦機房之電氣設備所引起之火災種類為 (C) C類（電氣火災）。
+消防法令查詢系統 火災分類簡介
+C類火災：指通電中的電氣設備（如電腦、變壓器、配電盤、電氣配線等）所引起的火災。
+A類（甲類）：普通固體火災（木材、紙張等）。
+B類（乙類）：液體與可燃性油脂火災。
+D類（丁類）：金屬火災。
+內政部消防署全球資訊網</t>
+        </is>
+      </c>
+      <c r="I880" s="2" t="inlineStr"/>
     </row>
     <row r="881" ht="92.59999999999999" customHeight="1">
       <c r="A881" s="2" t="n">
@@ -39327,8 +39384,91 @@
       <c r="G881" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H881" s="2" t="n"/>
-      <c r="I881" s="2" t="n"/>
+      <c r="H881" s="2" t="inlineStr">
+        <is>
+          <t>常用乾粉滅火器的主要成分為 (A) 碳酸氫鈉、碳酸氫鉀（或磷酸二氫銨）。
+載入中...
+顯示更多
+網頁搜尋結果
+43. () 常用乾粉滅火器的主要成分為下列何者？ (A)碳酸氫鈉
+› item-43.+()+常用乾粉滅火器的主要成...
+2020年1月21日 — 43. () 常用乾粉滅火器的主要成分為下列何者？ (A)碳酸氫鈉、碳酸氫鉀(B)二氧化碳(C)隋性氣體(D)鹵化烷 ，包含題目內容、選項、詳解等，幫助學生提升 ...
+缺少字詞： 分 ‎下 ‎到
+滅火器種類一次看懂，6種滅火器成份分類、原理解析
+正德防火
+› 消防知識 › 滅火器知識
+二氧化碳滅火器內部填充加壓二氧化碳氣體（CO2），對準火源噴射後會排擠掉火源周遭的氧氣，讓火源窒息停止燃燒。 二氧化碳可說是汙染最小的滅火器種類之一，缺點是對於普通 ...
+缺少字詞： 常用 ‎主要 ‎何者 ‎碳酸 ‎鈉、 ‎鉀 ‎隋
+乾粉滅火器完整指南：原理、種類、4步驟使用教學與常見問題 ...
+中華都市安全推廣協會
+› fire-safety-home › dry-powd...
+ABC 乾粉滅火器：使用磷酸銨鹽類乾粉，可撲滅A、B、C 類火災，是目前最常見、通用性最高的類型，廣泛配置於住宅、辦公室、小型商家與公共場所。 · KBC 乾粉滅火器：以碳酸氫 ...
+缺少字詞： 常用 ‎何者 ‎隋 ‎鹵化 ‎烷
+39 常用乾粉滅火器的主要成分為下列何者？ (A)碳酸氫鈉
+› item-39+常用乾粉滅火器的主要成分...
+2023年8月24日 — (A)碳酸氫鈉、碳酸氫鉀(B)二氧化碳(C)隋性氣體(D)鹵化烷. #2164204 · 43. 常用乾粉滅火器的主要成分為下列何者？ (A)碳酸氫鈉、碳酸氫鉀(B)二氧化碳(C)隋 ...
+缺少字詞： 分 ‎下 ‎到 ‎2
+相關問題
+乾粉滅火器的主要成分是什麼?
+一般常見的乾粉滅火器無法對應哪一類火災？
+滅火的三要素是什麼?
+二氧化碳型滅火器是用於哪些種類火災？
+網頁搜尋結果
+火災初期滅火-滅火器
+消防防災館
+› cht
+二、滅火器怎麼用？記住「拉、瞄、壓、掃」 · 【拉】開安全插梢。 · 握住皮管前端，【瞄】向火源底部。 · 【壓】下握把，壓到底，讓滅火劑完全噴出。 · 向火源根部左右移動【掃】 ...
+乾粉滅火器種類
+賜億消防器材實業有限公司
+› 最新消息 › 防災相關知識
+乾粉滅火器種類 · 1.多效磷鹽乾粉ABC乾粉磷酸二氫銨(NH4H2PO4)70%以上白色或紫色以外 · 2.普通乾粉BC乾粉碳酸氫鈉（NaHCO3）90%以上白 · 3.紫焰乾粉KBC乾粉碳酸氫鉀（KHCO3） ...
+缺少字詞： 常用 ‎主要 ‎到 ‎何者 ‎隋 ‎性 ‎烷
+廢滅火器用滅火藥劑認可基準（961102訂定） - 消防法令查詢
+消防法令查詢系統
+› MOBILE › law
+普通乾粉│BC 乾粉│碳酸氫鈉（NaHC│白色│ │ │ │O3）90 ％以上 ... （2）碳酸氫鈉（或碳酸氫鉀）：秤取樣品0.7 至0.8 公克於錐形瓶中，加數滴中性 ...
+缺少字詞： 常用 ‎何者 ‎隋 ‎烷
+最新乾粉滅火器使用方法、原理以及成份介紹！ - 熊安心的生活
+熊安心的生活
+› 部落格列表
+2023年5月23日 — 前述有提到，乾粉滅火器主成份為碳酸氫鉀或磷酸二氫銨等製劑，這些是腐蝕性粉塵，吸入人體後可能會造成呼吸器官過敏、受傷，嚴重者甚至會當場劇烈咳嗽、 ...
+缺少字詞： 常用 ‎何者 ‎鈉、 ‎隋 ‎鹵化 ‎烷
+滅火器的介紹-尚好消防
+尚好消防有限公司
+› 消防設備
+二、六大滅火器種類原理 ; 乾粉滅火器, 1.B、C類乾粉滅火器的主要成分為小蘇打粉。 2.A、B、C類乾粉滅火器的主要成分為磷酸二氫銨。 1.乾粉滅火器為市面上最常見的滅火器。( ...
+缺少字詞： 常用 ‎下 ‎何者 ‎碳酸 ‎隋
+其他人也搜尋了以下項目
+乾粉滅火器成分
+乾粉滅火器滅火原理
+二氧化碳滅火器
+乾粉滅火器化學式
+滅火器種類
+氣體滅火器保存期限
+強化液滅火器
+氣體滅火器優缺點
+頁面導覽
+1
+2
+3
+4
+5
+6
+7
+8
+9
+下一頁
+頁尾連結
+台灣
+708 臺南市安平區 - 根據你的 IP 位址
+- 更新位置
+說明
+提供意見
+隱私權
+服務條款</t>
+        </is>
+      </c>
+      <c r="I881" s="2" t="inlineStr"/>
     </row>
     <row r="882" ht="77.15000000000001" customHeight="1">
       <c r="A882" s="2" t="n">
@@ -39362,8 +39502,18 @@
       <c r="G882" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H882" s="2" t="n"/>
-      <c r="I882" s="2" t="n"/>
+      <c r="H882" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+金屬鉀所引起之火災適合用特種金屬化學乾粉滅火劑。
+原因說明
+D類金屬火災：鉀屬於活性金屬（禁水性物質），與水或含水分子的滅火劑（如泡沫）接觸會產生劇烈反應甚至爆炸。
+二氧化碳與惰性氣體：對高溫燃燒的鉀金屬效果有限，甚至可能引發其他反應。
+特種金屬化學乾粉：專門用來撲滅 D 類金屬火災（如氯化鈉、石墨粉等乾粉），能覆蓋燃燒表面並隔絕氧氣。
+正德防火</t>
+        </is>
+      </c>
+      <c r="I882" s="2" t="inlineStr"/>
     </row>
     <row r="883" ht="77.15000000000001" customHeight="1">
       <c r="A883" s="2" t="n">
@@ -39397,8 +39547,17 @@
       <c r="G883" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H883" s="2" t="n"/>
-      <c r="I883" s="2" t="n"/>
+      <c r="H883" s="2" t="inlineStr">
+        <is>
+          <t>金屬鎂所引起之火災屬於 D類火災（金屬火災）。
+正德防火
+火災分類重點
+D類火災定義：指鈉、鉀、鎂、鋰、鈦與鋯等可燃性金屬物質及禁水性物質引起的火災。
+滅火注意事項：這類金屬燃燒時溫度極高，且部分具禁水性（遇水會劇烈反應並釋放氫氣），絕對不能直接用水或一般滅火器撲滅，必須使用金屬火災專用滅火劑。
+正德防火</t>
+        </is>
+      </c>
+      <c r="I883" s="2" t="inlineStr"/>
     </row>
     <row r="884" ht="92.59999999999999" customHeight="1">
       <c r="A884" s="2" t="n">
@@ -39432,8 +39591,22 @@
       <c r="G884" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H884" s="2" t="n"/>
-      <c r="I884" s="2" t="n"/>
+      <c r="H884" s="2" t="inlineStr">
+        <is>
+          <t>當家用天然氣洩漏時，不能開啟抽風機等電氣設備，主要避免開關之電氣火花引起火災。
+原因說明
+電氣開關火花：按下或啟動電器開關的瞬間，內部接點常會產生微小的肉眼可見或隱性電氣火花。
+引燃風險：天然氣（主要成分為甲烷）只要達到爆炸極限，極微小的電氣火花就足以點燃並引發嚴重氣爆或火災。
+新竹縣消防局
+正確應對步驟：
+禁：禁止開、關任何電燈、抽風機或電器，以免產生火花。
+關：關閉瓦斯總開關或瓦斯桶閥門。
+推：輕輕推開窗戶讓空氣流通，切勿動作過大。
+離：離開現場到戶外安全處，撥打119或通報瓦斯公司。
+臺北市政府全球資訊網</t>
+        </is>
+      </c>
+      <c r="I884" s="2" t="inlineStr"/>
     </row>
     <row r="885" ht="92.59999999999999" customHeight="1">
       <c r="A885" s="2" t="n">
@@ -39467,8 +39640,17 @@
       <c r="G885" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H885" s="2" t="n"/>
-      <c r="I885" s="2" t="n"/>
+      <c r="H885" s="2" t="inlineStr">
+        <is>
+          <t>防爆危險區域劃分為 0 區 (Zone 0) 之作業場所，應使用本質安全防爆構造之電動機。
+防爆區域與防爆構造對應說明
+0 區 (Zone 0)：爆炸性氣體環境連續性或長期存在之場所，風險最高，必須採用本質安全防爆型（Ex ia）等極高安全等級之設備。
+耐壓防爆：通常適用於 1 區或 2 區。
+安全增防爆 / 內壓防爆：多用於 1 區或 2 區之特定條件。
+全民勞教e網</t>
+        </is>
+      </c>
+      <c r="I885" s="2" t="inlineStr"/>
     </row>
     <row r="886" ht="108" customHeight="1">
       <c r="A886" s="2" t="n">
@@ -39502,8 +39684,19 @@
       <c r="G886" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H886" s="2" t="n"/>
-      <c r="I886" s="2" t="n"/>
+      <c r="H886" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+因為修護、保養作業或洩漏而使爆炸性氣體環境經常存在之場所，屬於 1 區 (Zone 1)。
+中小企業安全衛生資訊網
+危險區域劃分重點說明
+0 區 (Zone 0)：爆炸性氣體環境為連續性或長時間存在之場所。
+1 區 (Zone 1)：爆炸性氣體環境在正常操作下可能存在，或因修護、保養作業及洩漏而經常存在之場所。
+2 區 (Zone 2)：爆炸性氣體環境在正常操作下不太可能發生，若發生也僅存在短暫期間之場所。
+iPEDIA 百科</t>
+        </is>
+      </c>
+      <c r="I886" s="2" t="inlineStr"/>
     </row>
     <row r="887" ht="77.15000000000001" customHeight="1">
       <c r="A887" s="2" t="n">
@@ -39537,8 +39730,18 @@
       <c r="G887" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H887" s="2" t="n"/>
-      <c r="I887" s="2" t="n"/>
+      <c r="H887" s="2" t="inlineStr">
+        <is>
+          <t>鎂粉、鋁粉所造成的火災，是屬於 (D) D類 火災。
+火災分類簡介
+A類（普通火災）：木材、紙張、布料等固體物質引起的火災。
+B類（油類火災）：汽油、油漆、油脂等液體物質引起的火災。
+C類（電器火災）：通電中的電氣設備引起的火災。
+D類（金屬火災）：鎂、鉀、鈉、鈦、鋯等 可燃性金屬 或 禁水性物質 引起的火災。
+消防法令查詢系統</t>
+        </is>
+      </c>
+      <c r="I887" s="2" t="inlineStr"/>
     </row>
     <row r="888" ht="92.59999999999999" customHeight="1">
       <c r="A888" s="2" t="n">
@@ -39572,8 +39775,22 @@
       <c r="G888" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H888" s="2" t="n"/>
-      <c r="I888" s="2" t="n"/>
+      <c r="H888" s="2" t="inlineStr">
+        <is>
+          <t>裝設無熔絲開關之主要目的為防止電氣火災（選項 C）。
+原因解析
+無熔絲開關（NFB）：主要功能是用來感測電路中的過載或短路狀況。當電流過大或發生短路時，它會自動跳脫以切斷電源，進而避免電線過熱走火，達到防止電氣火災的目的。
+財團法人職業災害預防及重建中心 其他選項說明：
+防止感電：通常是透過「漏電斷路器（ELCB）」或「接地」來達成，而非無熔絲開關。
+防止靜電：需透過接地、導電材質或控制相對濕度等方式預防。
+增加電阻：不符合開關的保護功能。
+行政院公共工程委員會全球資訊網 需要了解無熔絲開關與漏電斷路器的差異嗎？
+兩者功能與差異比較
+無熔絲開關常見跳電原因
+最新資料 - () 裝設無熔絲開關之主要目的為何？ (A)防止感電(B)防止靜電(C)防止電氣火災(D)增加電阻 · 207. () 雇主不應要求醫護人員臨廠服務下列何事項？ (A)提供健康檢查資料以 ...</t>
+        </is>
+      </c>
+      <c r="I888" s="2" t="inlineStr"/>
     </row>
     <row r="889" ht="92.59999999999999" customHeight="1">
       <c r="A889" s="2" t="n">
@@ -39607,8 +39824,18 @@
       <c r="G889" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H889" s="2" t="n"/>
-      <c r="I889" s="2" t="n"/>
+      <c r="H889" s="2" t="inlineStr">
+        <is>
+          <t>電焊操作人員所穿的防火衣，以不導電之尼龍材質為佳不屬於電氣火災之防止對策。
+原因解析
+尼龍（Nylon）材質的特性：尼龍屬於合成纖維，加熱後容易熔化（熔點較低），在進行電焊作業時，若接觸到高溫火花或熔渣容易熔穿並黏附在皮膚上造成嚴重灼傷；此外，防火衣應考慮耐高溫及阻燃性，而非單純以「不導電之尼龍」視為理想材質。
+正確的電氣火災防止對策：
+導線之負載勿超過規定容量：避免電流過載產生高溫起火。
+導線應定期檢查：及早發現絕緣破損或老化現象。
+電氣設備在不使用時，應確實關閉電源：防止設備異常發熱或走火。</t>
+        </is>
+      </c>
+      <c r="I889" s="2" t="inlineStr"/>
     </row>
     <row r="890" ht="77.15000000000001" customHeight="1">
       <c r="A890" s="2" t="n">
@@ -39642,8 +39869,34 @@
       <c r="G890" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H890" s="2" t="n"/>
-      <c r="I890" s="2" t="n"/>
+      <c r="H890" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+答案為 乙炔氣。
+原因解析
+乙炔氣（
+𝐶
+2
+𝐻
+2
+𝑪
+𝟐
+𝑯
+𝟐
+）：化學性質極不穩定，分子內含有參鍵，具有高能量。當受到高壓、高溫、撞擊或震動時，即使在沒有氧氣或空氣等助燃物的情況下，也會自身發生分解反應並放出大量熱能，進而引起分解爆炸。
+防爆電氣暨危險區域劃分資訊網 氫氣、氧氣、氯氣：氫氣與氧氣/氯氣混合時會發生「燃燒或混合氣體爆炸」，氧氣是助燃物，氯氣則常與氫氣或有機物發生化學反應爆炸，但本身不屬於在無助燃物下會自行發生分解反應的氣體。
+需要了解更多乙炔高壓鋼瓶的安全使用規範嗎？
+儲存與搬運規定
+逆火防止器作用
+壓力調整器限制
+一般業（重要資料）重新排序版112.07.22 (1465題) (79-104)
+(1)下列何種氣體可能引起分解爆炸? ①乙炔②氧③氫④氯 70.(2)家庭常用的桶裝液化 ... (4)四氯化碳最可能循下列何種路徑進入人體？①皮膚接觸②口腔③眼睛接觸④ ...
+防爆電氣暨危險區域劃分資訊網
+常見問題 - 防爆電氣暨危險區域劃分資訊網
+氫氣（爆炸範圍廣，4%–75%）; 乙炔（極易爆，且無需氧氣即可分解爆炸）; 甲烷（天然氣，常見於燃料與煤礦） ; 麵粉（食品加工廠常見）; 鋁粉（輕金屬加工業）; 碳黑（橡膠與 ...</t>
+        </is>
+      </c>
+      <c r="I890" s="2" t="inlineStr"/>
     </row>
     <row r="891" ht="77.15000000000001" customHeight="1">
       <c r="A891" s="2" t="n">
@@ -39677,8 +39930,20 @@
       <c r="G891" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H891" s="2" t="n"/>
-      <c r="I891" s="2" t="n"/>
+      <c r="H891" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+常溫水瞬間接受極大能量轉變為蒸汽造成的爆炸，屬於物理性爆炸。
+原因解析
+物理性變化：水由液態迅速膨脹汽化成氣態（蒸汽），其化學結構並沒有改變（仍是
+H
+2
+O
+），僅有狀態與體積劇烈改變。
+壓力瞬間釋放：短時間內體積劇烈膨脹產生極大壓力，因此歸類為物理性爆炸。</t>
+        </is>
+      </c>
+      <c r="I891" s="2" t="inlineStr"/>
     </row>
     <row r="892" ht="77.15000000000001" customHeight="1">
       <c r="A892" s="2" t="n">
@@ -39712,8 +39977,17 @@
       <c r="G892" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H892" s="2" t="n"/>
-      <c r="I892" s="2" t="n"/>
+      <c r="H892" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+變電設備所引起之火災（屬於 C 類電氣火災）不適用泡沫滅火劑。
+中華都市安全推廣協會 原因說明
+泡沫滅火劑：主要成分包含水分，而水會導電，用在通電的變電設備上可能會造成觸電危險或使災害擴大。
+二氧化碳、ABC 類乾粉、BC 類乾粉：皆具備絕緣或適用於 C 類電氣火災的特性，可以用於變電設備火災。
+苗栗縣政府消防局</t>
+        </is>
+      </c>
+      <c r="I892" s="2" t="inlineStr"/>
     </row>
     <row r="893" ht="92.59999999999999" customHeight="1">
       <c r="A893" s="2" t="n">
@@ -39747,8 +40021,19 @@
       <c r="G893" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H893" s="2" t="n"/>
-      <c r="I893" s="2" t="n"/>
+      <c r="H893" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+大部分易燃液體火災無法以水滅火的主要原因為：易燃物質密度較水低，易懸浮水面上，擴散燃燒範圍。
+原因說明
+密度差異：大部分常見的易燃液體（如汽油、柴油等油品）密度都比水小（比重小於1）。
+浮在水面：若直接用水灌救，水會沉在下方，而易燃液體會浮在水面上。
+擴大災情：液體隨水流四處漂散，反而會讓火勢跟著擴散到更大的範圍，使燃燒面積增加、更難控制。
+因此，應對B類（油類）火災時，通常會使用泡沫、乾粉、二氧化碳等專用滅火設備，來達到覆蓋窒息或抑制滅火的效果，而不直接使用水。
+消防防災館</t>
+        </is>
+      </c>
+      <c r="I893" s="2" t="inlineStr"/>
     </row>
     <row r="894" ht="92.59999999999999" customHeight="1">
       <c r="A894" s="2" t="n">
@@ -39782,8 +40067,83 @@
       <c r="G894" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H894" s="2" t="n"/>
-      <c r="I894" s="2" t="n"/>
+      <c r="H894" s="2" t="inlineStr">
+        <is>
+          <t>敘述錯誤的是「購買成本較低」。
+與一般電氣設備相較，防爆電氣設備因採用特殊的防爆構造（如耐壓防爆、增安全構造等），需要更高的材質強度、更嚴格的密合與製造工藝，因此其購買與維護成本相對較高，而非較低。
+正確特性對照
+體積相對較大：為承受內部爆炸或提供足夠的散熱與安全距離，體積通常較大。
+構造較複雜：需要特殊接合面、密封圈或耐壓外殼，構造比一般設備複雜。
+購買成本較高：由於製造標準嚴格、產量較小且需認證，成本顯著高於一般設備。
+國際標準完善：國際間（如 IECEx、ATEX 等）已建立完整的構造與測試標準。
+您是否需要了解更多關於防爆構造的類型（如 Ex d、Ex e）？
+耐壓防爆構造 (Ex d)
+增安全防爆構造 (Ex e)
+本質安全防爆構造 (Ex i)
+一般業（重要資料）重新排序版112.08.20 (1489題) 練習題有 ...
+電壓不拘。 45.(3)有關防爆電氣設備構造的特性，與一般電氣設備相較，下列敘述何者錯誤？ ①體積相對較大②構造較複雜③購買成本較低④國際上已建立相關構造標準 46.(1) ...
+顯示更多
+網頁搜尋結果
+558. () 有關防爆電氣設備構造的特性，與一般電氣設備相較 ...
+› item-558.+()+有關防爆電氣設備構造...
+2020年1月21日 — 558. () 有關防爆電氣設備構造的特性，與一般電氣設備相較，下列敘述何 者錯誤？ (A)體積相對較大 (B)構造較複雜 (C)購買成本較低 (D)國際上已建立相關 ...
+553. () HazOp為下列何種評估方法之縮寫？ (A)初步危害 ...
+› item-553.+()+HazOp為下列何種評估...
+2020年1月21日 — () 有關防爆電氣設備構造的特性，與一般電氣設備相較，下列敘述何 者錯誤？ (A)體積相對較大(B)構造較複雜(C)購買成本較低(D)國際上已建立相關 構造標準.
+一般業（重要資料）重新排序版112.08.20 (1489題) 練習題有 ...
+› document › 一般業-重要資料...
+電壓不拘。 45.(3)有關防爆電氣設備構造的特性，與一般電氣設備相較，下列敘述何者錯誤？ ①體積相對較大②構造較複雜③購買成本較低④國際上已建立相關構造標準 46.(1) ...
+防爆電氣說明
+防爆電氣暨危險區域劃分資訊網
+› content › info › Introduce
+在爆炸性環境中選用電氣設備，除了要符合其防爆保護型式、群組和溫度分類外，還必須全面考量設備所處的**外在環境影響**。這些環境因素可能直接影響設備的性能、可靠性， ...
+缺少字詞： 一般 ‎相 ‎下列 ‎何者 ‎錯誤 ? ‎體積 ‎相對 ‎大 ‎複雜 ‎購買 ‎成本 ‎國際 ‎已 ‎建立
+耐壓型防爆- 112年職業安全衛生附詳解
+刷題王
+› question
+「耐壓型防爆構造」（防爆防護型式代號：Ex d）之防爆原理主要基於「內部爆炸容忍」與「外部引燃防止」兩大核心物理機制，其工程控制原理如下： 一、承受內部爆炸壓力（ ...
+編撰危險區域劃分及防爆電氣設備選用技術指引-氣體(蒸氣)類
+全民勞教e網
+› door › 報告區
+PDF
+在可能潛存易燃性氣體或蒸氣之危險場所，為防止電氣設備之火花或高溫，造成. 火災或爆炸事故，採用防爆電氣設備在安全防護上具有非常大的意義。而採用防爆電.
+缺少字詞： 何者 ‎成本 ‎建立
+正確選用防爆電氣設備，保障勞工職業安全。
+勞動及職業安全衛生研究所
+› ...
+0區場所風險較高，對防爆要求也相對較高，其次為1區場所，再其次為2區場所。換言之，一般適用於0區場所之防爆電氣設備也可裝設在1區或2區場所，適用於1區場所之 ...
+缺少字詞： 特性, ‎相 ‎何者 ‎錯誤 ? ‎體積 ‎複雜 ‎購買 ‎成本 ‎低
+防爆電氣原理與防爆電氣機具之使用
+環保資訊月刊
+› paper
+所示，採用不同之防爆構造。0區因為風險較高，故對電氣設備要求也相對較高，其次為1區，再其次為2區。因此，一般適用於0區之防爆電氣設備也可裝設在1區或2區，適用於1 ...
+缺少字詞： 相 ‎何者 ‎錯誤 ? ‎體積 ‎複雜 ‎購買 ‎建立
+爆炸性環境與危險區域劃分– II (易燃物質特性確認)
+Facebook · 工安百科
+超過 50 個回應 · 6 年前
+而採用防爆電氣設備之首要工作，需將該危險場 所做適當之電氣防爆區域劃分，然後再根據所規劃之危 險區域等級及易燃性氣體或蒸氣之火災或爆炸特性，選 用 ...
+缺少字詞： 一般 ‎下列 ‎何者 ‎錯誤 ? ‎體積 ‎相對 ‎複雜 ‎購買 ‎成本 ‎低 ‎已 ‎建立
+頁面導覽
+1
+2
+3
+4
+5
+6
+7
+8
+下一頁
+頁尾連結
+台灣
+708 臺南市安平區 - 根據你的 IP 位址
+- 更新位置
+說明
+提供意見
+隱私權
+服務條款</t>
+        </is>
+      </c>
+      <c r="I894" s="2" t="inlineStr"/>
     </row>
     <row r="895" ht="77.15000000000001" customHeight="1">
       <c r="A895" s="2" t="n">
@@ -39817,8 +40177,12 @@
       <c r="G895" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H895" s="2" t="n"/>
-      <c r="I895" s="2" t="n"/>
+      <c r="H895" s="2" t="inlineStr">
+        <is>
+          <t>Google AI 摘要未抓取到，請手動補充。</t>
+        </is>
+      </c>
+      <c r="I895" s="2" t="inlineStr"/>
     </row>
     <row r="896" ht="92.59999999999999" customHeight="1">
       <c r="A896" s="2" t="n">
@@ -39852,8 +40216,18 @@
       <c r="G896" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H896" s="2" t="n"/>
-      <c r="I896" s="2" t="n"/>
+      <c r="H896" s="2" t="inlineStr">
+        <is>
+          <t>去除連鎖反應之滅火方法為抑制法。
+滅火四種方法說明
+抑制法：加入能破壞化學連鎖反應的物質（如乾粉滅火劑），阻斷燃燒持續進行。
+冷卻法：使用水等介質降低燃燒溫度，使其降到引燃點以下。
+窒息法：阻絕或減少氧氣與助燃物接觸，使火熄滅。
+隔離法（移除法）：將周遭未燃燒的可燃物移除，讓火失去燃料。
+桃園防災館</t>
+        </is>
+      </c>
+      <c r="I896" s="2" t="inlineStr"/>
     </row>
     <row r="897" ht="77.15000000000001" customHeight="1">
       <c r="A897" s="2" t="n">
@@ -39887,8 +40261,18 @@
       <c r="G897" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H897" s="2" t="n"/>
-      <c r="I897" s="2" t="n"/>
+      <c r="H897" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+去漬油所引起之火災，不適用水。
+原因說明
+去漬油性質：去漬油屬於可燃性液體（B類火災），其密度比水小，且不溶於水。
+用水的危險：如果用水滅火，去漬油會浮在水面上隨處流動，反而會讓火勢迅速擴大蔓延。
+適用的滅火劑：應使用泡沫、二氧化碳或乾粉等滅火劑來進行窒息或抑制滅火。
+正德防火</t>
+        </is>
+      </c>
+      <c r="I897" s="2" t="inlineStr"/>
     </row>
     <row r="898" ht="77.15000000000001" customHeight="1">
       <c r="A898" s="2" t="n">
@@ -39922,8 +40306,16 @@
       <c r="G898" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H898" s="2" t="n"/>
-      <c r="I898" s="2" t="n"/>
+      <c r="H898" s="2" t="inlineStr">
+        <is>
+          <t>答案是 (A) 濃煙。
+火災與濃煙影響
+妨礙視線： 濃煙中的微小粒子會遮蔽光線，使人看不清逃生路線，大幅降低能見度。
+頭號殺手：濃煙除了影響視線，還伴隨有毒氣體、高溫與缺氧，是火場中最危險致命的因素。
+臺中市大肚區公所 您可以參考 Yamol 題庫解析 了解更多相關考試題目與統計資料。</t>
+        </is>
+      </c>
+      <c r="I898" s="2" t="inlineStr"/>
     </row>
     <row r="899" ht="92.59999999999999" customHeight="1">
       <c r="A899" s="2" t="n">
@@ -39957,8 +40349,17 @@
       <c r="G899" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H899" s="2" t="n"/>
-      <c r="I899" s="2" t="n"/>
+      <c r="H899" s="2" t="inlineStr">
+        <is>
+          <t>錯誤的敘述為：「為便於作業方便，拔卸電器插頭時可自電線處拉出」。
+根據《職業安全衛生設施規則》第276條第6款規定，拔卸電氣插頭時，應確實自插頭處拉出，不得直接拉扯電線，以免造成電線內部斷裂、短路或觸電危險。
+其他選項皆為正確規定：
+切斷開關應迅速確實。
+不得以濕手操作開關。
+發電室、變電室或受電室，非工作人員不得任意進入。</t>
+        </is>
+      </c>
+      <c r="I899" s="2" t="inlineStr"/>
     </row>
     <row r="900" ht="77.15000000000001" customHeight="1">
       <c r="A900" s="2" t="n">
@@ -39992,8 +40393,15 @@
       <c r="G900" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H900" s="2" t="n"/>
-      <c r="I900" s="2" t="n"/>
+      <c r="H900" s="2" t="inlineStr">
+        <is>
+          <t>依職業安全衛生設施規則規定，熔融高熱物之處理設備避免與水接觸，係為防止水蒸氣爆炸災害。
+第二節熔融高熱物等設備 - 勞動部-所有條文
+雇主對於建築物中熔融高熱物之處理設備,為避免引起水蒸汽爆炸,該建築物應有地板面不積水及可以防止雨水由屋頂、牆壁、窗戶等滲入之構造。
+AI 回覆可能有誤。如需法律建議，請諮詢專業人士。 瞭解詳情</t>
+        </is>
+      </c>
+      <c r="I900" s="2" t="inlineStr"/>
     </row>
     <row r="901" ht="108" customHeight="1">
       <c r="A901" s="2" t="n">
@@ -40027,8 +40435,21 @@
       <c r="G901" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H901" s="2" t="n"/>
-      <c r="I901" s="2" t="n"/>
+      <c r="H901" s="2" t="inlineStr">
+        <is>
+          <t>錯誤的敘述為：「物質的爆炸下限愈高者，其爆炸範圍愈廣，愈危險」。
+正確觀念解析
+爆炸下限（LEL）與危險性：
+物質的爆炸下限愈低，代表只要一點點濃度就能達到爆炸極限，因此愈危險、爆炸範圍也通常愈廣。相反地，爆炸下限愈高，代表需要累積到較高濃度才可能起爆，危險性相對較低。
+宜蘭縣勞工教育協進會
+其他選項正確原因：
+沸點與蒸發：沸點愈低的液體揮發性與蒸發速率愈大，閃火點通常愈低，發生火災與爆炸的可能性就愈高。
+比重與溶解度：多數常見的易燃液體（如汽油、有機溶劑）比重小於水且難溶於水，浮在水面上容易造成火災擴大。
+熱值：物質燃燒釋放的熱值愈大，火災爆炸時釋放的能量愈多，危害程度自然愈大。
+新北市政府電子法規查詢系統</t>
+        </is>
+      </c>
+      <c r="I901" s="2" t="inlineStr"/>
     </row>
     <row r="902" ht="77.15000000000001" customHeight="1">
       <c r="A902" s="2" t="n">
@@ -40062,8 +40483,15 @@
       <c r="G902" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H902" s="2" t="n"/>
-      <c r="I902" s="2" t="n"/>
+      <c r="H902" s="2" t="inlineStr">
+        <is>
+          <t>為越高。
+原因說明
+起爆能量低：指爆炸物只需要微小的撞擊、摩擦或外力就能被引爆。
+危險性高：因為極不安定、容易因不小心碰到而發生意外，所以危險性相對提高。</t>
+        </is>
+      </c>
+      <c r="I902" s="2" t="inlineStr"/>
     </row>
     <row r="903" ht="77.15000000000001" customHeight="1">
       <c r="A903" s="2" t="n">
@@ -40097,8 +40525,17 @@
       <c r="G903" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H903" s="2" t="n"/>
-      <c r="I903" s="2" t="n"/>
+      <c r="H903" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+當水接受極大的能量、瞬間由液態迅速轉變為蒸汽而造成爆炸現象時，屬於物理性爆炸。
+原因解析
+物理性變化：水汽化成水蒸氣的過程屬於物理狀態的改變，並沒有產生新的化學物質或燃燒反應。
+體積劇烈膨脹：水在瞬間變成同溫體積的水蒸氣時，體積會急劇膨脹（約數百到上千倍），在極短時間內釋放巨大壓力，因而形成所謂的水蒸氣爆炸（Steam Explosion）或蒸氣爆炸。
+銳傳媒</t>
+        </is>
+      </c>
+      <c r="I903" s="2" t="inlineStr"/>
     </row>
     <row r="904" ht="77.15000000000001" customHeight="1">
       <c r="A904" s="2" t="n">
@@ -40132,8 +40569,18 @@
       <c r="G904" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H904" s="2" t="n"/>
-      <c r="I904" s="2" t="n"/>
+      <c r="H904" s="2" t="inlineStr">
+        <is>
+          <t>工業火災的發生火源中，以電氣火花的比例最高。
+根據職業安全衛生考題以及內政部消防署的工廠火災原因統計，因電線短路、設備過載或接觸不良所引起的電氣因素（電氣火花）長期高居工業與工廠火災起火原因的第一位，占比通常高達 40% 至 50% 以上。
+臺中市政府消防局 您是否正在準備職業安全衛生業務主管或消防設備師/士的相關資格檢定考試？我可以為您提供更多相關章節的重點題庫與解析。
+臺中市政府消防局
+中市近3年工廠火災態樣分析消防救災挑戰及預防對策(消防新聞
+2025年3月29日 — 因此，深入了解工廠火災的可能態樣，並掌握有效的搶救要領，將有助於提升工廠的安全管理意識，更能進一步保障消防人員的救災安全。 消防局藉由分析臺中市近三年（111至113年）合計140件工廠火災之起火處、起火原因及產業型態，發現具有以下特性： 一、起火處：以作業區...
+顯示全部 內容</t>
+        </is>
+      </c>
+      <c r="I904" s="2" t="inlineStr"/>
     </row>
     <row r="905" ht="92.59999999999999" customHeight="1">
       <c r="A905" s="2" t="n">
@@ -40167,8 +40614,18 @@
       <c r="G905" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H905" s="2" t="n"/>
-      <c r="I905" s="2" t="n"/>
+      <c r="H905" s="2" t="inlineStr">
+        <is>
+          <t>選項「對 BB 頻火災有效」有誤，正確應為對 B、C 類火災（或 A、B、C 類火災）有效，題目中的「BB 頻」為筆誤或錯字。
+乾粉滅火器重點整理
+驅動氣體：使用氮氣加壓於容器內（或採蓄壓式以氮氣填裝）。
+主要成分：常用成分為碳酸氫鈉（B、C類）、碳酸氫鉀（BC類）或磷酸二氫銨（ABC類）。
+滅火效果：用於易燃液體（B類火災）時，其覆蓋與抑制連鎖反應的效果較 CO2 滅火器佳。
+適用火災：對B類（油類）與C類（電器）甚至A類（普通固體，如ABC乾粉）火災有效。
+中華都市安全推廣協會</t>
+        </is>
+      </c>
+      <c r="I905" s="2" t="inlineStr"/>
     </row>
     <row r="906" ht="92.59999999999999" customHeight="1">
       <c r="A906" s="2" t="n">
@@ -40202,8 +40659,17 @@
       <c r="G906" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H906" s="2" t="n"/>
-      <c r="I906" s="2" t="n"/>
+      <c r="H906" s="2" t="inlineStr">
+        <is>
+          <t>使用槽車灌注危險物前，槽車之引擎無須關火這項控制措施有誤。
+正確做法是：使用槽車灌注危險物前，槽車之引擎必須熄火（關閉引擎），以防止引擎產生的火花或高溫引發危險物爆炸。
+其他選項的正確說明：
+不同物質應採取專用連接頭：可防止接錯管線導致化學物質混合反應或洩漏。
+灌注處應有明確標示：提醒操作人員注意並確認管線與物質正確無誤。
+設置現場監督人員監督作業：確保灌注作業依安全程序進行，並能在發生異常時立即處理。</t>
+        </is>
+      </c>
+      <c r="I906" s="2" t="inlineStr"/>
     </row>
     <row r="907" ht="92.59999999999999" customHeight="1">
       <c r="A907" s="2" t="n">
@@ -40237,8 +40703,36 @@
       <c r="G907" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H907" s="2" t="n"/>
-      <c r="I907" s="2" t="n"/>
+      <c r="H907" s="2" t="inlineStr">
+        <is>
+          <t>爆炸危險性（危險指數
+𝐻
+𝐻
+）的公式為 (爆炸上限－爆炸下限) ／ 爆炸下限。
+爆炸危險性公式
+公式表達：
+爆炸上限
+−
+爆炸下限
+爆炸下限
+爆
+炸
+上
+限
+−
+爆
+炸
+下
+限
+爆
+炸
+下
+限
+意義：數值愈大代表該可燃性氣體的爆炸範圍相對其爆炸下限越寬廣，潛在危險性越高。
+-三民輔考</t>
+        </is>
+      </c>
+      <c r="I907" s="2" t="inlineStr"/>
     </row>
     <row r="908" ht="92.59999999999999" customHeight="1">
       <c r="A908" s="2" t="n">
@@ -40273,8 +40767,16 @@
       <c r="G908" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H908" s="2" t="n"/>
-      <c r="I908" s="2" t="n"/>
+      <c r="H908" s="2" t="inlineStr">
+        <is>
+          <t>勞工於潮濕或導電性良好場所使用移動式電動機具，為防止感電，應於該電路設置漏電斷路器。
+依據《職業安全衛生設施規則》第243條規定，雇主為避免漏電而發生感電危害，應於下列場所或機具之連接電路上，設置適合其規格、具高敏感度且高速型能確實動作之漏電斷路器：
+使用對地電壓在150伏特以上之移動式或攜帶式電動機具。
+於含水或被其他導電度高之液體濕潤之潮濕場所、金屬板上或鋼架上等導電性良好場所使用移動式或攜帶式電動機具。
+建築或工程作業之臨時用電設備。</t>
+        </is>
+      </c>
+      <c r="I908" s="2" t="inlineStr"/>
     </row>
     <row r="909" ht="92.59999999999999" customHeight="1">
       <c r="A909" s="2" t="n">
@@ -40308,8 +40810,20 @@
       <c r="G909" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H909" s="2" t="n"/>
-      <c r="I909" s="2" t="n"/>
+      <c r="H909" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+設備有接地即可免裝漏電斷路器為非（錯誤的觀念）。
+原因解析
+接地與漏電斷路器之功能不同：設備接地主要是在漏電時提供一條低電阻路徑讓電流導入大地，使金屬外殼不致帶高電壓；而漏電斷路器（ELCB）則是用來偵測微小漏電並在極短時間內自動跳脫斷電，兩者相輔相成，不能互相取代。
+依照《職業安全衛生設施規則》等相關規定，於濕潤場所或特定導電性良好場所使用移動式或攜帶式電動機械，皆須依規定裝設漏電斷路器，並不能因為設備已有接地就免除裝設。
+正確做法
+使用防水插頭：防止水分滲入造成短路或感電。
+避免不當延長接線：減少電線破損、過載及接觸不良引發的危險。
+電線架高或加以防護：避免車輛輾壓、人員絆倒或絕緣皮破損。</t>
+        </is>
+      </c>
+      <c r="I909" s="2" t="inlineStr"/>
     </row>
     <row r="910" ht="108" customHeight="1">
       <c r="A910" s="2" t="n">
@@ -40343,8 +40857,16 @@
       <c r="G910" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H910" s="2" t="n"/>
-      <c r="I910" s="2" t="n"/>
+      <c r="H910" s="2" t="inlineStr">
+        <is>
+          <t>無絕緣被覆之架空電路下進行吊掛作業是近接架空電線作業中的不當（違規）行為。
+原因與安全規範
+不當行為：在無絕緣被覆的架空電路下方進行起重吊掛作業，極易因吊具晃動、操作不慎或距離誤判而碰觸高壓帶電體，造成嚴重感電災害。
+正確做法：應保持安全距離、裝設絕緣用防護裝備、設置護圍或警戒隔離及監視人員，必要時應請電力公司協助斷電或遷移電線。
+職業安全衛生法規查詢系統</t>
+        </is>
+      </c>
+      <c r="I910" s="2" t="inlineStr"/>
     </row>
     <row r="911" ht="92.59999999999999" customHeight="1">
       <c r="A911" s="2" t="n">
@@ -40378,8 +40900,24 @@
       <c r="G911" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H911" s="2" t="n"/>
-      <c r="I911" s="2" t="n"/>
+      <c r="H911" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+依據 職業安全衛生設施規則 第 243 條規定，選項中「使用單相三線 220 伏特之冷氣機」無強制規定要裝設感電防止用漏電斷路器。
+Quizlet
+法規依據與解析
+依據 職業安全衛生設施規則 第 243 條，雇主應裝設防止感電用漏電斷路器的狀況包含：
+對電壓的要求：使用對地電壓在 150 伏特以上之移動式或攜帶式電動機具。
+對環境的要求：於潮濕場所、金屬板或鋼架等導電性良好場所使用移動式或攜帶式電動機具。
+對作業的要求：建築或工程作業使用之臨時用電設備。
+選項對照檢視
+營造工地之電氣設備 / 臨時用電：屬於建築或工程作業之臨時用電，強制規定裝設。
+對地電壓 220 伏特之手提電鑽：屬於對地電壓超過 150 伏特之攜帶式電動機具，強制規定裝設。
+於潮濕場所使用電焊機：屬於導電性良好之潮濕場所使用移動式/攜帶式機具，強制規定裝設。
+使用單相三線 220 伏特之冷氣機：冷氣機為固定式設備，且單相三線 220V 的對地電壓為 110V（未超過 150V），亦非位於移動/攜帶或特殊高濕導電之臨時施工環境，故無強制規定裝設漏電斷路器。</t>
+        </is>
+      </c>
+      <c r="I911" s="2" t="inlineStr"/>
     </row>
     <row r="912" ht="92.59999999999999" customHeight="1">
       <c r="A912" s="2" t="n">
@@ -40413,8 +40951,13 @@
       <c r="G912" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H912" s="2" t="n"/>
-      <c r="I912" s="2" t="n"/>
+      <c r="H912" s="2" t="inlineStr">
+        <is>
+          <t>正確答案是 150 伏特。
+根據《職業安全衛生設施規則》第 243 條規定，使用對地電壓在 150 伏特以上之移動式或攜帶式電動機具，應於該電路設置具有高敏感度、高速型之感電防止用漏電斷路器。</t>
+        </is>
+      </c>
+      <c r="I912" s="2" t="inlineStr"/>
     </row>
     <row r="913" ht="92.59999999999999" customHeight="1">
       <c r="A913" s="2" t="n">
@@ -40448,8 +40991,17 @@
       <c r="G913" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H913" s="2" t="n"/>
-      <c r="I913" s="2" t="n"/>
+      <c r="H913" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+用戶用電設備裝置規則所規定之高速型漏電斷路器，在額定動作電流下，其動作時間需在 0.1 秒以內。
+漏電斷路器動作時間分類
+高速型：動作時間在 0.1 秒以內。
+延時形：動作時間在 0.1 秒以上 2.0 秒以內（通常應用於比高速型需要時間差配合的場域）。
+www.tra-in.com</t>
+        </is>
+      </c>
+      <c r="I913" s="2" t="inlineStr"/>
     </row>
     <row r="914" ht="92.59999999999999" customHeight="1">
       <c r="A914" s="2" t="n">
@@ -40483,8 +41035,12 @@
       <c r="G914" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H914" s="2" t="n"/>
-      <c r="I914" s="2" t="n"/>
+      <c r="H914" s="2" t="inlineStr">
+        <is>
+          <t>Google AI 摘要未抓取到，請手動補充。</t>
+        </is>
+      </c>
+      <c r="I914" s="2" t="inlineStr"/>
     </row>
     <row r="915" ht="92.59999999999999" customHeight="1">
       <c r="A915" s="2" t="n">
@@ -40516,8 +41072,13 @@
       <c r="G915" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H915" s="2" t="n"/>
-      <c r="I915" s="2" t="n"/>
+      <c r="H915" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+漏電斷路器電壓動作型用來檢測電動機或機器外殼之零相電壓，於動作時限 0.2 秒以下切斷電路時，其動作電壓為 20～30 伏特。</t>
+        </is>
+      </c>
+      <c r="I915" s="2" t="inlineStr"/>
     </row>
     <row r="916" ht="92.59999999999999" customHeight="1">
       <c r="A916" s="2" t="n">
@@ -40551,8 +41112,12 @@
       <c r="G916" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H916" s="2" t="n"/>
-      <c r="I916" s="2" t="n"/>
+      <c r="H916" s="2" t="inlineStr">
+        <is>
+          <t>Google AI 摘要未抓取到，請手動補充。</t>
+        </is>
+      </c>
+      <c r="I916" s="2" t="inlineStr"/>
     </row>
     <row r="917" ht="92.59999999999999" customHeight="1">
       <c r="A917" s="2" t="n">
@@ -40586,8 +41151,32 @@
       <c r="G917" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H917" s="2" t="n"/>
-      <c r="I917" s="2" t="n"/>
+      <c r="H917" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+15mA 0.1秒動作者可作為感電防止用漏電斷路器。
+規格解析
+感電防止用標準：防止人體觸電（感電）危害的漏電斷路器，必須具備高敏感度（額定感度電流在 30mA 以下，15mA 更佳）與高速型（動作時間在 0.1 秒以內）的特性。
+臺北市政府全球資訊網 選項比較：
+50mA / 100mA：感度電流太大，超過 30mA，無法有效保護人體避免嚴重感電傷害。
+30mA 2秒動作者：動作時間 2 秒太慢，無法在 0.1 秒內瞬時斷電，屬於延時型而非高速型。
+15mA 0.1秒動作者：符合高敏感度（
+≤
+3
+0
+m
+A
+）及高速型（
+≤
+0
+.
+1
+秒
+），能迅速切斷電流，防止觸電。
+經濟部能源署</t>
+        </is>
+      </c>
+      <c r="I917" s="2" t="inlineStr"/>
     </row>
     <row r="918" ht="92.59999999999999" customHeight="1">
       <c r="A918" s="2" t="n">
@@ -40621,8 +41210,16 @@
       <c r="G918" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H918" s="2" t="n"/>
-      <c r="I918" s="2" t="n"/>
+      <c r="H918" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+接地之目的為防止感電（選項C）。
+接地核心原因
+當電氣設備的絕緣體損壞時，金屬外殼等容易接觸的外露部件可能會因累積漏電流而使電位升高。
+進行接地可將漏電迅速導入大地，降低設備金屬外殼對地電位，避免人員觸碰時發生觸電（感電）危險。</t>
+        </is>
+      </c>
+      <c r="I918" s="2" t="inlineStr"/>
     </row>
     <row r="919" ht="92.59999999999999" customHeight="1">
       <c r="A919" s="2" t="n">
@@ -40656,8 +41253,17 @@
       <c r="G919" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H919" s="2" t="n"/>
-      <c r="I919" s="2" t="n"/>
+      <c r="H919" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+(A) 防止機械災害不是接地的目的。
+接地的主要目的
+防止感電：電動機具絕緣物劣化或損傷發生漏電時，電流可經由接地線導入大地，保護人員免於觸電。
+防止高低壓混觸傷害：高低壓混觸時，高壓電流可流經接地迴路以免傷害人員。
+使電驛動作確實：輸電線、配電線、高低壓線路發生接地故障時，讓保護電驛（Relay）確實感應並切斷電源。</t>
+        </is>
+      </c>
+      <c r="I919" s="2" t="inlineStr"/>
     </row>
     <row r="920" ht="92.59999999999999" customHeight="1">
       <c r="A920" s="2" t="n">
@@ -40691,8 +41297,19 @@
       <c r="G920" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H920" s="2" t="n"/>
-      <c r="I920" s="2" t="n"/>
+      <c r="H920" s="2" t="inlineStr">
+        <is>
+          <t>下列何者不是電氣接地之目的的正確答案為：「(A) 提高電阻，防止觸電」。
+原因解析
+接地是為了降低電阻：電氣接地主要是利用大地作為導電體，提供一條低電阻的迴路，以便在漏電或發生故障時，讓電流迅速流入大地，並促使保護裝置（如無熔絲開關或漏電斷路器）動作切斷電源。
+選項 (A) 的錯誤之處：接地並非「提高電阻」，高電阻反而無法有效宣洩漏電電流。
+其他選項皆為正確目的：
+(B) 電線絕緣劣化時，防止感電。
+(C) 以大地為迴路，降低感電之可能性。
+(D) 防止雷擊災害（避雷接地）。</t>
+        </is>
+      </c>
+      <c r="I920" s="2" t="inlineStr"/>
     </row>
     <row r="921" ht="92.59999999999999" customHeight="1">
       <c r="A921" s="2" t="n">
@@ -40726,8 +41343,18 @@
       <c r="G921" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H921" s="2" t="n"/>
-      <c r="I921" s="2" t="n"/>
+      <c r="H921" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+答案為：在配電線接地故障時使繼電器不動作（與其無關，實際上接地故障時是為了讓保護繼電器動作以切除故障）。
+詳細說明
+(A) 防止因絕緣不良感電：有關。設備漏電時，接地可提供低電阻路徑將電流導向大地，保護人體安全。
+(B) 避免高低壓混觸高壓經接地回路而危害人畜：有關。高低壓混觸時，接地能宣洩高壓電流。
+(C) 避雷：有關。接地能將雷擊的突波電流引入大地。
+(D) 在配電線接地故障時使繼電器不動作：無關。發生接地故障時，接地迴路會產生故障電流，其目的反而是要讓保護繼電器動作（Trip），以便迅速切斷電源、排除危害。</t>
+        </is>
+      </c>
+      <c r="I921" s="2" t="inlineStr"/>
     </row>
     <row r="922" ht="92.59999999999999" customHeight="1">
       <c r="A922" s="2" t="n">
@@ -40761,8 +41388,16 @@
       <c r="G922" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H922" s="2" t="n"/>
-      <c r="I922" s="2" t="n"/>
+      <c r="H922" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+簡易接地電阻測定器因測定值包含系統接地電阻，而導致精確度較差。
+原因說明
+簡易測量法：利用低壓電源迴路進行兩極法測量時，不需要打入輔助接地棒。
+誤差來源：測定迴路會額外串聯並計入系統接地電阻（變壓器中性點接地等），導致讀數不只是單純待測物的接地阻抗，因而影響準確度。</t>
+        </is>
+      </c>
+      <c r="I922" s="2" t="inlineStr"/>
     </row>
     <row r="923" ht="92.59999999999999" customHeight="1">
       <c r="A923" s="2" t="n">
@@ -40790,8 +41425,20 @@
       <c r="G923" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H923" s="2" t="n"/>
-      <c r="I923" s="2" t="n"/>
+      <c r="H923" s="2" t="inlineStr">
+        <is>
+          <t>正確答案是 100 歐姆以下。根據台灣的《用戶用電設備裝置規則》（原用戶用電設備裝置法規規定），第三種接地（第三種地線）主要用於低壓用電設備、內線系統及變比器二次側等接地。當電路對地電壓在 150 伏特以下時，其接地電阻應保持在 100 歐姆以下。
+mail.ncku.edu.tw 💡 第三種接地的完整電阻規範
+根據對地電壓的不同，第三種接地的接地電阻規定如下：
+www.tra-in.com
+對地電壓 150 伏特以下：100 歐姆以下
+對地電壓 151 伏特至 300 伏特：50 歐姆以下
+對地電壓 301 伏特以上：10 歐姆以下
+www.tra-in.com
+請問這題是您在準備室內配線證照、電氣安全法規還是其他相關考試的考古題呢？</t>
+        </is>
+      </c>
+      <c r="I923" s="2" t="inlineStr"/>
     </row>
     <row r="924" ht="92.59999999999999" customHeight="1">
       <c r="A924" s="2" t="n">
@@ -40819,8 +41466,24 @@
       <c r="G924" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H924" s="2" t="n"/>
-      <c r="I924" s="2" t="n"/>
+      <c r="H924" s="2" t="inlineStr">
+        <is>
+          <t>用戶用電設備裝置規則所規定的第二種接地，其接地電阻應在 50 歐姆以下（選項 D）。
+行政院公共工程委員會全球資訊網 各種接地電阻標準快速對照
+特種接地：10 歐姆以下
+www.tra-in.com
+第一種接地：25 歐姆以下
+www.tra-in.com
+第二種接地：50 歐姆以下
+www.tra-in.com
+第三種接地：
+對地電壓 150 伏以下：100 歐姆以下
+對地電壓 151 伏至 300 伏：50 歐姆以下
+對地電壓 301 伏以上：10 歐姆以下
+www.tra-in.com</t>
+        </is>
+      </c>
+      <c r="I924" s="2" t="inlineStr"/>
     </row>
     <row r="925" ht="92.59999999999999" customHeight="1">
       <c r="A925" s="2" t="n">
@@ -40854,8 +41517,26 @@
       <c r="G925" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H925" s="2" t="n"/>
-      <c r="I925" s="2" t="n"/>
+      <c r="H925" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+下列何者為非的選項是第三種接地：接地電阻 10~150 Ω。
+詳細說明與法規標準
+根據經濟部主管之用戶用電設備裝置規則（或相關職業安全衛生法規）中的接地種類與電阻標準：
+特種接地：接地電阻 10 Ω 以下（正確）
+經濟部主管法規共用系統
+第一種接地：接地電阻 25 Ω 以下（正確）
+經濟部主管法規共用系統
+第二種接地：接地電阻 50 Ω 以下（正確）
+經濟部主管法規共用系統
+第三種接地：其接地電阻值並非固定 10~150 Ω，而是依對地電壓來區分：
+對地電壓 150V 以下：100 Ω 以下
+對地電壓 151V 至 300V：50 Ω 以下
+對地電壓 301V 以上：10 Ω 以下
+經濟部主管法規共用系統</t>
+        </is>
+      </c>
+      <c r="I925" s="2" t="inlineStr"/>
     </row>
     <row r="926" ht="92.59999999999999" customHeight="1">
       <c r="A926" s="2" t="n">
@@ -40889,8 +41570,12 @@
       <c r="G926" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H926" s="2" t="n"/>
-      <c r="I926" s="2" t="n"/>
+      <c r="H926" s="2" t="inlineStr">
+        <is>
+          <t>Google AI 摘要未抓取到，請手動補充。</t>
+        </is>
+      </c>
+      <c r="I926" s="2" t="inlineStr"/>
     </row>
     <row r="927" ht="92.59999999999999" customHeight="1">
       <c r="A927" s="2" t="n">
@@ -40924,8 +41609,61 @@
       <c r="G927" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H927" s="2" t="n"/>
-      <c r="I927" s="2" t="n"/>
+      <c r="H927" s="2" t="inlineStr">
+        <is>
+          <t>這是一道常見的職業安全衛生與工安考試題目，正確答案是 (A) 所有電氣設備。
+載入中...
+顯示更多
+網頁搜尋結果
+1096. 下列何種電氣設備需要接地?(A)所有電氣設備(B)電動 ...
+› item-1096.+下列何種電氣設備需要接...
+2024年10月7日 — 下列何種電氣設備需要接地? (A)所有電氣設備 (B)電動工具 (C)會被雷打中者 (D)易漏電者. 答案：登入後查看 統計： A(917), B(23), C(19), D(96), ...
+21.下列何種電氣設備需要接地?(A)電動工具(B)所有 ...
+› item-21.下列何種電氣設備需要接地(...
+2024年5月29日 — 21.下列何種電氣設備需要接地?(A)電動工具(B)所有電氣設備(C)會被雷打 中者(D)易漏電者。，包含題目內容、選項、詳解等，幫助學生提升學習效果。
+50. 下列何種電氣設備需要接地? (A)電動工具(B)所有 ...
+› item-50.+下列何種電氣設備需要接地 ...
+2018年9月30日 — 50. 下列何種電氣設備需要接地? (A)電動工具(B)所有電氣設備(C)會被雷打中者(D)易漏電者 ，包含題目內容、選項、詳解等，幫助學生提升學習效果。
+878. () 下列何種電氣設備需要接地？ (A)所有 ...
+› item-878.+()+下列何種電氣設備需要...
+2020年1月21日 — () 下列何種電氣設備需要接地？ (A)所有電氣設備 (B)電動工具 (C)會被雷打中者 (D)易漏電者. 答案：登入後查看 統計： A(2125), B(47), C(35), ...
+一般業（重要資料）重新排序版112.07.22 (1465題) (79-104)
+› document › 一般業-重要資料...
+(1)下列何種電氣設備較不需要接地？①電動工具②會被雷打中者③ 所有電氣設備④易漏電者 19.(2)下列何種電氣設備需要接地? ①電動工具②所有電氣設備③會被雷打中者④ ...
+12.下列何種電氣設備較不需要接地？(A)電動工具(B)會被雷 ...
+› item-12.下列何種電氣設備較不需要...
+2024年5月29日 — 12.下列何種電氣設備較不需要接地？(A)電動工具(B)會被雷打中者(C)所有電器設備(D)易漏電者。 #1878106 · 13.下列何者為交流電焊機較不易生感電之處？(A) ...
+工(職)業安全衛生教育題庫
+國立岡山高級農工職業學校
+› ...
+PDF
+76. (B) 防護帽依其性質，用於電器類工作者為(A)A 類(B)B 類(C)C 類(D)D. 類。 77. (C) 一般電氣設備的接地線顏色為(A)紅色(B)黃色(C)綠色(D) ...
+電氣設備接地了，漏電就沒危險嗎？
+勞動及職業安全衛生研究所
+› post
+大部分人應該都有這樣的經驗吧，在購買電氣設備後，其設備標示或安裝說明書常要求為防止感電危害，應將設備外殼接地（例如冷氣機、馬達或電動手工具之外殼接地）。沒錯， ...
+缺少字詞： 被 ‎雷 ‎易
+[題庫][職業安全衛生管理(乙)][03：專業課程] BLOCK 學習網
+BLOCK 學習網
+› question
+電氣安全中，有關接地種類及接地電阻，下列何者為非？ A 特種接地：接地電阻10Ω以下. B 第一種接地：接地電阻25Ω以下. C 第二種接地：接地電阻50Ω以下. D 第三種接地：接地 ...
+頁面導覽
+1
+2
+3
+4
+下一頁
+頁尾連結
+台灣
+708 臺南市安平區 - 根據你的 IP 位址
+- 更新位置
+說明
+提供意見
+隱私權
+服務條款</t>
+        </is>
+      </c>
+      <c r="I927" s="2" t="inlineStr"/>
     </row>
     <row r="928" ht="92.59999999999999" customHeight="1">
       <c r="A928" s="2" t="n">
@@ -40959,8 +41697,21 @@
       <c r="G928" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H928" s="2" t="n"/>
-      <c r="I928" s="2" t="n"/>
+      <c r="H928" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+正確的敘述為：焊接柄彈簧有效緊夾焊條。
+安全注意事項說明
+焊接柄功能：電焊作業使用的焊接柄必須具備良好的絕緣耐力與耐熱性。
+臺北市政府全球資訊網
+正確夾持：焊接柄的彈簧必須能有效緊夾焊條，避免焊條鬆脫或接觸導電部分造成危險。
+錯誤選項分析：
+作業時應戴防護/絕緣手套，而非僅戴一般棉紗手套。
+絕緣柄若破損，應立即更換新品，不能僅靠絕緣手套繼續勉強作業。
+焊接柄本身必須同時具備絕緣耐力與耐熱性。</t>
+        </is>
+      </c>
+      <c r="I928" s="2" t="inlineStr"/>
     </row>
     <row r="929" ht="92.59999999999999" customHeight="1">
       <c r="A929" s="2" t="n">
@@ -40994,8 +41745,16 @@
       <c r="G929" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H929" s="2" t="n"/>
-      <c r="I929" s="2" t="n"/>
+      <c r="H929" s="2" t="inlineStr">
+        <is>
+          <t>交流電焊裝置自動電擊防止裝置，以抑制電焊機電源線間電壓應在 25V 以下。
+詳細說明
+標準規定：依據中華民國國家標準（CNS 4782）交流電弧電焊用自動電擊防止裝置之規定，其安全電壓在額定輸入電壓下必須在 25伏特（25V）以下。
+功用：在未起弧焊接的待機狀態下，自動將輸出電壓（無載電壓）降至安全電壓（25V以下），以防止工作人員誤觸夾嘴而發生感電意外。
+高雄市政府全球資訊網</t>
+        </is>
+      </c>
+      <c r="I929" s="2" t="inlineStr"/>
     </row>
     <row r="930" ht="92.59999999999999" customHeight="1">
       <c r="A930" s="2" t="n">
@@ -41025,8 +41784,17 @@
       <c r="G930" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H930" s="2" t="n"/>
-      <c r="I930" s="2" t="n"/>
+      <c r="H930" s="2" t="inlineStr">
+        <is>
+          <t>鋼架上作業使用交流電焊機本體應裝設 防止自動電擊器（自動電擊防止裝置）。
+Quizlet
+相關法規與說明
+法規依據：依據《職業安全衛生設施規則》第 250 條規定，雇主對勞工於良導體機器設備內之狹小空間，或於鋼架等致有觸及高導電性接地物之虞之場所作業時所使用之交流電焊機，應有自動電擊防止裝置。
+主要功能：自動電擊防止裝置能在電焊機處於待機狀態（未焊接）時，將輸出端電壓降至安全電壓（通常為 20V 或 25V 以下），以防止焊工因意外碰觸電極而造成感電觸電事故。
+mail.ncku.edu.tw</t>
+        </is>
+      </c>
+      <c r="I930" s="2" t="inlineStr"/>
     </row>
     <row r="931" ht="92.59999999999999" customHeight="1">
       <c r="A931" s="2" t="n">
@@ -41060,8 +41828,20 @@
       <c r="G931" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H931" s="2" t="n"/>
-      <c r="I931" s="2" t="n"/>
+      <c r="H931" s="2" t="inlineStr">
+        <is>
+          <t>電焊機裝設自動電擊防止裝置的用意是為了防止感電（或選項中的 (B) 不被電擊／預防觸電災害）。
+相關重點整理
+防止感電：當電焊作業中斷、更換焊條或待機時，自動電擊防止裝置會使電焊機二次側（負載側）的輸出電壓降至安全電壓（25伏特以下），保護作業人員不被電擊。
+適用場所：在良導體機器設備內的狹小空間，或於鋼架等具高導電性接地之虞的場所從事電焊作業時，特別需要強制裝設。
+高雄市政府全球資訊網 為了提供更精確的備考或作業安全資訊，想請問您：
+您目前是在準備哪一類型的證照考試（例如：職業安全衛生業務主管、技術士技能檢定）？
+是否需要更多關於電氣安全或防感電的法規規定？
+電焊機裝自動電擊防止裝置用意為何？(A)漏電。(B)不被 ...
+2024年6月18日 — 254 電焊機裝自動電擊防止裝置用意為何？(A)漏電。(B)不被電擊。(C)感電。(D)無法使用。 ，包含題目內容、選項、詳解等，幫助學生提升學習效果。 D)無法使用。 | Yamol Logo 登入 首頁 &gt; 營造業甲種職業安全衛...</t>
+        </is>
+      </c>
+      <c r="I931" s="2" t="inlineStr"/>
     </row>
     <row r="932" ht="92.59999999999999" customHeight="1">
       <c r="A932" s="2" t="n">
@@ -41095,8 +41875,16 @@
       <c r="G932" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H932" s="2" t="n"/>
-      <c r="I932" s="2" t="n"/>
+      <c r="H932" s="2" t="inlineStr">
+        <is>
+          <t>電焊作業需設置的保護裝置為 (B) 自動電擊防止裝置。
+說明
+自動電擊防止裝置：是針對電焊機（特別是交流電焊機）規定的安全防護「裝置」，用來降低待機時的輸出電壓，防止焊工發生感電意外。
+防塵口罩與防護面罩：屬於個人「防護具」（PE），而非機器設備上需要「設置」的保護裝置。這題是常見的職安卡／勞安考試題，標準答案為自動電擊防止裝置。
+高雄市政府全球資訊網</t>
+        </is>
+      </c>
+      <c r="I932" s="2" t="inlineStr"/>
     </row>
     <row r="933" ht="92.59999999999999" customHeight="1">
       <c r="A933" s="2" t="n">
@@ -41130,8 +41918,29 @@
       <c r="G933" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H933" s="2" t="n"/>
-      <c r="I933" s="2" t="n"/>
+      <c r="H933" s="2" t="inlineStr">
+        <is>
+          <t>在身體電阻值相同的情況下，接觸電壓愈高，對人體的感電危害程度為(A) 愈大。
+解析：
+根據歐姆定律
+𝐼
+=
+𝑉
+𝑅
+，當人體電阻
+𝑅
+𝑅
+固定不變時，接觸電壓
+𝑉
+𝑉
+愈高，流經人體的電流
+𝐼
+𝐼
+就會愈大。而電流通過人體的大小是決定感電危害（如肌肉痙攣、心室顫動、組織燒傷等）嚴重程度的關鍵因素，因此電流愈大，感電危害程度也愈大。
+ROHM</t>
+        </is>
+      </c>
+      <c r="I933" s="2" t="inlineStr"/>
     </row>
     <row r="934" ht="92.59999999999999" customHeight="1">
       <c r="A934" s="2" t="n">
@@ -41165,8 +41974,17 @@
       <c r="G934" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H934" s="2" t="n"/>
-      <c r="I934" s="2" t="n"/>
+      <c r="H934" s="2" t="inlineStr">
+        <is>
+          <t>人體感電是指電流通過身體。
+维基百科
+相關說明
+電流：感電（觸電）造成的生理反應與傷害，決定於流經人體之電流大小與時間。
+電壓與電阻：電壓是推動電流的力量，人體電阻會影響電流的大小，但直接造成傷害與麻痺的是通過身體的電流。
+虎科電機系網</t>
+        </is>
+      </c>
+      <c r="I934" s="2" t="inlineStr"/>
     </row>
     <row r="935" ht="92.59999999999999" customHeight="1">
       <c r="A935" s="2" t="n">
@@ -41200,8 +42018,16 @@
       <c r="G935" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H935" s="2" t="n"/>
-      <c r="I935" s="2" t="n"/>
+      <c r="H935" s="2" t="inlineStr">
+        <is>
+          <t>尖端部分較易形成較高的電荷密度。
+電荷分布特性
+曲率與密度：導體表面越尖銳（即曲率半徑越小、曲率越大），該處的電荷密度就會越高。
+尖端放電：因為尖端電荷密度大，附近的電場強度也非常強，容易使空氣游離而產生放電現象。
+國立臺灣師範大學開放式課程</t>
+        </is>
+      </c>
+      <c r="I935" s="2" t="inlineStr"/>
     </row>
     <row r="936" ht="92.59999999999999" customHeight="1">
       <c r="A936" s="2" t="n">
@@ -41235,8 +42061,13 @@
       <c r="G936" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H936" s="2" t="n"/>
-      <c r="I936" s="2" t="n"/>
+      <c r="H936" s="2" t="inlineStr">
+        <is>
+          <t>最有效的方式為(C) 構築安全的工作平台。
+依據職業安全衛生相關法規與題庫標準，在高處進行活線作業時，若勞工因感電等意外導致身體失控，直接提供一個固定、穩固且有護欄等防護的作業平台，是最根本且有效的工程控制方法，能直接防止人員直接墜落。</t>
+        </is>
+      </c>
+      <c r="I936" s="2" t="inlineStr"/>
     </row>
     <row r="937" ht="92.59999999999999" customHeight="1">
       <c r="A937" s="2" t="n">
@@ -41270,8 +42101,17 @@
       <c r="G937" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H937" s="2" t="n"/>
-      <c r="I937" s="2" t="n"/>
+      <c r="H937" s="2" t="inlineStr">
+        <is>
+          <t>答案是 (A) 氧乙炔焊接。
+原因解析
+氧乙炔焊接：是利用氧氣和乙炔混合燃燒產生的化學火焰來進行金屬焊接或切割，屬於化學能/燃燒反應，不會產生電氣性質的電弧。
+短路：電路發生短路時，瞬時產生巨大電流，極易伴隨高溫與強烈電弧。
+閃絡（Flashover）：指絕緣體表面在高電壓下發生氣體游離而形成電弧放電的現象。
+靜電電荷蓄積：當累積的靜電電壓過高而發生放電時，也會產生靜電火花或電弧。</t>
+        </is>
+      </c>
+      <c r="I937" s="2" t="inlineStr"/>
     </row>
     <row r="938" ht="92.59999999999999" customHeight="1">
       <c r="A938" s="2" t="n">
@@ -41305,8 +42145,17 @@
       <c r="G938" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H938" s="2" t="n"/>
-      <c r="I938" s="2" t="n"/>
+      <c r="H938" s="2" t="inlineStr">
+        <is>
+          <t>答案是 熔絲（或熔絲斷路器）。
+選項解析
+熔絲：當電路發生過載或短路等過電流狀況時，熔絲會因過高電流產生的熱量而自行熔斷，藉此切斷電路，保護線路與設備安全，是標準的過電流保護裝置。
+避雷針：用來防範雷擊，將雷電引導至大地，屬於防雷裝置而非過電流保護裝置。
+變壓器：用來改變交流電壓的大小，屬於變壓設備。
+電阻器：用來調整或限制電路中的電流大小，屬於阻抗元件。</t>
+        </is>
+      </c>
+      <c r="I938" s="2" t="inlineStr"/>
     </row>
     <row r="939" ht="92.59999999999999" customHeight="1">
       <c r="A939" s="2" t="n">
@@ -41340,8 +42189,17 @@
       <c r="G939" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H939" s="2" t="n"/>
-      <c r="I939" s="2" t="n"/>
+      <c r="H939" s="2" t="inlineStr">
+        <is>
+          <t>熔絲開關可作為電氣迴路過載或過電流之保護裝置。
+保護裝置說明
+熔絲開關 (Fuse Switch)：內部含有熔絲（保險絲）。當電氣迴路發生過載或短路而產生過大電流時，熔絲會因過熱而熔斷，藉此自動切斷電路，保護線路與設備不被燒損。
+變壓器：用於改變交流電的電壓值，不具備過載保護功能。
+電阻器：用於限制電流或調節電壓大小，本身會消耗電能並產生熱量，無法作為保護裝置。
+接地裝置：用於將設備金屬外殼等導電部分與大地相連，主要用來防止漏電時人員觸電，而非過載保護裝置。</t>
+        </is>
+      </c>
+      <c r="I939" s="2" t="inlineStr"/>
     </row>
     <row r="940" ht="92.59999999999999" customHeight="1">
       <c r="A940" s="2" t="n">
@@ -41375,8 +42233,24 @@
       <c r="G940" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H940" s="2" t="n"/>
-      <c r="I940" s="2" t="n"/>
+      <c r="H940" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+漏電斷路器（部分不具過電流保護功能的RCCB型式）非過電流保護之裝置。
+詳細說明
+熔絲（Fuse）：利用電流過大時產生的熱量使導線熔斷，屬於傳統的過電流（過載與短路）保護裝置。
+無熔絲開關（NFB）：當電路發生過載或短路時會自動跳脫，屬於常見的過電流保護裝置。
+斷路器（Circuit Breaker）：專門用來切斷過載或短路故障電流的保護裝置。
+漏電斷路器（ELCB / RCCB）：主要用於偵測漏電流以防止人員觸電，不一定具備過電流保護功能（若為純漏電斷路器，需另外搭配無熔絲開關或熔絲作為過電流保護）。
+經濟部主管法規查詢系統 Would you like to explore more about electrical safety devices?
+Difference between NFB and ELCB
+How fuses work
+Mobile01
+無溶絲開關與漏電斷路器之先後 - Mobile01
+2025年2月1日 — 無溶絲開關（MCB）是過載或短路時保護電路的，而漏電斷路器（RCD）是防止人員觸電用的。一般來說，MCB在前，RCD在後，也就是MCB先檢測電流超載或短路後跳 ...</t>
+        </is>
+      </c>
+      <c r="I940" s="2" t="inlineStr"/>
     </row>
     <row r="941" ht="92.59999999999999" customHeight="1">
       <c r="A941" s="2" t="n">
@@ -41410,8 +42284,19 @@
       <c r="G941" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H941" s="2" t="n"/>
-      <c r="I941" s="2" t="n"/>
+      <c r="H941" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+鐵線不得作為電氣迴路過電流之保護裝置。
+選項說明
+保險絲：當電流過大時會自行熔斷，屬於合法的過電流保護裝置。
+鐵線：電阻大且熔點高，無法在電流過載時及時安全熔斷，絕不可用來替代保險絲或作為保護裝置，容易導致電線走火。
+無熔絲開關：過載或短路時會自動跳脫，是常見的保護裝置。
+積熱熔絲：具備過載保護功能的熔斷保護元件。
+經濟部主管法規查詢系統</t>
+        </is>
+      </c>
+      <c r="I941" s="2" t="inlineStr"/>
     </row>
     <row r="942" ht="92.59999999999999" customHeight="1">
       <c r="A942" s="2" t="n">
@@ -41445,8 +42330,18 @@
       <c r="G942" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H942" s="2" t="n"/>
-      <c r="I942" s="2" t="n"/>
+      <c r="H942" s="2" t="inlineStr">
+        <is>
+          <t>電氣設備故障修理時，為防止事故發生，較不適當的做法是「確認電源維持開啟」。
+安全修理原則
+確認電源維持開啟：不適當。修理電氣設備前必須先切斷電源並確認關閉，以防止感電事故。
+確認電源開關是否關閉：適當。維修前應確認開關確實切斷。
+機械修理中要懸掛標示牌：適當。應在開關處懸掛警告標示，防止他人誤觸送電。
+非相關人員，禁止操作：適當。管制現場以策安全。
+中壢家商</t>
+        </is>
+      </c>
+      <c r="I942" s="2" t="inlineStr"/>
     </row>
     <row r="943" ht="92.59999999999999" customHeight="1">
       <c r="A943" s="2" t="n">
@@ -41480,8 +42375,17 @@
       <c r="G943" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H943" s="2" t="n"/>
-      <c r="I943" s="2" t="n"/>
+      <c r="H943" s="2" t="inlineStr">
+        <is>
+          <t>錯誤的選項為：設備運轉中進行維護作業時，可直接打開接線盒蓋與檢查窗口。
+正確觀念與注意事項
+運轉中嚴禁開啟：設備在運轉或通電時，絕對不能直接打開接線盒蓋或檢查窗口，以免內部產生火花引燃周圍易爆氣體。
+停機與確認安全：進行維護或檢查前，必須先停止設備運轉，並確實切斷及確認電路已無安全疑慮。
+使用防爆儀器：在具備爆炸性危險的環境中進行檢測或維護時，應使用專用的防爆型測量儀器。
+切勿任意拆解：防爆電氣設備的構造具備特殊設計，不得任意拆解或破壞其防爆性能。</t>
+        </is>
+      </c>
+      <c r="I943" s="2" t="inlineStr"/>
     </row>
     <row r="944" ht="92.59999999999999" customHeight="1">
       <c r="A944" s="2" t="n">
@@ -41515,8 +42419,17 @@
       <c r="G944" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H944" s="2" t="n"/>
-      <c r="I944" s="2" t="n"/>
+      <c r="H944" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+防止靜電危害可使用接地（以及加濕、使用除電裝置等方法）。
+常用靜電防制方法
+接地：將導電性物件實施接地並保持低接地電阻，讓電荷導入大地，是最有效且經濟的方法。
+加濕：提高環境濕度（相對濕度通常保持在 60% 以上），使表面形成微小水膜，幫助電荷洩漏。
+使用除電裝置：如靜電消除器、除電劑或游離化裝置來中和電荷。</t>
+        </is>
+      </c>
+      <c r="I944" s="2" t="inlineStr"/>
     </row>
     <row r="945" ht="92.59999999999999" customHeight="1">
       <c r="A945" s="2" t="n">
@@ -41550,8 +42463,19 @@
       <c r="G945" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H945" s="2" t="n"/>
-      <c r="I945" s="2" t="n"/>
+      <c r="H945" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+隔離產生靜電之設備非為消除靜電電荷累積的方法。
+說明
+消除靜電累積的方法：
+以導體接地：將導電體與大地連接，使累積的電荷流入大地。
+提高靜電環境之濕度：空氣中濕度提高時，物體表面會形成微薄水膜，幫助電荷洩漏。
+裝置靜電消除器：利用離子中和或電暈放電來消除帶電物體上的電荷。
+台灣防雷股份有限公司 隔離設備：屬於空間或物理上的隔離防護，用來防止靜電引發災害或減少接觸，但並未「消除」已經產生或累積的靜電電荷。</t>
+        </is>
+      </c>
+      <c r="I945" s="2" t="inlineStr"/>
     </row>
     <row r="946" ht="92.59999999999999" customHeight="1">
       <c r="A946" s="2" t="n">
@@ -41585,8 +42509,20 @@
       <c r="G946" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H946" s="2" t="n"/>
-      <c r="I946" s="2" t="n"/>
+      <c r="H946" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+答案是 使用絕緣性之材料。
+說明
+防止靜電危害的正確對策包含：
+抑制靜電產生：減少摩擦、避免使用容易起電的設備或製程。
+接地疏導：將導電體接地，讓累積的電荷排入大地，避免高電位。
+加濕或游離化：提高環境濕度或使用除靜電離子設備，使空氣導電並消除表面電荷。
+而使用絕緣性之材料反而容易讓電荷無法流失而持續累積，導致靜電危害與電擊、火災爆炸風險，因此不是正確的防止對策。
+iPEDIA 百科</t>
+        </is>
+      </c>
+      <c r="I946" s="2" t="inlineStr"/>
     </row>
     <row r="947" ht="92.59999999999999" customHeight="1">
       <c r="A947" s="2" t="n">
@@ -41620,8 +42556,21 @@
       <c r="G947" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H947" s="2" t="n"/>
-      <c r="I947" s="2" t="n"/>
+      <c r="H947" s="2" t="inlineStr">
+        <is>
+          <t>在電氣安全中，正確的靜電危害防止對策為接地。
+選擇題解析
+接地：正確。透過接地或等電位搭接，能將帶電體上蓄積的電荷迅速導入大地散逸，防止靜電累積與放電引發爆炸或火災。
+乾燥：錯誤。乾燥環境反而容易使靜電累積；實務上應「增加濕度」來抑制靜電。
+使用非導電性之材料：錯誤。非導電材料容易積蓄靜電，應使用導電性材料、抗電劑或抗靜電材質。
+使成為帶電體：錯誤。帶電體本身就是靜電危害的根源，防止對策應避免電荷累積。
+台灣防雷股份有限公司 常見靜電危害防止方法
+預防產生：降低摩擦速率、使用導電材質、添加抗靜電劑。
+消除電荷：接地、使用靜電消除器、穿戴導電器具。
+改善環境：增加相對濕度。</t>
+        </is>
+      </c>
+      <c r="I947" s="2" t="inlineStr"/>
     </row>
     <row r="948" ht="92.59999999999999" customHeight="1">
       <c r="A948" s="2" t="n">
@@ -41655,8 +42604,49 @@
       <c r="G948" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H948" s="2" t="n"/>
-      <c r="I948" s="2" t="n"/>
+      <c r="H948" s="2" t="inlineStr">
+        <is>
+          <t>電容器之放電能量為
+0.5
+𝐶
+𝑉
+2
+𝟎
+.
+𝟓
+𝑪
+𝑽
+𝟐
+（即
+1
+2
+𝐶
+𝑉
+2
+）。
+說明
+公式來源：電容器儲存的能量
+𝑊
+𝑊
+或放電能量計算公式為
+𝑊
+=
+1
+2
+𝐶
+𝑉
+2
+。
+符號定義：
+𝐶
+𝐶
+：電容量（單位為法拉, F）
+𝑉
+𝑉
+：電壓值（單位為伏特, V）</t>
+        </is>
+      </c>
+      <c r="I948" s="2" t="inlineStr"/>
     </row>
     <row r="949" ht="92.59999999999999" customHeight="1">
       <c r="A949" s="2" t="n">
@@ -41690,8 +42680,18 @@
       <c r="G949" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H949" s="2" t="n"/>
-      <c r="I949" s="2" t="n"/>
+      <c r="H949" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+依據職業安全衛生設施規則第259條規定，距離勞工身體60公分以內之高壓電路，應在該電路設置絕緣用防護裝備。
+相關法規重點
+法規依據：職業安全衛生設施規則第259條
+防護範圍：在距離勞工頭上、身側及腳下 60 公分以內之高壓電路。
+例外規定：若已使該作業勞工戴用絕緣用防護具而無感電之虞者，不在此限。
+正確答案為：60 公分。</t>
+        </is>
+      </c>
+      <c r="I949" s="2" t="inlineStr"/>
     </row>
     <row r="950" ht="92.59999999999999" customHeight="1">
       <c r="A950" s="2" t="n">
@@ -41725,8 +42725,16 @@
       <c r="G950" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H950" s="2" t="n"/>
-      <c r="I950" s="2" t="n"/>
+      <c r="H950" s="2" t="inlineStr">
+        <is>
+          <t>依據職業安全衛生設施規則第272條規定，絕緣用防護具應每隔半年（每六個月）進行性能檢驗一次。
+重點整理
+性能檢驗頻率：每 半年（六個月）一次。
+使用前自行點檢：工作人員應於每次使用前自行點檢，若發現不合格應立即更換。
+適用對象：絕緣用防護裝備、防護具、活線作業用工具等。</t>
+        </is>
+      </c>
+      <c r="I950" s="2" t="inlineStr"/>
     </row>
     <row r="951" ht="92.59999999999999" customHeight="1">
       <c r="A951" s="2" t="n">
@@ -41760,8 +42768,17 @@
       <c r="G951" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H951" s="2" t="n"/>
-      <c r="I951" s="2" t="n"/>
+      <c r="H951" s="2" t="inlineStr">
+        <is>
+          <t>「人體感覺有電流通過，稍感刺痛」是屬於感知電流值的描述。
+🔌 電流對人體的影響分類
+感知電流值：人體開始感覺到電流通過的最小電流。此時通常會產生微弱的刺痛感或發麻。
+可逃脫電流值：人體觸電後仍能自主擺脫電源的最大電流。
+無法逃脫電流值：電流超過一定限度，導致肌肉非自主性強烈收縮，人體手部會緊握電源而無法自行放開。
+心臟麻痺電流值：電流過大，直接導致心臟發生心室纖顫、停止跳動或造成嚴重傷亡。</t>
+        </is>
+      </c>
+      <c r="I951" s="2" t="inlineStr"/>
     </row>
     <row r="952" ht="92.59999999999999" customHeight="1">
       <c r="A952" s="2" t="n">
@@ -41795,8 +42812,16 @@
       <c r="G952" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H952" s="2" t="n"/>
-      <c r="I952" s="2" t="n"/>
+      <c r="H952" s="2" t="inlineStr">
+        <is>
+          <t>這屬於無法脫逃電流值（或稱擺脫電流）的描述。
+電流對人體的影響分類：
+💡 感知電流：人體開始感覺到有電流通過的最小電流（約 1 mA），此時只會有微弱的刺痛或麻木感。
+✊ 無法脫逃電流值（擺脫電流）：電流大到讓肌肉發生痙攣、肌肉收縮，導致手指緊握導線而無法自行逃脫。如果時間過長，會因胸肌收縮引發呼吸困難，最終窒息而死（約 10 ~ 20 mA）。
+⚡ 休克/心臟麻痺電流值（心室纖維顫動電流）：電流過大直接影響心臟，導致心臟停止跳動、心室顫動或呼吸停止，極度危險（通常大於 50 mA 或 100 mA）。 內容</t>
+        </is>
+      </c>
+      <c r="I952" s="2" t="inlineStr"/>
     </row>
     <row r="953" ht="92.59999999999999" customHeight="1">
       <c r="A953" s="2" t="n">
@@ -41830,8 +42855,18 @@
       <c r="G953" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H953" s="2" t="n"/>
-      <c r="I953" s="2" t="n"/>
+      <c r="H953" s="2" t="inlineStr">
+        <is>
+          <t>肌肉僵硬、呼吸困難是屬於休克電流值通過人體的描述。
+iPEDIA 百科 在工安與用電安全分類中，不同電流值對人體的生理影響如下：
+感知電流值：人體開始感覺有電流通過，稍微有刺痛感。
+無法脫逃電流值（可脫逃電流值）：肌肉發生劇烈痙攣，情況持續會讓人無法自行鬆脫電源。
+休克電流值：電流更大，會導致肌肉僵硬、收縮以及呼吸困難，進而引發休克。
+心臟麻痺電流值：會直接引起心臟麻痺，使其失去血液循環功能，並造成呼吸停止。
+內政部消防署全球資訊網</t>
+        </is>
+      </c>
+      <c r="I953" s="2" t="inlineStr"/>
     </row>
     <row r="954" ht="92.59999999999999" customHeight="1">
       <c r="A954" s="2" t="n">
@@ -41865,8 +42900,18 @@
       <c r="G954" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H954" s="2" t="n"/>
-      <c r="I954" s="2" t="n"/>
+      <c r="H954" s="2" t="inlineStr">
+        <is>
+          <t>這個描述屬於心臟麻痺電流值。
+iPEDIA 百科 在職業安全與電氣危害認知中，不同的電流值通過人體會產生不同的生理效應，其分類與特徵如下：
+內政部消防署全球資訊網 感知電流值：人體開始感覺到有電流通過的最小電流，通常會伴隨輕微的刺痛感。
+無法脫逃電流值（電凍電流）：電流使人體肌肉發生劇烈痙攣、收縮，導致觸電者雙手緊握電源而無法靠自己的力量自行脫逃。若持續時間過長，可能會因呼吸困難而窒息。
+休克電流值：此電流值會導致人體肌肉嚴重僵硬、呼吸困難，進而引發休克。
+心臟麻痺電流值：這是更危險的電流等級，會直接引起心臟麻痺、失去血液循環的功能（引起心室顫動），並導致呼吸停止。
+虎科電機系網</t>
+        </is>
+      </c>
+      <c r="I954" s="2" t="inlineStr"/>
     </row>
     <row r="955" ht="92.59999999999999" customHeight="1">
       <c r="A955" s="2" t="n">
@@ -41900,8 +42945,17 @@
       <c r="G955" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H955" s="2" t="n"/>
-      <c r="I955" s="2" t="n"/>
+      <c r="H955" s="2" t="inlineStr">
+        <is>
+          <t>使用電線時要注意不可破損。
+正確用電守則
+不可破損：電線絕緣外皮若有破損應立即停止使用並更換，以防觸電或短路。
+不可重壓：電線絕對不能被重物或家具壓住，以免內部銅線斷裂或散熱不良引發火災。
+正確插拔：拔插頭時應握住插頭本體拔除，不可直接拉扯電線。
+臺中市大肚區衛生所</t>
+        </is>
+      </c>
+      <c r="I955" s="2" t="inlineStr"/>
     </row>
     <row r="956" ht="108" customHeight="1">
       <c r="A956" s="2" t="n">
@@ -41935,8 +42989,13 @@
       <c r="G956" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H956" s="2" t="n"/>
-      <c r="I956" s="2" t="n"/>
+      <c r="H956" s="2" t="inlineStr">
+        <is>
+          <t>根據現行用戶用電設備裝置規則（原名屋內線路裝置規則）第10條規定，新設線路之絕緣電阻應在一百萬歐姆（即 1MΩ）以上。
+所以正確答案是：(A) 1MΩ 以上。</t>
+        </is>
+      </c>
+      <c r="I956" s="2" t="inlineStr"/>
     </row>
     <row r="957" ht="92.59999999999999" customHeight="1">
       <c r="A957" s="2" t="n">
@@ -41970,8 +43029,17 @@
       <c r="G957" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H957" s="2" t="n"/>
-      <c r="I957" s="2" t="n"/>
+      <c r="H957" s="2" t="inlineStr">
+        <is>
+          <t>罹災者因感電而墜落時，應歸類為感電災害。
+桃園市政府勞動檢查處
+災害歸類說明
+根本原因原則：依職業安全衛生災害類型分類說明，當事故是由於感電（觸電）引起連帶反應（如墜落或跌倒），其起始誘發原因為感電，故統一歸類為「感電」類型。
+不歸類為墜落：雖然形式上有從高處落下的狀況，但因為是觸電導致身體失控或休克而墜落，所以不視為單純的墜落災害。
+社團法人中華民國技能發展協會</t>
+        </is>
+      </c>
+      <c r="I957" s="2" t="inlineStr"/>
     </row>
     <row r="958" ht="92.59999999999999" customHeight="1">
       <c r="A958" s="2" t="n">
@@ -42005,8 +43073,13 @@
       <c r="G958" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H958" s="2" t="n"/>
-      <c r="I958" s="2" t="n"/>
+      <c r="H958" s="2" t="inlineStr">
+        <is>
+          <t>拆除結構物之作業為防止感電，正確的敘述為：切斷欲拆除牆面之電源並拆除設備及線路。
+依據勞工職業安全衛生相關法規（如營造安全衛生設施標準規定），雇主於拆除構造物前，應先切斷電源，並拆除配電設備及線路，以防止作業時發生感電危害。</t>
+        </is>
+      </c>
+      <c r="I958" s="2" t="inlineStr"/>
     </row>
     <row r="959" ht="108" customHeight="1">
       <c r="A959" s="2" t="n">
@@ -42040,8 +43113,16 @@
       <c r="G959" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H959" s="2" t="n"/>
-      <c r="I959" s="2" t="n"/>
+      <c r="H959" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+在高壓電線旁架設施工架應「先移設高壓電線」（選項 1 / A）。
+處理原則
+正確做法：在高壓電線附近作業時，應先聯繫相關單位將高壓電線移設、斷電或加裝絕緣防護裝備，以防止感電事故。
+錯誤示範：「不理高壓電線」或「摸摸看」均極度危險，會造成嚴重觸電甚至死亡。</t>
+        </is>
+      </c>
+      <c r="I959" s="2" t="inlineStr"/>
     </row>
     <row r="960" ht="92.59999999999999" customHeight="1">
       <c r="A960" s="2" t="n">
@@ -42075,8 +43156,18 @@
       <c r="G960" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H960" s="2" t="n"/>
-      <c r="I960" s="2" t="n"/>
+      <c r="H960" s="2" t="inlineStr">
+        <is>
+          <t>人體在平常狀態下（非濕潤狀態）觸及帶電部位時，處於危險性高的狀態下，其安全電壓須在 50 伏特以下。
+安全電壓標準對照
+50 伏特以下：適用於人體在平常狀態（非濕潤狀態）但處於危險性高之環境或狀況。
+25 伏特以下：適用於人體處於濕潤狀態或導電性良好的環境（如良導體金屬表面、潮濕場所）。
+2.5 伏特以下：適用於人體大部分浸在水中的極高度危險狀態。
+Threads
+·osh_flourishing</t>
+        </is>
+      </c>
+      <c r="I960" s="2" t="inlineStr"/>
     </row>
     <row r="961" ht="77.15000000000001" customHeight="1">
       <c r="A961" s="2" t="n">
@@ -42110,8 +43201,20 @@
       <c r="G961" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H961" s="2" t="n"/>
-      <c r="I961" s="2" t="n"/>
+      <c r="H961" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+在有爆炸之虞場所測定絕緣電阻時，其發生火花之原因與連接線之完全放電無關。
+相關原因說明
+有關的原因：
+連接線與未完全放電之機器碰撞：可能因殘餘電荷引起局部短路或放電而產生火花。
+試驗中絕緣損壞處產生電弧：測試高壓下若絕緣損壞穿透，會伴隨電弧與火花。
+測驗完畢時之電容放電：受測設備如具電容特性，測驗後若未妥善放電就拔除或接觸，會釋放儲存能量產生火花。
+無關的原因：
+連接線之完全放電：連接線如果已經「完全放電」（無殘餘電荷、無電位差），則不會釋放能量或產生火花。</t>
+        </is>
+      </c>
+      <c r="I961" s="2" t="inlineStr"/>
     </row>
     <row r="962" ht="92.59999999999999" customHeight="1">
       <c r="A962" s="2" t="n">
@@ -42145,8 +43248,12 @@
       <c r="G962" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H962" s="2" t="n"/>
-      <c r="I962" s="2" t="n"/>
+      <c r="H962" s="2" t="inlineStr">
+        <is>
+          <t>Google AI 摘要未抓取到，請手動補充。</t>
+        </is>
+      </c>
+      <c r="I962" s="2" t="inlineStr"/>
     </row>
     <row r="963" ht="92.59999999999999" customHeight="1">
       <c r="A963" s="2" t="n">
@@ -42180,8 +43287,18 @@
       <c r="G963" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H963" s="2" t="n"/>
-      <c r="I963" s="2" t="n"/>
+      <c r="H963" s="2" t="inlineStr">
+        <is>
+          <t>避免感電的正確處理方式是 (A) 電路要經漏電斷路器。
+原因說明
+漏電斷路器：當發生漏電時，能在極短時間內自動斷電，防止電流通過人體造成嚴重傷害。
+不應喝酒 (B)：喝酒會導致精神不濟、反應遲鈍及身體排汗增加，反而大幅提高感電與工安事故的風險。
+使用安全帶 (C)：主要用於防止高處墜落，無法直接防止電擊。
+戴遮陽帽 (D)：用於防曬，對預防感電沒有實質保護效果。
+LINE TODAY</t>
+        </is>
+      </c>
+      <c r="I963" s="2" t="inlineStr"/>
     </row>
     <row r="964" ht="92.59999999999999" customHeight="1">
       <c r="A964" s="2" t="n">
@@ -42215,8 +43332,12 @@
       <c r="G964" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H964" s="2" t="n"/>
-      <c r="I964" s="2" t="n"/>
+      <c r="H964" s="2" t="inlineStr">
+        <is>
+          <t>Google AI 摘要未抓取到，請手動補充。</t>
+        </is>
+      </c>
+      <c r="I964" s="2" t="inlineStr"/>
     </row>
     <row r="965" ht="92.59999999999999" customHeight="1">
       <c r="A965" s="2" t="n">
@@ -42250,8 +43371,17 @@
       <c r="G965" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H965" s="2" t="n"/>
-      <c r="I965" s="2" t="n"/>
+      <c r="H965" s="2" t="inlineStr">
+        <is>
+          <t>使用電動工具要注意的正確答案是 以上皆是（包含防護罩完整、接地線接地、機身良好）。
+注意事項說明
+防護罩完整：防止切削物噴濺或身體部位誤觸轉動中的刀具。
+接地線接地：避免機具漏電時造成人員感電（觸電）危害。
+機身良好：確保外殼無破損、絕緣正常、開關功能健全。
+臺北市政府勞動局勞動即時通</t>
+        </is>
+      </c>
+      <c r="I965" s="2" t="inlineStr"/>
     </row>
     <row r="966" ht="92.59999999999999" customHeight="1">
       <c r="A966" s="2" t="n">
@@ -42285,8 +43415,17 @@
       <c r="G966" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H966" s="2" t="n"/>
-      <c r="I966" s="2" t="n"/>
+      <c r="H966" s="2" t="inlineStr">
+        <is>
+          <t>防止作業人員遭受電擊之有效措施為裝漏電斷路器。
+原因說明
+漏電斷路器：當電器發生漏電時，能以極快速度自動切斷電源，防止電流通過人體造成感電（電擊）傷害。
+無熔絲開關、開刀開關（閘刀開關）、保險絲：主要作用為短路或過載（過電流）保護，無法在發生微小漏電、人員觸電時提供有效的感電防護。
+臺北市政府勞動局勞動即時通 . () 下列何者為防止作業人員遭受電擊之有效措施？ (A)裝漏電 ...
+2020年1月21日 — 相關試題. 79. 下列何者為防止作業人員遭受電擊之有效措施？ (A)裝漏電斷路器(B)裝無熔絲開關(C)裝閘刀開關(D)裝保險絲. #3033746 · 1136. 下列何者為防止作業人員遭受電擊之有效措施？ (A)裝漏電斷路器(B)裝無熔絲開關(C)裝閘刀...</t>
+        </is>
+      </c>
+      <c r="I966" s="2" t="inlineStr"/>
     </row>
     <row r="967" ht="92.59999999999999" customHeight="1">
       <c r="A967" s="2" t="n">
@@ -42320,8 +43459,24 @@
       <c r="G967" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H967" s="2" t="n"/>
-      <c r="I967" s="2" t="n"/>
+      <c r="H967" s="2" t="inlineStr">
+        <is>
+          <t>身體在潮濕的狀況下，電阻值之變化為降低。
+Threads
+·iceforestmusic
+原因說明
+皮膚乾燥與潮濕的差別：人體皮膚乾燥時，電阻大約是 10 萬歐姆（Ω）；當皮膚潮濕或流汗時，水分與汗水中的電解質會使皮膚電阻大幅降低。
+觸電風險：根據歐姆定律（
+𝐼
+=
+𝑉
+/
+𝑅
+），電阻變小會使通過人體的電流變大，因此身體潮濕時非常容易觸電或造成更嚴重的電擊傷害。
+ROHM</t>
+        </is>
+      </c>
+      <c r="I967" s="2" t="inlineStr"/>
     </row>
     <row r="968" ht="92.59999999999999" customHeight="1">
       <c r="A968" s="2" t="n">
@@ -42355,8 +43510,16 @@
       <c r="G968" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H968" s="2" t="n"/>
-      <c r="I968" s="2" t="n"/>
+      <c r="H968" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+使用氣流管線輸送粉體物料時，當粉體輸送速度越快，粉粒帶靜電量越高。
+原因說明
+摩擦加劇：速度越快，粉粒與管壁以及粉粒之間的摩擦與碰撞越劇烈。
+電荷累積：摩擦越劇烈，產生的靜電荷就越多，導致帶電量升高。</t>
+        </is>
+      </c>
+      <c r="I968" s="2" t="inlineStr"/>
     </row>
     <row r="969" ht="92.59999999999999" customHeight="1">
       <c r="A969" s="2" t="n">
@@ -42390,8 +43553,28 @@
       <c r="G969" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H969" s="2" t="n"/>
-      <c r="I969" s="2" t="n"/>
+      <c r="H969" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+若電氣迴路之電壓越高，該迴路電擊之危害性為越高。
+核心原因
+歐姆定律：依據
+𝐼
+=
+𝑉
+𝑅
+（電流＝電壓÷電阻），在人體電阻固定的情況下，電壓 (
+𝑉
+𝑉
+) 越高，流經人體的電流 (
+𝐼
+𝐼
+) 就越大。
+生理影響：流經人體的電流越大，對心臟、神經系統的破壞與組織加熱效應就越嚴重，因此高電壓帶來的感電與電擊嚴重性隨之增加。
+aim.org.tw</t>
+        </is>
+      </c>
+      <c r="I969" s="2" t="inlineStr"/>
     </row>
     <row r="970" ht="92.59999999999999" customHeight="1">
       <c r="A970" s="2" t="n">
@@ -42425,8 +43608,18 @@
       <c r="G970" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H970" s="2" t="n"/>
-      <c r="I970" s="2" t="n"/>
+      <c r="H970" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+電氣迴路中，火線係指 (A) 通電中導線。
+相關概念簡介
+火線（Live Wire / Hot Wire）：又稱相線，是帶有電壓且正在通電、輸送電流的導線。
+中性線（Neutral Wire）：俗稱零線，通常與電力系統的中性點連接，用以構成電流迴路。
+接地導線（Ground Wire）：俗稱地線，是用於設備漏電時導引電流流入大地以策安全的保護線，正常情況下不帶工作電流。
+立宇生活科技</t>
+        </is>
+      </c>
+      <c r="I970" s="2" t="inlineStr"/>
     </row>
     <row r="971" ht="92.59999999999999" customHeight="1">
       <c r="A971" s="2" t="n">
@@ -42460,8 +43653,25 @@
       <c r="G971" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H971" s="2" t="n"/>
-      <c r="I971" s="2" t="n"/>
+      <c r="H971" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+降低人體電阻，以降低感電電流是錯誤的敘述。
+原因解析
+正確觀念：根據歐姆定律（
+𝐼
+=
+𝑉
+/
+𝑅
+），在電壓一定的情況下，電阻越小，通過人體的電流反而越大，更容易造成嚴重的感電（觸電）傷害。因此，若要降低感電電流，應該要提高人體電阻（例如穿戴絕緣手套、穿絕緣鞋、保持乾燥等），而不是降低人體電阻。
+其他選項：
+降低使用電壓：可直接降低感電時的電流大小，屬於正確的預防方法。
+裝置漏電斷路器：當發生漏電時能自動迅速切斷電源，防止觸電，屬於正確防護裝置。
+電氣接地：能將漏電導向大地，避免金屬外殼帶電而使人體感電，屬於正確安全措施。</t>
+        </is>
+      </c>
+      <c r="I971" s="2" t="inlineStr"/>
     </row>
     <row r="972" ht="92.59999999999999" customHeight="1">
       <c r="A972" s="2" t="n">
@@ -42495,8 +43705,16 @@
       <c r="G972" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H972" s="2" t="n"/>
-      <c r="I972" s="2" t="n"/>
+      <c r="H972" s="2" t="inlineStr">
+        <is>
+          <t>心室規則收縮不屬於人體感電（觸電）後所產生的生理反應。
+解答說明
+正確反應：人體感電後，電流會刺激或干擾神經與肌肉，造成肌肉收縮（如胸部肌肉收縮導致呼吸困難而窒息），以及影響心臟正常運作，導致心室顫動（即心室不規則收縮），進而造成血液停止循環而死亡。
+不屬於的反應：觸電不會讓心室「規則」收縮，反而會引起心室亂跳（細動或纖維顫動）。
+虎科電機系網</t>
+        </is>
+      </c>
+      <c r="I972" s="2" t="inlineStr"/>
     </row>
     <row r="973" ht="92.59999999999999" customHeight="1">
       <c r="A973" s="2" t="n">
@@ -42530,8 +43748,19 @@
       <c r="G973" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H973" s="2" t="n"/>
-      <c r="I973" s="2" t="n"/>
+      <c r="H973" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+答案是 人體之身高。
+影響感電傷害嚴重度的直接因素
+當電流流經人體時，決定傷害嚴重度的三大主要／直接因素為：
+流經身體的電流量之大小：電流越大，對人體組織與心臟的破壞越強。
+電流流經身體之路徑：若電流經過心臟、腦部或肺部等重要器官，危險性會顯著增加。
+身體之電阻：電阻決定了在特定電壓下會有多少電流通過人體。
+aim.org.tw 而「人體之身高」與電流流經人體造成的生理破壞、心室顫動或組織灼傷無直接因果關係，因此不是影響感電傷害嚴重度的直接因素。</t>
+        </is>
+      </c>
+      <c r="I973" s="2" t="inlineStr"/>
     </row>
     <row r="974" ht="108" customHeight="1">
       <c r="A974" s="2" t="n">
@@ -42565,8 +43794,19 @@
       <c r="G974" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H974" s="2" t="n"/>
-      <c r="I974" s="2" t="n"/>
+      <c r="H974" s="2" t="inlineStr">
+        <is>
+          <t>正確的敘述為：(C) 接地是避免感電危害的有效方法。
+各選項解析
+(A) 電器之接地線可接於天然氣鋼管上：錯誤。天然氣鋼管或瓦斯管絕對不可作為接地線連接點，以免因漏電產生火花引發氣爆或火災。
+(B) 電動手工具無須接地：錯誤。手提式電動工具或電動手工具金屬外殼極易因絕緣劣化漏電，依規定均應確實接地（或使用雙重絕緣構造）以策安全。
+勞動及職業安全衛生研究所
+(C) 接地是避免感電危害的有效方法：正確。設備金屬外殼接地能將漏電電流導向大地，大幅降低人員碰觸時遭受感電（觸電）的危害。
+台灣防雷股份有限公司 (D) 無熔絲開關亦可避免遭受感電危害：錯誤。無熔絲開關（NFB）是用於防止「過載」或「短路」引起電線走火的過電流保護裝置，無法直接防止人體遭受感電危害（防感電需依賴漏電斷路器或接地裝置）。
+勞動部職業安全衛生署</t>
+        </is>
+      </c>
+      <c r="I974" s="2" t="inlineStr"/>
     </row>
     <row r="975" ht="108" customHeight="1">
       <c r="A975" s="2" t="n">
@@ -42600,8 +43840,17 @@
       <c r="G975" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H975" s="2" t="n"/>
-      <c r="I975" s="2" t="n"/>
+      <c r="H975" s="2" t="inlineStr">
+        <is>
+          <t>正確答案是 (D) 純質油品靜態儲存於儲槽中。
+原因解析
+純質油品靜態儲存於儲槽中：油品處於靜止狀態，沒有流動、摩擦、噴射或晃動，因此不易產生或誘發靜電電荷。
+油品由金屬管線噴出：高速噴射會使油品與管口產生強烈摩擦與電荷分離，容易誘發靜電。
+使用量尺量測油品液位：金屬量尺在插入或抽出時會與油面及導電部件摩擦、相對運動，易產生靜電導至危險。
+油品在管線中高速流動：流速越快，油品與管壁摩擦越劇烈，極易累積高電位靜電。</t>
+        </is>
+      </c>
+      <c r="I975" s="2" t="inlineStr"/>
     </row>
     <row r="976" ht="92.59999999999999" customHeight="1">
       <c r="A976" s="2" t="n">
@@ -42627,8 +43876,18 @@
       <c r="G976" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H976" s="2" t="n"/>
-      <c r="I976" s="2" t="n"/>
+      <c r="H976" s="2" t="inlineStr">
+        <is>
+          <t>人體對於電流強度的最小感知電流通常為 1 毫安培 (mA)（選項 A）。
+電流對人體的影響反應參考
+1 mA：人體能感覺到觸電的最小電流（產生輕微麻感或刺痛感）。
+10 mA：會產生強烈麻痺、痙攣或劇痛。
+50 mA：可能引起呼吸困難或心臟顫動，具有生命危險。
+100 mA 以上：極易致命。
+詳細的電氣安全知識可以參考 臺灣大學科學教育發展中心 的說明。</t>
+        </is>
+      </c>
+      <c r="I976" s="2" t="inlineStr"/>
     </row>
     <row r="977" ht="108" customHeight="1">
       <c r="A977" s="2" t="n">
@@ -42662,8 +43921,18 @@
       <c r="G977" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H977" s="2" t="n"/>
-      <c r="I977" s="2" t="n"/>
+      <c r="H977" s="2" t="inlineStr">
+        <is>
+          <t>錯誤的敘述為：「電擊之傷害程度與電流之流經路徑無關」。
+正確觀念解析
+電流路徑有關：電流如果流經心臟、腦部或呼吸中樞等重要器官，會比單純流經四肢造成更嚴重的致命傷害（例如引發心室顫動），因此傷害程度與流經路徑息息相關。
+乾燥皮膚電阻較高：皮膚乾燥時電阻大（約數萬至十幾萬歐姆），潮濕時電阻會大幅降低，因此潮濕時更容易觸電。
+與電流大小成正相關：通過人體的電流越大，對人體的生理傷害（如肌肉痙攣、心律不整、組織灼傷）就越嚴重。
+與接觸電壓成正相關：接觸電壓越高，在電阻固定的情況下產生的電流也越大，傷害程度隨之增加。
+考古豹</t>
+        </is>
+      </c>
+      <c r="I977" s="2" t="inlineStr"/>
     </row>
     <row r="978" ht="92.59999999999999" customHeight="1">
       <c r="A978" s="2" t="n">
@@ -42697,8 +43966,16 @@
       <c r="G978" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H978" s="2" t="n"/>
-      <c r="I978" s="2" t="n"/>
+      <c r="H978" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+答案是 絕緣良好之握把。
+說明
+絕緣良好之握把：因為具備良好的絕緣防護能力，能有效隔絕電流，所以較不易發生感電（觸電）事故。
+其他選項（如待機中接於電焊柄之焊條端、一次側線路端子、二次側線路端子）皆屬於帶電或容易接觸到電壓的部分，相對容易發生感電危險。</t>
+        </is>
+      </c>
+      <c r="I978" s="2" t="inlineStr"/>
     </row>
     <row r="979" ht="92.59999999999999" customHeight="1">
       <c r="A979" s="2" t="n">
@@ -42732,8 +44009,25 @@
       <c r="G979" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H979" s="2" t="n"/>
-      <c r="I979" s="2" t="n"/>
+      <c r="H979" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+發生感電（觸電）時，流經人體的電流量與與人體當時的情緒狀況較無關。
+相關因素說明
+與人體接觸的電壓值：根據歐姆定律（
+𝐼
+=
+𝑉
+/
+𝑅
+），電壓越高，在電阻固定的情況下，流經人體的電流就會越大。
+與人所處位置的絕緣性：人體是否與地面絕緣（例如穿著絕緣鞋或站在絕緣墊上）會直接影響電流形成迴路的阻抗與大小。
+與人體皮膚、衣著的電阻：皮膚乾濕程度與衣著阻抗是決定總電阻的重要部分，電阻越小，流經的電流就越大。
+與人體當時的情緒狀況：情緒屬於心理或生理狀態，並不會直接改變物理上的電路電阻或接觸電壓，因此與瞬間流經人體的電流量無直接關係。
+內政部消防署全球資訊網</t>
+        </is>
+      </c>
+      <c r="I979" s="2" t="inlineStr"/>
     </row>
     <row r="980" ht="108" customHeight="1">
       <c r="A980" s="2" t="n">
@@ -42767,8 +44061,15 @@
       <c r="G980" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H980" s="2" t="n"/>
-      <c r="I980" s="2" t="n"/>
+      <c r="H980" s="2" t="inlineStr">
+        <is>
+          <t>閃絡係指高壓帶電導體與接近物體所產生之火花放電。
+閃絡（Flashover）說明
+定義：當高壓導體與接地物體或鄰近物體距離過近時，空氣絕緣被強大電壓擊穿，因而發生瞬間的火花放電或電弧現象。
+特性：通常發生在絕緣體表面或空氣間隙中，放電後電壓會急劇下降。</t>
+        </is>
+      </c>
+      <c r="I980" s="2" t="inlineStr"/>
     </row>
     <row r="981" ht="92.59999999999999" customHeight="1">
       <c r="A981" s="2" t="n">
@@ -42802,8 +44103,15 @@
       <c r="G981" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H981" s="2" t="n"/>
-      <c r="I981" s="2" t="n"/>
+      <c r="H981" s="2" t="inlineStr">
+        <is>
+          <t>人體接近特高壓電路時發生此種現象稱為 閃絡。
+閃絡現象說明
+定義：高壓或特高壓帶電導體與接近的人體或物體之間，因空氣絕緣被強電場破壞而產生的表面或空間火花放電現象。
+特點：人體雖未直接接觸線路本體，但仍會因強電場引發放電並感應出電流。</t>
+        </is>
+      </c>
+      <c r="I981" s="2" t="inlineStr"/>
     </row>
     <row r="982" ht="92.59999999999999" customHeight="1">
       <c r="A982" s="2" t="n">
@@ -42837,8 +44145,18 @@
       <c r="G982" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H982" s="2" t="n"/>
-      <c r="I982" s="2" t="n"/>
+      <c r="H982" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+電氣迴路中，接地線外圍絕緣皮之顏色為綠色。
+電線顏色快速對照
+火線 (Live)：常見為紅、黑、藍等顏色。
+中性線 (Neutral)：常見為白色或灰色。
+接地線 (Earth/Ground)：規定使用綠色或黃綠雙色。
+www.aim.org.tw</t>
+        </is>
+      </c>
+      <c r="I982" s="2" t="inlineStr"/>
     </row>
     <row r="983" ht="92.59999999999999" customHeight="1">
       <c r="A983" s="2" t="n">
@@ -42872,8 +44190,18 @@
       <c r="G983" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H983" s="2" t="n"/>
-      <c r="I983" s="2" t="n"/>
+      <c r="H983" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+有誤的選項是：穿釘鞋直接碰觸電氣設備，不會感電。
+原因說明
+錯誤選項解析：釘鞋通常含有金屬釘或金屬材質，穿著釘鞋直接碰觸電氣設備不但無法絕緣，金屬釘反而可能導電或增加觸電風險，甚至在潮濕或接地良好的環境下更容易構成感電迴路 而造成嚴重感電災害。
+臺北市政府全球資訊網
+正確做法：進行電氣相關作業或接近電氣設備時，應穿戴合格的絕緣防護具（如絕緣鞋、絕緣手套），嚴禁赤腳或使用導電器具，並落實設備接地及加裝漏電斷路器。
+勞動部職業安全衛生署</t>
+        </is>
+      </c>
+      <c r="I983" s="2" t="inlineStr"/>
     </row>
     <row r="984" ht="92.59999999999999" customHeight="1">
       <c r="A984" s="2" t="n">
@@ -42907,8 +44235,18 @@
       <c r="G984" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H984" s="2" t="n"/>
-      <c r="I984" s="2" t="n"/>
+      <c r="H984" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+若電氣迴路中之過載電流越小，則斷路器可允許之操作時間為越長。
+原因解析
+反時限特性：斷路器具有「反時限保護特性」，即過電流愈大，動作時間愈短；過電流愈小，允許延遲的時間愈長。
+導線受熱差異：
+過載電流大：線路會快速升溫，必須快速斷開以避免絕緣燒壞或引發火災。
+過載電流小：線路升溫較慢，系統允許延遲一點時間再跳脫，以避免因短暫的突波電流（浪湧電流）造成誤動作。</t>
+        </is>
+      </c>
+      <c r="I984" s="2" t="inlineStr"/>
     </row>
     <row r="985" ht="92.59999999999999" customHeight="1">
       <c r="A985" s="2" t="n">
@@ -42942,8 +44280,19 @@
       <c r="G985" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H985" s="2" t="n"/>
-      <c r="I985" s="2" t="n"/>
+      <c r="H985" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+檢查牆上插座是否有電，最適合的方法是以電壓表量其兩端（或稱以電壓表量其開路電壓）。
+台灣區電信工程工業同業公會 原因說明
+電壓表：用來測量電路兩端的電位差（電壓）。當插座有電時，電壓表接上就會顯示正常的電壓數值（例如台灣常見的 110V 或 220V），若沒電則顯示 0V，是最直接且安全的檢測方式。
+其他選項不適當的原因：
+瓦特計：用來測量功率或所耗電能，在未接負載的情況下無法檢測插座本身是否有電壓。
+歐姆表：用來測量電阻，必須在斷電狀態下使用；若帶電去量電阻會損壞儀表甚至發生危險。
+電流表：串聯或直接短路測量電流會造成短路危險（短路電流過大會燒毀儀表或跳電）。</t>
+        </is>
+      </c>
+      <c r="I985" s="2" t="inlineStr"/>
     </row>
     <row r="986" ht="92.59999999999999" customHeight="1">
       <c r="A986" s="2" t="n">
@@ -42977,8 +44326,23 @@
       <c r="G986" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H986" s="2" t="n"/>
-      <c r="I986" s="2" t="n"/>
+      <c r="H986" s="2" t="inlineStr">
+        <is>
+          <t>根據您的題目描述，第一個問題的答案是開路。
+當電路中的開關呈斷開狀態或失去負載，導致電流中斷、無法形成閉合迴路時，這種電路狀態就稱為開路（或稱斷路）。
+至於您的第二個問題，在台灣的室內配線法規中，火線（Phase/Line）的標準導線顏色通常為黑色或紅色（一般單相二線式電路中常以黑色代表火線，白色代表中性線；單相三線式則常以紅、黑代表火線，白色代表中性線）。
+為了讓您更清楚傳統電力系統與電路的基本觀念，以下為您整理常見的電路狀態與導線顏色對照：
+常見電路狀態對照
+開路 (Open Circuit)： 電路中途斷開（如開關切斷），電流為零，電器不工作。
+短路 (Short Circuit)： 火線與中性線（或地線）未經過負載直接接觸，導致電阻極小、電流瞬間暴增，容易引發火災。
+通路 (Closed Circuit)： 電路完整閉合，電流正常流過負載，電器正常運作。
+台灣常見室內配線顏色（法規標準）
+火線 (非接地導線)： 黑色 或 紅色（有時三相電路會使用藍色）
+中性線 (被接地導線)： 白色 或 淺灰色
+地線 (接地導線)： 綠色</t>
+        </is>
+      </c>
+      <c r="I986" s="2" t="inlineStr"/>
     </row>
     <row r="987" ht="92.59999999999999" customHeight="1">
       <c r="A987" s="2" t="n">
@@ -43012,8 +44376,19 @@
       <c r="G987" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H987" s="2" t="n"/>
-      <c r="I987" s="2" t="n"/>
+      <c r="H987" s="2" t="inlineStr">
+        <is>
+          <t>火線（Live Wire）在這幾個選項中最標準且常見的顏色是紅色。
+國霖機電
+選項對應的電線功能：
+紅色：代表火線（帶電線，電流來源）。
+白色：在台灣居家配線中通常代表中性線（零線）。
+藍色：常代表中性線（如國際或新式電工標準）或部分控制線。
+綠色：代表接地線。
+立宇生活科技</t>
+        </is>
+      </c>
+      <c r="I987" s="2" t="inlineStr"/>
     </row>
     <row r="988" ht="92.59999999999999" customHeight="1">
       <c r="A988" s="2" t="n">
@@ -43047,8 +44422,97 @@
       <c r="G988" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H988" s="2" t="n"/>
-      <c r="I988" s="2" t="n"/>
+      <c r="H988" s="2" t="inlineStr">
+        <is>
+          <t>綠色。在電氣安全法規中，接地線（導線）的標準顏色通常為綠色（或綠色帶黃色條紋）。
+載入中...
+顯示更多
+網頁搜尋結果
+1157. 請問接地導線是什麼顏色？ (A)綠色(B)白色(C)藍色(D ...
+› item-1157.+請問接地導線是什麼顏色...
+2024年10月7日 — 請問接地導線是什麼顏色？ (A)綠色 (B)白色 (C)藍色 (D)紅色. 答案：登入後查看 統計： A(1114), B(101), C(68), D(89), E(0) #3327155 ...
+缺少字詞： 崩塌、 ‎管理 ‎實務
+中性線、地線：電線顏色、接法與法規，保障居家電力安全必看！
+立宇生活科技
+› 居家DIY
+中性線（Neutral Wire） · 常見顏色：白色。 · 電壓：0V（理論上，與大地電位相同）。 · 作用：提供電流回流路徑，搭配火線形成完整迴路。在台灣，中性線常與「零線」混用，但 ...
+缺少字詞： 倒塌 ‎崩塌、 ‎物體 ‎飛 ‎落、 ‎撞 ‎危害
+居家配線「電線顏色」的含意
+國霖機電
+› news
+電工法規第69條至74條中有明確規範：我们平常最容易見到的「紅色」即代表火線，摸到它會被觸電的；「白色線」即代表中性線，摸到它不會被觸電；還有「綠色線」即代表接地線 ...
+缺少字詞： 倒塌 ‎崩塌、 ‎物體 ‎飛 ‎落、 ‎撞 ‎危害 ‎預防 ‎管理 ‎實務
+接地線怎麼選才安全？綠黃雙色、線徑對照與5 大常見接地錯誤 ...
+derrong.com.tw
+› articles › grounding-earth-wir...
+2026年7月1日 — 接地線的顏色：綠色或綠黃雙色，別再用黑線代替 ... 依CNS 與國內配線慣例，接地導線一律使用綠色或綠／黃雙色絕緣，這是國際共通的識別，不可以拿來當火線 ...
+缺少字詞： 白色 ‎藍 ‎色 ‎紅色。 ‎倒塌 ‎崩塌、 ‎物體 ‎飛 ‎落、 ‎撞 ‎危害 ‎預防 ‎管理
+電線顏色分類：台灣火線、中性線、地線標準與接線方式
+RS-online.com
+› web › wiring-colours-guide
+2023年9月12日 — 在台灣，火線（Live）顏色會依電路而有所不同，常見為紅色、黑色、棕色或灰色；藍色代表中性線（Neutral）；綠色或黃綠雙色代表接地線（Earth）。
+缺少字詞： 倒塌 ‎崩塌、 ‎物體 ‎飛 ‎落、 ‎被 ‎撞 ‎危害 ‎預防 ‎實務
+圖片
+秒懂火線、中性線、地線：電線顏色、接法與法規，保障居家電力 ...
+立宇生活科技
+一般業（重要資料）重新排序版112.07.22 (1465題) (79-104) | PDF
+💡💡家昕小知識, 常見電線顏色為, 火線：紅色、黑色 ⚫🔴, 中性線、地線：白色 ⚪, 接地線：綠色🟢, 居家最重要的即是水與電, 一個不小心就會有安全疑慮問題💥😭, 不過您可以放心, 我們檢驗項目有包含電箱檢測🔌, 電線年份路孔徑、壓接端子、絕緣色套、220伏特, 皆會為您一一把關家的品質💪🏻, 驗屋找家昕，讓您居住很放心❤, ▶客服專線：0809080512 , -, ...
+Instagram
+顯示更多圖片
+相關問題
+在工廠安全標示中,代表危險的顏色是什麼?
+都市計畫圖中,工業區是用什麼顏色的外框表示的?
+職業安全衛生法的目的是為了保障工作者安全與健康,防止以下哪種災害?
+網頁搜尋結果
+營造工地電氣作業安全檢查重點及注意事項
+臺北市政府全球資訊網
+› Upload › relfile
+PDF
+說明接地線以使用銅線為原則，可使用裸線、被覆線或絕緣線。個別被覆或絕緣. 之接地線，其外觀應為綠色或綠色加一條以上之黃色條紋者。
+36 頁
+缺少字詞： 顏色 ? ‎倒塌 ‎崩塌、 ‎飛 ‎落、 ‎撞
+【了解電線分顏色？小心用電安全又省心！】 大家有沒有注意 ...
+Facebook · 銅心水電材料專門戶
+超過 380 個回應 · 1 年前
+白色線：一般在線路時用於中性線。 綠色線：通常被用來做大地線，也可以當作系統線的 配線，或是接地線接到接地極的導線。 小提醒 家中插座或 ...
+家昕小知識常見電線顏色為火線：紅色、黑色 中性線、地線： ...
+Facebook · 家昕科技驗屋
+2 則回應 · 2 年前
+0:48
+家昕小知識 常見電線顏色為 火線：紅色、黑色⚫ 中性線、地線：白色⚪ 接地線：綠色 居家最重要的即是水與電...
+缺少字詞： 藍 ‎倒塌 ‎崩塌、 ‎物體 ‎飛 ‎落、 ‎撞 ‎危害 ‎預防 ‎管理 ‎實務
+其他人也搜尋了以下項目
+電線顏色接法
+電線顏色對照表
+火線地線怎麼分
+電燈電線顏色接法
+中性線是什麼
+中性線作用
+電線顏色法規
+火線是l還是n
+頁面導覽
+1
+2
+3
+4
+5
+6
+7
+8
+9
+10
+下一頁
+頁尾連結
+台灣
+708 臺南市安平區 - 根據你的 IP 位址
+- 更新位置
+說明
+提供意見
+隱私權
+服務條款</t>
+        </is>
+      </c>
+      <c r="I988" s="2" t="inlineStr"/>
     </row>
     <row r="989" ht="108" customHeight="1">
       <c r="A989" s="2" t="n">
@@ -43082,8 +44546,15 @@
       <c r="G989" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H989" s="2" t="n"/>
-      <c r="I989" s="2" t="n"/>
+      <c r="H989" s="2" t="inlineStr">
+        <is>
+          <t>這題的正確答案是：物體倒塌（或物體倒塌、崩塌）。
+職業安全衛生統計定義
+物體倒塌、崩塌：指堆積物（包含積垛）、施工架、建築物等崩落或倒塌碰觸到人體的災害情形。
+桃園市政府勞動檢查處</t>
+        </is>
+      </c>
+      <c r="I989" s="2" t="inlineStr"/>
     </row>
     <row r="990" ht="92.59999999999999" customHeight="1">
       <c r="A990" s="2" t="n">
@@ -43117,8 +44588,13 @@
       <c r="G990" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H990" s="2" t="n"/>
-      <c r="I990" s="2" t="n"/>
+      <c r="H990" s="2" t="inlineStr">
+        <is>
+          <t>被夾、被捲不是造紙廠勞工進入散漿槽清掃作業時較易發生的危害。
+散漿槽內部屬於侷限空間，在進行清掃作業時，最主要且常見的職災危險源來自槽內殘留的化學品、有機物腐敗或通風不良所引發的中毒與缺氧（窒息）災害，或是人員不慎跌落、上方物體掉落的倒塌（崩塌/墜落）風險。而「被夾、被捲」通常較常發生在散漿槽運轉中、或是面對機械傳動軸、滾輪等動力機械操作時，在已停機並進入內部清掃的靜態作業中相對並非最主要的危害。</t>
+        </is>
+      </c>
+      <c r="I990" s="2" t="inlineStr"/>
     </row>
     <row r="991" ht="92.59999999999999" customHeight="1">
       <c r="A991" s="2" t="n">
@@ -43152,8 +44628,18 @@
       <c r="G991" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H991" s="2" t="n"/>
-      <c r="I991" s="2" t="n"/>
+      <c r="H991" s="2" t="inlineStr">
+        <is>
+          <t>有誤的選項是：各堆鋼材之距離應儘量縮小。
+正確觀念
+依據《營造安全衛生設施標準》第32條規定，雇主對於鋼材之儲存，應依下列規定辦理：
+各堆鋼材之間應有適當之距離，而不是儘量縮小，以確保通道暢通、搬運安全及避免相互影響倒塌。
+應預防傾斜、滾落，必要時應用纜索等加以適當捆紮。
+儲存之場地應為堅固之地面。
+置放地點應避免在電線下方或上方。</t>
+        </is>
+      </c>
+      <c r="I991" s="2" t="inlineStr"/>
     </row>
     <row r="992" ht="92.59999999999999" customHeight="1">
       <c r="A992" s="2" t="n">
@@ -43187,8 +44673,15 @@
       <c r="G992" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H992" s="2" t="n"/>
-      <c r="I992" s="2" t="n"/>
+      <c r="H992" s="2" t="inlineStr">
+        <is>
+          <t>為確保鋼筋儲存時之安全性，有誤的選項是：應盡可能堆高以節省空間。
+原因說明
+錯誤選項： 鋼筋與鋼材等重物若盡可能堆高，容易因重心不穩、超載或地基下陷而發生傾斜、滾落或倒塌，造成嚴重的工安意外。
+正確做法： 根據《營造安全衛生設施標準》規定，儲存鋼材時應預防傾斜與滾落（必要時用纜索捆紮）、地面要堅固、各堆之間保持適當距離、遠離電源及避免置於電力線下方。</t>
+        </is>
+      </c>
+      <c r="I992" s="2" t="inlineStr"/>
     </row>
     <row r="993" ht="77.15000000000001" customHeight="1">
       <c r="A993" s="2" t="n">
@@ -43222,8 +44715,18 @@
       <c r="G993" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H993" s="2" t="n"/>
-      <c r="I993" s="2" t="n"/>
+      <c r="H993" s="2" t="inlineStr">
+        <is>
+          <t>吊掛作業為防止荷件物飛落，有誤的措施是「以最快速度吊至定位」。
+正確觀念與說明
+以最快速度吊至定位（有誤）：吊掛作業應平穩、緩慢地進行，避免因速度過快產生離心力、晃動或重心不穩，導致荷件物飛落或碰撞。
+禁止人員進入吊掛作業半徑（正確）：應確實管制危險區域，嚴禁人員進入吊舉物下方或作業半徑內，以策安全。
+繩索綑綁必須牢固（正確）：吊掛前必須確認吊索與荷件綑綁緊密、牢固，防止鬆脫。
+繩索綑綁並使用索網以防止荷件飛落（正確）：針對散裝或易散落物，應配合索網或適當防護措施來加強固定。
+桃園市幼獅產業協進會</t>
+        </is>
+      </c>
+      <c r="I993" s="2" t="inlineStr"/>
     </row>
     <row r="994" ht="108" customHeight="1">
       <c r="A994" s="2" t="n">
@@ -43257,8 +44760,13 @@
       <c r="G994" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H994" s="2" t="n"/>
-      <c r="I994" s="2" t="n"/>
+      <c r="H994" s="2" t="inlineStr">
+        <is>
+          <t>護欄前方 2 公尺內之樓板、地板，嚴禁堆放任何物料、設備。
+根據《營造安全衛生設施標準》第20條規定，護欄前方二公尺內之樓板、地板，不得堆放任何物料、設備，並不得使用梯子、合梯、踏凳作業及停放車輛機械供勞工使用。</t>
+        </is>
+      </c>
+      <c r="I994" s="2" t="inlineStr"/>
     </row>
     <row r="995" ht="92.59999999999999" customHeight="1">
       <c r="A995" s="2" t="n">
@@ -43292,8 +44800,13 @@
       <c r="G995" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H995" s="2" t="n"/>
-      <c r="I995" s="2" t="n"/>
+      <c r="H995" s="2" t="inlineStr">
+        <is>
+          <t>答案為 3 公尺。
+依據《職業安全衛生設施規則》第 237 條規定：「雇主對於自高度在三公尺以上之場所投下物體有危害勞工之虞時，應設置適當之滑槽、承受設備，並指派監視人員。」</t>
+        </is>
+      </c>
+      <c r="I995" s="2" t="inlineStr"/>
     </row>
     <row r="996" ht="92.59999999999999" customHeight="1">
       <c r="A996" s="2" t="n">
@@ -43327,8 +44840,12 @@
       <c r="G996" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H996" s="2" t="n"/>
-      <c r="I996" s="2" t="n"/>
+      <c r="H996" s="2" t="inlineStr">
+        <is>
+          <t>Google AI 摘要未抓取到，請手動補充。</t>
+        </is>
+      </c>
+      <c r="I996" s="2" t="inlineStr"/>
     </row>
     <row r="997" ht="92.59999999999999" customHeight="1">
       <c r="A997" s="2" t="n">
@@ -43362,8 +44879,17 @@
       <c r="G997" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H997" s="2" t="n"/>
-      <c r="I997" s="2" t="n"/>
+      <c r="H997" s="2" t="inlineStr">
+        <is>
+          <t>以飛來物、落下物等為主體碰撞人體的情況，屬於 物體飛落 災害類型。
+考試院主管法規查詢系統
+災害類型說明
+物體飛落：指以飛來物、落下物為主體碰觸或碰撞人體的狀況。
+常見情境：包含研磨砂輪破裂、切斷片或切削粉飛出，以及自己手持的物品掉落砸到腳等情況。
+桃園市政府勞動檢查處</t>
+        </is>
+      </c>
+      <c r="I997" s="2" t="inlineStr"/>
     </row>
     <row r="998" ht="92.59999999999999" customHeight="1">
       <c r="A998" s="2" t="n">
@@ -43398,8 +44924,13 @@
       <c r="G998" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H998" s="2" t="n"/>
-      <c r="I998" s="2" t="n"/>
+      <c r="H998" s="2" t="inlineStr">
+        <is>
+          <t>設置適當滑槽供高處投下物體，屬防止物體飛落（或稱落物擊傷）危害之設施。
+依據《職業安全衛生設施規則》第237條規定：「雇主對於自高度在三公尺以上之場所投下物體有危害勞工之虞時，應設置適當之滑槽、承受設備，並指派監視人員」，此規範歸納於「物體飛落防止」專章中，用以避免高處墜落物砸傷下方或周遭作業人員。</t>
+        </is>
+      </c>
+      <c r="I998" s="2" t="inlineStr"/>
     </row>
     <row r="999" ht="92.59999999999999" customHeight="1">
       <c r="A999" s="2" t="n">
@@ -43427,8 +44958,12 @@
       <c r="G999" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H999" s="2" t="n"/>
-      <c r="I999" s="2" t="n"/>
+      <c r="H999" s="2" t="inlineStr">
+        <is>
+          <t>Google AI 摘要未抓取到，請手動補充。</t>
+        </is>
+      </c>
+      <c r="I999" s="2" t="inlineStr"/>
     </row>
     <row r="1000" ht="108" customHeight="1">
       <c r="A1000" s="2" t="n">
@@ -43462,8 +44997,16 @@
       <c r="G1000" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H1000" s="2" t="n"/>
-      <c r="I1000" s="2" t="n"/>
+      <c r="H1000" s="2" t="inlineStr">
+        <is>
+          <t>依據營造安全衛生設施標準第29條規定，營造用各類物料之儲存、堆積及排列，應井然有序，且不得儲存於距庫門或升降機 2 公尺範圍以內或足以妨礙交通的地點。因此正確答案為 2 公尺。
+法規重點摘要
+距離限制：距庫門或升降機 2 公尺以內不得堆放物料。
+倉庫安全設施：倉庫內應設置必要的警告標示、護圍及防火設備。
+走道與設備維護：物料儲存不得妨礙消防與緊急設備（如滅火器、火警警報器）之使用。</t>
+        </is>
+      </c>
+      <c r="I1000" s="2" t="inlineStr"/>
     </row>
     <row r="1001" ht="92.59999999999999" customHeight="1">
       <c r="A1001" s="2" t="n">
@@ -43497,8 +45040,15 @@
       <c r="G1001" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H1001" s="2" t="n"/>
-      <c r="I1001" s="2" t="n"/>
+      <c r="H1001" s="2" t="inlineStr">
+        <is>
+          <t>根據中華民國《營造安全衛生設施標準》第 35 條規定，磚、瓦、木塊或同類材料之堆放高度不得超過 1.8 公尺。
+💡 相關法規重點
+材料堆放規定：雇主對於磚、瓦、木塊、管料、鋼筋、鋼材或相同及類似營建材料之堆放，應置放於穩固、平坦之處，整齊緊靠堆置，其高度不得超過 1.8 公尺。
+鄰近開口限制：儲存位置若鄰近開口部分時，應距離該開口部分 2 公尺以上。</t>
+        </is>
+      </c>
+      <c r="I1001" s="2" t="inlineStr"/>
     </row>
     <row r="1002" ht="92.59999999999999" customHeight="1">
       <c r="A1002" s="2" t="n">
@@ -43532,8 +45082,14 @@
       <c r="G1002" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H1002" s="2" t="n"/>
-      <c r="I1002" s="2" t="n"/>
+      <c r="H1002" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+堆放磚、瓦、木塊或同類材料應距離開口部分 2 公尺以上。
+根據《營造安全衛生設施標準》第35條規定，雇主對於磚、瓦、木塊、管料、鋼筋、鋼材或相同及類似營建材料之堆放，儲存位置鄰近開口部分時，應距離該開口部分二公尺以上，且堆置高度不得超過 1.8 公尺。</t>
+        </is>
+      </c>
+      <c r="I1002" s="2" t="inlineStr"/>
     </row>
     <row r="1003" ht="92.59999999999999" customHeight="1">
       <c r="A1003" s="2" t="n">
@@ -43567,8 +45123,18 @@
       <c r="G1003" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H1003" s="2" t="n"/>
-      <c r="I1003" s="2" t="n"/>
+      <c r="H1003" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+防護網（覆網）下之最低點應離作業勞工工作平面 3 公尺以上。
+相關規定重點
+法規標準：依據《營造安全衛生設施標準》規定，覆網下之最低點應離作業勞工工作平面三公尺以上。
+不足時的處置：如果距離不足三公尺，則必須改以其他適當的防護設施來保障勞工安全。
+營造安全衛生設施標準 - 勞動部-所有條文
+二、覆網下之最低點應離作業勞工工作平面三公尺以上，如其距離不足三公尺，應改以其他設施防護。 三、覆網攔截之飛落物件應隨時清理。 四、覆網有劣化、破損、腐蝕等情況應 ...</t>
+        </is>
+      </c>
+      <c r="I1003" s="2" t="inlineStr"/>
     </row>
     <row r="1004" ht="108" customHeight="1">
       <c r="A1004" s="2" t="n">
@@ -43602,8 +45168,19 @@
       <c r="G1004" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H1004" s="2" t="n"/>
-      <c r="I1004" s="2" t="n"/>
+      <c r="H1004" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+研磨機之護罩應標示 磨輪直徑、圓週速度與轉動方向。
+詳細說明
+依據職業安全衛生相關法規與安衛考古題標準答案：
+研磨機的護罩上必須清楚標示適用之研磨輪相關安全限制與方向。
+應標示項目包含：磨輪直徑、圓週速度（最高使用周速度）以及轉動方向，以防止裝錯或超速運轉造成危險。
+其他選項如研磨輪材質、護罩尺寸、研磨輪顏色均非護罩規定應標示之項目。
+您可以在 查看此題目的詳細記錄。</t>
+        </is>
+      </c>
+      <c r="I1004" s="2" t="inlineStr"/>
     </row>
     <row r="1005" ht="92.59999999999999" customHeight="1">
       <c r="A1005" s="2" t="n">
@@ -43637,8 +45214,13 @@
       <c r="G1005" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H1005" s="2" t="n"/>
-      <c r="I1005" s="2" t="n"/>
+      <c r="H1005" s="2" t="inlineStr">
+        <is>
+          <t>研磨機每日作業前應試轉 1 分鐘以上。
+根據《職業安全衛生設施規則》第 62 條規定，研磨機使用應於每日作業開始前試轉 1 分鐘以上；若是更換研磨輪時，則應先檢驗有無裂痕，並在防護罩下試轉 3 分鐘以上。</t>
+        </is>
+      </c>
+      <c r="I1005" s="2" t="inlineStr"/>
     </row>
     <row r="1006" ht="92.59999999999999" customHeight="1">
       <c r="A1006" s="2" t="n">
@@ -43672,8 +45254,21 @@
       <c r="G1006" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H1006" s="2" t="n"/>
-      <c r="I1006" s="2" t="n"/>
+      <c r="H1006" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+研磨輪（砂輪）更換後須在防護罩下試轉 3 分鐘 以上。
+依據《職業安全衛生設施規則》第 62 條規定：
+每日作業開始前：應試轉 1 分鐘以上。
+更換研磨輪時：應先檢驗有無裂痕，並在防護罩下試轉 3 分鐘 以上。
+觀看關於研磨機防護與試轉規定的重點整理：
+3:16
+研磨機研磨輪輕鬆記｜liwei職安圖像筆記
+觀看次數：1.1萬 · 1 年前
+YouTube · liwei職業安全衛生圖像記憶筆記</t>
+        </is>
+      </c>
+      <c r="I1006" s="2" t="inlineStr"/>
     </row>
     <row r="1007" ht="92.59999999999999" customHeight="1">
       <c r="A1007" s="2" t="n">
@@ -43707,8 +45302,17 @@
       <c r="G1007" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1007" s="2" t="n"/>
-      <c r="I1007" s="2" t="n"/>
+      <c r="H1007" s="2" t="inlineStr">
+        <is>
+          <t>研磨機之研磨輪破裂損害屬物體飛落類型的災害。
+災害類型說明
+物體飛落：指以飛行物、落下物為主體碰觸到人的情形，包含研削物破裂、切斷片、切削粉飛來等。研磨輪高速旋轉破裂時，碎片會因慣性高速飛出並傷及人員，因此歸類在此項。
+物體破裂：指物體本身斷裂，但其碎塊或物體本身並未飛出造成撞擊。
+被撞：指人本身去撞擊或被靜態/一般物體撞擊。
+與有害物接觸：指人因接觸危險化學品或有害物質而受傷。</t>
+        </is>
+      </c>
+      <c r="I1007" s="2" t="inlineStr"/>
     </row>
     <row r="1008" ht="92.59999999999999" customHeight="1">
       <c r="A1008" s="2" t="n">
@@ -43734,8 +45338,13 @@
       <c r="G1008" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H1008" s="2" t="n"/>
-      <c r="I1008" s="2" t="n"/>
+      <c r="H1008" s="2" t="inlineStr">
+        <is>
+          <t>答案是 25。
+根據中華民國《職業安全衛生設施規則》第 84 條規定，雇主在施行旋轉輪機、離心分離機等高速回轉體之試驗時，若其週邊速率超越每秒 25 公尺以上，為了防止回轉體破裂發生危險，應於專用之堅固建築物內或以堅固之隔牆隔離之場所實施。</t>
+        </is>
+      </c>
+      <c r="I1008" s="2" t="inlineStr"/>
     </row>
     <row r="1009" ht="92.59999999999999" customHeight="1">
       <c r="A1009" s="2" t="n">
@@ -43769,8 +45378,17 @@
       <c r="G1009" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1009" s="2" t="n"/>
-      <c r="I1009" s="2" t="n"/>
+      <c r="H1009" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+電動研磨機之使用，應採取「以上皆是」之措施（答案為 (D)）。
+根據《職業安全衛生設施規則》第62條規定，雇主對於研磨機之使用應採取相關安全規定：
+不使用沒有防護罩之研磨機：研磨機應設置防護罩（護罩），以防止研磨輪破損飛散造成災害。
+研磨輪應採用經速率試驗合格者：研磨輪應採用經速率試驗合格且有明確記載最高使用周速度者。
+研磨機之使用不得超過最高使用周速度：規定研磨機之使用不得超過規定之最高使用周速度。</t>
+        </is>
+      </c>
+      <c r="I1009" s="2" t="inlineStr"/>
     </row>
     <row r="1010" ht="92.59999999999999" customHeight="1">
       <c r="A1010" s="2" t="n">
@@ -43796,8 +45414,17 @@
       <c r="G1010" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1010" s="2" t="n"/>
-      <c r="I1010" s="2" t="n"/>
+      <c r="H1010" s="2" t="inlineStr">
+        <is>
+          <t>進行研磨機研磨輪速率試驗時，應按最高使用周速度增加 50（百分之五十）為之。
+相關法規規定
+依據 職業安全衛生設施規則 第 62 條規定：
+速率試驗標準：研磨輪應採用經速率試驗合格且有明確記載最高使用周速度者，其速率試驗應按最高使用周速度增加百分之五十為之。
+豁免條件：直徑不滿十公分之研磨輪得免予速率試驗。
+日常試轉：每日作業開始前應試轉 1 分鐘以上，更換研磨輪時應先檢驗有無裂痕，並在防護罩下試轉 3 分鐘以上。</t>
+        </is>
+      </c>
+      <c r="I1010" s="2" t="inlineStr"/>
     </row>
     <row r="1011" ht="92.59999999999999" customHeight="1">
       <c r="A1011" s="2" t="n">
@@ -43831,8 +45458,19 @@
       <c r="G1011" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H1011" s="2" t="n"/>
-      <c r="I1011" s="2" t="n"/>
+      <c r="H1011" s="2" t="inlineStr">
+        <is>
+          <t>作業人員佩戴使用安全帶無法防止物體飛落災害發生，它是用來防止人員「墜落」的防護裝備。
+解析說明
+作業人員佩戴使用安全帶：屬於防止墜落災害的措施，當人員從高處不慎跌落時將其拉住，與物體從高處落下砸傷人的「飛落」災害無關。
+起重設備安全檢查：可確保起重機具結構安全，避免吊物墜落或設備崩塌引發飛落災害。
+使用吊具安全檢查：能確保鋼索、鉤環等吊掛工具沒有破損，防止吊掛物脫落。
+開口設置攔物用防護網：可直接阻擋或承接自開口處掉落的物體，防止其砸落下方人員。
+.下列那種設備措施，無法防止物體飛落災害發生?(A)作業人員 ...
+2024年5月14日 — 6.下列那種設備措施，無法防止物體飛落災害發生?(A)作業人員佩戴使用 安全帶(B)起重設備安全檢查(C)吊具安全檢查(D)開口設置攔物用防護網。， ...</t>
+        </is>
+      </c>
+      <c r="I1011" s="2" t="inlineStr"/>
     </row>
     <row r="1012" ht="108" customHeight="1">
       <c r="A1012" s="2" t="n">
@@ -43866,8 +45504,75 @@
       <c r="G1012" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H1012" s="2" t="n"/>
-      <c r="I1012" s="2" t="n"/>
+      <c r="H1012" s="2" t="inlineStr">
+        <is>
+          <t>，請稍後再試。
+網頁搜尋結果
+應有防止飛落作為，以下何者為非？ (A)安全移除 ...
+› item-1176.+工作場所有物體飛落之虞...
+2024年10月7日 — 1176. 工作場所有物體飛落之虞時，應有防止飛落作為，以下何者為非？ (A)安全移除可能飛落物體(B)供給勞工安全帽，並確實戴用(C)穿著背負式安全帶(D) ...
+缺少字詞： 注意 ‎人員 ‎區域 ‎反光 ‎施工
+營造業甲種職業安全衛生業務主管_參考題型1-50#103732 ...
+› item
+10.以下何者非工作場所有物體飛落之虞時應注意事項? (A) 供給勞工安全帽，並確實戴用. (B) 禁止人員進入物體飛落區域. (C) 作業人員應穿著有反光帶之施工背心. (D) 設置 ...
+第238 條
+› flaw › FLAWDOC01
+第238 條. 雇主對於工作場所有物體飛落之虞者，應設置防止物體飛落之設備，並供給安全帽等防護具，使勞工戴用。 法規類別. 全選; 行政函釋(0); 相關法條(0); 歷史法條(2) ...
+缺少字詞： 以下 ‎何者 ‎非 ‎時 ‎注意 ‎事項 ? ‎禁止 ‎人員 ‎進入 ‎區域 ‎作業 ‎穿著 ‎反光 ‎施工
+職業安全衛生設施規則第238條規定雇主對於工作場所有物體 ...
+Facebook · 勞動部
+超過 140 個回應 · 7 年前
+職業安全衛生設施規則第238條規定雇主對於工作場 所有物體飛落之虞者，應設置防止物體飛落之設備，並 供給安全帽等防護具，使勞工戴用。
+缺少字詞： 何者 ‎非 ‎禁止 ‎進入 ‎作業 ‎穿著 ‎反光 ‎施工
+職業安全衛生設施規則第238條規定雇主對於工作場所有物體飛 ...
+Facebook · 勞動部
+超過 140 個回應 · 7 年前
+0:50
+⚠職業安全衛生設施規則第238條規定雇主對於工作場 所有物體飛落之虞者，應設置防止物體飛落之設備，並 供給安全帽等防護具，使勞工戴用。 ... 勞動部以下.
+缺少字詞： 何者 ‎時 ‎注意 ‎禁止 ‎人員 ‎進入 ‎區域 ‎作業 ‎穿著 ‎反光 ‎施工
+職業安全衛生設施規則(民國115 年06 月30 日修正)
+› flaw › FLAWDAT0201
+... 虞時，應設置適當之滑槽、承受設備，並指派監視人員。 第238 條. 雇主對於工作場所有物體飛落之虞者，應設置防止物體飛落之設備，並供給安全帽等防護具，使勞工戴用。
+缺少字詞： 何者 ‎| 必須包含以下字詞： 何者
+4.下列何者不屬於局限空間作業之危害防止計畫應訂定事項? ...
+› item-4.下列何者不屬於局限空間作業...
+2021年11月8日 — ... 勞工安全帽，並確實戴用(C)穿著背負式安全帶(D)設置防止物體飛落設備. #2800361 · 10.以下何者非工作場所有物體飛落之虞時應注意事項? (A)供給勞工安全帽 ...
+〔營造業甲種〕職業安全衛生業務主管參考題型| PDF
+› document › 營造業甲種-職業...
+以下何者非工作場所有物體飛落之虞時應注意事項? ①供給勞工安全帽，並確實戴用② 禁止人員進入物體飛落區域③作業人員應穿著有反光帶之施工背心④設置攔截設備 (4)11 ...
+相關問題
+甲業跟乙安差在哪？
+在工地未戴安全帽會被罰款嗎?
+請問設規 177 條的內容是什麼?
+請問以下哪種情況下吊掛用鋼索不能作為起重機具的吊掛用具?
+網頁搜尋結果
+臺北市法規查詢系統
+臺北市政府全球資訊網
+› LawSearch › LawChapterArticle
+雇主對於從事地面下或隧道工程等作業，有物體飛落、有害物中毒、或缺氧危害之虞者；應使勞工確實使用安全帽，必要時應置備空氣呼吸器、氧氣呼吸器、防毒面具、防塵面具等 ...
+頁面導覽
+1
+2
+3
+4
+5
+6
+7
+8
+9
+10
+下一頁
+頁尾連結
+台灣
+708 臺南市安平區 - 根據你的 IP 位址
+- 更新位置
+說明
+提供意見
+隱私權
+服務條款</t>
+        </is>
+      </c>
+      <c r="I1012" s="2" t="inlineStr"/>
     </row>
     <row r="1013" ht="92.59999999999999" customHeight="1">
       <c r="A1013" s="2" t="n">
@@ -43901,8 +45606,12 @@
       <c r="G1013" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H1013" s="2" t="n"/>
-      <c r="I1013" s="2" t="n"/>
+      <c r="H1013" s="2" t="inlineStr">
+        <is>
+          <t>Google AI 摘要未抓取到，請手動補充。</t>
+        </is>
+      </c>
+      <c r="I1013" s="2" t="inlineStr"/>
     </row>
     <row r="1014" ht="92.59999999999999" customHeight="1">
       <c r="A1014" s="2" t="n">
@@ -43936,8 +45645,83 @@
       <c r="G1014" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1014" s="2" t="n"/>
-      <c r="I1014" s="2" t="n"/>
+      <c r="H1014" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+一般作業勞工戴用之安全帽多採用合成樹脂材質。
+合成樹脂（如 ABS、PE 等）具有輕量、耐衝擊且絕緣的特性，最適合一般工作環境防護使用。
+需要更多職業安全衛生相關考題或解答嗎？
+勞工安全衛生管理乙級考古題
+個人防護具法規與選用標準
+危害標示與通識規則
+顯示更多
+網頁搜尋結果
+1178. 一般作業勞工戴用之安全帽多採用何種材質？ (A)鋼鐵 ...
+› item-1178.+一般作業勞工戴用之安全...
+2024年10月7日 — 54. 一般作業勞工戴用之安全帽多採用何種材質？(A)鋼鐡(B)輕金屬(C)合成樹脂(D)橡膠。 ... 1184. 吊掛作業為防止荷件物飛落,下列措施何者有誤?(A)以最快速度 ...
+267. 一般作業勞工戴用之安全帽多採用何種材質？ (A) 鋼鐵 ...
+› item-267.+一般作業勞工戴用之安全...
+2025年7月9日 — 267. 一般作業勞工戴用之安全帽多採用何種材質？ (A) 鋼鐵(B) 輕金屬(C) 合成樹脂(D) 橡膠 ，包含題目內容、選項、詳解等，幫助學生提升學習效果。
+46. 一般作業勞工戴用之安全帽多採用何種材質？(A)鋼鐵(B) ...
+› item-46. 一般作業勞工戴用之安全帽...
+2015年1月11日 — 46. 一般作業勞工戴用之安全帽多採用何種材質？(A)鋼鐵(B)輕金屬(C)合成樹脂(D)橡膠。 ，包含題目內容、選項、詳解等，幫助學生提升學習效果。
+一般作業勞工戴用之安全帽多採用何種材質？
+職業安全衛生管理證照題庫練習
+› content › qbDetail
+一般作業勞工戴用之安全帽多採用何種材質？ 做記號. 242 / 472. A 鋼鐵; B 輕金屬; C 合成樹脂; D 橡膠. 答案：C 說明：目前帽體得材質有兩種，1.ESP(合成樹脂、保麗龍發泡 ...
+1 個答案
+·
+最佳解答:
+正確答案：C。目前帽體得材質有兩種，1.ESP(合成樹脂、保麗龍發泡體)、2.EPU(合成樹脂)
+222002-1安衛乙學1093(春)單詞卡
+Quizlet
+› 222002-1安衛乙學1093春-flash-c...
+①勞工背後腰帶②勞工前腹腰帶③勞工側邊腰帶④勞工衣領處。 4. 9.一般作業勞工戴用之安全帽多採用何種材質？①輕金屬②鋼鐵③合成樹脂④橡膠。 ... 作業人員應接受下列何種 ...
+相關問題
+一般作業勞工戴用的安全帽多採用什麼材質?
+勞工安全帽常用的材質有哪些?
+安全帽是什麼材質？
+安全帽有哪幾種分級?
+網頁搜尋結果
+附錄 3
+中華民國國防部- 全球資訊網
+› File
+PDF
+一般作業勞工戴用之安全帽多採用何種材質？ ①鋼鐵②輕金屬③橡膠④合成. 樹脂。 163. 依職業安全衛生教育訓練規則規定，新僱勞工所接受之一般安全衛生教育訓. 練，不得少 ...
+102 年度10300勞工安全衛生管理乙級 ...
+應用化學及材料科學系
+› var › file › img
+PDF
+46.(3)一般作業勞工戴用之安全帽多採用何種材質?①鋼鐵②輕金屬③合成樹脂④橡膠。 47.(3)皮膚燒傷至感覺消失,屬幾級燒傷?①1②2③3④4 。 48.(2)釐訂勞工安全衛生管理 ...
+4 頁
+42. 一般作業勞工戴用之安全帽多採用何種材質？(A)鋼鐵(B) ...
+› item-42.++一般作業勞工戴用之安全...
+2020年5月10日 — 一般作業勞工戴用之安全帽多採用何種材質？ (A)鋼鐵 (B)輕金屬 (C)橡膠 (D)合成樹脂。 答案：登入後查看 統計： A(3), B(25), C(111), D(1295), ...
+個人防護具
+wunan.com.tw
+› download › preview
+PDF
+一般作業勞工戴用之安全帽多採用何種材質？ （91-4）. 鋼鐵. 輕金屬. 合成樹脂 ... 防護具一般使用金屬、纖維、橡膠、皮革、合成樹脂等材料製造，因此，. 在 ...
+10 頁
+頁面導覽
+1
+2
+3
+4
+5
+6
+下一頁
+頁尾連結
+台灣
+708 臺南市安平區 - 根據你的 IP 位址
+- 更新位置
+說明
+提供意見
+隱私權
+服務條款</t>
+        </is>
+      </c>
+      <c r="I1014" s="2" t="inlineStr"/>
     </row>
     <row r="1015" ht="92.59999999999999" customHeight="1">
       <c r="A1015" s="2" t="n">
@@ -43971,8 +45755,19 @@
       <c r="G1015" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H1015" s="2" t="n"/>
-      <c r="I1015" s="2" t="n"/>
+      <c r="H1015" s="2" t="inlineStr">
+        <is>
+          <t>安全帽受過大衝擊，雖外觀良好，應採取的處理方式為廢棄。
+原因說明
+內部結構受損：安全帽吸收衝擊主要靠內部的緩衝材質（如保麗龍內襯），當承受過大撞擊後，內部結構可能已經碎裂或變形，失去再次吸收衝擊的能力。
+肉眼無法辨識：即使安全帽的外觀看起來完好無缺，內部的防護效能已經大幅降低，繼續使用將無法提供應有的安全保護。
+是否需要了解更多關於勞工安全衛生防護具或安全帽的正確使用與保存期限相關規定？
+職業安全衛生管理證照題庫練習
+安全帽受過大衝擊，雖外觀良好，應採下列何種處理方式？
+安全帽受過大衝擊，雖外觀良好，應採下列何種處理方式？ 做記號. 241 / 472. A 廢棄; B 繼續使用; C 送修; D 油漆保護. 答案：A 說明：安全帽受過大衝擊，雖外觀良好，但其 ... 內容</t>
+        </is>
+      </c>
+      <c r="I1015" s="2" t="inlineStr"/>
     </row>
     <row r="1016" ht="92.59999999999999" customHeight="1">
       <c r="A1016" s="2" t="n">
@@ -44006,8 +45801,15 @@
       <c r="G1016" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H1016" s="2" t="n"/>
-      <c r="I1016" s="2" t="n"/>
+      <c r="H1016" s="2" t="inlineStr">
+        <is>
+          <t>使用防塵眼鏡應優先確認鏡片有否裂傷、破損。
+原因說明
+維護視力安全：若鏡片帶有裂痕或破損，不僅無法有效阻擋微粒，更可能在遭受異物撞擊時碎裂，進而二次傷害眼睛。
+其他項目次之：遮光度、防氣體或阻絕輻射熱是針對特定工作環境（如焊接或化學作業）的需求，但在使用任何防護具前，檢查結構完整性與有無破損永遠是首要步驟。</t>
+        </is>
+      </c>
+      <c r="I1016" s="2" t="inlineStr"/>
     </row>
     <row r="1017" ht="92.59999999999999" customHeight="1">
       <c r="A1017" s="2" t="n">
@@ -44041,8 +45843,17 @@
       <c r="G1017" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1017" s="2" t="n"/>
-      <c r="I1017" s="2" t="n"/>
+      <c r="H1017" s="2" t="inlineStr">
+        <is>
+          <t>下列何者非為危害眼睛之因素的答案是 噪音。
+危害眼睛與耳朵之因素說明
+飛濺之粒子：屬於物理性危害，容易直接擊中或刮傷眼角膜。
+熔融金屬：高溫液態金屬飛濺會造成嚴重的眼睛灼傷。
+有害光線：如強烈紫外線或紅外線，會對視網膜與角膜造成慢性或急性傷害。
+噪音：屬於聽覺系統的危害因子，主要危害的是耳朵而非眼睛。</t>
+        </is>
+      </c>
+      <c r="I1017" s="2" t="inlineStr"/>
     </row>
     <row r="1018" ht="92.59999999999999" customHeight="1">
       <c r="A1018" s="2" t="n">
@@ -44076,8 +45887,13 @@
       <c r="G1018" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1018" s="2" t="n"/>
-      <c r="I1018" s="2" t="n"/>
+      <c r="H1018" s="2" t="inlineStr">
+        <is>
+          <t>安全眼鏡應有的構造為(D) 側護片。
+安全眼鏡（或稱護目鏡）為了防止異物、飛屑或化學液體從側邊飛入或濺入眼睛，設計上必須具備側邊防護功能，因此應有側護片構造。</t>
+        </is>
+      </c>
+      <c r="I1018" s="2" t="inlineStr"/>
     </row>
     <row r="1019" ht="77.15000000000001" customHeight="1">
       <c r="A1019" s="2" t="n">
@@ -44103,8 +45919,17 @@
       <c r="G1019" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H1019" s="2" t="n"/>
-      <c r="I1019" s="2" t="n"/>
+      <c r="H1019" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+依法令規定，荷重1.5公噸堆高機之頂蓬，至少應足以承受 3 公噸之重量（即最大荷重之2倍）。正確答案為 3。
+法規重點
+計算方式：依據《機械設備器具安全標準》規定，堆高機頂蓬強度應足以承受最大荷重之 2倍 之值等分布靜荷重。
+上限規定：該等分布靜荷重之值若超過4公噸，則以 4公噸 為限。
+本題計算：1.5公噸 × 2 = 3公噸（未超過4公噸），因此至少需承受 3 公噸。</t>
+        </is>
+      </c>
+      <c r="I1019" s="2" t="inlineStr"/>
     </row>
     <row r="1020" ht="92.59999999999999" customHeight="1">
       <c r="A1020" s="2" t="n">
@@ -44138,8 +45963,16 @@
       <c r="G1020" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H1020" s="2" t="n"/>
-      <c r="I1020" s="2" t="n"/>
+      <c r="H1020" s="2" t="inlineStr">
+        <is>
+          <t>正確答案為 (C) 佩戴安全帽。
+詳細說明
+佩戴安全帽屬於個人防護具（PPE），是在發生意外時減少頭部傷害的防護措施，無法預防石材板本身倒塌。
+設置擋樁、以繩索捆綁皆為防止物料倒塌、崩塌或掉落之直接物理預防設施（依據勞工職業安全衛生相關規定）。
+實施環境巡查有助於及早發現堆置異常或安全隱患，屬於預防管理方法。</t>
+        </is>
+      </c>
+      <c r="I1020" s="2" t="inlineStr"/>
     </row>
     <row r="1021" ht="92.59999999999999" customHeight="1">
       <c r="A1021" s="2" t="n">
@@ -44165,8 +45998,13 @@
       <c r="G1021" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H1021" s="2" t="n"/>
-      <c r="I1021" s="2" t="n"/>
+      <c r="H1021" s="2" t="inlineStr">
+        <is>
+          <t>對於置放於高處且有飛落之虞的物件，位能超過 12 公斤·公尺者，應予以固定。因此正確選項為 12。
+依據營造安全衛生設施標準第26條規定：「雇主對於置放於高處，位能超過十二公斤‧公尺之物件有飛落之虞者，應予以固定之。」</t>
+        </is>
+      </c>
+      <c r="I1021" s="2" t="inlineStr"/>
     </row>
     <row r="1022" ht="92.59999999999999" customHeight="1">
       <c r="A1022" s="2" t="n">
@@ -44200,8 +46038,17 @@
       <c r="G1022" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1022" s="2" t="n"/>
-      <c r="I1022" s="2" t="n"/>
+      <c r="H1022" s="2" t="inlineStr">
+        <is>
+          <t>正確答案是 75 公斤。
+相關法規規定
+依據 營造安全衛生設施標準第 27 條 規定：
+雇主設置覆網攔截位能小於 12 公斤‧公尺之高處物件時，方形、菱形之網目任一邊長不得大於 2 公分。
+其餘形狀之網目，每一網目不得大於 4 平方公分。
+其強度應能承受直徑 45 公分、重 75 公斤之物體自高度 1 公尺處落下之衝擊力。</t>
+        </is>
+      </c>
+      <c r="I1022" s="2" t="inlineStr"/>
     </row>
     <row r="1023" ht="92.59999999999999" customHeight="1">
       <c r="A1023" s="2" t="n">
@@ -44235,8 +46082,17 @@
       <c r="G1023" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H1023" s="2" t="n"/>
-      <c r="I1023" s="2" t="n"/>
+      <c r="H1023" s="2" t="inlineStr">
+        <is>
+          <t>這題的正確答案是 12 公斤（即 12 公斤．公尺）。
+💡 法規依據與說明
+根據台灣的《營造安全衛生設施標準》相關規定：
+固定措施： 雇主對於置放於高處，位能超過 12 公斤．公尺且有飛落之虞的物件，應予以固定。
+攔截措施： 雇主設置覆網攔截位能小於 12 公斤．公尺之高處物件時，應依規定辦理（如網目大小、防護高度等）。
+因此，本題答案應選 12 公斤。</t>
+        </is>
+      </c>
+      <c r="I1023" s="2" t="inlineStr"/>
     </row>
     <row r="1024" ht="92.59999999999999" customHeight="1">
       <c r="A1024" s="2" t="n">
@@ -44270,8 +46126,13 @@
       <c r="G1024" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H1024" s="2" t="n"/>
-      <c r="I1024" s="2" t="n"/>
+      <c r="H1024" s="2" t="inlineStr">
+        <is>
+          <t>覆網下之最低點應離作業勞工工作平面 3 公尺以上。
+根據《營造安全衛生設施標準》第 27 條規定，雇主設置覆網攔截高處物件時，覆網下之最低點應離作業勞工工作平面在 3 公尺以上；如距離不足 3 公尺，則應改以其他設施進行防護。因此正確答案為 3 公尺。</t>
+        </is>
+      </c>
+      <c r="I1024" s="2" t="inlineStr"/>
     </row>
     <row r="1025" ht="92.59999999999999" customHeight="1">
       <c r="A1025" s="2" t="n">
@@ -44305,8 +46166,15 @@
       <c r="G1025" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H1025" s="2" t="n"/>
-      <c r="I1025" s="2" t="n"/>
+      <c r="H1025" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+「以繩索綑綁物料堆置高度可無限制」是有誤的防護措施。
+正確法規依據
+依據《職業安全衛生設施規則》第 153 條規定，對於搬運、堆放或處置物料，為防止倒塌、崩塌或掉落，應採取繩索捆綁、護網、擋樁、限制高度或變更堆積等必要設施，並禁止與作業無關人員進入該等場所。因此物料堆置高度必須有所限制，不可無限制堆疊。</t>
+        </is>
+      </c>
+      <c r="I1025" s="2" t="inlineStr"/>
     </row>
     <row r="1026" ht="108" customHeight="1">
       <c r="A1026" s="2" t="n">
@@ -44340,8 +46208,18 @@
       <c r="G1026" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H1026" s="2" t="n"/>
-      <c r="I1026" s="2" t="n"/>
+      <c r="H1026" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+錯誤的選項是：從事載貨台裝卸貨物其高差在 2 公尺以上者，才需提供勞工安全上下之設備。
+正確法規說明
+高差標準：依據《職業安全衛生設施規則》第166條規定，雇主對於勞工從事載貨台裝卸貨物，其高差在 1.5公尺以上者，就應提供勞工安全上下之設備，而非 2 公尺。
+其他選項：
+纖維纜繩已斷一股子索者，不得使用（符合規定）。
+物料處置時不得影響照明、不得阻礙交通（皆為正確之安全衛生規定）。</t>
+        </is>
+      </c>
+      <c r="I1026" s="2" t="inlineStr"/>
     </row>
     <row r="1027" ht="77.15000000000001" customHeight="1">
       <c r="A1027" s="2" t="n">
@@ -44375,8 +46253,15 @@
       <c r="G1027" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H1027" s="2" t="n"/>
-      <c r="I1027" s="2" t="n"/>
+      <c r="H1027" s="2" t="inlineStr">
+        <is>
+          <t>(C) 機械器具型式檢定
+說明
+依危害性化學品標示及通識規則規定，應採取之措施包含：危害物質（化學品）標示、製備安全資料表（SDS）、訂定危害通識計畫及化學品清單、教育訓練等。
+機械器具型式檢定屬於職業安全衛生法規中針對特定機械設備（如壓床、起重機、防爆電氣等）的安全檢定規範，與化學品標示及通識規則無關。</t>
+        </is>
+      </c>
+      <c r="I1027" s="2" t="inlineStr"/>
     </row>
     <row r="1028" ht="77.15000000000001" customHeight="1">
       <c r="A1028" s="2" t="n">
@@ -44410,8 +46295,17 @@
       <c r="G1028" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H1028" s="2" t="n"/>
-      <c r="I1028" s="2" t="n"/>
+      <c r="H1028" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+依危害性化學品標示及通識規則及GHS分類規定，禁水性物質之危害圖式符號為火焰。
+國立嘉義大學 相關說明
+危害圖式符號：火焰
+對應危害：與水作用後，可具有自燃性或產生危險量易燃氣體的物質或混合物。
+輔仁大學</t>
+        </is>
+      </c>
+      <c r="I1028" s="2" t="inlineStr"/>
     </row>
     <row r="1029" ht="77.15000000000001" customHeight="1">
       <c r="A1029" s="2" t="n">
@@ -44445,8 +46339,17 @@
       <c r="G1029" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H1029" s="2" t="n"/>
-      <c r="I1029" s="2" t="n"/>
+      <c r="H1029" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+依「危害性化學品標示及通識規則」之規定，氧化性固體之危害圖式符號為圓圈上一團火焰。
+危害圖式說明
+正確答案：(D) 圓圈上一團火焰
+代表意義：表示該化學品具有氧化性（包含氧化性氣體、氧化性液體及氧化性固體），可能會引發或加劇火災、爆炸。
+輔仁大學</t>
+        </is>
+      </c>
+      <c r="I1029" s="2" t="inlineStr"/>
     </row>
     <row r="1030" ht="77.15000000000001" customHeight="1">
       <c r="A1030" s="2" t="n">
@@ -44480,8 +46383,15 @@
       <c r="G1030" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H1030" s="2" t="n"/>
-      <c r="I1030" s="2" t="n"/>
+      <c r="H1030" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+依據危害性化學品標示及通識規則之規定，骷髏頭與二根交叉骨之圖式符號代表為急毒性物質。
+骷顱頭與二根交叉骨之圖式符號代表為何？ (A)急毒性物質(B ...
+2020年1月21日 — 73.依危害性化學品標示及通識規則之規定，骷顱頭與兩根交叉骨之圖式符號代表為何？(A)急毒性 物質(B)生殖毒性物質(C)金屬腐蝕物(D)致癌物質。 #3161052.</t>
+        </is>
+      </c>
+      <c r="I1030" s="2" t="inlineStr"/>
     </row>
     <row r="1031" ht="77.15000000000001" customHeight="1">
       <c r="A1031" s="2" t="n">
@@ -44515,8 +46425,16 @@
       <c r="G1031" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1031" s="2" t="n"/>
-      <c r="I1031" s="2" t="n"/>
+      <c r="H1031" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+依危害性化學品標示及通識規則規定，致癌物質之危害圖式為(D)人頭及胸腔。
+相關重點整理
+危害圖式：人頭及胸腔（健康危害圖示，包含呼吸道過敏原、生殖細胞致突變性、致癌物質、生殖毒性、標的器官系統毒性等）。
+圖式外形：直立四十五度角之正方形（菱形），紅框、白底、黑色符號。</t>
+        </is>
+      </c>
+      <c r="I1031" s="2" t="inlineStr"/>
     </row>
     <row r="1032" ht="77.15000000000001" customHeight="1">
       <c r="A1032" s="2" t="n">
@@ -44550,8 +46468,24 @@
       <c r="G1032" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H1032" s="2" t="n"/>
-      <c r="I1032" s="2" t="n"/>
+      <c r="H1032" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+依「危害性化學品標示及通識規則」第5條規定，用途說明非屬危害性化學品容器應標示之內容。
+國立臺灣師範大學－環境安全衛生中心 應標示之法定事項
+容器上應明顯標示下列事項：
+國立臺灣師範大學－環境安全衛生中心
+危害圖式
+名稱
+危害成分
+警示語
+危害警告訊息
+危害防範措施
+製造者、輸入者或供應者之名稱、地址及電話
+國立臺灣師範大學－環境安全衛生中心</t>
+        </is>
+      </c>
+      <c r="I1032" s="2" t="inlineStr"/>
     </row>
     <row r="1033" ht="77.15000000000001" customHeight="1">
       <c r="A1033" s="2" t="n">
@@ -44585,8 +46519,16 @@
       <c r="G1033" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1033" s="2" t="n"/>
-      <c r="I1033" s="2" t="n"/>
+      <c r="H1033" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+訂定作業環境監測計畫非屬危害性化學品標示及通識規則規定應採取之措施。
+說明
+危害性化學品標示及通識規則規範的重點為化學品容器標示、製備安全資料表（SDS）與清單、以及訂定危害通識計畫與教育訓練等。
+作業環境監測計畫是依據《勞動作業場所容許暴露標準》及《勞工作業環境監測實施辦法》等相關規定辦理，不屬於危害性化學品標示及通識規則的規範範圍。</t>
+        </is>
+      </c>
+      <c r="I1033" s="2" t="inlineStr"/>
     </row>
     <row r="1034" ht="77.15000000000001" customHeight="1">
       <c r="A1034" s="2" t="n">

--- a/salf/丙種職業安全衛生業務主管題庫.xlsx
+++ b/salf/丙種職業安全衛生業務主管題庫.xlsx
@@ -46562,8 +46562,13 @@
       <c r="G1034" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H1034" s="2" t="n"/>
-      <c r="I1034" s="2" t="n"/>
+      <c r="H1034" s="2" t="inlineStr">
+        <is>
+          <t>依危害性化學品標示及通識規則之規定，容器之容積在 100 毫升以下者，得僅標示名稱、危害圖式及警示語。
+正確選項為：100 毫升。</t>
+        </is>
+      </c>
+      <c r="I1034" s="2" t="inlineStr"/>
     </row>
     <row r="1035" ht="108" customHeight="1">
       <c r="A1035" s="2" t="n">
@@ -46597,8 +46602,12 @@
       <c r="G1035" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H1035" s="2" t="n"/>
-      <c r="I1035" s="2" t="n"/>
+      <c r="H1035" s="2" t="inlineStr">
+        <is>
+          <t>Google AI 摘要未抓取到，請手動補充。</t>
+        </is>
+      </c>
+      <c r="I1035" s="2" t="inlineStr"/>
     </row>
     <row r="1036" ht="77.15000000000001" customHeight="1">
       <c r="A1036" s="2" t="n">
@@ -46632,8 +46641,14 @@
       <c r="G1036" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H1036" s="2" t="n"/>
-      <c r="I1036" s="2" t="n"/>
+      <c r="H1036" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+正確答案為：白底、黑色圖式符號、紅框。
+依據《危害性化學品標示及通識規則》第7條規定，危害圖式的形狀為直立四十五度角之正方形，其圖式符號應使用黑色，背景為白色，且圖式須具有足夠警示作用寬度的紅框。</t>
+        </is>
+      </c>
+      <c r="I1036" s="2" t="inlineStr"/>
     </row>
     <row r="1037" ht="77.15000000000001" customHeight="1">
       <c r="A1037" s="2" t="n">
@@ -46667,8 +46682,17 @@
       <c r="G1037" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H1037" s="2" t="n"/>
-      <c r="I1037" s="2" t="n"/>
+      <c r="H1037" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+依據危害性化學品標示及通識規則第7條規定，危害圖式之形狀為直立 45 度角之正方形（即菱形）。
+標示相關規定要點
+形狀：直立 45 度角之正方形。
+顏色配置：圖式符號為黑色，背景為白色，外框為具有足夠警示作用寬度的紅色。
+大小：需能辨識清楚。</t>
+        </is>
+      </c>
+      <c r="I1037" s="2" t="inlineStr"/>
     </row>
     <row r="1038" ht="77.15000000000001" customHeight="1">
       <c r="A1038" s="2" t="n">
@@ -46694,8 +46718,16 @@
       <c r="G1038" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1038" s="2" t="n"/>
-      <c r="I1038" s="2" t="n"/>
+      <c r="H1038" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+安全資料表（SDS）應列內容項目共分為 16 大項。
+說明
+依據《危害性化學品標示及通識規則》及聯合國 GHS 標準，安全資料表必須包含固定順序的 16 大章節內容，不得任意刪減或合併。
+帷鈊檢驗科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="I1038" s="2" t="inlineStr"/>
     </row>
     <row r="1039" ht="77.15000000000001" customHeight="1">
       <c r="A1039" s="2" t="n">
@@ -46729,8 +46761,16 @@
       <c r="G1039" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H1039" s="2" t="n"/>
-      <c r="I1039" s="2" t="n"/>
+      <c r="H1039" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+依據《危害性化學品標示及通識規則》之規定，危害性化學品分為危險物或有害物，是依據國家標準 CNS15030。
+相關定義說明
+危險物：符合國家標準 CNS15030 分類，具有物理性危害者。
+有害物：符合國家標準 CNS15030 分類，具有健康危害者。</t>
+        </is>
+      </c>
+      <c r="I1039" s="2" t="inlineStr"/>
     </row>
     <row r="1040" ht="77.15000000000001" customHeight="1">
       <c r="A1040" s="2" t="n">
@@ -46764,8 +46804,14 @@
       <c r="G1040" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1040" s="2" t="n"/>
-      <c r="I1040" s="2" t="n"/>
+      <c r="H1040" s="2" t="inlineStr">
+        <is>
+          <t>依據危害性化學品標示及通識規則第3條第2款之規定，答案為以上皆是（即包含袋、筒、瓶、箱、罐、桶、反應器、儲槽、管路及其他可盛裝危害性化學品者）。
+相關法規依據
+名詞定義：「容器」指任何袋、筒、瓶、箱、罐、桶、反應器、儲槽、管路及其他可盛裝危害性化學品者。</t>
+        </is>
+      </c>
+      <c r="I1040" s="2" t="inlineStr"/>
     </row>
     <row r="1041" ht="92.59999999999999" customHeight="1">
       <c r="A1041" s="2" t="n">
@@ -46799,8 +46845,16 @@
       <c r="G1041" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1041" s="2" t="n"/>
-      <c r="I1041" s="2" t="n"/>
+      <c r="H1041" s="2" t="inlineStr">
+        <is>
+          <t>食品與飲料等物品不須檢附安全資料表（物質安全資料表），即可買賣與飲用。
+說明
+必須標示的項目：依據《食品安全衛生管理法》，市售包裝食品與飲料依法皆須標示成分（內容物）、有效期限等重要資訊，以保障消費者的飲食衛生與安全。
+安全資料表：這是化學品或工業用危險物質（如實驗室藥品、危害性化學品）專用的文件（SDS / MSDS），食品與飲料並不適用此規定。
+展榮商號</t>
+        </is>
+      </c>
+      <c r="I1041" s="2" t="inlineStr"/>
     </row>
     <row r="1042" ht="77.15000000000001" customHeight="1">
       <c r="A1042" s="2" t="n">
@@ -46834,8 +46888,17 @@
       <c r="G1042" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1042" s="2" t="n"/>
-      <c r="I1042" s="2" t="n"/>
+      <c r="H1042" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+依「危害性化學品標示及通識規則」第15條規定，關於安全資料表（SDS）內容之正確性，最適當的選項為每三年檢討（應依實際狀況適時更新，並至少每三年檢討一次）。
+勞動部職業安全衛生署 根據法規重點：
+檢討頻率：至少每3年檢討1次，並應依實際狀況適時更新。
+紀錄保存：更新之內容、日期、版次等相關紀錄應保存3年。
+勞動部職業安全衛生署</t>
+        </is>
+      </c>
+      <c r="I1042" s="2" t="inlineStr"/>
     </row>
     <row r="1043" ht="77.15000000000001" customHeight="1">
       <c r="A1043" s="2" t="n">
@@ -46869,8 +46932,12 @@
       <c r="G1043" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H1043" s="2" t="n"/>
-      <c r="I1043" s="2" t="n"/>
+      <c r="H1043" s="2" t="inlineStr">
+        <is>
+          <t>Google AI 摘要未抓取到，請手動補充。</t>
+        </is>
+      </c>
+      <c r="I1043" s="2" t="inlineStr"/>
     </row>
     <row r="1044" ht="77.15000000000001" customHeight="1">
       <c r="A1044" s="2" t="n">
@@ -46904,8 +46971,16 @@
       <c r="G1044" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H1044" s="2" t="n"/>
-      <c r="I1044" s="2" t="n"/>
+      <c r="H1044" s="2" t="inlineStr">
+        <is>
+          <t>製造商及供應商提供安全資料表給事業單位，是屬於義務性質（選項 A）。
+詳細說明
+法規要求：依據《危害性化學品標示及通識規則》規定，製造者、輸入者或供應者在提供危害性化學品給事業單位或自營作業者前，應予標示及提供安全資料表 (SDS)。
+性質判定：這是法律規定的強制性責任，因此屬於法律上的「義務」，而非權利、個人道德或選擇性行為。
+國立臺中科技大學</t>
+        </is>
+      </c>
+      <c r="I1044" s="2" t="inlineStr"/>
     </row>
     <row r="1045" ht="77.15000000000001" customHeight="1">
       <c r="A1045" s="2" t="n">
@@ -46939,8 +47014,18 @@
       <c r="G1045" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1045" s="2" t="n"/>
-      <c r="I1045" s="2" t="n"/>
+      <c r="H1045" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+環境監測是非必要直接歸類在職安法第10條針對具有危害性化學品通識規定的直接預設第一線強制措施（標示、製備清單及揭示安全資料表）。
+依據《職業安全衛生法》第10條規定，雇主對於具有危害性之化學品，應採取下列必要措施：
+標示
+製備化學品清單
+揭示物質安全資料表（安全資料表，SDS）
+因此，選項中「環境監測」雖在特定作業環境或存有特定有害物質時另有規定需要實施，但並非第10條通識規範中針對所有具有危害性化學品「直接要求標示/製備清單/揭示」的同一範疇必要直接措施。</t>
+        </is>
+      </c>
+      <c r="I1045" s="2" t="inlineStr"/>
     </row>
     <row r="1046" ht="77.15000000000001" customHeight="1">
       <c r="A1046" s="2" t="n">
@@ -46974,8 +47059,18 @@
       <c r="G1046" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1046" s="2" t="n"/>
-      <c r="I1046" s="2" t="n"/>
+      <c r="H1046" s="2" t="inlineStr">
+        <is>
+          <t>環境照明最不可能是影響化學性危害的因素。
+Quizlet
+影響化學性危害的關鍵因素
+毒性物質本身的毒性：物質本身的化學性質與對人體的毒性強弱決定了危害的根本程度。
+毒性物質的濃度：劑量決定毒性，濃度越高通常對人體的危害越大。
+暴露途徑：如吸入、皮膚接觸或食入等，會影響毒物進入人體的效率與器官反應。
+國家環境毒物研究中心</t>
+        </is>
+      </c>
+      <c r="I1046" s="2" t="inlineStr"/>
     </row>
     <row r="1047" ht="92.59999999999999" customHeight="1">
       <c r="A1047" s="2" t="n">
@@ -47009,8 +47104,12 @@
       <c r="G1047" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H1047" s="2" t="n"/>
-      <c r="I1047" s="2" t="n"/>
+      <c r="H1047" s="2" t="inlineStr">
+        <is>
+          <t>Google AI 摘要未抓取到，請手動補充。</t>
+        </is>
+      </c>
+      <c r="I1047" s="2" t="inlineStr"/>
     </row>
     <row r="1048" ht="92.59999999999999" customHeight="1">
       <c r="A1048" s="2" t="n">
@@ -47044,8 +47143,18 @@
       <c r="G1048" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1048" s="2" t="n"/>
-      <c r="I1048" s="2" t="n"/>
+      <c r="H1048" s="2" t="inlineStr">
+        <is>
+          <t>有誤的敘述是 「中毒後絕對不會有後遺症」（選項 D）。
+原因解析
+無色無味：一氧化碳（CO）是一種無色、無味的氣體，極難被人體察覺。
+與血色素親合力比氧氣強：它與血紅素（血色素）的親和力比氧氣高出約 200 到 300 倍。
+會造成組織缺氧：它會優先搶佔血紅素形成碳氧血紅素，導致氧氣無法運送，進而使全身組織與器官嚴重缺氧。
+中毒後會有後遺症：嚴重的一氧化碳中毒可能會留下神經學或精神方面的後遺症（如記憶力減退、遲發性腦病變等），並非「絕對不會有後遺症」。
+榮民總醫院</t>
+        </is>
+      </c>
+      <c r="I1048" s="2" t="inlineStr"/>
     </row>
     <row r="1049" ht="92.59999999999999" customHeight="1">
       <c r="A1049" s="2" t="n">
@@ -47079,8 +47188,27 @@
       <c r="G1049" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H1049" s="2" t="n"/>
-      <c r="I1049" s="2" t="n"/>
+      <c r="H1049" s="2" t="inlineStr">
+        <is>
+          <t>下列何者為窒息性物質？正確答案是 (A) 氮氣。
+解析
+氮氣（
+N
+2
+𝐍
+𝟐
+）：屬於單純性窒息性物質。它本身無毒或毒性極低，但在密閉或通風不良的空間中，若大量存在會排擠並稀釋空氣中的氧氣濃度，導致人體因缺氧而窒息。
+正己醇：屬於有機溶劑/醇類化學物質，具刺激性或麻醉性，非窒息性物質。
+三氯乙烯：屬於氯化烴類有機溶劑，主要具麻醉性與肝腎毒性。
+氧氣（
+O
+2
+𝐎
+𝟐
+）：維持生命必需之氣體，非窒息性物質。</t>
+        </is>
+      </c>
+      <c r="I1049" s="2" t="inlineStr"/>
     </row>
     <row r="1050" ht="92.59999999999999" customHeight="1">
       <c r="A1050" s="2" t="n">
@@ -47114,8 +47242,18 @@
       <c r="G1050" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H1050" s="2" t="n"/>
-      <c r="I1050" s="2" t="n"/>
+      <c r="H1050" s="2" t="inlineStr">
+        <is>
+          <t>雇主使勞工從事有機溶劑作業時，應使該勞工就其作業有關事項實施檢點。
+依據《職業安全衛生設施規則》（或相關職業安全衛生管理法規）規定，有害物作業相關之作業檢點包含：
+有機溶劑作業
+鉛作業
+四烷基鉛作業
+特定化學物質作業
+粉塵作業</t>
+        </is>
+      </c>
+      <c r="I1050" s="2" t="inlineStr"/>
     </row>
     <row r="1051" ht="92.59999999999999" customHeight="1">
       <c r="A1051" s="2" t="n">
@@ -47149,8 +47287,16 @@
       <c r="G1051" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H1051" s="2" t="n"/>
-      <c r="I1051" s="2" t="n"/>
+      <c r="H1051" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+答案是：局部排氣。
+解析與法規說明
+法規依據：依據《有機溶劑中毒預防規則》第6條規定，於室內作業場所或儲槽等之作業場所，從事第一種有機溶劑或其混存物之作業時，應設置密閉設備或局部排氣裝置。
+原因：第一種有機溶劑的毒性較強、危害風險高，整體換氣、自然換氣或溫差換氣的效果不足以在有害物擴散前有效收集並排出，因此規定必須使用防護效果較佳的局部排氣（或密閉設備）。</t>
+        </is>
+      </c>
+      <c r="I1051" s="2" t="inlineStr"/>
     </row>
     <row r="1052" ht="77.15000000000001" customHeight="1">
       <c r="A1052" s="2" t="n">
@@ -47184,8 +47330,27 @@
       <c r="G1052" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1052" s="2" t="n"/>
-      <c r="I1052" s="2" t="n"/>
+      <c r="H1052" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+甲醇非屬可燃性氣體。
+詳細說明
+甲醇（
+𝐶
+𝐻
+3
+𝑂
+𝐻
+𝐶
+𝐻
+3
+𝑂
+𝐻
+）在常溫常壓下是液體（易燃液體），而不是氣體。
+氫氣、乙炔與甲烷在常溫常壓下皆為氣體，且屬於法規定義的可燃性氣體。</t>
+        </is>
+      </c>
+      <c r="I1052" s="2" t="inlineStr"/>
     </row>
     <row r="1053" ht="77.15000000000001" customHeight="1">
       <c r="A1053" s="2" t="n">
@@ -47219,8 +47384,20 @@
       <c r="G1053" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H1053" s="2" t="n"/>
-      <c r="I1053" s="2" t="n"/>
+      <c r="H1053" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+乙醚非屬可燃性氣體。
+詳細說明
+依照中華民國《職業安全衛生設施規則》第15條規定，可燃性氣體包含：
+氫
+乙炔、乙烯
+甲烷、乙烷、丙烷、丁烷
+其他於一大氣壓、攝氏15度具可燃性之氣體
+選項中的氫氣、乙炔與丙烷都屬於可燃性氣體；而乙醚常溫下為液體（易燃液體），其蒸氣雖具燃燒危險，但在法規定義中它不屬於可燃性「氣體」。</t>
+        </is>
+      </c>
+      <c r="I1053" s="2" t="inlineStr"/>
     </row>
     <row r="1054" ht="77.15000000000001" customHeight="1">
       <c r="A1054" s="2" t="n">
@@ -47254,8 +47431,18 @@
       <c r="G1054" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1054" s="2" t="n"/>
-      <c r="I1054" s="2" t="n"/>
+      <c r="H1054" s="2" t="inlineStr">
+        <is>
+          <t>對於防止化學品引起之職業災害，應列為最優先考量的措施是尋求無害之替代物（選項 D）。
+職業安全衛生危害控制原則
+源頭管理（第一優先）： 尋求無害之替代物或減害物質，從根本消除或降低化學品的危害風險。
+工程控制： 採用密閉、隔離、局部排氣等設施減少暴露。
+管理控制： 進行作業檢點、教育訓練與標示。
+個人防護具（最後防線）： 使用防護衣、防護面罩或呼吸器等，為保護勞工的最後一線防護。
+Quizlet</t>
+        </is>
+      </c>
+      <c r="I1054" s="2" t="inlineStr"/>
     </row>
     <row r="1055" ht="92.59999999999999" customHeight="1">
       <c r="A1055" s="2" t="n">

--- a/salf/丙種職業安全衛生業務主管題庫.xlsx
+++ b/salf/丙種職業安全衛生業務主管題庫.xlsx
@@ -47476,8 +47476,24 @@
       <c r="G1055" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H1055" s="2" t="n"/>
-      <c r="I1055" s="2" t="n"/>
+      <c r="H1055" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+正確答案：(B) 游離二氧化矽
+解析說明
+游離二氧化矽（Free Silica / Crystalline Silica）：
+吸入肺部後會被肺泡巨噬細胞吞噬，但巨噬細胞無法將其分解，反而會釋出毒性物質與發炎因子，進而刺激纖維母細胞增生，最終導致矽肺症（Silicosis）與嚴重的肺部纖維化。
+其他選項之影響：
+鉛：主要造成神經系統、造血系統及腎臟等全身性中毒（鉛中毒），較不以肺部纖維化為主要病變。
+氧化鐵：長期吸入會造成良性塵肺症（鐵沉著症，Siderosis），通常不會引起明顯的肺部纖維化。
+石膏：屬於相對惰性的粉塵，吸入後引起的組織反應極為輕微，一般不會導致顯著的肺纖維化。
+職業安全衛生管理證照題庫練習
+以下何者被吸入人體，較可能會導致肺部纖維化？
+以下何者被吸入人體，較可能會導致肺部纖維化？ 做記號. 202 / 472. A 鉛; B 游離二氧化矽; C 氧化鐵; D 石膏. 答案：B 說明：結晶型游離二氧化矽可能引起之疾病，矽肺 ...
+這項資訊僅供參考，如需醫療建議或診斷，請諮詢專業人士。AI 回覆可能有誤。 瞭解詳情</t>
+        </is>
+      </c>
+      <c r="I1055" s="2" t="inlineStr"/>
     </row>
     <row r="1056" ht="92.59999999999999" customHeight="1">
       <c r="A1056" s="2" t="n">
@@ -47511,8 +47527,20 @@
       <c r="G1056" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H1056" s="2" t="n"/>
-      <c r="I1056" s="2" t="n"/>
+      <c r="H1056" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+鍍鉻作業易使勞工暴露於鉻酸霧滴，易造成鼻中膈穿孔。
+疾病說明與危害
+鼻中膈穿孔：長期吸入具腐蝕性的六價鉻酸霧滴，會破壞鼻腔黏膜，導致發炎、潰瘍，嚴重時會造成鼻中膈軟骨穿孔。
+NTNU
+其他選項：
+青光眼：眼壓升高疾病，與鉻酸霧滴暴露無直接因果關係。
+白指症：又稱雷諾氏現象，通常因長期使用震動工具（如鏈鋸、氣動鎚）引起局部血液循環障礙。
+白內障：水晶體混濁疾病，常見於長期暴露於紅外線、強光或特定化學/物理因子，而非鍍鉻霧滴的主要特異性病變。</t>
+        </is>
+      </c>
+      <c r="I1056" s="2" t="inlineStr"/>
     </row>
     <row r="1057" ht="92.59999999999999" customHeight="1">
       <c r="A1057" s="2" t="n">
@@ -47546,8 +47574,19 @@
       <c r="G1057" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H1057" s="2" t="n"/>
-      <c r="I1057" s="2" t="n"/>
+      <c r="H1057" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+鍍鉻作業易使勞工暴露於霧滴形態之鉻而造成鼻中膈（試題筆誤作鼻中腸）穿孔。
+原因說明
+作業原理：在電鍍鉻作業中，工件是浸泡在鉻酸等化學藥液中進行電解反應。
+物質形態：電解過程產生的氣泡在液面破裂時，會將液體激發並散發至空氣中，形成細小的液體微粒，即為霧滴（如鉻酸霧滴）。
+健康危害：吸入高濃度的鉻酸霧滴具強烈腐蝕性，容易造成鼻黏膜受損、潰瘍，長期下來便會導致鼻中膈穿孔。
+Threads
+·osh_flourishing</t>
+        </is>
+      </c>
+      <c r="I1057" s="2" t="inlineStr"/>
     </row>
     <row r="1058" ht="92.59999999999999" customHeight="1">
       <c r="A1058" s="2" t="n">
@@ -47581,8 +47620,18 @@
       <c r="G1058" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H1058" s="2" t="n"/>
-      <c r="I1058" s="2" t="n"/>
+      <c r="H1058" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+勞工可能會發生鼻中膈穿孔現象的選項是 鉻酸（例如電鍍、鍍鉻作業）。
+相關物質與職業病對照
+鉻酸：常出現於鍍鉻或電鍍作業中，空氣中的鉻酸霧滴會腐蝕鼻黏膜，嚴重時導致鼻中膈穿孔及皮膚潰瘍。
+苯：主要影響造血系統，長期暴露可能引起再生不良性貧血或血癌（白血病）。
+硫酸：具強烈腐蝕性與刺激性，吸入酸霧主要造成呼吸道及肺部疾病。
+鎘：長期暴露會蓄積在腎臟與骨骼，可能引起腎小管功能障礙及骨痛病（又稱痛痛病）。</t>
+        </is>
+      </c>
+      <c r="I1058" s="2" t="inlineStr"/>
     </row>
     <row r="1059" ht="92.59999999999999" customHeight="1">
       <c r="A1059" s="2" t="n">
@@ -47616,8 +47665,17 @@
       <c r="G1059" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1059" s="2" t="n"/>
-      <c r="I1059" s="2" t="n"/>
+      <c r="H1059" s="2" t="inlineStr">
+        <is>
+          <t>氯痤瘡是因暴露於多氯聯苯而造成的。
+氯痤瘡簡介
+成因：由多氯聯苯（PCB）、多氯二苯戴奧辛等氯化多環芳烴化合物引起。
+症狀：皮膚出現類似嚴重青春痘的囊狀皮疹，常伴隨肝功能異常。
+好發部位：臉部、耳周、頸部及肩膀等。
+维基百科</t>
+        </is>
+      </c>
+      <c r="I1059" s="2" t="inlineStr"/>
     </row>
     <row r="1060" ht="92.59999999999999" customHeight="1">
       <c r="A1060" s="2" t="n">
@@ -47651,8 +47709,17 @@
       <c r="G1060" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1060" s="2" t="n"/>
-      <c r="I1060" s="2" t="n"/>
+      <c r="H1060" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+二異氰酸甲苯（TDI）會造成過敏性氣喘。它是強烈的呼吸道過敏原與致敏物質，會刺激呼吸道黏膜並引發免疫反應，導致立即性或遲發性氣喘。
+其他選項的健康危害
+甲烷：屬於單純性窒息性氣體，高濃度時會因排擠氧氣而導致缺氧，不具過敏原特性。
+氯乙烯：為常用於製造聚氯乙烯（PVC）的原料，長期接觸主要與肝臟血管肉瘤等癌症風險相關。
+硫化氫：具有強烈臭雞蛋味的劇毒性氣體，高濃度暴露會直接抑制呼吸中樞、導致呼吸麻痺與死亡。</t>
+        </is>
+      </c>
+      <c r="I1060" s="2" t="inlineStr"/>
     </row>
     <row r="1061" ht="92.59999999999999" customHeight="1">
       <c r="A1061" s="2" t="n">
@@ -47686,8 +47753,17 @@
       <c r="G1061" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H1061" s="2" t="n"/>
-      <c r="I1061" s="2" t="n"/>
+      <c r="H1061" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+二異氰酸甲苯（TDI）對人體會造成危害，它屬於致過敏性物質。
+危害特性說明
+呼吸道過敏：二異氰酸甲苯是強烈的呼吸道過敏原，常引起職業性哮喘、支氣管炎或呼吸道水腫。
+刺激性：對眼睛、皮膚及黏膜具有強烈刺激性。
+Merck Millipore</t>
+        </is>
+      </c>
+      <c r="I1061" s="2" t="inlineStr"/>
     </row>
     <row r="1062" ht="92.59999999999999" customHeight="1">
       <c r="A1062" s="2" t="n">
@@ -47722,8 +47798,17 @@
       <c r="G1062" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H1062" s="2" t="n"/>
-      <c r="I1062" s="2" t="n"/>
+      <c r="H1062" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+刺激性危害物質具高溶解度者，主要會作用於暴露者的上呼吸道。
+呼吸道刺激性物質與溶解度關係
+高溶解度者：如氨、氯化氫、甲醛等，容易被上呼吸道的水分吸收，主要作用於上呼吸道（如鼻、咽、喉）。
+中溶解度者：如二氧化硫、氯氣等，可同時影響上呼吸道及下呼吸道。
+低溶解度者：如二氧化氮、光氣等，不易在上呼吸道被吸收，會深入並主要作用於下呼吸道及呼吸道末端。</t>
+        </is>
+      </c>
+      <c r="I1062" s="2" t="inlineStr"/>
     </row>
     <row r="1063" ht="92.59999999999999" customHeight="1">
       <c r="A1063" s="2" t="n">
@@ -47757,8 +47842,16 @@
       <c r="G1063" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H1063" s="2" t="n"/>
-      <c r="I1063" s="2" t="n"/>
+      <c r="H1063" s="2" t="inlineStr">
+        <is>
+          <t>依據《職業安全衛生法施行細則》（或早期勞工安全衛生法施行細則）的分類規定，答案為 氧化性物質。
+💡 核心觀念解析
+在職業安全衛生相關法規中，危害性化學品主要依據國家標準 CNS 15030 分為危險物與有害物兩大類：
+有害物（具有健康危害者）： 題目中的 致癌物、劇毒物質、腐蝕性物質皆屬於有害物，因為它們會對人體的健康與生理造成不良影響。
+危險物（具有物理性危害者）： 氧化性物質（如氯酸鉀、硝酸銨等）屬於「危險物」，主要會引發火災、爆炸等物理性化學災害，而非直接歸類於健康危害的有害物。</t>
+        </is>
+      </c>
+      <c r="I1063" s="2" t="inlineStr"/>
     </row>
     <row r="1064" ht="92.59999999999999" customHeight="1">
       <c r="A1064" s="2" t="n">
@@ -47792,8 +47885,18 @@
       <c r="G1064" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H1064" s="2" t="n"/>
-      <c r="I1064" s="2" t="n"/>
+      <c r="H1064" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+氯乙烯單體（Vinyl chloride monomer, VCM）屬於致肝癌物質。
+考古豹
+詳細說明
+健康危害：氯乙烯是確定的人類致癌物（IARC Group 1），長期暴露或吸入會導致罕見的肝臟惡性腫瘤——肝血管肉瘤（hepatic angiosarcoma），是職業醫學中的經典考點。
+用途：主要用來製造聚氯乙烯（PVC）塑膠原料。
+考古豹</t>
+        </is>
+      </c>
+      <c r="I1064" s="2" t="inlineStr"/>
     </row>
     <row r="1065" ht="108" customHeight="1">
       <c r="A1065" s="2" t="n">
@@ -47827,8 +47930,18 @@
       <c r="G1065" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H1065" s="2" t="n"/>
-      <c r="I1065" s="2" t="n"/>
+      <c r="H1065" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+選項 (B) 氣體容器閥門應有提供最小流率之裝置 是有誤的。
+根據職業安全衛生設施規則第 185-1 條規定，雇主對於常溫下具有自燃性之四氫化矽（矽甲烷）之處理，氣體容器之閥門應具有「限制最大流率」之流率限制孔，而非提供最小流率。
+其他選項皆符合規定：
+(A) 應儲存於室外安全處所或室內有效通風換氣之處所，使用時應置於氣瓶櫃內。
+(C) 應設置氣體洩漏檢知警報系統。
+(D) 未使用之氣體容器與供氣中之容器，應分隔放置。</t>
+        </is>
+      </c>
+      <c r="I1065" s="2" t="inlineStr"/>
     </row>
     <row r="1066" ht="92.59999999999999" customHeight="1">
       <c r="A1066" s="2" t="n">
@@ -47862,8 +47975,26 @@
       <c r="G1066" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H1066" s="2" t="n"/>
-      <c r="I1066" s="2" t="n"/>
+      <c r="H1066" s="2" t="inlineStr">
+        <is>
+          <t>該儲槽屬於第二種壓力容器。
+以下為法規定義的詳細判斷與分析：
+1. 為什麼不是「高壓氣體特定設備」？
+依據中華民國《危險性機械及設備安全檢查規則》第四條第三款規定，高壓氣體特定設備之判定雖然通常看壓力與內容積之積（超過 0.04），但該款同時設有排除條款：
+排除項目：「溫度在攝氏三十五度時，表壓力在每平方公分五十公斤以下之空氣壓縮裝置之容器。」
+本題狀況：此為空氣壓縮機用之空氣儲槽，壓力為 20 公斤/平方公分，低於法規排除上限的 50 公斤/平方公分，因此不屬於高壓氣體特定設備。
+2. 為什麼不是「第一種壓力容器」？
+依據《鍋爐及壓力容器安全規則》，第一種壓力容器主要是指內部有涉及「接受外來熱媒加熱、反應產生蒸氣、蒸餾分離或保存超過沸點液體」之容器。本題僅為一般空壓機儲氣用的空氣儲槽，內部無上述熱交換或化學反應，因此不屬於第一種壓力容器。
+www.fsair.com.tw 3. 為什麼是「第二種壓力容器」？
+依據《鍋爐及壓力容器安全規則》第四條規定，第二種壓力容器指內存氣體之壓力在每平方公分二公斤以上，且合於下列規定之一者：
+內容積在 0.04 立方公尺以上之容器。
+胴體內徑在 200 毫米以上，長度在 1000 毫米以上之容器。
+本題數據完全符合上述條件：
+氣體壓力：20 公斤/平方公分（大於 2 公斤/平方公分）
+內容積：0.5 立方公尺（大於 0.04 立方公尺）</t>
+        </is>
+      </c>
+      <c r="I1066" s="2" t="inlineStr"/>
     </row>
     <row r="1067" ht="92.59999999999999" customHeight="1">
       <c r="A1067" s="2" t="n">
@@ -47889,8 +48020,12 @@
       <c r="G1067" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H1067" s="2" t="n"/>
-      <c r="I1067" s="2" t="n"/>
+      <c r="H1067" s="2" t="inlineStr">
+        <is>
+          <t>Google AI 摘要未抓取到，請手動補充。</t>
+        </is>
+      </c>
+      <c r="I1067" s="2" t="inlineStr"/>
     </row>
     <row r="1068" ht="77.15000000000001" customHeight="1">
       <c r="A1068" s="2" t="n">
@@ -47916,8 +48051,15 @@
       <c r="G1068" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H1068" s="2" t="n"/>
-      <c r="I1068" s="2" t="n"/>
+      <c r="H1068" s="2" t="inlineStr">
+        <is>
+          <t>依據《高壓氣體勞工安全規則》第 53 條規定，答案是 5 公尺。
+相關法規重點
+距離規定：設置於內容積在 5,000 公升以上之可燃性氣體、毒性氣體或氧氣等液化氣體儲槽之配管，應於距離該儲槽外側 5公尺 以上之安全處所設置可操作之緊急遮斷裝置。
+例外規定：僅用於接受該液態氣體之配管者，得以逆止閥代替。</t>
+        </is>
+      </c>
+      <c r="I1068" s="2" t="inlineStr"/>
     </row>
     <row r="1069" ht="108" customHeight="1">
       <c r="A1069" s="2" t="n">
@@ -47951,8 +48093,25 @@
       <c r="G1069" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1069" s="2" t="n"/>
-      <c r="I1069" s="2" t="n"/>
+      <c r="H1069" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+硫化氫較易滯留於局限空間場所底部。
+勞動部職業安全衛生署
+原因說明：
+比空氣重：硫化氫（
+H
+2
+S
+）的氣體密度比空氣重，因此容易沉積、滯留在下水道、廢水池或局限空間的底部。
+特性：具無色、低濃度時有臭雞蛋味、高濃度時會使人嗅覺麻痺等特點，對作業人員危害極大。
+iPEDIA 百科 Further Exploration
+了解勞動部職業安全衛生署提供的局限空間作業危害介紹。
+檢視工安百科整理的認識局限空間作業危害。
+參考線上題庫平台 Yamol 上的一般甲業考題解析。</t>
+        </is>
+      </c>
+      <c r="I1069" s="2" t="inlineStr"/>
     </row>
     <row r="1070" ht="92.59999999999999" customHeight="1">
       <c r="A1070" s="2" t="n">
@@ -47986,8 +48145,15 @@
       <c r="G1070" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1070" s="2" t="n"/>
-      <c r="I1070" s="2" t="n"/>
+      <c r="H1070" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+依職業安全衛生設施規則規定，氫氣屬於 可燃性氣體。
+根據《職業安全衛生設施規則》相關條文定義：
+可燃性氣體：包含氫、乙炔、乙烯、甲烷、乙烷、丙烷、丁烷等危險物。</t>
+        </is>
+      </c>
+      <c r="I1070" s="2" t="inlineStr"/>
     </row>
     <row r="1071" ht="92.59999999999999" customHeight="1">
       <c r="A1071" s="2" t="n">
@@ -48021,8 +48187,15 @@
       <c r="G1071" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H1071" s="2" t="n"/>
-      <c r="I1071" s="2" t="n"/>
+      <c r="H1071" s="2" t="inlineStr">
+        <is>
+          <t>答案為：(C) 於鍋爐房從事工作之作業場所。
+解析
+鍋爐房從事工作之作業場所屬物理性因子之高溫作業場所（監測綜合溫度熱指數 WBGT），而非屬化學性因子作業環境監測之對象。
+其他選項（特定粉塵作業場所、有機溶劑作業場所、隧道掘削之建設工程之場所）皆屬於應實施化學性因子作業環境監測之作業場所。</t>
+        </is>
+      </c>
+      <c r="I1071" s="2" t="inlineStr"/>
     </row>
     <row r="1072" ht="92.59999999999999" customHeight="1">
       <c r="A1072" s="2" t="n">

--- a/salf/丙種職業安全衛生業務主管題庫.xlsx
+++ b/salf/丙種職業安全衛生業務主管題庫.xlsx
@@ -48229,8 +48229,20 @@
       <c r="G1072" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1072" s="2" t="n"/>
-      <c r="I1072" s="2" t="n"/>
+      <c r="H1072" s="2" t="inlineStr">
+        <is>
+          <t>「迅速查出肇災人員，依規定處分」非化學品災後復原階段應確認之事項。
+說明
+在化學品災害的災後復原階段，重點在於檢討、恢復裝備與追蹤人員健康，而非在第一時間進行懲處：
+應確認之事項包含：
+補充滅火藥劑
+檢討廣播器材之有效性
+注意事故處理人員之後續健康狀況
+不屬於復原階段確認項目：
+迅速查出肇災人員，依規定處分（此為後續調查與行政程序，不列入災後立即復原與整備的確認事項）。</t>
+        </is>
+      </c>
+      <c r="I1072" s="2" t="inlineStr"/>
     </row>
     <row r="1073" ht="77.15000000000001" customHeight="1">
       <c r="A1073" s="2" t="n">
@@ -48264,8 +48276,15 @@
       <c r="G1073" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1073" s="2" t="n"/>
-      <c r="I1073" s="2" t="n"/>
+      <c r="H1073" s="2" t="inlineStr">
+        <is>
+          <t>災害通報非化學品災後復原階段應確認之事項。
+解析
+災害通報屬於災害發生當下或初期應立即執行的緊急應變處置，而非災後復原階段的事項。
+災後復原階段應確認的事項包含：補充防護器材、檢討偵測器材之有效性、以及檢討事故原因等。</t>
+        </is>
+      </c>
+      <c r="I1073" s="2" t="inlineStr"/>
     </row>
     <row r="1074" ht="92.59999999999999" customHeight="1">
       <c r="A1074" s="2" t="n">
@@ -48293,8 +48312,15 @@
       <c r="G1074" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H1074" s="2" t="n"/>
-      <c r="I1074" s="2" t="n"/>
+      <c r="H1074" s="2" t="inlineStr">
+        <is>
+          <t>應增加 3 小時的相關課程。
+勞動部職業安全衛生署
+依據《職業安全衛生教育訓練規則》規定，雇主使勞工從事製造、處置或使用危害性化學品時，除應實施 3 小時的一般安全衛生教育訓練外，應依工作性質各增列（增加） 3 小時的訓練課程。
+社團法人中華民國技能發展協會</t>
+        </is>
+      </c>
+      <c r="I1074" s="2" t="inlineStr"/>
     </row>
     <row r="1075" ht="108" customHeight="1">
       <c r="A1075" s="2" t="n">
@@ -48328,8 +48354,29 @@
       <c r="G1075" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1075" s="2" t="n"/>
-      <c r="I1075" s="2" t="n"/>
+      <c r="H1075" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+正確答案：硫化氫
+原因解析
+硫化氫（
+𝐻
+2
+𝑆
+𝑯
+𝟐
+𝑺
+）的溶解特性：
+硫化氫氣體主要由有機廢液、汙泥等經分解後產生，它極易溶解於水溶液及積存於泥狀物質中。
+當局限空間底部的廢液或淤泥受到攪動或環境改變時，溶解在其中的硫化氫會大量釋放出來，造成嚴重中毒危險。
+勞動部職業安全衛生署 其他氣體比較：
+甲烷、一氧化碳與氮氣在水或廢液中的溶解度都相對較低，主要以氣態存在於局限空間的空氣中。
+勞動部職業安全衛生署
+局限空間作業危害介紹 - 勞動部職業安全衛生署
+硫化氫中毒：作業場所硫化氫濃度不得超過10ppm。硫化氫氣體主要產生</t>
+        </is>
+      </c>
+      <c r="I1075" s="2" t="inlineStr"/>
     </row>
     <row r="1076" ht="92.59999999999999" customHeight="1">
       <c r="A1076" s="2" t="n">
@@ -48357,8 +48404,14 @@
       <c r="G1076" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H1076" s="2" t="n"/>
-      <c r="I1076" s="2" t="n"/>
+      <c r="H1076" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+依據職業安全衛生設施規則第107條規定，高壓氣體容器於貯存或搬運時，溫度應保持在攝氏 40 度以下。
+正確答案為：40</t>
+        </is>
+      </c>
+      <c r="I1076" s="2" t="inlineStr"/>
     </row>
     <row r="1077" ht="92.59999999999999" customHeight="1">
       <c r="A1077" s="2" t="n">
@@ -48392,8 +48445,18 @@
       <c r="G1077" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H1077" s="2" t="n"/>
-      <c r="I1077" s="2" t="n"/>
+      <c r="H1077" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+作業場所設置以動力吸引排出已發散之有害氣體或蒸氣之設備，為 局部排氣裝置。
+相關名詞定義對照
+局部排氣裝置：指藉動力強制吸引並排出已發散之有害氣體或蒸氣（或有機溶劑蒸氣）之設備。
+整體換氣裝置：指藉動力稀釋已發散之有害氣體或蒸氣之設備。
+密閉設備：指將發生源密閉，使其蒸氣或氣體不致發散之設備。
+送風機：為提供風力或送風的機械零件/風機，並非指整個排氣系統設備。</t>
+        </is>
+      </c>
+      <c r="I1077" s="2" t="inlineStr"/>
     </row>
     <row r="1078" ht="92.59999999999999" customHeight="1">
       <c r="A1078" s="2" t="n">
@@ -48427,8 +48490,19 @@
       <c r="G1078" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H1078" s="2" t="n"/>
-      <c r="I1078" s="2" t="n"/>
+      <c r="H1078" s="2" t="inlineStr">
+        <is>
+          <t>「半數致死濃度」非屬勞工作業場所容許暴露濃度標準所使用之容許濃度標準。
+勞工作業場所容許濃度標準
+依據《勞工作業場所容許暴露標準》第三條規定，我國法規所使用的容許濃度標準包含以下三種：
+植根法律網
+8 小時日時量平均容許濃度 (TWA)：勞工每天工作 8 小時，重複暴露不致有不良反應之濃度。
+短時間時量平均容許濃度 (STEL)：勞工連續暴露 15 分鐘不致有害之濃度。
+最高容許濃度 (Ceiling)：任何時間均不得超過之暴露濃度。
+而「半數致死濃度 (LC50)」是用來衡量化學品毒性或半數實驗動物死亡的劑量/濃度指標，並非我國勞工作業環境中規定的容許暴露標準。</t>
+        </is>
+      </c>
+      <c r="I1078" s="2" t="inlineStr"/>
     </row>
     <row r="1079" ht="92.59999999999999" customHeight="1">
       <c r="A1079" s="2" t="n">
@@ -48456,8 +48530,12 @@
       <c r="G1079" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H1079" s="2" t="n"/>
-      <c r="I1079" s="2" t="n"/>
+      <c r="H1079" s="2" t="inlineStr">
+        <is>
+          <t>勞工作業場所容許暴露標準之短時間時量平均容許濃度，為一般勞工連續暴露在此濃度以下任何 15 分鐘（勞工作業場所容許暴露標準第3條規定）。</t>
+        </is>
+      </c>
+      <c r="I1079" s="2" t="inlineStr"/>
     </row>
     <row r="1080" ht="77.15000000000001" customHeight="1">
       <c r="A1080" s="2" t="n">
@@ -48491,8 +48569,16 @@
       <c r="G1080" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H1080" s="2" t="n"/>
-      <c r="I1080" s="2" t="n"/>
+      <c r="H1080" s="2" t="inlineStr">
+        <is>
+          <t>答案是氫。
+原因說明
+氫：在常溫常壓下為氣體，且具高度可燃性（可燃性氣體）。
+乙醇（酒精）、苯、汽油：在常溫常壓下皆為液體（易燃液體），而非氣體。
+宜蘭縣勞工教育協進會</t>
+        </is>
+      </c>
+      <c r="I1080" s="2" t="inlineStr"/>
     </row>
     <row r="1081" ht="92.59999999999999" customHeight="1">
       <c r="A1081" s="2" t="n">
@@ -48526,8 +48612,17 @@
       <c r="G1081" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H1081" s="2" t="n"/>
-      <c r="I1081" s="2" t="n"/>
+      <c r="H1081" s="2" t="inlineStr">
+        <is>
+          <t>選項「周圍 2 公尺內得放置引火性物品」有誤。
+根據《職業安全衛生設施規則》第 108 條規定，高壓氣體貯存場所之周圍 2 公尺內不得放置有煙火及著火性、引火性物品，而不是「得放置」。
+正確規定摘要
+禁止煙火：周圍 2 公尺內不得放置煙火、著火性及引火性物品，且場所應有適當警戒標示。
+分區放置：盛裝容器和空容器應分區放置。
+分類隔離：可燃性氣體、有毒性氣體及氧氣容器應分開貯存。</t>
+        </is>
+      </c>
+      <c r="I1081" s="2" t="inlineStr"/>
     </row>
     <row r="1082" ht="77.15000000000001" customHeight="1">
       <c r="A1082" s="2" t="n">
@@ -48561,8 +48656,18 @@
       <c r="G1082" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H1082" s="2" t="n"/>
-      <c r="I1082" s="2" t="n"/>
+      <c r="H1082" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+燃燒 PVC（聚氯乙烯）電纜線時，會產生 (C) 氯化氫（Hydrogen Chloride，又稱鹽酸氣體）毒性氣體。
+原因說明
+化學成分：PVC 的化學名稱為聚氯乙烯，其分子結構中含有大量的氯元素。
+燃燒反應：當 PVC 電纜燃燒或受熱分解時，氯元素會與氫結合，釋放出大量的氯化氫氣體。
+危害特性：氯化氫具有強烈的刺激性與腐蝕性，若接觸到空氣中的水分（如呼吸道黏膜或眼睛），會形成強酸，對人體呼吸道造成嚴重傷害。
+泰通電線電纜股份有限公司</t>
+        </is>
+      </c>
+      <c r="I1082" s="2" t="inlineStr"/>
     </row>
     <row r="1083" ht="92.59999999999999" customHeight="1">
       <c r="A1083" s="2" t="n">
@@ -48596,8 +48701,19 @@
       <c r="G1083" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H1083" s="2" t="n"/>
-      <c r="I1083" s="2" t="n"/>
+      <c r="H1083" s="2" t="inlineStr">
+        <is>
+          <t>依據勞工作業環境監測實施辦法第2條之定義，雇主使勞工每日作業時間在 1 小時以內者為作業時間短暫。
+正確選項為：作業時間短暫。
+想進一步了解其他相關定義嗎？例如：
+作業期間短暫的具體天數限制為何？
+或是需要探討臨時性作業的規定？
+這能幫助您更完整掌握職業安全衛生相關法規與考試重點。
+勞工作業環境監測實施辦法 - 勞動部-所有條文
+三、作業時間短暫：指雇主使勞工每日作業時間在一小時以內者。 四、作業期間短暫：指作業期間不超過一個月，且確知自該作業終了日起六個月，不再實施該作業者。 五 ...</t>
+        </is>
+      </c>
+      <c r="I1083" s="2" t="inlineStr"/>
     </row>
     <row r="1084" ht="77.15000000000001" customHeight="1">
       <c r="A1084" s="2" t="n">
@@ -48631,8 +48747,16 @@
       <c r="G1084" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H1084" s="2" t="n"/>
-      <c r="I1084" s="2" t="n"/>
+      <c r="H1084" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+細胞色素氧化酵素易與氰化物（Cyanide）作用，造成人體危害。
+危害重點說明
+作用機轉：氰化物會結合細胞內的鐵細胞色素氧化酵素（Cytochrome c oxidase），阻止細胞正常利用氧氣進行呼吸作用。
+物質分類：屬於化學性窒息性物質，會直接影響細胞層級的氧氣代謝，導致組織缺氧。</t>
+        </is>
+      </c>
+      <c r="I1084" s="2" t="inlineStr"/>
     </row>
     <row r="1085" ht="108" customHeight="1">
       <c r="A1085" s="2" t="n">
@@ -48660,8 +48784,12 @@
       <c r="G1085" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H1085" s="2" t="n"/>
-      <c r="I1085" s="2" t="n"/>
+      <c r="H1085" s="2" t="inlineStr">
+        <is>
+          <t>進入儲槽等局限空間作業，為避免缺氧危害，應確認其內部空氣中氧氣濃度大於 18 百分比（選項 18）。依據《缺氧症預防規則》，雇主應保持作業場所空氣中氧氣濃度在 18% 以上。</t>
+        </is>
+      </c>
+      <c r="I1085" s="2" t="inlineStr"/>
     </row>
     <row r="1086" ht="92.59999999999999" customHeight="1">
       <c r="A1086" s="2" t="n">
@@ -48695,8 +48823,14 @@
       <c r="G1086" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H1086" s="2" t="n"/>
-      <c r="I1086" s="2" t="n"/>
+      <c r="H1086" s="2" t="inlineStr">
+        <is>
+          <t>依據《勞工作業環境監測實施辦法》之定義，答案為臨時性作業。
+相關定義
+臨時性作業：指正常作業以外之作業，其作業期間不超過3個月，且1年內不再重複者。</t>
+        </is>
+      </c>
+      <c r="I1086" s="2" t="inlineStr"/>
     </row>
     <row r="1087" ht="92.59999999999999" customHeight="1">
       <c r="A1087" s="2" t="n">
@@ -48730,8 +48864,27 @@
       <c r="G1087" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H1087" s="2" t="n"/>
-      <c r="I1087" s="2" t="n"/>
+      <c r="H1087" s="2" t="inlineStr">
+        <is>
+          <t>家庭常用的桶裝液化石油氣（LPG），其成分主要為丙烷、丁烷。
+主要成分說明
+丙烷（Propane,
+𝐂
+𝟑
+𝐇
+𝟖
+）：碳氫化合物的一種，常溫常壓下為氣體，易於加壓液化。
+丁烷（Butane,
+𝐂
+𝟒
+𝐇
+𝟏
+𝟎
+）：碳氫化合物的一種，與丙烷混合裝入鋼瓶中作為燃料。
+能源教育資源總中心</t>
+        </is>
+      </c>
+      <c r="I1087" s="2" t="inlineStr"/>
     </row>
     <row r="1088" ht="92.59999999999999" customHeight="1">
       <c r="A1088" s="2" t="n">
@@ -48765,8 +48918,21 @@
       <c r="G1088" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H1088" s="2" t="n"/>
-      <c r="I1088" s="2" t="n"/>
+      <c r="H1088" s="2" t="inlineStr">
+        <is>
+          <t>對於具有氰化物或硫化物之廢水，應嚴格管制不得與酸液混合，以避免產生有害氣體（如劇毒的氰化氫
+HCN
+H
+C
+N
+或硫化氫
+H
+2
+S
+氣體）。</t>
+        </is>
+      </c>
+      <c r="I1088" s="2" t="inlineStr"/>
     </row>
     <row r="1089" ht="92.59999999999999" customHeight="1">
       <c r="A1089" s="2" t="n">
@@ -48800,8 +48966,18 @@
       <c r="G1089" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H1089" s="2" t="n"/>
-      <c r="I1089" s="2" t="n"/>
+      <c r="H1089" s="2" t="inlineStr">
+        <is>
+          <t>應採作業環境監測（或稱作業環境測定）措施。
+措施說明
+作業環境監測：透過科學的採樣、分析與評估，直接掌握工作場所中化學性或物理性有害因子的真實濃度或強度，並據此建立勞工的暴露資料。
+工程改善：屬於降低危害的控制手段，而非用來「瞭解強度與建立資料」的調查評估方法。
+低毒性取代高毒性：是預防職業病的替代原則，同樣不屬於環境測量的調查措施。
+有害物標示：是用於警示與告知危險的標示方式，無法測得實際數值或暴露強度。
+gosh.com.tw</t>
+        </is>
+      </c>
+      <c r="I1089" s="2" t="inlineStr"/>
     </row>
     <row r="1090" ht="92.59999999999999" customHeight="1">
       <c r="A1090" s="2" t="n">
@@ -48827,8 +49003,16 @@
       <c r="G1090" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1090" s="2" t="n"/>
-      <c r="I1090" s="2" t="n"/>
+      <c r="H1090" s="2" t="inlineStr">
+        <is>
+          <t>依據《勞工作業場所容許暴露標準》之規定，二氧化碳之8小時日時量平均容許濃度為 5000 ppm。因此正確答案為 5000。
+相關標準說明
+容許濃度：指勞工在全程工作日暴露其中，對健康不至於有不良影響的濃度。
+二氧化碳標準：法定的 8 小時日時量平均容許濃度（TWA）為 5000 ppm。
+比較基準：一般室內空氣品質（如辦公大樓或商場）建議維持在 1000 ppm 以下，但勞工作業場所的法定容許標準為 5000 ppm。</t>
+        </is>
+      </c>
+      <c r="I1090" s="2" t="inlineStr"/>
     </row>
     <row r="1091" ht="77.15000000000001" customHeight="1">
       <c r="A1091" s="2" t="n">
@@ -48862,8 +49046,19 @@
       <c r="G1091" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H1091" s="2" t="n"/>
-      <c r="I1091" s="2" t="n"/>
+      <c r="H1091" s="2" t="inlineStr">
+        <is>
+          <t>這名勞工很有可能是一氧化碳（Carbon Monoxide, CO）中毒。
+關鍵原因分析
+桃紅色皮膚：一氧化碳吸入人體後，會與血液中的血紅素緊密結合，形成「碳氧血紅素（HbCO）」。由於碳氧血紅素呈現鮮紅色（或稱桃紅色、櫻桃紅），因此中毒者的皮膚、黏膜或指甲床常會呈現特殊的桃紅色反應，這是辨識一氧化碳中毒的經典指標特徵。
+昏迷：一氧化碳會阻斷血液輸送氧氣的功能，導致全身組織（特別是大腦與心臟）嚴重缺氧，進而引發昏迷。
+其他選項排除原因
+甲烷：本身無色無味無毒，主要藉由取代空氣中的氧氣造成「缺氧窒息」，不會讓皮膚變成桃紅色（通常呈發紺、發紫）。
+氨（阿摩尼亞）：具強烈刺激性臭味，吸入會造成呼吸道嚴重灼傷、腐蝕與水腫，主要特徵為強烈刺鼻感與呼吸困難。
+硫化氫：具有臭雞蛋味，高濃度時會迅速使人昏迷（電擊樣倒地），但其造成的發紺通常會使皮膚呈現青紫色或灰黑色，而非桃紅色。</t>
+        </is>
+      </c>
+      <c r="I1091" s="2" t="inlineStr"/>
     </row>
     <row r="1092" ht="77.15000000000001" customHeight="1">
       <c r="A1092" s="2" t="n">
@@ -48897,8 +49092,35 @@
       <c r="G1092" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H1092" s="2" t="n"/>
-      <c r="I1092" s="2" t="n"/>
+      <c r="H1092" s="2" t="inlineStr">
+        <is>
+          <t>此現象係屬於相加作用（Additive effect）。
+毒性交互作用簡介
+相加作用：兩種或多種物質同時暴露的總效應，等於各自暴露效應的數學總和（
+1
++
+1
+=
+2
+）。
+協同作用（Synergism）：同時暴露的總效應大於各自效應的總和（
+1
++
+1
+&gt;
+2
+）。
+拮抗作用（Antagonism）：同時暴露的總效應小於其中個別效應或總和（
+1
++
+1
+&lt;
+1
+或小於單獨預期）。
+相減作用：通常指其中一種物質抵銷部分另一物質之毒性，亦屬於廣義的拮抗概念。</t>
+        </is>
+      </c>
+      <c r="I1092" s="2" t="inlineStr"/>
     </row>
     <row r="1093" ht="92.59999999999999" customHeight="1">
       <c r="A1093" s="2" t="n">
@@ -48932,8 +49154,16 @@
       <c r="G1093" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H1093" s="2" t="n"/>
-      <c r="I1093" s="2" t="n"/>
+      <c r="H1093" s="2" t="inlineStr">
+        <is>
+          <t>錳對人體之主要危害為(A) 神經系統。
+主要危害說明
+神經系統受損：長期或高濃度吸入錳粉塵、煙霧會侵襲中樞神經系統。
+典型職業病：可能導致類似巴金森氏症候群的症狀，例如肢體動作變得緩慢、笨拙、步態不穩或面部表情僵硬等。
+國家環境毒物研究中心</t>
+        </is>
+      </c>
+      <c r="I1093" s="2" t="inlineStr"/>
     </row>
     <row r="1094" ht="92.59999999999999" customHeight="1">
       <c r="A1094" s="2" t="n">
@@ -48967,8 +49197,18 @@
       <c r="G1094" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H1094" s="2" t="n"/>
-      <c r="I1094" s="2" t="n"/>
+      <c r="H1094" s="2" t="inlineStr">
+        <is>
+          <t>國內錳作業工廠曾發生的職業病是巴金森氏症候群。
+相關重點整理
+錳中毒（巴金森氏症候群）：長期吸入高濃度的錳塵或錳煙，會對中樞神經系統造成損害，引發類似巴金森氏症的神經症狀（如肌肉僵硬、顫抖、步態不穩等）。
+其他選項對應的毒物：
+鼻中膈穿孔：多見於鉻作業（鉻酸）等環境。
+痛痛病：由鎘（Cadmium）污染引發。
+水俣症：由甲基汞（Mercury）中毒引發。</t>
+        </is>
+      </c>
+      <c r="I1094" s="2" t="inlineStr"/>
     </row>
     <row r="1095" ht="92.59999999999999" customHeight="1">
       <c r="A1095" s="2" t="n">
@@ -49002,8 +49242,17 @@
       <c r="G1095" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H1095" s="2" t="n"/>
-      <c r="I1095" s="2" t="n"/>
+      <c r="H1095" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+勞工長期使用高錳成分焊條從事電焊作業，有可能造成巴金森氏症（類似錳中毒症狀）。
+原因說明
+錳煙塵危害：電焊時會產生含錳的銲接燻煙，長期吸入會在大腦中樞神經系統累積。
+錳中毒（Manganism）：這是一種神經病變，會出現動作遲緩、肌肉僵硬、顫抖、平衡變差等類似巴金森氏症的臨床症狀。
+勞動部職業安全衛生署</t>
+        </is>
+      </c>
+      <c r="I1095" s="2" t="inlineStr"/>
     </row>
     <row r="1096" ht="92.59999999999999" customHeight="1">
       <c r="A1096" s="2" t="n">
@@ -49037,8 +49286,22 @@
       <c r="G1096" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1096" s="2" t="n"/>
-      <c r="I1096" s="2" t="n"/>
+      <c r="H1096" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+四氯化碳最可能危害肝腎。
+根據職業安全衛生與環境毒物相關資料，四氯化碳（
+CCl
+4
+C
+C
+l
+4
+）具有高度肝毒性與腎毒性，人體暴露在高劑量或長期接觸下，肝臟與腎臟最容易受到嚴重損傷或破壞。
+國家環境毒物研究中心</t>
+        </is>
+      </c>
+      <c r="I1096" s="2" t="inlineStr"/>
     </row>
     <row r="1097" ht="92.59999999999999" customHeight="1">
       <c r="A1097" s="2" t="n">
@@ -49072,8 +49335,13 @@
       <c r="G1097" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H1097" s="2" t="n"/>
-      <c r="I1097" s="2" t="n"/>
+      <c r="H1097" s="2" t="inlineStr">
+        <is>
+          <t>四氯化碳最可能透過呼吸（吸入蒸氣）路徑進入人體。
+四氯化碳常溫下容易揮發為蒸氣，在工作場所或環境中，勞工或大眾最常見且最主要的暴露與進入人體途徑就是經由呼吸道吸入。</t>
+        </is>
+      </c>
+      <c r="I1097" s="2" t="inlineStr"/>
     </row>
     <row r="1098" ht="77.15000000000001" customHeight="1">
       <c r="A1098" s="2" t="n">
@@ -49107,8 +49375,12 @@
       <c r="G1098" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1098" s="2" t="n"/>
-      <c r="I1098" s="2" t="n"/>
+      <c r="H1098" s="2" t="inlineStr">
+        <is>
+          <t>Google AI 摘要未抓取到，請手動補充。</t>
+        </is>
+      </c>
+      <c r="I1098" s="2" t="inlineStr"/>
     </row>
     <row r="1099" ht="92.59999999999999" customHeight="1">
       <c r="A1099" s="2" t="n">
@@ -49142,8 +49414,18 @@
       <c r="G1099" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H1099" s="2" t="n"/>
-      <c r="I1099" s="2" t="n"/>
+      <c r="H1099" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+依職業安全衛生設施規則規定，過氧化丁酮屬於(A) 爆炸性物質。
+法規依據
+根據《職業安全衛生設施規則》第11條規定，所稱爆炸性物質包含：
+硝化甘油、硝化纖維及其他硝酸酯類等爆炸性硝酸酯類。
+三硝基苯、三硝基甲苯、三硝基酚及其他具有爆炸性質之硝基化合物。
+過醋酸、過氧化丁酮、過氧化二苯甲醯及其他過氧化有機物。</t>
+        </is>
+      </c>
+      <c r="I1099" s="2" t="inlineStr"/>
     </row>
     <row r="1100" ht="92.59999999999999" customHeight="1">
       <c r="A1100" s="2" t="n">
@@ -49177,8 +49459,18 @@
       <c r="G1100" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H1100" s="2" t="n"/>
-      <c r="I1100" s="2" t="n"/>
+      <c r="H1100" s="2" t="inlineStr">
+        <is>
+          <t>正己烷可能產生的有害物是 (B) 蒸氣。
+為什麼答案是蒸氣？
+正己烷是一種有機溶劑，在常溫下容易揮發。
+高雄市政府全球資訊網 在職業衛生分類中：
+氣狀有害物包含氣體（Gas）與蒸氣（Vapor，通常指有機溶劑揮發形成的氣態物質）。
+正己烷常以液體形式存在，使用時會揮發並釋放蒸氣到空氣中，吸入後對人體健康及神經系統造成危害。
+勞動部職業安全衛生署</t>
+        </is>
+      </c>
+      <c r="I1100" s="2" t="inlineStr"/>
     </row>
     <row r="1101" ht="92.59999999999999" customHeight="1">
       <c r="A1101" s="2" t="n">
@@ -49212,8 +49504,19 @@
       <c r="G1101" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H1101" s="2" t="n"/>
-      <c r="I1101" s="2" t="n"/>
+      <c r="H1101" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+依職業安全衛生設施規則規定，汽油屬於易燃液體。
+根據該規則第13條，「易燃液體」包含乙醚、汽油、乙醛等閃火點未滿攝氏零下三十度或其他符合規定的危險物。
+想進一步確認這類法規考題嗎？你可以告訴我：
+你正在準備哪一種類別的證照考試（例如：甲種職業安全衛生業務主管、乙級職業安全衛生管理員等）？
+是否需要其他危險物（如爆炸性物質、著火性物質）的法規條文與分類重點？
+這能讓我為你整理出對應的歷屆考題精華與記憶口訣。
+資料</t>
+        </is>
+      </c>
+      <c r="I1101" s="2" t="inlineStr"/>
     </row>
     <row r="1102" ht="108" customHeight="1">
       <c r="A1102" s="2" t="n">
@@ -49247,8 +49550,12 @@
       <c r="G1102" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H1102" s="2" t="n"/>
-      <c r="I1102" s="2" t="n"/>
+      <c r="H1102" s="2" t="inlineStr">
+        <is>
+          <t>Google AI 摘要未抓取到，請手動補充。</t>
+        </is>
+      </c>
+      <c r="I1102" s="2" t="inlineStr"/>
     </row>
     <row r="1103" ht="92.59999999999999" customHeight="1">
       <c r="A1103" s="2" t="n">
@@ -49282,8 +49589,12 @@
       <c r="G1103" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H1103" s="2" t="n"/>
-      <c r="I1103" s="2" t="n"/>
+      <c r="H1103" s="2" t="inlineStr">
+        <is>
+          <t>Google AI 摘要未抓取到，請手動補充。</t>
+        </is>
+      </c>
+      <c r="I1103" s="2" t="inlineStr"/>
     </row>
     <row r="1104" ht="92.59999999999999" customHeight="1">
       <c r="A1104" s="2" t="n">
@@ -49317,8 +49628,18 @@
       <c r="G1104" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1104" s="2" t="n"/>
-      <c r="I1104" s="2" t="n"/>
+      <c r="H1104" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+依職業安全衛生設施規則規定，氯酸鉀屬於氧化性物質。
+法規依據
+依據職業安全衛生設施規則第14條規定，所稱氧化性物質包含：
+氯酸鉀、氯酸鈉、氯酸銨及其他之氯酸鹽類。
+過氯酸鉀、過氯酸鈉、過氯酸銨及其他之過氯酸鹽類。
+其他無機過氧化物與硝酸鹽類等危險物。</t>
+        </is>
+      </c>
+      <c r="I1104" s="2" t="inlineStr"/>
     </row>
     <row r="1105" ht="92.59999999999999" customHeight="1">
       <c r="A1105" s="2" t="n">
@@ -49352,8 +49673,22 @@
       <c r="G1105" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H1105" s="2" t="n"/>
-      <c r="I1105" s="2" t="n"/>
+      <c r="H1105" s="2" t="inlineStr">
+        <is>
+          <t>在都會區利用管線輸送到各用戶端的天然氣，其主要成分為甲烷。
+Quizlet 天然氣與瓦斯小知識
+天然氣 (NG)：主要成分為甲烷 (
+CH
+4
+C
+H
+4
+)，比空氣輕，透過地下管線輸送到家庭中。
+液化石油氣 (LPG)：常見的桶裝瓦斯，主要成分為丙烷與丁烷，比空氣重。
+教育大市集</t>
+        </is>
+      </c>
+      <c r="I1105" s="2" t="inlineStr"/>
     </row>
     <row r="1106" ht="92.59999999999999" customHeight="1">
       <c r="A1106" s="2" t="n">
@@ -49387,8 +49722,17 @@
       <c r="G1106" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1106" s="2" t="n"/>
-      <c r="I1106" s="2" t="n"/>
+      <c r="H1106" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+金屬鋰、金屬鈉（題目常寫作金屬鈉或筆誤為金屬鋼）與金屬鉀均屬於禁水性物質。
+原因與特性
+禁水性物質是指與水接觸會發生強烈化學反應，並放出易燃氣體的危險物品。
+金屬鋰、鈉、鉀如果碰到水，會把水分子分解並產生氫氣與高熱，甚至引發燃燒或爆炸。因此，這類金屬通常不能存放在水中，必須保存在石油醚或礦物油中以隔絕空氣和水分。
+myMKC管理知識中心</t>
+        </is>
+      </c>
+      <c r="I1106" s="2" t="inlineStr"/>
     </row>
     <row r="1107" ht="92.59999999999999" customHeight="1">
       <c r="A1107" s="2" t="n">
@@ -49422,8 +49766,20 @@
       <c r="G1107" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1107" s="2" t="n"/>
-      <c r="I1107" s="2" t="n"/>
+      <c r="H1107" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+答案是 煤油，它屬於易燃液體，而不是著火性物質。
+根據台灣《職業安全衛生設施規則》第12條規定，著火性物質包含以下危險物：
+金屬鋰、金屬鈉、金屬鉀
+黃磷、赤磷、硫化磷等
+賽璐珞類
+碳化鈣、磷化鈣
+鎂粉、鋁粉
+其中金屬鉀、金屬鈉與鋁粉皆名列其中，而煤油則屬於易燃液體。</t>
+        </is>
+      </c>
+      <c r="I1107" s="2" t="inlineStr"/>
     </row>
     <row r="1108" ht="77.15000000000001" customHeight="1">
       <c r="A1108" s="2" t="n">
@@ -49449,8 +49805,12 @@
       <c r="G1108" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H1108" s="2" t="n"/>
-      <c r="I1108" s="2" t="n"/>
+      <c r="H1108" s="2" t="inlineStr">
+        <is>
+          <t>Google AI 摘要未抓取到，請手動補充。</t>
+        </is>
+      </c>
+      <c r="I1108" s="2" t="inlineStr"/>
     </row>
     <row r="1109" ht="77.15000000000001" customHeight="1">
       <c r="A1109" s="2" t="n">
@@ -49484,8 +49844,18 @@
       <c r="G1109" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H1109" s="2" t="n"/>
-      <c r="I1109" s="2" t="n"/>
+      <c r="H1109" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+作業人員欲瞭解化學品之危害預防措施，可由安全資料表（SDS，Safety Data Sheet）獲得相關資訊。
+安全資料表（SDS）的重要內容
+危害辨識：列出化學品對健康的危害及物理性危害。
+預防措施：提供安全處置、儲存條件及個人防護具（如護目鏡、防毒面具、手套）的建議。
+急救措施：說明吸入、皮膚接觸、眼睛接觸或誤食時的立即處理方式。
+洩漏處理：指導意外洩漏時的清理與環境保護步驟。</t>
+        </is>
+      </c>
+      <c r="I1109" s="2" t="inlineStr"/>
     </row>
     <row r="1110" ht="92.59999999999999" customHeight="1">
       <c r="A1110" s="2" t="n">
@@ -49519,8 +49889,17 @@
       <c r="G1110" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H1110" s="2" t="n"/>
-      <c r="I1110" s="2" t="n"/>
+      <c r="H1110" s="2" t="inlineStr">
+        <is>
+          <t>執業之工業安全技師非作業環境監測機構應具備之資格。
+依據《勞工作業環境監測實施辦法》第 18 條規定，作業環境監測機構應具備下列資格條件：
+必要之採樣及測定儀器設備
+3 人以上甲級作業環境監測人員或執業之工礦衛生（職業衛生）技師 1 人以上
+具專屬之認證實驗室
+勞工作業環境監測及暴露危害管理 因此，「執業之工業安全技師」不在法定應具備之資格內。</t>
+        </is>
+      </c>
+      <c r="I1110" s="2" t="inlineStr"/>
     </row>
     <row r="1111" ht="92.59999999999999" customHeight="1">
       <c r="A1111" s="2" t="n">
@@ -49554,8 +49933,12 @@
       <c r="G1111" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H1111" s="2" t="n"/>
-      <c r="I1111" s="2" t="n"/>
+      <c r="H1111" s="2" t="inlineStr">
+        <is>
+          <t>Google AI 摘要未抓取到，請手動補充。</t>
+        </is>
+      </c>
+      <c r="I1111" s="2" t="inlineStr"/>
     </row>
     <row r="1112" ht="77.15000000000001" customHeight="1">
       <c r="A1112" s="2" t="n">
@@ -49589,8 +49972,19 @@
       <c r="G1112" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1112" s="2" t="n"/>
-      <c r="I1112" s="2" t="n"/>
+      <c r="H1112" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+順丁烯二酸非屬爆炸性物質。
+相關法規說明
+依據《職業安全衛生設施規則》第11條規定，所稱爆炸性物質包含：
+硝酸酯類：如硝化乙二醇、硝化甘油、硝化纖維等。
+硝基化合物：如三硝基苯、三硝基甲苯（TNT）、三硝基酚等（注意選項中的「硝基苯」屬於此類硝基化合物範疇/具有爆炸性質之硝基化合物或符合規範提及範圍）。
+過氧化有機物：如過醋酸、過氧化丁酮、過氧化二苯甲醯等。
+而順丁烯二酸（Maleic acid）為一種有機二羧酸，不屬於上述法規定義之爆炸性物質。</t>
+        </is>
+      </c>
+      <c r="I1112" s="2" t="inlineStr"/>
     </row>
     <row r="1113" ht="92.59999999999999" customHeight="1">
       <c r="A1113" s="2" t="n">
@@ -49624,8 +50018,15 @@
       <c r="G1113" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1113" s="2" t="n"/>
-      <c r="I1113" s="2" t="n"/>
+      <c r="H1113" s="2" t="inlineStr">
+        <is>
+          <t>這題的答案是 高壓氣體容器。
+相關法規與判斷依據
+高壓氣體容器定義：依據《高壓氣體勞工安全規則》及相關危險性機械及設備安全檢查規則，係指供灌裝高壓氣體之容器中，相對於地面可移動，且其內容積在五百公升（即 0.5 立方公尺）以上者。
+www.fsair.com.tw 題目給出之條件為：相對於地面可移動、氣體壓力 18 kg/cm²、內容積為 0.5 立方公尺（500公升），符合高壓氣體容器的定義範圍。</t>
+        </is>
+      </c>
+      <c r="I1113" s="2" t="inlineStr"/>
     </row>
     <row r="1114" ht="108" customHeight="1">
       <c r="A1114" s="2" t="n">
@@ -49659,8 +50060,17 @@
       <c r="G1114" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1114" s="2" t="n"/>
-      <c r="I1114" s="2" t="n"/>
+      <c r="H1114" s="2" t="inlineStr">
+        <is>
+          <t>「多批次作業所需的有機過氧化物以一次領取為最佳」是不正確的敘述。
+正確觀念與說明
+領料原則：有機過氧化物具強烈分解性與危險性，多批次作業所需之用料應依實際需要分批領用，避免一次領取過多而放置於工作場所增加風險。
+溫度控制：儲存場所確實應設有溫度控制裝置，以防止因過熱引發分解或爆炸。
+先進先出：儲存管理應採先進先出（FIFO），確保品質穩定。
+區隔存放：儲存場所應獨立且與製程區分開，以降低災害擴散的風險。</t>
+        </is>
+      </c>
+      <c r="I1114" s="2" t="inlineStr"/>
     </row>
     <row r="1115" ht="77.15000000000001" customHeight="1">
       <c r="A1115" s="2" t="n">
@@ -49694,8 +50104,19 @@
       <c r="G1115" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H1115" s="2" t="n"/>
-      <c r="I1115" s="2" t="n"/>
+      <c r="H1115" s="2" t="inlineStr">
+        <is>
+          <t>依特定化學物質危害預防標準之規定，氮氣並不屬於甲類、乙類、丙類或丁類中任何一類的特定化學物質。
+氮氣的危害與適用法規
+危害性質：氮氣屬於單純性窒息性物質，外洩或累積時會取代並稀釋空氣中的氧氣，導致作業場所缺氧窒息。
+相關法規：氮氣雖不在特定化學物質危害預防標準的列管清單中，但針對其造成的缺氧風險，適用勞動部的缺氧症預防規則以及職業安全衛生設施規則進行規範與管理。
+中山醫學大學 如果這是考試題目，建議確認題意是否為「非屬」特定化學物質，或提供其他選項以便進一步協助判斷。
+中山醫學大學
+授課講師 - 環境與安全衛生中心
+化學性危害因子的分類. 一、窒息性物質. 一般空氣中氧氣含量約佔20.91~20.96%. (一)單純性窒息性物質: 如氮氣、氬氣、甲烷、丙烷、丁烷及二氧化碳等會稀釋氧. 氣濃度造成缺氧窒息者。 (二)化學性窒息性物質: 一氧化碳及氰化物等影響組織對氧之利用或...</t>
+        </is>
+      </c>
+      <c r="I1115" s="2" t="inlineStr"/>
     </row>
     <row r="1116" ht="77.15000000000001" customHeight="1">
       <c r="A1116" s="2" t="n">
@@ -49729,8 +50150,18 @@
       <c r="G1116" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H1116" s="2" t="n"/>
-      <c r="I1116" s="2" t="n"/>
+      <c r="H1116" s="2" t="inlineStr">
+        <is>
+          <t>正確答案是 (A) 一氧化碳。
+相關概念
+化學窒息性物質（Chemical asphyxiants）：指在進入人體後，會經由化學作用阻礙血液攜帶氧氣或干擾細胞利用氧氣，導致身體組織缺氧的化學物質，如一氧化碳（會與血紅素結合阻礙輸氧）、氰化物等。
+其他選項：
+正己醇：屬於有機溶劑/醇類。
+1,1,1-三氯乙烷：屬於氯化烴類有機溶劑。
+石綿：屬於纖維狀矽酸鹽類礦物，主要會引起肺部纖維化或致癌。</t>
+        </is>
+      </c>
+      <c r="I1116" s="2" t="inlineStr"/>
     </row>
     <row r="1117" ht="92.59999999999999" customHeight="1">
       <c r="A1117" s="2" t="n">
@@ -49764,8 +50195,17 @@
       <c r="G1117" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H1117" s="2" t="n"/>
-      <c r="I1117" s="2" t="n"/>
+      <c r="H1117" s="2" t="inlineStr">
+        <is>
+          <t>二氧化矽作業勞工因作業環境不良，較易罹患的疾病是塵肺症。
+疾病相關重點
+塵肺症：長期吸入游離二氧化矽粉塵後，粉塵沉積在肺部引發肺部組織纖維化及發炎。
+常見症狀：呼吸喘、咳嗽以及多痰。
+常見高風險行業：礦工、窯業、陶瓷業、鑄造業及營建石作工人。
+NTNU</t>
+        </is>
+      </c>
+      <c r="I1117" s="2" t="inlineStr"/>
     </row>
     <row r="1118" ht="92.59999999999999" customHeight="1">
       <c r="A1118" s="2" t="n">
@@ -49799,8 +50239,17 @@
       <c r="G1118" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1118" s="2" t="n"/>
-      <c r="I1118" s="2" t="n"/>
+      <c r="H1118" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+暴露於 35℃ 以上的環境溫度時，對人體開始較會有熱蓄積危害（正確答案為 (C) 35℃）。
+重點說明
+35℃ 臨界點：當環境溫度高於 35℃ 時，人體皮膚與周遭環境的溫差縮小或逆轉，輻射與對流散熱效果大打折扣，主要靠汗液蒸發散熱。若濕度再增加，人體內便容易快速累積熱能，導致熱傷害。
+常見職業安全考題：此題為職業安全衛生業務主管等相關考試的常見物理性危害預防考題。
+iPEDIA 百科</t>
+        </is>
+      </c>
+      <c r="I1118" s="2" t="inlineStr"/>
     </row>
     <row r="1119" ht="92.59999999999999" customHeight="1">
       <c r="A1119" s="2" t="n">
@@ -49834,8 +50283,17 @@
       <c r="G1119" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H1119" s="2" t="n"/>
-      <c r="I1119" s="2" t="n"/>
+      <c r="H1119" s="2" t="inlineStr">
+        <is>
+          <t>勞工在無色無味的有害物質特性下進行作業是最危險的。
+為什麼「無色無味」最危險？
+無法自覺：勞工無法透過視覺（顏色）或嗅覺（氣味）察覺危害的存在。
+失去警覺：在毫無防備的情況下，勞工可能會吸入高濃度的有害氣體，導致急性中毒、窒息甚至死亡（例如常見的一氧化碳、氮氣或局限空間內的缺氧氣體）。
+延誤逃生：當身體出現症狀時，往往已經造成嚴重的生理傷害，錯失最佳逃生時機。
+相較之下，其他特性（如有色、有味）都能提供人體感官基本的「預警作用」，讓勞工能提早察覺異常並採取配戴防護具或撤離等應變措施。</t>
+        </is>
+      </c>
+      <c r="I1119" s="2" t="inlineStr"/>
     </row>
     <row r="1120" ht="92.59999999999999" customHeight="1">
       <c r="A1120" s="2" t="n">
@@ -49869,8 +50327,16 @@
       <c r="G1120" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1120" s="2" t="n"/>
-      <c r="I1120" s="2" t="n"/>
+      <c r="H1120" s="2" t="inlineStr">
+        <is>
+          <t>預防職業病最根本的措施為實施作業環境改善。
+說明
+根本預防：從源頭改善工作環境（如降低粉塵、噪音、改善通風與有害物質暴露），才能實質防止勞工受到危害。
+其他選項：雇用前體格檢查、定期健康檢查與特殊健康檢查屬於「健康管理」與「早期發現」的追蹤機制，並非最根本的源頭預防手段。
+育才國際文化事業有限公司</t>
+        </is>
+      </c>
+      <c r="I1120" s="2" t="inlineStr"/>
     </row>
     <row r="1121" ht="92.59999999999999" customHeight="1">
       <c r="A1121" s="2" t="n">
@@ -49904,8 +50370,18 @@
       <c r="G1121" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1121" s="2" t="n"/>
-      <c r="I1121" s="2" t="n"/>
+      <c r="H1121" s="2" t="inlineStr">
+        <is>
+          <t>答案為：(D) 暴露季節
+職業病判定要件說明
+判定是否為職業病（或職業性疾病），通常需要符合以下核心醫學與工作相關性原則：
+有害物確實存在：工作場所中確實有該種物理、化學或生物等有害因子。
+曾暴露於有害環境：勞工在工作中有實際接觸或暴露於該有害因子的紀錄。
+時序性（先後順序）：疾病發生的時間必須在接觸或暴露於有害因子之後，兩者具備合理的時間因果關係。
+「暴露季節」與職業病的成因、劑量及病理機制無直接關係，因此不屬於判定職業病的要件。</t>
+        </is>
+      </c>
+      <c r="I1121" s="2" t="inlineStr"/>
     </row>
     <row r="1122" ht="92.59999999999999" customHeight="1">
       <c r="A1122" s="2" t="n">
@@ -49939,8 +50415,19 @@
       <c r="G1122" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1122" s="2" t="n"/>
-      <c r="I1122" s="2" t="n"/>
+      <c r="H1122" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+起因與非職業原因有關非屬職業病的判定條件。
+職業病判定條件說明
+我國目前職業病必須由專家判定，其主要判定條件包含：
+工作場所中有害因子確實存在
+得病的人必須曾經在有害因子的環境下工作
+發病必須在接觸有害因子之後
+NTNU 若疾病的起因與非職業原因有關，則不符合職業病的因果關係判定。</t>
+        </is>
+      </c>
+      <c r="I1122" s="2" t="inlineStr"/>
     </row>
     <row r="1123" ht="92.59999999999999" customHeight="1">
       <c r="A1123" s="2" t="n">
@@ -49974,8 +50461,16 @@
       <c r="G1123" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H1123" s="2" t="n"/>
-      <c r="I1123" s="2" t="n"/>
+      <c r="H1123" s="2" t="inlineStr">
+        <is>
+          <t>人體中總體氧氣消耗量最大的器官是腦（佔基礎代謝與耗氧量約20%）。
+說明
+腦：雖然只佔成人體重的約2%，但靜止時的耗氧量卻佔了全身的20%左右，是對氧氣需求量極高且最不能缺氧的器官。
+選項比較：在常見的生物或生理學考題選項（肝臟、腎臟、腦、胃/心臟）中，大腦通常被視為整體耗氧或對氧需求最顯著的器官。
+元氣網</t>
+        </is>
+      </c>
+      <c r="I1123" s="2" t="inlineStr"/>
     </row>
     <row r="1124" ht="92.59999999999999" customHeight="1">
       <c r="A1124" s="2" t="n">
@@ -50009,8 +50504,12 @@
       <c r="G1124" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1124" s="2" t="n"/>
-      <c r="I1124" s="2" t="n"/>
+      <c r="H1124" s="2" t="inlineStr">
+        <is>
+          <t>Google AI 摘要未抓取到，請手動補充。</t>
+        </is>
+      </c>
+      <c r="I1124" s="2" t="inlineStr"/>
     </row>
     <row r="1125" ht="77.15000000000001" customHeight="1">
       <c r="A1125" s="2" t="n">
@@ -50044,8 +50543,16 @@
       <c r="G1125" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H1125" s="2" t="n"/>
-      <c r="I1125" s="2" t="n"/>
+      <c r="H1125" s="2" t="inlineStr">
+        <is>
+          <t>職業安全衛生法所稱具有危害性化學品，係指符合國家標準 CNS15030 分類之危險物或有害物。
+相關說明
+危險物：指符合國家標準 CNS15030 分類，具有物理性危害者。
+有害物：指符合國家標準 CNS15030 分類，具有健康危害者。
+GHS 制度：此標準配合我國實施之「化學品全球分類與標示調和制度（GHS）」，規範化學品之分類與標示。</t>
+        </is>
+      </c>
+      <c r="I1125" s="2" t="inlineStr"/>
     </row>
     <row r="1126" ht="92.59999999999999" customHeight="1">
       <c r="A1126" s="2" t="n">
@@ -50079,8 +50586,13 @@
       <c r="G1126" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H1126" s="2" t="n"/>
-      <c r="I1126" s="2" t="n"/>
+      <c r="H1126" s="2" t="inlineStr">
+        <is>
+          <t>勞工在坑內、儲槽、隧道等自然換氣不充分之場所工作，不得使用具有內燃機之機械，以避免排出之廢氣（如一氧化碳等）造成勞工窒息或中毒危害。
+正確答案為：具有內燃機之機械。</t>
+        </is>
+      </c>
+      <c r="I1126" s="2" t="inlineStr"/>
     </row>
     <row r="1127" ht="77.15000000000001" customHeight="1">
       <c r="A1127" s="2" t="n">
@@ -50114,8 +50626,19 @@
       <c r="G1127" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H1127" s="2" t="n"/>
-      <c r="I1127" s="2" t="n"/>
+      <c r="H1127" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+化學性有害物進入人體最常見的路徑是呼吸道。
+進入人體的主要路徑說明
+呼吸道：工作場所中的氣體、蒸氣、粉塵或霧滴等，最容易經由呼吸作用吸入肺部並快速進入血液循環，因此是最常見且最主要的路徑。
+皮膚：液體或固體化學物質接觸皮膚時可能被吸收，但機率通常低於吸入。
+口腔：經由誤食或飲食時沾染而進入，通常發生在衛生習慣不佳或意外情況下。
+眼睛：雖會造成局部刺激或傷害，但一般不是物質進入體內的主要吸收路徑。
+NTNU</t>
+        </is>
+      </c>
+      <c r="I1127" s="2" t="inlineStr"/>
     </row>
     <row r="1128" ht="92.59999999999999" customHeight="1">
       <c r="A1128" s="2" t="n">
@@ -50149,8 +50672,24 @@
       <c r="G1128" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H1128" s="2" t="n"/>
-      <c r="I1128" s="2" t="n"/>
+      <c r="H1128" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+水銀（汞）為可影響神經系統之危害因子。
+原因解析
+水銀（汞）：屬於神經毒性物質，會損害中樞及周邊神經系統，引發手足顫抖、記憶力衰退、情緒不穩等症狀。
+石綿：主要危害呼吸系統，易引起石綿肺症、肺癌及間皮細胞瘤。
+游離二氧化矽：主要危害呼吸系統，吸入過多會導致矽肺症（塵肺症）。
+鉻酸：具強烈腐蝕性與刺激性，主要危害皮膚、呼吸道黏膜，並可能具致癌性。
+環境部化學署
+若想了解更多職業衛生相關內容，可以告訴我你想針對：
+物理性危害因子（如噪音、輻射、振動）
+化學性危害因子（如有機溶劑、重金屬）
+職業安全衛生法規與題庫解析
+哪一部分進行補充？</t>
+        </is>
+      </c>
+      <c r="I1128" s="2" t="inlineStr"/>
     </row>
     <row r="1129" ht="92.59999999999999" customHeight="1">
       <c r="A1129" s="2" t="n">
@@ -50184,8 +50723,17 @@
       <c r="G1129" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H1129" s="2" t="n"/>
-      <c r="I1129" s="2" t="n"/>
+      <c r="H1129" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+甲醇對人體最主要的危害是中樞神經及視神經。
+危害重點說明
+中樞神經系統：甲醇進入人體後會被代謝成劇毒的甲酸（蟻酸），抑制中樞神經，導致頭暈、意識混亂、抽搐甚至昏迷。
+視神經：甲醇中毒會特別對視神經造成嚴重損傷，引發視力模糊、視野缺損，甚至永久失明。
+社團法人台灣醫事檢驗學會</t>
+        </is>
+      </c>
+      <c r="I1129" s="2" t="inlineStr"/>
     </row>
     <row r="1130" ht="108" customHeight="1">
       <c r="A1130" s="2" t="n">
@@ -50219,8 +50767,15 @@
       <c r="G1130" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H1130" s="2" t="n"/>
-      <c r="I1130" s="2" t="n"/>
+      <c r="H1130" s="2" t="inlineStr">
+        <is>
+          <t>依據《缺氧症預防規則》第21條之規定，正確答案為 1 人（應指派一人以上之監視人員）。
+法規條文：雇主使勞工從事缺氧危險作業時，應指派 1 人以上之監視人員，隨時監視作業狀況。
+職責說明：監視人員發覺有異常時，應即與缺氧作業主管及有關人員聯繫，並採取緊急措施。
+高雄市政府全球資訊網</t>
+        </is>
+      </c>
+      <c r="I1130" s="2" t="inlineStr"/>
     </row>
     <row r="1131" ht="123.45" customHeight="1">
       <c r="A1131" s="2" t="n">
@@ -50254,8 +50809,13 @@
       <c r="G1131" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H1131" s="2" t="n"/>
-      <c r="I1131" s="2" t="n"/>
+      <c r="H1131" s="2" t="inlineStr">
+        <is>
+          <t>從事缺氧危險作業時，應予 (A) 適當換氣，以保持該作業場所空氣含氧量 18% 以上。
+依據《缺氧症預防規則》第 5 條規定，雇主使勞工從事缺氧危險作業時，應採取通風換氣措施，維持氧氣濃度達 18% 以上，且換氣時不得使用純氧。</t>
+        </is>
+      </c>
+      <c r="I1131" s="2" t="inlineStr"/>
     </row>
     <row r="1132" ht="55" customHeight="1">
       <c r="A1132" s="2" t="n">
@@ -50290,8 +50850,18 @@
       <c r="G1132" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H1132" s="2" t="n"/>
-      <c r="I1132" s="2" t="n"/>
+      <c r="H1132" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+依據《缺氧症預防規則》規定，從事缺氧危險作業時，佩戴防毒面具（或醫療口罩）非屬應採取之設施。
+缺氧危險作業應備設施
+置備測定儀器：應置備測定空氣中氧氣濃度（及必要時有害氣體濃度）之測定儀器。
+實施通風換氣：應實施適當之通風換氣（禁止使用純氧進行換氣）。
+置備呼吸防護具：應置備空氣呼吸器、輸氣管面罩等裝備供勞工戴用。
+注意：防毒面具僅能過濾特定化學毒氣或粉塵，無法提供氧氣，在缺氧環境中佩戴防毒面具仍會導致缺氧窒息。</t>
+        </is>
+      </c>
+      <c r="I1132" s="2" t="inlineStr"/>
     </row>
     <row r="1133" ht="108" customHeight="1">
       <c r="A1133" s="2" t="n">
@@ -50325,8 +50895,15 @@
       <c r="G1133" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H1133" s="2" t="n"/>
-      <c r="I1133" s="2" t="n"/>
+      <c r="H1133" s="2" t="inlineStr">
+        <is>
+          <t>依缺氧症預防規則規定，地下室餐廳非為缺氧危險場所。
+相關說明
+供裝設電纜之人孔內部、置放木屑之倉庫內部及置放紙漿液之槽內部，因容易產生氧氣濃度不足之情形，皆屬於法規規範之缺氧危險場所。
+地下室餐廳屬於一般通風與營業場所，並不屬於缺氧危險場所。</t>
+        </is>
+      </c>
+      <c r="I1133" s="2" t="inlineStr"/>
     </row>
     <row r="1134" ht="108" customHeight="1">
       <c r="A1134" s="2" t="n">
@@ -50360,8 +50937,18 @@
       <c r="G1134" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H1134" s="2" t="n"/>
-      <c r="I1134" s="2" t="n"/>
+      <c r="H1134" s="2" t="inlineStr">
+        <is>
+          <t>作業工期及費用不屬於局限空間作業之危害防止計畫應訂定事項。
+局限空間危害防止計畫應訂定事項
+根據職業安全衛生設施規則規定，危害防止計畫應包含以下重點：
+危害確認：確認局限空間內的潛在危險（如缺氧、中毒、感電、爆炸等）安。
+濃度測定：測定氧氣、危險物及有害物濃度。
+通風換氣：訂定通風換氣的實施方式。
+作業許可：訂定人員進入作業的許可程序等相關安全措施。</t>
+        </is>
+      </c>
+      <c r="I1134" s="2" t="inlineStr"/>
     </row>
     <row r="1135" ht="108" customHeight="1">
       <c r="A1135" s="2" t="n">
@@ -50395,8 +50982,16 @@
       <c r="G1135" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1135" s="2" t="n"/>
-      <c r="I1135" s="2" t="n"/>
+      <c r="H1135" s="2" t="inlineStr">
+        <is>
+          <t>正確答案是 (D) 橋梁井式基礎內作業。
+答案解析
+缺氧危害通常發生在通風不良、密閉或半密閉的空間（如坑井、沉箱、隧道內部、井式基礎等），因為氧氣容易被消耗或被其他氣體取代。
+橋梁井式基礎內作業屬於侷限空間，深度較深且空氣流通困難，極易累積有害氣體或發生缺氧。
+其他選項如隧道洞口噴漿、鋼構建築物及鋼構建築焊接作業，通常處於開放或通風良好的環境，較不易發生缺氧危害。</t>
+        </is>
+      </c>
+      <c r="I1135" s="2" t="inlineStr"/>
     </row>
     <row r="1136" ht="108" customHeight="1">
       <c r="A1136" s="2" t="n">
@@ -50430,8 +51025,16 @@
       <c r="G1136" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H1136" s="2" t="n"/>
-      <c r="I1136" s="2" t="n"/>
+      <c r="H1136" s="2" t="inlineStr">
+        <is>
+          <t>錯誤的選項是使用防塵口罩。
+原因說明
+污水管道連接井屬於局限空間，作業時可能存在缺氧或硫化氫等有害氣體中毒的危險。
+防塵口罩只能阻擋粉塵，無法過濾有害氣體或提供氧氣，在缺氧或中毒環境中完全無防護效果。應依規定使用空氣呼吸器等適當的呼吸防護具。
+其他選項（佩戴背負式安全帶與防墜器、開啟前後人孔並通風、測定有害氣體濃度）皆為正確且規定的安全措施。</t>
+        </is>
+      </c>
+      <c r="I1136" s="2" t="inlineStr"/>
     </row>
     <row r="1137" ht="92.59999999999999" customHeight="1">
       <c r="A1137" s="2" t="n">
@@ -50465,8 +51068,16 @@
       <c r="G1137" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1137" s="2" t="n"/>
-      <c r="I1137" s="2" t="n"/>
+      <c r="H1137" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+從事水箱作業時，要有缺氧作業主管監督才可作業。
+相關說明
+水箱特性：水箱屬於密闭或通風不良的局域空間，容易產生缺氧環境，因此依規定需指派缺氧作業主管在場監督。
+主要職責：缺氧作業主管須在當班作業前確認換氣裝置、測定儀器與呼吸防護具等狀況，並決定作業方法及指揮勞工作業。</t>
+        </is>
+      </c>
+      <c r="I1137" s="2" t="inlineStr"/>
     </row>
     <row r="1138" ht="108" customHeight="1">
       <c r="A1138" s="2" t="n">
@@ -50500,8 +51111,14 @@
       <c r="G1138" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1138" s="2" t="n"/>
-      <c r="I1138" s="2" t="n"/>
+      <c r="H1138" s="2" t="inlineStr">
+        <is>
+          <t>勞工須從事局限空間作業時，雇主應派員使其接受缺氧作業主管安全衛生教育訓練。
+依據《職業安全衛生教育訓練規則》第11條規定，局限空間作業常伴隨空氣不流通及有害氣體蓄積之潛在危害，因此法規將其歸類並指定須接受缺氧作業主管安全衛生教育訓練（共計18小時）。
+中國勞工安全衛生管理學會</t>
+        </is>
+      </c>
+      <c r="I1138" s="2" t="inlineStr"/>
     </row>
     <row r="1139" ht="108" customHeight="1">
       <c r="A1139" s="2" t="n">
@@ -50527,8 +51144,15 @@
       <c r="G1139" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H1139" s="2" t="n"/>
-      <c r="I1139" s="2" t="n"/>
+      <c r="H1139" s="2" t="inlineStr">
+        <is>
+          <t>根據《缺氧症預防規則》，缺氧場所是指空氣中氧氣濃度未達 18%（0.18）的狀態。
+在法規定義中：
+缺氧：指空氣中氧氣濃度未達 18% 的狀態。
+缺氧危險作業：指前往缺氧場所從事之作業。</t>
+        </is>
+      </c>
+      <c r="I1139" s="2" t="inlineStr"/>
     </row>
     <row r="1140" ht="108" customHeight="1">
       <c r="A1140" s="2" t="n">
@@ -50562,8 +51186,19 @@
       <c r="G1140" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H1140" s="2" t="n"/>
-      <c r="I1140" s="2" t="n"/>
+      <c r="H1140" s="2" t="inlineStr">
+        <is>
+          <t>被撞不是局限空間可能的主要危害類型。
+局限空間主要危害類型說明
+依據《職業安全衛生設施規則》規定，雇主使勞工於局限空間從事作業前，應確認可能引起的危害包含：
+缺氧
+中毒
+感電
+塌陷、被夾、被捲、火災及爆炸等
+選項中的「缺氧」、「中毒」、「感電」皆屬法規規定的局限空間主要危害，僅「被撞」非其主要危害類型。</t>
+        </is>
+      </c>
+      <c r="I1140" s="2" t="inlineStr"/>
     </row>
     <row r="1141" ht="108" customHeight="1">
       <c r="A1141" s="2" t="n">
@@ -50597,8 +51232,17 @@
       <c r="G1141" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H1141" s="2" t="n"/>
-      <c r="I1141" s="2" t="n"/>
+      <c r="H1141" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+於缺氧（或缺氣）作業場所工作，應適合佩戴供氣式呼吸防護具。
+原因說明
+缺氧環境指空氣中氧氣濃度不足（通常低於18%），淨氣式防護具（如口罩、N95、濾毒罐）僅能過濾或吸附有害氣體與微粒，無法增加或提供氧氣。
+供氣式呼吸防護具能直接外接或自攜乾淨的呼吸空氣源，確保勞工在氧氣不足的環境中有足夠的氧氣可以呼吸。
+勞動部職業安全衛生署</t>
+        </is>
+      </c>
+      <c r="I1141" s="2" t="inlineStr"/>
     </row>
     <row r="1142" ht="92.59999999999999" customHeight="1">
       <c r="A1142" s="2" t="n">
@@ -50632,8 +51276,48 @@
       <c r="G1142" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1142" s="2" t="n"/>
-      <c r="I1142" s="2" t="n"/>
+      <c r="H1142" s="2" t="inlineStr">
+        <is>
+          <t>四用氣體偵測器無法偵測的氣體是氮氣。
+相關概念解析
+標準的四用氣體偵測器（四合一氣體偵測器）主要用來檢測密閉空間或局限空間作業時常見的四種危害氣體與指標：
+氧氣 (
+𝑂
+2
+𝑶
+𝟐
+)
+可燃性氣體 (
+𝐿
+𝐸
+𝐿
+𝑳
+𝑬
+𝑳
+)
+一氧化碳 (
+𝐶
+𝑂
+𝑪
+𝑶
+)
+硫化氫 (
+𝐻
+2
+𝑆
+𝑯
+𝟐
+𝑺
+)
+氮氣 (
+𝑁
+2
+𝑁
+2
+) 為空氣中主要的成分（約占 78%），本身無毒但過高會排擠氧氣造成缺氧，標準四用機並不具備直接針對氮氣濃度的專屬感測器；缺氧環境通常是藉由偵測氧氣濃度不足（未滿 18%）來判斷風險。</t>
+        </is>
+      </c>
+      <c r="I1142" s="2" t="inlineStr"/>
     </row>
     <row r="1143" ht="92.59999999999999" customHeight="1">
       <c r="A1143" s="2" t="n">
@@ -50667,8 +51351,12 @@
       <c r="G1143" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H1143" s="2" t="n"/>
-      <c r="I1143" s="2" t="n"/>
+      <c r="H1143" s="2" t="inlineStr">
+        <is>
+          <t>Google AI 摘要未抓取到，請手動補充。</t>
+        </is>
+      </c>
+      <c r="I1143" s="2" t="inlineStr"/>
     </row>
     <row r="1144" ht="108" customHeight="1">
       <c r="A1144" s="2" t="n">
@@ -50702,8 +51390,18 @@
       <c r="G1144" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1144" s="2" t="n"/>
-      <c r="I1144" s="2" t="n"/>
+      <c r="H1144" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+正確答案為 充分實施換氣。
+詳細說明
+充分實施換氣：正確。依據相關安全規則，機械換氣必須達到充分、有效程度，保持氧氣濃度在 18% 以上。
+使吸氣口接近排氣口：錯誤。吸氣口若接近排氣口會導致新鮮空氣直接被抽走，形成短路，無法有效更新作業場所內的空氣。
+使用純氧實施換氣：錯誤。嚴禁使用純氧換氣，因為高濃度氧氣極易引發火災與嚴重爆炸危險。
+不考慮換氣情形：錯誤。作業必須隨時檢視與考量換氣效果。</t>
+        </is>
+      </c>
+      <c r="I1144" s="2" t="inlineStr"/>
     </row>
     <row r="1145" ht="92.59999999999999" customHeight="1">
       <c r="A1145" s="2" t="n">
@@ -50737,8 +51435,13 @@
       <c r="G1145" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H1145" s="2" t="n"/>
-      <c r="I1145" s="2" t="n"/>
+      <c r="H1145" s="2" t="inlineStr">
+        <is>
+          <t>氣狀物質（如有害氣體、蒸氣）在職業安全衛生與空氣污染檢測中，其濃度通常以 (B) ppm（百萬分之一，體積濃度）作為主要表示單位。相較之下，粒狀物質（如粉塵、懸浮微粒）則常以 mg/m³（毫克／立方公尺，重量體積濃度）表示。
+勞工作業環境監測及暴露危害管理</t>
+        </is>
+      </c>
+      <c r="I1145" s="2" t="inlineStr"/>
     </row>
     <row r="1146" ht="108" customHeight="1">
       <c r="A1146" s="2" t="n">
@@ -50772,8 +51475,18 @@
       <c r="G1146" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H1146" s="2" t="n"/>
-      <c r="I1146" s="2" t="n"/>
+      <c r="H1146" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+在缺氧及高濃度有害物質作業場所，勞工應使用空氣呼吸器或輸氣管面罩等供氣式呼吸防護具。
+勞動部職業安全衛生署 原因說明
+防毒面罩屬於淨氣式防護具，僅能過濾特定有害氣體，無法增加氧氣濃度，因此絕對不能在缺氧環境中使用。
+氧氣呼吸器一般在缺氧或無火災爆炸之虞的特定場所雖有應用，但法規與實務上針對缺氧及立即危害高濃度有害物，主要標準配備與考題選用的供氣防護具為：
+空氣呼吸器（包含自給式空氣呼吸器 SCBA）
+輸氣管面罩（由外部安全氣源輸氣）</t>
+        </is>
+      </c>
+      <c r="I1146" s="2" t="inlineStr"/>
     </row>
     <row r="1147" ht="92.59999999999999" customHeight="1">
       <c r="A1147" s="2" t="n">
@@ -50807,8 +51520,17 @@
       <c r="G1147" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H1147" s="2" t="n"/>
-      <c r="I1147" s="2" t="n"/>
+      <c r="H1147" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+進入含氧氣3％室內作業場所，應配戴供氣式呼吸器。
+原因說明
+缺氧環境：空氣中含氧量僅剩 3％（正常大氣中氧氣約為 21％），屬於極度缺氧的立即致危環境。
+過濾式限制：一般防毒面具、防塵口罩等過濾式或淨氣式防護具無法增加氧氣，無法在缺氧環境中使用。
+正確選擇：必須使用能獨立供應外在新鮮空氣或氧氣的供氣式呼吸防護具（如輸氣管面罩、自攜式空氣呼吸器等）。</t>
+        </is>
+      </c>
+      <c r="I1147" s="2" t="inlineStr"/>
     </row>
     <row r="1148" ht="108" customHeight="1">
       <c r="A1148" s="2" t="n">
@@ -50842,8 +51564,18 @@
       <c r="G1148" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H1148" s="2" t="n"/>
-      <c r="I1148" s="2" t="n"/>
+      <c r="H1148" s="2" t="inlineStr">
+        <is>
+          <t>防護具之保管應儲放於 (C) 不受有害物汙染通風良好場所。
+正確答案解析
+正確選項：(C) 不受有害物汙染通風良好場所，以防止防護具變質、受損或殘留有害物質。
+錯誤原因：
+密閉櫃內：容易悶濕、滋生細菌或殘留異味（除非是專門乾燥通風的置物櫃，但一般密閉不通風處不宜）。
+日曬乾燥處所：陽光直射（紫外線）容易使橡膠、塑膠材質的防護具硬化、老化或脆化。
+高溫爐旁：高溫會直接融化或破壞防護具的材質。</t>
+        </is>
+      </c>
+      <c r="I1148" s="2" t="inlineStr"/>
     </row>
     <row r="1149" ht="92.59999999999999" customHeight="1">
       <c r="A1149" s="2" t="n">
@@ -50877,8 +51609,12 @@
       <c r="G1149" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1149" s="2" t="n"/>
-      <c r="I1149" s="2" t="n"/>
+      <c r="H1149" s="2" t="inlineStr">
+        <is>
+          <t>Google AI 摘要未抓取到，請手動補充。</t>
+        </is>
+      </c>
+      <c r="I1149" s="2" t="inlineStr"/>
     </row>
     <row r="1150" ht="108" customHeight="1">
       <c r="A1150" s="2" t="n">
@@ -50912,8 +51648,15 @@
       <c r="G1150" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H1150" s="2" t="n"/>
-      <c r="I1150" s="2" t="n"/>
+      <c r="H1150" s="2" t="inlineStr">
+        <is>
+          <t>依據中華民國《缺氧症預防規則》第 30 條規定，雇主使勞工戴用輸氣管面罩之連續作業時間，每次不得超過 1 小時（選項 C）。
+相關法規重點
+每次時間限制：不得超過 1 小時。
+休息與安全：每次作業完畢後應給予適當的休息時間，維護勞工健康與呼吸防護安全。</t>
+        </is>
+      </c>
+      <c r="I1150" s="2" t="inlineStr"/>
     </row>
     <row r="1151" ht="108" customHeight="1">
       <c r="A1151" s="2" t="n">
@@ -50949,8 +51692,20 @@
       <c r="G1151" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1151" s="2" t="n"/>
-      <c r="I1151" s="2" t="n"/>
+      <c r="H1151" s="2" t="inlineStr">
+        <is>
+          <t>下列何者為非的答案是 扭傷。
+Quizlet
+相關法規依據
+依據 勞動部之《缺氧症預防規則》第 31 條規定，雇主對從事缺氧危險作業之勞工，發生下列症狀時，應即由醫師診治：
+初期症狀：顏面蒼白或紅暈、脈搏及呼吸加快、呼吸困難、目眩或頭痛等。
+末期症狀：意識不明、痙攣、呼吸停止或心臟停止跳動等。
+其他：硫化氫、一氧化碳等其他有害物中毒症狀。
+「扭傷」屬於一般肌肉關節傷害，並非缺氧或有害物中毒之相關症狀。
+Quizlet</t>
+        </is>
+      </c>
+      <c r="I1151" s="2" t="inlineStr"/>
     </row>
     <row r="1152" ht="108" customHeight="1">
       <c r="A1152" s="2" t="n">
@@ -50984,8 +51739,15 @@
       <c r="G1152" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H1152" s="2" t="n"/>
-      <c r="I1152" s="2" t="n"/>
+      <c r="H1152" s="2" t="inlineStr">
+        <is>
+          <t>依據《職業安全衛生設施規則》第29-5條規定，其檢點紀錄應保存 3年。
+重點整理
+法規依據：職業安全衛生設施規則第29-5條。
+保存年限：應由專人辦理確認，其相關檢點與測定紀錄應保存 3年。</t>
+        </is>
+      </c>
+      <c r="I1152" s="2" t="inlineStr"/>
     </row>
     <row r="1153" ht="108" customHeight="1">
       <c r="A1153" s="2" t="n">
@@ -51019,8 +51781,20 @@
       <c r="G1153" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1153" s="2" t="n"/>
-      <c r="I1153" s="2" t="n"/>
+      <c r="H1153" s="2" t="inlineStr">
+        <is>
+          <t>下列何者為非：現場監視人員家裡住址。
+相關法規說明
+依據《職業安全衛生設施規則》第 29-2 條規定，雇主使勞工於局限空間從事作業，有危害勞工之虞時，應於作業場所入口顯而易見處所公告下列注意事項，以使作業勞工周知：
+作業有可能引起缺氧等危害時，應經許可始得進入之重要性
+進入該場所時應採取之措施
+事故發生時之緊急措施及緊急聯絡方式
+現場監視人員姓名
+其他作業安全應注意事項
+公告事項中並不包含「現場監視人員家裡住址」。</t>
+        </is>
+      </c>
+      <c r="I1153" s="2" t="inlineStr"/>
     </row>
     <row r="1154" ht="108" customHeight="1">
       <c r="A1154" s="2" t="n">
@@ -51055,8 +51829,13 @@
       <c r="G1154" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H1154" s="2" t="n"/>
-      <c r="I1154" s="2" t="n"/>
+      <c r="H1154" s="2" t="inlineStr">
+        <is>
+          <t>依據《職業安全衛生設施規則》第 19-1 條規定，局限空間之定義為：「非供勞工在其內部從事經常性作業，勞工進出方法受限制，且無法以自然通風來維持充分、清淨空氣之空間」。
+因此，選項中「無法與外面聯繫之場所」非為局限空間之法定定義。</t>
+        </is>
+      </c>
+      <c r="I1154" s="2" t="inlineStr"/>
     </row>
     <row r="1155" ht="92.59999999999999" customHeight="1">
       <c r="A1155" s="2" t="n">
@@ -51090,8 +51869,14 @@
       <c r="G1155" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H1155" s="2" t="n"/>
-      <c r="I1155" s="2" t="n"/>
+      <c r="H1155" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+應使用勞工配戴輸氣管面罩。
+依據《有機溶劑中毒預防規則》規定，於通風不充分之室內作業場所從事有機溶劑作業，若未設通風設備且作業時間短暫，雇主應使勞工佩戴輸氣管面罩。</t>
+        </is>
+      </c>
+      <c r="I1155" s="2" t="inlineStr"/>
     </row>
     <row r="1156" ht="108" customHeight="1">
       <c r="A1156" s="2" t="n">
@@ -51125,8 +51910,13 @@
       <c r="G1156" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H1156" s="2" t="n"/>
-      <c r="I1156" s="2" t="n"/>
+      <c r="H1156" s="2" t="inlineStr">
+        <is>
+          <t>下列何者非上述危害的答案是：墜落 (A)。
+依據《職業安全衛生設施規則》第 29-1 條規定，雇主使勞工於局限空間從事作業前，應先確認該空間內有無可能引起勞工缺氧、中毒、感電、塌陷、被夾、被捲及火災、爆炸等危害。選項中的「缺氣（缺氧）」、「中毒」及「感電」皆屬法規列舉之局限空間作業危害，唯獨「墜落」不在其中。</t>
+        </is>
+      </c>
+      <c r="I1156" s="2" t="inlineStr"/>
     </row>
     <row r="1157" ht="92.59999999999999" customHeight="1">
       <c r="A1157" s="2" t="n">
@@ -51160,8 +51950,15 @@
       <c r="G1157" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H1157" s="2" t="n"/>
-      <c r="I1157" s="2" t="n"/>
+      <c r="H1157" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+通風不充分之場所使用氬、二氧化碳或氦等從事熔接作業時，應予適當換氣，以保持作業場所空氣中氧氣濃度在百分之十八以上。
+正確答案為：(B) 適當換氣。
+根據勞動部《缺氧症預防規則》第9條規定：「雇主使勞工於儲槽、鍋爐或反應槽之內部或其他通風不充分之場所，使用氬、二氧化碳或氦等從事熔接作業時，應予適當換氣以保持作業場所空氣中氧氣濃度在百分之十八以上。」</t>
+        </is>
+      </c>
+      <c r="I1157" s="2" t="inlineStr"/>
     </row>
     <row r="1158" ht="92.59999999999999" customHeight="1">
       <c r="A1158" s="2" t="n">
@@ -51189,8 +51986,20 @@
       <c r="G1158" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H1158" s="2" t="n"/>
-      <c r="I1158" s="2" t="n"/>
+      <c r="H1158" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+依職業安全衛生設施規則規定，雇主對於廚房及餐廳，通風窗之面積不得少於總面積百分之 12（即選項中的 12）。
+相關法規重點
+法規依據：依據《職業安全衛生設施規則》第 322 條規定辦理。
+通風規範：廚房及餐廳的通風窗面積，不得少於總面積的 12%（百分之十二）。
+其他規定：餐廳與廚房應適當隔離，並設置穩妥有蓋之垃圾容器、適當排水設備以及防止病媒蚊蟲侵入之設備。
+查看完整條文內容於 勞動部。
+練習相關考古題與解析於 Yamol 題庫站。
+&lt;/Further Exploration&gt;</t>
+        </is>
+      </c>
+      <c r="I1158" s="2" t="inlineStr"/>
     </row>
     <row r="1159" ht="92.59999999999999" customHeight="1">
       <c r="A1159" s="2" t="n">
@@ -51224,8 +52033,16 @@
       <c r="G1159" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1159" s="2" t="n"/>
-      <c r="I1159" s="2" t="n"/>
+      <c r="H1159" s="2" t="inlineStr">
+        <is>
+          <t>有機溶劑不屬於物理性因子危害。
+危害因子分類說明
+物理性危害：指來自物理能量的危害，包含高溫（異常溫濕度）、噪音、振動及異常氣壓、輻射等。
+化學性危害：指化學物質所造成的危害，有機溶劑、粉塵、重金屬、一氧化碳等皆歸類在此類。
+考古豹</t>
+        </is>
+      </c>
+      <c r="I1159" s="2" t="inlineStr"/>
     </row>
     <row r="1160" ht="92.59999999999999" customHeight="1">
       <c r="A1160" s="2" t="n">
@@ -51259,8 +52076,17 @@
       <c r="G1160" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H1160" s="2" t="n"/>
-      <c r="I1160" s="2" t="n"/>
+      <c r="H1160" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+答案為 (A) 粉塵。
+說明
+粉塵：屬於化學性危害（或粒狀汙染物），因為它是固體微粒物質，透過呼吸道吸入對人體造成危害。
+高溫、輻射、噪音：均屬於能量形式的物理性危害。
+考古豹</t>
+        </is>
+      </c>
+      <c r="I1160" s="2" t="inlineStr"/>
     </row>
     <row r="1161" ht="92.59999999999999" customHeight="1">
       <c r="A1161" s="2" t="n">
@@ -51294,8 +52120,19 @@
       <c r="G1161" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H1161" s="2" t="n"/>
-      <c r="I1161" s="2" t="n"/>
+      <c r="H1161" s="2" t="inlineStr">
+        <is>
+          <t>下列何者非屬游離輻射？答案是紅外線。
+輻射簡單介紹
+游離輻射：能量較高，能使物質的原子或分子產生游離（電離）現象。包含：
+X射線
+中子射線
+α粒子（阿伐粒子）
+维基百科 非游離輻射：能量較低，無法引起物質的游離。包含紅外線、可見光、紫外線（部分低頻）、微波與無線電波等。
+考古豹</t>
+        </is>
+      </c>
+      <c r="I1161" s="2" t="inlineStr"/>
     </row>
     <row r="1162" ht="92.59999999999999" customHeight="1">
       <c r="A1162" s="2" t="n">
@@ -51329,8 +52166,39 @@
       <c r="G1162" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H1162" s="2" t="n"/>
-      <c r="I1162" s="2" t="n"/>
+      <c r="H1162" s="2" t="inlineStr">
+        <is>
+          <t>電磁波的能量與波長呈反比關係。
+相關原理解析
+核心公式：電磁波的光子能量公式為
+𝐸
+=
+ℎ
+𝑐
+𝜆
+（其中
+𝐸
+𝐸
+為能量，
+ℎ
+ℎ
+為普朗克常數，
+𝑐
+𝑐
+為光速，
+𝜆
+𝜆
+為波長）。
+波長與能量的變動：當波長
+𝜆
+𝜆
+愈長時，能量
+𝐸
+𝐸
+愈小；反之，波長愈短，頻率愈高，能量亦愈大。</t>
+        </is>
+      </c>
+      <c r="I1162" s="2" t="inlineStr"/>
     </row>
     <row r="1163" ht="92.59999999999999" customHeight="1">
       <c r="A1163" s="2" t="n">
@@ -51364,8 +52232,37 @@
       <c r="G1163" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H1163" s="2" t="n"/>
-      <c r="I1163" s="2" t="n"/>
+      <c r="H1163" s="2" t="inlineStr">
+        <is>
+          <t>電磁波的能量與頻率成正比。
+根據普朗克光量子假說，電磁波能量的計算公式為：
+𝐸
+=
+ℎ
+𝜈
+𝐸
+=
+ℎ
+𝜈
+𝐸
+𝐸
+代表能量
+ℎ
+ℎ
+代表普朗克常數（Planck constant）
+𝜈
+𝜈
+代表頻率
+當電磁波的頻率
+𝜈
+𝜈
+越高，其攜帶的能量
+𝐸
+𝐸
+就越大；反之，頻率越低，能量越小。</t>
+        </is>
+      </c>
+      <c r="I1163" s="2" t="inlineStr"/>
     </row>
     <row r="1164" ht="92.59999999999999" customHeight="1">
       <c r="A1164" s="2" t="n">
@@ -51399,8 +52296,31 @@
       <c r="G1164" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H1164" s="2" t="n"/>
-      <c r="I1164" s="2" t="n"/>
+      <c r="H1164" s="2" t="inlineStr">
+        <is>
+          <t>答案是：鉛（選項中通常為鉛，代號或位置依題目而定）。
+原因說明
+高原子序與高密度：鉛（Lead）的原子序（
+𝑍
+=
+8
+2
+）與密度（約
+1
+1
+.
+3
+4
+g
+/
+c
+m
+3
+）極高。
+電子交互作用強：游離輻射（如 X 射線或加馬射線）穿透物質時，主要靠物質內的電子來吸收與衰減能量。鉛含有大量電子，因此具備最好的阻擋與吸收效果。</t>
+        </is>
+      </c>
+      <c r="I1164" s="2" t="inlineStr"/>
     </row>
     <row r="1165" ht="92.59999999999999" customHeight="1">
       <c r="A1165" s="2" t="n">
@@ -51434,8 +52354,16 @@
       <c r="G1165" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H1165" s="2" t="n"/>
-      <c r="I1165" s="2" t="n"/>
+      <c r="H1165" s="2" t="inlineStr">
+        <is>
+          <t>從事游離輻射作業之勞工，特別需要定期接受甲狀腺檢查。
+相關說明
+甲狀腺功能：游離輻射容易影響內分泌系統，特別是甲狀腺，因此常被列為特別健康檢查或健康追蹤的重要項目之一。
+其他選項：心電圖、腎功能、聽力則是針對特定噪音、心血管或一般代謝作業的檢查項目，而非游離輻射特別指定的項目。
+臨場健康守護犬</t>
+        </is>
+      </c>
+      <c r="I1165" s="2" t="inlineStr"/>
     </row>
     <row r="1166" ht="92.59999999999999" customHeight="1">
       <c r="A1166" s="2" t="n">
@@ -51469,8 +52397,16 @@
       <c r="G1166" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1166" s="2" t="n"/>
-      <c r="I1166" s="2" t="n"/>
+      <c r="H1166" s="2" t="inlineStr">
+        <is>
+          <t>照明不是體外輻射防護的原則。
+體外輻射防護的核心為 TSD 三原則：
+高雄榮民總醫院全球資訊網 時間（Time）：儘可能縮短暴露在輻射中的時間。
+距離（Distance）：拉開與輻射源的距離，藉此降低劑量。
+屏蔽（Shielding）：利用適當的屏蔽材質（如鉛板、混凝土等）來阻擋輻射。</t>
+        </is>
+      </c>
+      <c r="I1166" s="2" t="inlineStr"/>
     </row>
     <row r="1167" ht="92.59999999999999" customHeight="1">
       <c r="A1167" s="2" t="n">
@@ -51504,8 +52440,16 @@
       <c r="G1167" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H1167" s="2" t="n"/>
-      <c r="I1167" s="2" t="n"/>
+      <c r="H1167" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+答案是 (A) 極低頻磁場。
+原因說明
+極低頻磁場：頻率極低（如電力頻率 60Hz），波長非常長，穿透力極強，幾乎無法被一般建築物（如鋼筋混凝土、磚牆）或樹木所屏蔽。
+紅外線、射頻輻射、微波：頻率較高，波長較短，相對容易受到建築物結構、金屬網或牆面的反射與阻擋（屏蔽）。</t>
+        </is>
+      </c>
+      <c r="I1167" s="2" t="inlineStr"/>
     </row>
     <row r="1168" ht="92.59999999999999" customHeight="1">
       <c r="A1168" s="2" t="n">
@@ -51539,8 +52483,17 @@
       <c r="G1168" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H1168" s="2" t="n"/>
-      <c r="I1168" s="2" t="n"/>
+      <c r="H1168" s="2" t="inlineStr">
+        <is>
+          <t>輻射源強度與距離之關係為距離二次方成反比。
+重點說明
+平方反比定律：當距離輻射源的距離增加一倍時，輻射強度會降為原本的四分之一；距離增加三倍，強度降為九分之一。
+輻射防護：這也是輻射防護三原則（時間、距離、屏蔽）中強調「拉開距離」能大幅降低輻射劑量的主要原因。
+Facebook
+·核安會 輻務小站</t>
+        </is>
+      </c>
+      <c r="I1168" s="2" t="inlineStr"/>
     </row>
     <row r="1169" ht="92.59999999999999" customHeight="1">
       <c r="A1169" s="2" t="n">
@@ -51574,8 +52527,16 @@
       <c r="G1169" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1169" s="2" t="n"/>
-      <c r="I1169" s="2" t="n"/>
+      <c r="H1169" s="2" t="inlineStr">
+        <is>
+          <t>答案是 (D) 電焊。
+原因說明
+電焊：電焊作業時會產生強烈的電弧光，其中包含大量的紫外線（UV）與紅外線等非游離輻射線，容易對眼睛（如電弧眼、結膜炎）及皮膚造成嚴重傷害。
+玻璃成型與熔鐵：主要產生的是紅外線與高熱（熱危害），紫外線相對較少。
+鍋爐房：主要屬於高溫作業環境的熱危害。</t>
+        </is>
+      </c>
+      <c r="I1169" s="2" t="inlineStr"/>
     </row>
     <row r="1170" ht="92.59999999999999" customHeight="1">
       <c r="A1170" s="2" t="n">
@@ -51609,8 +52570,74 @@
       <c r="G1170" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H1170" s="2" t="n"/>
-      <c r="I1170" s="2" t="n"/>
+      <c r="H1170" s="2" t="inlineStr">
+        <is>
+          <t>，請稍後再試。
+網頁搜尋結果
+應特別注意下列何種危害？ (A)紫外線(B)紅外線(C)雷射(D) ...
+› item-613.++使用一般殺菌燈時，應特...
+2022年12月11日 — 613. 使用一般殺菌燈時，應特別注意下列何種危害？ (A)紫外線 (B)紅外線 (C)雷射 (D)射頻輻射. 答案：登入後查看 統計： A(2590), B(208), C(19), D ...
+應特別注意下列何種危害？ (A)紫外線(B)紅外線(C)雷射(D) ...
+› item-613.+()+使用一般殺菌燈時，應...
+2020年1月21日 — 613. () 使用一般殺菌燈時，應特別注意下列何種危害？ (A)紫外線 (B)紅外線 (C)雷射 (D)射頻輻射. 答案：登入後查看 統計： A(1362), B(126), C(8), D ...
+紫外線消毒(殺菌)燈使用注意事項
+桃園市政府教育局
+› modules › tadnews
+應在無人、無動/植物的情況下使用。開燈後迅速離開消毒區域，避免受到紫外線輻射；並設定定時功能，且應於定時關閉後才能進入消毒區域。
+安心使用紫外線消毒燈你不可不知
+經濟部標準檢驗局
+› wSite
+2026年9月3日 — 五、對於固定式、移動式紫外線消毒燈，開燈後應迅速離開消毒區域，避免受到紫外線輻射，並設定定時功能，且應於定時關閉後才能進入消毒區域。 六、對於 ...
+缺少字詞： 特別 ‎紅外線 ‎雷 ‎射 ‎射頻
+使用紫外線消毒(殺菌)燈時，應注意以下事項 - 溪湖國小
+溪湖國小
+› posts
+使用紫外線消毒(殺菌)燈時，應注意以下事項： ... (一) 使用前應詳細閱讀產品說明書，並依說明書要求使用產品。 (二) 避免眼睛直視紫外線燈管或直接照射肌膚。 (三) 如產品 ...
+《小心紫外燈消毒的傷害》 #我們身體標準NPI防疫措施並沒有 ...
+Facebook · 黃軒醫師 Dr. Ooi Hean
+超過 150 個回應 · 4 年前
+UVB 導致DNA 損傷，並且是導致皮膚癌和白內障的危險。 UVA： UVA 輻射的危害性低於UVB 輻射，但有效殺其他 Coronavirus 像SARS 病毒方面也明顯（約1000 倍 ...
+缺少字詞： 應 ‎特別 ‎紅外線 ‎雷 ‎射 ‎射頻
+相關問題
+紫外線殺菌燈有哪些危害?
+紫外線殺菌燈有用嗎？
+紫外線燈可以每天用嗎？
+紫外線殺菌燈應該如何使用?
+網頁搜尋結果
+「紫外線消毒燈使用須知」宣導| 臺北市立第一女子高級中學
+北一女
+› news › 「紫外線消毒燈使用...
+(四)應在無人、無動/植物的情況下使用。開燈後迅速離開消毒區域，避免受到紫外線輻射；並設定定時功能，且應於定時關閉後才能進入消毒區域。
+專家觀點| 紫外線殺菌燈必知的安全隱憂
+UL Solutions Taiwan
+› Blog
+現階段，我們呼籲消費者必須正視紫外線消毒殺菌燈可能造成的危害，謹慎使用，避免自己和家人受到紫外線的輻射。尤其是有兒童，老人及特殊人群的家庭，甚至包括寵物，一旦 ...
+缺少字詞： 一般 ‎紅外線 ‎雷 ‎射 ‎射頻
+消毒靠紫外線？ 小細節不能忽視
+中華民國消費者文教基金會
+› product-detail-2598143
+2020年4月22日 — 光是以直線進行，且UVC穿透力較差，用於消毒時若被消毒的物品有重疊，被遮蔽的物品即無法有消毒的效果。舉例來說，若使用固定式的紫外線燈消毒室內，被 ...
+缺少字詞： 雷 ‎射
+頁面導覽
+1
+2
+3
+4
+5
+6
+7
+下一頁
+頁尾連結
+台灣
+708 臺南市安平區 - 根據你的 IP 位址
+- 更新位置
+說明
+提供意見
+隱私權
+服務條款</t>
+        </is>
+      </c>
+      <c r="I1170" s="2" t="inlineStr"/>
     </row>
     <row r="1171" ht="92.59999999999999" customHeight="1">
       <c r="A1171" s="2" t="n">
@@ -51644,8 +52671,15 @@
       <c r="G1171" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H1171" s="2" t="n"/>
-      <c r="I1171" s="2" t="n"/>
+      <c r="H1171" s="2" t="inlineStr">
+        <is>
+          <t>近紫外線除了會對皮膚造成傷害外，也常會對 眼球 造成傷害（如角膜炎、白內障等）。
+正確答案：(A) 眼球
+也常會對下列何種器官造成傷害？(A)眼球(B)肝臟(C)腎臟(D ...
+2018年10月1日 — 25.靠近紫外線除了會對皮膚造成傷害外，也常會對下列何種器官造成傷 害？(A)眼球(B)肝臟(C)腎臟(D)牙齒。 ... 26.下列何者不是體外輻射防護的原則？(A)時間( ...</t>
+        </is>
+      </c>
+      <c r="I1171" s="2" t="inlineStr"/>
     </row>
     <row r="1172" ht="92.59999999999999" customHeight="1">
       <c r="A1172" s="2" t="n">
@@ -51679,8 +52713,16 @@
       <c r="G1172" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H1172" s="2" t="n"/>
-      <c r="I1172" s="2" t="n"/>
+      <c r="H1172" s="2" t="inlineStr">
+        <is>
+          <t>非游離輻射中波長最短、能量最大者為(B) 紫外線。
+相關概念解析
+非游離輻射頻譜順序：按波長從長到短（或能量從弱到強）排列，依次為：微波、紅外線、可見光、紫外線。
+紫外線的特性：在常見的非游離輻射選項中，紫外線的波長最短，因此其頻率最高、能量最強，容易對人體的皮膚與眼睛（如引起角膜炎）造成傷害。
+非屬原子能游離輻射管制網</t>
+        </is>
+      </c>
+      <c r="I1172" s="2" t="inlineStr"/>
     </row>
     <row r="1173" ht="92.59999999999999" customHeight="1">
       <c r="A1173" s="2" t="n">
@@ -51714,8 +52756,18 @@
       <c r="G1173" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H1173" s="2" t="n"/>
-      <c r="I1173" s="2" t="n"/>
+      <c r="H1173" s="2" t="inlineStr">
+        <is>
+          <t>勞工於室外高溫作業環境工作，可能對身體產生的危害為 (C) 中暑。
+高溫作業的健康危害
+熱傷害：在高溫、高濕度或無風的環境下，人體排汗與散熱功能受阻，容易導致體溫調節失調，引發中暑、熱衰竭、熱痙攣等熱疾病。
+其他選項說明：
+塵肺症：屬於吸入粉塵（如二氧化矽）引起的肺部纖維化疾病，與高溫無直接關係。
+聽力損失：屬於長期暴露於高噪音環境下造成的職業病。
+下背痛：多與重物搬運、不良姿勢或長時間固定姿勢有關。</t>
+        </is>
+      </c>
+      <c r="I1173" s="2" t="inlineStr"/>
     </row>
     <row r="1174" ht="92.59999999999999" customHeight="1">
       <c r="A1174" s="2" t="n">
@@ -51749,8 +52801,15 @@
       <c r="G1174" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H1174" s="2" t="n"/>
-      <c r="I1174" s="2" t="n"/>
+      <c r="H1174" s="2" t="inlineStr">
+        <is>
+          <t>人體受熱最有效之降低熱蓄積方式為出汗。
+當人體受熱或處於高溫環境時，汗腺會分泌汗液，透過水分蒸發帶走大量的身體熱量，這是調節體溫、減少熱蓄積最主要且最有效的物理散熱機制。
+是否需要我為您補充更多職業安全衛生或熱危害預防的相關考題與觀念？
+一般甲業考題 - 何者為第一優先採行的措施？ 178. ( 2 ) 人體受熱最有效之降低熱蓄積方式，為下列何者？ ① 增加血液流速② 出汗③ 飲食④ 不要移動 179. ( 1 ) 在立健康工作環境時 ...</t>
+        </is>
+      </c>
+      <c r="I1174" s="2" t="inlineStr"/>
     </row>
     <row r="1175" ht="92.59999999999999" customHeight="1">
       <c r="A1175" s="2" t="n">
@@ -51784,8 +52843,15 @@
       <c r="G1175" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H1175" s="2" t="n"/>
-      <c r="I1175" s="2" t="n"/>
+      <c r="H1175" s="2" t="inlineStr">
+        <is>
+          <t>對於高溫作業勞工補充適量食鹽水可預防熱痙攣。
+原因說明
+熱痙攣（Heat cramp）：當勞工在高溫環境下大量流汗，身體流失大量水分與鹽分（電解質），若只補充純水而未補充適量電解質，容易造成電解質不平衡，進而引發肌肉強烈抽筋與疼痛。補充含鹽分的食鹽水可以有效預防此現象。
+勞動部職業安全衛生署</t>
+        </is>
+      </c>
+      <c r="I1175" s="2" t="inlineStr"/>
     </row>
     <row r="1176" ht="92.59999999999999" customHeight="1">
       <c r="A1176" s="2" t="n">
@@ -51819,8 +52885,13 @@
       <c r="G1176" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H1176" s="2" t="n"/>
-      <c r="I1176" s="2" t="n"/>
+      <c r="H1176" s="2" t="inlineStr">
+        <is>
+          <t>依據勞工作業環境監測實施辦法規定，高溫作業場所應每 3 個月監測綜合溫度熱指數一次以上。
+因此正確答案為：3 個月。</t>
+        </is>
+      </c>
+      <c r="I1176" s="2" t="inlineStr"/>
     </row>
     <row r="1177" ht="92.59999999999999" customHeight="1">
       <c r="A1177" s="2" t="n">
@@ -51854,8 +52925,13 @@
       <c r="G1177" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H1177" s="2" t="n"/>
-      <c r="I1177" s="2" t="n"/>
+      <c r="H1177" s="2" t="inlineStr">
+        <is>
+          <t>對於勞工作業受熱超過綜合溫度熱指數規定時，應優先採取 (B) 工程改善 措施。
+依據職業安全衛生相關法規與高溫作業勞工作息時間標準，當作業場所的綜合溫度熱指數（WBGT）超過規定標準時，雇主應從源頭及環境改善著手，優先以 工程改善（如設置隔熱、通風換氣、水霧降溫或遮陽等設施）來降低作業環境的溫度，其次再配合管理措施與個人防護（如多喝水、調整作息時間、教育訓練等）。</t>
+        </is>
+      </c>
+      <c r="I1177" s="2" t="inlineStr"/>
     </row>
     <row r="1178" ht="92.59999999999999" customHeight="1">
       <c r="A1178" s="2" t="n">
@@ -51889,8 +52965,16 @@
       <c r="G1178" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H1178" s="2" t="n"/>
-      <c r="I1178" s="2" t="n"/>
+      <c r="H1178" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+高溫作業環境可能造成物理性危害。
+危害說明
+物理性危害包含異常溫濕度（如高溫或低溫）、噪音、振動、游離輻射等。
+高溫危害會引起熱中暑、熱衰竭、熱痙攣或熱暈厥等熱傷害。</t>
+        </is>
+      </c>
+      <c r="I1178" s="2" t="inlineStr"/>
     </row>
     <row r="1179" ht="92.59999999999999" customHeight="1">
       <c r="A1179" s="2" t="n">
@@ -51924,8 +53008,16 @@
       <c r="G1179" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H1179" s="2" t="n"/>
-      <c r="I1179" s="2" t="n"/>
+      <c r="H1179" s="2" t="inlineStr">
+        <is>
+          <t>高溫作業場所應充份供應攝氏 15 度之飲水及食鹽。
+詳細說明
+飲水溫度：建議為約攝氏 10 至 15 度的清涼飲用水或含電解質飲料，以利勞工消暑並幫助身體吸收。
+補充原則：每 15 至 20 分鐘補充一次（每次約 150 至 200 毫升），並且應規律補充，不宜等到口渴才喝。必要時應準備食鹽供勞工適度補充鹽分。
+中華民國交通部公路局</t>
+        </is>
+      </c>
+      <c r="I1179" s="2" t="inlineStr"/>
     </row>
     <row r="1180" ht="92.59999999999999" customHeight="1">
       <c r="A1180" s="2" t="n">
@@ -51953,8 +53045,17 @@
       <c r="G1180" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1180" s="2" t="n"/>
-      <c r="I1180" s="2" t="n"/>
+      <c r="H1180" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+人工濕潤工作場所，濕球溫度超過攝氏 27 度時（選項D），應立即停止人工濕潤。
+相關法規規定
+依據 職業安全衛生設施規則 第 306 條規定：
+人工濕潤標準：作業上必須實施人工濕潤時，應使用清潔之水源噴霧。
+停止條件：濕球溫度超過攝氏 27度，或濕球與乾球溫度相差攝氏 1.4度 以下時，應立即停止人工濕潤。</t>
+        </is>
+      </c>
+      <c r="I1180" s="2" t="inlineStr"/>
     </row>
     <row r="1181" ht="108" customHeight="1">
       <c r="A1181" s="2" t="n">
@@ -51988,8 +53089,19 @@
       <c r="G1181" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H1181" s="2" t="n"/>
-      <c r="I1181" s="2" t="n"/>
+      <c r="H1181" s="2" t="inlineStr">
+        <is>
+          <t>下列耳塞佩戴方法中敘述錯誤的是 「可快速佩戴耳塞，不會掉落即可」（選項 C）。
+正確的耳塞佩戴觀念
+密合與效果：佩戴耳塞不能只求「不會掉落」，必須確實深入耳道並等待泡棉完全膨脹、與耳道密合，才能達到應有的隔音與聽力防護效果。
+正確步驟：
+搓揉壓縮：用食指與拇指將泡棉耳塞搓揉壓縮成細長條狀。
+提拉耳道：另一手繞過頭後向上向後拉提耳朵（例如戴右耳時用左手繞到腦後拉右耳），把彎曲的耳道拉直。
+置入與膨脹：將耳塞慢慢塞入耳道適當位置，並按住或等待其膨脹填滿耳道。
+笨象生活</t>
+        </is>
+      </c>
+      <c r="I1181" s="2" t="inlineStr"/>
     </row>
     <row r="1182" ht="92.59999999999999" customHeight="1">
       <c r="A1182" s="2" t="n">
@@ -52023,8 +53135,14 @@
       <c r="G1182" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1182" s="2" t="n"/>
-      <c r="I1182" s="2" t="n"/>
+      <c r="H1182" s="2" t="inlineStr">
+        <is>
+          <t>答案為：緊急應變計畫。
+說明
+依據《職業安全衛生設施規則》第 300-1 條規定，雇主對於噪音作業場所應採行的聽力保護措施與計畫內容，包含噪音監測及暴露評估、危害控制、防護具選用及佩戴、教育訓練、健康檢查與管理、成效評估與改善等。其中並不包含與噪音聽力保護無直接對應的「緊急應變計畫」。</t>
+        </is>
+      </c>
+      <c r="I1182" s="2" t="inlineStr"/>
     </row>
     <row r="1183" ht="92.59999999999999" customHeight="1">
       <c r="A1183" s="2" t="n">
@@ -52058,8 +53176,16 @@
       <c r="G1183" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H1183" s="2" t="n"/>
-      <c r="I1183" s="2" t="n"/>
+      <c r="H1183" s="2" t="inlineStr">
+        <is>
+          <t>作業場所高頻率噪音較易導致的症狀為聽力損失（選項 B）。
+相關說明
+聽力損失：高頻率噪音（或長期處於高分貝環境）最直接且容易對人體造成的職業傷害就是噪音性聽力損失，初期常表現為高頻聽力受損（例如聽不見蟲鳴鳥叫或高音調聲音）。
+其他選項如失眠、肺部疾病、腕道症候群，與高頻噪音的直接因果關聯較低。
+Occupational Safety and Health Administration (.gov)</t>
+        </is>
+      </c>
+      <c r="I1183" s="2" t="inlineStr"/>
     </row>
     <row r="1184" ht="92.59999999999999" customHeight="1">
       <c r="A1184" s="2" t="n">
@@ -52085,8 +53211,13 @@
       <c r="G1184" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1184" s="2" t="n"/>
-      <c r="I1184" s="2" t="n"/>
+      <c r="H1184" s="2" t="inlineStr">
+        <is>
+          <t>依職業安全衛生設施規則規定，對於勞工八小時日時量平均音壓級超過 85 分貝之噪音作業場所，應使勞工戴用有效之耳塞或耳罩。
+www.wphp.doctor 正確答案為：85。</t>
+        </is>
+      </c>
+      <c r="I1184" s="2" t="inlineStr"/>
     </row>
     <row r="1185" ht="92.59999999999999" customHeight="1">
       <c r="A1185" s="2" t="n">
@@ -52112,8 +53243,71 @@
       <c r="G1185" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H1185" s="2" t="n"/>
-      <c r="I1185" s="2" t="n"/>
+      <c r="H1185" s="2" t="inlineStr">
+        <is>
+          <t>，請稍後再試。
+網頁搜尋結果
+3.距離機械4 公尺處測得噪音為90 分貝，若另有一噪音量相同 ...
+› item-3.距離機械 +公尺處測得噪音...
+2024年5月29日 — 8.距某機械4公尺處測得噪音為90分貝，若另有一噪音量相同之機械併置一起，於原測量處測量噪音量約為多少分貝？(A)90(B)93(C)122(D)180。 #2892694 · 274.
+缺少字詞： 噪 ‎音
+若另有一噪音量相同之機械併置一起，於原測量處測量噪音約 ...
+› item-3.距離機械4+公尺處測得噪音為...
+2018年10月1日 — 8.距某機械4公尺處測得噪音為90分貝，若另有一噪音量相同之機械併置一起，於原測量處測量噪音量約為多少分貝？(A)90(B)93(C)122(D)180。
+乙級衛生管理員自學(考題練習50)
+› ... › 乙級職業安全衛生 自我學習
+2026年1月4日 — 距某機械4公尺處測得噪音為90分貝，若另有一噪音量相同之機械併置一起，於原測量處測量噪音量約為多少分貝？ ... (90 + 3 = 93)，因此正確答案是(2) 93.
+缺少字詞： 噪 ‎音
+距某機械4 公尺處測得噪音為90 分- 108年職業安全衛生附詳解
+刷題王
+› 距某機械-4-公尺處測得噪音為-9...
+距某機械4 公尺處測得噪音為90 分貝，若另有一噪音量相同之機械併置一起，於原測量處測量噪音量約為多少分貝？ A 90; B 93; C 96; D 120. 思路引導VIP. 當環境中的物理能量 ...
+缺少字詞： 噪 ‎| 必須包含以下字詞： 噪
+[題庫][職業安全衛生管理(乙)][03：專業課程] BLOCK 學習網
+BLOCK 學習網
+› question
+2 272. 距某機械4公尺處測得噪音為90分貝，若另有一噪音量相同之機械併置一起，於原測量處測量噪音量約為多少分貝？ A 90. B 92. C 93. D 180. 答案 ...
+缺少字詞： 噪 ‎| 必須包含以下字詞： 噪
+272. 距某機械4 公尺處測得噪音為90 分貝，若另有一噪音量 ...
+› item-272.+距某機械 +公尺處測得噪...
+2020年2月10日 — 272. 距某機械4 公尺處測得噪音為90 分貝，若另有一噪音量相同之機械併置 一起，於原測量處測量噪音量約為多少分貝？ (A)90 (B)92 (C)93 (D)180 。
+缺少字詞： 噪 ‎音
+距某機械4公尺處測得噪音為90分貝
+職業安全衛生管理證照題庫練習
+› content › qbDetail
+距某機械4公尺處測得噪音為90分貝，若另有一噪音量相同之機械併置一起，於原測量處測量噪音量約為多少分貝？ 做記號. 272 / 472. A 90; B 92; C 93; D 180. 答案：C
+1 個答案
+·
+最佳解答:
+正確答案：C。依照噪音相加公式 Lp= 10log(10^(L1/10) ^(L2/10)) = 10log(10^(90/10) ^(90/10)) =10log(2x10^(90/10)) =10log(2) log(10^(90/10) ...
+缺少字詞： 距離 ‎噪
+59 .距某機械4 公尺處測得噪音為90 分貝，若另有一噪音量 ...
+› item-59+.距某機械4+公尺處測得噪音...
+2014年7月23日 — 274.距某機械四公尺處測得噪音為90分貝，若有另一噪音量相同之機械併置一起，於原測量處測量音量約為多少分貝？(A)60(B)93(C)122(D)180。
+工作場所有2台相同機械，分別於4公尺遠處- 111年職業安全 ...
+刷題王
+› 工作場所有2台相同機械-分別於...
+工作場所有2台相同機械，分別於4公尺遠處測定噪音皆為90分貝，假設兩機械皆視為點音源，且置於同一處，則於相同距離之位置測定，其理論合成音壓級為多少分貝？
+缺少字詞： 噪 ‎| 必須包含以下字詞： 噪
+頁面導覽
+1
+2
+3
+4
+5
+6
+下一頁
+頁尾連結
+台灣
+708 臺南市安平區 - 根據你的 IP 位址
+- 更新位置
+說明
+提供意見
+隱私權
+服務條款</t>
+        </is>
+      </c>
+      <c r="I1185" s="2" t="inlineStr"/>
     </row>
     <row r="1186" ht="92.59999999999999" customHeight="1">
       <c r="A1186" s="2" t="n">
@@ -52139,8 +53333,17 @@
       <c r="G1186" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H1186" s="2" t="n"/>
-      <c r="I1186" s="2" t="n"/>
+      <c r="H1186" s="2" t="inlineStr">
+        <is>
+          <t>依據《職業安全衛生設施規則》第300條規定，工作場所因機械設備所發生之聲音超過 90 分貝時，雇主即應採取工程控制、減少勞工噪音暴露時間。
+正確答案為：90 分貝。
+重點整理
+超過 90 分貝：雇主應採取工程控制與減少暴露時間。
+超過 85 分貝（或暴露劑量超過 50%）：雇主應使勞工佩戴有效的耳塞、耳罩等防音防護具。
+極限限制：任何時間不得暴露於峰值超過 140 分貝之衝擊性噪音或 115 分貝之連續性噪音。</t>
+        </is>
+      </c>
+      <c r="I1186" s="2" t="inlineStr"/>
     </row>
     <row r="1187" ht="92.59999999999999" customHeight="1">
       <c r="A1187" s="2" t="n">
@@ -52166,8 +53369,17 @@
       <c r="G1187" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H1187" s="2" t="n"/>
-      <c r="I1187" s="2" t="n"/>
+      <c r="H1187" s="2" t="inlineStr">
+        <is>
+          <t>依職業安全衛生設施規則規定，噪音超過 90分貝 之工作場所，雇主應標示並公告噪音危害之預防事項，使勞工周知。故正確答案為 90。
+相關噪音規定重點
+90分貝以上：工作場所應標示並公告噪音危害預防事項，且為每日8小時容許暴露基準。
+85分貝以上：勞工8小時日時量平均音壓級超過85分貝時，雇主應採取聽力保護措施（如提供防音防護具、實施噪音監測與教育訓練等）。
+極限限制：任何時間不得暴露於峰值超過140分貝之衝擊性噪音或115分貝之連續性噪音。
+勞工作業環境監測及暴露危害管理</t>
+        </is>
+      </c>
+      <c r="I1187" s="2" t="inlineStr"/>
     </row>
     <row r="1188" ht="92.59999999999999" customHeight="1">
       <c r="A1188" s="2" t="n">
@@ -52193,8 +53405,16 @@
       <c r="G1188" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H1188" s="2" t="n"/>
-      <c r="I1188" s="2" t="n"/>
+      <c r="H1188" s="2" t="inlineStr">
+        <is>
+          <t>依據《職業安全衛生設施規則》規定，勞工工作場所噪音音壓級為 90 分貝時，工作日容許暴露時間最多為 8 小時。
+重點整理
+90 分貝：工作日容許暴露時間為 8 小時（對應法規中的基準日時量平均音壓級）。
+防護措施：若 8 小時日時量平均音壓級超過 85 分貝，雇主就必須讓勞工佩戴耳塞或耳罩等防音防護具。
+詳細考古題與法規對照可參考 。</t>
+        </is>
+      </c>
+      <c r="I1188" s="2" t="inlineStr"/>
     </row>
     <row r="1189" ht="92.59999999999999" customHeight="1">
       <c r="A1189" s="2" t="n">
@@ -52220,8 +53440,22 @@
       <c r="G1189" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H1189" s="2" t="n"/>
-      <c r="I1189" s="2" t="n"/>
+      <c r="H1189" s="2" t="inlineStr">
+        <is>
+          <t>勞工工作場所噪音音壓級為95分貝時，工作日容許暴露時間最多為 4 小時。
+Facebook
+·職業傷病服務網
+噪音暴露標準
+依據 職業安全衛生設施規則 規定，我國採用 5分貝交換率（噪音每增加5分貝，容許暴露時間減半）：
+www.wphp.doctor 90分貝：容許暴露時間為 8 小時
+95分貝：容許暴露時間為 4 小時
+100分貝：容許暴露時間為 2 小時
+105分貝：容許暴露時間為 0.5（半）小時
+Facebook
+·職業傷病服務網</t>
+        </is>
+      </c>
+      <c r="I1189" s="2" t="inlineStr"/>
     </row>
     <row r="1190" ht="92.59999999999999" customHeight="1">
       <c r="A1190" s="2" t="n">
@@ -52247,8 +53481,20 @@
       <c r="G1190" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H1190" s="2" t="n"/>
-      <c r="I1190" s="2" t="n"/>
+      <c r="H1190" s="2" t="inlineStr">
+        <is>
+          <t>我國職業安全衛生法規（依據職業安全衛生設施規則第300條）規定，噪音每增加 5 分貝，勞工容許暴露時間即減半（即5分貝交換率）。
+重點整理
+交換率：5 分貝
+www.wphp.doctor
+標準範例：
+90 分貝：容許暴露時間為 8 小時
+95 分貝：容許暴露時間為 4 小時
+100 分貝：容許暴露時間為 2 小時
+www.wphp.doctor</t>
+        </is>
+      </c>
+      <c r="I1190" s="2" t="inlineStr"/>
     </row>
     <row r="1191" ht="92.59999999999999" customHeight="1">
       <c r="A1191" s="2" t="n">
@@ -52274,8 +53520,16 @@
       <c r="G1191" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1191" s="2" t="n"/>
-      <c r="I1191" s="2" t="n"/>
+      <c r="H1191" s="2" t="inlineStr">
+        <is>
+          <t>依職業安全衛生設施規則規定，勞工暴露衝擊性噪音峰值不得超過 140 分貝（選項 D）。
+勞工作業環境監測及暴露危害管理 根據《職業安全衛生設施規則》第 300 條規定：
+衝擊性噪音峰值上限：任何時間不得超過 140 分貝。
+連續性噪音上限：任何時間不得超過 115 分貝。
+勞工作業環境監測及暴露危害管理</t>
+        </is>
+      </c>
+      <c r="I1191" s="2" t="inlineStr"/>
     </row>
     <row r="1192" ht="92.59999999999999" customHeight="1">
       <c r="A1192" s="2" t="n">
@@ -52303,8 +53557,17 @@
       <c r="G1192" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H1192" s="2" t="n"/>
-      <c r="I1192" s="2" t="n"/>
+      <c r="H1192" s="2" t="inlineStr">
+        <is>
+          <t>依據職業安全衛生設施規則第300條規定，勞工暴露連續性噪音峰值不得超過 115 分貝（衝擊性噪音則不得超過 140 分貝）。因此正確答案為 115。
+重點整理
+連續性噪音上限：任何時間不得超過 115 分貝。
+衝擊性噪音上限：任何時間不得超過 140 分貝。
+85分貝：8小時日時量平均音壓級超過此數值時，雇主應使勞工佩戴防音防護具或採取聽力保護措施。
+90分貝：8小時日時量平均音壓級的容許基準起點，超過時應採取工程控制與減少暴露時間。</t>
+        </is>
+      </c>
+      <c r="I1192" s="2" t="inlineStr"/>
     </row>
     <row r="1193" ht="92.59999999999999" customHeight="1">
       <c r="A1193" s="2" t="n">
@@ -52338,8 +53601,18 @@
       <c r="G1193" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H1193" s="2" t="n"/>
-      <c r="I1193" s="2" t="n"/>
+      <c r="H1193" s="2" t="inlineStr">
+        <is>
+          <t>人耳對於 2000～4000 Hz（赫茲）的聲音頻率最為敏感。
+Facebook
+·婦聯聽覺健康基金會
+聲音頻率與人耳聽覺
+最敏感區間：2000～4000 Hz。這與外耳道的共振頻率有關，因此人耳在這個頻段聽覺閾值最低、最容易察覺聲音。
+整體聽覺範圍：人耳可以聽到的頻率大約介於 20～20000 Hz 之間。
+語言頻率區間：人類日常談話的語音頻率主要分布在 500～2000 Hz 左右。</t>
+        </is>
+      </c>
+      <c r="I1193" s="2" t="inlineStr"/>
     </row>
     <row r="1194" ht="92.59999999999999" customHeight="1">
       <c r="A1194" s="2" t="n">
@@ -52365,8 +53638,17 @@
       <c r="G1194" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H1194" s="2" t="n"/>
-      <c r="I1194" s="2" t="n"/>
+      <c r="H1194" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+人耳可聽見之聲音頻率下限大致為 20 Hz。
+聲音頻率範圍
+聽覺範圍：正常人耳能聽到的聲音頻率大約是 20 Hz 到 20,000 Hz。
+次聲波：低於 20 Hz 的聲音稱為次聲波，人耳聽不見。
+超音波：高於 20,000 Hz 的聲音稱為超音波（或超聲波），人耳也聽不見。</t>
+        </is>
+      </c>
+      <c r="I1194" s="2" t="inlineStr"/>
     </row>
     <row r="1195" ht="92.59999999999999" customHeight="1">
       <c r="A1195" s="2" t="n">
@@ -52392,8 +53674,21 @@
       <c r="G1195" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H1195" s="2" t="n"/>
-      <c r="I1195" s="2" t="n"/>
+      <c r="H1195" s="2" t="inlineStr">
+        <is>
+          <t>人耳可聽見之聲音頻率上限大致為 20,000 Hz。
+Facebook
+·婦聯聽覺健康基金會
+聽覺頻率範圍
+人類聽力範圍：正常人耳能聽到大約 20 Hz 至 20,000 Hz 的聲音。
+頻率上限與下限：
+低於 20 Hz 的聲音稱為次聲波，人耳聽不見。
+高於 20,000 Hz 的聲音稱為超聲波（或超音波），人耳也聽不見。
+翰林雲端學院 個體差異：隨著年齡增長或聽力受損，人耳對高頻聲音的敏感度會逐漸降低，聽力上限會下降。
+维基百科</t>
+        </is>
+      </c>
+      <c r="I1195" s="2" t="inlineStr"/>
     </row>
     <row r="1196" ht="92.59999999999999" customHeight="1">
       <c r="A1196" s="2" t="n">
@@ -52419,8 +53714,17 @@
       <c r="G1196" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1196" s="2" t="n"/>
-      <c r="I1196" s="2" t="n"/>
+      <c r="H1196" s="2" t="inlineStr">
+        <is>
+          <t>一旦發生噪音性聽力損失，最先發生且最明顯的聲音頻率是 4000 Hz。
+噪音性聽力損失的特徵
+4000 Hz 凹陷：在聽力檢查的聽力圖（Audiogram）上，早期最典型的特徵是在高音頻區的 3000、4000 與 6000 Hz 產生聽力凹陷（notch），其中又以 4000 Hz 最為嚴重和常見。
+高頻先受損：耳蝸對高頻聲音的感覺細胞比低頻更容易受到強烈噪音的破壞。
+高低頻差異：初期時，低頻區（如 500、1000、2000 Hz）的聽力通常保持得相對正常，受損主要集中在高頻。
+雲林縣政府全球資訊網</t>
+        </is>
+      </c>
+      <c r="I1196" s="2" t="inlineStr"/>
     </row>
     <row r="1197" ht="92.59999999999999" customHeight="1">
       <c r="A1197" s="2" t="n">
@@ -52454,8 +53758,22 @@
       <c r="G1197" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H1197" s="2" t="n"/>
-      <c r="I1197" s="2" t="n"/>
+      <c r="H1197" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+防止噪音危害之治本對策為消除發生源。
+相關對策解析
+治本對策：
+消除發生源：從根本上移除、更換或改善會產生噪音的機械設備與作業流程（如汰換老舊機械、改善減振設計、加強隔音），直接降低或消除噪音。
+勞動部職業安全衛生署
+治標或輔助對策：
+使用耳塞、耳罩：屬於個人防護具，為最後防線（治標而非治本）。
+實施職業安全衛生教育訓練：增進工作者安全衛生知能，建立正確防護觀念。
+實施特殊健康檢查：用於追蹤與評估健康狀況，屬於事後健康管理。
+全民勞教e網</t>
+        </is>
+      </c>
+      <c r="I1197" s="2" t="inlineStr"/>
     </row>
     <row r="1198" ht="92.59999999999999" customHeight="1">
       <c r="A1198" s="2" t="n">
@@ -52489,8 +53807,18 @@
       <c r="G1198" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H1198" s="2" t="n"/>
-      <c r="I1198" s="2" t="n"/>
+      <c r="H1198" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+評估噪音對人耳之聽力危害與健康影響時，應使用 A 權衡電網（A-weighting）。
+各權衡電網之用途與特性
+A 權衡電網 (A)：模擬人耳在一般日常或工作音量下的聽覺反應，對低頻較不敏感、對中高頻較敏感，其量測結果最符合人耳聽覺的主觀感受，為評估聽力危害與職業環境噪音的標準選擇。
+B 權衡電網 (B)：模擬中等音量下的聽覺反應，現今極少在一般噪音量測中使用。
+C 權衡電網 (C)：模擬高音量下的聽覺反應，對全頻段較為平坦，常應用於高音量機械噪音或評估耳罩等防音防護具性能。
+D 權衡電網 (D)：專門用來評估極高音量之特殊噪音，例如飛機起降等航空噪音。</t>
+        </is>
+      </c>
+      <c r="I1198" s="2" t="inlineStr"/>
     </row>
     <row r="1199" ht="92.59999999999999" customHeight="1">
       <c r="A1199" s="2" t="n">
@@ -52524,8 +53852,25 @@
       <c r="G1199" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1199" s="2" t="n"/>
-      <c r="I1199" s="2" t="n"/>
+      <c r="H1199" s="2" t="inlineStr">
+        <is>
+          <t>頻譜分析儀（Frequency Analyzer / Spectrum Analyzer）可用來測定噪音之頻率分佈範圍。
+相關儀器功能簡介
+頻譜分析儀：用來分析聲音在不同頻率（如倍頻程或1/3倍頻程）下的能量分佈狀況。
+噪音計（Sound Level Meter）：主要用來測定特定時間內的瞬時音壓位準或均能音量（
+𝐿
+𝑒
+𝑞
+𝐿
+𝑒
+𝑞
+），無法直接詳細解析各頻率的分部範圍。
+噪音劑量計（Noise Dosimeter）：用來累積記錄勞工在一段工作時間內（如8小時）的總噪音暴露劑量。
+噪音校正器（Sound Calibrator）：用在測量前、後檢查與校正噪音計或噪音劑量計的準確度，不具備測量功能。
+勞動及職業安全衛生研究所</t>
+        </is>
+      </c>
+      <c r="I1199" s="2" t="inlineStr"/>
     </row>
     <row r="1200" ht="92.59999999999999" customHeight="1">
       <c r="A1200" s="2" t="n">
@@ -52559,8 +53904,17 @@
       <c r="G1200" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H1200" s="2" t="n"/>
-      <c r="I1200" s="2" t="n"/>
+      <c r="H1200" s="2" t="inlineStr">
+        <is>
+          <t>答案是 (A) A 權衡電網。
+詳細說明
+A權衡電網 (A-weighting)：模擬人耳在一般低音量或日常環境下的聽覺反應，對低頻和極高頻的靈敏度較低、對中高頻較敏感。它與人耳的真實聽覺感應最接近，因此成為目前環保及職業衛生法規中最常用的標準量測設定。
+B權衡電網：模擬中等音量感受，目前極少使用。
+C權衡電網：模擬高音量（很大聲）時的聽覺反應，對全頻段較為平直，常用於高噪音或機械性能評估。
+D權衡電網：專門用於飛機噪音等特定高噪音評估。</t>
+        </is>
+      </c>
+      <c r="I1200" s="2" t="inlineStr"/>
     </row>
     <row r="1201" ht="92.59999999999999" customHeight="1">
       <c r="A1201" s="2" t="n">
@@ -52586,8 +53940,17 @@
       <c r="G1201" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1201" s="2" t="n"/>
-      <c r="I1201" s="2" t="n"/>
+      <c r="H1201" s="2" t="inlineStr">
+        <is>
+          <t>對於勞工八小時日時量平均音壓級超過 85 分貝之工作場所，雇主應使勞工戴用有效之耳塞、耳罩等防音防護具。
+相關法規規定
+法規依據：依據《職業安全衛生設施規則》第300條規定辦理。
+標準值：當勞工八小時日時量平均音壓級超過 85分貝（或暴露劑量超過50%）時，雇主即應提供並強制勞工配戴有效的防音防護具（如耳塞、耳罩）。
+噪音標示：若機械設備所發出的聲音超過 90分貝 的工作場所，雇主應標示並公告噪音危害預防事項。
+勞工作業環境監測及暴露危害管理</t>
+        </is>
+      </c>
+      <c r="I1201" s="2" t="inlineStr"/>
     </row>
     <row r="1202" ht="92.59999999999999" customHeight="1">
       <c r="A1202" s="2" t="n">
@@ -52615,8 +53978,17 @@
       <c r="G1202" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H1202" s="2" t="n"/>
-      <c r="I1202" s="2" t="n"/>
+      <c r="H1202" s="2" t="inlineStr">
+        <is>
+          <t>依據《職業安全衛生設施規則》第300條規定，工作場所因機械設備所發生之聲音超過 90分貝 時，雇主即應採取工程控制、減少勞工噪音暴露時間。
+正確答案為：(B) 90。
+相關法規重點
+超過 90 分貝：雇主應採取工程控制、減少勞工噪音暴露時間，使8小時日時量平均音壓級符合容許暴露標準。
+超過 85 分貝（或暴露劑量超過50%）：雇主應使勞工佩戴有效之耳塞、耳罩等防音防護具，並採取聽力保護措施。
+極限限制：任何時間不得暴露於峰值超過 140 分貝之衝擊性噪音或 115 分貝之連續性噪音。</t>
+        </is>
+      </c>
+      <c r="I1202" s="2" t="inlineStr"/>
     </row>
     <row r="1203" ht="92.59999999999999" customHeight="1">
       <c r="A1203" s="2" t="n">
@@ -52642,8 +54014,12 @@
       <c r="G1203" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1203" s="2" t="n"/>
-      <c r="I1203" s="2" t="n"/>
+      <c r="H1203" s="2" t="inlineStr">
+        <is>
+          <t>Google AI 摘要未抓取到，請手動補充。</t>
+        </is>
+      </c>
+      <c r="I1203" s="2" t="inlineStr"/>
     </row>
     <row r="1204" ht="92.59999999999999" customHeight="1">
       <c r="A1204" s="2" t="n">
@@ -52677,8 +54053,18 @@
       <c r="G1204" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H1204" s="2" t="n"/>
-      <c r="I1204" s="2" t="n"/>
+      <c r="H1204" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+人體對高頻噪音的聽力損失最敏感。
+虎科電機系網
+聽力與頻率的關係
+高頻較敏感：人耳對於不同頻率聲音的感受度不同，通常對高頻音較為敏銳，因此由噪音引起的聽力損失也最容易由高頻開始，常在 4000 Hz 左右最先發生。
+低頻較不敏感：人類聽覺系統對低頻或超低頻聲音的感知閾值較高，因此較不敏感。
+環保資訊月刊</t>
+        </is>
+      </c>
+      <c r="I1204" s="2" t="inlineStr"/>
     </row>
     <row r="1205" ht="92.59999999999999" customHeight="1">
       <c r="A1205" s="2" t="n">
@@ -52712,8 +54098,17 @@
       <c r="G1205" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H1205" s="2" t="n"/>
-      <c r="I1205" s="2" t="n"/>
+      <c r="H1205" s="2" t="inlineStr">
+        <is>
+          <t>感音性聽力損失（題目中的「威音性」應為「感音性」之筆誤）主要是因為內耳受損所導致。
+聽力損失的分類與受損部位
+感音性聽力損失：由內耳的聽覺感覺器官（如耳蝸內的毛細胞）或聽神經受損引起。
+傳導性（傳音性）聽力損失：由外耳或中耳受損或阻塞，導致聲音無法順利傳遞所造成。
+耳殼：主要負責收集聲音，其本身的問題不直接歸類為聽力損失的主因。
+科林助聽器</t>
+        </is>
+      </c>
+      <c r="I1205" s="2" t="inlineStr"/>
     </row>
     <row r="1206" ht="92.59999999999999" customHeight="1">
       <c r="A1206" s="2" t="n">
@@ -52741,8 +54136,12 @@
       <c r="G1206" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1206" s="2" t="n"/>
-      <c r="I1206" s="2" t="n"/>
+      <c r="H1206" s="2" t="inlineStr">
+        <is>
+          <t>Google AI 摘要未抓取到，請手動補充。</t>
+        </is>
+      </c>
+      <c r="I1206" s="2" t="inlineStr"/>
     </row>
     <row r="1207" ht="92.59999999999999" customHeight="1">
       <c r="A1207" s="2" t="n">
@@ -52776,8 +54175,16 @@
       <c r="G1207" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H1207" s="2" t="n"/>
-      <c r="I1207" s="2" t="n"/>
+      <c r="H1207" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+傳音性（傳導性）聽力損失主要是因為外耳或中耳受損所導致。
+說明
+外耳或中耳受損：當外耳（如耳道阻塞、耳垢栓塞）或中耳（如中耳炎、耳膜穿孔、聽小骨斷裂）發生問題時，聲音的能量無法順利傳遞到內耳，因而造成傳音性聽力損失。
+選項比較：在常見的生物學分類中，此狀況涵蓋外耳與中耳（若為單一選項對應，題目通常指向外耳或中耳的結構障礙，內耳受損則多屬於感音神經性聽力損失）。</t>
+        </is>
+      </c>
+      <c r="I1207" s="2" t="inlineStr"/>
     </row>
     <row r="1208" ht="92.59999999999999" customHeight="1">
       <c r="A1208" s="2" t="n">
@@ -52803,8 +54210,13 @@
       <c r="G1208" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H1208" s="2" t="n"/>
-      <c r="I1208" s="2" t="n"/>
+      <c r="H1208" s="2" t="inlineStr">
+        <is>
+          <t>勞工噪音暴露工作日 8 小時日時量平均不得超過 90 分貝。因此正確答案為 90。
+依據《職業安全衛生設施規則》第 300 條規定，工作場所因機械設備產生的聲音超過 90 分貝時，雇主應採取工程控制或減少暴露時間，使 8 小時日時量平均音壓級不超過 90 分貝。</t>
+        </is>
+      </c>
+      <c r="I1208" s="2" t="inlineStr"/>
     </row>
     <row r="1209" ht="92.59999999999999" customHeight="1">
       <c r="A1209" s="2" t="n">
@@ -52830,8 +54242,33 @@
       <c r="G1209" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H1209" s="2" t="n"/>
-      <c r="I1209" s="2" t="n"/>
+      <c r="H1209" s="2" t="inlineStr">
+        <is>
+          <t>答案是 90 分貝。
+說明與公式換算
+根據我國《職業安全衛生設施規則》第 300 條規定，勞工工作日 8 小時的噪音容許暴露標準為 90 分貝（dBA）。
+當噪音暴露劑量（D）等於 100% 時，代表勞工已達到當日法規容許的暴露上限。我們也可以透過「五分貝原則」的八小時日時量平均音壓級（TWA）公式來進行驗證：
+勞動及職業安全衛生研究所 TWA
+=
+16.61
+×
+log
+10
+(
+𝐷
+100
+)
++
+90
+T
+W
+A
+=
+1
+6</t>
+        </is>
+      </c>
+      <c r="I1209" s="2" t="inlineStr"/>
     </row>
     <row r="1210" ht="92.59999999999999" customHeight="1">
       <c r="A1210" s="2" t="n">
@@ -52857,8 +54294,15 @@
       <c r="G1210" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H1210" s="2" t="n"/>
-      <c r="I1210" s="2" t="n"/>
+      <c r="H1210" s="2" t="inlineStr">
+        <is>
+          <t>答案是 (A) 85。
+依據《勞工作業環境監測實施辦法》規定，勞工噪音暴露工作日 8 小時日時量平均音壓級達 85 分貝以上之作業場所，雇主應依規定每 6 個月實施噪音監測（測定）一次以上。
+.依勞工作業環境監測實施辦法之規定，勞工噪音暴露工作8 ...
+2018年9月30日 — (A)85 (B)90 … 高溫作業場所應每隔多久測定綜合溫度熱指數一次以上</t>
+        </is>
+      </c>
+      <c r="I1210" s="2" t="inlineStr"/>
     </row>
     <row r="1211" ht="92.59999999999999" customHeight="1">
       <c r="A1211" s="2" t="n">
@@ -52884,8 +54328,89 @@
       <c r="G1211" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H1211" s="2" t="n"/>
-      <c r="I1211" s="2" t="n"/>
+      <c r="H1211" s="2" t="inlineStr">
+        <is>
+          <t>，請稍後再試。
+網頁搜尋結果
+1313. 依職業安全衛生設施規則規定,於時量平均音壓級為 ...
+› item-1313.+依職業安全衛生設施規則...
+2024年10月7日 — 1313. 依職業安全衛生設施規則規定,於時量平均音壓級為90dBA 之噪音環境下,勞工一天容許暴露時間至多幾小時? (A)2 (B)4 (C)8 (D)10。 答案：登入後 ...
+職業安全衛生設施規則有關勞工噪音暴露之相關規定
+勞工作業環境監測及暴露危害管理
+› content › about › About1
+噪音超過90分貝之工作場所，應標示並公告噪音危害之預防事項，使勞工周知。 (二)雇主對於勞工八小時日時量平均音壓級超過85分貝 ...
+缺少字詞： 一天 ‎| 必須包含以下字詞： 一天
+第300 條
+› FLAW › FLAWDOC01
+雇主對於發生噪音之工作場所，應依下列規定辦理： 一、勞工工作場所因機械設備所發生之聲音超過九十分貝時，雇主應採取工程控制、減少勞工噪音暴露時間，使勞工噪音 ...
+缺少字詞： 90dBA ‎下, ‎一天 ‎至多
+463. () 依職業安全衛生設施規則規定，於時量平均音壓級為 ...
+› item-463.+()+依職業安全衛生設施規...
+2020年1月21日 — 463. () 依職業安全衛生設施規則規定，於時量平均音壓級為90 dBA之噪音 環境下，勞工一天容許暴露時間至多幾小時？ (A)2 (B)4 (C)8 (D)10.
+職業安全衛生設施規則修正日期：民國115 年06 月30 日施行 ...
+臺北市政府全球資訊網
+› LawSearch › LawExport
+PDF
+2026年6月30日 — 一、勞工工作場所因機械設備所發生之聲音超過九十分貝時，雇主應採取. 工程控制、減少勞工噪音暴露時間，使勞工噪音暴露工作日八小時日. 時量平均不超過（ ...
+缺少字詞： 90dBA ‎一天 ‎至多 ‎幾
+相關問題
+噪音90分貝的話,工作時間可以限制多久?
+勞工 於 工作 8 小時 之 噪音 暴露 劑量 200 即 表示 其 相當 8 小時 日時 量 平均 音壓 級 超過 多少 分貝？
+晚上幾點以後算噪音？
+依規定(沒有配音),高差超過幾公尺上,就必須設置安全上下設備？
+網頁搜尋結果
+作業環境噪音量測與暴露評估建議方法第一版
+勞動及職業安全衛生研究所
+› media › obdbdbtb › il...
+PDF
+(五)噪音劑量(Dose, D):可將8 小時日時量平均音壓級轉換成噪音暴露劑量，如公式(3). 所示(基於勞工8 小時日時量平均音壓級90 分貝，工作日容許暴露時間為8 小時. 之情況)。
+缺少字詞： 90dBA ‎至多
+淺談噪音作業之危害及危害預防
+myMKC管理知識中心
+› 主題 › 職業安全衛生
+2021年4月14日 — （1）勞工工作場所因機械設備所產生之音響超過90分貝時，僱主應採取工程控制、減少勞工噪音暴露時間，使勞工噪音暴露工作日八小時日時量平均不超過下表所 ...
+缺少字詞： 90dBA ‎至多 ‎幾
+職場噪音知多少-Ⅲ
+怡安職護殿堂
+› 部落格
+2022年5月6日 — 依據《職業安全衛生設施規則》第300條規定，勞工工作場所因機械設備所發生之聲音超過九十分貝時，雇主應採取工程控制、減少勞工噪音暴露時間；對於勞工八 ...
+缺少字詞： 依 ‎於 ‎為 ‎90dBA ‎環境 ‎一天 ‎容許 ‎至多 ‎幾
+職業安全衛生設施規則第300 條- 2026 最新全國法規資料庫
+› ... › 職業安全衛生設施規則
+職業安全衛生設施規則 第300 條 ... （三）測定勞工八小時日時量平均音壓級時，應將八十分貝以上之噪音以增加五分貝降低容許暴露時間一半之方式納入計算。 二、工作場所之 ...
+缺少字詞： 90dBA ‎一天 ‎至多 ‎幾
+其他人也搜尋了以下項目
+依職業安全衛生設施規則規定八小時時量平均音壓級超過多少分貝時雇主應採取工程控制並減少勞工噪音暴露時間
+噪音容許暴露時間公式
+噪音暴露劑量計算公式
+8小時日時量平均音壓級
+85分貝容許暴露時間
+評估勞工8小時日時量平均音壓級時依職業安全衛生設施規則規定應將多少分貝以上的噪音納入計算
+依職業安全衛生設施規則規定噪音超過多少分貝之工作場所應標示並公告其危害之預防事項供勞工周知
+多少分貝db以上之區域稱為噪音作業場所
+頁面導覽
+1
+2
+3
+4
+5
+6
+7
+8
+9
+10
+下一頁
+頁尾連結
+台灣
+708 臺南市安平區 - 根據你的 IP 位址
+- 更新位置
+說明
+提供意見
+隱私權
+服務條款</t>
+        </is>
+      </c>
+      <c r="I1211" s="2" t="inlineStr"/>
     </row>
     <row r="1212" ht="92.59999999999999" customHeight="1">
       <c r="A1212" s="2" t="n">
@@ -52919,8 +54444,17 @@
       <c r="G1212" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1212" s="2" t="n"/>
-      <c r="I1212" s="2" t="n"/>
+      <c r="H1212" s="2" t="inlineStr">
+        <is>
+          <t>從事電焊作業的主要之危害非為噪音（題目中的「叨音」應為噪音之筆誤）。
+電焊作業危害分析
+火災：焊接時產生的熔渣、高溫火花容易引燃周遭可燃物。
+爆炸：於存有易燃氣體、油類或有機溶劑等密閉容器或場所施作時容易引發爆炸。
+感電：接觸破損電線、焊接柄夾頭帶電部分或於潮濕環境作業常造成感電事故。
+噪音：一般電焊本身並不會產生持續性超高分貝的強力噪音，故不屬於其主要核心職業危害。</t>
+        </is>
+      </c>
+      <c r="I1212" s="2" t="inlineStr"/>
     </row>
     <row r="1213" ht="92.59999999999999" customHeight="1">
       <c r="A1213" s="2" t="n">
@@ -52954,8 +54488,17 @@
       <c r="G1213" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1213" s="2" t="n"/>
-      <c r="I1213" s="2" t="n"/>
+      <c r="H1213" s="2" t="inlineStr">
+        <is>
+          <t>正確答案是 (D) 密閉噪音源。
+各選項解析
+密閉噪音源：屬於工程改善／工程控制項目，透過實體隔離或包覆來降低噪音的傳遞與發生。
+減少暴露時間：屬於行政管理控制項目。
+標示公告噪音危害預防事項：屬於行政管理／標示公告項目。
+佩戴適當的防音防護具：屬於個體防護具項目。</t>
+        </is>
+      </c>
+      <c r="I1213" s="2" t="inlineStr"/>
     </row>
     <row r="1214" ht="92.59999999999999" customHeight="1">
       <c r="A1214" s="2" t="n">
@@ -52989,8 +54532,43 @@
       <c r="G1214" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H1214" s="2" t="n"/>
-      <c r="I1214" s="2" t="n"/>
+      <c r="H1214" s="2" t="inlineStr">
+        <is>
+          <t>聲音在固體中傳播速度最快。
+聲速快慢比較
+聲音是一種力學波，需要靠介質才能傳遞。介質分子的緊密程度會影響傳聲速度，一般原則為：
+固體 ＞ 液體 ＞ 空氣（氣體） ＞ 真空
+真空中沒有介質，因此無法傳播聲音。
+翰林雲端學院 常見介質的聲速參考（以大約數值為例）
+空氣（20℃）：約
+343
+3
+4
+3
+公尺／秒
+水：約
+1
+,
+4
+6
+3
+公尺／秒
+玻璃／鐵等固體：約
+5
+,
+0
+0
+0
+至
+5
+,
+5
+0
+0
+公尺／秒以上</t>
+        </is>
+      </c>
+      <c r="I1214" s="2" t="inlineStr"/>
     </row>
     <row r="1215" ht="92.59999999999999" customHeight="1">
       <c r="A1215" s="2" t="n">
@@ -53024,8 +54602,17 @@
       <c r="G1215" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1215" s="2" t="n"/>
-      <c r="I1215" s="2" t="n"/>
+      <c r="H1215" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+吵雜的環境最不可能為肌肉骨骼傷害的原因。
+原因解析
+過度施力、姿勢不當以及無適當的休息皆屬於人因工程危害（Ergonomic Hazards），是造成工作相關肌肉骨骼疾病（WMSDs）的核心危險因子。
+吵雜的環境（噪音）屬於物理性危害，雖然會造成聽力受損或心理壓力，但並非直接導致肌肉、肌腱、關節或脊椎等肌肉骨骼傷害的主因。
+iPEDIA 百科</t>
+        </is>
+      </c>
+      <c r="I1215" s="2" t="inlineStr"/>
     </row>
     <row r="1216" ht="92.59999999999999" customHeight="1">
       <c r="A1216" s="2" t="n">
@@ -53059,8 +54646,14 @@
       <c r="G1216" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H1216" s="2" t="n"/>
-      <c r="I1216" s="2" t="n"/>
+      <c r="H1216" s="2" t="inlineStr">
+        <is>
+          <t>坐姿不當或不良（題目中的「坐麥雪勢不良」應為「坐姿姿勢不良」的打字造字或語音輸入錯誤）屬於人因工程危害。
+說明：
+人因工程危害（Ergonomic hazards）：主要指由於工作環境設計不良、長時間維持不良姿勢、重複性動作或用力不當，導致肌肉骨骼系統受到傷害（如酸痛、拉傷、職業性肌肉骨骼疾病）的危害因素。</t>
+        </is>
+      </c>
+      <c r="I1216" s="2" t="inlineStr"/>
     </row>
     <row r="1217" ht="92.59999999999999" customHeight="1">
       <c r="A1217" s="2" t="n">
@@ -53094,8 +54687,19 @@
       <c r="G1217" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1217" s="2" t="n"/>
-      <c r="I1217" s="2" t="n"/>
+      <c r="H1217" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+以不適當的姿勢做重複性的動作，屬 (D) 人因工程 危害因子。
+危害因子說明
+人因工程危害：指工作姿勢不良、重複性動作、施力過大或工作步調過快等，容易造成肌肉骨骼累積性傷害。
+化學性危害：如粉塵、氣體、有機溶劑等。
+物理性危害：如噪音、振動、異常溫濕度、輻射等。
+生物性危害：如細菌、病毒、寄生蟲等傳染原。
+NTNU</t>
+        </is>
+      </c>
+      <c r="I1217" s="2" t="inlineStr"/>
     </row>
     <row r="1218" ht="92.59999999999999" customHeight="1">
       <c r="A1218" s="2" t="n">
@@ -53129,8 +54733,17 @@
       <c r="G1218" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H1218" s="2" t="n"/>
-      <c r="I1218" s="2" t="n"/>
+      <c r="H1218" s="2" t="inlineStr">
+        <is>
+          <t>在提舉重物時，為避免發生人因工程危害，應儘量利用人體之腿部力量。
+台灣省工礦安全衛生技師公會
+正確姿勢與原因
+利用大腿肌肉：腿部（特別是股四頭肌等大肌群）力量較強且耐操，用來起 F 舉重物最安全。
+保持背部挺直：搬重物時應以半蹲姿勢（膝蓋彎曲、腰背打直）代償，絕對不能直接彎腰，以免造成背部與腰椎受傷。
+國立岡山高級農工職業學校</t>
+        </is>
+      </c>
+      <c r="I1218" s="2" t="inlineStr"/>
     </row>
     <row r="1219" ht="92.59999999999999" customHeight="1">
       <c r="A1219" s="2" t="n">
@@ -53164,8 +54777,19 @@
       <c r="G1219" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H1219" s="2" t="n"/>
-      <c r="I1219" s="2" t="n"/>
+      <c r="H1219" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+低作業頻率不易人造成累積性肌肉骨骼傷害。
+累積性肌肉骨骼傷害的危險因子
+重覆性作業：短時間內重複相同動作，容易導致肌肉疲勞與組織受損。
+長時間作業：長時間維持固定姿勢或持續工作，缺乏足夠休息。
+不自然的姿勢：如過度彎腰、扭轉或舉手過高，會增加關節與肌肉的負荷。
+低作業頻率：動作之間有足夠的休息與恢復時間，因此不易累積造成傷害。
+iPEDIA 百科</t>
+        </is>
+      </c>
+      <c r="I1219" s="2" t="inlineStr"/>
     </row>
     <row r="1220" ht="92.59999999999999" customHeight="1">
       <c r="A1220" s="2" t="n">
@@ -53199,8 +54823,17 @@
       <c r="G1220" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H1220" s="2" t="n"/>
-      <c r="I1220" s="2" t="n"/>
+      <c r="H1220" s="2" t="inlineStr">
+        <is>
+          <t>手腕隧道症候群是手腕之神經（正中神經）受傷或受壓迫。
+疾病核心解析
+受損組織：正中神經（Median nerve），在經過手腕的腕隧道時受到腕橫韌帶壓迫所引起。
+常見症狀：大拇指、食指、中指及無名指橈側（半側）出現麻木、刺痛或灼熱感，夜間或清晨通常會加劇。
+嚴重表現：長期壓迫會導致手部無力、甚至大魚際肌（拇指下方肌肉）萎縮。
+新竹臺大分院</t>
+        </is>
+      </c>
+      <c r="I1220" s="2" t="inlineStr"/>
     </row>
     <row r="1221" ht="108" customHeight="1">
       <c r="A1221" s="2" t="n">
@@ -53234,8 +54867,17 @@
       <c r="G1221" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H1221" s="2" t="n"/>
-      <c r="I1221" s="2" t="n"/>
+      <c r="H1221" s="2" t="inlineStr">
+        <is>
+          <t>答案為：「應考慮勞工之體能負荷情形，減少工作時間給予充分休息，休息時間每小時不得少於 30 分鐘」。
+錯誤原因解析
+依據重體力勞動作業勞工保護措施標準第 3 條規定，雇主使勞工從事重體力勞動作業時，應考慮勞工之體能負荷情形，減少工作時間給予充分休息，其規定的休息時間為每小時不得少於 20 分鐘（並非選項中所述的 30 分鐘）。
+相關法規重點
+休息時間規定：每小時休息時間不得少於 20 分鐘。
+作業改善與機械替代：應致力於作業方法之改善、作業頻率之減低、搬運距離之縮短、搬運物體重量之減少及適當搬運速度之調整，並儘量以機械代替人力。</t>
+        </is>
+      </c>
+      <c r="I1221" s="2" t="inlineStr"/>
     </row>
     <row r="1222" ht="92.59999999999999" customHeight="1">
       <c r="A1222" s="2" t="n">
@@ -53269,8 +54911,15 @@
       <c r="G1222" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H1222" s="2" t="n"/>
-      <c r="I1222" s="2" t="n"/>
+      <c r="H1222" s="2" t="inlineStr">
+        <is>
+          <t>依據《重體力勞動作業勞工保護措施標準》第5條規定，正確答案是 食鹽。
+相關規定說明
+法規條文：雇主使勞工從事重體力勞動作業時，應充分供應飲用水及食鹽，並採取必要措施指導勞工避免重體力勞動之危害。
+原因：從事重體力勞動時，勞工會大量流汗，導致體內水分與電解質（尤其是鹽分）流失，因此補充食鹽與水分有助於預防熱中暑或電解質失衡。</t>
+        </is>
+      </c>
+      <c r="I1222" s="2" t="inlineStr"/>
     </row>
     <row r="1223" ht="92.59999999999999" customHeight="1">
       <c r="A1223" s="2" t="n">
@@ -53304,8 +54953,15 @@
       <c r="G1223" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1223" s="2" t="n"/>
-      <c r="I1223" s="2" t="n"/>
+      <c r="H1223" s="2" t="inlineStr">
+        <is>
+          <t>一般而言，霧滴（Mist）不會經由(D) 不完全燃燒的作用方式形成。
+霧滴的形成與特性
+霧滴通常是指液體微粒，可以透過機械力（如噴霧作用）、高溫氣態分子冷凝或凝結作用凝聚而成。
+不完全燃燒主要會產生煙霧（如碳粒、燻煙等固體微粒或氣體副產物），而不是液態的霧滴。</t>
+        </is>
+      </c>
+      <c r="I1223" s="2" t="inlineStr"/>
     </row>
     <row r="1224" ht="77.15000000000001" customHeight="1">
       <c r="A1224" s="2" t="n">
@@ -53339,8 +54995,18 @@
       <c r="G1224" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H1224" s="2" t="n"/>
-      <c r="I1224" s="2" t="n"/>
+      <c r="H1224" s="2" t="inlineStr">
+        <is>
+          <t>物質的最小著火能量越低，其引火之容易度為(A) 愈高。
+觀念解析
+最小著火能量 (MIE, Minimum Ignition Energy)：指引起可燃物（如氣體、蒸氣或粉塵與空氣的混合物）燃燒所需的最低能量（例如微小靜電火花或電火花）。
+引火容易度：當 MIE 數值越低，代表只要極微小的能量（如微量靜電）就能把物質點燃，因此引燃或引火的容易度就愈高、危險性也越大。
+公職王 為了提供更精準的資訊，請問您是在準備哪一類型的考試或培訓？
+職業安全衛生業務主管（如甲種、乙種、丙種）
+消防設備人員／警察特考</t>
+        </is>
+      </c>
+      <c r="I1224" s="2" t="inlineStr"/>
     </row>
     <row r="1225" ht="77.15000000000001" customHeight="1">
       <c r="A1225" s="2" t="n">
@@ -53374,8 +55040,18 @@
       <c r="G1225" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H1225" s="2" t="n"/>
-      <c r="I1225" s="2" t="n"/>
+      <c r="H1225" s="2" t="inlineStr">
+        <is>
+          <t>下列選項中，以氫氣的最小著火能量（MIE, Minimum Ignition Energy）最低，最容易引火。
+各物質最小著火能量比較
+氫氣：約 0.011 mJ（最低，最易引燃）
+乙烯：約 0.07 mJ
+丙烷：約 0.25 mJ
+甲烷：約 0.29 mJ
+說明：最小著火能量（MIE）是指引起氣體或蒸氣混合物燃燒所需的最低電火花能量。數值越低，代表只需極微小的能量（如微弱靜電花火）就可能引發火災或爆炸。</t>
+        </is>
+      </c>
+      <c r="I1225" s="2" t="inlineStr"/>
     </row>
     <row r="1226" ht="92.59999999999999" customHeight="1">
       <c r="A1226" s="2" t="n">
@@ -53409,8 +55085,12 @@
       <c r="G1226" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H1226" s="2" t="n"/>
-      <c r="I1226" s="2" t="n"/>
+      <c r="H1226" s="2" t="inlineStr">
+        <is>
+          <t>Google AI 摘要未抓取到，請手動補充。</t>
+        </is>
+      </c>
+      <c r="I1226" s="2" t="inlineStr"/>
     </row>
     <row r="1227" ht="92.59999999999999" customHeight="1">
       <c r="A1227" s="2" t="n">
@@ -53444,8 +55124,28 @@
       <c r="G1227" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1227" s="2" t="n"/>
-      <c r="I1227" s="2" t="n"/>
+      <c r="H1227" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+電功率之單位為瓦特（Watt，簡稱瓦，符號為
+W
+W
+）。
+EMSD
+相關單位對照
+瓦特（Watt）：電功率的單位，等於伏特乘以安培（
+𝑃
+=
+𝑉
+×
+𝐼
+）。
+伏特（Volt）：電壓的單位。
+安培（Ampere）：電流的單位。
+法拉（Farad）：電容的單位。</t>
+        </is>
+      </c>
+      <c r="I1227" s="2" t="inlineStr"/>
     </row>
     <row r="1228" ht="92.59999999999999" customHeight="1">
       <c r="A1228" s="2" t="n">
@@ -53479,8 +55179,28 @@
       <c r="G1228" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1228" s="2" t="n"/>
-      <c r="I1228" s="2" t="n"/>
+      <c r="H1228" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+可以進入到人體肺泡區的微粒是可呼吸性微粒（Respirable particles）。
+SMC台灣科技媒體中心
+微粒分類與深入呼吸道的能力
+落塵：粒徑最大，通常會直接沉降在地面或環境中，無法被人體呼吸系統大量吸入。
+可吸入性微粒（Inhalable particles）：粒徑小於 100 微米（
+𝜇
+𝑚
+），是指所有能經由口、鼻進入呼吸系統的微粒。
+胸腔性微粒（Thoracic particles）：粒徑小於 10 微米（
+𝜇
+𝑚
+），能穿越咽喉並進入胸腔，到達氣管與支氣管。
+可呼吸性微粒（Respirable particles）：粒徑小於 2.5 至 4 微米（
+𝜇
+𝑚
+）以下，能通過氣管與支氣管，直接到達肺部氣體交換區（肺泡區）並沉積。</t>
+        </is>
+      </c>
+      <c r="I1228" s="2" t="inlineStr"/>
     </row>
     <row r="1229" ht="92.59999999999999" customHeight="1">
       <c r="A1229" s="2" t="n">
@@ -53514,8 +55234,20 @@
       <c r="G1229" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H1229" s="2" t="n"/>
-      <c r="I1229" s="2" t="n"/>
+      <c r="H1229" s="2" t="inlineStr">
+        <is>
+          <t>藉由高溫氣態分子冷凝而成之固態微粒，係指 (C) 燻煙。
+iPEDIA 百科
+相關名詞解析
+燻煙（Fume）：由氣態物質凝結（冷凝）而懸浮於空氣中的固體微粒，粒徑通常小於 0.1 微米（例如金屬焊接或熔煉時產生的金屬燻煙）。
+粉塵（Dust）：因物理性力量（如機械破碎、研磨、鑽孔等作業）所產生並懸浮於空氣中的固體微粒。
+霧滴（Mist）：液體霧化或蒸氣凝結所形成的液體微粒。
+煙塵（Smoke/Soot）：含碳燃料或有機物質不完全燃燒所產生的碳粒與有機物混合微粒。
+Facebook
+·工安百科</t>
+        </is>
+      </c>
+      <c r="I1229" s="2" t="inlineStr"/>
     </row>
     <row r="1230" ht="92.59999999999999" customHeight="1">
       <c r="A1230" s="2" t="n">
@@ -53549,8 +55281,25 @@
       <c r="G1230" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1230" s="2" t="n"/>
-      <c r="I1230" s="2" t="n"/>
+      <c r="H1230" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+氮氣不屬於氣膠。
+氣膠（Aerosol）簡介
+定義：氣膠又稱氣溶膠，是指固體或液體微粒懸浮在氣體中形成的混合物。
+選項分析：
+粉塵：固體微粒懸浮於空氣中，屬於氣膠。
+霧滴：液體微粒懸浮於空氣中，屬於氣膠。
+燻煙：固體微粒（通常由化學反應或凝結產生）懸浮於空氣中，屬於氣膠。
+氮氣：是一種單一的氣體分子（
+𝑁
+2
+𝑁
+2
+），並非懸浮微粒的混合物，因此不屬於氣膠。</t>
+        </is>
+      </c>
+      <c r="I1230" s="2" t="inlineStr"/>
     </row>
     <row r="1231" ht="92.59999999999999" customHeight="1">
       <c r="A1231" s="2" t="n">
@@ -53580,8 +55329,18 @@
       <c r="G1231" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H1231" s="2" t="n"/>
-      <c r="I1231" s="2" t="n"/>
+      <c r="H1231" s="2" t="inlineStr">
+        <is>
+          <t>若控制設備不良，最容易使懷孕中胎兒智力受到影響的物質是鉛。
+為什麼是「鉛」？
+胎盤屏障無法阻擋：母體吸入或食入的鉛，會透過胎盤直接進入胎兒體內。
+神經毒性：鉛是一種強烈的神經毒物。胎兒在發育過程中，大腦和神經系統對鉛極為敏感，即使是低劑量的鉛暴露，也可能導致智力發育遲緩、認知功能障礙及行為異常。
+其他選項說明
+石灰：主要成分為氧化鈣，具腐蝕性與刺激性，主要危害為皮膚灼傷及呼吸道刺激，不會直接導致胎兒智力受損。
+石綿：屬於一級致癌物，長期吸入石綿纖維會導致肺纖維化（石綿肺）或間皮瘤等癌症，但其主要危害在於呼吸系統與致癌性，非直接影響胎兒智力的神經毒物。</t>
+        </is>
+      </c>
+      <c r="I1231" s="2" t="inlineStr"/>
     </row>
     <row r="1232" ht="92.59999999999999" customHeight="1">
       <c r="A1232" s="2" t="n">
@@ -53615,8 +55374,16 @@
       <c r="G1232" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H1232" s="2" t="n"/>
-      <c r="I1232" s="2" t="n"/>
+      <c r="H1232" s="2" t="inlineStr">
+        <is>
+          <t>勞工從事異常氣壓作業可能導致的職業病是(C) 減壓病（俗稱潛水夫症）。
+iPEDIA 百科 減壓病簡介
+成因：在高壓環境（如潛水、高壓艙或沉箱作業）下，勞工呼吸高壓氣體，使大量氣體（主要是氮氣）溶解在血液和組織液中。當環境壓力急速降低（減壓）時，溶解在體內的氣體會形成氣泡，阻塞血管或壓迫神經組織。
+常見症狀：關節劇痛（俗稱屈肢症）、皮膚紅疹、頭暈、呼吸困難、甚至神經系統麻痺。
+iPEDIA 百科</t>
+        </is>
+      </c>
+      <c r="I1232" s="2" t="inlineStr"/>
     </row>
     <row r="1233" ht="92.59999999999999" customHeight="1">
       <c r="A1233" s="2" t="n">
@@ -53650,8 +55417,18 @@
       <c r="G1233" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H1233" s="2" t="n"/>
-      <c r="I1233" s="2" t="n"/>
+      <c r="H1233" s="2" t="inlineStr">
+        <is>
+          <t>為防止壓力槽內壓力過高而發生事故，應裝置釋壓閥（安全閥）。
+財團法人職業災害預防及重建中心 相關安全設備說明
+釋壓閥（安全閥）：當壓力槽內部壓力超過設定的最大允許壓力時，會自動開啟並進行排氣洩壓，以防止設備發生過壓爆炸。
+反撥裝置：主要用於防止木材加工機械（如圓盤鋸）發生木料反彈回擊的防護裝置。
+制動裝置：用於讓機械運動部件減速或停止運轉的煞車設備。
+光電開關：通常應用於衝剪機械等危險區域的安全感應防護，用來偵測人員接近並停止機械動作。
+花職訓</t>
+        </is>
+      </c>
+      <c r="I1233" s="2" t="inlineStr"/>
     </row>
     <row r="1234" ht="77.15000000000001" customHeight="1">
       <c r="A1234" s="2" t="n">
@@ -53685,8 +55462,15 @@
       <c r="G1234" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1234" s="2" t="n"/>
-      <c r="I1234" s="2" t="n"/>
+      <c r="H1234" s="2" t="inlineStr">
+        <is>
+          <t>電焊作業具有粉塵及非游離輻射危害。
+危害說明
+粉塵：電焊過程中會產生含有金屬氧化物等的銲煙與粉塵。
+非游離輻射：電焊時產生的強烈光線（如紫外線、紅外線）屬於非游離輻射，會對眼睛及皮膚造成危害。</t>
+        </is>
+      </c>
+      <c r="I1234" s="2" t="inlineStr"/>
     </row>
     <row r="1235" ht="92.59999999999999" customHeight="1">
       <c r="A1235" s="2" t="n">
@@ -53720,8 +55504,18 @@
       <c r="G1235" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H1235" s="2" t="n"/>
-      <c r="I1235" s="2" t="n"/>
+      <c r="H1235" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+金屬燻煙熱之主要症狀與感冒（流行性感冒）類似。
+金屬燻煙熱簡介
+定義：吸入新鮮金屬氧化物（如氧化鋅）燻煙引起的急性疾病。
+常見族群：焊工、金屬鑄造與切割作業人員。
+主要症狀：發燒、發冷、頭痛、咳嗽、疲勞及肌肉痠痛，極像重感冒。
+病程特點：通常在工作後數小時發作，停止接觸後約 1 至 2 天內可自行緩解痊癒。詳細考古題解析可參考 Yamol 詳解。</t>
+        </is>
+      </c>
+      <c r="I1235" s="2" t="inlineStr"/>
     </row>
     <row r="1236" ht="92.59999999999999" customHeight="1">
       <c r="A1236" s="2" t="n">
@@ -53755,8 +55549,16 @@
       <c r="G1236" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H1236" s="2" t="n"/>
-      <c r="I1236" s="2" t="n"/>
+      <c r="H1236" s="2" t="inlineStr">
+        <is>
+          <t>造成金屬燻煙熱之主要暴露途徑為 (A) 吸入。
+原因說明
+吸入危害：金屬燻煙熱是由於吸入加熱後產生的金屬氧化物細微煙霧（如鋅、銅、錳等金屬蒸氣凝結成的微粒）進入呼吸道與肺部所引起的急性發炎反應。
+常見情境：常發生在電焊、鍍鋅鐵板焊接或金屬熔解等作業環境中。
+長庚醫療財團法人全球資訊網</t>
+        </is>
+      </c>
+      <c r="I1236" s="2" t="inlineStr"/>
     </row>
     <row r="1237" ht="77.15000000000001" customHeight="1">
       <c r="A1237" s="2" t="n">
@@ -53790,8 +55592,17 @@
       <c r="G1237" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H1237" s="2" t="n"/>
-      <c r="I1237" s="2" t="n"/>
+      <c r="H1237" s="2" t="inlineStr">
+        <is>
+          <t>勞工從事 (C) 裝卸石英粉 作業最容易罹患塵肺症。
+原因解析
+石英粉含有結晶型游離二氧化矽（Crystalline Free Silica）。
+長期吸入二氧化矽微小粉塵會沉積在肺泡中，導致肺部組織發炎與纖維化，進而引發塵肺症（或稱矽肺症）。
+其他選項如麵粉、塑膠粉、糖粉等屬於有機或一般高分子粉塵，雖可能引起呼吸道過敏、氣喘或塵肺以外的呼吸道不適，但不會像石英粉那樣造成嚴重的肺纖維化塵肺症。
+考古豹</t>
+        </is>
+      </c>
+      <c r="I1237" s="2" t="inlineStr"/>
     </row>
     <row r="1238" ht="92.59999999999999" customHeight="1">
       <c r="A1238" s="2" t="n">
@@ -53825,8 +55636,18 @@
       <c r="G1238" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H1238" s="2" t="n"/>
-      <c r="I1238" s="2" t="n"/>
+      <c r="H1238" s="2" t="inlineStr">
+        <is>
+          <t>這題的答案是 (C) 胸腔性微粒。
+Quizlet 解析
+胸腔性微粒（Thoracic particles）：粒徑通常在 10 微米以下，主要能進入氣管與支氣管，但較難深入到達最末端的肺泡區。
+可呼吸性微粒（Respirable particles）：粒徑更小（約 4 微米以下），能夠通過氣管並深入到達肺部之肺泡區進行沉積。
+奈米微粒：粒徑小於 0.1 微米（100奈米），尺寸極小，極易穿透並抵達肺泡區。
+氧氣：為氣體分子，能直接隨著呼吸作用通透進入肺泡並進行氣體交換。
+SMC台灣科技媒體中心</t>
+        </is>
+      </c>
+      <c r="I1238" s="2" t="inlineStr"/>
     </row>
     <row r="1239" ht="92.59999999999999" customHeight="1">
       <c r="A1239" s="2" t="n">
@@ -53860,8 +55681,19 @@
       <c r="G1239" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1239" s="2" t="n"/>
-      <c r="I1239" s="2" t="n"/>
+      <c r="H1239" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+答案是 可呼吸性微粒。
+微粒分類與深入呼吸道的能力
+可呼吸性微粒（Respirable particles）：粒徑極小（通常在 4 微米或 2.5 微米以下），能通過氣管、支氣管，直接到達人體的肺泡區（氣體交換區）並沉積。
+胸腔性微粒（Thoracic particles）：粒徑小於 10 微米，能進入胸腔，到達氣管與支氣管，但較難全部深入最末端的肺泡區。
+可吸入性微粒（Inhalable particles）：粒徑小於 100 微米，指所有能經由口鼻進入呼吸系統的粉塵，主要沉積在上呼吸道。
+Facebook
+·工安百科 落塵：粒徑最大，會直接沉降在地面或鼻腔外，無法進入呼吸道深處。</t>
+        </is>
+      </c>
+      <c r="I1239" s="2" t="inlineStr"/>
     </row>
     <row r="1240" ht="92.59999999999999" customHeight="1">
       <c r="A1240" s="2" t="n">
@@ -53895,8 +55727,41 @@
       <c r="G1240" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H1240" s="2" t="n"/>
-      <c r="I1240" s="2" t="n"/>
+      <c r="H1240" s="2" t="inlineStr">
+        <is>
+          <t>通常粒徑小於 100nm 之微粒，稱為奈米微粒。
+相關尺度說明
+奈米（nm）：等於
+10
+-9
+1
+0
+−
+9
+公尺（十億分之一公尺），粒徑小於 100 奈米的微粒即為奈米微粒。
+微米（
+𝜇
+𝝁
+m）：等於
+10
+-6
+1
+0
+−
+6
+公尺，大於奈米一個數量級。
+毫米（mm）：等於
+10
+-3
+1
+0
+−
+3
+公尺。
+公尺（m）：基本長度單位。</t>
+        </is>
+      </c>
+      <c r="I1240" s="2" t="inlineStr"/>
     </row>
     <row r="1241" ht="92.59999999999999" customHeight="1">
       <c r="A1241" s="2" t="n">
@@ -53930,8 +55795,20 @@
       <c r="G1241" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H1241" s="2" t="n"/>
-      <c r="I1241" s="2" t="n"/>
+      <c r="H1241" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+形成燻煙的作用方式為高溫氣態分子冷凝。
+Quizlet 燻煙的特性
+定義：指固體物質（如金屬）經高溫加熱蒸發成氣態或蒸氣分子後，在空氣中冷卻凝結而成的固態微粒。
+Quizlet
+與其他粒狀物的區別：
+粉塵：由機械力（如研磨、粉碎）破碎固體物質產生。
+霧滴：由液體經噴霧或凝結作用產生。
+Quizlet</t>
+        </is>
+      </c>
+      <c r="I1241" s="2" t="inlineStr"/>
     </row>
     <row r="1242" ht="92.59999999999999" customHeight="1">
       <c r="A1242" s="2" t="n">
@@ -53965,8 +55842,12 @@
       <c r="G1242" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H1242" s="2" t="n"/>
-      <c r="I1242" s="2" t="n"/>
+      <c r="H1242" s="2" t="inlineStr">
+        <is>
+          <t>Google AI 摘要未抓取到，請手動補充。</t>
+        </is>
+      </c>
+      <c r="I1242" s="2" t="inlineStr"/>
     </row>
     <row r="1243" ht="92.59999999999999" customHeight="1">
       <c r="A1243" s="2" t="n">
@@ -54000,8 +55881,18 @@
       <c r="G1243" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1243" s="2" t="n"/>
-      <c r="I1243" s="2" t="n"/>
+      <c r="H1243" s="2" t="inlineStr">
+        <is>
+          <t>災後復原時短時間內較不會發生的是慢性職業病。
+原因說明
+慢性職業病：需要長期、持續接觸特定有害環境或物質（如長期粉塵、噪音、化學物質暴露）才會逐漸形成，屬於長期累積的健康效應，因此在短期的「災後復原」階段較不會突然發生。
+災後復原常見急性危險：
+恢復供電時感電：線路受損或潮濕未察覺即送電，易導致觸電。
+設備未經安全性確認，發生二次事故：機械、電氣或構造物受損未檢修就使用，引發崩塌或故障。
+因地面積水而滑倒：積水、泥濘或雜物導致環境濕滑，造成立即的跌倒受傷風險。</t>
+        </is>
+      </c>
+      <c r="I1243" s="2" t="inlineStr"/>
     </row>
     <row r="1244" ht="92.59999999999999" customHeight="1">
       <c r="A1244" s="2" t="n">
@@ -54035,8 +55926,16 @@
       <c r="G1244" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1244" s="2" t="n"/>
-      <c r="I1244" s="2" t="n"/>
+      <c r="H1244" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+氧乙炔焊接時若發生突發回火（緊急處置），應先關氧氣，再關乙炔。
+回火與正常關閉的差別
+緊急回火：應先關氧氣，再關乙炔。這樣做能切斷助燃氣體（氧氣），防止火勢往管線內部擴大或爆炸。
+正常工作結束熄火：應先關乙炔，再關氧氣，避免管腔內殘留乙炔碳化積碳。</t>
+        </is>
+      </c>
+      <c r="I1244" s="2" t="inlineStr"/>
     </row>
     <row r="1245" ht="92.59999999999999" customHeight="1">
       <c r="A1245" s="2" t="n">
@@ -54070,8 +55969,19 @@
       <c r="G1245" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H1245" s="2" t="n"/>
-      <c r="I1245" s="2" t="n"/>
+      <c r="H1245" s="2" t="inlineStr">
+        <is>
+          <t>關於粉塵顆粒大小的影響，敘述有誤的是「顆粒愈大，容易帶電，有較大電容量」（即選項 C 為誤）。
+錯誤原因解析
+帶電量與電容量：粉塵顆粒愈小，其比表面積（單位重量或單位體積的表面積）愈大，因此在摩擦或接觸時愈容易帶電荷；而粒徑較大的顆粒表面積相對較小，反而不容易累積大量電荷或具備較大的表面電荷容量。
+其他選項正確說明
+顆粒愈小，愈容易在空氣中懸浮：質量與體積小的微粒受重力影響小，隨空氣流動飄浮的時間更長。
+顆粒愈小，單位重量粉塵的吸氧量愈大：因為粒徑愈小，總表面積（比表面積）愈大，接觸與吸附氧氣或其他化學物質的面積也隨之增加。
+顆粒愈大，相對體表面積愈小：隨著顆粒直徑增大，體積增加的速率大於表面積，因此單位質量或體積下的相對表面積（比表面積）會變小。
+www2.nurse-newsletter.org.tw</t>
+        </is>
+      </c>
+      <c r="I1245" s="2" t="inlineStr"/>
     </row>
     <row r="1246" ht="92.59999999999999" customHeight="1">
       <c r="A1246" s="2" t="n">
@@ -54105,8 +56015,16 @@
       <c r="G1246" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1246" s="2" t="n"/>
-      <c r="I1246" s="2" t="n"/>
+      <c r="H1246" s="2" t="inlineStr">
+        <is>
+          <t>銅（或銅錠）熔解爐最主要危害為水蒸氣爆炸。
+危害原因
+水分接觸高溫：當潮濕的原料、工具或冷卻水不慎接觸到高溫熔融金屬或爐內高溫時，水分會瞬間汽化並急遽膨脹。
+劇烈爆炸：體積瞬間膨脹會導致熔爐或熔液劇烈噴濺爆炸，造成嚴重人員傷亡與財物損失。
+內政部消防署全球資訊網</t>
+        </is>
+      </c>
+      <c r="I1246" s="2" t="inlineStr"/>
     </row>
     <row r="1247" ht="92.59999999999999" customHeight="1">
       <c r="A1247" s="2" t="n">
@@ -54140,8 +56058,17 @@
       <c r="G1247" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1247" s="2" t="n"/>
-      <c r="I1247" s="2" t="n"/>
+      <c r="H1247" s="2" t="inlineStr">
+        <is>
+          <t>物質的酸鹼性最不可能影響物質被人體攝食吸收的程度。
+詳細原因說明
+物質的酸鹼性：雖然酸鹼性可能會影響物質在胃腸道特定部位的溶解度或刺激性，但比起分子大小、水溶解度與脂溶性，它本身不是決定物質是否能跨越生物膜被直接吸收的核心物理化學特性。
+物質分子的大小：分子越小越容易通過細胞膜或細胞間隙進入體內。
+物質的水溶解度：影響物質在消化道液體中溶解並接觸吸收表面的能力。
+物質的脂溶性：脂溶性高的物質極易穿過細胞膜的雙層脂質結構，被人體大量吸收。</t>
+        </is>
+      </c>
+      <c r="I1247" s="2" t="inlineStr"/>
     </row>
     <row r="1248" ht="92.59999999999999" customHeight="1">
       <c r="A1248" s="2" t="n">
@@ -54175,8 +56102,13 @@
       <c r="G1248" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H1248" s="2" t="n"/>
-      <c r="I1248" s="2" t="n"/>
+      <c r="H1248" s="2" t="inlineStr">
+        <is>
+          <t>水是身體中最容易吸收微波能量的成分。
+微波加熱主要是透過偶極轉動（Dipole rotation）的物理機制。因為水分子具有很強的極性（正負電極不對稱），在微波的高頻交變電場下會快速旋轉、相互摩擦，進而產生熱能。因此，含水量越高的生物組織（如肌肉、內臟），吸收微波能量的效率就比含水量低的組織（如骨骼中的鈣、磷或脂肪）要高出許多。</t>
+        </is>
+      </c>
+      <c r="I1248" s="2" t="inlineStr"/>
     </row>
     <row r="1249" ht="92.59999999999999" customHeight="1">
       <c r="A1249" s="2" t="n">
@@ -54210,8 +56142,15 @@
       <c r="G1249" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H1249" s="2" t="n"/>
-      <c r="I1249" s="2" t="n"/>
+      <c r="H1249" s="2" t="inlineStr">
+        <is>
+          <t>答案是 (C) 營建機械車輛操作。
+解析
+局部振動（Hand-arm vibration）：是指手部接觸或操作會產生振動的機械、工具或設備，振動能量主要傳播至手和手臂（例如鏈鋸、破碎機、氣動手工具等）。
+營建機械車輛操作：屬於全身振動（Whole-body vibration），因為操作時振動是透過全身（臀部或雙腳）傳遞，而非僅侷限於手部。</t>
+        </is>
+      </c>
+      <c r="I1249" s="2" t="inlineStr"/>
     </row>
     <row r="1250" ht="92.59999999999999" customHeight="1">
       <c r="A1250" s="2" t="n">
@@ -54245,8 +56184,18 @@
       <c r="G1250" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H1250" s="2" t="n"/>
-      <c r="I1250" s="2" t="n"/>
+      <c r="H1250" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+白手病（又稱白指病）之症狀是由振動危害所引起。
+dpt.cch.org.tw
+疾病與危害說明
+原因：長期使用或手握高頻率動力機械工具（如鏈鋸、風鑽等），使手部直接暴露在強烈振動中。
+症狀：造成手部末梢神經與血管受損，導致血管收縮、手指發白、麻痺、疼痛，甚至骨質疏鬆。若處於寒冷環境中，低溫會讓症狀更加嚴重。
+dpt.cch.org.tw</t>
+        </is>
+      </c>
+      <c r="I1250" s="2" t="inlineStr"/>
     </row>
     <row r="1251" ht="92.59999999999999" customHeight="1">
       <c r="A1251" s="2" t="n">
@@ -54280,8 +56229,13 @@
       <c r="G1251" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1251" s="2" t="n"/>
-      <c r="I1251" s="2" t="n"/>
+      <c r="H1251" s="2" t="inlineStr">
+        <is>
+          <t>精密工作需要具備較佳之照明。
+在所有選項中，照明强度的需求由低到高依序為：室外走道 &lt; 倉庫 &lt; 一般辦公場所 &lt; 精密工作。精密工作（如電子零件組裝、精密儀器校正等）因為視覺精細度要求極高，需要充足且均勻的光線以防止視力疲勞並確保作業安全。</t>
+        </is>
+      </c>
+      <c r="I1251" s="2" t="inlineStr"/>
     </row>
     <row r="1252" ht="92.59999999999999" customHeight="1">
       <c r="A1252" s="2" t="n">
@@ -54315,8 +56269,25 @@
       <c r="G1252" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H1252" s="2" t="n"/>
-      <c r="I1252" s="2" t="n"/>
+      <c r="H1252" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+正確答案為 (A) 1:1/5:1/20。
+詳細說明
+依據《精密作業勞工視機能保護設施標準》第 7 條規定：
+雇主使勞工從事精密作業時，其工作台面照明與其半徑一公尺以內接鄰地區照明之比率不得低於 1:1/5（即 1 比 5 分之一）。
+與鄰近地區照明之比率不得低於 1:1/20（即 1 比 20 分之一）。
+也就是工作台面、半徑 1 公尺以內接鄰地區、鄰近地區之照度比標準為 1:1/5:1/20。
+需要為您整理更多職業安全衛生法規或考古題解析嗎？
+歷屆熱門工安考題
+照明與視力保護標準
+. 依精密作業勞工視機能保護措施標準規定 ... - 年10月30日 — 精密作業照度分佈以均勻為宜,務使工作台面:半徑1 公尺以內接鄰地區:鄰近地區之照度比不得低於下列何者? (A)1:1/5:1/20 (B)1:1/10:1/30 (C)1:1/15:1/40 (D)1:1/20:1/50
+職業安全衛生管理證照題庫練習
+精密作業照度分佈以均勻為宜，務使工作台面：半徑1公尺以內 ...
+A 1:1/5:1/20; B 1:1/10:1/30; C 1:1/15:1/40; D 1:1/20:1/50. 答案:A 說明:精密作業勞工視機能保護設施標準. A 1:1/5:1/20; B 1:1/10:1/30; C 1:1/15:1/40; D ...</t>
+        </is>
+      </c>
+      <c r="I1252" s="2" t="inlineStr"/>
     </row>
     <row r="1253" ht="92.59999999999999" customHeight="1">
       <c r="A1253" s="2" t="n">
@@ -54350,8 +56321,15 @@
       <c r="G1253" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H1253" s="2" t="n"/>
-      <c r="I1253" s="2" t="n"/>
+      <c r="H1253" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+該照明係指(B) 局部照明。
+依據《職業安全衛生設施規則》附表及相關規定，針對須極精辨物體而對襯不良之作業（如印刷品校對、極精細儀器組合、鐘錶珠寶鑲製等），其作業區之採光照明應達 1,000 米燭光（Lux）以上，此標準規範通常需藉由局部照明來達成。
+臺北市政府全球資訊網</t>
+        </is>
+      </c>
+      <c r="I1253" s="2" t="inlineStr"/>
     </row>
     <row r="1254" ht="77.15000000000001" customHeight="1">
       <c r="A1254" s="2" t="n">
@@ -54385,8 +56363,15 @@
       <c r="G1254" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H1254" s="2" t="n"/>
-      <c r="I1254" s="2" t="n"/>
+      <c r="H1254" s="2" t="inlineStr">
+        <is>
+          <t>依據勞工健康保護規則規定，正確答案為 CD。
+解析
+依《勞工健康保護規則》規定，雇主實施勞工 C. 特殊健康檢查 及 D. 健康追蹤檢查 後，應填具規定之勞工特殊健康檢查結果報告書，報請事業單位所在地之勞工及衛生主管機關備查，並副知當地勞動檢查機構。
+一般健康檢查（A）與特殊體格檢查（B）則無須辦理此項通報備查程序。</t>
+        </is>
+      </c>
+      <c r="I1254" s="2" t="inlineStr"/>
     </row>
     <row r="1255" ht="92.59999999999999" customHeight="1">
       <c r="A1255" s="2" t="n">
@@ -54420,8 +56405,20 @@
       <c r="G1255" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H1255" s="2" t="n"/>
-      <c r="I1255" s="2" t="n"/>
+      <c r="H1255" s="2" t="inlineStr">
+        <is>
+          <t>依「勞工健康保護規則」相關規定（如附表），勞工的定期健康檢查項目比一般體格檢查項目主要增加了低密度脂蛋白膽固醇的檢查。
+NCNU
+檢查項目差異簡述
+一般體格檢查（新進受僱時）：
+包含作業經歷與既往病史調查、理學檢查、胸部X光、尿液檢查以及基本血液檢查（如血色素、白血球數、血糖、肝腎功能、總膽固醇、三酸甘油酯、高密度脂蛋白膽固醇等）。
+新北勞動雲
+定期健康檢查（在職定期實施）：
+在上述基礎上，額外增加了低密度脂蛋白膽固醇（LDL）項目，以全面評估心血管疾病風險。
+新北勞動雲</t>
+        </is>
+      </c>
+      <c r="I1255" s="2" t="inlineStr"/>
     </row>
     <row r="1256" ht="92.59999999999999" customHeight="1">
       <c r="A1256" s="2" t="n">
@@ -54447,8 +56444,17 @@
       <c r="G1256" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H1256" s="2" t="n"/>
-      <c r="I1256" s="2" t="n"/>
+      <c r="H1256" s="2" t="inlineStr">
+        <is>
+          <t>依據「勞工健康保護規則」之規定，特殊健康檢查結果的分級健康管理共分為 4 級（第一級至第四級管理）。
+第一級管理：檢查結果綜合判定為無異常者。
+第二級管理：檢查結果綜合判定為異常，而與工作無關者。
+第三級管理：檢查結果綜合判定為異常，可能與工作相關，應予追蹤評估。
+第四級管理：檢查結果綜合判定為異常，與工作相關，應予醫療及勞動場所危害控制等處理。
+臨場健康守護犬</t>
+        </is>
+      </c>
+      <c r="I1256" s="2" t="inlineStr"/>
     </row>
     <row r="1257" ht="108" customHeight="1">
       <c r="A1257" s="2" t="n">
@@ -54482,8 +56488,17 @@
       <c r="G1257" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H1257" s="2" t="n"/>
-      <c r="I1257" s="2" t="n"/>
+      <c r="H1257" s="2" t="inlineStr">
+        <is>
+          <t>健康檢查結果異常，無法確定異常與工作之相關性，應進一步請職業醫學科專科醫師評估者。
+勞工特殊健康檢查分級管理標準
+第一級管理：全部正常，或部分異常但判定無異常。
+第二級管理：異常，且與工作無關。
+第三級管理：異常，無法確定與工作之相關性，需請職業醫學科專科醫師進一步評估。
+第四級管理：異常，且與工作有關。</t>
+        </is>
+      </c>
+      <c r="I1257" s="2" t="inlineStr"/>
     </row>
     <row r="1258" ht="92.59999999999999" customHeight="1">
       <c r="A1258" s="2" t="n">
@@ -54517,8 +56532,13 @@
       <c r="G1258" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1258" s="2" t="n"/>
-      <c r="I1258" s="2" t="n"/>
+      <c r="H1258" s="2" t="inlineStr">
+        <is>
+          <t>答案為：第四級。
+依據《勞工健康保護規則》規定，從事特別危害健康作業之勞工，特殊健康檢查結果屬第四級管理者（檢查結果異常且與工作有關），經醫師評估現場仍有工作危害因子之暴露者，雇主應採取危害控制及相關管理措施。</t>
+        </is>
+      </c>
+      <c r="I1258" s="2" t="inlineStr"/>
     </row>
     <row r="1259" ht="92.59999999999999" customHeight="1">
       <c r="A1259" s="2" t="n">
@@ -54552,8 +56572,16 @@
       <c r="G1259" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H1259" s="2" t="n"/>
-      <c r="I1259" s="2" t="n"/>
+      <c r="H1259" s="2" t="inlineStr">
+        <is>
+          <t>一般健康檢查紀錄資料至少要保存 7年。
+桃園市政府勞動檢查處
+依據台灣《勞工健康保護規則》規定：
+一般健康檢查紀錄：雇主應至少保存 7年。
+特殊健康檢查紀錄：依作業類別不同，通常保存 10年 或甚至 30年（如游離輻射、粉塵等作業）。</t>
+        </is>
+      </c>
+      <c r="I1259" s="2" t="inlineStr"/>
     </row>
     <row r="1260" ht="92.59999999999999" customHeight="1">
       <c r="A1260" s="2" t="n">
@@ -54587,8 +56615,17 @@
       <c r="G1260" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H1260" s="2" t="n"/>
-      <c r="I1260" s="2" t="n"/>
+      <c r="H1260" s="2" t="inlineStr">
+        <is>
+          <t>特殊健康檢查資料依作業類別不同，一般特殊健康檢查紀錄至少保存 10年，而從事游離輻射、粉塵、石綿、苯等特定特別危害健康作業的檢查紀錄則應至少保存 30年。
+在選項中（7年、3年、10年、5年），一般特殊健康檢查紀錄對應的最低法定保存年限為 10年。
+相關法規重點
+一般健康檢查紀錄：至少保存 7年。
+一般特殊健康檢查紀錄：至少保存 10年。
+指定危害作業特殊檢查紀錄（如游離輻射、粉塵、石綿、苯、鉛、甲醛等16類作業）：因潛伏期長，須至少保存 30年。</t>
+        </is>
+      </c>
+      <c r="I1260" s="2" t="inlineStr"/>
     </row>
     <row r="1261" ht="92.59999999999999" customHeight="1">
       <c r="A1261" s="2" t="n">
@@ -54616,8 +56653,12 @@
       <c r="G1261" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1261" s="2" t="n"/>
-      <c r="I1261" s="2" t="n"/>
+      <c r="H1261" s="2" t="inlineStr">
+        <is>
+          <t>依據《勞工健康保護規則》規定，從事致癌性物質等特別危害健康作業勞工之特殊健康檢查紀錄，最少應保存 30年（選項 D）。</t>
+        </is>
+      </c>
+      <c r="I1261" s="2" t="inlineStr"/>
     </row>
     <row r="1262" ht="92.59999999999999" customHeight="1">
       <c r="A1262" s="2" t="n">
@@ -54651,8 +56692,18 @@
       <c r="G1262" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H1262" s="2" t="n"/>
-      <c r="I1262" s="2" t="n"/>
+      <c r="H1262" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+推行職場健康促進最主要目的為使勞工身心處最適宜狀態。
+職場健康促進重點
+核心目標：營造健康的工作環境與資源，讓勞工在生理與心理上都達到最佳狀態。
+宜蘭縣政府衛生局 其他選項分析：
+使勞工多工作、使產量增加：屬於企業生產力考量，並非健康促進的初衷與主要目的。
+調合勞工與主管關係：屬於職場人際與組織溝通範疇，非健康促進的直接核心。</t>
+        </is>
+      </c>
+      <c r="I1262" s="2" t="inlineStr"/>
     </row>
     <row r="1263" ht="92.59999999999999" customHeight="1">
       <c r="A1263" s="2" t="n">
@@ -54686,8 +56737,12 @@
       <c r="G1263" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H1263" s="2" t="n"/>
-      <c r="I1263" s="2" t="n"/>
+      <c r="H1263" s="2" t="inlineStr">
+        <is>
+          <t>Google AI 摘要未抓取到，請手動補充。</t>
+        </is>
+      </c>
+      <c r="I1263" s="2" t="inlineStr"/>
     </row>
     <row r="1264" ht="92.59999999999999" customHeight="1">
       <c r="A1264" s="2" t="n">
@@ -54721,8 +56776,21 @@
       <c r="G1264" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1264" s="2" t="n"/>
-      <c r="I1264" s="2" t="n"/>
+      <c r="H1264" s="2" t="inlineStr">
+        <is>
+          <t>💡 正確答案
+職場健康促進活動中，不屬於推行健康生活範圍的是：投資理財。
+📊 解析與說明
+健康生活範圍：包含營養指導、菸害防制、體重管理及壓力紓解等，旨在促進員工身體健康與良好生活習慣。
+不屬健康生活：投資理財屬於財務規劃或員工福利補助的延伸，與生理健康促進無直接關聯。
+需要了解更多職業安全衛生或職場健康促進的相關題庫與解析嗎？
+職場健康促進的其他分類
+職安衛管理乙級/甲級考古題
+職業安全衛生業務主管練習題庫：健康管理與健康促進#120062
+2022年12月31日 — 職業健康促進活動中,下列何者不屬推行健康生活範圍?(A)投資理財(B) 營養指導(C)菸害防制(D)體重管理。 2.雇主對勞工實施特殊健康檢查</t>
+        </is>
+      </c>
+      <c r="I1264" s="2" t="inlineStr"/>
     </row>
     <row r="1265" ht="92.59999999999999" customHeight="1">
       <c r="A1265" s="2" t="n">
@@ -54756,8 +56824,18 @@
       <c r="G1265" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H1265" s="2" t="n"/>
-      <c r="I1265" s="2" t="n"/>
+      <c r="H1265" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+在職場健康促進活動中，績效目標不屬於推行友善職場的範圍。
+友善職場的涵蓋項目包含：
+性別平等
+人性管理
+無障礙設施
+績效目標屬於營運管理與工作績效評估的範疇，而非直接針對員工身心健康與工作環境友善支持的健康促進措施。</t>
+        </is>
+      </c>
+      <c r="I1265" s="2" t="inlineStr"/>
     </row>
     <row r="1266" ht="92.59999999999999" customHeight="1">
       <c r="A1266" s="2" t="n">
@@ -54791,8 +56869,24 @@
       <c r="G1266" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1266" s="2" t="n"/>
-      <c r="I1266" s="2" t="n"/>
+      <c r="H1266" s="2" t="inlineStr">
+        <is>
+          <t>在職場健康促進活動中，員工協助方案不屬於推行舒適環境的範圍。
+選項解析
+員工協助方案（EAP）：
+屬於心理健康、諮商輔導與組織支持層面。
+主要在處理員工的心理、家庭、法律或財務等個人困擾，不歸類在實體或人因的「舒適環境」中。
+下班隨手作
+健康工時：
+屬於工作時間與休息安排的調節，有助於減少疲勞、打造舒適與健康的工作節奏，歸在舒適或友善工作環境範圍。
+人因工程：
+改善工作姿勢、設備與操作介面，減少身體負荷，屬於舒適與安全的工作環境範疇。
+作業環境：
+改善物理性、化學性等現場作業條件（如照明、噪音、通風），直接攸關環境的舒適與安全。
+合勤投控</t>
+        </is>
+      </c>
+      <c r="I1266" s="2" t="inlineStr"/>
     </row>
     <row r="1267" ht="92.59999999999999" customHeight="1">
       <c r="A1267" s="2" t="n">
@@ -54826,8 +56920,16 @@
       <c r="G1267" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1267" s="2" t="n"/>
-      <c r="I1267" s="2" t="n"/>
+      <c r="H1267" s="2" t="inlineStr">
+        <is>
+          <t>疾病治療不屬於職場健康促進的主要推行工作範圍。
+職場健康促進之說明
+健康促進的核心在於預防、提升健康意識與改善生活品質，而非針對已經發生疾病的醫療與疾病治療。
+主要範圍包含健康生活、友善職場與舒適環境等預防及支持性層面。
+國泰金控</t>
+        </is>
+      </c>
+      <c r="I1267" s="2" t="inlineStr"/>
     </row>
     <row r="1268" ht="108" customHeight="1">
       <c r="A1268" s="2" t="n">
@@ -54861,8 +56963,17 @@
       <c r="G1268" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1268" s="2" t="n"/>
-      <c r="I1268" s="2" t="n"/>
+      <c r="H1268" s="2" t="inlineStr">
+        <is>
+          <t>「異常結果之健康檢查手冊應公告周知」是不適當的措施。
+根據《勞工健康保護規則》及相關規定，勞工的健康檢查結果及個人健康隱私應予保密，不得作為健康管理目的以外之用途，更不得任意公告周知。
+應採取之正確措施
+參採醫師建議：告知勞工，並適當配置勞工於工作場所作業。
+發給檢查結果：將健康檢查結果發給受檢勞工。
+彙編健康檢查手冊：將健康檢查紀錄彙編成健康檢查手冊發給勞工，並妥善保護個人隱私。</t>
+        </is>
+      </c>
+      <c r="I1268" s="2" t="inlineStr"/>
     </row>
     <row r="1269" ht="92.59999999999999" customHeight="1">
       <c r="A1269" s="2" t="n">
@@ -54896,8 +57007,20 @@
       <c r="G1269" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1269" s="2" t="n"/>
-      <c r="I1269" s="2" t="n"/>
+      <c r="H1269" s="2" t="inlineStr">
+        <is>
+          <t>飲食習慣較不屬於一般健康體能檢測項目。
+健康體能的四大要素
+一般健康體能（健康體適能）主要包含以下四個核心要素，並會透過實際檢測來評估身體機能：
+www.hpa.gov.tw 心肺適能（心肺耐力）：評估心臟、肺臟與血管輸送氧氣至全身的能力（如登階測驗、原地抬膝踏步）。
+肌力與肌耐力：評估肌肉產生最大力量或持續耐受的持久性（如仰臥捲腹、握力、伏地挺身）。
+柔軟度：評估關節活動的最大範圍與肌肉韌帶的伸展能力（如坐姿體前彎）。
+身體組成：評估身體脂肪與瘦體組織的比例（如身體質量指數 BMI、體脂率）。
+衛生福利部 而「飲食習慣」屬於營養與生活型態管理的範疇，雖然會影響身體組成與健康，但並非實際進行動作測試的體能檢測項目。
+啟新診所</t>
+        </is>
+      </c>
+      <c r="I1269" s="2" t="inlineStr"/>
     </row>
     <row r="1270" ht="92.59999999999999" customHeight="1">
       <c r="A1270" s="2" t="n">
@@ -54931,8 +57054,15 @@
       <c r="G1270" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H1270" s="2" t="n"/>
-      <c r="I1270" s="2" t="n"/>
+      <c r="H1270" s="2" t="inlineStr">
+        <is>
+          <t>正確答案是 (C) 供膳作業。
+原因說明
+供膳作業：涉及食物的調理、接觸與分發，若從事此類工作的人員患有傳染病（如傷寒、痢疾、肝炎或呼吸道傳染病等），極易透過食物或餐具傳染給消費者或大眾。
+相關法規與衛生標準規定，具備傳染病或開放性傳染疾病者，不得從事餐飲及食品調理等供膳相關作業。</t>
+        </is>
+      </c>
+      <c r="I1270" s="2" t="inlineStr"/>
     </row>
     <row r="1271" ht="108" customHeight="1">
       <c r="A1271" s="2" t="n">
@@ -54966,8 +57096,16 @@
       <c r="G1271" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H1271" s="2" t="n"/>
-      <c r="I1271" s="2" t="n"/>
+      <c r="H1271" s="2" t="inlineStr">
+        <is>
+          <t>雇主不應要求醫護人員臨廠服務的事項為 (A) 提供健康檢查資料以作為開除員工之依據。
+說明
+保密與職業倫理：勞工的健康檢查資料與隱私受相關法規及醫學倫理保護，醫護人員不得將健康檢查資料提供給雇主作為解雇或不利處分員工的依據。
+合法臨場服務事項：依據《勞工健康保護規則》，醫護人員臨廠主要協助健康教育與促進、職業傷病防治、健康檢查結果分析與評估、以及協助選配適當工作等，不包含提供資料供資遣或開除之用。
+高雄市政府全球資訊網</t>
+        </is>
+      </c>
+      <c r="I1271" s="2" t="inlineStr"/>
     </row>
     <row r="1272" ht="92.59999999999999" customHeight="1">
       <c r="A1272" s="2" t="n">
@@ -55001,8 +57139,16 @@
       <c r="G1272" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H1272" s="2" t="n"/>
-      <c r="I1272" s="2" t="n"/>
+      <c r="H1272" s="2" t="inlineStr">
+        <is>
+          <t>辦理登山郊遊較屬於健康促進之相關活動。
+原因說明
+辦理登山郊遊：屬於戶外休閒與體能鍛鍊活動，有助於增進身體活動量、舒緩壓力，符合健康促進（促進身體與心理健康）的概念。
+請休假：屬於個人休息或假別管理，並非主動推動或組織的健康促進活動。
+辦理業務競賽 / 辦理業務檢討：屬於工作業務與績效管理的範疇，與健康促進無關。</t>
+        </is>
+      </c>
+      <c r="I1272" s="2" t="inlineStr"/>
     </row>
     <row r="1273" ht="92.59999999999999" customHeight="1">
       <c r="A1273" s="2" t="n">
@@ -55028,8 +57174,17 @@
       <c r="G1273" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1273" s="2" t="n"/>
-      <c r="I1273" s="2" t="n"/>
+      <c r="H1273" s="2" t="inlineStr">
+        <is>
+          <t>雇主對於勞工投保加保年資連續滿 12個月（即1年）以上，即可向勞保局申請支付預防職業病健康檢查（特殊健康檢查）經費。正確選項為 (D) 12。
+申請重點摘要
+投保年資：最近加保年資連續滿 12個月。
+作業類別：從事噪音、游離輻射、粉塵、甲醛等指定有害作業。
+申請頻率：每年可向勞保局申請 1 次。
+勞動部勞工保險局</t>
+        </is>
+      </c>
+      <c r="I1273" s="2" t="inlineStr"/>
     </row>
     <row r="1274" ht="92.59999999999999" customHeight="1">
       <c r="A1274" s="2" t="n">
@@ -55063,8 +57218,21 @@
       <c r="G1274" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H1274" s="2" t="n"/>
-      <c r="I1274" s="2" t="n"/>
+      <c r="H1274" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+空氣非愛滋病（HIV）之主要傳染途徑。
+愛滋病的三大主要傳染途徑
+性行為傳染：發生不安全性行為（如未全程正確使用保險套），透過口交、肛交、陰道交或其他體液交換而感染。
+血液傳染：輸進或接觸受汙染的血液、血液製劑，或共用針具、針筒，以及接受器官移植。
+母子垂直傳染：感染愛滋病毒的母親，經由懷孕、生產或哺餵母乳等過程將病毒傳給新生兒。
+衛生福利部疾病管制署 為什麼空氣不會傳染？
+愛滋病毒（HIV）離開人體後十分脆弱，無法在空氣中存活或繁殖。
+與感染者共餐、共浴、握手、擁抱、共用馬桶或處於同一個空間呼吸空氣，都不會感染愛滋病。
+考古豹</t>
+        </is>
+      </c>
+      <c r="I1274" s="2" t="inlineStr"/>
     </row>
     <row r="1275" ht="92.59999999999999" customHeight="1">
       <c r="A1275" s="2" t="n">
@@ -55098,8 +57266,23 @@
       <c r="G1275" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H1275" s="2" t="n"/>
-      <c r="I1275" s="2" t="n"/>
+      <c r="H1275" s="2" t="inlineStr">
+        <is>
+          <t>指定醫療機構來廠內辦理勞工健康檢查時，可不包括牙醫師。
+說明
+依規定，辦理勞工巡迴健康檢查時，現場應配置醫師、醫事檢驗師、醫事放射師、護理人員及其他相關檢查之必要醫事人員。
+牙醫師非一般廠內勞工健檢現場強制配置的醫事人員。
+行政院公報資訊網
+想更了解其他勞工健檢法規或醫事人員配置規定嗎？
+了解粉塵、噪音等特殊作業健檢規定？
+查詢事業單位違規的罰鍰金額與法條？
+行政院公報資訊網
+辦理勞工體格與健康檢查醫療機構認可及管理辦法修正條文
+第十五條 認可醫療機構辦理巡迴檢查時，應依下列規定辦理：. 一、置有醫師、醫事檢驗師（生）、護理人員及其他相關檢查之必要醫事人員各一人以上在現場執行業務。 二、辦理噪音作業勞工特殊體格及健康檢查時，其聽力檢查室（亭）背景噪音量，於實施勞工聽力檢查期間，測定值符...
+顯示全部 內容</t>
+        </is>
+      </c>
+      <c r="I1275" s="2" t="inlineStr"/>
     </row>
     <row r="1276" ht="92.59999999999999" customHeight="1">
       <c r="A1276" s="2" t="n">
@@ -55133,8 +57316,16 @@
       <c r="G1276" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H1276" s="2" t="n"/>
-      <c r="I1276" s="2" t="n"/>
+      <c r="H1276" s="2" t="inlineStr">
+        <is>
+          <t>下列何者為較適當之鈣質攝取來源？ 小魚乾是最適當的鈣質攝取來源。
+常見食物鈣質比較
+小魚乾：含有豐富的鈣質與維生素 D，是極佳的天然鈣質來源。
+菸草、檳榔：屬於有害健康物質，會增加罹癌與心血管疾病風險。
+果汁：通常含糖量高且缺乏鈣質（除非是特別添加鈣的強化果汁）。</t>
+        </is>
+      </c>
+      <c r="I1276" s="2" t="inlineStr"/>
     </row>
     <row r="1277" ht="92.59999999999999" customHeight="1">
       <c r="A1277" s="2" t="n">
@@ -55168,8 +57359,15 @@
       <c r="G1277" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1277" s="2" t="n"/>
-      <c r="I1277" s="2" t="n"/>
+      <c r="H1277" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+對於噪音（題目誤植為咪音）作業勞工是否有效佩戴防護具，可依健康管理（透過聽力檢查結果評估防護成效）來了解成效。
+在職業安全衛生實務與相關考題中：
+健康管理：藉由實施勞工特殊健康檢查（如聽力檢查），追蹤與評估聽力損失情形，以此檢驗防音防護具佩戴是否具備實質保護效果。</t>
+        </is>
+      </c>
+      <c r="I1277" s="2" t="inlineStr"/>
     </row>
     <row r="1278" ht="92.59999999999999" customHeight="1">
       <c r="A1278" s="2" t="n">
@@ -55203,8 +57401,21 @@
       <c r="G1278" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1278" s="2" t="n"/>
-      <c r="I1278" s="2" t="n"/>
+      <c r="H1278" s="2" t="inlineStr">
+        <is>
+          <t>答案是 衛生所。
+根據《勞工健康保護規則》的法規規定：
+雇主實施勞工特殊健康檢查及健康追蹤檢查後，應填具勞工特殊健康檢查結果報告書：
+高雄市茄萣區衛生所
+報請 備查：事業單位所在地之 勞工主管機關 與 衛生主管機關（例如地方政府的勞工局、衛生局）。
+副知（通知）：當地 勞動檢查機構。
+因此，結果報告書 不需要 報請或副知基層的 衛生所。
+您是否正在準備職業安全衛生相關證照考試（如甲、乙級勞安檢定）呢？如果有其他法規題目的疑義，我可以幫您快速解析！
+.雇主對勞工實施特殊健康檢查，其結果報告書不需要報請或 ...
+2014年5月7日 — ... 副知事 業單位所在地之何種機關？ (A)勞工主管機關(B)衛生主管機關(C)勞動檢查機構(D)衛生所. #2164885 · 604. 雇主對勞工實施特殊健康檢查，其結果報告書不需要報請或副知事 業單位所在地之何種機關？ (A)勞工主管機關(B)衛生主...</t>
+        </is>
+      </c>
+      <c r="I1278" s="2" t="inlineStr"/>
     </row>
     <row r="1279" ht="92.59999999999999" customHeight="1">
       <c r="A1279" s="2" t="n">
@@ -55238,8 +57449,17 @@
       <c r="G1279" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H1279" s="2" t="n"/>
-      <c r="I1279" s="2" t="n"/>
+      <c r="H1279" s="2" t="inlineStr">
+        <is>
+          <t>答案是 (A) 高麗菜。
+為什麼是高麗菜？
+高麗菜：屬於蔬菜類，含有天然的膳食纖維，可以增加糞便體積、促進腸胃蠕動。
+炸排骨、滷雞翅：屬於肉類與油炸/滷製食品，蛋白質與脂肪含量高，幾乎不含膳食纖維。
+泡麵：屬於精緻加工澱粉，纖維質含量極低。
+安心醫療社團法人安心醫院</t>
+        </is>
+      </c>
+      <c r="I1279" s="2" t="inlineStr"/>
     </row>
     <row r="1280" ht="92.59999999999999" customHeight="1">
       <c r="A1280" s="2" t="n">
@@ -55273,8 +57493,18 @@
       <c r="G1280" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1280" s="2" t="n"/>
-      <c r="I1280" s="2" t="n"/>
+      <c r="H1280" s="2" t="inlineStr">
+        <is>
+          <t>錯誤的敘述為：視野愈小愈好（正確原則應為視野愈大愈好，才不會影響視線而導致工作危險）。
+育才國際文化事業有限公司 防塵口罩選用原則
+捕集效率愈高愈好：能更有效阻擋粉塵與微粒。
+吸氣阻抗愈低愈好：呼吸越順暢、配戴越舒適。
+重量愈輕愈好：減少臉部負擔。
+視野愈大愈好：避免視線受阻而引發安全意外。
+育才國際文化事業有限公司</t>
+        </is>
+      </c>
+      <c r="I1280" s="2" t="inlineStr"/>
     </row>
     <row r="1281" ht="92.59999999999999" customHeight="1">
       <c r="A1281" s="2" t="n">
@@ -55308,8 +57538,17 @@
       <c r="G1281" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H1281" s="2" t="n"/>
-      <c r="I1281" s="2" t="n"/>
+      <c r="H1281" s="2" t="inlineStr">
+        <is>
+          <t>雇主使勞工從事特別危害健康作業，應於其僱用或變更其工作時，實施特殊體格檢查。
+Quizlet
+依據《勞工健康保護規則》規定：
+僱用或變更工作時：應實施特殊體格檢查，以識別勞工的工作適性。
+在職期間（每年或變更作業時）：應定期實施特殊健康檢查。
+勞動部職業安全衛生署</t>
+        </is>
+      </c>
+      <c r="I1281" s="2" t="inlineStr"/>
     </row>
     <row r="1282" ht="92.59999999999999" customHeight="1">
       <c r="A1282" s="2" t="n">
@@ -55343,8 +57582,17 @@
       <c r="G1282" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1282" s="2" t="n"/>
-      <c r="I1282" s="2" t="n"/>
+      <c r="H1282" s="2" t="inlineStr">
+        <is>
+          <t>從事有機溶劑（如去漬油、噴漆等「甲類」或相關塗裝作業，題目中「甲菜」應為「甲苯」或「甲類有機溶劑」之打字造字錯誤）作業之勞工，應正確配戴防毒面具較為適當。
+以下為四種口罩的防護特性比較：
+防毒面具：專為過濾化學氣體與有機蒸氣設計。內含活性碳濾毒盒，能有效吸附有害化學物質，是從事有機溶劑作業的唯一正確選擇。
+N95 口罩：僅能防護粒狀污染物（如粉塵、飛沫、PM2.5）。無法阻擋化學有機蒸氣。
+外科口罩：主要用於阻隔飛沫與粗大顆粒。不具備防塵及防化學毒氣功能。
+一般棉紗口罩：僅能過濾較大顆粒的灰塵。對微細粉塵及化學蒸氣完全沒有防護效果。</t>
+        </is>
+      </c>
+      <c r="I1282" s="2" t="inlineStr"/>
     </row>
     <row r="1283" ht="77.15000000000001" customHeight="1">
       <c r="A1283" s="2" t="n">
@@ -55378,8 +57626,13 @@
       <c r="G1283" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H1283" s="2" t="n"/>
-      <c r="I1283" s="2" t="n"/>
+      <c r="H1283" s="2" t="inlineStr">
+        <is>
+          <t>同時暴露石綿與吸菸造成肺癌，其交互作用屬於加乘作用（或稱相乘作用），也就是兩者並存時所產生的致癌風險遠高於各自風險的簡單相加。
+國立臺中科技大學</t>
+        </is>
+      </c>
+      <c r="I1283" s="2" t="inlineStr"/>
     </row>
     <row r="1284" ht="92.59999999999999" customHeight="1">
       <c r="A1284" s="2" t="n">
@@ -55413,8 +57666,17 @@
       <c r="G1284" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H1284" s="2" t="n"/>
-      <c r="I1284" s="2" t="n"/>
+      <c r="H1284" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+答案是 (C) 預防注射。
+選項解析
+預防注射：屬於實際的醫療與健康服務預防措施。
+工作姿勢：屬於人因工程或工作環境設計層面。
+領導風格與團隊互助：屬於組織文化或組織管理層面。</t>
+        </is>
+      </c>
+      <c r="I1284" s="2" t="inlineStr"/>
     </row>
     <row r="1285" ht="92.59999999999999" customHeight="1">
       <c r="A1285" s="2" t="n">
@@ -55448,8 +57710,12 @@
       <c r="G1285" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H1285" s="2" t="n"/>
-      <c r="I1285" s="2" t="n"/>
+      <c r="H1285" s="2" t="inlineStr">
+        <is>
+          <t>Google AI 摘要未抓取到，請手動補充。</t>
+        </is>
+      </c>
+      <c r="I1285" s="2" t="inlineStr"/>
     </row>
     <row r="1286" ht="92.59999999999999" customHeight="1">
       <c r="A1286" s="2" t="n">
@@ -55483,8 +57749,15 @@
       <c r="G1286" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H1286" s="2" t="n"/>
-      <c r="I1286" s="2" t="n"/>
+      <c r="H1286" s="2" t="inlineStr">
+        <is>
+          <t>當燈具之輝度遠高於室內平均輝度時，可能造成的現象是眩光。
+眩光說明
+定義：視野中因亮度分布極不均勻或對比過強，使眼睛無法適應而產生刺眼、不舒服的感覺。
+影響：會降低視覺清晰度並容易造成眼睛疲勞。</t>
+        </is>
+      </c>
+      <c r="I1286" s="2" t="inlineStr"/>
     </row>
     <row r="1287" ht="77.15000000000001" customHeight="1">
       <c r="A1287" s="2" t="n">
@@ -55512,8 +57785,12 @@
       <c r="G1287" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H1287" s="2" t="n"/>
-      <c r="I1287" s="2" t="n"/>
+      <c r="H1287" s="2" t="inlineStr">
+        <is>
+          <t>依據《勞工健康保護規則》規定，從事苯作業等特別危害健康作業的勞工特殊健康檢查紀錄，應至少保存 30年（選項 C）。</t>
+        </is>
+      </c>
+      <c r="I1287" s="2" t="inlineStr"/>
     </row>
     <row r="1288" ht="77.15000000000001" customHeight="1">
       <c r="A1288" s="2" t="n">
@@ -55547,8 +57824,17 @@
       <c r="G1288" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H1288" s="2" t="n"/>
-      <c r="I1288" s="2" t="n"/>
+      <c r="H1288" s="2" t="inlineStr">
+        <is>
+          <t>長期直視高溫熔融金屬較易導致白內障（選項D）。
+Quizlet
+原因說明
+高溫熔融金屬會散發強烈的紅外線與可見光。
+長期暴露或直視會使眼睛的水晶體吸收過多熱能與紅外線輻射。
+水晶體蛋白質因此變性、混濁，進而引發職業性白內障。</t>
+        </is>
+      </c>
+      <c r="I1288" s="2" t="inlineStr"/>
     </row>
     <row r="1289" ht="92.59999999999999" customHeight="1">
       <c r="A1289" s="2" t="n">
@@ -55582,8 +57868,18 @@
       <c r="G1289" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1289" s="2" t="n"/>
-      <c r="I1289" s="2" t="n"/>
+      <c r="H1289" s="2" t="inlineStr">
+        <is>
+          <t>答案是 (D) 耳塞（或部分題庫對應之選項，依常見職業安全衛生考試題目「下列何者非電弧焊接作業之必要個人防護具」為 耳塞）。
+在電弧焊接作業中：
+護目鏡／安全面罩：用來防止強烈電弧光（紫外線、紅外線）傷害眼睛與面部。
+安全胸圍／皮衣／防護衣：用來防止焊接火花與高熱金屬飛濺燙傷胸腹部與皮膚。
+防護手套：用來防止燙傷及觸電。
+耳塞：一般噪音防護具，並非電弧焊接作業本身之必要防護具。
+www.wunan.com.tw</t>
+        </is>
+      </c>
+      <c r="I1289" s="2" t="inlineStr"/>
     </row>
     <row r="1290" ht="92.59999999999999" customHeight="1">
       <c r="A1290" s="2" t="n">
@@ -55617,8 +57913,19 @@
       <c r="G1290" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H1290" s="2" t="n"/>
-      <c r="I1290" s="2" t="n"/>
+      <c r="H1290" s="2" t="inlineStr">
+        <is>
+          <t>白吐司非適當之纖維質攝取來源。
+原因解析
+白吐司：屬於精製澱粉，製作過程中已經去除大部分的麩皮與胚芽，膳食纖維含量極低。
+蒟蒻：富含水溶性膳食纖維（葡萄甘露聚醣），常被用作補充纖維與低熱量的食材。
+蘿蔔：屬於根莖類蔬菜，含有豐富的植物纖維。
+地瓜：屬於未精製的全穀雜糧類（原型食物），保留了外皮與豐富的膳食纖維。
+Facebook
+·楊斯涵營養師的美味生活</t>
+        </is>
+      </c>
+      <c r="I1290" s="2" t="inlineStr"/>
     </row>
     <row r="1291" ht="92.59999999999999" customHeight="1">
       <c r="A1291" s="2" t="n">
@@ -55652,8 +57959,16 @@
       <c r="G1291" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H1291" s="2" t="n"/>
-      <c r="I1291" s="2" t="n"/>
+      <c r="H1291" s="2" t="inlineStr">
+        <is>
+          <t>勞工從事游離輻射作業，特別需要定期接受甲狀腺功能檢查。
+重點整理
+正確答案：游離輻射
+原因簡述：游離輻射暴露容易對人體的內分泌系統（特別是甲狀腺）造成影響，可能引發甲狀腺功能低下或相關異常，因此法規與指引中特別針對從事游離輻射作業的勞工安排甲狀腺及甲狀腺功能（如 Free T4、TSH）檢查。
+勞動部職業安全衛生署</t>
+        </is>
+      </c>
+      <c r="I1291" s="2" t="inlineStr"/>
     </row>
     <row r="1292" ht="92.59999999999999" customHeight="1">
       <c r="A1292" s="2" t="n">
@@ -55681,8 +57996,15 @@
       <c r="G1292" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H1292" s="2" t="n"/>
-      <c r="I1292" s="2" t="n"/>
+      <c r="H1292" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+法令規定的禁菸室內工作場所是指 3 人以上的室內工作場所。
+依據台灣《菸害防制法》規定，三人以上共用之室內工作場所全面禁止吸菸。
+衛生福利部</t>
+        </is>
+      </c>
+      <c r="I1292" s="2" t="inlineStr"/>
     </row>
     <row r="1293" ht="92.59999999999999" customHeight="1">
       <c r="A1293" s="2" t="n">
@@ -55716,8 +58038,12 @@
       <c r="G1293" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1293" s="2" t="n"/>
-      <c r="I1293" s="2" t="n"/>
+      <c r="H1293" s="2" t="inlineStr">
+        <is>
+          <t>Google AI 摘要未抓取到，請手動補充。</t>
+        </is>
+      </c>
+      <c r="I1293" s="2" t="inlineStr"/>
     </row>
     <row r="1294" ht="92.59999999999999" customHeight="1">
       <c r="A1294" s="2" t="n">
@@ -55751,8 +58077,15 @@
       <c r="G1294" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H1294" s="2" t="n"/>
-      <c r="I1294" s="2" t="n"/>
+      <c r="H1294" s="2" t="inlineStr">
+        <is>
+          <t>氯乙烯與生物性危害因子無關。
+原因解析
+氯乙烯：屬於化學性危害因子。它是一種人工合成的有機化學物質，主要用於製造聚氯乙烯（PVC），已被世界衛生組織列為確定的人類致癌物。
+動物、植物、微生物：皆屬於生物性危害因子。這些因子源自活的生物體及其產物（如細菌、病毒、黴菌、花粉、動物皮屑等），可能透過感染、過敏或毒素對人體健康造成危害。</t>
+        </is>
+      </c>
+      <c r="I1294" s="2" t="inlineStr"/>
     </row>
     <row r="1295" ht="77.15000000000001" customHeight="1">
       <c r="A1295" s="2" t="n">
@@ -55786,8 +58119,12 @@
       <c r="G1295" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H1295" s="2" t="n"/>
-      <c r="I1295" s="2" t="n"/>
+      <c r="H1295" s="2" t="inlineStr">
+        <is>
+          <t>Google AI 摘要未抓取到，請手動補充。</t>
+        </is>
+      </c>
+      <c r="I1295" s="2" t="inlineStr"/>
     </row>
     <row r="1296" ht="92.59999999999999" customHeight="1">
       <c r="A1296" s="2" t="n">
@@ -55821,8 +58158,18 @@
       <c r="G1296" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H1296" s="2" t="n"/>
-      <c r="I1296" s="2" t="n"/>
+      <c r="H1296" s="2" t="inlineStr">
+        <is>
+          <t>自一百十一年一月一日施行。
+ManpowerGroup 萬寶華 依據《勞工健康保護規則》之分階段施行規定：
+臺北市勞動檢查處
+勞工總人數在 200人至299人：自 107年7月1日 起施行
+勞工總人數在 100人至199人：自 109年1月1日 起施行
+勞工總人數在 50人至99人：自 111年1月1日 起施行
+ManpowerGroup 萬寶華</t>
+        </is>
+      </c>
+      <c r="I1296" s="2" t="inlineStr"/>
     </row>
     <row r="1297" ht="92.59999999999999" customHeight="1">
       <c r="A1297" s="2" t="n">
@@ -55856,8 +58203,18 @@
       <c r="G1297" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H1297" s="2" t="n"/>
-      <c r="I1297" s="2" t="n"/>
+      <c r="H1297" s="2" t="inlineStr">
+        <is>
+          <t>事業單位勞工人數達 100 人以上者，雇主應依勞工執行職務之風險特性，參照中央主管機關公告之相關指引，訂定執行職務遭受不法侵害預防計畫，並據以執行。
+因此正確選項為：100 人。
+相關法規重點
+法源依據：依據《職業安全衛生設施規則》第 324 條之 3 規定辦理。
+適用對象：平時雇用勞工人數達 100 人以上的事業單位。
+執行要求：雇主須參照勞動部公告之「執行職務遭受不法侵害預防指引」，針對職場暴力、脅迫、騷擾等不法侵害進行預防、辨識、評估及處置。
+勞動部職業安全衛生署</t>
+        </is>
+      </c>
+      <c r="I1297" s="2" t="inlineStr"/>
     </row>
     <row r="1298" ht="92.59999999999999" customHeight="1">
       <c r="A1298" s="2" t="n">
@@ -55891,8 +58248,13 @@
       <c r="G1298" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H1298" s="2" t="n"/>
-      <c r="I1298" s="2" t="n"/>
+      <c r="H1298" s="2" t="inlineStr">
+        <is>
+          <t>相關執行紀錄應保存 3 年。
+依據《職業安全衛生設施規則》第 324 條之 3 規定，雇主為預防勞工於執行職務時，因他人行為遭受身體或精神上不法侵害所採取的暴力預防措施，相關執行紀錄或文件應留存 3 年。</t>
+        </is>
+      </c>
+      <c r="I1298" s="2" t="inlineStr"/>
     </row>
     <row r="1299" ht="92.59999999999999" customHeight="1">
       <c r="A1299" s="2" t="n">
@@ -55926,8 +58288,17 @@
       <c r="G1299" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H1299" s="2" t="n"/>
-      <c r="I1299" s="2" t="n"/>
+      <c r="H1299" s="2" t="inlineStr">
+        <is>
+          <t>依據《職業安全衛生法》規定，僱用勞工人數達 10 人以上者，應訂定職場霸凌申訴管道，並在工作場所公開揭示。因此正確答案是 10 人。
+額外規模門檻重點：
+10 人以上：應訂定並公開揭示職場霸凌申訴管道。
+30 人以上：應訂定並公開揭示防治措施、申訴及懲處規範，並設立申訴處理單位與實施教育訓練。
+100 人以上：受理申訴後須依法組成調查小組（外部專業人士須達半數以上）。
+勞動部職業安全衛生署</t>
+        </is>
+      </c>
+      <c r="I1299" s="2" t="inlineStr"/>
     </row>
     <row r="1300" ht="92.59999999999999" customHeight="1">
       <c r="A1300" s="2" t="n">
@@ -55953,8 +58324,16 @@
       <c r="G1300" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H1300" s="2" t="n"/>
-      <c r="I1300" s="2" t="n"/>
+      <c r="H1300" s="2" t="inlineStr">
+        <is>
+          <t>依據《職場霸凌防治措施準則》規定，僱用勞工人數達 100 人以上者所組成之調查小組，其外聘（外部專業人士）成員比例不得少於二分之一。
+調查小組組成重點
+總人數：至少 3 人。
+外聘比例：外部專業人士不得少於二分之一。
+性別比例：任一性別比例不得少於三分之一。</t>
+        </is>
+      </c>
+      <c r="I1300" s="2" t="inlineStr"/>
     </row>
     <row r="1301" ht="92.59999999999999" customHeight="1">
       <c r="A1301" s="2" t="n">
@@ -55988,8 +58367,13 @@
       <c r="G1301" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H1301" s="2" t="n"/>
-      <c r="I1301" s="2" t="n"/>
+      <c r="H1301" s="2" t="inlineStr">
+        <is>
+          <t>當被申訴人為最高負責人時，勞工得逕向直轄市或縣（市）主管機關提起申訴。
+依據《職業安全衛生法》第22條之3第1項規定，勞工遭受職場霸凌時，原則上應向雇主提起申訴；但若被申訴人為公司的最高負責人（如董事長、老闆等），則可直接向地方的勞工主管機關（直轄市或縣（市）主管機關，即各地方政府勞動局/處）提出申訴。</t>
+        </is>
+      </c>
+      <c r="I1301" s="2" t="inlineStr"/>
     </row>
     <row r="1302" ht="92.59999999999999" customHeight="1">
       <c r="A1302" s="2" t="n">
@@ -56023,8 +58407,20 @@
       <c r="G1302" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H1302" s="2" t="n"/>
-      <c r="I1302" s="2" t="n"/>
+      <c r="H1302" s="2" t="inlineStr">
+        <is>
+          <t>1 萬元以上，100 萬元以下。
+stellexlaw.com 根據我國現行《職業安全衛生法》第 46 條規定，若事業單位的最高負責人（如老闆、董事長、總經理或機關首長等） 經地方主管機關調查並認定確實有職場霸凌之行為者，將直接處以個人新台幣 1 萬元以上，100 萬元以下的罰鍰。
+謙眾國際法律事務所 職場霸凌新制的重要裁罰標準如下：
+負責人個人責任：最高負責人本人涉及霸凌，處 1 萬至 100 萬元罰鍰。
+企業軍師林郁汶
+公司處理面義務：若公司接獲申訴卻拒絕受理、未依法啟動調查或未採必要保護措施，可處 3 萬至 75 萬元罰鍰。
+企業軍師林郁汶
+嚴重後果加重：若雇主未落實防治義務，導致員工不幸引發職業病等身心重大傷害，最高可處 5 萬至 300 萬元罰鍰（情節嚴重者最高可加重至 450 萬元）。
+中銀律師事務所</t>
+        </is>
+      </c>
+      <c r="I1302" s="2" t="inlineStr"/>
     </row>
     <row r="1303" ht="92.59999999999999" customHeight="1">
       <c r="A1303" s="2" t="n">
@@ -56058,8 +58454,15 @@
       <c r="G1303" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H1303" s="2" t="n"/>
-      <c r="I1303" s="2" t="n"/>
+      <c r="H1303" s="2" t="inlineStr">
+        <is>
+          <t>答案是 正 相關（增加罹病風險）。
+Quizlet
+說明
+正相關：根據流行病學與職業衛生研究，輪班、夜間及長時間工作會干擾人體的生理時鐘與晝夜節律，導致心肌梗塞、高血壓、睡眠障礙與憂鬱等疾病的罹病風險顯著增加。</t>
+        </is>
+      </c>
+      <c r="I1303" s="2" t="inlineStr"/>
     </row>
     <row r="1304" ht="92.59999999999999" customHeight="1">
       <c r="A1304" s="2" t="n">
@@ -56093,8 +58496,20 @@
       <c r="G1304" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H1304" s="2" t="n"/>
-      <c r="I1304" s="2" t="n"/>
+      <c r="H1304" s="2" t="inlineStr">
+        <is>
+          <t>依據《勞工健康保護規則》規定，醫護人員臨場健康服務應辦理之事項，不包含「定期辦理健康檢查」。
+說明
+健康檢查的執行主體：依規定健康檢查通常是由雇主委託「醫療機構」或符合規定的特約醫院來定期辦理，醫護人員（廠護或特約醫護人員）在廠內的職責是進行健檢結果的分析與評估、異常者追蹤管理及健康指導，而非由醫護人員親自「定期辦理健康檢查」本身。
+包含之事項：
+協助雇主選配勞工從事適當工作。
+健康促進之規劃和實施（健康教育、衛生指導等）。
+健康諮詢和急救及緊急處置。
+Facebook
+·臺北市政府勞動局 - 勞動臺北</t>
+        </is>
+      </c>
+      <c r="I1304" s="2" t="inlineStr"/>
     </row>
     <row r="1305" ht="92.59999999999999" customHeight="1">
       <c r="A1305" s="2" t="n">
@@ -56128,8 +58543,18 @@
       <c r="G1305" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H1305" s="2" t="n"/>
-      <c r="I1305" s="2" t="n"/>
+      <c r="H1305" s="2" t="inlineStr">
+        <is>
+          <t>答案為：暴飲暴食。
+原因說明
+暴飲暴食：屬於不健康的應對機制，會對身體健康造成負擔，並不是正確或有效的壓力改善方法。
+學習自我放鬆及調適、改善工作環境、坦誠傾吐：均為正向且有助於舒緩、調適或解決工作壓力的有效方法。
+Further Exploration
+參考 職業安全衛生管理乙級題庫 了解更多相關考題與解析。
+在 查看其他使用者的討論與統計。</t>
+        </is>
+      </c>
+      <c r="I1305" s="2" t="inlineStr"/>
     </row>
     <row r="1306" ht="92.59999999999999" customHeight="1">
       <c r="A1306" s="2" t="n">
@@ -56163,8 +58588,38 @@
       <c r="G1306" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H1306" s="2" t="n"/>
-      <c r="I1306" s="2" t="n"/>
+      <c r="H1306" s="2" t="inlineStr">
+        <is>
+          <t>答案是：身高之平方。
+BMI 計算公式重點
+分子：體重（公斤，kg）
+分母：身高之平方（公尺平方，
+m
+2
+m
+2
+）
+完整公式：
+B
+M
+I
+=
+體
+重
+(
+k
+g
+)
+身
+高
+2
+(
+m
+2
+)</t>
+        </is>
+      </c>
+      <c r="I1306" s="2" t="inlineStr"/>
     </row>
     <row r="1307" ht="92.59999999999999" customHeight="1">
       <c r="A1307" s="2" t="n">
@@ -56190,8 +58645,20 @@
       <c r="G1307" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1307" s="2" t="n"/>
-      <c r="I1307" s="2" t="n"/>
+      <c r="H1307" s="2" t="inlineStr">
+        <is>
+          <t>以身體質量指數（BMI）來說，26 不屬於正常範圍，它已經達到過重的標準（24 ≦ BMI ＜ 27）。
+依據我國衛生福利部國民健康署的成人健康體位標準：
+www.hpa.gov.tw
+體重過輕：BMI ＜ 18.5
+正常範圍：18.5 ≦ BMI ＜ 24
+過重：24 ≦ BMI ＜ 27
+輕度肥胖：27 ≦ BMI ＜ 30
+dpt.cch.org.tw
+選項中的 19、21、23 皆介於 18.5 與 24 之間，屬於正常範圍。</t>
+        </is>
+      </c>
+      <c r="I1307" s="2" t="inlineStr"/>
     </row>
     <row r="1308" ht="92.59999999999999" customHeight="1">
       <c r="A1308" s="2" t="n">
@@ -56217,8 +58684,12 @@
       <c r="G1308" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H1308" s="2" t="n"/>
-      <c r="I1308" s="2" t="n"/>
+      <c r="H1308" s="2" t="inlineStr">
+        <is>
+          <t>Google AI 摘要未抓取到，請手動補充。</t>
+        </is>
+      </c>
+      <c r="I1308" s="2" t="inlineStr"/>
     </row>
     <row r="1309" ht="92.59999999999999" customHeight="1">
       <c r="A1309" s="2" t="n">
@@ -56244,8 +58715,16 @@
       <c r="G1309" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H1309" s="2" t="n"/>
-      <c r="I1309" s="2" t="n"/>
+      <c r="H1309" s="2" t="inlineStr">
+        <is>
+          <t>根據衛生福利部國民健康署的建議，成人男性的腰圍應小於 90 公分。
+以下是台灣成人健康腰圍的標準：
+男性：應小於 90 公分（約 35.5 吋）
+女性：應小於 80 公分（約 31.5 吋）
+若腰圍超過此標準，代表腹部脂肪累積過多（中心型肥胖），會大幅增加罹患代謝症候群、心血管疾病及糖尿病的風險。</t>
+        </is>
+      </c>
+      <c r="I1309" s="2" t="inlineStr"/>
     </row>
     <row r="1310" ht="92.59999999999999" customHeight="1">
       <c r="A1310" s="2" t="n">
@@ -56271,8 +58750,13 @@
       <c r="G1310" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H1310" s="2" t="n"/>
-      <c r="I1310" s="2" t="n"/>
+      <c r="H1310" s="2" t="inlineStr">
+        <is>
+          <t>依據衛生福利部國民健康署之建議，成人女性的腰圍應小於 80 公分（約31吋）。
+www.hpa.gov.tw</t>
+        </is>
+      </c>
+      <c r="I1310" s="2" t="inlineStr"/>
     </row>
     <row r="1311" ht="92.59999999999999" customHeight="1">
       <c r="A1311" s="2" t="n">
@@ -56306,8 +58790,20 @@
       <c r="G1311" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H1311" s="2" t="n"/>
-      <c r="I1311" s="2" t="n"/>
+      <c r="H1311" s="2" t="inlineStr">
+        <is>
+          <t>勞工因長期工作壓迫及重複性作業引起椎間盤突出，屬於人因工程（或稱人因性）危害因子。
+奇美醫院 危害解析
+人因工程危害：指工作環境、操作工具、機器設備與人體施力、姿勢之間的互動關係不良。長期重複性動作、過度施力、姿勢不良或身體局部壓迫，容易促發肌肉骨骼疾病，如椎間盤突出、腕隧道症候群等。
+奇美醫院
+與其他因子的區別：
+化學性：如粉塵、有機溶劑、氣體等引起的中毒或病變。
+物理性：如噪音、異常溫濕度、輻射、振動等物理能量造成的危害。
+生物性：如細菌、病毒、寄生蟲等感染。
+NTNU</t>
+        </is>
+      </c>
+      <c r="I1311" s="2" t="inlineStr"/>
     </row>
     <row r="1312" ht="92.59999999999999" customHeight="1">
       <c r="A1312" s="2" t="n">
@@ -56341,8 +58837,17 @@
       <c r="G1312" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H1312" s="2" t="n"/>
-      <c r="I1312" s="2" t="n"/>
+      <c r="H1312" s="2" t="inlineStr">
+        <is>
+          <t>依據《職業安全衛生法》第20條規定，雇主對在職勞工應施行健康檢查，其健康檢查費用應由雇主全額負擔。
+臺北市政府全球資訊網 相關重點整理
+在職勞工健檢：包含一般健康檢查及特殊健康檢查，費用皆須由[勞動部職業安全衛生署雇主全額負擔]。
+新進員工體檢：任職前實施的「體格檢查」，法規未明定，得由勞資雙方自行協商。
+勞工義務：勞工有接受健康檢查之義務，若無故拒絕受檢，依同法可處新臺幣 3,000 元以下罰鍰。
+www.hrdaily.tw</t>
+        </is>
+      </c>
+      <c r="I1312" s="2" t="inlineStr"/>
     </row>
     <row r="1313" ht="92.59999999999999" customHeight="1">
       <c r="A1313" s="2" t="n">
@@ -56376,8 +58881,22 @@
       <c r="G1313" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H1313" s="2" t="n"/>
-      <c r="I1313" s="2" t="n"/>
+      <c r="H1313" s="2" t="inlineStr">
+        <is>
+          <t>具有面無表情、講話結巴、輕微顫抖等症狀，最可能的答案是 (A) 巴金森氏症候群。
+症狀解析
+面無表情（面具臉）：因臉部肌肉僵硬、表情肌活動減少所致。
+講話結巴、語音含糊：因喉部與發音肌肉控制力變差、說話單調或含糊不清。
+輕微顫抖：常見如靜止性震顫（手部在放鬆、靜止時不自主抖動），為巴金森氏症候群的核心特徵之一。
+亞東醫院 To help you with similar questions, could you tell me:
+What field of study or exam you are preparing for (e.g., nursing, physical therapy)?
+If you need further explanations for the other options listed?
+This will help me tailor the level of detail for future explanations.
+.具有面無表情，講話結巴、輕微顫抖等症狀，可能為下列何 ...
+2018年10月1日 — 15.具有面無表情，講話結巴、輕微顫抖等症狀，可能為下列何種症狀？ (A)巴金森氏症候群 (B)末梢 血管病變 (C)多發性神經病變 (D)化學性肝炎。</t>
+        </is>
+      </c>
+      <c r="I1313" s="2" t="inlineStr"/>
     </row>
     <row r="1314" ht="92.59999999999999" customHeight="1">
       <c r="A1314" s="2" t="n">
@@ -56411,8 +58930,20 @@
       <c r="G1314" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H1314" s="2" t="n"/>
-      <c r="I1314" s="2" t="n"/>
+      <c r="H1314" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+關節活動度與柔軟度最相關。
+花蓮縣衛生局
+相關說明
+柔軟度：指人體關節能夠活動的最大範圍，主要受到骨骼結構、肌肉、肌腱與韌帶等組織的影響。
+肌耐力：指肌肉持續收縮或對抗阻力時的持久性，與關節的可動範圍不同。
+身體組成：指身體脂肪組織與非脂肪組織（肌肉、骨骼等）的比例。
+心肺適能：指心臟、肺臟與血管輸送氧氣至全身肌肉供利用的綜合能力。
+www.hpa.gov.tw</t>
+        </is>
+      </c>
+      <c r="I1314" s="2" t="inlineStr"/>
     </row>
     <row r="1315" ht="92.59999999999999" customHeight="1">
       <c r="A1315" s="2" t="n">
@@ -56446,8 +58977,17 @@
       <c r="G1315" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1315" s="2" t="n"/>
-      <c r="I1315" s="2" t="n"/>
+      <c r="H1315" s="2" t="inlineStr">
+        <is>
+          <t>以上皆是。
+這三類戶外工作者在日常作業中，都有極高機率接觸到虎頭蜂：
+園藝業工作者：經常在樹木、灌木叢中修剪枝葉，容易驚動在樹枝上或草叢中築巢的虎頭蜂。
+空調裝修業工作者：室外機周邊、屋簷下及建築物夾縫是虎頭蜂極為喜愛的築巢地點，維修時很容易正面遭遇。
+田野調查人員：需要深入山林、草叢或未開發的自然環境，直接進入虎頭蜂的活動核心區域。
+為了保障您的安全，請問您需要了解防蜂穿著建議、遭遇虎頭蜂時的緊急應變避險流程，還是被螫傷後的急救處理步驟呢？ 內容</t>
+        </is>
+      </c>
+      <c r="I1315" s="2" t="inlineStr"/>
     </row>
     <row r="1316" ht="77.15000000000001" customHeight="1">
       <c r="A1316" s="2" t="n">
@@ -56481,8 +59021,17 @@
       <c r="G1316" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H1316" s="2" t="n"/>
-      <c r="I1316" s="2" t="n"/>
+      <c r="H1316" s="2" t="inlineStr">
+        <is>
+          <t>烏腳病（題目誤寫為鳥腳病）是砷中毒。
+维基百科
+1950年代，台灣西南沿海地區（如台南、嘉義濱海鄉鎮）的居民因為飲用含砷量過高的深井水，導致慢性砷中毒。這種中毒會引發嚴重的末梢周邊血管病變，使患者雙足缺血、發黑甚至壞疽，因此被稱為「烏腳病」。
+國家文化記憶庫 所以正確答案應選擇：砷（或選項中的 B）。
+請問您是在準備特定的考試（如醫學、公衛或歷史題），還是想了解更多關於台灣烏腳病的歷史與防治背景呢？
+.烏腳病是什麼中毒?(A)銀(B)砷(C)鉛(D)錳。 - 年5月29日 — 32.烏腳病是什麼中毒? (A)銀 (B)砷 (C)鉛 (D)錳。 答案：登入後查看 統計： A(21), B(401), C(83), D(20), E(0) #3243050 ...</t>
+        </is>
+      </c>
+      <c r="I1316" s="2" t="inlineStr"/>
     </row>
     <row r="1317" ht="92.59999999999999" customHeight="1">
       <c r="A1317" s="2" t="n">
@@ -56516,8 +59065,21 @@
       <c r="G1317" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H1317" s="2" t="n"/>
-      <c r="I1317" s="2" t="n"/>
+      <c r="H1317" s="2" t="inlineStr">
+        <is>
+          <t>員工發生傷害事故時，應由發生事故部門（即主管或現場負責人）負責主導填寫災害事故調查表。
+各部門在事故調查中的主要分工與角色如下：
+部門	核心職責	在事故調查中的角色
+發生事故部門	主導填寫與改善	最了解現場實際狀況與作業流程，須主導填寫事故經過，並提出立即改善對策。
+工安部門	協助、審查與分析	負責協助事故部門進行原因分析、提供法規諮詢，並追蹤後續改善措施的落實情況。
+人事部門	權益辦理	負責後續的勞保職災補償、請假手續及員工關懷。
+政風部門	一般不參與	僅在涉及公務人員舞弊、貪瀆或重大違法失職時才介入，不參與一般職業災害調查。
+為了協助您更精準地處理後續流程，請問：
+這起事故是否已達到重大職災（如死亡或3人以上受傷）需要通報勞檢所的標準？
+您需要填寫的是內部留存的調查表，還是申報勞保職災用的特定官方書表？ 內容</t>
+        </is>
+      </c>
+      <c r="I1317" s="2" t="inlineStr"/>
     </row>
     <row r="1318" ht="92.59999999999999" customHeight="1">
       <c r="A1318" s="2" t="n">
@@ -56551,8 +59113,15 @@
       <c r="G1318" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H1318" s="2" t="n"/>
-      <c r="I1318" s="2" t="n"/>
+      <c r="H1318" s="2" t="inlineStr">
+        <is>
+          <t>發生事故處理以 (A) 停止作業避免災害持續擴大 為最優先。
+事故處理原則
+立即停工：發生事故時，首要之務是停止現場作業，防止危害擴散或造成二次災害。
+後續步驟：待災害控制與人員急救（搶救）告一段落後，才進行現場封鎖、展開事故調查與相關通報。</t>
+        </is>
+      </c>
+      <c r="I1318" s="2" t="inlineStr"/>
     </row>
     <row r="1319" ht="77.15000000000001" customHeight="1">
       <c r="A1319" s="2" t="n">
@@ -56586,8 +59155,15 @@
       <c r="G1319" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H1319" s="2" t="n"/>
-      <c r="I1319" s="2" t="n"/>
+      <c r="H1319" s="2" t="inlineStr">
+        <is>
+          <t>職業安全衛生法所定義之職業災害，是指因勞動場所之建築物、機械、設備、原料、材料、化學品、氣體、蒸氣、粉塵等或作業活動及其他職業上原因引起之工作者疾病、傷害、失能或死亡。
+選項中的正確答案為：勞動場所。
+依據職業安全衛生法第2條規定：
+勞動場所：指於勞動契約存續中，由雇主所提示，使勞工履行契約提供勞務之場所；自營作業者實際從事勞動之場所；及其他受工作場所負責人指揮或監督從事勞動之人員，實際從事勞動之場所。</t>
+        </is>
+      </c>
+      <c r="I1319" s="2" t="inlineStr"/>
     </row>
     <row r="1320" ht="92.59999999999999" customHeight="1">
       <c r="A1320" s="2" t="n">
@@ -56621,8 +59197,20 @@
       <c r="G1320" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H1320" s="2" t="n"/>
-      <c r="I1320" s="2" t="n"/>
+      <c r="H1320" s="2" t="inlineStr">
+        <is>
+          <t>這題的正確答案是 緊急應變計畫。
+解析與說明
+事業單位為了因應地震、火災、風災或化學品洩漏等突發災害，平時必須做好各項防災措施，並會依據《職業安全衛生管理辦法》等法規，制訂「緊急應變計畫」。
+在緊急應變計畫中，通常會成立緊急應變小組，並將成員區分為五大任務編組，以確保災害發生時能有條不紊地進行處置：
+指揮官（或通報班/連絡編組）：負責對外聯絡、內部通報與整體指揮。
+警戒組（警戒編組）：負責管制災區現場、協助維持秩序及交通疏導。
+搶救組（搶救編組）：負責初期滅火、關閉危險源（如瓦斯、電源）及基礎搶救。
+避難引導組（疏散組）：負責引導員工及現場人員依循安全路線疏散。
+安全防護組（救護編組）：負責受傷人員的緊急包紮、CPR 救護及送醫協調。</t>
+        </is>
+      </c>
+      <c r="I1320" s="2" t="inlineStr"/>
     </row>
     <row r="1321" ht="92.59999999999999" customHeight="1">
       <c r="A1321" s="2" t="n">
@@ -56656,8 +59244,19 @@
       <c r="G1321" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1321" s="2" t="n"/>
-      <c r="I1321" s="2" t="n"/>
+      <c r="H1321" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+職業災害調查、分析時，應分析的正確選項為 (D) 以上皆是。
+職業災害的原因分析通常採分層架構進行完整檢討：
+社團法人中華民國技能發展協會
+直接原因：指立即導致災害或傷害發生的接觸因素（如人體直接接觸能量、危害物，或物體飛落、墜落等）。
+間接原因：指促成事故發生的不安全狀況（環境或設備缺陷）與不安全行為（人員操作失誤或未依規定）。
+基本原因：指更深層的安全衛生管理系統缺陷或組織疏失。
+iPEDIA 百科</t>
+        </is>
+      </c>
+      <c r="I1321" s="2" t="inlineStr"/>
     </row>
     <row r="1322" ht="92.59999999999999" customHeight="1">
       <c r="A1322" s="2" t="n">
@@ -56691,8 +59290,18 @@
       <c r="G1322" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1322" s="2" t="n"/>
-      <c r="I1322" s="2" t="n"/>
+      <c r="H1322" s="2" t="inlineStr">
+        <is>
+          <t>(D) 評價非屬職業災害原因之調查步驟。
+職業災害調查的主要四步驟
+職業災害原因之調查與分析主要包含以下四個步驟：
+掌握災害狀況（確認事實）：收集與災害發生有關的人、物、管理及時間序列等經過。
+發現問題點（掌握災害要因）：找出不安全動作、不安全狀態及安全衛生管理缺陷等因素。
+決定根本問題點（決定災害原因）：檢討各項要因之相互關係與影響程度，決定直接與根本原因。
+「評價」通常屬於事後安全衛生管理系統或改善措施的成效檢討，而非災害原因調查的直接步驟。</t>
+        </is>
+      </c>
+      <c r="I1322" s="2" t="inlineStr"/>
     </row>
     <row r="1323" ht="92.59999999999999" customHeight="1">
       <c r="A1323" s="2" t="n">
@@ -56726,8 +59335,17 @@
       <c r="G1323" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H1323" s="2" t="n"/>
-      <c r="I1323" s="2" t="n"/>
+      <c r="H1323" s="2" t="inlineStr">
+        <is>
+          <t>職業災害發生因不安全狀態或不安全行為引起者，屬間接原因。
+職業災害原因分析
+直接原因：人體直接接觸能量、危險物或有害物。
+間接原因：包含不安全行為（人為缺失）與不安全狀態（環境或設備缺陷）。
+基本原因：源自安全衛生管理系統的缺陷或政策不足。
+iPEDIA 百科</t>
+        </is>
+      </c>
+      <c r="I1323" s="2" t="inlineStr"/>
     </row>
     <row r="1324" ht="108" customHeight="1">
       <c r="A1324" s="2" t="n">
@@ -56761,8 +59379,17 @@
       <c r="G1324" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1324" s="2" t="n"/>
-      <c r="I1324" s="2" t="n"/>
+      <c r="H1324" s="2" t="inlineStr">
+        <is>
+          <t>在施工架上作業的災害原因分析中，答案是 以上皆是。
+在職業安全衛生的災害原因分析（事故連鎖理論）中，原因通常分為：
+直接原因：不安全狀態（如人體墜落、物體飛落）與不安全動作。
+間接原因：技術、教育或身體精神上的缺陷（例如：未配戴或未使用正確的個人防護具、未設置必要的安全防護設施等管理與執行面疏失）。
+基本原因：管理制度不健全。
+題目中所提到的未配戴個人防護具安全帽、未使用安全帶、以及未設置及使用安全踏板，皆屬於造成墜落或飛落災害的典型間接原因（安全管理與防護措施未落實）。</t>
+        </is>
+      </c>
+      <c r="I1324" s="2" t="inlineStr"/>
     </row>
     <row r="1325" ht="92.59999999999999" customHeight="1">
       <c r="A1325" s="2" t="n">
@@ -56796,8 +59423,17 @@
       <c r="G1325" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H1325" s="2" t="n"/>
-      <c r="I1325" s="2" t="n"/>
+      <c r="H1325" s="2" t="inlineStr">
+        <is>
+          <t>職業災害發生係因管理上缺陷，屬於(C) 基本原因。
+iPEDIA 百科 職業災害原因分類
+直接原因：人體直接接觸能量（如機械能、電能、熱能）或暴露於有害物、危險物。
+間接原因：屬於人為的不安全動作或環境的不安全狀況。
+基本原因：源自潛在管理系統的缺陷，例如安全衛生政策、教育訓練或管理制度的缺失。
+應用化學及材料科學系</t>
+        </is>
+      </c>
+      <c r="I1325" s="2" t="inlineStr"/>
     </row>
     <row r="1326" ht="92.59999999999999" customHeight="1">
       <c r="A1326" s="2" t="n">
@@ -56827,8 +59463,17 @@
       <c r="G1326" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H1326" s="2" t="n"/>
-      <c r="I1326" s="2" t="n"/>
+      <c r="H1326" s="2" t="inlineStr">
+        <is>
+          <t>職業災害發生係因能量吸收或危害物暴露，屬於直接原因。
+原因解析
+直接原因：人體直接接觸或吸收過量的能量（如機械能、電能、熱能等）或暴露於危害物（如化學品、毒物質）而造成傷害。
+間接原因：包含不安全行為與不安全狀況（如未設置防護設備、違規操作等）。
+基本原因：指管理上的缺陷或個人基本因素等根源。
+iPEDIA 百科</t>
+        </is>
+      </c>
+      <c r="I1326" s="2" t="inlineStr"/>
     </row>
     <row r="1327" ht="92.59999999999999" customHeight="1">
       <c r="A1327" s="2" t="n">
@@ -56862,8 +59507,16 @@
       <c r="G1327" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H1327" s="2" t="n"/>
-      <c r="I1327" s="2" t="n"/>
+      <c r="H1327" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+此能量或危害物即為引起災害的直接原因。
+原因解析
+直接原因：指直接導致傷害或損失的能量（如電能、動能、熱能）或危害物（如毒化物、腐蝕性物質），當人體或物體無法承受或安全吸收時便會發生災害。
+間接/基本原因：通常指造成不安全動作或不安全設備的背後因素（如管理缺失、教育訓練不足、個人心理或生理因素等）。</t>
+        </is>
+      </c>
+      <c r="I1327" s="2" t="inlineStr"/>
     </row>
     <row r="1328" ht="108" customHeight="1">
       <c r="A1328" s="2" t="n">
@@ -56897,8 +59550,19 @@
       <c r="G1328" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H1328" s="2" t="n"/>
-      <c r="I1328" s="2" t="n"/>
+      <c r="H1328" s="2" t="inlineStr">
+        <is>
+          <t>在勞工作業安全與職業災害分析中，未設置護欄屬於間接原因（又稱不安全狀態）[1]。
+職業災害原因分析
+根據勞安與職災分析的理論（如瑞士乳酪理論或海因里希法則），災害原因通常分為以下三個層次：
+直接原因：直接接觸並對勞工身體造成傷害的物理現象或能量。在此案例中，直接原因為「勞工發生墜落（人體與地面或下層撞擊）」[1]。
+間接原因：導致直接原因發生的不安全動作或不安全狀態[1]。
+不安全狀態（物的原因）：例如本題的「開放邊緣未設置護欄」、設備缺陷或照明不足等[1]。
+不安全動作（人的原因）：例如勞工未配戴安全帶、違規操作等[1]。
+基本原因：最深層的管理、制度或教育訓練問題。例如「安全衛生管理不善」、未落實自動檢查、未實施安全教育訓練等[1]。</t>
+        </is>
+      </c>
+      <c r="I1328" s="2" t="inlineStr"/>
     </row>
     <row r="1329" ht="92.59999999999999" customHeight="1">
       <c r="A1329" s="2" t="n">
@@ -56932,8 +59596,17 @@
       <c r="G1329" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H1329" s="2" t="n"/>
-      <c r="I1329" s="2" t="n"/>
+      <c r="H1329" s="2" t="inlineStr">
+        <is>
+          <t>雇主未指派作業主管於現場指揮監督是屬於職業災害發生的基本原因。
+職業災害原因分類
+直接原因：人體直接接觸能量（如機械能、電能）或危險、有害物質而導致傷害的立即原因。
+間接原因：屬於現場的不安全狀況（如未設防墜設施）或勞工的不安全行為（如未正確配戴安全帶）。
+基本原因：屬於管理上的缺陷，如雇主未設置作業主管在場監督、未實施教育訓練或未訂定安全衛生管理計畫等。
+勞動部職業安全衛生署</t>
+        </is>
+      </c>
+      <c r="I1329" s="2" t="inlineStr"/>
     </row>
     <row r="1330" ht="92.59999999999999" customHeight="1">
       <c r="A1330" s="2" t="n">
@@ -56967,8 +59640,17 @@
       <c r="G1330" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H1330" s="2" t="n"/>
-      <c r="I1330" s="2" t="n"/>
+      <c r="H1330" s="2" t="inlineStr">
+        <is>
+          <t>雇主未對作業人員實施教育訓練是屬於職業災害原因分析中的基本原因（選項C）。
+職業災害原因分級說明
+直接原因：人體直接接觸能量（如機械能、電能、熱能）或危險、有害物而導致傷害或死亡（例如：自高處墜落、感電、機械捲入）。
+間接原因：屬於現場的不安全狀況（如未設防護網、未裝安全護具）或勞工的不安全行為（如未配戴安全帽、未用防護具）。
+基本原因：追根究底屬於管理上的缺陷與制度缺失，例如未實施自動檢查、未訂定安全衛生工作守則以及未對勞工實施安全衛生教育訓練等。
+勞動部職業安全衛生署</t>
+        </is>
+      </c>
+      <c r="I1330" s="2" t="inlineStr"/>
     </row>
     <row r="1331" ht="92.59999999999999" customHeight="1">
       <c r="A1331" s="2" t="n">
@@ -57002,8 +59684,19 @@
       <c r="G1331" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H1331" s="2" t="n"/>
-      <c r="I1331" s="2" t="n"/>
+      <c r="H1331" s="2" t="inlineStr">
+        <is>
+          <t>作業人員未確實使用個人防護具（PPE）屬於間接原因（不安全行為）。
+在職業安全衛生的事故原因分析中，通常分為以下三個層次：
+直接原因：直接導致受傷的能量或物質。例如：墜落、感電、被撞擊、切傷。
+間接原因：引發直接原因的因素，分為兩大類：
+不安全行為：人的錯誤。例如：未確實佩戴防護具、違規操作、疲勞駕駛。
+不安全設備/環境：物的缺陷。例如：機具防護罩破損、照明不足、通道堆滿雜物。
+基本原因：管理、組織或法規層面的根本問題。例如：安全訓練不足、缺乏安全管理制度、無經費購置防護具。
+由於「未確實使用個人防護具」屬於作業人員的不安全行為，因此歸類為間接原因。</t>
+        </is>
+      </c>
+      <c r="I1331" s="2" t="inlineStr"/>
     </row>
     <row r="1332" ht="92.59999999999999" customHeight="1">
       <c r="A1332" s="2" t="n">
@@ -57037,8 +59730,17 @@
       <c r="G1332" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1332" s="2" t="n"/>
-      <c r="I1332" s="2" t="n"/>
+      <c r="H1332" s="2" t="inlineStr">
+        <is>
+          <t>答案是：工廠爆炸至居民死傷多人。
+原因說明
+依據《職業安全衛生法》第2條第5項規定，職業災害係指工作者因勞動場所之建築物、機械、設備、原料、材料、化學品、氣體、蒸氣、粉塵等媒介物或作業活動及其他職業上原因引起之工作者疾病、傷害、失能或死亡。
+勞動部職業安全衛生署 屬於職災：勞工於噴漆時有機溶劑中毒、勞工因工作罹患疾病、勞工屋頂作業墜落，均屬於工作者自身的職業傷害或職業疾病。
+不屬於職災：工廠爆炸造成一般「居民」死傷，因受害者並非該工作場所從事勞動的「工作者」，故不屬於職業安全衛生法所稱之職業災害。
+桃園市政府勞動檢查處</t>
+        </is>
+      </c>
+      <c r="I1332" s="2" t="inlineStr"/>
     </row>
     <row r="1333" ht="92.59999999999999" customHeight="1">
       <c r="A1333" s="2" t="n">
@@ -57072,8 +59774,22 @@
       <c r="G1333" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H1333" s="2" t="n"/>
-      <c r="I1333" s="2" t="n"/>
+      <c r="H1333" s="2" t="inlineStr">
+        <is>
+          <t>發生重大職業災害時，報告勞動檢查機構之責任屬於雇主。
+勞動部職業安全衛生署 依據《職業安全衛生法》第37條第2項規定，事業單位勞動場所發生死亡災害、3人以上罹災、1人以上罹災且需住院治療等重大職業災害時，雇主應於8小時內通報當地勞動檢查機構。
+勞動部職業安全衛生署
+需要了解更多職災通報的規定與罰則嗎？
+通報時限與情節
+罰鍰金額範圍
+現場保持原狀規範
+勞動部職業安全衛生署
+事業單位職災通報 - 勞動部職業安全衛生署
+依據職業安全衛生法第37條第2項規定: 事業單位勞動場所發生下列職業災害之一者，雇主應於八小時內通報勞動檢查機構： 一、發生死亡災害。 二、發生災害之罹災人數在三人以上。 三、發生災害之罹災人數在一人以上，且需住院治療。 四、其他經中央主管機關指定公告之災害。...
+顯示全部 內容</t>
+        </is>
+      </c>
+      <c r="I1333" s="2" t="inlineStr"/>
     </row>
     <row r="1334" ht="92.59999999999999" customHeight="1">
       <c r="A1334" s="2" t="n">
@@ -57107,8 +59823,17 @@
       <c r="G1334" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H1334" s="2" t="n"/>
-      <c r="I1334" s="2" t="n"/>
+      <c r="H1334" s="2" t="inlineStr">
+        <is>
+          <t>職業災害防止主要為職業安全衛生法。
+相關法規重點
+職業安全衛生法：第一條即明定「為防止職業災害，保障工作者安全及健康，特制定本法」。
+勞動檢查法：主要規範勞動檢查機構與檢查員的職權，以監督事業單位遵守勞動法令。
+勞動基準法：規範勞動條件最低標準，並包含職災補償責任，但非以「防止職災」為主要立法目的。
+勞工保險條例：規範社會保險給付，提供職災發生後的經濟補償。</t>
+        </is>
+      </c>
+      <c r="I1334" s="2" t="inlineStr"/>
     </row>
     <row r="1335" ht="92.59999999999999" customHeight="1">
       <c r="A1335" s="2" t="n">
@@ -57142,8 +59867,12 @@
       <c r="G1335" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1335" s="2" t="n"/>
-      <c r="I1335" s="2" t="n"/>
+      <c r="H1335" s="2" t="inlineStr">
+        <is>
+          <t>Google AI 摘要未抓取到，請手動補充。</t>
+        </is>
+      </c>
+      <c r="I1335" s="2" t="inlineStr"/>
     </row>
     <row r="1336" ht="92.59999999999999" customHeight="1">
       <c r="A1336" s="2" t="n">
@@ -57169,8 +59898,13 @@
       <c r="G1336" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H1336" s="2" t="n"/>
-      <c r="I1336" s="2" t="n"/>
+      <c r="H1336" s="2" t="inlineStr">
+        <is>
+          <t>傷害事故（輕傷事故）是指 24 小時內可恢復工作之輕傷害。
+正確答案為 24。</t>
+        </is>
+      </c>
+      <c r="I1336" s="2" t="inlineStr"/>
     </row>
     <row r="1337" ht="92.59999999999999" customHeight="1">
       <c r="A1337" s="2" t="n">
@@ -57204,8 +59938,18 @@
       <c r="G1337" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H1337" s="2" t="n"/>
-      <c r="I1337" s="2" t="n"/>
+      <c r="H1337" s="2" t="inlineStr">
+        <is>
+          <t>輕傷害非屬失能傷害。
+失能傷害在職業安全衛生統計中，主要包含下列四種分類：
+死亡
+永久全失能
+永久部分失能（或稱永久部份失能）
+暫時全失能
+勞動部職業安全衛生署 而「輕傷害」（或稱非失能傷害、僅需急救不至於失能或休班的輕微傷害）不屬於失能傷害的統計範疇。</t>
+        </is>
+      </c>
+      <c r="I1337" s="2" t="inlineStr"/>
     </row>
     <row r="1338" ht="92.59999999999999" customHeight="1">
       <c r="A1338" s="2" t="n">
@@ -57231,8 +59975,20 @@
       <c r="G1338" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1338" s="2" t="n"/>
-      <c r="I1338" s="2" t="n"/>
+      <c r="H1338" s="2" t="inlineStr">
+        <is>
+          <t>職業安全衛生法規所稱重傷之災害，住院治療連續達 24 小時以上。
+依據《職業安全衛生法施行細則》第49條規定，重傷災害係指造成罹災者肢體或器官嚴重受損、危及生命或造成身體機能嚴重喪失，且須住院治療連續達二十四小時以上之災害。因此正確選項為 24。
+想了解更多相關規定嗎？
+8小時內通報義務的災害類型
+違反規定的罰鍰金額
+勞動部-條文內容
+法規：職業安全衛生法施行細則（115.06.26修正）第49條 勞檢機構職責： - 派員檢查職場死亡/重傷災害，調查原因及責任歸屬 - 例外：其他法律已定有火災、爆炸、礦災、空難、海難、震災、毒化災、輻射事故、陸上交通事故之檢查/調查/鑑定機制者免除 重傷定義...
+顯示全部
+AI 回覆可能有誤。如需法律建議，請諮詢專業人士。 瞭解詳情</t>
+        </is>
+      </c>
+      <c r="I1338" s="2" t="inlineStr"/>
     </row>
     <row r="1339" ht="92.59999999999999" customHeight="1">
       <c r="A1339" s="2" t="n">
@@ -57266,8 +60022,13 @@
       <c r="G1339" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H1339" s="2" t="n"/>
-      <c r="I1339" s="2" t="n"/>
+      <c r="H1339" s="2" t="inlineStr">
+        <is>
+          <t>依據《職業安全衛生法》第37條第1項規定，事業單位工作場所發生職業災害時，雇主應即採取必要之急救、搶救等措施，並會同勞工代表實施調查、分析及作成紀錄。
+正確答案為：勞工代表</t>
+        </is>
+      </c>
+      <c r="I1339" s="2" t="inlineStr"/>
     </row>
     <row r="1340" ht="92.59999999999999" customHeight="1">
       <c r="A1340" s="2" t="n">
@@ -57301,8 +60062,18 @@
       <c r="G1340" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H1340" s="2" t="n"/>
-      <c r="I1340" s="2" t="n"/>
+      <c r="H1340" s="2" t="inlineStr">
+        <is>
+          <t>事業單位勞動場所發生死亡職業災害時，雇主應於 8 小時內通報勞動檢查機構。
+相關法規與通報要件
+依據《職業安全衛生法》第 37 條第 2 項規定，勞動場所發生下列重大職業災害之一時，雇主應在知悉後 8 小時內通報當地勞動部職業安全衛生署所屬勞動檢查機構：
+勞動部職業安全衛生署 發生死亡災害
+發生災害之罹災人數在三人以上
+發生災害之罹災人數在一人以上，且需住院治療
+勞動部職業安全衛生署</t>
+        </is>
+      </c>
+      <c r="I1340" s="2" t="inlineStr"/>
     </row>
     <row r="1341" ht="77.15000000000001" customHeight="1">
       <c r="A1341" s="2" t="n">
@@ -57336,8 +60107,12 @@
       <c r="G1341" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1341" s="2" t="n"/>
-      <c r="I1341" s="2" t="n"/>
+      <c r="H1341" s="2" t="inlineStr">
+        <is>
+          <t>Google AI 摘要未抓取到，請手動補充。</t>
+        </is>
+      </c>
+      <c r="I1341" s="2" t="inlineStr"/>
     </row>
     <row r="1342" ht="77.15000000000001" customHeight="1">
       <c r="A1342" s="2" t="n">
@@ -57371,8 +60146,18 @@
       <c r="G1342" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1342" s="2" t="n"/>
-      <c r="I1342" s="2" t="n"/>
+      <c r="H1342" s="2" t="inlineStr">
+        <is>
+          <t>以上皆是。
+依據《職業安全衛生法》第37條第2項規定，事業單位勞動場所發生下列職業災害之一者，雇主應於知悉後 8小時內 通報勞動檢查機構：
+勞動部職業安全衛生署 發生死亡災害
+發生災害之罹災人數在3人以上
+發生災害之罹災人數在1人以上，且需住院治療（不包含僅留院觀察）
+其他經中央主管機關指定公告之災害
+勞動部職業安全衛生署</t>
+        </is>
+      </c>
+      <c r="I1342" s="2" t="inlineStr"/>
     </row>
     <row r="1343" ht="77.15000000000001" customHeight="1">
       <c r="A1343" s="2" t="n">
@@ -57406,8 +60191,12 @@
       <c r="G1343" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H1343" s="2" t="n"/>
-      <c r="I1343" s="2" t="n"/>
+      <c r="H1343" s="2" t="inlineStr">
+        <is>
+          <t>Google AI 摘要未抓取到，請手動補充。</t>
+        </is>
+      </c>
+      <c r="I1343" s="2" t="inlineStr"/>
     </row>
     <row r="1344" ht="92.59999999999999" customHeight="1">
       <c r="A1344" s="2" t="n">
@@ -57441,8 +60230,16 @@
       <c r="G1344" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1344" s="2" t="n"/>
-      <c r="I1344" s="2" t="n"/>
+      <c r="H1344" s="2" t="inlineStr">
+        <is>
+          <t>此事故為職業災害，答案選 是。
+判定原因
+因工作受傷：勞工是在工作時間內、因執行職務而導致身體受傷，符合職業災害（或稱職業傷害）的定義。
+與情節無關：是否為職業災害，與「受傷的嚴重程度」或「勞工有沒有特別提出繁複申請」無關，只要事實上是因公受傷，就直接認定為職業災害。
+Yourator 新創・數位人才求職平台</t>
+        </is>
+      </c>
+      <c r="I1344" s="2" t="inlineStr"/>
     </row>
     <row r="1345" ht="92.59999999999999" customHeight="1">
       <c r="A1345" s="2" t="n">
@@ -57468,8 +60265,18 @@
       <c r="G1345" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1345" s="2" t="n"/>
-      <c r="I1345" s="2" t="n"/>
+      <c r="H1345" s="2" t="inlineStr">
+        <is>
+          <t>直屬勞動部職業災害統計規範（暫時全失能損失日數計算方式），受傷當日及恢復工作當日均不計入損失工作日數。
+勞動部職業安全衛生署
+正確答案：0
+勞動部職業安全衛生署 損失日數計算原則
+不計入當日：不包括受傷當日（第一天上午）以及恢復工作當日（第二天下午復工）。
+未達整日不能工作：因為兩天都沒有達到「全日不能工作」的狀態，中間也沒有經過其他全日無法出勤的完整天數，所以失能損失工作日數為 0日。
+勞動部職業安全衛生署</t>
+        </is>
+      </c>
+      <c r="I1345" s="2" t="inlineStr"/>
     </row>
     <row r="1346" ht="92.59999999999999" customHeight="1">
       <c r="A1346" s="2" t="n">
@@ -57503,8 +60310,17 @@
       <c r="G1346" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1346" s="2" t="n"/>
-      <c r="I1346" s="2" t="n"/>
+      <c r="H1346" s="2" t="inlineStr">
+        <is>
+          <t>此勞工缺席兩個半天之工資應 領全薪。
+臺中市勞工局
+職業災害與公傷病假薪資處理
+法令依據：依據《勞動基準法》第59條第2款及《勞工請假規則》第6條規定，勞工因遭遇職業災害而致傷害，在治療、休養期間，雇主應給予公傷病假，並應按其原領工資數額予以補償（即領取全薪）。
+本題解析：勞工因工作受傷請公傷假，雖請假期間涵蓋兩個半天（當天下午與隔天上午），但因屬於公傷病假且醫療不能工作期間，雇主必須全額給付原領工資，故應選「領全薪」。
+臺中市勞工局</t>
+        </is>
+      </c>
+      <c r="I1346" s="2" t="inlineStr"/>
     </row>
     <row r="1347" ht="92.59999999999999" customHeight="1">
       <c r="A1347" s="2" t="n">
@@ -57538,8 +60354,16 @@
       <c r="G1347" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H1347" s="2" t="n"/>
-      <c r="I1347" s="2" t="n"/>
+      <c r="H1347" s="2" t="inlineStr">
+        <is>
+          <t>依勞工保險職業災害給付案件統計，選項中以 (B) 被夾、被捲 較常發生。
+職業災害類型比較
+被夾、被捲：在機械操作、製造業等工作場所中，因接觸轉動機械或夾夾狀態，屬於發生頻率相對較高的職災傷害類型。
+墜落：雖為常見且容易導致嚴重失能或死亡的重大災害類型，但在全體勞保職災給付案件的整體發生「總人次」統計中，被夾、被捲的案件數量通常居多。
+感電 與 火災、爆炸：發生的機率與總案件數相對較低。</t>
+        </is>
+      </c>
+      <c r="I1347" s="2" t="inlineStr"/>
     </row>
     <row r="1348" ht="108" customHeight="1">
       <c r="A1348" s="2" t="n">
@@ -57573,8 +60397,17 @@
       <c r="G1348" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1348" s="2" t="n"/>
-      <c r="I1348" s="2" t="n"/>
+      <c r="H1348" s="2" t="inlineStr">
+        <is>
+          <t>敘述「於當月職業災害統計月報表陳報者，得免24小時內（或8小時內）報告檢查機構」是有誤的（選項D錯誤）。
+依據現行《職業安全衛生法》第37條規定，事業單位工作場所發生勞工死亡等職災時，雇主應於8小時內通報勞動檢查機構，並無「透過月報表陳報即可免除8小時內通報義務」的規定。
+相關規定重點
+採取必要措施：發生職災時，雇主應即採取急救、搶救等必要措施。
+保護現場：除必要之急救、搶救外，非經司法機關或勞動檢查機構許可，不得移動或破壞現場。
+通報時限：發生死亡災害、3人以上傷病等重大職業災害，應於 8小時內 報告勞動檢查機構。</t>
+        </is>
+      </c>
+      <c r="I1348" s="2" t="inlineStr"/>
     </row>
     <row r="1349" ht="92.59999999999999" customHeight="1">
       <c r="A1349" s="2" t="n">
@@ -57608,8 +60441,13 @@
       <c r="G1349" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1349" s="2" t="n"/>
-      <c r="I1349" s="2" t="n"/>
+      <c r="H1349" s="2" t="inlineStr">
+        <is>
+          <t>應由雇主會同勞工代表實施調查、分析及作成紀錄。
+依據《職業安全衛生法》第37條第1項規定：「事業單位工作場所發生職業災害，雇主應即採取必要之急救、搶救等措施，並會同勞工代表實施調查、分析及作成紀錄。」</t>
+        </is>
+      </c>
+      <c r="I1349" s="2" t="inlineStr"/>
     </row>
     <row r="1350" ht="77.15000000000001" customHeight="1">
       <c r="A1350" s="2" t="n">
@@ -57643,8 +60481,12 @@
       <c r="G1350" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1350" s="2" t="n"/>
-      <c r="I1350" s="2" t="n"/>
+      <c r="H1350" s="2" t="inlineStr">
+        <is>
+          <t>事業單位勞動場所發生勞工死亡或罹災人數在3人以上之職業災害，雇主未於8小時內報告勞動檢查機構，依現行《職業安全衛生法》第43條規定，將處新臺幣3萬元以上30萬元以下罰鍰（選項中的「新臺幣3萬元以上30萬元以下罰鍰」）。</t>
+        </is>
+      </c>
+      <c r="I1350" s="2" t="inlineStr"/>
     </row>
     <row r="1351" ht="77.15000000000001" customHeight="1">
       <c r="A1351" s="2" t="n">
@@ -57678,8 +60520,13 @@
       <c r="G1351" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H1351" s="2" t="n"/>
-      <c r="I1351" s="2" t="n"/>
+      <c r="H1351" s="2" t="inlineStr">
+        <is>
+          <t>依職業安全衛生法第38條規定，中央主管機關指定之事業，雇主應每月依規定填載職業災害內容及統計，報請勞動檢查機構備查，並公布於工作場所。正確答案為「每月」。
+臺中市政府</t>
+        </is>
+      </c>
+      <c r="I1351" s="2" t="inlineStr"/>
     </row>
     <row r="1352" ht="77.15000000000001" customHeight="1">
       <c r="A1352" s="2" t="n">
@@ -57713,8 +60560,14 @@
       <c r="G1352" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H1352" s="2" t="n"/>
-      <c r="I1352" s="2" t="n"/>
+      <c r="H1352" s="2" t="inlineStr">
+        <is>
+          <t>目前最常採用上網線上填報的方式報請勞動檢查機構備查。
+依據《職業安全衛生法》第38條規定，事業單位通常透過勞動部職業安全衛生署建置的安全衛生履歷智能雲系統進行網路填報與申報。
+臺北市勞動檢查處</t>
+        </is>
+      </c>
+      <c r="I1352" s="2" t="inlineStr"/>
     </row>
     <row r="1353" ht="77.15000000000001" customHeight="1">
       <c r="A1353" s="2" t="n">
@@ -57748,8 +60601,12 @@
       <c r="G1353" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H1353" s="2" t="n"/>
-      <c r="I1353" s="2" t="n"/>
+      <c r="H1353" s="2" t="inlineStr">
+        <is>
+          <t>中央主管機關指定需每月填載職業災害統計的事業，是指勞工人數在 50 人以上之事業（或勞工人數未滿 50 人但經中央主管機關指定並由勞動檢查機構函知者）。因此正確選項為 50 人。</t>
+        </is>
+      </c>
+      <c r="I1353" s="2" t="inlineStr"/>
     </row>
     <row r="1354" ht="92.59999999999999" customHeight="1">
       <c r="A1354" s="2" t="n">
@@ -57783,8 +60640,13 @@
       <c r="G1354" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H1354" s="2" t="n"/>
-      <c r="I1354" s="2" t="n"/>
+      <c r="H1354" s="2" t="inlineStr">
+        <is>
+          <t>勞工因職業災害死亡，雇主應於 3 日內給予其遺屬喪葬費。
+依據《勞動基準法施行細則》第33條規定：「雇主依本法第五十九條第四款給與勞工之喪葬費應於死亡後三日內，死亡補償應於死亡後十五日內給付。 」</t>
+        </is>
+      </c>
+      <c r="I1354" s="2" t="inlineStr"/>
     </row>
     <row r="1355" ht="92.59999999999999" customHeight="1">
       <c r="A1355" s="2" t="n">
@@ -57818,8 +60680,15 @@
       <c r="G1355" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1355" s="2" t="n"/>
-      <c r="I1355" s="2" t="n"/>
+      <c r="H1355" s="2" t="inlineStr">
+        <is>
+          <t>勞工因職業災害死亡，雇主應於勞工死亡後 15日 內給予其遺屬死亡補償。
+相關法規重點
+死亡補償期限：依《勞動基準法施行細則》第33條規定，雇主給與勞工的死亡補償應於 15日內 給付；喪葬費則應於 3日內 給付。
+補償內容：依《勞動基準法》第59條，勞工因職災死亡時，雇主應給予5個月平均工資的喪葬費，以及40個月平均工資的死亡補償。</t>
+        </is>
+      </c>
+      <c r="I1355" s="2" t="inlineStr"/>
     </row>
     <row r="1356" ht="92.59999999999999" customHeight="1">
       <c r="A1356" s="2" t="n">
@@ -57853,8 +60722,16 @@
       <c r="G1356" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H1356" s="2" t="n"/>
-      <c r="I1356" s="2" t="n"/>
+      <c r="H1356" s="2" t="inlineStr">
+        <is>
+          <t>勞工於職業災害醫療期間不能工作而請公傷病假時，雇主應給全薪（按其原領工資數額予以補償）。
+Workstem 重點解析
+法源依據：依據《勞動基準法》第59條第2款規定，勞工在職災醫療中不能工作時，雇主應按其原領工資數額予以補償（即全薪）。
+假別規定：依《勞工請假規則》第6條，勞工因職業災害致傷害或疾病，治療與休養期間雇主應給予公傷病假。
+全勤獎金：雇主不得因勞工請公傷病假而扣發全勤獎金。</t>
+        </is>
+      </c>
+      <c r="I1356" s="2" t="inlineStr"/>
     </row>
     <row r="1357" ht="92.59999999999999" customHeight="1">
       <c r="A1357" s="2" t="n">
@@ -57888,8 +60765,16 @@
       <c r="G1357" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H1357" s="2" t="n"/>
-      <c r="I1357" s="2" t="n"/>
+      <c r="H1357" s="2" t="inlineStr">
+        <is>
+          <t>勞動場所發生職業災害，災害搶救中第一要務為搶救罹災勞工迅速送醫。
+災害搶救與通報重點
+以人為先：發生職災時，確保人員生命安全與迅速送醫急救永遠是第一優先。
+通報時效：若符合發生死亡災害、3人以上死傷或1人以上受傷需住院治療等重大職業災害，雇主應於8小時內向當地勞動檢查機構通報（注意現行法規為8小時內，而非舊規的24小時）。
+現場保護：除必要的急救、搶救外，未經許可不得移動或破壞現場。</t>
+        </is>
+      </c>
+      <c r="I1357" s="2" t="inlineStr"/>
     </row>
     <row r="1358" ht="92.59999999999999" customHeight="1">
       <c r="A1358" s="2" t="n">
@@ -57923,8 +60808,17 @@
       <c r="G1358" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1358" s="2" t="n"/>
-      <c r="I1358" s="2" t="n"/>
+      <c r="H1358" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+以某一要素為基源並連鎖發展形成災害的職業災害發生模式為連鎖型。
+職業災害發生模式簡介
+連鎖型：以某一基本要素為基源，衍生出新要素，再層層衍生，各要素之間環環相扣、連鎖發展並擴大規模形成災害。
+聚合型：由多個獨立的要素組合、聚集而引起災害。
+複合型：由聚合型與連鎖型兩者綜合組合而成的模式。</t>
+        </is>
+      </c>
+      <c r="I1358" s="2" t="inlineStr"/>
     </row>
     <row r="1359" ht="92.59999999999999" customHeight="1">
       <c r="A1359" s="2" t="n">
@@ -57958,8 +60852,21 @@
       <c r="G1359" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1359" s="2" t="n"/>
-      <c r="I1359" s="2" t="n"/>
+      <c r="H1359" s="2" t="inlineStr">
+        <is>
+          <t>所謂失能傷害係指損失日數在 1日 以上。
+鼎文公職行動版 失能傷害重點整理
+定義：指勞工因工作傷害造成死亡、永久全失能、永久部分失能或暫時全失能，且損失工作時間或不能恢復工作在 1日以上（不含受傷當日）。
+勞動部全球資訊網 包含範圍：
+死亡
+永久全失能
+永久部分失能
+暫時全失能（損失工作日數達1日以上者）
+iPEDIA 百科 計算方式：不包含受傷當日與恢復工作當日，但包含中間經過的休假日、例假日。
+iPEDIA 百科</t>
+        </is>
+      </c>
+      <c r="I1359" s="2" t="inlineStr"/>
     </row>
     <row r="1360" ht="92.59999999999999" customHeight="1">
       <c r="A1360" s="2" t="n">
@@ -57993,8 +60900,19 @@
       <c r="G1360" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H1360" s="2" t="n"/>
-      <c r="I1360" s="2" t="n"/>
+      <c r="H1360" s="2" t="inlineStr">
+        <is>
+          <t>職業災害統計中，有關失能傷害之損失日數，不包括 (A) 受傷當日。
+損失日數計算規則
+不包括：
+受傷當日
+恢復工作當日
+包括：
+中間所經過之日數（包括星期日、休假日或事業單位停工日）
+復工後因該災害導致之任何不能工作之整日數</t>
+        </is>
+      </c>
+      <c r="I1360" s="2" t="inlineStr"/>
     </row>
     <row r="1361" ht="92.59999999999999" customHeight="1">
       <c r="A1361" s="2" t="n">
@@ -58028,8 +60946,12 @@
       <c r="G1361" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H1361" s="2" t="n"/>
-      <c r="I1361" s="2" t="n"/>
+      <c r="H1361" s="2" t="inlineStr">
+        <is>
+          <t>Google AI 摘要未抓取到，請手動補充。</t>
+        </is>
+      </c>
+      <c r="I1361" s="2" t="inlineStr"/>
     </row>
     <row r="1362" ht="92.59999999999999" customHeight="1">
       <c r="A1362" s="2" t="n">
@@ -58063,8 +60985,17 @@
       <c r="G1362" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H1362" s="2" t="n"/>
-      <c r="I1362" s="2" t="n"/>
+      <c r="H1362" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+勞工於 2 公尺以上場所作業，未有合規定之工作台或防護網等措施因此導致之災害，其原因歸類為不安全狀態。
+原因解析
+不安全狀態（Unsafe Condition）：指物體、設備、環境本身的缺失或未符合安全標準（如未設置合規的工作台、防護網、護欄不足等外在環境與設備缺陷）。
+不安全動作：指人員自身的行為不當或違反操作規定。
+相關討論與考題解析可參考 Yamol 題庫討論。</t>
+        </is>
+      </c>
+      <c r="I1362" s="2" t="inlineStr"/>
     </row>
     <row r="1363" ht="92.59999999999999" customHeight="1">
       <c r="A1363" s="2" t="n">
@@ -58098,8 +61029,17 @@
       <c r="G1363" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H1363" s="2" t="n"/>
-      <c r="I1363" s="2" t="n"/>
+      <c r="H1363" s="2" t="inlineStr">
+        <is>
+          <t>在您列出的選項中，屬於「不安全環境或設備」（屬於「物」的因素）的是：
+施工未設置護欄
+💡 為什麼？
+在職業安全衛生管理中，不安全因素通常分為兩大類：
+不安全環境或設備（物的狀態）： 指的是硬體、空間、設備或防護措施出現缺失。例如：施工未設置護欄、機械沒有防護罩、照明不足、通道堆滿雜物等。
+不安全行為（人的不安全動作）： 指的是人員因為人為疏忽、未照規定操作所導致的危險。其餘三個選項（人員未按標準作業程序工作、未接受安全衛生教育訓練、疏忽大意及判斷錯誤）皆屬於人的不安全行為。</t>
+        </is>
+      </c>
+      <c r="I1363" s="2" t="inlineStr"/>
     </row>
     <row r="1364" ht="108" customHeight="1">
       <c r="A1364" s="2" t="n">
@@ -58133,8 +61073,18 @@
       <c r="G1364" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H1364" s="2" t="n"/>
-      <c r="I1364" s="2" t="n"/>
+      <c r="H1364" s="2" t="inlineStr">
+        <is>
+          <t>在您列出的選項中，「未佩帶雇主提供之安全帶、安全帽」屬於工作人員的不安全行為。
+為了方便您區分，職業安全衛生上通常將危害分為以下兩大類：
+⚙️ 不安全動作（行為）：屬於「人」的因素。例如：未佩帶雇主提供之安全帶、安全帽、冒失冒險的行為、不當的站立位置等。
+🏗️ 不安全環境（狀態）：屬於「物」或「環境」的因素。您提到的其他三個選項都屬於此類：
+施工架未設置護欄
+施工架踏板寬度、強度不足或無防脫活扣
+施工架超搭</t>
+        </is>
+      </c>
+      <c r="I1364" s="2" t="inlineStr"/>
     </row>
     <row r="1365" ht="92.59999999999999" customHeight="1">
       <c r="A1365" s="2" t="n">
@@ -58168,8 +61118,17 @@
       <c r="G1365" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1365" s="2" t="n"/>
-      <c r="I1365" s="2" t="n"/>
+      <c r="H1365" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+地面作業較少發生人體墜落災害。
+答案解析
+地面作業：因為是在平地或地面上工作，沒有高度落差，所以基本上不會發生高處墜落災害。
+利用高架作業、利用合梯作業：都屬於高處或具備高度落差的作業，潛在的墜落風險較高。
+作業時配戴安全帶：雖然是防止墜落的防護措施，但該選項指的是「有墜落之虞的作業環境」中使用防護具，而不是指作業本身沒有高度。</t>
+        </is>
+      </c>
+      <c r="I1365" s="2" t="inlineStr"/>
     </row>
     <row r="1366" ht="92.59999999999999" customHeight="1">
       <c r="A1366" s="2" t="n">
@@ -58203,8 +61162,21 @@
       <c r="G1366" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H1366" s="2" t="n"/>
-      <c r="I1366" s="2" t="n"/>
+      <c r="H1366" s="2" t="inlineStr">
+        <is>
+          <t>答案為 (C) 機械防護措施之缺陷。
+答案解析
+在職業安全衛生中，災害原因通常區分為「不安全狀態（物的原因）」與「不安全動作（人的原因）」：
+不安全狀態（Unsafe Condition）：屬於機械、設備、環境或物體本身的缺陷。例如：機械防護措施之缺陷、設備損壞、護罩不足等。
+不安全動作（Unsafe Act）：屬於人為疏忽或違規操作的行為。例如：錯誤的操作、使安全裝置失效、使用指定外之機械等。
+選項比較
+(A) 錯誤的操作：人為的不安全動作
+(B) 使安全裝置失效：人為的不安全動作
+(C) 機械防護措施之缺陷：環境或設備的不安全狀態
+(D) 使用指定外之機械：人為的不安全動作</t>
+        </is>
+      </c>
+      <c r="I1366" s="2" t="inlineStr"/>
     </row>
     <row r="1367" ht="92.59999999999999" customHeight="1">
       <c r="A1367" s="2" t="n">
@@ -58238,8 +61210,16 @@
       <c r="G1367" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H1367" s="2" t="n"/>
-      <c r="I1367" s="2" t="n"/>
+      <c r="H1367" s="2" t="inlineStr">
+        <is>
+          <t>職業災害調查處理對於設備故障未修理及維修不良之不安全狀態，屬於設備本身的缺陷。
+說明
+在職業安全衛生與職業災害調查的分類中：
+設備本身的缺陷：包含機械、設備、工具、施工現場或附件本身的損壞、故障未修理、維修不良等物體本身的異常狀態。
+與防護措施缺陷、作業場所缺陷或防護具服裝缺陷有所區分。</t>
+        </is>
+      </c>
+      <c r="I1367" s="2" t="inlineStr"/>
     </row>
     <row r="1368" ht="92.59999999999999" customHeight="1">
       <c r="A1368" s="2" t="n">
@@ -58273,8 +61253,16 @@
       <c r="G1368" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1368" s="2" t="n"/>
-      <c r="I1368" s="2" t="n"/>
+      <c r="H1368" s="2" t="inlineStr">
+        <is>
+          <t>這題的正確答案是以上皆是。
+為了確保安全系統與工作實務被確實遵守，對工作者的訓練與指導必須涵蓋作業的各個層面。選項中提到的所有項目都至關重要：
+作業活動及現場誘導：確保工作者熟悉實際施作環境與具體的操作流程。
+在安全作業方法的說明措施：讓工作者明確了解並掌握符合安全標準的操作程序。
+事故、受傷或緊急應變事件的程序：確保在意外發生時，工作者能將傷害降到最低並迅速應變。</t>
+        </is>
+      </c>
+      <c r="I1368" s="2" t="inlineStr"/>
     </row>
     <row r="1369" ht="92.59999999999999" customHeight="1">
       <c r="A1369" s="2" t="n">
@@ -58308,8 +61296,13 @@
       <c r="G1369" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H1369" s="2" t="n"/>
-      <c r="I1369" s="2" t="n"/>
+      <c r="H1369" s="2" t="inlineStr">
+        <is>
+          <t>答案是現場作業主管。
+根據職業安全衛生相關法規，當勞工在作業場所發現有任何墜落危害的情形（例如：鷹架未設護欄、安全帶破損、開口未防護等）時，應立即向現場作業主管或場所負責人報告，以便主管能第一時間採取隔離、停工或修復等安全防災措施。</t>
+        </is>
+      </c>
+      <c r="I1369" s="2" t="inlineStr"/>
     </row>
     <row r="1370" ht="92.59999999999999" customHeight="1">
       <c r="A1370" s="2" t="n">
@@ -58343,8 +61336,18 @@
       <c r="G1370" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H1370" s="2" t="n"/>
-      <c r="I1370" s="2" t="n"/>
+      <c r="H1370" s="2" t="inlineStr">
+        <is>
+          <t>消除不安全的狀況及行為所採取的 4E 政策，還包括 (C) 熱心（Enthusiasm）。
+Quizlet 4E 政策內容
+工程 (Engineering)：改善機械設備、工作環境等硬體設施。
+教育 (Education)：對員工實施安全衛生教育訓練與宣導。
+執行 (Enforcement)：落實安全規章、監督與稽核。
+熱心 (Enthusiasm)：激發人員對安全工作的熱忱與關懷，主動參與安全管理。
+Quizlet</t>
+        </is>
+      </c>
+      <c r="I1370" s="2" t="inlineStr"/>
     </row>
     <row r="1371" ht="92.59999999999999" customHeight="1">
       <c r="A1371" s="2" t="n">
@@ -58378,8 +61381,13 @@
       <c r="G1371" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H1371" s="2" t="n"/>
-      <c r="I1371" s="2" t="n"/>
+      <c r="H1371" s="2" t="inlineStr">
+        <is>
+          <t>設備因素為造成事故的危害因子之一。
+在職業安全衛生領域中，造成工作場所事故的危害因子，除了人的因素、物料因素、環境因素外，還包含設備因素（或稱機械設備因素）。</t>
+        </is>
+      </c>
+      <c r="I1371" s="2" t="inlineStr"/>
     </row>
     <row r="1372" ht="92.59999999999999" customHeight="1">
       <c r="A1372" s="2" t="n">
@@ -58413,8 +61421,18 @@
       <c r="G1372" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H1372" s="2" t="n"/>
-      <c r="I1372" s="2" t="n"/>
+      <c r="H1372" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+作業中所存在的潛在危險或危害因素需加以分析，唯不分析「經費」。
+在進行工作安全分析或危害辨識時，分析的四大要素通常包含：
+人（人員的操作、行為與習慣）
+事/方法（作業程序、方法）
+物/機械與材料（設備、工具、物料）
+而「經費」屬於財務預算考量，不屬於作業現場實質存在的潛在危險與危害因素。</t>
+        </is>
+      </c>
+      <c r="I1372" s="2" t="inlineStr"/>
     </row>
     <row r="1373" ht="92.59999999999999" customHeight="1">
       <c r="A1373" s="2" t="n">
@@ -58448,8 +61466,15 @@
       <c r="G1373" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H1373" s="2" t="n"/>
-      <c r="I1373" s="2" t="n"/>
+      <c r="H1373" s="2" t="inlineStr">
+        <is>
+          <t>根據統計，災害發生多數都是受人為因素所影響。
+災害成因解析
+人為因素：多數意外與災害（如火災、工安事故等）往往起因於人為疏忽、操作不當或安全防範不足。
+其他因素：如環境、設備或氣候雖也會造成災害，但在各類統計中，人為疏失往往佔了最大多數比例。</t>
+        </is>
+      </c>
+      <c r="I1373" s="2" t="inlineStr"/>
     </row>
     <row r="1374" ht="92.59999999999999" customHeight="1">
       <c r="A1374" s="2" t="n">
@@ -58483,8 +61508,17 @@
       <c r="G1374" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1374" s="2" t="n"/>
-      <c r="I1374" s="2" t="n"/>
+      <c r="H1374" s="2" t="inlineStr">
+        <is>
+          <t>關於事故處理，第一步驟通常為「確認事實」（亦有部分安全管理流程將「確認事實」與「報告」並列或依情境調整，但在這四個選項的標準邏輯中，必須先掌握現場狀況、釐清發生了什麼事，才能進行後續的報告與處置）。
+以下為這四個步驟在事故處理中的標準順序與概念：
+確認事實（第一步）：了解事故現場狀況、人員傷亡情形、受損程度與影響範圍。
+報告（第二步）：將確認後的客觀事實立即向上級、相關主管或權責單位通報。
+聯絡（第三步）：聯繫外部支援單位（如救護車、消防隊、保險公司或受害者家屬）。
+處置（第四步）：進行現場應變措施、善後復原、召開檢討會並提出改善對策。</t>
+        </is>
+      </c>
+      <c r="I1374" s="2" t="inlineStr"/>
     </row>
     <row r="1375" ht="92.59999999999999" customHeight="1">
       <c r="A1375" s="2" t="n">
@@ -58518,8 +61552,17 @@
       <c r="G1375" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H1375" s="2" t="n"/>
-      <c r="I1375" s="2" t="n"/>
+      <c r="H1375" s="2" t="inlineStr">
+        <is>
+          <t>在實施職業災害調查時，「根據雇主說辭」並非正確的態度。
+職業災害調查需要客觀、全面且公正。正確的職災調查態度與做法包含：
+客觀中立調查：不能單憑雇主或任何單一方的說辭（如勞工、目擊者），必須多方查證，避免偏聽。
+收集客觀證據：必須拍攝災害現場實務環境、測量數據、保存相關事證。
+確認人員傷亡：確實調查受傷部位與傷勢情況，以評估災害嚴重程度與機轉。
+保持理性分析：調查人員必須冷靜判斷，依據科學證據與邏輯推理，找出災害的根本原因（如不安全動作或不安全設備），而不是推卸責任。</t>
+        </is>
+      </c>
+      <c r="I1375" s="2" t="inlineStr"/>
     </row>
     <row r="1376" ht="108" customHeight="1">
       <c r="A1376" s="2" t="n">
@@ -58553,8 +61596,22 @@
       <c r="G1376" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H1376" s="2" t="n"/>
-      <c r="I1376" s="2" t="n"/>
+      <c r="H1376" s="2" t="inlineStr">
+        <is>
+          <t>✅ 正確答案
+勞工因遭遇職業災害在醫療中不能工作時，雇主應按其原領工資數額作為補償。
+📊 勞基法第59條重點解析
+依據《勞動基準法》第59條規定，雇主對於職業災害勞工應負擔之補償責任包含：
+勞動部職業安全衛生署 🗓 工資補償
+標準：按勞工遭遇職業災害前的原領工資數額全額給付。
+目的：維持勞工在醫療不能工作期間的正常生活。
+法律百科Legispedia 💡 醫療費用補償
+勞工受傷或罹患職業病時，雇主應補償其必需之醫療費用。
+此項與工資補償分開計算，不能互相免除。
+玉鼎法律事務所</t>
+        </is>
+      </c>
+      <c r="I1376" s="2" t="inlineStr"/>
     </row>
     <row r="1377" ht="92.59999999999999" customHeight="1">
       <c r="A1377" s="2" t="n">
@@ -58588,8 +61645,19 @@
       <c r="G1377" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H1377" s="2" t="n"/>
-      <c r="I1377" s="2" t="n"/>
+      <c r="H1377" s="2" t="inlineStr">
+        <is>
+          <t>共計 45 個月平均工資。
+依據《勞動基準法》第 59 條第 4 款規定，勞工因遭遇職業傷害或罹患職業病而死亡時，雇主應給付：
+Facebook
+·臺北市政府勞動局 - 勞動臺北 喪葬費用：5 個月平均工資。
+死亡補償：40 個月平均工資。
+兩者合計共為 45 個月平均工資（5 個月 + 40 個月）。
+Facebook
+·臺北市政府勞動局 - 勞動臺北</t>
+        </is>
+      </c>
+      <c r="I1377" s="2" t="inlineStr"/>
     </row>
     <row r="1378" ht="92.59999999999999" customHeight="1">
       <c r="A1378" s="2" t="n">
@@ -58623,8 +61691,15 @@
       <c r="G1378" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H1378" s="2" t="n"/>
-      <c r="I1378" s="2" t="n"/>
+      <c r="H1378" s="2" t="inlineStr">
+        <is>
+          <t>依據職業災害勞工保護法第7條規定（現行勞工職業災害保險及保護法第90條亦同），如涉及民事損害賠償時，過失之舉證責任為雇主。
+重點整理
+答案：雇主
+法律依據：雇主必須自行證明自己對於該起職業災害的發生「沒有過失」，若無法證明無過失，就必須負擔損害賠償責任。</t>
+        </is>
+      </c>
+      <c r="I1378" s="2" t="inlineStr"/>
     </row>
     <row r="1379" ht="92.59999999999999" customHeight="1">
       <c r="A1379" s="2" t="n">
@@ -58659,8 +61734,16 @@
       <c r="G1379" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H1379" s="2" t="n"/>
-      <c r="I1379" s="2" t="n"/>
+      <c r="H1379" s="2" t="inlineStr">
+        <is>
+          <t>勞工或雇主對於職業疾病診斷有異議時，得檢附相關資料向直轄市、縣（市）主管機關申請認定。
+依據《職業災害勞工保護法》（相關規定現已納入《勞工職業災害保險及保護法》）規定：
+醫師診斷：勞工疑有職業疾病時，應先經醫師診斷。
+地方主管機關認定：勞工或雇主對於診斷結果有異議，可向地方直轄市、縣（市）主管機關（通常會交由地方設置的職業疾病認定委員會）申請認定。
+法律百科Legispedia</t>
+        </is>
+      </c>
+      <c r="I1379" s="2" t="inlineStr"/>
     </row>
     <row r="1380" ht="77.15000000000001" customHeight="1">
       <c r="A1380" s="2" t="n">
@@ -58694,8 +61777,13 @@
       <c r="G1380" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H1380" s="2" t="n"/>
-      <c r="I1380" s="2" t="n"/>
+      <c r="H1380" s="2" t="inlineStr">
+        <is>
+          <t>正確答案為：(A) 職業疾病鑑定委員會。
+根據相關勞動法規規定，中央主管機關為鑑定職業疾病、確保罹患職業疾病勞工之權益，應設職業疾病鑑定委員會。</t>
+        </is>
+      </c>
+      <c r="I1380" s="2" t="inlineStr"/>
     </row>
     <row r="1381" ht="92.59999999999999" customHeight="1">
       <c r="A1381" s="2" t="n">
@@ -58729,8 +61817,14 @@
       <c r="G1381" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H1381" s="2" t="n"/>
-      <c r="I1381" s="2" t="n"/>
+      <c r="H1381" s="2" t="inlineStr">
+        <is>
+          <t>正確答案為：(A) 職業災害勞工保護法。
+勞動部職業安全衛生署 依據《職業災害勞工保護法》第 1 條規定：「為保障職業災害勞工之權益，加強職業災害之預防，促進就業安全及經濟發展，爰制定本法。」
+勞動部職業安全衛生署</t>
+        </is>
+      </c>
+      <c r="I1381" s="2" t="inlineStr"/>
     </row>
     <row r="1382" ht="92.59999999999999" customHeight="1">
       <c r="A1382" s="2" t="n">
@@ -58764,8 +61858,24 @@
       <c r="G1382" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H1382" s="2" t="n"/>
-      <c r="I1382" s="2" t="n"/>
+      <c r="H1382" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+下列情況中屬於「永久部分失能」的是損失單目。
+職業安全衛生失能傷害分類說明
+死亡：指因職業災害導致生命終止。
+iPEDIA 百科
+永久全失能：指除死亡外，雙目失明，或一隻眼睛及一隻手（或手臂、腿、足）同時失去或失去機能者。
+iPEDIA 百科
+永久部分失能：指除死亡及永久全失能以外，造成身體或肢體某一部分完全失去（如損失單目、單指截斷）或失去機能之情況。
+勞動部職業安全衛生署 選項比較：
+損失雙目：屬於永久全失能。
+損失單目：屬於永久部分失能。
+一隻眼及一隻手失去機能：屬於永久全失能。
+死亡：屬於死亡案件。</t>
+        </is>
+      </c>
+      <c r="I1382" s="2" t="inlineStr"/>
     </row>
     <row r="1383" ht="92.59999999999999" customHeight="1">
       <c r="A1383" s="2" t="n">
@@ -58799,8 +61909,16 @@
       <c r="G1383" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1383" s="2" t="n"/>
-      <c r="I1383" s="2" t="n"/>
+      <c r="H1383" s="2" t="inlineStr">
+        <is>
+          <t>勞工在一次事故中受傷使雙眼失明，屬於永久全失能。
+桃園市政府勞動檢查處
+職業安全衛生統計定義
+永久全失能：指除死亡外，任何足使罹災者造成永久全失能，或在一次事故中損失雙目、或一隻眼睛及一隻手（手臂、腿、足）等永久失去機能之情形。其每人損失工作日數通常以 6,000 日計算。
+勞動部職業安全衛生署</t>
+        </is>
+      </c>
+      <c r="I1383" s="2" t="inlineStr"/>
     </row>
     <row r="1384" ht="108" customHeight="1">
       <c r="A1384" s="2" t="n">
@@ -58834,8 +61952,12 @@
       <c r="G1384" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1384" s="2" t="n"/>
-      <c r="I1384" s="2" t="n"/>
+      <c r="H1384" s="2" t="inlineStr">
+        <is>
+          <t>Google AI 摘要未抓取到，請手動補充。</t>
+        </is>
+      </c>
+      <c r="I1384" s="2" t="inlineStr"/>
     </row>
     <row r="1385" ht="92.59999999999999" customHeight="1">
       <c r="A1385" s="2" t="n">
@@ -58869,8 +61991,18 @@
       <c r="G1385" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H1385" s="2" t="n"/>
-      <c r="I1385" s="2" t="n"/>
+      <c r="H1385" s="2" t="inlineStr">
+        <is>
+          <t>否，此規定不合法。
+根據《勞工職業災害保險職業傷病審查準則》第16條（或舊法第17條）規定，勞工於工作日之用餐時間中，如雇主未規定必須於工作場所用餐，而為必要之外出用餐，於用餐往返應經途中發生事故而致之傷害，視為職業傷害。
+臺北市政府全球資訊網 因此，就算事業單位在廠區內有提供午餐：
+未強制規定：若公司沒有強制規定勞工「必須」在廠區內用餐，勞工選擇自行外出用餐並在往返途中發生車禍，依法仍屬職業災害，不能由公司自行明定或透過內部規定來排除。
+強制規定：唯有當雇主既提供用膳設施，且硬性規定勞工必須在工作場所用餐，勞工卻仍私自違規外出用餐而發生事故，才可能不被視為職業災害。
+此類法定職災認定標準是依據國家法規與客觀事實，不需要、也無法透過勞保局核准或向主管機關報備來將合法規定變更為無效或排除法定職災。
+104職場力</t>
+        </is>
+      </c>
+      <c r="I1385" s="2" t="inlineStr"/>
     </row>
     <row r="1386" ht="92.59999999999999" customHeight="1">
       <c r="A1386" s="2" t="n">
@@ -58904,8 +62036,17 @@
       <c r="G1386" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H1386" s="2" t="n"/>
-      <c r="I1386" s="2" t="n"/>
+      <c r="H1386" s="2" t="inlineStr">
+        <is>
+          <t>勞工由於智力或體力不能配合其現任工作是屬於不安全動作因素中之不能範圍。
+在職業安全衛生的不安全動作（行為）分類中：
+不知：不知安全的操作方法，不會使用防護器具。
+不顧：缺乏安全意願，或為圖舒適、方便而不顧安全守則。
+不能：智力、體能或技能不能配合從事的工作。
+不理：不聽信教導，拒絕使用防護具或不遵守安全守則。</t>
+        </is>
+      </c>
+      <c r="I1386" s="2" t="inlineStr"/>
     </row>
     <row r="1387" ht="92.59999999999999" customHeight="1">
       <c r="A1387" s="2" t="n">
@@ -58939,8 +62080,18 @@
       <c r="G1387" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H1387" s="2" t="n"/>
-      <c r="I1387" s="2" t="n"/>
+      <c r="H1387" s="2" t="inlineStr">
+        <is>
+          <t>4 月 28 日為工殤日（現已修正為「職業安全衛生日」）。
+相關資訊
+工殤日：台灣原訂每年 4 月 28 日為「工殤日」，配合國際工殤日悼念職災勞工。
+交通部 職業安全衛生日：因國際勞工組織（ILO）將其改為「世界職業安全衛生日」，台灣勞動部也已將該日修正為「職業安全衛生日」。
+內政部全球資訊網 其他選項參考：
+和平紀念日：為每年 2 月 28 日。
+國際勞工節：為每年 5 月 1 日。</t>
+        </is>
+      </c>
+      <c r="I1387" s="2" t="inlineStr"/>
     </row>
     <row r="1388" ht="92.59999999999999" customHeight="1">
       <c r="A1388" s="2" t="n">
@@ -58974,8 +62125,13 @@
       <c r="G1388" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H1388" s="2" t="n"/>
-      <c r="I1388" s="2" t="n"/>
+      <c r="H1388" s="2" t="inlineStr">
+        <is>
+          <t>敘述有誤者為 (A) 勞動檢查員。
+解析：發生職業災害時，事業單位內部實施災害調查的必要對象通常包含工作場所負責人、作業主管與安全衛生人員等內部管理與實務執行人員。而「勞動檢查員」屬於外部主管機關的稽查、審查與調查人員，並非事業單位內部實施職災調查的必要內部對象。</t>
+        </is>
+      </c>
+      <c r="I1388" s="2" t="inlineStr"/>
     </row>
     <row r="1389" ht="92.59999999999999" customHeight="1">
       <c r="A1389" s="2" t="n">
@@ -59009,8 +62165,20 @@
       <c r="G1389" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H1389" s="2" t="n"/>
-      <c r="I1389" s="2" t="n"/>
+      <c r="H1389" s="2" t="inlineStr">
+        <is>
+          <t>勞工薪資非屬職業疾病診斷所考量之因素。
+職業疾病診斷原則
+職業疾病的認定與診斷主要依據醫學與工作相關之因果關係，通常考量下列核心要素：
+勞動部職業安全衛生署
+危害暴露：證實勞工在工作中有接觸化學性、物理性、生物性或人因性等有害因子。
+時序性：疾病的發作或出現應在危害暴露之後，符合合理的疾病潛伏期或發生順序。
+家族病史 / 疾病證據：評估客觀臨床生理表現與排除其他非職業因素（如基因、家族遺傳或個人生活習慣等）。
+勞工的薪資高低與疾病本身是否因工作引起並無直接醫學因果關係，因此不列入診斷考量。
+花蓮縣政府全球資訊網</t>
+        </is>
+      </c>
+      <c r="I1389" s="2" t="inlineStr"/>
     </row>
     <row r="1390" ht="92.59999999999999" customHeight="1">
       <c r="A1390" s="2" t="n">
@@ -59044,8 +62212,17 @@
       <c r="G1390" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1390" s="2" t="n"/>
-      <c r="I1390" s="2" t="n"/>
+      <c r="H1390" s="2" t="inlineStr">
+        <is>
+          <t>勞工因工作傷害雙目失明，依國家標準 (CNS) 其損失日數為 6000 日（選項 D）。
+Quizlet 相關說明
+永久全失能：雙目失明屬於永久全失能（Permanent Total Disability）的一種。
+勞動部全球資訊網
+計算標準：依據國家標準規定，每次發生永久全失能時，其傷害損失日數應一律按 6,000 日計算登記。
+iPEDIA 百科</t>
+        </is>
+      </c>
+      <c r="I1390" s="2" t="inlineStr"/>
     </row>
     <row r="1391" ht="92.59999999999999" customHeight="1">
       <c r="A1391" s="2" t="n">
@@ -59079,8 +62256,15 @@
       <c r="G1391" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H1391" s="2" t="n"/>
-      <c r="I1391" s="2" t="n"/>
+      <c r="H1391" s="2" t="inlineStr">
+        <is>
+          <t>永久全失能之損失天數應以 6000日 來計算。
+職安幫
+根據職業安全衛生統計規定，無論是「死亡」或是「永久全失能」案件，每人均應固定按損失 6000日 進行登記與計算。
+勞動部職業安全衛生署</t>
+        </is>
+      </c>
+      <c r="I1391" s="2" t="inlineStr"/>
     </row>
     <row r="1392" ht="92.59999999999999" customHeight="1">
       <c r="A1392" s="2" t="n">
@@ -59114,8 +62298,19 @@
       <c r="G1392" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H1392" s="2" t="n"/>
-      <c r="I1392" s="2" t="n"/>
+      <c r="H1392" s="2" t="inlineStr">
+        <is>
+          <t>✅ 6000 日
+傷害損失日數之計算，遇到死亡或永久全失能時，每次均應按損失 6,000 日登記。
+勞動部職業安全衛生署
+📊 相關規定對照
+死亡：應按損失 6,000 日登記。
+永久全失能：每次應按損失 6,000 日登記。
+永久部分失能：每次按實際損失日數或指定身體部位失能標準表登記。
+iPEDIA 百科</t>
+        </is>
+      </c>
+      <c r="I1392" s="2" t="inlineStr"/>
     </row>
     <row r="1393" ht="61.75" customHeight="1">
       <c r="A1393" s="2" t="n">
@@ -59149,8 +62344,55 @@
       <c r="G1393" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1393" s="2" t="n"/>
-      <c r="I1393" s="2" t="n"/>
+      <c r="H1393" s="2" t="inlineStr">
+        <is>
+          <t>失能傷害頻率公式中之分子為失能傷害次數（或失能傷害總人次數）。
+相關計算公式
+失能傷害頻率 (FR)：
+失能傷害頻率
+=
+失能傷害次數
+×
+1
+,
+000
+,
+000
+總經歷工時
+失
+能
+傷
+害
+頻
+率
+=
+失
+能
+傷
+害
+次
+數
+×
+1
+,
+0
+0
+0
+,
+0
+0
+0
+總
+經
+歷
+工
+時
+分子：失能傷害次數（發生失能傷害的總人次）
+分母：總經歷工時
+*(註：選項中的「總損失日數」則是**失能傷害嚴重率 (SR)*公式中的分子。)</t>
+        </is>
+      </c>
+      <c r="I1393" s="2" t="inlineStr"/>
     </row>
     <row r="1394" ht="61.75" customHeight="1">
       <c r="A1394" s="2" t="n">
@@ -59184,8 +62426,18 @@
       <c r="G1394" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H1394" s="2" t="n"/>
-      <c r="I1394" s="2" t="n"/>
+      <c r="H1394" s="2" t="inlineStr">
+        <is>
+          <t>失能傷害頻率公式中之分母為總經歷工時。
+勞動部全球資訊網
+失能傷害頻率 (FR) 公式
+公式：失能傷害頻率 ＝ (失能傷害次數 ÷ 總經歷工時) × 1,000,000
+分子：失能傷害次數
+分母：總經歷工時
+勞動部全球資訊網</t>
+        </is>
+      </c>
+      <c r="I1394" s="2" t="inlineStr"/>
     </row>
     <row r="1395" ht="61.75" customHeight="1">
       <c r="A1395" s="2" t="n">
@@ -59211,8 +62463,47 @@
       <c r="G1395" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1395" s="2" t="n"/>
-      <c r="I1395" s="2" t="n"/>
+      <c r="H1395" s="2" t="inlineStr">
+        <is>
+          <t>在失能傷害頻率（Frequency Rate, FR）的計算公式中，分子為失能傷害次數乘以 10 的 6 次方（即 1,000,000）。
+📊 公式說明
+失能傷害頻率表示每百萬個工時中所發生的失能傷害次數，公式如下：
+失能傷害頻率 (FR)
+=
+失能傷害次數
+總經歷工時
+×
+10
+6
+失
+能
+傷
+害
+頻
+率
+(
+F
+R
+)
+=
+失
+能
+傷
+害
+次
+數
+總
+經
+歷
+工
+時
+×
+1
+0
+6</t>
+        </is>
+      </c>
+      <c r="I1395" s="2" t="inlineStr"/>
     </row>
     <row r="1396" ht="92.59999999999999" customHeight="1">
       <c r="A1396" s="2" t="n">
@@ -59240,8 +62531,13 @@
       <c r="G1396" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H1396" s="2" t="n"/>
-      <c r="I1396" s="2" t="n"/>
+      <c r="H1396" s="2" t="inlineStr">
+        <is>
+          <t>失能傷害頻率（FR）數值之表示方式，通常取小數點第 2 位數。
+iPEDIA 百科</t>
+        </is>
+      </c>
+      <c r="I1396" s="2" t="inlineStr"/>
     </row>
     <row r="1397" ht="61.75" customHeight="1">
       <c r="A1397" s="2" t="n">
@@ -59275,8 +62571,40 @@
       <c r="G1397" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H1397" s="2" t="n"/>
-      <c r="I1397" s="2" t="n"/>
+      <c r="H1397" s="2" t="inlineStr">
+        <is>
+          <t>失能傷害嚴重率（SR）公式中之分子為總損失日數（或稱總損失工作日數）。
+考古豹 相關公式與說明
+公式：失能傷害嚴重率 =
+(
+總
+損
+失
+日
+數
+÷
+總
+經
+歷
+工
+時
+)
+×
+1
+,
+0
+0
+0
+,
+0
+0
+0
+分子：總損失日數（包含死亡、永久全失能、永久部分失能及暫時全失能所損失的工作日數）
+分母：總經歷工時
+iPEDIA 百科</t>
+        </is>
+      </c>
+      <c r="I1397" s="2" t="inlineStr"/>
     </row>
     <row r="1398" ht="61.75" customHeight="1">
       <c r="A1398" s="2" t="n">
@@ -59310,8 +62638,48 @@
       <c r="G1398" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H1398" s="2" t="n"/>
-      <c r="I1398" s="2" t="n"/>
+      <c r="H1398" s="2" t="inlineStr">
+        <is>
+          <t>失能傷害嚴重率公式中之分母為總經歷工時。
+勞動部全球資訊網
+失能傷害嚴重率 (SR) 公式
+公式：
+失
+能
+傷
+害
+嚴
+重
+率
+=
+總
+損
+失
+工
+作
+日
+數
+總
+經
+歷
+工
+時
+×
+1
+,
+0
+0
+0
+,
+0
+0
+0
+分子：總損失日數（失能傷害損失總日數）
+分母：總經歷工時
+勞動部全球資訊網</t>
+        </is>
+      </c>
+      <c r="I1398" s="2" t="inlineStr"/>
     </row>
     <row r="1399" ht="61.75" customHeight="1">
       <c r="A1399" s="2" t="n">
@@ -59339,8 +62707,17 @@
       <c r="G1399" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1399" s="2" t="n"/>
-      <c r="I1399" s="2" t="n"/>
+      <c r="H1399" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+失能傷害嚴重率（SR）數值之表示方式為取整數（不計小數點，小數點後無條件捨去）。
+相關規定與對比
+失能傷害嚴重率 (SR)：計算至整數位（取整數）。
+失能傷害頻率 (FR)：通常採計至小數點後取兩位（第三位四捨五入或捨棄，視具體規範而定）。
+職業安全衛生管理資訊平台</t>
+        </is>
+      </c>
+      <c r="I1399" s="2" t="inlineStr"/>
     </row>
     <row r="1400" ht="61.75" customHeight="1">
       <c r="A1400" s="2" t="n">
@@ -59374,8 +62751,16 @@
       <c r="G1400" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H1400" s="2" t="n"/>
-      <c r="I1400" s="2" t="n"/>
+      <c r="H1400" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+一般而言，失能傷害頻率 (FR) 與失能傷害嚴重率 (SR) 之數值相較為後者較大。
+說明
+失能傷害頻率（FR）：指每百萬工時中發生失能傷害的次數（人次），數值通常較小。
+失能傷害嚴重率（SR）：指每百萬工時中，失能傷害所造成的總損失日數，因為一次失能傷害往往會造成好幾天甚至高達數千天（如重大殘廢或死亡計算 6,000 日）的損失工時，所以累積的總損失日數往往遠大於發生人次，導致 SR 的數值通常比 FR 大很多。</t>
+        </is>
+      </c>
+      <c r="I1400" s="2" t="inlineStr"/>
     </row>
     <row r="1401" ht="77.15000000000001" customHeight="1">
       <c r="A1401" s="2" t="n">
@@ -59409,8 +62794,41 @@
       <c r="G1401" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H1401" s="2" t="n"/>
-      <c r="I1401" s="2" t="n"/>
+      <c r="H1401" s="2" t="inlineStr">
+        <is>
+          <t>職業災害統計中，失能傷害頻率（FR, Frequency Rate）的正確計算公式為「失能傷害人次數乘以
+10
+6
+1
+0
+6
+除以總經歷工時」。
+失能傷害頻率公式說明
+公式定義：指每百萬工時中，發生失能傷害的總人次數。
+數學表達：
+F
+R
+=
+失
+能
+傷
+害
+人
+次
+數
+×
+1
+0
+6
+總
+經
+歷
+工
+時
+iPEDIA 百科</t>
+        </is>
+      </c>
+      <c r="I1401" s="2" t="inlineStr"/>
     </row>
     <row r="1402" ht="92.59999999999999" customHeight="1">
       <c r="A1402" s="2" t="n">
@@ -59444,8 +62862,19 @@
       <c r="G1402" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H1402" s="2" t="n"/>
-      <c r="I1402" s="2" t="n"/>
+      <c r="H1402" s="2" t="inlineStr">
+        <is>
+          <t>此敘述中錯誤的是：「失能傷害千人率＝（傷害損失日數 × 10⁶）／總經歷工時」。
+原因解析
+錯誤敘述修正：（傷害損失日數 × 10⁶）／總經歷工時其實是失能傷害嚴重率（SR）的公式，而不是千人率。
+勞動部全球資訊網 正確公式對照：
+失能傷害頻率（FR）＝（失能傷害人次數 × 10⁶）／總經歷工時（每百萬工時失能傷害次數）
+失能傷害嚴重率（SR）＝（失能傷害損失總日數 × 10⁶）／總經歷工時（每百萬工時損失工作日數）
+每人平均損失日數＝失能傷害損失總日數／失能傷害人次數＝失能傷害嚴重率／失能傷害頻率
+iPEDIA 百科</t>
+        </is>
+      </c>
+      <c r="I1402" s="2" t="inlineStr"/>
     </row>
     <row r="1403" ht="108" customHeight="1">
       <c r="A1403" s="2" t="n">
@@ -59479,8 +62908,16 @@
       <c r="G1403" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H1403" s="2" t="n"/>
-      <c r="I1403" s="2" t="n"/>
+      <c r="H1403" s="2" t="inlineStr">
+        <is>
+          <t>敘述有誤的是：(C) 事業場所的失能傷害頻率與傷害嚴重率關聯性很高，因此傷害嚴重率僅做為參考。
+原因說明
+失能傷害頻率（FR） 與 傷害嚴重率（SR） 是評估事業單位安全績效的兩大核心指標，分別代表事故發生的「頻率」與所造成損失的「嚴重程度」。
+兩者代表不同的衡量面向，無法互相取代，傷害嚴重率（SR） 同樣具有獨立且重要的評估價值，並非僅做為參考。
+iPEDIA 百科</t>
+        </is>
+      </c>
+      <c r="I1403" s="2" t="inlineStr"/>
     </row>
     <row r="1404" ht="92.59999999999999" customHeight="1">
       <c r="A1404" s="2" t="n">
@@ -59514,8 +62951,74 @@
       <c r="G1404" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H1404" s="2" t="n"/>
-      <c r="I1404" s="2" t="n"/>
+      <c r="H1404" s="2" t="inlineStr">
+        <is>
+          <t>總合傷害指數（FSI，Frequency-Severity Indicator）之計算公式為
+(
+失能傷害頻率
+×
+失能傷害嚴重率
+)
+/
+1000
+(
+失
+能
+傷
+害
+頻
+率
+×
+失
+能
+傷
+害
+嚴
+重
+率
+)
+/
+𝟏
+𝟎
+𝟎
+𝟎
+（即失能傷害頻率與失能傷害嚴重率乘積除以 1000 之值的平方根）。
+福壽實業 在您列出的選項中，正確答案就是：
+(
+失能傷害頻率
+×
+失能傷害嚴重率
+)
+/
+1000
+(
+失
+能
+傷
+害
+頻
+率
+×
+失
+能
+傷
+害
+嚴
+重
+率
+)
+/
+𝟏
+𝟎
+𝟎
+𝟎
+相關指標小複習
+失能傷害頻率 (FR)：每百萬總經歷工時的失能傷害次數。
+失能傷害嚴重率 (SR)：每百萬總經歷工時的失能傷害損失工作日數。
+總合傷害指數 (FSI)：綜合評估頻率與嚴重度的指標，數值越大代表職場的安全衛生問題越嚴重。</t>
+        </is>
+      </c>
+      <c r="I1404" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:I1404"/>

--- a/salf/丙種職業安全衛生業務主管題庫.xlsx
+++ b/salf/丙種職業安全衛生業務主管題庫.xlsx
@@ -483,7 +483,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I1404"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.45" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.45"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="55" customWidth="1" min="2" max="2"/>
@@ -4090,7 +4090,11 @@
       <c r="G83" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>AI 模式已回覆：(function(){window.sn={_setImageSrc:function(b,c){var a=document.getElementById(`${b}`);a!==null&amp;&amp;(a.src=c,a.setAttribute("data-deferred","2"),google.rll(a,!0,()=&gt;{a.setAttribute("data-imgprocessed","true")}))}};}).call(this);勞工作業環境監測的頻率依危害因子與場所性質而定，一般規定為每 3 個月（每一季）或每 6 個月測定一次。 中華檢驗科技有限公司依據勞動部 中華民國工業安全衛生協會 發布的 勞工作業環境監測實施辦法，詳細頻率如下： 每 3 個月監測一次（至少每季一次）高溫作業場所：綜合溫度熱指數超過規定值之場所（如鍋爐房、熔煉、鍛造等）。特定化學物質與有機溶劑：製造、處置或使用特定化學物質或有機溶劑中高風險者。濃度超標改善期：若過去監測結果達到或超過「容許暴露標準」，頻率必須縮短為每 3 個月一次，直到改善為止。 國立臺灣科技大學 每 6 個月監測一次（至少每半年一次）噪音作業場所：勞工噪音暴露工作日八小時日時量平均音壓級達 85 分貝以上之作業場所。粉塵與二氧化碳：坑內作業場所、隧道掘削建設工程及已完工可通行之地下通道。一般化學性因子：一般有機溶劑、特定化學物質及鉛等作業場所。空調建築物：設有中央管理方式空氣調節設備之建築物室內作業場所。 詳細法規與通報規定可參考 勞工作業環境監測及暴露危害管理網路登錄系統。 第二章監測作業場所及監測頻率 - 勞動部-所有條文二）隧道掘削之建設工程之場所。 （三）前二目已完工可通行之地下通道。 三、勞工噪音暴露工作日八小時日時量平均音壓級八十五分貝以上之作業場所，應每六個月監測噪音一次以上。 前項第一款之作業場所，雇主已依室內空氣品質管理法規定實施二氧化碳檢驗測定者，得免監測。 第...www.wphp.doctor作業環境監測是什麼？一次搞懂法規規定、頻率與監測流程 - 職場健康促進綜合溫度熱指數 （高溫作業）, 每3個月, 適用於鍋爐房、熔煉、鍛造等高溫作業場所. 噪音, 每半年, 勞工噪音暴露超過85分貝者須監測. 粉塵, 每半年, 坑內作業場所，像是礦場、隧道等. 有機溶劑, 每半年, 製造、處置或使用有機溶劑的作業場所 ; 綜合溫...中華檢驗科技有限公司勞工作業環境監測多少做一次？ - 中華檢驗科技有限公司依據勞動部發布的勞工作業環境監測實施辦法，作業環境監測頻率依危害因子與場所性質而定，一般為每3 個月或每6 個月監測一次。若監測結果達到容許暴露標準，頻率會縮短為每3 個月一次以督促改善。 一般法定監測頻率. 每3 個月監測一次：. 高溫作業場所（綜合溫度熱指...國立臺灣科技大學【作業環境監測紀錄】 - 環境保護暨安全衛生室一、下列作業場所，其勞工工作日時量平均綜合溫度熱指數在中央主管機關規定值以上者，應每三個月監測綜合溫度熱指數一次以上：. （一）於鍋爐房從事工作之作業場所。 （二）處理灼熱鋼鐵或其他金屬塊之壓軋及鍛造之作業場所。 （三）鑄造間內處理熔融鋼鐵或其他金屬之作業場所...第二章監測作業場所及監測頻率 - 勞動部-所有條文二）隧道掘削之建設工程之場所。 （三）前二目已完工可通行之地下通道。 三、勞工噪音暴露工作日八小時日時量平均音壓級八十五分貝以上之作業場所，應每六個月監測噪音一次以上。 前項第一款之作業場所，雇主已依室內空氣品質管理法規定實施二氧化碳檢驗測定者，得免監測。 第...www.wphp.doctor作業環境監測是什麼？一次搞懂法規規定、頻率與監測流程 - 職場健康促進綜合溫度熱指數 （高溫作業）, 每3個月, 適用於鍋爐房、熔煉、鍛造等高溫作業場所. 噪音, 每半年, 勞工噪音暴露超過85分貝者須監測. 粉塵, 每半年, 坑內作業場所，像是礦場、隧道等. 有機溶劑, 每半年, 製造、處置或使用有機溶劑的作業場所 ; 綜合溫...中華檢驗科技有限公司勞工作業環境監測多少做一次？ - 中華檢驗科技有限公司依據勞動部發布的勞工作業環境監測實施辦法，作業環境監測頻率依危害因子與場所性質而定，一般為每3 個月或每6 個月監測一次。若監測結果達到容許暴露標準，頻率會縮短為每3 個月一次以督促改善。 一般法定監測頻率. 每3 個月監測一次：. 高溫作業場所（綜合溫度熱指...國立臺灣科技大學【作業環境監測紀錄】 - 環境保護暨安全衛生室一、下列作業場所，其勞工工作日時量平均綜合溫度熱指數在中央主管機關規定值以上者，應每三個月監測綜合溫度熱指數一次以上：. （一）於鍋爐房從事工作之作業場所。 （二）處理灼熱鋼鐵或其他金屬塊之壓軋及鍛造之作業場所。 （三）鑄造間內處理熔融鋼鐵或其他金屬之作業場所...顯示較少</t>
+        </is>
+      </c>
       <c r="I83" s="2" t="inlineStr"/>
     </row>
     <row r="84" ht="92.59999999999999" customHeight="1">
@@ -58993,10 +58997,55 @@
       </c>
       <c r="H1308" s="2" t="inlineStr">
         <is>
-          <t>Google AI 摘要未抓取到，請手動補充。</t>
-        </is>
-      </c>
-      <c r="I1308" s="2" t="n"/>
+          <t>身體質量指數（BMI）在正常範圍內的選項是 20。
+說明
+成人 BMI 正常範圍：介於
+1
+8
+.
+5
+≤
+B
+M
+I
+&lt;
+2
+4
+之間。
+亞東醫院
+選項分析：
+10：體重過輕（BMI 過低）。
+15：體重過輕（BMI 過低）。
+20：落在
+1
+8
+.
+5
+∼
+2
+4
+的正常範圍內。
+30：屬於中度肥胖（
+B
+M
+I
+≥
+2
+7
+為肥胖，
+3
+0
+≤
+B
+M
+I
+&lt;
+3
+5
+為中度肥胖）。</t>
+        </is>
+      </c>
+      <c r="I1308" s="2" t="inlineStr"/>
     </row>
     <row r="1309" ht="92.59999999999999" customHeight="1">
       <c r="A1309" s="2" t="n">
@@ -60176,10 +60225,12 @@
       </c>
       <c r="H1335" s="2" t="inlineStr">
         <is>
-          <t>Google AI 摘要未抓取到，請手動補充。</t>
-        </is>
-      </c>
-      <c r="I1335" s="2" t="n"/>
+          <t>答案為：以上皆是。
+勞動部職業安全衛生署
+依據《職業安全衛生法》第2條第5款規定，職業災害是指因勞動場所之建築物、機械、設備、原料、材料、化學品、氣體、蒸氣、粉塵等或作業活動及其他職業上原因所引起的工作者疾病、傷害、失能或死亡。</t>
+        </is>
+      </c>
+      <c r="I1335" s="2" t="inlineStr"/>
     </row>
     <row r="1336" ht="92.59999999999999" customHeight="1">
       <c r="A1336" s="2" t="n">
@@ -60416,10 +60467,19 @@
       </c>
       <c r="H1341" s="2" t="inlineStr">
         <is>
-          <t>Google AI 摘要未抓取到，請手動補充。</t>
-        </is>
-      </c>
-      <c r="I1341" s="2" t="n"/>
+          <t>依據《職業安全衛生法》規定，發生上下班交通死亡事故時，雇主無需於 8 小時內通報勞動檢查機構。
+勞動部職業安全衛生署
+相關法規重點
+需 8 小時內通報的重大職災：
+發生死亡災害
+罹災人數在 3 人以上
+1 人以上罹災且需住院治療
+石門管理處 上下班通勤車禍的例外規定：
+勞工於上下班通勤途中發生的交通事故，因不屬於雇主支配、管理的提供勞務工作場所，故不需依職安法第 37 條規定在 8 小時內向勞檢機構通報（但若屬於執行職務中如外出送貨發生車禍則仍須通報）。
+臺北市勞動檢查處</t>
+        </is>
+      </c>
+      <c r="I1341" s="2" t="inlineStr"/>
     </row>
     <row r="1342" ht="77.15000000000001" customHeight="1">
       <c r="A1342" s="2" t="n">
@@ -60500,10 +60560,21 @@
       </c>
       <c r="H1343" s="2" t="inlineStr">
         <is>
-          <t>Google AI 摘要未抓取到，請手動補充。</t>
-        </is>
-      </c>
-      <c r="I1343" s="2" t="n"/>
+          <t>依據勞動檢查法施行細則第31條規定，正確的選項是「光氣洩漏 1 人罹災需住院」。
+重大職業災害定義
+依照勞動檢查法施行細則第31條，重大職業災害包含以下情況：
+發生死亡災害。
+罹災人數達三人以上。
+氨、氯、氟化氫、光氣、硫化氫、二氧化硫等危險化學物質洩漏，造成一人以上需住院治療。
+其他中央主管機關指定公告之災害。
+選項分析
+發生罹災 1 人的輕傷害：不符合規定（未達死亡、3人以上或特定化學物質住院）。
+氨洩漏 2 人罹災但無需住院：必須「需住院治療」才算重大職業災害。
+光氣洩漏 1 人罹災需住院：符合光氣洩漏且 1 人以上需住院之規定。
+發生罹災 2 人需住院：人數須達 3 人以上才算重大職業災害（一般職災通報為 1 人以上住院，但勞檢法施行細則針對一般災害人數規定為 3 人以上）。</t>
+        </is>
+      </c>
+      <c r="I1343" s="2" t="inlineStr"/>
     </row>
     <row r="1344" ht="92.59999999999999" customHeight="1">
       <c r="A1344" s="2" t="n">
@@ -61255,10 +61326,16 @@
       </c>
       <c r="H1361" s="2" t="inlineStr">
         <is>
-          <t>Google AI 摘要未抓取到，請手動補充。</t>
-        </is>
-      </c>
-      <c r="I1361" s="2" t="n"/>
+          <t>敘述有誤的是 (C) 無須使用個人防護具。
+原因解析
+(C) 無須使用個人防護具：這是錯誤的。在進行有潛在危害的作業時，個人防護具（如安全帽、安全帶、護目鏡、防護口罩等）是最後防線，必須依規定確實佩戴與使用。
+(A) 作業前實施風險評估：正確。可預先辨識危害並採取控制措施。
+(B) 落實進場前教育訓練：正確。確保工作人員了解現場危害及應變處理。
+(D) 有效設置安全設施：正確。屬於工程控制，能預防或降低危害發生。
+桃園市政府</t>
+        </is>
+      </c>
+      <c r="I1361" s="2" t="inlineStr"/>
     </row>
     <row r="1362" ht="92.59999999999999" customHeight="1">
       <c r="A1362" s="2" t="n">
@@ -62259,12 +62336,8 @@
       <c r="G1384" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1384" s="2" t="inlineStr">
-        <is>
-          <t>Google AI 摘要未抓取到，請手動補充。</t>
-        </is>
-      </c>
-      <c r="I1384" s="2" t="n"/>
+      <c r="H1384" s="2" t="inlineStr"/>
+      <c r="I1384" s="2" t="inlineStr"/>
     </row>
     <row r="1385" ht="92.59999999999999" customHeight="1">
       <c r="A1385" s="2" t="n">

--- a/salf/丙種職業安全衛生業務主管題庫.xlsx
+++ b/salf/丙種職業安全衛生業務主管題庫.xlsx
@@ -483,7 +483,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I1404"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.45"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.45" outlineLevelCol="0"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="55" customWidth="1" min="2" max="2"/>
@@ -14007,7 +14007,16 @@
       <c r="G307" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H307" s="2" t="inlineStr"/>
+      <c r="H307" s="2" t="inlineStr">
+        <is>
+          <t>是的，鏟、掘、推等全身運動之工作屬於重工作（或稱重度工作）。
+勞工作業環境監測及暴露危害管理 依據台灣的高溫作業勞工作息時間標準規定，工作型態主要劃分如下：
+輕工作：僅以坐姿或立姿進行手臂部動作以操縱機器者。
+中度工作：於走動中提舉或推動一般重量物體者。
+重工作：鏟、掘、推等全身運動之工作者。
+勞工作業環境監測及暴露危害管理</t>
+        </is>
+      </c>
       <c r="I307" s="2" t="inlineStr"/>
     </row>
     <row r="308" ht="77.15000000000001" customHeight="1">
@@ -23110,7 +23119,17 @@
       <c r="G508" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H508" s="2" t="inlineStr"/>
+      <c r="H508" s="2" t="inlineStr">
+        <is>
+          <t>查看全部
+是的，業主將一項作業之不同分項工程交付二個以上事業單位承攬稱為平行承攬。
+相關名詞差異
+平行承攬（又稱平行分包）：業主將同一工程的不同分項（如土木、機電、空調等）分別發包給不同的承攬商。
+共同承攬：二個以上承攬人共同出資或提供技術，一起承攬同一項工程。
+單獨承攬：一項工程完全交由單一承攬單位負責。
+怡安職護殿堂</t>
+        </is>
+      </c>
       <c r="I508" s="2" t="inlineStr"/>
     </row>
     <row r="509" ht="92.59999999999999" customHeight="1">
@@ -33957,7 +33976,18 @@
       <c r="G753" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="H753" s="2" t="inlineStr"/>
+      <c r="H753" s="2" t="inlineStr">
+        <is>
+          <t>進行吊掛作業時，吊舉角（兩條吊索之間的夾角）通常建議最大不要超過 60 度。
+💡 為什麼是 60 度？
+隨著吊舉角度變大，吊索所承受的張力（拉力）會劇烈增加：
+當夾角為 0度 時：每根吊索只需承擔物重的一半（50%）。
+當夾角為 60度 時：每根吊索承受的張力會增加到物重的 58%。
+當夾角達到 90度 時：每根吊索承受的張力會飆升到物重的 71%。
+當夾角達到 120度 時：每根吊索承受的張力將等於物重的 100%，極易發生斷裂危險。
+因此，為了確保作業安全與吊具壽命，吊舉角應儘量保持在 60 度以內。</t>
+        </is>
+      </c>
       <c r="I753" s="2" t="inlineStr"/>
     </row>
     <row r="754" ht="92.59999999999999" customHeight="1">
@@ -36335,7 +36365,17 @@
       <c r="G808" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H808" s="2" t="inlineStr"/>
+      <c r="H808" s="2" t="inlineStr">
+        <is>
+          <t>機械設備安全防護之主要目的為避免機械動力與人體接觸所造成之傷害。
+選項分析如下：
+增加機械設備之美觀：非安全防護的目的。
+避免機械動力與人體接觸所造成之傷害：正確，安全防護的核心價值在於保護人員、預防職業災害。
+方便操作：屬於人機工程學或設計便利性考量。
+易於維護保養：屬於設備維修設計考量。
+高雄市政府全球資訊網</t>
+        </is>
+      </c>
       <c r="I808" s="2" t="inlineStr"/>
     </row>
     <row r="809" ht="92.59999999999999" customHeight="1">
@@ -36623,7 +36663,11 @@
       <c r="G815" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H815" s="2" t="inlineStr"/>
+      <c r="H815" s="2" t="inlineStr">
+        <is>
+          <t>在衝床作業時，以手工具代替人手伸進危險區送取料件，這種安全作業方式屬於遠離危險。</t>
+        </is>
+      </c>
       <c r="I815" s="2" t="inlineStr"/>
     </row>
     <row r="816" ht="92.59999999999999" customHeight="1">
@@ -45835,7 +45879,15 @@
       <c r="G1013" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H1013" s="2" t="inlineStr"/>
+      <c r="H1013" s="2" t="inlineStr">
+        <is>
+          <t>保護頭部以避免受到物體飛落或撞擊傷害，應佩戴安全帽（正確答案為 B）。
+答案解析
+安全帽：符合職業安全衛生法規與標準防護具要求，專門用於預防建築工地、礦場或工廠等場所中落物擊傷、碰撞或感電等危害。
+膠盔、便帽、工作帽：無法提供足夠的抗衝擊與緩衝保護，不具備法規認可的頭部防護功能。
+儀分實驗室</t>
+        </is>
+      </c>
       <c r="I1013" s="2" t="inlineStr"/>
     </row>
     <row r="1014" ht="92.59999999999999" customHeight="1">
@@ -48256,7 +48308,71 @@
       <c r="G1067" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H1067" s="2" t="inlineStr"/>
+      <c r="H1067" s="2" t="inlineStr">
+        <is>
+          <t>是的，1 ppm 相當於每 1 立方公尺（
+m
+3
+𝐦
+𝟑
+）空氣中所含有害氣體 1 立方公分（
+cm
+3
+𝐜
+𝐦
+𝟑
+）的體積數（即
+𝟏
+𝐩
+𝐩
+𝐦
+=
+𝟏
+𝐜
+𝐦
+𝟑
+/
+𝐦
+𝟑
+）。
+知乎专栏
+核心概念解析
+定義：ppm（Parts per million）代表百萬分率。在氣體體積濃度中，表示一百萬體積的空氣中所含污染物的體積數。
+桃園市政府衛生局 換算：
+1
+m
+3
+=
+1
+,
+0
+0
+0
+,
+0
+0
+0
+c
+m
+3
+（100萬立方公分）
+因此，當空氣中含有 1 立方公分的有害氣體，混在 1 立方公尺的空氣中，比例就是
+1
+/
+1
+,
+0
+0
+0
+,
+0
+0
+0
+，也就是 1 ppm。
+所以選項中的 1 是正確答案。
+知乎专栏</t>
+        </is>
+      </c>
       <c r="I1067" s="2" t="inlineStr"/>
     </row>
     <row r="1068" ht="77.15000000000001" customHeight="1">
@@ -58025,7 +58141,12 @@
       <c r="G1285" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H1285" s="2" t="inlineStr"/>
+      <c r="H1285" s="2" t="inlineStr">
+        <is>
+          <t>依據《職業安全衛生設施規則》第238條及第280條規定，雇主對作業中有物體飛落或飛散，致危害勞工之虞時，應置備並使勞工確實使用安全帽等必要之防護具。
+正確答案為：安全帽。</t>
+        </is>
+      </c>
       <c r="I1285" s="2" t="inlineStr"/>
     </row>
     <row r="1286" ht="92.59999999999999" customHeight="1">
@@ -58349,7 +58470,23 @@
       <c r="G1293" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1293" s="2" t="inlineStr"/>
+      <c r="H1293" s="2" t="inlineStr">
+        <is>
+          <t>這題的答案是 新冠肺炎（或依據某些特定勞安／公安職訓題庫的經典設定，亦可能為 破傷風）。
+若這是勞工安全衛生（職安）或特定考試的檢定題庫，通常這兩者在生物性危害的分類定義如下：
+新冠肺炎 (COVID-19)：由新型冠狀病毒引起，屬於典型的急性呼吸道傳染病，潛伏期短且發病快速。
+破傷風：由破傷風桿菌的外毒素直接破壞神經系統，會引發肌肉痙攣等嚴重的急性神經症狀。
+勞動部職業安全衛生署 為什麼其他選項不是最典型答案？
+瘧疾：屬於慢性或週期性發作的寄生蟲疾病（通常有特定的發冷、發燒週期循環）。
+皮膚症：通常屬於慢性或過敏性的病症（如部分職業性真菌或過敏原引起），非直接定義的急性傳染病。
+國立臺灣海洋大學生命科學院 建議您依據您正在準備的考卷教材或題庫標準答案進行核對。若在近年更新的題庫中（如包含新冠肺炎選項），多數是指 新冠肺炎；若是較早期的傳統職安題庫，則常以 破傷風 作為引起急性症狀的細菌危害代表。
+台灣大學醫學院附設醫院 國立臺灣海洋大學生命科學院
+生物安全會 - 國立臺灣海洋大學生命科學院
+一、生物危害. 生物性危害（Biological hazard 或Biohazard），又稱為「生物危害」，由生物性危害物質所造成的傷害即為生物危害。 生物危害物是指所有會造成健康影響的生物（或其產生不具活性的產物）。這些危害物質包含植物、節肢動物、鼠類和其他...
+顯示全部
+這項資訊僅供參考，如需醫療建議或診斷，請諮詢專業人士。AI 回覆可能有誤。 瞭解詳情</t>
+        </is>
+      </c>
       <c r="I1293" s="2" t="inlineStr"/>
     </row>
     <row r="1294" ht="92.59999999999999" customHeight="1">
@@ -62336,7 +62473,21 @@
       <c r="G1384" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="H1384" s="2" t="inlineStr"/>
+      <c r="H1384" s="2" t="inlineStr">
+        <is>
+          <t>職業災害統計中對於暫時全失能的定義為 (D) 暫時不能恢復工作 1 日以上。
+暫時全失能定義
+核心條件：指罹災人未死亡，亦未永久失能。
+工作影響：不能繼續其正常工作，必須休班離開工作場所。
+損失時間：損失工作時間在 1 日以上（包含星期日、休假日或事業單位停工日）。
+勞動部職業安全衛生署 想了解更多關於失能傷害頻率（FR）或嚴重率（SR）的計算方式嗎？
+失能傷害頻率 (FR) 公式
+失能傷害嚴重率 (SR) 公式
+兩者計算差異解析
+.職業災害統計中對於暫時全失能定義為下列何者？(A)死亡(B ...
+2024年5月29日 — 1.職業災害統計中對於暫時全失能定義為下列何者？(A)死亡(B)部分永久全 失能(C)輕傷害(D)暫時不能恢復工作1 日以上。，包含題目內容、選項、詳解等， ...</t>
+        </is>
+      </c>
       <c r="I1384" s="2" t="inlineStr"/>
     </row>
     <row r="1385" ht="92.59999999999999" customHeight="1">
